--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>الاسم</t>
   </si>
@@ -61,10 +61,25 @@
     <t>شروق احمد نصر الدين علي</t>
   </si>
   <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
     <t>30511272400503</t>
   </si>
   <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
     <t>01063495341</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>1418</t>
+  </si>
+  <si>
+    <t>70.9</t>
   </si>
   <si>
     <t>جيد</t>
@@ -423,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -475,43 +490,87 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
         <v>1418</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>70.90000000000001</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="N2" t="s">
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
         <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -835,381 +835,381 @@
     <t>ابراهيم محمد محمد ذكى</t>
   </si>
   <si>
+    <t>يوسف مصطفي سيد يوسف</t>
+  </si>
+  <si>
+    <t>رانيا سيد صلاح الدين على</t>
+  </si>
+  <si>
+    <t>حازم عباس خليفة عباس</t>
+  </si>
+  <si>
+    <t>رقيه على محمد خلف</t>
+  </si>
+  <si>
+    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
+  </si>
+  <si>
+    <t>ابراهيم محمود محمد عبدالنعيم</t>
+  </si>
+  <si>
+    <t>بهاء الدين محمد ابراهيم على</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>يوسف احمد سمير محمد</t>
+  </si>
+  <si>
+    <t>محمد رجب لطفى كامل</t>
+  </si>
+  <si>
+    <t>احمد طارق محمد محمود</t>
+  </si>
+  <si>
+    <t>عبدالله محمد سيد صادق</t>
+  </si>
+  <si>
+    <t>سهيله عبد القادر احمد عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد توفيق محمد محمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>مريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>شهد حسين محمود صابر</t>
+  </si>
+  <si>
+    <t>محمد سرحان محمد زكى</t>
+  </si>
+  <si>
+    <t>لمياء عبد القادر محمد فتحى</t>
+  </si>
+  <si>
+    <t>أميمة رأفت محمود احمد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>احمد رمضان محمد عبد الحميد</t>
+  </si>
+  <si>
+    <t>كريم محمد عبد الوهاب عيد</t>
+  </si>
+  <si>
+    <t>عمر رضا تونى طلبه</t>
+  </si>
+  <si>
+    <t>عبدالله ناصر أنور عبد المجيد</t>
+  </si>
+  <si>
+    <t>اندرو محروس مختار مهنى</t>
+  </si>
+  <si>
+    <t>فاطمه ناجى عبد السلام حسن</t>
+  </si>
+  <si>
+    <t>ماركو مجدى مكرم فريد</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
     <t>اميره حمدى مصطفى محمد</t>
   </si>
   <si>
-    <t>يوسف مصطفي سيد يوسف</t>
-  </si>
-  <si>
-    <t>رانيا سيد صلاح الدين على</t>
-  </si>
-  <si>
-    <t>حازم عباس خليفة عباس</t>
-  </si>
-  <si>
-    <t>رقيه على محمد خلف</t>
-  </si>
-  <si>
-    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
-  </si>
-  <si>
-    <t>ابراهيم محمود محمد عبدالنعيم</t>
-  </si>
-  <si>
-    <t>بهاء الدين محمد ابراهيم على</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>يوسف احمد سمير محمد</t>
-  </si>
-  <si>
-    <t>محمد رجب لطفى كامل</t>
-  </si>
-  <si>
-    <t>احمد طارق محمد محمود</t>
-  </si>
-  <si>
-    <t>عبدالله محمد سيد صادق</t>
-  </si>
-  <si>
-    <t>سهيله عبد القادر احمد عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد توفيق محمد محمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>مريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>شهد حسين محمود صابر</t>
-  </si>
-  <si>
-    <t>محمد سرحان محمد زكى</t>
-  </si>
-  <si>
-    <t>لمياء عبد القادر محمد فتحى</t>
-  </si>
-  <si>
-    <t>أميمة رأفت محمود احمد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>احمد رمضان محمد عبد الحميد</t>
-  </si>
-  <si>
-    <t>كريم محمد عبد الوهاب عيد</t>
-  </si>
-  <si>
-    <t>عمر رضا تونى طلبه</t>
-  </si>
-  <si>
-    <t>عبدالله ناصر أنور عبد المجيد</t>
-  </si>
-  <si>
-    <t>اندرو محروس مختار مهنى</t>
-  </si>
-  <si>
-    <t>فاطمه ناجى عبد السلام حسن</t>
-  </si>
-  <si>
-    <t>ماركو مجدى مكرم فريد</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -1984,381 +1984,381 @@
     <t>30504142403393</t>
   </si>
   <si>
+    <t>30506282400915</t>
+  </si>
+  <si>
+    <t>30409222403367</t>
+  </si>
+  <si>
+    <t>30507012411733</t>
+  </si>
+  <si>
+    <t>30411102404968</t>
+  </si>
+  <si>
+    <t>30310012403406</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
+  </si>
+  <si>
+    <t>30506082400619</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30503242401413</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
+  </si>
+  <si>
+    <t>30507262401954</t>
+  </si>
+  <si>
+    <t>30405262402457</t>
+  </si>
+  <si>
+    <t>30410312400403</t>
+  </si>
+  <si>
+    <t>30506152402932</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30509052401709</t>
+  </si>
+  <si>
+    <t>30408182401521</t>
+  </si>
+  <si>
+    <t>30410232401859</t>
+  </si>
+  <si>
+    <t>30409222402263</t>
+  </si>
+  <si>
+    <t>30308062400144</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30302142401658</t>
+  </si>
+  <si>
+    <t>30506272400259</t>
+  </si>
+  <si>
+    <t>30409012413599</t>
+  </si>
+  <si>
+    <t>30601162402453</t>
+  </si>
+  <si>
+    <t>30310012402973</t>
+  </si>
+  <si>
+    <t>30506170300209</t>
+  </si>
+  <si>
+    <t>30409172401791</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
     <t>30407122401208</t>
   </si>
   <si>
-    <t>30506282400915</t>
-  </si>
-  <si>
-    <t>30409222403367</t>
-  </si>
-  <si>
-    <t>30507012411733</t>
-  </si>
-  <si>
-    <t>30411102404968</t>
-  </si>
-  <si>
-    <t>30310012403406</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
-  </si>
-  <si>
-    <t>30506082400619</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30503242401413</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
-  </si>
-  <si>
-    <t>30507262401954</t>
-  </si>
-  <si>
-    <t>30405262402457</t>
-  </si>
-  <si>
-    <t>30410312400403</t>
-  </si>
-  <si>
-    <t>30506152402932</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30509052401709</t>
-  </si>
-  <si>
-    <t>30408182401521</t>
-  </si>
-  <si>
-    <t>30410232401859</t>
-  </si>
-  <si>
-    <t>30409222402263</t>
-  </si>
-  <si>
-    <t>30308062400144</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30302142401658</t>
-  </si>
-  <si>
-    <t>30506272400259</t>
-  </si>
-  <si>
-    <t>30409012413599</t>
-  </si>
-  <si>
-    <t>30601162402453</t>
-  </si>
-  <si>
-    <t>30310012402973</t>
-  </si>
-  <si>
-    <t>30506170300209</t>
-  </si>
-  <si>
-    <t>30409172401791</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3136,376 +3136,376 @@
     <t>01027158830</t>
   </si>
   <si>
+    <t>01156509914</t>
+  </si>
+  <si>
+    <t>01016327718</t>
+  </si>
+  <si>
+    <t>01094773238</t>
+  </si>
+  <si>
+    <t>01127048374</t>
+  </si>
+  <si>
+    <t>01006270603</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0114356079</t>
+  </si>
+  <si>
+    <t>01012467272</t>
+  </si>
+  <si>
+    <t>1010934419</t>
+  </si>
+  <si>
+    <t>01005363873</t>
+  </si>
+  <si>
+    <t>01146971936</t>
+  </si>
+  <si>
+    <t>01143749439</t>
+  </si>
+  <si>
+    <t>01099101872</t>
+  </si>
+  <si>
+    <t>01060726096</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01101609533</t>
+  </si>
+  <si>
+    <t>0111590035</t>
+  </si>
+  <si>
+    <t>01148375746</t>
+  </si>
+  <si>
+    <t>01115291432</t>
+  </si>
+  <si>
+    <t>01121482192</t>
+  </si>
+  <si>
+    <t>1060458756</t>
+  </si>
+  <si>
+    <t>01021408975</t>
+  </si>
+  <si>
+    <t>01068360992</t>
+  </si>
+  <si>
+    <t>01061982978</t>
+  </si>
+  <si>
+    <t>01092079993</t>
+  </si>
+  <si>
+    <t>01288364393</t>
+  </si>
+  <si>
+    <t>01157384981</t>
+  </si>
+  <si>
+    <t>01283970879</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01099393313</t>
+  </si>
+  <si>
+    <t>01093075647</t>
+  </si>
+  <si>
+    <t>01037186555</t>
+  </si>
+  <si>
+    <t>01129169104</t>
+  </si>
+  <si>
+    <t>01001362969</t>
+  </si>
+  <si>
+    <t>01151741232</t>
+  </si>
+  <si>
+    <t>01013305686</t>
+  </si>
+  <si>
+    <t>01150936407</t>
+  </si>
+  <si>
+    <t>01002331784</t>
+  </si>
+  <si>
+    <t>01150905692</t>
+  </si>
+  <si>
+    <t>01028993616</t>
+  </si>
+  <si>
+    <t>01119364560</t>
+  </si>
+  <si>
+    <t>01114623756</t>
+  </si>
+  <si>
+    <t>01110180758</t>
+  </si>
+  <si>
+    <t>01098408936</t>
+  </si>
+  <si>
+    <t>01026439570</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
     <t>01036343803</t>
-  </si>
-  <si>
-    <t>01156509914</t>
-  </si>
-  <si>
-    <t>01016327718</t>
-  </si>
-  <si>
-    <t>01094773238</t>
-  </si>
-  <si>
-    <t>01127048374</t>
-  </si>
-  <si>
-    <t>01006270603</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0114356079</t>
-  </si>
-  <si>
-    <t>01012467272</t>
-  </si>
-  <si>
-    <t>1010934419</t>
-  </si>
-  <si>
-    <t>01005363873</t>
-  </si>
-  <si>
-    <t>01146971936</t>
-  </si>
-  <si>
-    <t>01143749439</t>
-  </si>
-  <si>
-    <t>01099101872</t>
-  </si>
-  <si>
-    <t>01060726096</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01101609533</t>
-  </si>
-  <si>
-    <t>0111590035</t>
-  </si>
-  <si>
-    <t>01148375746</t>
-  </si>
-  <si>
-    <t>01115291432</t>
-  </si>
-  <si>
-    <t>01121482192</t>
-  </si>
-  <si>
-    <t>1060458756</t>
-  </si>
-  <si>
-    <t>01021408975</t>
-  </si>
-  <si>
-    <t>01068360992</t>
-  </si>
-  <si>
-    <t>01061982978</t>
-  </si>
-  <si>
-    <t>01092079993</t>
-  </si>
-  <si>
-    <t>01288364393</t>
-  </si>
-  <si>
-    <t>01157384981</t>
-  </si>
-  <si>
-    <t>01283970879</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01099393313</t>
-  </si>
-  <si>
-    <t>01093075647</t>
-  </si>
-  <si>
-    <t>01037186555</t>
-  </si>
-  <si>
-    <t>01129169104</t>
-  </si>
-  <si>
-    <t>01001362969</t>
-  </si>
-  <si>
-    <t>01151741232</t>
-  </si>
-  <si>
-    <t>01013305686</t>
-  </si>
-  <si>
-    <t>01150936407</t>
-  </si>
-  <si>
-    <t>01002331784</t>
-  </si>
-  <si>
-    <t>01150905692</t>
-  </si>
-  <si>
-    <t>01028993616</t>
-  </si>
-  <si>
-    <t>01119364560</t>
-  </si>
-  <si>
-    <t>01114623756</t>
-  </si>
-  <si>
-    <t>01110180758</t>
-  </si>
-  <si>
-    <t>01098408936</t>
-  </si>
-  <si>
-    <t>01026439570</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01159358898</t>
   </si>
   <si>
     <t>1353</t>
@@ -16443,34 +16443,34 @@
         <v>1040</v>
       </c>
       <c r="D261" t="s">
-        <v>1285</v>
+        <v>1315</v>
       </c>
       <c r="E261" t="s">
-        <v>1470</v>
+        <v>1500</v>
       </c>
       <c r="F261" t="s">
         <v>1534</v>
       </c>
       <c r="G261" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H261" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I261" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="J261" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="K261" t="s">
         <v>1545</v>
       </c>
       <c r="L261" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M261" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N261" t="s">
         <v>1547</v>
@@ -16487,10 +16487,10 @@
         <v>1041</v>
       </c>
       <c r="D262" t="s">
-        <v>1315</v>
+        <v>1263</v>
       </c>
       <c r="E262" t="s">
-        <v>1500</v>
+        <v>1448</v>
       </c>
       <c r="F262" t="s">
         <v>1534</v>
@@ -16502,19 +16502,19 @@
         <v>1543</v>
       </c>
       <c r="I262" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="J262" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K262" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L262" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M262" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="N262" t="s">
         <v>1547</v>
@@ -16531,10 +16531,10 @@
         <v>1042</v>
       </c>
       <c r="D263" t="s">
-        <v>1263</v>
+        <v>1316</v>
       </c>
       <c r="E263" t="s">
-        <v>1448</v>
+        <v>1501</v>
       </c>
       <c r="F263" t="s">
         <v>1534</v>
@@ -16543,13 +16543,13 @@
         <v>1540</v>
       </c>
       <c r="H263" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I263" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J263" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="K263" t="s">
         <v>1544</v>
@@ -16558,7 +16558,7 @@
         <v>1545</v>
       </c>
       <c r="M263" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N263" t="s">
         <v>1547</v>
@@ -16575,13 +16575,13 @@
         <v>1043</v>
       </c>
       <c r="D264" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="E264" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="F264" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G264" t="s">
         <v>1540</v>
@@ -16593,16 +16593,16 @@
         <v>1543</v>
       </c>
       <c r="J264" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="K264" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L264" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M264" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N264" t="s">
         <v>1547</v>
@@ -16619,19 +16619,19 @@
         <v>1044</v>
       </c>
       <c r="D265" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E265" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F265" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="G265" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H265" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="I265" t="s">
         <v>1543</v>
@@ -16643,7 +16643,7 @@
         <v>1541</v>
       </c>
       <c r="L265" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M265" t="s">
         <v>1545</v>
@@ -16663,31 +16663,31 @@
         <v>1045</v>
       </c>
       <c r="D266" t="s">
-        <v>1318</v>
+        <v>1247</v>
       </c>
       <c r="E266" t="s">
-        <v>1503</v>
+        <v>1432</v>
       </c>
       <c r="F266" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="G266" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H266" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="I266" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="J266" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K266" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="L266" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="M266" t="s">
         <v>1545</v>
@@ -16707,28 +16707,28 @@
         <v>1046</v>
       </c>
       <c r="D267" t="s">
-        <v>1247</v>
+        <v>1314</v>
       </c>
       <c r="E267" t="s">
-        <v>1432</v>
+        <v>1499</v>
       </c>
       <c r="F267" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G267" t="s">
         <v>1540</v>
       </c>
       <c r="H267" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I267" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="J267" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K267" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="L267" t="s">
         <v>1544</v>
@@ -16751,34 +16751,34 @@
         <v>1047</v>
       </c>
       <c r="D268" t="s">
-        <v>1314</v>
+        <v>1231</v>
       </c>
       <c r="E268" t="s">
-        <v>1499</v>
+        <v>1416</v>
       </c>
       <c r="F268" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G268" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H268" t="s">
         <v>1543</v>
       </c>
       <c r="I268" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="J268" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K268" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L268" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M268" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N268" t="s">
         <v>1547</v>
@@ -16795,25 +16795,25 @@
         <v>1048</v>
       </c>
       <c r="D269" t="s">
-        <v>1231</v>
+        <v>1250</v>
       </c>
       <c r="E269" t="s">
-        <v>1416</v>
+        <v>1435</v>
       </c>
       <c r="F269" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G269" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H269" t="s">
         <v>1543</v>
       </c>
       <c r="I269" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="J269" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="K269" t="s">
         <v>1544</v>
@@ -16822,7 +16822,7 @@
         <v>1545</v>
       </c>
       <c r="M269" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N269" t="s">
         <v>1547</v>
@@ -16839,34 +16839,34 @@
         <v>1049</v>
       </c>
       <c r="D270" t="s">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="E270" t="s">
-        <v>1435</v>
+        <v>1410</v>
       </c>
       <c r="F270" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G270" t="s">
         <v>1540</v>
       </c>
       <c r="H270" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I270" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J270" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K270" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="L270" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="M270" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N270" t="s">
         <v>1547</v>
@@ -16883,10 +16883,10 @@
         <v>1050</v>
       </c>
       <c r="D271" t="s">
-        <v>1225</v>
+        <v>1179</v>
       </c>
       <c r="E271" t="s">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F271" t="s">
         <v>1534</v>
@@ -16898,19 +16898,19 @@
         <v>1541</v>
       </c>
       <c r="I271" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J271" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="K271" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="L271" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="M271" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N271" t="s">
         <v>1547</v>
@@ -16927,10 +16927,10 @@
         <v>1051</v>
       </c>
       <c r="D272" t="s">
-        <v>1179</v>
+        <v>1226</v>
       </c>
       <c r="E272" t="s">
-        <v>1364</v>
+        <v>1411</v>
       </c>
       <c r="F272" t="s">
         <v>1534</v>
@@ -16942,19 +16942,19 @@
         <v>1541</v>
       </c>
       <c r="I272" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="J272" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K272" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="L272" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="M272" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N272" t="s">
         <v>1547</v>
@@ -16971,22 +16971,22 @@
         <v>1052</v>
       </c>
       <c r="D273" t="s">
-        <v>1226</v>
+        <v>1295</v>
       </c>
       <c r="E273" t="s">
-        <v>1411</v>
+        <v>1480</v>
       </c>
       <c r="F273" t="s">
         <v>1534</v>
       </c>
       <c r="G273" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H273" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="I273" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J273" t="s">
         <v>1546</v>
@@ -16995,7 +16995,7 @@
         <v>1542</v>
       </c>
       <c r="L273" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="M273" t="s">
         <v>1545</v>
@@ -17012,37 +17012,37 @@
         <v>669</v>
       </c>
       <c r="C274" t="s">
-        <v>1053</v>
+        <v>814</v>
       </c>
       <c r="D274" t="s">
-        <v>1295</v>
+        <v>1319</v>
       </c>
       <c r="E274" t="s">
-        <v>1480</v>
+        <v>1504</v>
       </c>
       <c r="F274" t="s">
         <v>1534</v>
       </c>
       <c r="G274" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H274" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I274" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J274" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="K274" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="L274" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M274" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N274" t="s">
         <v>1547</v>
@@ -17056,13 +17056,13 @@
         <v>670</v>
       </c>
       <c r="C275" t="s">
-        <v>814</v>
+        <v>1053</v>
       </c>
       <c r="D275" t="s">
-        <v>1319</v>
+        <v>1285</v>
       </c>
       <c r="E275" t="s">
-        <v>1504</v>
+        <v>1470</v>
       </c>
       <c r="F275" t="s">
         <v>1534</v>
@@ -17071,22 +17071,22 @@
         <v>1540</v>
       </c>
       <c r="H275" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I275" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J275" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="K275" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="L275" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M275" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N275" t="s">
         <v>1547</v>
@@ -17103,34 +17103,34 @@
         <v>1054</v>
       </c>
       <c r="D276" t="s">
-        <v>1285</v>
+        <v>1256</v>
       </c>
       <c r="E276" t="s">
-        <v>1470</v>
+        <v>1441</v>
       </c>
       <c r="F276" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G276" t="s">
         <v>1540</v>
       </c>
       <c r="H276" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I276" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J276" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="K276" t="s">
         <v>1542</v>
       </c>
       <c r="L276" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="M276" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="N276" t="s">
         <v>1547</v>
@@ -17147,13 +17147,13 @@
         <v>1055</v>
       </c>
       <c r="D277" t="s">
-        <v>1256</v>
+        <v>1287</v>
       </c>
       <c r="E277" t="s">
-        <v>1441</v>
+        <v>1472</v>
       </c>
       <c r="F277" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G277" t="s">
         <v>1540</v>
@@ -17165,7 +17165,7 @@
         <v>1546</v>
       </c>
       <c r="J277" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="K277" t="s">
         <v>1542</v>
@@ -17174,7 +17174,7 @@
         <v>1541</v>
       </c>
       <c r="M277" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="N277" t="s">
         <v>1547</v>
@@ -17191,10 +17191,10 @@
         <v>1056</v>
       </c>
       <c r="D278" t="s">
-        <v>1287</v>
+        <v>1191</v>
       </c>
       <c r="E278" t="s">
-        <v>1472</v>
+        <v>1376</v>
       </c>
       <c r="F278" t="s">
         <v>1534</v>
@@ -17209,13 +17209,13 @@
         <v>1546</v>
       </c>
       <c r="J278" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="K278" t="s">
         <v>1542</v>
       </c>
       <c r="L278" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="M278" t="s">
         <v>1545</v>
@@ -17235,10 +17235,10 @@
         <v>1057</v>
       </c>
       <c r="D279" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="E279" t="s">
-        <v>1376</v>
+        <v>1383</v>
       </c>
       <c r="F279" t="s">
         <v>1534</v>
@@ -17253,16 +17253,16 @@
         <v>1546</v>
       </c>
       <c r="J279" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K279" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L279" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="M279" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N279" t="s">
         <v>1547</v>
@@ -17279,13 +17279,13 @@
         <v>1058</v>
       </c>
       <c r="D280" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E280" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="F280" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G280" t="s">
         <v>1540</v>
@@ -17294,19 +17294,19 @@
         <v>1543</v>
       </c>
       <c r="I280" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J280" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K280" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="L280" t="s">
         <v>1541</v>
       </c>
       <c r="M280" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N280" t="s">
         <v>1547</v>
@@ -17323,10 +17323,10 @@
         <v>1059</v>
       </c>
       <c r="D281" t="s">
-        <v>1197</v>
+        <v>1176</v>
       </c>
       <c r="E281" t="s">
-        <v>1382</v>
+        <v>1361</v>
       </c>
       <c r="F281" t="s">
         <v>1535</v>
@@ -17335,22 +17335,22 @@
         <v>1540</v>
       </c>
       <c r="H281" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I281" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J281" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="K281" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="L281" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M281" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N281" t="s">
         <v>1547</v>
@@ -17367,25 +17367,25 @@
         <v>1060</v>
       </c>
       <c r="D282" t="s">
-        <v>1176</v>
+        <v>1320</v>
       </c>
       <c r="E282" t="s">
-        <v>1361</v>
+        <v>1505</v>
       </c>
       <c r="F282" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G282" t="s">
         <v>1540</v>
       </c>
       <c r="H282" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I282" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J282" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K282" t="s">
         <v>1541</v>
@@ -17394,7 +17394,7 @@
         <v>1545</v>
       </c>
       <c r="M282" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N282" t="s">
         <v>1547</v>
@@ -17411,34 +17411,34 @@
         <v>1061</v>
       </c>
       <c r="D283" t="s">
-        <v>1320</v>
+        <v>1164</v>
       </c>
       <c r="E283" t="s">
-        <v>1505</v>
+        <v>1349</v>
       </c>
       <c r="F283" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G283" t="s">
         <v>1540</v>
       </c>
       <c r="H283" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="I283" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J283" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="K283" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L283" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M283" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="N283" t="s">
         <v>1547</v>
@@ -17455,34 +17455,34 @@
         <v>1062</v>
       </c>
       <c r="D284" t="s">
-        <v>1164</v>
+        <v>1263</v>
       </c>
       <c r="E284" t="s">
-        <v>1349</v>
+        <v>1448</v>
       </c>
       <c r="F284" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G284" t="s">
         <v>1540</v>
       </c>
       <c r="H284" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I284" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J284" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="K284" t="s">
         <v>1544</v>
       </c>
       <c r="L284" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="M284" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N284" t="s">
         <v>1547</v>
@@ -17499,22 +17499,22 @@
         <v>1063</v>
       </c>
       <c r="D285" t="s">
-        <v>1263</v>
+        <v>1241</v>
       </c>
       <c r="E285" t="s">
-        <v>1448</v>
+        <v>1426</v>
       </c>
       <c r="F285" t="s">
         <v>1534</v>
       </c>
       <c r="G285" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="H285" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I285" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="J285" t="s">
         <v>1543</v>
@@ -17523,10 +17523,10 @@
         <v>1544</v>
       </c>
       <c r="L285" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="M285" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N285" t="s">
         <v>1547</v>
@@ -17543,34 +17543,34 @@
         <v>1064</v>
       </c>
       <c r="D286" t="s">
-        <v>1241</v>
+        <v>1213</v>
       </c>
       <c r="E286" t="s">
-        <v>1426</v>
+        <v>1398</v>
       </c>
       <c r="F286" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G286" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="H286" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="I286" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="J286" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K286" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="L286" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="M286" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N286" t="s">
         <v>1547</v>
@@ -17587,13 +17587,13 @@
         <v>1065</v>
       </c>
       <c r="D287" t="s">
-        <v>1213</v>
+        <v>1170</v>
       </c>
       <c r="E287" t="s">
-        <v>1398</v>
+        <v>1355</v>
       </c>
       <c r="F287" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G287" t="s">
         <v>1540</v>
@@ -17602,19 +17602,19 @@
         <v>1546</v>
       </c>
       <c r="I287" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J287" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K287" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="L287" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="M287" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N287" t="s">
         <v>1547</v>
@@ -17631,34 +17631,34 @@
         <v>1066</v>
       </c>
       <c r="D288" t="s">
-        <v>1170</v>
+        <v>1321</v>
       </c>
       <c r="E288" t="s">
-        <v>1355</v>
+        <v>1506</v>
       </c>
       <c r="F288" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G288" t="s">
         <v>1540</v>
       </c>
       <c r="H288" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I288" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J288" t="s">
         <v>1541</v>
       </c>
       <c r="K288" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L288" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M288" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N288" t="s">
         <v>1547</v>
@@ -17675,22 +17675,22 @@
         <v>1067</v>
       </c>
       <c r="D289" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E289" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="F289" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G289" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H289" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I289" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="J289" t="s">
         <v>1541</v>
@@ -17699,10 +17699,10 @@
         <v>1544</v>
       </c>
       <c r="L289" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M289" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N289" t="s">
         <v>1547</v>
@@ -17719,28 +17719,28 @@
         <v>1068</v>
       </c>
       <c r="D290" t="s">
-        <v>1322</v>
+        <v>1241</v>
       </c>
       <c r="E290" t="s">
-        <v>1507</v>
+        <v>1426</v>
       </c>
       <c r="F290" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G290" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="H290" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I290" t="s">
         <v>1546</v>
       </c>
       <c r="J290" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K290" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L290" t="s">
         <v>1545</v>
@@ -17763,13 +17763,13 @@
         <v>1069</v>
       </c>
       <c r="D291" t="s">
-        <v>1241</v>
+        <v>1314</v>
       </c>
       <c r="E291" t="s">
-        <v>1426</v>
+        <v>1499</v>
       </c>
       <c r="F291" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G291" t="s">
         <v>1540</v>
@@ -17784,13 +17784,13 @@
         <v>1544</v>
       </c>
       <c r="K291" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="L291" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M291" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N291" t="s">
         <v>1547</v>
@@ -17807,10 +17807,10 @@
         <v>1070</v>
       </c>
       <c r="D292" t="s">
-        <v>1314</v>
+        <v>1259</v>
       </c>
       <c r="E292" t="s">
-        <v>1499</v>
+        <v>1444</v>
       </c>
       <c r="F292" t="s">
         <v>1535</v>
@@ -17819,22 +17819,22 @@
         <v>1540</v>
       </c>
       <c r="H292" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I292" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J292" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="K292" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="L292" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M292" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="N292" t="s">
         <v>1547</v>
@@ -17851,10 +17851,10 @@
         <v>1071</v>
       </c>
       <c r="D293" t="s">
-        <v>1259</v>
+        <v>1323</v>
       </c>
       <c r="E293" t="s">
-        <v>1444</v>
+        <v>1508</v>
       </c>
       <c r="F293" t="s">
         <v>1535</v>
@@ -17863,22 +17863,22 @@
         <v>1540</v>
       </c>
       <c r="H293" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="I293" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J293" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="K293" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="L293" t="s">
         <v>1544</v>
       </c>
       <c r="M293" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N293" t="s">
         <v>1547</v>
@@ -17895,25 +17895,25 @@
         <v>1072</v>
       </c>
       <c r="D294" t="s">
-        <v>1323</v>
+        <v>1196</v>
       </c>
       <c r="E294" t="s">
-        <v>1508</v>
+        <v>1381</v>
       </c>
       <c r="F294" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="G294" t="s">
         <v>1540</v>
       </c>
       <c r="H294" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I294" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="J294" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="K294" t="s">
         <v>1545</v>
@@ -17922,7 +17922,7 @@
         <v>1544</v>
       </c>
       <c r="M294" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="N294" t="s">
         <v>1547</v>
@@ -17939,13 +17939,13 @@
         <v>1073</v>
       </c>
       <c r="D295" t="s">
-        <v>1196</v>
+        <v>1269</v>
       </c>
       <c r="E295" t="s">
-        <v>1381</v>
+        <v>1454</v>
       </c>
       <c r="F295" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="G295" t="s">
         <v>1540</v>
@@ -17983,19 +17983,19 @@
         <v>1074</v>
       </c>
       <c r="D296" t="s">
-        <v>1269</v>
+        <v>1164</v>
       </c>
       <c r="E296" t="s">
-        <v>1454</v>
+        <v>1349</v>
       </c>
       <c r="F296" t="s">
         <v>1534</v>
       </c>
       <c r="G296" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H296" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I296" t="s">
         <v>1546</v>
@@ -18004,13 +18004,13 @@
         <v>1541</v>
       </c>
       <c r="K296" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="L296" t="s">
         <v>1544</v>
       </c>
       <c r="M296" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N296" t="s">
         <v>1547</v>
@@ -18027,34 +18027,34 @@
         <v>1075</v>
       </c>
       <c r="D297" t="s">
-        <v>1164</v>
+        <v>1179</v>
       </c>
       <c r="E297" t="s">
-        <v>1349</v>
+        <v>1364</v>
       </c>
       <c r="F297" t="s">
         <v>1534</v>
       </c>
       <c r="G297" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H297" t="s">
         <v>1540</v>
       </c>
       <c r="I297" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="J297" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K297" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="L297" t="s">
         <v>1544</v>
       </c>
       <c r="M297" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N297" t="s">
         <v>1547</v>
@@ -18071,34 +18071,34 @@
         <v>1076</v>
       </c>
       <c r="D298" t="s">
-        <v>1179</v>
+        <v>1198</v>
       </c>
       <c r="E298" t="s">
-        <v>1364</v>
+        <v>1383</v>
       </c>
       <c r="F298" t="s">
         <v>1534</v>
       </c>
       <c r="G298" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H298" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="I298" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J298" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K298" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="L298" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M298" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N298" t="s">
         <v>1547</v>
@@ -18115,34 +18115,34 @@
         <v>1077</v>
       </c>
       <c r="D299" t="s">
-        <v>1198</v>
+        <v>1324</v>
       </c>
       <c r="E299" t="s">
-        <v>1383</v>
+        <v>1509</v>
       </c>
       <c r="F299" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G299" t="s">
         <v>1540</v>
       </c>
       <c r="H299" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I299" t="s">
         <v>1543</v>
       </c>
       <c r="J299" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K299" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L299" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M299" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="N299" t="s">
         <v>1547</v>
@@ -18159,31 +18159,31 @@
         <v>1078</v>
       </c>
       <c r="D300" t="s">
-        <v>1324</v>
+        <v>1212</v>
       </c>
       <c r="E300" t="s">
-        <v>1509</v>
+        <v>1397</v>
       </c>
       <c r="F300" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G300" t="s">
         <v>1540</v>
       </c>
       <c r="H300" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I300" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="J300" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K300" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L300" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M300" t="s">
         <v>1542</v>
@@ -18203,34 +18203,34 @@
         <v>1079</v>
       </c>
       <c r="D301" t="s">
-        <v>1212</v>
+        <v>1241</v>
       </c>
       <c r="E301" t="s">
-        <v>1397</v>
+        <v>1426</v>
       </c>
       <c r="F301" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G301" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="H301" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I301" t="s">
         <v>1545</v>
       </c>
       <c r="J301" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="K301" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="L301" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="M301" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N301" t="s">
         <v>1547</v>
@@ -18247,34 +18247,34 @@
         <v>1080</v>
       </c>
       <c r="D302" t="s">
-        <v>1241</v>
+        <v>1176</v>
       </c>
       <c r="E302" t="s">
-        <v>1426</v>
+        <v>1361</v>
       </c>
       <c r="F302" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G302" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="H302" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I302" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J302" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K302" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="L302" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M302" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="N302" t="s">
         <v>1547</v>
@@ -18291,10 +18291,10 @@
         <v>1081</v>
       </c>
       <c r="D303" t="s">
-        <v>1176</v>
+        <v>1282</v>
       </c>
       <c r="E303" t="s">
-        <v>1361</v>
+        <v>1467</v>
       </c>
       <c r="F303" t="s">
         <v>1534</v>
@@ -18312,13 +18312,13 @@
         <v>1541</v>
       </c>
       <c r="K303" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L303" t="s">
         <v>1544</v>
       </c>
       <c r="M303" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N303" t="s">
         <v>1547</v>
@@ -18335,10 +18335,10 @@
         <v>1082</v>
       </c>
       <c r="D304" t="s">
-        <v>1282</v>
+        <v>1325</v>
       </c>
       <c r="E304" t="s">
-        <v>1467</v>
+        <v>1510</v>
       </c>
       <c r="F304" t="s">
         <v>1534</v>
@@ -18347,19 +18347,19 @@
         <v>1540</v>
       </c>
       <c r="H304" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I304" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J304" t="s">
         <v>1541</v>
       </c>
       <c r="K304" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L304" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M304" t="s">
         <v>1542</v>
@@ -18379,13 +18379,13 @@
         <v>1083</v>
       </c>
       <c r="D305" t="s">
-        <v>1325</v>
+        <v>1181</v>
       </c>
       <c r="E305" t="s">
-        <v>1510</v>
+        <v>1366</v>
       </c>
       <c r="F305" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G305" t="s">
         <v>1540</v>
@@ -18397,16 +18397,16 @@
         <v>1546</v>
       </c>
       <c r="J305" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K305" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L305" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M305" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N305" t="s">
         <v>1547</v>
@@ -18423,13 +18423,13 @@
         <v>1084</v>
       </c>
       <c r="D306" t="s">
-        <v>1181</v>
+        <v>1317</v>
       </c>
       <c r="E306" t="s">
-        <v>1366</v>
+        <v>1502</v>
       </c>
       <c r="F306" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G306" t="s">
         <v>1540</v>
@@ -18438,16 +18438,16 @@
         <v>1543</v>
       </c>
       <c r="I306" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="J306" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K306" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L306" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M306" t="s">
         <v>1545</v>
@@ -18467,13 +18467,13 @@
         <v>1085</v>
       </c>
       <c r="D307" t="s">
-        <v>1317</v>
+        <v>1187</v>
       </c>
       <c r="E307" t="s">
-        <v>1502</v>
+        <v>1372</v>
       </c>
       <c r="F307" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G307" t="s">
         <v>1540</v>
@@ -18482,19 +18482,19 @@
         <v>1543</v>
       </c>
       <c r="I307" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="J307" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="K307" t="s">
         <v>1544</v>
       </c>
       <c r="L307" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="M307" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N307" t="s">
         <v>1547</v>
@@ -18511,34 +18511,34 @@
         <v>1086</v>
       </c>
       <c r="D308" t="s">
-        <v>1187</v>
+        <v>1276</v>
       </c>
       <c r="E308" t="s">
-        <v>1372</v>
+        <v>1461</v>
       </c>
       <c r="F308" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G308" t="s">
         <v>1540</v>
       </c>
       <c r="H308" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I308" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="J308" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="K308" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="L308" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M308" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N308" t="s">
         <v>1547</v>
@@ -18555,10 +18555,10 @@
         <v>1087</v>
       </c>
       <c r="D309" t="s">
-        <v>1276</v>
+        <v>1306</v>
       </c>
       <c r="E309" t="s">
-        <v>1461</v>
+        <v>1491</v>
       </c>
       <c r="F309" t="s">
         <v>1535</v>
@@ -18567,7 +18567,7 @@
         <v>1540</v>
       </c>
       <c r="H309" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I309" t="s">
         <v>1542</v>
@@ -18576,7 +18576,7 @@
         <v>1546</v>
       </c>
       <c r="K309" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="L309" t="s">
         <v>1545</v>
@@ -18599,13 +18599,13 @@
         <v>1088</v>
       </c>
       <c r="D310" t="s">
-        <v>1306</v>
+        <v>1322</v>
       </c>
       <c r="E310" t="s">
-        <v>1491</v>
+        <v>1507</v>
       </c>
       <c r="F310" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G310" t="s">
         <v>1540</v>
@@ -18643,34 +18643,34 @@
         <v>1089</v>
       </c>
       <c r="D311" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="E311" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="F311" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G311" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H311" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="I311" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="J311" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="K311" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="L311" t="s">
         <v>1545</v>
       </c>
       <c r="M311" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="N311" t="s">
         <v>1547</v>
@@ -18687,34 +18687,34 @@
         <v>1090</v>
       </c>
       <c r="D312" t="s">
-        <v>1326</v>
+        <v>1196</v>
       </c>
       <c r="E312" t="s">
-        <v>1511</v>
+        <v>1381</v>
       </c>
       <c r="F312" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="G312" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H312" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I312" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="J312" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K312" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="L312" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M312" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="N312" t="s">
         <v>1547</v>
@@ -18731,31 +18731,31 @@
         <v>1091</v>
       </c>
       <c r="D313" t="s">
-        <v>1196</v>
+        <v>1251</v>
       </c>
       <c r="E313" t="s">
-        <v>1381</v>
+        <v>1436</v>
       </c>
       <c r="F313" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G313" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H313" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I313" t="s">
         <v>1546</v>
       </c>
       <c r="J313" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K313" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="L313" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M313" t="s">
         <v>1542</v>
@@ -18775,28 +18775,28 @@
         <v>1092</v>
       </c>
       <c r="D314" t="s">
-        <v>1251</v>
+        <v>1270</v>
       </c>
       <c r="E314" t="s">
-        <v>1436</v>
+        <v>1455</v>
       </c>
       <c r="F314" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G314" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H314" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="I314" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J314" t="s">
         <v>1544</v>
       </c>
       <c r="K314" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="L314" t="s">
         <v>1545</v>
@@ -18819,34 +18819,34 @@
         <v>1093</v>
       </c>
       <c r="D315" t="s">
-        <v>1270</v>
+        <v>1282</v>
       </c>
       <c r="E315" t="s">
-        <v>1455</v>
+        <v>1467</v>
       </c>
       <c r="F315" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G315" t="s">
         <v>1540</v>
       </c>
       <c r="H315" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I315" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J315" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K315" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="L315" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M315" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N315" t="s">
         <v>1547</v>
@@ -18863,13 +18863,13 @@
         <v>1094</v>
       </c>
       <c r="D316" t="s">
-        <v>1282</v>
+        <v>1303</v>
       </c>
       <c r="E316" t="s">
-        <v>1467</v>
+        <v>1488</v>
       </c>
       <c r="F316" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G316" t="s">
         <v>1540</v>
@@ -18878,19 +18878,19 @@
         <v>1546</v>
       </c>
       <c r="I316" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="J316" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="K316" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L316" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M316" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N316" t="s">
         <v>1547</v>
@@ -18907,10 +18907,10 @@
         <v>1095</v>
       </c>
       <c r="D317" t="s">
-        <v>1303</v>
+        <v>1214</v>
       </c>
       <c r="E317" t="s">
-        <v>1488</v>
+        <v>1399</v>
       </c>
       <c r="F317" t="s">
         <v>1535</v>
@@ -18922,19 +18922,19 @@
         <v>1546</v>
       </c>
       <c r="I317" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J317" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K317" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L317" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M317" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N317" t="s">
         <v>1547</v>
@@ -18951,13 +18951,13 @@
         <v>1096</v>
       </c>
       <c r="D318" t="s">
-        <v>1214</v>
+        <v>1230</v>
       </c>
       <c r="E318" t="s">
-        <v>1399</v>
+        <v>1415</v>
       </c>
       <c r="F318" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G318" t="s">
         <v>1540</v>
@@ -18966,10 +18966,10 @@
         <v>1546</v>
       </c>
       <c r="I318" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="J318" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K318" t="s">
         <v>1545</v>
@@ -18995,10 +18995,10 @@
         <v>1097</v>
       </c>
       <c r="D319" t="s">
-        <v>1230</v>
+        <v>1327</v>
       </c>
       <c r="E319" t="s">
-        <v>1415</v>
+        <v>1512</v>
       </c>
       <c r="F319" t="s">
         <v>1534</v>
@@ -19007,22 +19007,22 @@
         <v>1540</v>
       </c>
       <c r="H319" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I319" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J319" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K319" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L319" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M319" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="N319" t="s">
         <v>1547</v>
@@ -19039,34 +19039,34 @@
         <v>1098</v>
       </c>
       <c r="D320" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E320" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="F320" t="s">
         <v>1534</v>
       </c>
       <c r="G320" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H320" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I320" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="J320" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K320" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L320" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M320" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="N320" t="s">
         <v>1547</v>
@@ -19083,10 +19083,10 @@
         <v>1099</v>
       </c>
       <c r="D321" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="E321" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F321" t="s">
         <v>1534</v>
@@ -19127,34 +19127,34 @@
         <v>1100</v>
       </c>
       <c r="D322" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="E322" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F322" t="s">
         <v>1534</v>
       </c>
       <c r="G322" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H322" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I322" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="J322" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="K322" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L322" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M322" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="N322" t="s">
         <v>1547</v>
@@ -19171,34 +19171,34 @@
         <v>1101</v>
       </c>
       <c r="D323" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E323" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F323" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="G323" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H323" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I323" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J323" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K323" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L323" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M323" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N323" t="s">
         <v>1547</v>
@@ -19215,34 +19215,34 @@
         <v>1102</v>
       </c>
       <c r="D324" t="s">
-        <v>1331</v>
+        <v>1300</v>
       </c>
       <c r="E324" t="s">
-        <v>1516</v>
+        <v>1485</v>
       </c>
       <c r="F324" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="G324" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H324" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I324" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J324" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K324" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L324" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M324" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N324" t="s">
         <v>1547</v>
@@ -19259,13 +19259,13 @@
         <v>1103</v>
       </c>
       <c r="D325" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="E325" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="F325" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G325" t="s">
         <v>1540</v>
@@ -19280,13 +19280,13 @@
         <v>1542</v>
       </c>
       <c r="K325" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L325" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M325" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N325" t="s">
         <v>1547</v>
@@ -19303,10 +19303,10 @@
         <v>1104</v>
       </c>
       <c r="D326" t="s">
-        <v>1306</v>
+        <v>1332</v>
       </c>
       <c r="E326" t="s">
-        <v>1491</v>
+        <v>1517</v>
       </c>
       <c r="F326" t="s">
         <v>1534</v>
@@ -19321,16 +19321,16 @@
         <v>1546</v>
       </c>
       <c r="J326" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K326" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L326" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M326" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N326" t="s">
         <v>1547</v>
@@ -19347,31 +19347,31 @@
         <v>1105</v>
       </c>
       <c r="D327" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="E327" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="F327" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G327" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H327" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I327" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="J327" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="K327" t="s">
         <v>1544</v>
       </c>
       <c r="L327" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M327" t="s">
         <v>1542</v>
@@ -19391,34 +19391,34 @@
         <v>1106</v>
       </c>
       <c r="D328" t="s">
-        <v>1333</v>
+        <v>1299</v>
       </c>
       <c r="E328" t="s">
-        <v>1518</v>
+        <v>1484</v>
       </c>
       <c r="F328" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G328" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="H328" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I328" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="J328" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="K328" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L328" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M328" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N328" t="s">
         <v>1547</v>
@@ -19435,34 +19435,34 @@
         <v>1107</v>
       </c>
       <c r="D329" t="s">
-        <v>1299</v>
+        <v>1209</v>
       </c>
       <c r="E329" t="s">
-        <v>1484</v>
+        <v>1394</v>
       </c>
       <c r="F329" t="s">
         <v>1535</v>
       </c>
       <c r="G329" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H329" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I329" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="J329" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="K329" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="L329" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M329" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="N329" t="s">
         <v>1547</v>
@@ -19479,34 +19479,34 @@
         <v>1108</v>
       </c>
       <c r="D330" t="s">
-        <v>1209</v>
+        <v>1247</v>
       </c>
       <c r="E330" t="s">
-        <v>1394</v>
+        <v>1432</v>
       </c>
       <c r="F330" t="s">
         <v>1535</v>
       </c>
       <c r="G330" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H330" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I330" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="J330" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K330" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L330" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="M330" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N330" t="s">
         <v>1547</v>
@@ -19523,34 +19523,34 @@
         <v>1109</v>
       </c>
       <c r="D331" t="s">
-        <v>1247</v>
+        <v>1276</v>
       </c>
       <c r="E331" t="s">
-        <v>1432</v>
+        <v>1461</v>
       </c>
       <c r="F331" t="s">
         <v>1535</v>
       </c>
       <c r="G331" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="H331" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I331" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J331" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="K331" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L331" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M331" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N331" t="s">
         <v>1547</v>
@@ -19567,34 +19567,34 @@
         <v>1110</v>
       </c>
       <c r="D332" t="s">
-        <v>1276</v>
+        <v>1247</v>
       </c>
       <c r="E332" t="s">
-        <v>1461</v>
+        <v>1432</v>
       </c>
       <c r="F332" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G332" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="H332" t="s">
         <v>1540</v>
       </c>
       <c r="I332" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J332" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K332" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L332" t="s">
         <v>1545</v>
       </c>
       <c r="M332" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N332" t="s">
         <v>1547</v>
@@ -19611,31 +19611,31 @@
         <v>1111</v>
       </c>
       <c r="D333" t="s">
-        <v>1247</v>
+        <v>1334</v>
       </c>
       <c r="E333" t="s">
-        <v>1432</v>
+        <v>1519</v>
       </c>
       <c r="F333" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="G333" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H333" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I333" t="s">
         <v>1546</v>
       </c>
       <c r="J333" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K333" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L333" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M333" t="s">
         <v>1541</v>
@@ -19655,10 +19655,10 @@
         <v>1112</v>
       </c>
       <c r="D334" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E334" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F334" t="s">
         <v>1538</v>
@@ -19673,16 +19673,16 @@
         <v>1546</v>
       </c>
       <c r="J334" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K334" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L334" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M334" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="N334" t="s">
         <v>1547</v>
@@ -19699,13 +19699,13 @@
         <v>1113</v>
       </c>
       <c r="D335" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="E335" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F335" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="G335" t="s">
         <v>1540</v>
@@ -19717,13 +19717,13 @@
         <v>1546</v>
       </c>
       <c r="J335" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K335" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L335" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M335" t="s">
         <v>1542</v>
@@ -19743,34 +19743,34 @@
         <v>1114</v>
       </c>
       <c r="D336" t="s">
-        <v>1336</v>
+        <v>1316</v>
       </c>
       <c r="E336" t="s">
-        <v>1521</v>
+        <v>1501</v>
       </c>
       <c r="F336" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G336" t="s">
         <v>1540</v>
       </c>
       <c r="H336" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I336" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J336" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K336" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L336" t="s">
         <v>1541</v>
       </c>
       <c r="M336" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N336" t="s">
         <v>1547</v>
@@ -19787,25 +19787,25 @@
         <v>1115</v>
       </c>
       <c r="D337" t="s">
-        <v>1316</v>
+        <v>1186</v>
       </c>
       <c r="E337" t="s">
-        <v>1501</v>
+        <v>1371</v>
       </c>
       <c r="F337" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="G337" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H337" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I337" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J337" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="K337" t="s">
         <v>1544</v>
@@ -19831,31 +19831,31 @@
         <v>1116</v>
       </c>
       <c r="D338" t="s">
-        <v>1186</v>
+        <v>1256</v>
       </c>
       <c r="E338" t="s">
-        <v>1371</v>
+        <v>1441</v>
       </c>
       <c r="F338" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="G338" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H338" t="s">
         <v>1543</v>
       </c>
       <c r="I338" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J338" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="K338" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L338" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="M338" t="s">
         <v>1545</v>
@@ -19875,34 +19875,34 @@
         <v>1117</v>
       </c>
       <c r="D339" t="s">
-        <v>1256</v>
+        <v>1337</v>
       </c>
       <c r="E339" t="s">
-        <v>1441</v>
+        <v>1522</v>
       </c>
       <c r="F339" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G339" t="s">
         <v>1540</v>
       </c>
       <c r="H339" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I339" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J339" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K339" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L339" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="M339" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N339" t="s">
         <v>1547</v>
@@ -19919,34 +19919,34 @@
         <v>1118</v>
       </c>
       <c r="D340" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="E340" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="F340" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G340" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H340" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I340" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J340" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K340" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L340" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="M340" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N340" t="s">
         <v>1547</v>
@@ -19963,34 +19963,34 @@
         <v>1119</v>
       </c>
       <c r="D341" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="E341" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="F341" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G341" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="H341" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I341" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="J341" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K341" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="L341" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="M341" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N341" t="s">
         <v>1547</v>
@@ -20007,34 +20007,34 @@
         <v>1120</v>
       </c>
       <c r="D342" t="s">
-        <v>1339</v>
+        <v>1215</v>
       </c>
       <c r="E342" t="s">
-        <v>1524</v>
+        <v>1400</v>
       </c>
       <c r="F342" t="s">
         <v>1536</v>
       </c>
       <c r="G342" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="H342" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="I342" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="J342" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="K342" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="L342" t="s">
         <v>1545</v>
       </c>
       <c r="M342" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N342" t="s">
         <v>1547</v>
@@ -20051,10 +20051,10 @@
         <v>1121</v>
       </c>
       <c r="D343" t="s">
-        <v>1215</v>
+        <v>1340</v>
       </c>
       <c r="E343" t="s">
-        <v>1400</v>
+        <v>1525</v>
       </c>
       <c r="F343" t="s">
         <v>1536</v>
@@ -20063,13 +20063,13 @@
         <v>1541</v>
       </c>
       <c r="H343" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I343" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="J343" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="K343" t="s">
         <v>1546</v>
@@ -20078,7 +20078,7 @@
         <v>1545</v>
       </c>
       <c r="M343" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="N343" t="s">
         <v>1547</v>
@@ -20095,34 +20095,34 @@
         <v>1122</v>
       </c>
       <c r="D344" t="s">
-        <v>1340</v>
+        <v>1181</v>
       </c>
       <c r="E344" t="s">
-        <v>1525</v>
+        <v>1366</v>
       </c>
       <c r="F344" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G344" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H344" t="s">
         <v>1540</v>
       </c>
       <c r="I344" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="J344" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K344" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="L344" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M344" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N344" t="s">
         <v>1547</v>
@@ -20139,34 +20139,34 @@
         <v>1123</v>
       </c>
       <c r="D345" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="E345" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="F345" t="s">
         <v>1534</v>
       </c>
       <c r="G345" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H345" t="s">
         <v>1540</v>
       </c>
       <c r="I345" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J345" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="K345" t="s">
         <v>1544</v>
       </c>
       <c r="L345" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="M345" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="N345" t="s">
         <v>1547</v>
@@ -20183,34 +20183,34 @@
         <v>1124</v>
       </c>
       <c r="D346" t="s">
-        <v>1179</v>
+        <v>1314</v>
       </c>
       <c r="E346" t="s">
-        <v>1364</v>
+        <v>1499</v>
       </c>
       <c r="F346" t="s">
         <v>1534</v>
       </c>
       <c r="G346" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H346" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="I346" t="s">
         <v>1543</v>
       </c>
       <c r="J346" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="K346" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L346" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M346" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N346" t="s">
         <v>1547</v>
@@ -20227,34 +20227,34 @@
         <v>1125</v>
       </c>
       <c r="D347" t="s">
-        <v>1314</v>
+        <v>1341</v>
       </c>
       <c r="E347" t="s">
-        <v>1499</v>
+        <v>1526</v>
       </c>
       <c r="F347" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G347" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H347" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="I347" t="s">
         <v>1543</v>
       </c>
       <c r="J347" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="K347" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="L347" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="M347" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N347" t="s">
         <v>1547</v>
@@ -20271,34 +20271,34 @@
         <v>1126</v>
       </c>
       <c r="D348" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="E348" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="F348" t="s">
         <v>1535</v>
       </c>
       <c r="G348" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="H348" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="I348" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="J348" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="K348" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="L348" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M348" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N348" t="s">
         <v>1547</v>
@@ -20315,34 +20315,34 @@
         <v>1127</v>
       </c>
       <c r="D349" t="s">
-        <v>1342</v>
+        <v>1247</v>
       </c>
       <c r="E349" t="s">
-        <v>1527</v>
+        <v>1432</v>
       </c>
       <c r="F349" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G349" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="H349" t="s">
         <v>1540</v>
       </c>
       <c r="I349" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="J349" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K349" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L349" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M349" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N349" t="s">
         <v>1547</v>
@@ -20359,28 +20359,28 @@
         <v>1128</v>
       </c>
       <c r="D350" t="s">
-        <v>1247</v>
+        <v>1212</v>
       </c>
       <c r="E350" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="F350" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G350" t="s">
         <v>1544</v>
       </c>
       <c r="H350" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I350" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J350" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="K350" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="L350" t="s">
         <v>1541</v>
@@ -20403,31 +20403,31 @@
         <v>1129</v>
       </c>
       <c r="D351" t="s">
-        <v>1212</v>
+        <v>1288</v>
       </c>
       <c r="E351" t="s">
-        <v>1397</v>
+        <v>1473</v>
       </c>
       <c r="F351" t="s">
         <v>1535</v>
       </c>
       <c r="G351" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="H351" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I351" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J351" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K351" t="s">
         <v>1542</v>
       </c>
       <c r="L351" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="M351" t="s">
         <v>1545</v>
@@ -20447,31 +20447,31 @@
         <v>1130</v>
       </c>
       <c r="D352" t="s">
-        <v>1288</v>
+        <v>1343</v>
       </c>
       <c r="E352" t="s">
-        <v>1473</v>
+        <v>1528</v>
       </c>
       <c r="F352" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="G352" t="s">
         <v>1540</v>
       </c>
       <c r="H352" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I352" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J352" t="s">
         <v>1541</v>
       </c>
       <c r="K352" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="L352" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M352" t="s">
         <v>1545</v>
@@ -20491,13 +20491,13 @@
         <v>1131</v>
       </c>
       <c r="D353" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E353" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F353" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G353" t="s">
         <v>1540</v>
@@ -20509,16 +20509,16 @@
         <v>1546</v>
       </c>
       <c r="J353" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K353" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L353" t="s">
         <v>1542</v>
       </c>
       <c r="M353" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N353" t="s">
         <v>1547</v>
@@ -20535,13 +20535,13 @@
         <v>1132</v>
       </c>
       <c r="D354" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E354" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="F354" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="G354" t="s">
         <v>1540</v>
@@ -20553,16 +20553,16 @@
         <v>1546</v>
       </c>
       <c r="J354" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="K354" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L354" t="s">
         <v>1542</v>
       </c>
       <c r="M354" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N354" t="s">
         <v>1547</v>
@@ -20579,31 +20579,31 @@
         <v>1133</v>
       </c>
       <c r="D355" t="s">
-        <v>1345</v>
+        <v>1210</v>
       </c>
       <c r="E355" t="s">
-        <v>1530</v>
+        <v>1395</v>
       </c>
       <c r="F355" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="G355" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H355" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I355" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J355" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="K355" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="L355" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M355" t="s">
         <v>1545</v>
@@ -20623,34 +20623,34 @@
         <v>1134</v>
       </c>
       <c r="D356" t="s">
-        <v>1210</v>
+        <v>1346</v>
       </c>
       <c r="E356" t="s">
-        <v>1395</v>
+        <v>1531</v>
       </c>
       <c r="F356" t="s">
         <v>1535</v>
       </c>
       <c r="G356" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H356" t="s">
         <v>1541</v>
       </c>
       <c r="I356" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J356" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="K356" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="L356" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M356" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="N356" t="s">
         <v>1547</v>
@@ -20667,13 +20667,13 @@
         <v>1135</v>
       </c>
       <c r="D357" t="s">
-        <v>1346</v>
+        <v>1188</v>
       </c>
       <c r="E357" t="s">
-        <v>1531</v>
+        <v>1373</v>
       </c>
       <c r="F357" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G357" t="s">
         <v>1540</v>
@@ -20682,16 +20682,16 @@
         <v>1541</v>
       </c>
       <c r="I357" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J357" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="K357" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="L357" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M357" t="s">
         <v>1544</v>
@@ -20711,10 +20711,10 @@
         <v>1136</v>
       </c>
       <c r="D358" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E358" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="F358" t="s">
         <v>1534</v>
@@ -20755,10 +20755,10 @@
         <v>1137</v>
       </c>
       <c r="D359" t="s">
-        <v>1190</v>
+        <v>1338</v>
       </c>
       <c r="E359" t="s">
-        <v>1375</v>
+        <v>1523</v>
       </c>
       <c r="F359" t="s">
         <v>1534</v>
@@ -20767,22 +20767,22 @@
         <v>1540</v>
       </c>
       <c r="H359" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="I359" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="J359" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="K359" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="L359" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M359" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="N359" t="s">
         <v>1547</v>
@@ -20799,34 +20799,34 @@
         <v>1138</v>
       </c>
       <c r="D360" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="E360" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="F360" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="G360" t="s">
         <v>1540</v>
       </c>
       <c r="H360" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="I360" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J360" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="K360" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="L360" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M360" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N360" t="s">
         <v>1547</v>
@@ -20843,13 +20843,13 @@
         <v>1139</v>
       </c>
       <c r="D361" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="E361" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="F361" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="G361" t="s">
         <v>1540</v>
@@ -20858,19 +20858,19 @@
         <v>1541</v>
       </c>
       <c r="I361" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="J361" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="K361" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L361" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M361" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="N361" t="s">
         <v>1547</v>
@@ -20887,10 +20887,10 @@
         <v>1140</v>
       </c>
       <c r="D362" t="s">
-        <v>1347</v>
+        <v>1301</v>
       </c>
       <c r="E362" t="s">
-        <v>1532</v>
+        <v>1486</v>
       </c>
       <c r="F362" t="s">
         <v>1536</v>
@@ -20899,22 +20899,22 @@
         <v>1540</v>
       </c>
       <c r="H362" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I362" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="J362" t="s">
         <v>1542</v>
       </c>
       <c r="K362" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="L362" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="M362" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N362" t="s">
         <v>1547</v>
@@ -20931,13 +20931,13 @@
         <v>1141</v>
       </c>
       <c r="D363" t="s">
-        <v>1301</v>
+        <v>1262</v>
       </c>
       <c r="E363" t="s">
-        <v>1486</v>
+        <v>1447</v>
       </c>
       <c r="F363" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G363" t="s">
         <v>1540</v>
@@ -20946,19 +20946,19 @@
         <v>1543</v>
       </c>
       <c r="I363" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J363" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K363" t="s">
         <v>1541</v>
       </c>
       <c r="L363" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M363" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N363" t="s">
         <v>1547</v>
@@ -20975,34 +20975,34 @@
         <v>1142</v>
       </c>
       <c r="D364" t="s">
-        <v>1262</v>
+        <v>1241</v>
       </c>
       <c r="E364" t="s">
-        <v>1447</v>
+        <v>1426</v>
       </c>
       <c r="F364" t="s">
         <v>1535</v>
       </c>
       <c r="G364" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H364" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I364" t="s">
         <v>1544</v>
       </c>
       <c r="J364" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K364" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="L364" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M364" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N364" t="s">
         <v>1547</v>
@@ -21019,34 +21019,34 @@
         <v>1143</v>
       </c>
       <c r="D365" t="s">
-        <v>1241</v>
+        <v>1201</v>
       </c>
       <c r="E365" t="s">
-        <v>1426</v>
+        <v>1386</v>
       </c>
       <c r="F365" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G365" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H365" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="I365" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="J365" t="s">
         <v>1541</v>
       </c>
       <c r="K365" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="L365" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M365" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="N365" t="s">
         <v>1547</v>
@@ -21063,34 +21063,34 @@
         <v>1144</v>
       </c>
       <c r="D366" t="s">
-        <v>1201</v>
+        <v>1319</v>
       </c>
       <c r="E366" t="s">
-        <v>1386</v>
+        <v>1504</v>
       </c>
       <c r="F366" t="s">
         <v>1534</v>
       </c>
       <c r="G366" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H366" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I366" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="J366" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="K366" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="L366" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M366" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="N366" t="s">
         <v>1547</v>
@@ -21107,10 +21107,10 @@
         <v>1145</v>
       </c>
       <c r="D367" t="s">
-        <v>1319</v>
+        <v>1265</v>
       </c>
       <c r="E367" t="s">
-        <v>1504</v>
+        <v>1450</v>
       </c>
       <c r="F367" t="s">
         <v>1534</v>
@@ -21122,16 +21122,16 @@
         <v>1543</v>
       </c>
       <c r="I367" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="J367" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K367" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L367" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="M367" t="s">
         <v>1541</v>
@@ -21151,34 +21151,34 @@
         <v>1146</v>
       </c>
       <c r="D368" t="s">
-        <v>1265</v>
+        <v>1295</v>
       </c>
       <c r="E368" t="s">
-        <v>1450</v>
+        <v>1480</v>
       </c>
       <c r="F368" t="s">
         <v>1534</v>
       </c>
       <c r="G368" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H368" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I368" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="J368" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="K368" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="L368" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="M368" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="N368" t="s">
         <v>1547</v>
@@ -21195,34 +21195,34 @@
         <v>1147</v>
       </c>
       <c r="D369" t="s">
-        <v>1295</v>
+        <v>1250</v>
       </c>
       <c r="E369" t="s">
-        <v>1480</v>
+        <v>1435</v>
       </c>
       <c r="F369" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G369" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H369" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I369" t="s">
         <v>1540</v>
       </c>
       <c r="J369" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K369" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="L369" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M369" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N369" t="s">
         <v>1547</v>
@@ -21239,34 +21239,34 @@
         <v>1148</v>
       </c>
       <c r="D370" t="s">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="E370" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="F370" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G370" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H370" t="s">
         <v>1543</v>
       </c>
       <c r="I370" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="J370" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K370" t="s">
         <v>1544</v>
       </c>
       <c r="L370" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M370" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N370" t="s">
         <v>1547</v>
@@ -21283,34 +21283,34 @@
         <v>1149</v>
       </c>
       <c r="D371" t="s">
-        <v>1240</v>
+        <v>1188</v>
       </c>
       <c r="E371" t="s">
-        <v>1425</v>
+        <v>1373</v>
       </c>
       <c r="F371" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G371" t="s">
         <v>1540</v>
       </c>
       <c r="H371" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I371" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J371" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="K371" t="s">
         <v>1544</v>
       </c>
       <c r="L371" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="M371" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N371" t="s">
         <v>1547</v>
@@ -21327,34 +21327,34 @@
         <v>1150</v>
       </c>
       <c r="D372" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="E372" t="s">
-        <v>1373</v>
+        <v>1389</v>
       </c>
       <c r="F372" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G372" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="H372" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I372" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J372" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K372" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="L372" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="M372" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="N372" t="s">
         <v>1547</v>
@@ -21371,34 +21371,34 @@
         <v>1151</v>
       </c>
       <c r="D373" t="s">
-        <v>1204</v>
+        <v>1252</v>
       </c>
       <c r="E373" t="s">
-        <v>1389</v>
+        <v>1437</v>
       </c>
       <c r="F373" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G373" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="H373" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I373" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="J373" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="K373" t="s">
         <v>1542</v>
       </c>
       <c r="L373" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M373" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="N373" t="s">
         <v>1547</v>
@@ -21415,19 +21415,19 @@
         <v>1152</v>
       </c>
       <c r="D374" t="s">
-        <v>1252</v>
+        <v>1271</v>
       </c>
       <c r="E374" t="s">
-        <v>1437</v>
+        <v>1456</v>
       </c>
       <c r="F374" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G374" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H374" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="I374" t="s">
         <v>1543</v>
@@ -21436,10 +21436,10 @@
         <v>1546</v>
       </c>
       <c r="K374" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="L374" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M374" t="s">
         <v>1545</v>
@@ -21459,34 +21459,34 @@
         <v>1153</v>
       </c>
       <c r="D375" t="s">
-        <v>1271</v>
+        <v>1185</v>
       </c>
       <c r="E375" t="s">
-        <v>1456</v>
+        <v>1370</v>
       </c>
       <c r="F375" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G375" t="s">
         <v>1541</v>
       </c>
       <c r="H375" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="I375" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J375" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="K375" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L375" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M375" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N375" t="s">
         <v>1547</v>
@@ -21503,34 +21503,34 @@
         <v>1154</v>
       </c>
       <c r="D376" t="s">
-        <v>1185</v>
+        <v>1346</v>
       </c>
       <c r="E376" t="s">
-        <v>1370</v>
+        <v>1531</v>
       </c>
       <c r="F376" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G376" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="H376" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I376" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="J376" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K376" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="L376" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M376" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N376" t="s">
         <v>1547</v>
@@ -21547,34 +21547,34 @@
         <v>1155</v>
       </c>
       <c r="D377" t="s">
-        <v>1346</v>
+        <v>1231</v>
       </c>
       <c r="E377" t="s">
-        <v>1531</v>
+        <v>1416</v>
       </c>
       <c r="F377" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G377" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="H377" t="s">
         <v>1543</v>
       </c>
       <c r="I377" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="J377" t="s">
         <v>1542</v>
       </c>
       <c r="K377" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="L377" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M377" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="N377" t="s">
         <v>1547</v>
@@ -21591,34 +21591,34 @@
         <v>1156</v>
       </c>
       <c r="D378" t="s">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="E378" t="s">
-        <v>1416</v>
+        <v>1425</v>
       </c>
       <c r="F378" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G378" t="s">
         <v>1540</v>
       </c>
       <c r="H378" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I378" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J378" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K378" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="L378" t="s">
         <v>1544</v>
       </c>
       <c r="M378" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N378" t="s">
         <v>1547</v>
@@ -21635,34 +21635,34 @@
         <v>1157</v>
       </c>
       <c r="D379" t="s">
-        <v>1240</v>
+        <v>1200</v>
       </c>
       <c r="E379" t="s">
-        <v>1425</v>
+        <v>1385</v>
       </c>
       <c r="F379" t="s">
         <v>1535</v>
       </c>
       <c r="G379" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H379" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I379" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J379" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K379" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L379" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M379" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N379" t="s">
         <v>1547</v>
@@ -21679,31 +21679,31 @@
         <v>1158</v>
       </c>
       <c r="D380" t="s">
-        <v>1200</v>
+        <v>1244</v>
       </c>
       <c r="E380" t="s">
-        <v>1385</v>
+        <v>1429</v>
       </c>
       <c r="F380" t="s">
         <v>1535</v>
       </c>
       <c r="G380" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H380" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I380" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="J380" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K380" t="s">
         <v>1544</v>
       </c>
       <c r="L380" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="M380" t="s">
         <v>1545</v>
@@ -21723,31 +21723,31 @@
         <v>1159</v>
       </c>
       <c r="D381" t="s">
-        <v>1244</v>
+        <v>1211</v>
       </c>
       <c r="E381" t="s">
-        <v>1429</v>
+        <v>1396</v>
       </c>
       <c r="F381" t="s">
         <v>1535</v>
       </c>
       <c r="G381" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H381" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I381" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="J381" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K381" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L381" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="M381" t="s">
         <v>1545</v>
@@ -21767,34 +21767,34 @@
         <v>1160</v>
       </c>
       <c r="D382" t="s">
-        <v>1211</v>
+        <v>1297</v>
       </c>
       <c r="E382" t="s">
-        <v>1396</v>
+        <v>1482</v>
       </c>
       <c r="F382" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G382" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H382" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="I382" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="J382" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="K382" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="L382" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M382" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="N382" t="s">
         <v>1547</v>
@@ -21811,10 +21811,10 @@
         <v>1161</v>
       </c>
       <c r="D383" t="s">
-        <v>1297</v>
+        <v>1348</v>
       </c>
       <c r="E383" t="s">
-        <v>1482</v>
+        <v>1533</v>
       </c>
       <c r="F383" t="s">
         <v>1534</v>
@@ -21855,34 +21855,34 @@
         <v>1162</v>
       </c>
       <c r="D384" t="s">
-        <v>1348</v>
+        <v>1194</v>
       </c>
       <c r="E384" t="s">
-        <v>1533</v>
+        <v>1379</v>
       </c>
       <c r="F384" t="s">
         <v>1534</v>
       </c>
       <c r="G384" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H384" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I384" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="J384" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="K384" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="L384" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="M384" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="N384" t="s">
         <v>1547</v>
@@ -21899,34 +21899,34 @@
         <v>1163</v>
       </c>
       <c r="D385">
-        <v>1448</v>
+        <v>1347</v>
       </c>
       <c r="E385">
-        <v>72.40000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F385" t="s">
         <v>1534</v>
       </c>
       <c r="G385" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H385" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I385" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J385" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="K385" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L385" t="s">
         <v>1544</v>
       </c>
       <c r="M385" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N385" t="s">
         <v>1547</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1204,12 +1204,12 @@
     <t>عمر عماد فرغلى على</t>
   </si>
   <si>
+    <t>اميره حمدى مصطفى محمد</t>
+  </si>
+  <si>
     <t>نور شحاته نور الدين ابو الليل</t>
   </si>
   <si>
-    <t>اميره حمدى مصطفى محمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>30507022403518</t>
   </si>
   <si>
+    <t>30407122401208</t>
+  </si>
+  <si>
     <t>30505142403454</t>
   </si>
   <si>
-    <t>30407122401208</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3502,10 +3502,10 @@
     <t>01155910557</t>
   </si>
   <si>
+    <t>01036343803</t>
+  </si>
+  <si>
     <t>01159358898</t>
-  </si>
-  <si>
-    <t>01036343803</t>
   </si>
   <si>
     <t>1353</t>
@@ -21855,34 +21855,34 @@
         <v>1162</v>
       </c>
       <c r="D384" t="s">
-        <v>1194</v>
+        <v>1285</v>
       </c>
       <c r="E384" t="s">
-        <v>1379</v>
+        <v>1470</v>
       </c>
       <c r="F384" t="s">
         <v>1534</v>
       </c>
       <c r="G384" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H384" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I384" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J384" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="K384" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L384" t="s">
         <v>1544</v>
       </c>
       <c r="M384" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N384" t="s">
         <v>1547</v>
@@ -21899,34 +21899,34 @@
         <v>1163</v>
       </c>
       <c r="D385">
-        <v>1347</v>
+        <v>1448</v>
       </c>
       <c r="E385">
-        <v>67.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F385" t="s">
         <v>1534</v>
       </c>
       <c r="G385" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H385" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I385" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J385" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K385" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="L385" t="s">
         <v>1544</v>
       </c>
       <c r="M385" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N385" t="s">
         <v>1547</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1204,12 +1204,12 @@
     <t>عمر عماد فرغلى على</t>
   </si>
   <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
     <t>اميره حمدى مصطفى محمد</t>
   </si>
   <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2353,12 +2353,12 @@
     <t>30507022403518</t>
   </si>
   <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
     <t>30407122401208</t>
   </si>
   <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3502,10 +3502,10 @@
     <t>01155910557</t>
   </si>
   <si>
+    <t>01159358898</t>
+  </si>
+  <si>
     <t>01036343803</t>
-  </si>
-  <si>
-    <t>01159358898</t>
   </si>
   <si>
     <t>1353</t>
@@ -21855,34 +21855,34 @@
         <v>1162</v>
       </c>
       <c r="D384" t="s">
-        <v>1285</v>
+        <v>1194</v>
       </c>
       <c r="E384" t="s">
-        <v>1470</v>
+        <v>1379</v>
       </c>
       <c r="F384" t="s">
         <v>1534</v>
       </c>
       <c r="G384" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H384" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I384" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J384" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K384" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="L384" t="s">
         <v>1544</v>
       </c>
       <c r="M384" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N384" t="s">
         <v>1547</v>
@@ -21899,34 +21899,34 @@
         <v>1163</v>
       </c>
       <c r="D385">
-        <v>1448</v>
+        <v>1347</v>
       </c>
       <c r="E385">
-        <v>72.40000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F385" t="s">
         <v>1534</v>
       </c>
       <c r="G385" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H385" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I385" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J385" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="K385" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L385" t="s">
         <v>1544</v>
       </c>
       <c r="M385" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N385" t="s">
         <v>1547</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -943,273 +943,273 @@
     <t>حازم محمد احمد هارون</t>
   </si>
   <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>اميره حمدى مصطفى محمد</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
     <t>الاء سميح عبدالعظيم محمد</t>
   </si>
   <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>اميره حمدى مصطفى محمد</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2092,273 +2092,273 @@
     <t>30504302401554</t>
   </si>
   <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30407122401208</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
     <t>30012012409985</t>
   </si>
   <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30407122401208</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3241,271 +3241,271 @@
     <t>01013305686</t>
   </si>
   <si>
+    <t>01002331784</t>
+  </si>
+  <si>
+    <t>01150905692</t>
+  </si>
+  <si>
+    <t>01028993616</t>
+  </si>
+  <si>
+    <t>01119364560</t>
+  </si>
+  <si>
+    <t>01114623756</t>
+  </si>
+  <si>
+    <t>01110180758</t>
+  </si>
+  <si>
+    <t>01098408936</t>
+  </si>
+  <si>
+    <t>01026439570</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01036343803</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
     <t>01150936407</t>
-  </si>
-  <si>
-    <t>01002331784</t>
-  </si>
-  <si>
-    <t>01150905692</t>
-  </si>
-  <si>
-    <t>01028993616</t>
-  </si>
-  <si>
-    <t>01119364560</t>
-  </si>
-  <si>
-    <t>01114623756</t>
-  </si>
-  <si>
-    <t>01110180758</t>
-  </si>
-  <si>
-    <t>01098408936</t>
-  </si>
-  <si>
-    <t>01026439570</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01036343803</t>
-  </si>
-  <si>
-    <t>01159358898</t>
   </si>
   <si>
     <t>1353</t>
@@ -18027,34 +18027,34 @@
         <v>1075</v>
       </c>
       <c r="D297" t="s">
-        <v>1179</v>
+        <v>1198</v>
       </c>
       <c r="E297" t="s">
-        <v>1364</v>
+        <v>1383</v>
       </c>
       <c r="F297" t="s">
         <v>1534</v>
       </c>
       <c r="G297" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H297" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="I297" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J297" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K297" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="L297" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M297" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N297" t="s">
         <v>1547</v>
@@ -18071,34 +18071,34 @@
         <v>1076</v>
       </c>
       <c r="D298" t="s">
-        <v>1198</v>
+        <v>1324</v>
       </c>
       <c r="E298" t="s">
-        <v>1383</v>
+        <v>1509</v>
       </c>
       <c r="F298" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G298" t="s">
         <v>1540</v>
       </c>
       <c r="H298" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I298" t="s">
         <v>1543</v>
       </c>
       <c r="J298" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K298" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L298" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M298" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="N298" t="s">
         <v>1547</v>
@@ -18115,31 +18115,31 @@
         <v>1077</v>
       </c>
       <c r="D299" t="s">
-        <v>1324</v>
+        <v>1212</v>
       </c>
       <c r="E299" t="s">
-        <v>1509</v>
+        <v>1397</v>
       </c>
       <c r="F299" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G299" t="s">
         <v>1540</v>
       </c>
       <c r="H299" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I299" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="J299" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K299" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L299" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M299" t="s">
         <v>1542</v>
@@ -18159,34 +18159,34 @@
         <v>1078</v>
       </c>
       <c r="D300" t="s">
-        <v>1212</v>
+        <v>1241</v>
       </c>
       <c r="E300" t="s">
-        <v>1397</v>
+        <v>1426</v>
       </c>
       <c r="F300" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G300" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="H300" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I300" t="s">
         <v>1545</v>
       </c>
       <c r="J300" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="K300" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="L300" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="M300" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N300" t="s">
         <v>1547</v>
@@ -18203,34 +18203,34 @@
         <v>1079</v>
       </c>
       <c r="D301" t="s">
-        <v>1241</v>
+        <v>1176</v>
       </c>
       <c r="E301" t="s">
-        <v>1426</v>
+        <v>1361</v>
       </c>
       <c r="F301" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G301" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="H301" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I301" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J301" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K301" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="L301" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M301" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="N301" t="s">
         <v>1547</v>
@@ -18247,10 +18247,10 @@
         <v>1080</v>
       </c>
       <c r="D302" t="s">
-        <v>1176</v>
+        <v>1282</v>
       </c>
       <c r="E302" t="s">
-        <v>1361</v>
+        <v>1467</v>
       </c>
       <c r="F302" t="s">
         <v>1534</v>
@@ -18268,13 +18268,13 @@
         <v>1541</v>
       </c>
       <c r="K302" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L302" t="s">
         <v>1544</v>
       </c>
       <c r="M302" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N302" t="s">
         <v>1547</v>
@@ -18291,10 +18291,10 @@
         <v>1081</v>
       </c>
       <c r="D303" t="s">
-        <v>1282</v>
+        <v>1325</v>
       </c>
       <c r="E303" t="s">
-        <v>1467</v>
+        <v>1510</v>
       </c>
       <c r="F303" t="s">
         <v>1534</v>
@@ -18303,19 +18303,19 @@
         <v>1540</v>
       </c>
       <c r="H303" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I303" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J303" t="s">
         <v>1541</v>
       </c>
       <c r="K303" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L303" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M303" t="s">
         <v>1542</v>
@@ -18335,13 +18335,13 @@
         <v>1082</v>
       </c>
       <c r="D304" t="s">
-        <v>1325</v>
+        <v>1181</v>
       </c>
       <c r="E304" t="s">
-        <v>1510</v>
+        <v>1366</v>
       </c>
       <c r="F304" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G304" t="s">
         <v>1540</v>
@@ -18353,16 +18353,16 @@
         <v>1546</v>
       </c>
       <c r="J304" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K304" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L304" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M304" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N304" t="s">
         <v>1547</v>
@@ -18379,13 +18379,13 @@
         <v>1083</v>
       </c>
       <c r="D305" t="s">
-        <v>1181</v>
+        <v>1317</v>
       </c>
       <c r="E305" t="s">
-        <v>1366</v>
+        <v>1502</v>
       </c>
       <c r="F305" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G305" t="s">
         <v>1540</v>
@@ -18394,16 +18394,16 @@
         <v>1543</v>
       </c>
       <c r="I305" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="J305" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K305" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L305" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M305" t="s">
         <v>1545</v>
@@ -18423,13 +18423,13 @@
         <v>1084</v>
       </c>
       <c r="D306" t="s">
-        <v>1317</v>
+        <v>1187</v>
       </c>
       <c r="E306" t="s">
-        <v>1502</v>
+        <v>1372</v>
       </c>
       <c r="F306" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G306" t="s">
         <v>1540</v>
@@ -18438,19 +18438,19 @@
         <v>1543</v>
       </c>
       <c r="I306" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="J306" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="K306" t="s">
         <v>1544</v>
       </c>
       <c r="L306" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="M306" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N306" t="s">
         <v>1547</v>
@@ -18467,34 +18467,34 @@
         <v>1085</v>
       </c>
       <c r="D307" t="s">
-        <v>1187</v>
+        <v>1276</v>
       </c>
       <c r="E307" t="s">
-        <v>1372</v>
+        <v>1461</v>
       </c>
       <c r="F307" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G307" t="s">
         <v>1540</v>
       </c>
       <c r="H307" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I307" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="J307" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="K307" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="L307" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M307" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N307" t="s">
         <v>1547</v>
@@ -18511,10 +18511,10 @@
         <v>1086</v>
       </c>
       <c r="D308" t="s">
-        <v>1276</v>
+        <v>1306</v>
       </c>
       <c r="E308" t="s">
-        <v>1461</v>
+        <v>1491</v>
       </c>
       <c r="F308" t="s">
         <v>1535</v>
@@ -18523,7 +18523,7 @@
         <v>1540</v>
       </c>
       <c r="H308" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I308" t="s">
         <v>1542</v>
@@ -18532,7 +18532,7 @@
         <v>1546</v>
       </c>
       <c r="K308" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="L308" t="s">
         <v>1545</v>
@@ -18555,13 +18555,13 @@
         <v>1087</v>
       </c>
       <c r="D309" t="s">
-        <v>1306</v>
+        <v>1322</v>
       </c>
       <c r="E309" t="s">
-        <v>1491</v>
+        <v>1507</v>
       </c>
       <c r="F309" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G309" t="s">
         <v>1540</v>
@@ -18599,34 +18599,34 @@
         <v>1088</v>
       </c>
       <c r="D310" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="E310" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="F310" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G310" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H310" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="I310" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="J310" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="K310" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="L310" t="s">
         <v>1545</v>
       </c>
       <c r="M310" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="N310" t="s">
         <v>1547</v>
@@ -18643,34 +18643,34 @@
         <v>1089</v>
       </c>
       <c r="D311" t="s">
-        <v>1326</v>
+        <v>1196</v>
       </c>
       <c r="E311" t="s">
-        <v>1511</v>
+        <v>1381</v>
       </c>
       <c r="F311" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="G311" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H311" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I311" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="J311" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K311" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="L311" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M311" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="N311" t="s">
         <v>1547</v>
@@ -18687,31 +18687,31 @@
         <v>1090</v>
       </c>
       <c r="D312" t="s">
-        <v>1196</v>
+        <v>1251</v>
       </c>
       <c r="E312" t="s">
-        <v>1381</v>
+        <v>1436</v>
       </c>
       <c r="F312" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G312" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H312" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I312" t="s">
         <v>1546</v>
       </c>
       <c r="J312" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K312" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="L312" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M312" t="s">
         <v>1542</v>
@@ -18731,28 +18731,28 @@
         <v>1091</v>
       </c>
       <c r="D313" t="s">
-        <v>1251</v>
+        <v>1270</v>
       </c>
       <c r="E313" t="s">
-        <v>1436</v>
+        <v>1455</v>
       </c>
       <c r="F313" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G313" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H313" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="I313" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J313" t="s">
         <v>1544</v>
       </c>
       <c r="K313" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="L313" t="s">
         <v>1545</v>
@@ -18775,34 +18775,34 @@
         <v>1092</v>
       </c>
       <c r="D314" t="s">
-        <v>1270</v>
+        <v>1282</v>
       </c>
       <c r="E314" t="s">
-        <v>1455</v>
+        <v>1467</v>
       </c>
       <c r="F314" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G314" t="s">
         <v>1540</v>
       </c>
       <c r="H314" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I314" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J314" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K314" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="L314" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M314" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N314" t="s">
         <v>1547</v>
@@ -18819,13 +18819,13 @@
         <v>1093</v>
       </c>
       <c r="D315" t="s">
-        <v>1282</v>
+        <v>1303</v>
       </c>
       <c r="E315" t="s">
-        <v>1467</v>
+        <v>1488</v>
       </c>
       <c r="F315" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G315" t="s">
         <v>1540</v>
@@ -18834,19 +18834,19 @@
         <v>1546</v>
       </c>
       <c r="I315" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="J315" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="K315" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L315" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M315" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N315" t="s">
         <v>1547</v>
@@ -18863,10 +18863,10 @@
         <v>1094</v>
       </c>
       <c r="D316" t="s">
-        <v>1303</v>
+        <v>1214</v>
       </c>
       <c r="E316" t="s">
-        <v>1488</v>
+        <v>1399</v>
       </c>
       <c r="F316" t="s">
         <v>1535</v>
@@ -18878,19 +18878,19 @@
         <v>1546</v>
       </c>
       <c r="I316" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J316" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K316" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L316" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M316" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N316" t="s">
         <v>1547</v>
@@ -18907,13 +18907,13 @@
         <v>1095</v>
       </c>
       <c r="D317" t="s">
-        <v>1214</v>
+        <v>1230</v>
       </c>
       <c r="E317" t="s">
-        <v>1399</v>
+        <v>1415</v>
       </c>
       <c r="F317" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G317" t="s">
         <v>1540</v>
@@ -18922,10 +18922,10 @@
         <v>1546</v>
       </c>
       <c r="I317" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="J317" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K317" t="s">
         <v>1545</v>
@@ -18951,10 +18951,10 @@
         <v>1096</v>
       </c>
       <c r="D318" t="s">
-        <v>1230</v>
+        <v>1327</v>
       </c>
       <c r="E318" t="s">
-        <v>1415</v>
+        <v>1512</v>
       </c>
       <c r="F318" t="s">
         <v>1534</v>
@@ -18963,22 +18963,22 @@
         <v>1540</v>
       </c>
       <c r="H318" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I318" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J318" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K318" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L318" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M318" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="N318" t="s">
         <v>1547</v>
@@ -18995,34 +18995,34 @@
         <v>1097</v>
       </c>
       <c r="D319" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E319" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="F319" t="s">
         <v>1534</v>
       </c>
       <c r="G319" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H319" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I319" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="J319" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K319" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L319" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M319" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="N319" t="s">
         <v>1547</v>
@@ -19039,10 +19039,10 @@
         <v>1098</v>
       </c>
       <c r="D320" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="E320" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F320" t="s">
         <v>1534</v>
@@ -19083,34 +19083,34 @@
         <v>1099</v>
       </c>
       <c r="D321" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="E321" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="F321" t="s">
         <v>1534</v>
       </c>
       <c r="G321" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H321" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I321" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="J321" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="K321" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L321" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M321" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="N321" t="s">
         <v>1547</v>
@@ -19127,34 +19127,34 @@
         <v>1100</v>
       </c>
       <c r="D322" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E322" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F322" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="G322" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H322" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I322" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J322" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K322" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L322" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M322" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N322" t="s">
         <v>1547</v>
@@ -19171,34 +19171,34 @@
         <v>1101</v>
       </c>
       <c r="D323" t="s">
-        <v>1331</v>
+        <v>1300</v>
       </c>
       <c r="E323" t="s">
-        <v>1516</v>
+        <v>1485</v>
       </c>
       <c r="F323" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="G323" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H323" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I323" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J323" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K323" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L323" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M323" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N323" t="s">
         <v>1547</v>
@@ -19215,13 +19215,13 @@
         <v>1102</v>
       </c>
       <c r="D324" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="E324" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="F324" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G324" t="s">
         <v>1540</v>
@@ -19236,13 +19236,13 @@
         <v>1542</v>
       </c>
       <c r="K324" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L324" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M324" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N324" t="s">
         <v>1547</v>
@@ -19259,10 +19259,10 @@
         <v>1103</v>
       </c>
       <c r="D325" t="s">
-        <v>1306</v>
+        <v>1332</v>
       </c>
       <c r="E325" t="s">
-        <v>1491</v>
+        <v>1517</v>
       </c>
       <c r="F325" t="s">
         <v>1534</v>
@@ -19277,16 +19277,16 @@
         <v>1546</v>
       </c>
       <c r="J325" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K325" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L325" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M325" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N325" t="s">
         <v>1547</v>
@@ -19303,31 +19303,31 @@
         <v>1104</v>
       </c>
       <c r="D326" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="E326" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="F326" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G326" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H326" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I326" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="J326" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="K326" t="s">
         <v>1544</v>
       </c>
       <c r="L326" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M326" t="s">
         <v>1542</v>
@@ -19347,34 +19347,34 @@
         <v>1105</v>
       </c>
       <c r="D327" t="s">
-        <v>1333</v>
+        <v>1299</v>
       </c>
       <c r="E327" t="s">
-        <v>1518</v>
+        <v>1484</v>
       </c>
       <c r="F327" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G327" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="H327" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I327" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="J327" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="K327" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L327" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M327" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N327" t="s">
         <v>1547</v>
@@ -19391,34 +19391,34 @@
         <v>1106</v>
       </c>
       <c r="D328" t="s">
-        <v>1299</v>
+        <v>1209</v>
       </c>
       <c r="E328" t="s">
-        <v>1484</v>
+        <v>1394</v>
       </c>
       <c r="F328" t="s">
         <v>1535</v>
       </c>
       <c r="G328" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H328" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I328" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="J328" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="K328" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="L328" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M328" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="N328" t="s">
         <v>1547</v>
@@ -19435,34 +19435,34 @@
         <v>1107</v>
       </c>
       <c r="D329" t="s">
-        <v>1209</v>
+        <v>1247</v>
       </c>
       <c r="E329" t="s">
-        <v>1394</v>
+        <v>1432</v>
       </c>
       <c r="F329" t="s">
         <v>1535</v>
       </c>
       <c r="G329" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H329" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I329" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="J329" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K329" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L329" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="M329" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N329" t="s">
         <v>1547</v>
@@ -19479,34 +19479,34 @@
         <v>1108</v>
       </c>
       <c r="D330" t="s">
-        <v>1247</v>
+        <v>1276</v>
       </c>
       <c r="E330" t="s">
-        <v>1432</v>
+        <v>1461</v>
       </c>
       <c r="F330" t="s">
         <v>1535</v>
       </c>
       <c r="G330" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="H330" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I330" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J330" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="K330" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L330" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M330" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N330" t="s">
         <v>1547</v>
@@ -19523,34 +19523,34 @@
         <v>1109</v>
       </c>
       <c r="D331" t="s">
-        <v>1276</v>
+        <v>1247</v>
       </c>
       <c r="E331" t="s">
-        <v>1461</v>
+        <v>1432</v>
       </c>
       <c r="F331" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G331" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="H331" t="s">
         <v>1540</v>
       </c>
       <c r="I331" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J331" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K331" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L331" t="s">
         <v>1545</v>
       </c>
       <c r="M331" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="N331" t="s">
         <v>1547</v>
@@ -19567,31 +19567,31 @@
         <v>1110</v>
       </c>
       <c r="D332" t="s">
-        <v>1247</v>
+        <v>1334</v>
       </c>
       <c r="E332" t="s">
-        <v>1432</v>
+        <v>1519</v>
       </c>
       <c r="F332" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="G332" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H332" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I332" t="s">
         <v>1546</v>
       </c>
       <c r="J332" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K332" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L332" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M332" t="s">
         <v>1541</v>
@@ -19611,10 +19611,10 @@
         <v>1111</v>
       </c>
       <c r="D333" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E333" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F333" t="s">
         <v>1538</v>
@@ -19629,16 +19629,16 @@
         <v>1546</v>
       </c>
       <c r="J333" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="K333" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L333" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M333" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="N333" t="s">
         <v>1547</v>
@@ -19655,13 +19655,13 @@
         <v>1112</v>
       </c>
       <c r="D334" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="E334" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F334" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="G334" t="s">
         <v>1540</v>
@@ -19673,13 +19673,13 @@
         <v>1546</v>
       </c>
       <c r="J334" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K334" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L334" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M334" t="s">
         <v>1542</v>
@@ -19699,34 +19699,34 @@
         <v>1113</v>
       </c>
       <c r="D335" t="s">
-        <v>1336</v>
+        <v>1316</v>
       </c>
       <c r="E335" t="s">
-        <v>1521</v>
+        <v>1501</v>
       </c>
       <c r="F335" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G335" t="s">
         <v>1540</v>
       </c>
       <c r="H335" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I335" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J335" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K335" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L335" t="s">
         <v>1541</v>
       </c>
       <c r="M335" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N335" t="s">
         <v>1547</v>
@@ -19743,25 +19743,25 @@
         <v>1114</v>
       </c>
       <c r="D336" t="s">
-        <v>1316</v>
+        <v>1186</v>
       </c>
       <c r="E336" t="s">
-        <v>1501</v>
+        <v>1371</v>
       </c>
       <c r="F336" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="G336" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H336" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I336" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J336" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="K336" t="s">
         <v>1544</v>
@@ -19787,31 +19787,31 @@
         <v>1115</v>
       </c>
       <c r="D337" t="s">
-        <v>1186</v>
+        <v>1256</v>
       </c>
       <c r="E337" t="s">
-        <v>1371</v>
+        <v>1441</v>
       </c>
       <c r="F337" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="G337" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H337" t="s">
         <v>1543</v>
       </c>
       <c r="I337" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J337" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="K337" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="L337" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="M337" t="s">
         <v>1545</v>
@@ -19831,34 +19831,34 @@
         <v>1116</v>
       </c>
       <c r="D338" t="s">
-        <v>1256</v>
+        <v>1337</v>
       </c>
       <c r="E338" t="s">
-        <v>1441</v>
+        <v>1522</v>
       </c>
       <c r="F338" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G338" t="s">
         <v>1540</v>
       </c>
       <c r="H338" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I338" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J338" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K338" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="L338" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="M338" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N338" t="s">
         <v>1547</v>
@@ -19875,34 +19875,34 @@
         <v>1117</v>
       </c>
       <c r="D339" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="E339" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="F339" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G339" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H339" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I339" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J339" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K339" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L339" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="M339" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N339" t="s">
         <v>1547</v>
@@ -19919,34 +19919,34 @@
         <v>1118</v>
       </c>
       <c r="D340" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="E340" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="F340" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G340" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="H340" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I340" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="J340" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K340" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="L340" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="M340" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N340" t="s">
         <v>1547</v>
@@ -19963,34 +19963,34 @@
         <v>1119</v>
       </c>
       <c r="D341" t="s">
-        <v>1339</v>
+        <v>1215</v>
       </c>
       <c r="E341" t="s">
-        <v>1524</v>
+        <v>1400</v>
       </c>
       <c r="F341" t="s">
         <v>1536</v>
       </c>
       <c r="G341" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="H341" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="I341" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="J341" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="K341" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="L341" t="s">
         <v>1545</v>
       </c>
       <c r="M341" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="N341" t="s">
         <v>1547</v>
@@ -20007,10 +20007,10 @@
         <v>1120</v>
       </c>
       <c r="D342" t="s">
-        <v>1215</v>
+        <v>1340</v>
       </c>
       <c r="E342" t="s">
-        <v>1400</v>
+        <v>1525</v>
       </c>
       <c r="F342" t="s">
         <v>1536</v>
@@ -20019,13 +20019,13 @@
         <v>1541</v>
       </c>
       <c r="H342" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I342" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="J342" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="K342" t="s">
         <v>1546</v>
@@ -20034,7 +20034,7 @@
         <v>1545</v>
       </c>
       <c r="M342" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="N342" t="s">
         <v>1547</v>
@@ -20051,34 +20051,34 @@
         <v>1121</v>
       </c>
       <c r="D343" t="s">
-        <v>1340</v>
+        <v>1181</v>
       </c>
       <c r="E343" t="s">
-        <v>1525</v>
+        <v>1366</v>
       </c>
       <c r="F343" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G343" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H343" t="s">
         <v>1540</v>
       </c>
       <c r="I343" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="J343" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="K343" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="L343" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M343" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N343" t="s">
         <v>1547</v>
@@ -20095,34 +20095,34 @@
         <v>1122</v>
       </c>
       <c r="D344" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="E344" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="F344" t="s">
         <v>1534</v>
       </c>
       <c r="G344" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H344" t="s">
         <v>1540</v>
       </c>
       <c r="I344" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J344" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="K344" t="s">
         <v>1544</v>
       </c>
       <c r="L344" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="M344" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="N344" t="s">
         <v>1547</v>
@@ -20139,34 +20139,34 @@
         <v>1123</v>
       </c>
       <c r="D345" t="s">
-        <v>1179</v>
+        <v>1314</v>
       </c>
       <c r="E345" t="s">
-        <v>1364</v>
+        <v>1499</v>
       </c>
       <c r="F345" t="s">
         <v>1534</v>
       </c>
       <c r="G345" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H345" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="I345" t="s">
         <v>1543</v>
       </c>
       <c r="J345" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="K345" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L345" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M345" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N345" t="s">
         <v>1547</v>
@@ -20183,34 +20183,34 @@
         <v>1124</v>
       </c>
       <c r="D346" t="s">
-        <v>1314</v>
+        <v>1341</v>
       </c>
       <c r="E346" t="s">
-        <v>1499</v>
+        <v>1526</v>
       </c>
       <c r="F346" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G346" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H346" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="I346" t="s">
         <v>1543</v>
       </c>
       <c r="J346" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="K346" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="L346" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="M346" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N346" t="s">
         <v>1547</v>
@@ -20227,34 +20227,34 @@
         <v>1125</v>
       </c>
       <c r="D347" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="E347" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="F347" t="s">
         <v>1535</v>
       </c>
       <c r="G347" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="H347" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="I347" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="J347" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="K347" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="L347" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="M347" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N347" t="s">
         <v>1547</v>
@@ -20271,34 +20271,34 @@
         <v>1126</v>
       </c>
       <c r="D348" t="s">
-        <v>1342</v>
+        <v>1247</v>
       </c>
       <c r="E348" t="s">
-        <v>1527</v>
+        <v>1432</v>
       </c>
       <c r="F348" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G348" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="H348" t="s">
         <v>1540</v>
       </c>
       <c r="I348" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="J348" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K348" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L348" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="M348" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N348" t="s">
         <v>1547</v>
@@ -20315,28 +20315,28 @@
         <v>1127</v>
       </c>
       <c r="D349" t="s">
-        <v>1247</v>
+        <v>1212</v>
       </c>
       <c r="E349" t="s">
-        <v>1432</v>
+        <v>1397</v>
       </c>
       <c r="F349" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G349" t="s">
         <v>1544</v>
       </c>
       <c r="H349" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I349" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J349" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="K349" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="L349" t="s">
         <v>1541</v>
@@ -20359,31 +20359,31 @@
         <v>1128</v>
       </c>
       <c r="D350" t="s">
-        <v>1212</v>
+        <v>1288</v>
       </c>
       <c r="E350" t="s">
-        <v>1397</v>
+        <v>1473</v>
       </c>
       <c r="F350" t="s">
         <v>1535</v>
       </c>
       <c r="G350" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="H350" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="I350" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J350" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K350" t="s">
         <v>1542</v>
       </c>
       <c r="L350" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="M350" t="s">
         <v>1545</v>
@@ -20403,31 +20403,31 @@
         <v>1129</v>
       </c>
       <c r="D351" t="s">
-        <v>1288</v>
+        <v>1343</v>
       </c>
       <c r="E351" t="s">
-        <v>1473</v>
+        <v>1528</v>
       </c>
       <c r="F351" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="G351" t="s">
         <v>1540</v>
       </c>
       <c r="H351" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I351" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J351" t="s">
         <v>1541</v>
       </c>
       <c r="K351" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="L351" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M351" t="s">
         <v>1545</v>
@@ -20447,13 +20447,13 @@
         <v>1130</v>
       </c>
       <c r="D352" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E352" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F352" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G352" t="s">
         <v>1540</v>
@@ -20465,16 +20465,16 @@
         <v>1546</v>
       </c>
       <c r="J352" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K352" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L352" t="s">
         <v>1542</v>
       </c>
       <c r="M352" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="N352" t="s">
         <v>1547</v>
@@ -20491,13 +20491,13 @@
         <v>1131</v>
       </c>
       <c r="D353" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E353" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="F353" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="G353" t="s">
         <v>1540</v>
@@ -20509,16 +20509,16 @@
         <v>1546</v>
       </c>
       <c r="J353" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="K353" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L353" t="s">
         <v>1542</v>
       </c>
       <c r="M353" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="N353" t="s">
         <v>1547</v>
@@ -20535,31 +20535,31 @@
         <v>1132</v>
       </c>
       <c r="D354" t="s">
-        <v>1345</v>
+        <v>1210</v>
       </c>
       <c r="E354" t="s">
-        <v>1530</v>
+        <v>1395</v>
       </c>
       <c r="F354" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="G354" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="H354" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I354" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J354" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="K354" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="L354" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M354" t="s">
         <v>1545</v>
@@ -20579,34 +20579,34 @@
         <v>1133</v>
       </c>
       <c r="D355" t="s">
-        <v>1210</v>
+        <v>1346</v>
       </c>
       <c r="E355" t="s">
-        <v>1395</v>
+        <v>1531</v>
       </c>
       <c r="F355" t="s">
         <v>1535</v>
       </c>
       <c r="G355" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H355" t="s">
         <v>1541</v>
       </c>
       <c r="I355" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J355" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="K355" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="L355" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M355" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="N355" t="s">
         <v>1547</v>
@@ -20623,13 +20623,13 @@
         <v>1134</v>
       </c>
       <c r="D356" t="s">
-        <v>1346</v>
+        <v>1188</v>
       </c>
       <c r="E356" t="s">
-        <v>1531</v>
+        <v>1373</v>
       </c>
       <c r="F356" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G356" t="s">
         <v>1540</v>
@@ -20638,16 +20638,16 @@
         <v>1541</v>
       </c>
       <c r="I356" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="J356" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="K356" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="L356" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="M356" t="s">
         <v>1544</v>
@@ -20667,10 +20667,10 @@
         <v>1135</v>
       </c>
       <c r="D357" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="E357" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="F357" t="s">
         <v>1534</v>
@@ -20711,10 +20711,10 @@
         <v>1136</v>
       </c>
       <c r="D358" t="s">
-        <v>1190</v>
+        <v>1338</v>
       </c>
       <c r="E358" t="s">
-        <v>1375</v>
+        <v>1523</v>
       </c>
       <c r="F358" t="s">
         <v>1534</v>
@@ -20723,22 +20723,22 @@
         <v>1540</v>
       </c>
       <c r="H358" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="I358" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="J358" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="K358" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="L358" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="M358" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="N358" t="s">
         <v>1547</v>
@@ -20755,34 +20755,34 @@
         <v>1137</v>
       </c>
       <c r="D359" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="E359" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="F359" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="G359" t="s">
         <v>1540</v>
       </c>
       <c r="H359" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="I359" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J359" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="K359" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="L359" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M359" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N359" t="s">
         <v>1547</v>
@@ -20799,13 +20799,13 @@
         <v>1138</v>
       </c>
       <c r="D360" t="s">
-        <v>1340</v>
+        <v>1347</v>
       </c>
       <c r="E360" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="F360" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="G360" t="s">
         <v>1540</v>
@@ -20814,19 +20814,19 @@
         <v>1541</v>
       </c>
       <c r="I360" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="J360" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="K360" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="L360" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M360" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="N360" t="s">
         <v>1547</v>
@@ -20843,10 +20843,10 @@
         <v>1139</v>
       </c>
       <c r="D361" t="s">
-        <v>1347</v>
+        <v>1301</v>
       </c>
       <c r="E361" t="s">
-        <v>1532</v>
+        <v>1486</v>
       </c>
       <c r="F361" t="s">
         <v>1536</v>
@@ -20855,22 +20855,22 @@
         <v>1540</v>
       </c>
       <c r="H361" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I361" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="J361" t="s">
         <v>1542</v>
       </c>
       <c r="K361" t="s">
-        <v>1545</v>
+        <v>1541</v>
       </c>
       <c r="L361" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="M361" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="N361" t="s">
         <v>1547</v>
@@ -20887,13 +20887,13 @@
         <v>1140</v>
       </c>
       <c r="D362" t="s">
-        <v>1301</v>
+        <v>1262</v>
       </c>
       <c r="E362" t="s">
-        <v>1486</v>
+        <v>1447</v>
       </c>
       <c r="F362" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G362" t="s">
         <v>1540</v>
@@ -20902,19 +20902,19 @@
         <v>1543</v>
       </c>
       <c r="I362" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="J362" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K362" t="s">
         <v>1541</v>
       </c>
       <c r="L362" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M362" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N362" t="s">
         <v>1547</v>
@@ -20931,34 +20931,34 @@
         <v>1141</v>
       </c>
       <c r="D363" t="s">
-        <v>1262</v>
+        <v>1241</v>
       </c>
       <c r="E363" t="s">
-        <v>1447</v>
+        <v>1426</v>
       </c>
       <c r="F363" t="s">
         <v>1535</v>
       </c>
       <c r="G363" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H363" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I363" t="s">
         <v>1544</v>
       </c>
       <c r="J363" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K363" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="L363" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M363" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N363" t="s">
         <v>1547</v>
@@ -20975,34 +20975,34 @@
         <v>1142</v>
       </c>
       <c r="D364" t="s">
-        <v>1241</v>
+        <v>1201</v>
       </c>
       <c r="E364" t="s">
-        <v>1426</v>
+        <v>1386</v>
       </c>
       <c r="F364" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G364" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H364" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="I364" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="J364" t="s">
         <v>1541</v>
       </c>
       <c r="K364" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="L364" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M364" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="N364" t="s">
         <v>1547</v>
@@ -21019,34 +21019,34 @@
         <v>1143</v>
       </c>
       <c r="D365" t="s">
-        <v>1201</v>
+        <v>1319</v>
       </c>
       <c r="E365" t="s">
-        <v>1386</v>
+        <v>1504</v>
       </c>
       <c r="F365" t="s">
         <v>1534</v>
       </c>
       <c r="G365" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="H365" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I365" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="J365" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="K365" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="L365" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M365" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="N365" t="s">
         <v>1547</v>
@@ -21063,10 +21063,10 @@
         <v>1144</v>
       </c>
       <c r="D366" t="s">
-        <v>1319</v>
+        <v>1265</v>
       </c>
       <c r="E366" t="s">
-        <v>1504</v>
+        <v>1450</v>
       </c>
       <c r="F366" t="s">
         <v>1534</v>
@@ -21078,16 +21078,16 @@
         <v>1543</v>
       </c>
       <c r="I366" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="J366" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K366" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L366" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="M366" t="s">
         <v>1541</v>
@@ -21107,34 +21107,34 @@
         <v>1145</v>
       </c>
       <c r="D367" t="s">
-        <v>1265</v>
+        <v>1295</v>
       </c>
       <c r="E367" t="s">
-        <v>1450</v>
+        <v>1480</v>
       </c>
       <c r="F367" t="s">
         <v>1534</v>
       </c>
       <c r="G367" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H367" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I367" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="J367" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="K367" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="L367" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="M367" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="N367" t="s">
         <v>1547</v>
@@ -21151,34 +21151,34 @@
         <v>1146</v>
       </c>
       <c r="D368" t="s">
-        <v>1295</v>
+        <v>1250</v>
       </c>
       <c r="E368" t="s">
-        <v>1480</v>
+        <v>1435</v>
       </c>
       <c r="F368" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G368" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H368" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I368" t="s">
         <v>1540</v>
       </c>
       <c r="J368" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K368" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="L368" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="M368" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N368" t="s">
         <v>1547</v>
@@ -21195,34 +21195,34 @@
         <v>1147</v>
       </c>
       <c r="D369" t="s">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="E369" t="s">
-        <v>1435</v>
+        <v>1425</v>
       </c>
       <c r="F369" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G369" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H369" t="s">
         <v>1543</v>
       </c>
       <c r="I369" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="J369" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K369" t="s">
         <v>1544</v>
       </c>
       <c r="L369" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="M369" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N369" t="s">
         <v>1547</v>
@@ -21239,34 +21239,34 @@
         <v>1148</v>
       </c>
       <c r="D370" t="s">
-        <v>1240</v>
+        <v>1188</v>
       </c>
       <c r="E370" t="s">
-        <v>1425</v>
+        <v>1373</v>
       </c>
       <c r="F370" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G370" t="s">
         <v>1540</v>
       </c>
       <c r="H370" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I370" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="J370" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="K370" t="s">
         <v>1544</v>
       </c>
       <c r="L370" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="M370" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N370" t="s">
         <v>1547</v>
@@ -21283,34 +21283,34 @@
         <v>1149</v>
       </c>
       <c r="D371" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="E371" t="s">
-        <v>1373</v>
+        <v>1389</v>
       </c>
       <c r="F371" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="G371" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="H371" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="I371" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J371" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K371" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="L371" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="M371" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="N371" t="s">
         <v>1547</v>
@@ -21327,34 +21327,34 @@
         <v>1150</v>
       </c>
       <c r="D372" t="s">
-        <v>1204</v>
+        <v>1252</v>
       </c>
       <c r="E372" t="s">
-        <v>1389</v>
+        <v>1437</v>
       </c>
       <c r="F372" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G372" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="H372" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I372" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="J372" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="K372" t="s">
         <v>1542</v>
       </c>
       <c r="L372" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M372" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="N372" t="s">
         <v>1547</v>
@@ -21371,19 +21371,19 @@
         <v>1151</v>
       </c>
       <c r="D373" t="s">
-        <v>1252</v>
+        <v>1271</v>
       </c>
       <c r="E373" t="s">
-        <v>1437</v>
+        <v>1456</v>
       </c>
       <c r="F373" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="G373" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H373" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="I373" t="s">
         <v>1543</v>
@@ -21392,10 +21392,10 @@
         <v>1546</v>
       </c>
       <c r="K373" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="L373" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M373" t="s">
         <v>1545</v>
@@ -21415,34 +21415,34 @@
         <v>1152</v>
       </c>
       <c r="D374" t="s">
-        <v>1271</v>
+        <v>1185</v>
       </c>
       <c r="E374" t="s">
-        <v>1456</v>
+        <v>1370</v>
       </c>
       <c r="F374" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="G374" t="s">
         <v>1541</v>
       </c>
       <c r="H374" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="I374" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J374" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="K374" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="L374" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="M374" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N374" t="s">
         <v>1547</v>
@@ -21459,34 +21459,34 @@
         <v>1153</v>
       </c>
       <c r="D375" t="s">
-        <v>1185</v>
+        <v>1346</v>
       </c>
       <c r="E375" t="s">
-        <v>1370</v>
+        <v>1531</v>
       </c>
       <c r="F375" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G375" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="H375" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="I375" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="J375" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K375" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="L375" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="M375" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="N375" t="s">
         <v>1547</v>
@@ -21503,34 +21503,34 @@
         <v>1154</v>
       </c>
       <c r="D376" t="s">
-        <v>1346</v>
+        <v>1231</v>
       </c>
       <c r="E376" t="s">
-        <v>1531</v>
+        <v>1416</v>
       </c>
       <c r="F376" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G376" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
       <c r="H376" t="s">
         <v>1543</v>
       </c>
       <c r="I376" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="J376" t="s">
         <v>1542</v>
       </c>
       <c r="K376" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="L376" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="M376" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="N376" t="s">
         <v>1547</v>
@@ -21547,34 +21547,34 @@
         <v>1155</v>
       </c>
       <c r="D377" t="s">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="E377" t="s">
-        <v>1416</v>
+        <v>1425</v>
       </c>
       <c r="F377" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="G377" t="s">
         <v>1540</v>
       </c>
       <c r="H377" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="I377" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="J377" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="K377" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="L377" t="s">
         <v>1544</v>
       </c>
       <c r="M377" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N377" t="s">
         <v>1547</v>
@@ -21591,34 +21591,34 @@
         <v>1156</v>
       </c>
       <c r="D378" t="s">
-        <v>1240</v>
+        <v>1200</v>
       </c>
       <c r="E378" t="s">
-        <v>1425</v>
+        <v>1385</v>
       </c>
       <c r="F378" t="s">
         <v>1535</v>
       </c>
       <c r="G378" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="H378" t="s">
-        <v>1541</v>
+        <v>1546</v>
       </c>
       <c r="I378" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="J378" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K378" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="L378" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="M378" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N378" t="s">
         <v>1547</v>
@@ -21635,31 +21635,31 @@
         <v>1157</v>
       </c>
       <c r="D379" t="s">
-        <v>1200</v>
+        <v>1244</v>
       </c>
       <c r="E379" t="s">
-        <v>1385</v>
+        <v>1429</v>
       </c>
       <c r="F379" t="s">
         <v>1535</v>
       </c>
       <c r="G379" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H379" t="s">
-        <v>1546</v>
+        <v>1542</v>
       </c>
       <c r="I379" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="J379" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K379" t="s">
         <v>1544</v>
       </c>
       <c r="L379" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="M379" t="s">
         <v>1545</v>
@@ -21679,31 +21679,31 @@
         <v>1158</v>
       </c>
       <c r="D380" t="s">
-        <v>1244</v>
+        <v>1211</v>
       </c>
       <c r="E380" t="s">
-        <v>1429</v>
+        <v>1396</v>
       </c>
       <c r="F380" t="s">
         <v>1535</v>
       </c>
       <c r="G380" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H380" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="I380" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="J380" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="K380" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="L380" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="M380" t="s">
         <v>1545</v>
@@ -21723,34 +21723,34 @@
         <v>1159</v>
       </c>
       <c r="D381" t="s">
-        <v>1211</v>
+        <v>1297</v>
       </c>
       <c r="E381" t="s">
-        <v>1396</v>
+        <v>1482</v>
       </c>
       <c r="F381" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G381" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H381" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="I381" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="J381" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="K381" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="L381" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="M381" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="N381" t="s">
         <v>1547</v>
@@ -21767,10 +21767,10 @@
         <v>1160</v>
       </c>
       <c r="D382" t="s">
-        <v>1297</v>
+        <v>1348</v>
       </c>
       <c r="E382" t="s">
-        <v>1482</v>
+        <v>1533</v>
       </c>
       <c r="F382" t="s">
         <v>1534</v>
@@ -21811,10 +21811,10 @@
         <v>1161</v>
       </c>
       <c r="D383" t="s">
-        <v>1348</v>
+        <v>1285</v>
       </c>
       <c r="E383" t="s">
-        <v>1533</v>
+        <v>1470</v>
       </c>
       <c r="F383" t="s">
         <v>1534</v>
@@ -21823,22 +21823,22 @@
         <v>1541</v>
       </c>
       <c r="H383" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="I383" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="J383" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="K383" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="L383" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="M383" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="N383" t="s">
         <v>1547</v>
@@ -21855,34 +21855,34 @@
         <v>1162</v>
       </c>
       <c r="D384" t="s">
-        <v>1285</v>
+        <v>1194</v>
       </c>
       <c r="E384" t="s">
-        <v>1470</v>
+        <v>1379</v>
       </c>
       <c r="F384" t="s">
         <v>1534</v>
       </c>
       <c r="G384" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H384" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="I384" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="J384" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="K384" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="L384" t="s">
         <v>1544</v>
       </c>
       <c r="M384" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="N384" t="s">
         <v>1547</v>
@@ -21899,34 +21899,34 @@
         <v>1163</v>
       </c>
       <c r="D385">
-        <v>1448</v>
+        <v>1300</v>
       </c>
       <c r="E385">
-        <v>72.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="F385" t="s">
         <v>1534</v>
       </c>
       <c r="G385" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H385" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="I385" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="J385" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K385" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="L385" t="s">
         <v>1544</v>
       </c>
       <c r="M385" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="N385" t="s">
         <v>1547</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -784,447 +784,447 @@
     <t>نورهان محمود محمد احمد</t>
   </si>
   <si>
+    <t>عمرو محمد أحمد دردير</t>
+  </si>
+  <si>
+    <t>محمد احمد حسن محمد</t>
+  </si>
+  <si>
+    <t>اسلام عبد العال عبد السلام عبد الحميد</t>
+  </si>
+  <si>
+    <t>حسام احمد عبد المطلب احمد</t>
+  </si>
+  <si>
+    <t>حازم ياسر عبد النبى عبد الوهاب</t>
+  </si>
+  <si>
+    <t>أحمد عاطف حسين محمد</t>
+  </si>
+  <si>
+    <t>فاتن حماد عبد الحليم على</t>
+  </si>
+  <si>
+    <t>كريم جمال سعيد على</t>
+  </si>
+  <si>
+    <t>يحيى صفوت يحيى رمضان</t>
+  </si>
+  <si>
+    <t>احمد محمود عبدالمنعم احمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد محمود أحمد</t>
+  </si>
+  <si>
+    <t>زياد محمد رجائى محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن اشرف موسى هاشم</t>
+  </si>
+  <si>
+    <t>دميانه أشرف ماهر اسحق</t>
+  </si>
+  <si>
+    <t>زياد أشرف محمد محمود</t>
+  </si>
+  <si>
+    <t>ابراهيم محمد محمد ذكى</t>
+  </si>
+  <si>
+    <t>اميره حمدى مصطفى محمد</t>
+  </si>
+  <si>
+    <t>يوسف مصطفي سيد يوسف</t>
+  </si>
+  <si>
+    <t>رانيا سيد صلاح الدين على</t>
+  </si>
+  <si>
+    <t>حازم عباس خليفة عباس</t>
+  </si>
+  <si>
+    <t>رقيه على محمد خلف</t>
+  </si>
+  <si>
+    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
+  </si>
+  <si>
+    <t>ابراهيم محمود محمد عبدالنعيم</t>
+  </si>
+  <si>
+    <t>بهاء الدين محمد ابراهيم على</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>يوسف احمد سمير محمد</t>
+  </si>
+  <si>
+    <t>محمد رجب لطفى كامل</t>
+  </si>
+  <si>
+    <t>احمد طارق محمد محمود</t>
+  </si>
+  <si>
+    <t>عبدالله محمد سيد صادق</t>
+  </si>
+  <si>
+    <t>سهيله عبد القادر احمد عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد توفيق محمد محمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>مريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>شهد حسين محمود صابر</t>
+  </si>
+  <si>
+    <t>محمد سرحان محمد زكى</t>
+  </si>
+  <si>
+    <t>لمياء عبد القادر محمد فتحى</t>
+  </si>
+  <si>
+    <t>أميمة رأفت محمود احمد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>احمد رمضان محمد عبد الحميد</t>
+  </si>
+  <si>
+    <t>كريم محمد عبد الوهاب عيد</t>
+  </si>
+  <si>
+    <t>عمر رضا تونى طلبه</t>
+  </si>
+  <si>
+    <t>عبدالله ناصر أنور عبد المجيد</t>
+  </si>
+  <si>
+    <t>اندرو محروس مختار مهنى</t>
+  </si>
+  <si>
+    <t>فاطمه ناجى عبد السلام حسن</t>
+  </si>
+  <si>
+    <t>ماركو مجدى مكرم فريد</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
     <t>محمد ناصف عبدالعظيم محمد</t>
   </si>
   <si>
-    <t>عمرو محمد أحمد دردير</t>
-  </si>
-  <si>
-    <t>محمد احمد حسن محمد</t>
-  </si>
-  <si>
-    <t>اسلام عبد العال عبد السلام عبد الحميد</t>
-  </si>
-  <si>
-    <t>حسام احمد عبد المطلب احمد</t>
-  </si>
-  <si>
-    <t>حازم ياسر عبد النبى عبد الوهاب</t>
-  </si>
-  <si>
-    <t>أحمد عاطف حسين محمد</t>
-  </si>
-  <si>
-    <t>فاتن حماد عبد الحليم على</t>
-  </si>
-  <si>
-    <t>كريم جمال سعيد على</t>
-  </si>
-  <si>
-    <t>يحيى صفوت يحيى رمضان</t>
-  </si>
-  <si>
-    <t>احمد محمود عبدالمنعم احمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد محمود أحمد</t>
-  </si>
-  <si>
-    <t>زياد محمد رجائى محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن اشرف موسى هاشم</t>
-  </si>
-  <si>
-    <t>دميانه أشرف ماهر اسحق</t>
-  </si>
-  <si>
-    <t>زياد أشرف محمد محمود</t>
-  </si>
-  <si>
-    <t>ابراهيم محمد محمد ذكى</t>
-  </si>
-  <si>
-    <t>اميره حمدى مصطفى محمد</t>
-  </si>
-  <si>
-    <t>يوسف مصطفي سيد يوسف</t>
-  </si>
-  <si>
-    <t>رانيا سيد صلاح الدين على</t>
-  </si>
-  <si>
-    <t>حازم عباس خليفة عباس</t>
-  </si>
-  <si>
-    <t>رقيه على محمد خلف</t>
-  </si>
-  <si>
-    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
-  </si>
-  <si>
-    <t>ابراهيم محمود محمد عبدالنعيم</t>
-  </si>
-  <si>
-    <t>بهاء الدين محمد ابراهيم على</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>يوسف احمد سمير محمد</t>
-  </si>
-  <si>
-    <t>محمد رجب لطفى كامل</t>
-  </si>
-  <si>
-    <t>احمد طارق محمد محمود</t>
-  </si>
-  <si>
-    <t>عبدالله محمد سيد صادق</t>
-  </si>
-  <si>
-    <t>سهيله عبد القادر احمد عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد توفيق محمد محمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>مريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>شهد حسين محمود صابر</t>
-  </si>
-  <si>
-    <t>محمد سرحان محمد زكى</t>
-  </si>
-  <si>
-    <t>لمياء عبد القادر محمد فتحى</t>
-  </si>
-  <si>
-    <t>أميمة رأفت محمود احمد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>احمد رمضان محمد عبد الحميد</t>
-  </si>
-  <si>
-    <t>كريم محمد عبد الوهاب عيد</t>
-  </si>
-  <si>
-    <t>عمر رضا تونى طلبه</t>
-  </si>
-  <si>
-    <t>عبدالله ناصر أنور عبد المجيد</t>
-  </si>
-  <si>
-    <t>اندرو محروس مختار مهنى</t>
-  </si>
-  <si>
-    <t>فاطمه ناجى عبد السلام حسن</t>
-  </si>
-  <si>
-    <t>ماركو مجدى مكرم فريد</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -1951,444 +1951,444 @@
     <t>30303262400287</t>
   </si>
   <si>
+    <t>30507152404052</t>
+  </si>
+  <si>
+    <t>30205122402776</t>
+  </si>
+  <si>
+    <t>30511242401912</t>
+  </si>
+  <si>
+    <t>30512202400154</t>
+  </si>
+  <si>
+    <t>30411012411337</t>
+  </si>
+  <si>
+    <t>٣٠٣٠٤١٣٢٤٠٠٦٠٥</t>
+  </si>
+  <si>
+    <t>30507232402859</t>
+  </si>
+  <si>
+    <t>30305232401877</t>
+  </si>
+  <si>
+    <t>30102042403077</t>
+  </si>
+  <si>
+    <t>30411062404552</t>
+  </si>
+  <si>
+    <t>30408062402354</t>
+  </si>
+  <si>
+    <t>30307102401398</t>
+  </si>
+  <si>
+    <t>30507032403826</t>
+  </si>
+  <si>
+    <t>30504282401757</t>
+  </si>
+  <si>
+    <t>30504142403393</t>
+  </si>
+  <si>
+    <t>30407122401208</t>
+  </si>
+  <si>
+    <t>30506282400915</t>
+  </si>
+  <si>
+    <t>30409222403367</t>
+  </si>
+  <si>
+    <t>30507012411733</t>
+  </si>
+  <si>
+    <t>30411102404968</t>
+  </si>
+  <si>
+    <t>30310012403406</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
+  </si>
+  <si>
+    <t>30506082400619</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30503242401413</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
+  </si>
+  <si>
+    <t>30507262401954</t>
+  </si>
+  <si>
+    <t>30405262402457</t>
+  </si>
+  <si>
+    <t>30410312400403</t>
+  </si>
+  <si>
+    <t>30506152402932</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30509052401709</t>
+  </si>
+  <si>
+    <t>30408182401521</t>
+  </si>
+  <si>
+    <t>30410232401859</t>
+  </si>
+  <si>
+    <t>30409222402263</t>
+  </si>
+  <si>
+    <t>30308062400144</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30302142401658</t>
+  </si>
+  <si>
+    <t>30506272400259</t>
+  </si>
+  <si>
+    <t>30409012413599</t>
+  </si>
+  <si>
+    <t>30601162402453</t>
+  </si>
+  <si>
+    <t>30310012402973</t>
+  </si>
+  <si>
+    <t>30506170300209</t>
+  </si>
+  <si>
+    <t>30409172401791</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
     <t>30504152400759</t>
   </si>
   <si>
-    <t>30507152404052</t>
-  </si>
-  <si>
-    <t>30205122402776</t>
-  </si>
-  <si>
-    <t>30511242401912</t>
-  </si>
-  <si>
-    <t>30512202400154</t>
-  </si>
-  <si>
-    <t>30411012411337</t>
-  </si>
-  <si>
-    <t>٣٠٣٠٤١٣٢٤٠٠٦٠٥</t>
-  </si>
-  <si>
-    <t>30507232402859</t>
-  </si>
-  <si>
-    <t>30305232401877</t>
-  </si>
-  <si>
-    <t>30102042403077</t>
-  </si>
-  <si>
-    <t>30411062404552</t>
-  </si>
-  <si>
-    <t>30408062402354</t>
-  </si>
-  <si>
-    <t>30307102401398</t>
-  </si>
-  <si>
-    <t>30507032403826</t>
-  </si>
-  <si>
-    <t>30504282401757</t>
-  </si>
-  <si>
-    <t>30504142403393</t>
-  </si>
-  <si>
-    <t>30407122401208</t>
-  </si>
-  <si>
-    <t>30506282400915</t>
-  </si>
-  <si>
-    <t>30409222403367</t>
-  </si>
-  <si>
-    <t>30507012411733</t>
-  </si>
-  <si>
-    <t>30411102404968</t>
-  </si>
-  <si>
-    <t>30310012403406</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
-  </si>
-  <si>
-    <t>30506082400619</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30503242401413</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
-  </si>
-  <si>
-    <t>30507262401954</t>
-  </si>
-  <si>
-    <t>30405262402457</t>
-  </si>
-  <si>
-    <t>30410312400403</t>
-  </si>
-  <si>
-    <t>30506152402932</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30509052401709</t>
-  </si>
-  <si>
-    <t>30408182401521</t>
-  </si>
-  <si>
-    <t>30410232401859</t>
-  </si>
-  <si>
-    <t>30409222402263</t>
-  </si>
-  <si>
-    <t>30308062400144</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30302142401658</t>
-  </si>
-  <si>
-    <t>30506272400259</t>
-  </si>
-  <si>
-    <t>30409012413599</t>
-  </si>
-  <si>
-    <t>30601162402453</t>
-  </si>
-  <si>
-    <t>30310012402973</t>
-  </si>
-  <si>
-    <t>30506170300209</t>
-  </si>
-  <si>
-    <t>30409172401791</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3115,9 +3115,6 @@
     <t>01558260721</t>
   </si>
   <si>
-    <t>1129974304</t>
-  </si>
-  <si>
     <t>01097343197</t>
   </si>
   <si>
@@ -3551,6 +3548,9 @@
   </si>
   <si>
     <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
   </si>
   <si>
     <t>1353</t>
@@ -15758,25 +15758,25 @@
         <v>1033</v>
       </c>
       <c r="D244" t="s">
-        <v>1191</v>
+        <v>1322</v>
       </c>
       <c r="E244" t="s">
-        <v>1379</v>
+        <v>1510</v>
       </c>
       <c r="F244" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G244" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H244" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I244" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J244" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K244" t="s">
         <v>1565</v>
@@ -15785,7 +15785,7 @@
         <v>1566</v>
       </c>
       <c r="M244" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N244" t="s">
         <v>1568</v>
@@ -15802,34 +15802,34 @@
         <v>1034</v>
       </c>
       <c r="D245" t="s">
-        <v>1322</v>
+        <v>1262</v>
       </c>
       <c r="E245" t="s">
-        <v>1510</v>
+        <v>1450</v>
       </c>
       <c r="F245" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G245" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H245" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I245" t="s">
         <v>1564</v>
       </c>
       <c r="J245" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K245" t="s">
         <v>1565</v>
       </c>
       <c r="L245" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M245" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N245" t="s">
         <v>1568</v>
@@ -15840,16 +15840,16 @@
         <v>258</v>
       </c>
       <c r="B246" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C246" t="s">
         <v>1035</v>
       </c>
       <c r="D246" t="s">
-        <v>1262</v>
+        <v>1315</v>
       </c>
       <c r="E246" t="s">
-        <v>1450</v>
+        <v>1503</v>
       </c>
       <c r="F246" t="s">
         <v>1555</v>
@@ -15858,22 +15858,22 @@
         <v>1561</v>
       </c>
       <c r="H246" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I246" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J246" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K246" t="s">
         <v>1565</v>
       </c>
       <c r="L246" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M246" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N246" t="s">
         <v>1568</v>
@@ -15890,34 +15890,34 @@
         <v>1036</v>
       </c>
       <c r="D247" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
       <c r="E247" t="s">
-        <v>1503</v>
+        <v>1512</v>
       </c>
       <c r="F247" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G247" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H247" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I247" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J247" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K247" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L247" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="M247" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N247" t="s">
         <v>1568</v>
@@ -15934,13 +15934,13 @@
         <v>1037</v>
       </c>
       <c r="D248" t="s">
-        <v>1324</v>
+        <v>1219</v>
       </c>
       <c r="E248" t="s">
-        <v>1512</v>
+        <v>1407</v>
       </c>
       <c r="F248" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G248" t="s">
         <v>1563</v>
@@ -15978,34 +15978,34 @@
         <v>1038</v>
       </c>
       <c r="D249" t="s">
-        <v>1219</v>
+        <v>1325</v>
       </c>
       <c r="E249" t="s">
-        <v>1407</v>
+        <v>1513</v>
       </c>
       <c r="F249" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G249" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H249" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I249" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J249" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K249" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L249" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M249" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N249" t="s">
         <v>1568</v>
@@ -16022,13 +16022,13 @@
         <v>1039</v>
       </c>
       <c r="D250" t="s">
-        <v>1325</v>
+        <v>1216</v>
       </c>
       <c r="E250" t="s">
-        <v>1513</v>
+        <v>1404</v>
       </c>
       <c r="F250" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G250" t="s">
         <v>1561</v>
@@ -16037,16 +16037,16 @@
         <v>1564</v>
       </c>
       <c r="I250" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J250" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K250" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L250" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M250" t="s">
         <v>1566</v>
@@ -16066,13 +16066,13 @@
         <v>1040</v>
       </c>
       <c r="D251" t="s">
-        <v>1216</v>
+        <v>1326</v>
       </c>
       <c r="E251" t="s">
-        <v>1404</v>
+        <v>1514</v>
       </c>
       <c r="F251" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G251" t="s">
         <v>1561</v>
@@ -16084,16 +16084,16 @@
         <v>1562</v>
       </c>
       <c r="J251" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K251" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L251" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M251" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N251" t="s">
         <v>1568</v>
@@ -16110,13 +16110,13 @@
         <v>1041</v>
       </c>
       <c r="D252" t="s">
-        <v>1326</v>
+        <v>1224</v>
       </c>
       <c r="E252" t="s">
-        <v>1514</v>
+        <v>1412</v>
       </c>
       <c r="F252" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G252" t="s">
         <v>1561</v>
@@ -16125,13 +16125,13 @@
         <v>1564</v>
       </c>
       <c r="I252" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J252" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K252" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L252" t="s">
         <v>1565</v>
@@ -16154,13 +16154,13 @@
         <v>1042</v>
       </c>
       <c r="D253" t="s">
-        <v>1224</v>
+        <v>1327</v>
       </c>
       <c r="E253" t="s">
-        <v>1412</v>
+        <v>1515</v>
       </c>
       <c r="F253" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="G253" t="s">
         <v>1561</v>
@@ -16169,19 +16169,19 @@
         <v>1564</v>
       </c>
       <c r="I253" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J253" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K253" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L253" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M253" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N253" t="s">
         <v>1568</v>
@@ -16198,34 +16198,34 @@
         <v>1043</v>
       </c>
       <c r="D254" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E254" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F254" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G254" t="s">
         <v>1561</v>
       </c>
       <c r="H254" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="I254" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J254" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K254" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L254" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M254" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N254" t="s">
         <v>1568</v>
@@ -16242,10 +16242,10 @@
         <v>1044</v>
       </c>
       <c r="D255" t="s">
-        <v>1328</v>
+        <v>1214</v>
       </c>
       <c r="E255" t="s">
-        <v>1516</v>
+        <v>1402</v>
       </c>
       <c r="F255" t="s">
         <v>1556</v>
@@ -16254,22 +16254,22 @@
         <v>1561</v>
       </c>
       <c r="H255" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="I255" t="s">
         <v>1567</v>
       </c>
       <c r="J255" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K255" t="s">
         <v>1562</v>
       </c>
       <c r="L255" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M255" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N255" t="s">
         <v>1568</v>
@@ -16286,10 +16286,10 @@
         <v>1045</v>
       </c>
       <c r="D256" t="s">
-        <v>1214</v>
+        <v>1269</v>
       </c>
       <c r="E256" t="s">
-        <v>1402</v>
+        <v>1457</v>
       </c>
       <c r="F256" t="s">
         <v>1556</v>
@@ -16301,10 +16301,10 @@
         <v>1564</v>
       </c>
       <c r="I256" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J256" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K256" t="s">
         <v>1562</v>
@@ -16313,7 +16313,7 @@
         <v>1566</v>
       </c>
       <c r="M256" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N256" t="s">
         <v>1568</v>
@@ -16330,10 +16330,10 @@
         <v>1046</v>
       </c>
       <c r="D257" t="s">
-        <v>1269</v>
+        <v>1329</v>
       </c>
       <c r="E257" t="s">
-        <v>1457</v>
+        <v>1517</v>
       </c>
       <c r="F257" t="s">
         <v>1556</v>
@@ -16342,22 +16342,22 @@
         <v>1561</v>
       </c>
       <c r="H257" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I257" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J257" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K257" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L257" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M257" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N257" t="s">
         <v>1568</v>
@@ -16374,34 +16374,34 @@
         <v>1047</v>
       </c>
       <c r="D258" t="s">
-        <v>1329</v>
+        <v>1225</v>
       </c>
       <c r="E258" t="s">
-        <v>1517</v>
+        <v>1413</v>
       </c>
       <c r="F258" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G258" t="s">
         <v>1561</v>
       </c>
       <c r="H258" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I258" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J258" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="K258" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L258" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M258" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N258" t="s">
         <v>1568</v>
@@ -16418,10 +16418,10 @@
         <v>1048</v>
       </c>
       <c r="D259" t="s">
-        <v>1225</v>
+        <v>1245</v>
       </c>
       <c r="E259" t="s">
-        <v>1413</v>
+        <v>1433</v>
       </c>
       <c r="F259" t="s">
         <v>1555</v>
@@ -16442,10 +16442,10 @@
         <v>1562</v>
       </c>
       <c r="L259" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M259" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N259" t="s">
         <v>1568</v>
@@ -16462,34 +16462,34 @@
         <v>1049</v>
       </c>
       <c r="D260" t="s">
-        <v>1245</v>
+        <v>1300</v>
       </c>
       <c r="E260" t="s">
-        <v>1433</v>
+        <v>1488</v>
       </c>
       <c r="F260" t="s">
         <v>1555</v>
       </c>
       <c r="G260" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H260" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I260" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J260" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K260" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L260" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M260" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N260" t="s">
         <v>1568</v>
@@ -16506,34 +16506,34 @@
         <v>1050</v>
       </c>
       <c r="D261" t="s">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="E261" t="s">
-        <v>1488</v>
+        <v>1518</v>
       </c>
       <c r="F261" t="s">
         <v>1555</v>
       </c>
       <c r="G261" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H261" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I261" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J261" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K261" t="s">
         <v>1566</v>
       </c>
       <c r="L261" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M261" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N261" t="s">
         <v>1568</v>
@@ -16550,10 +16550,10 @@
         <v>1051</v>
       </c>
       <c r="D262" t="s">
-        <v>1330</v>
+        <v>1278</v>
       </c>
       <c r="E262" t="s">
-        <v>1518</v>
+        <v>1466</v>
       </c>
       <c r="F262" t="s">
         <v>1555</v>
@@ -16565,19 +16565,19 @@
         <v>1564</v>
       </c>
       <c r="I262" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J262" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K262" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L262" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M262" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N262" t="s">
         <v>1568</v>
@@ -16594,10 +16594,10 @@
         <v>1052</v>
       </c>
       <c r="D263" t="s">
-        <v>1278</v>
+        <v>1331</v>
       </c>
       <c r="E263" t="s">
-        <v>1466</v>
+        <v>1519</v>
       </c>
       <c r="F263" t="s">
         <v>1555</v>
@@ -16606,13 +16606,13 @@
         <v>1561</v>
       </c>
       <c r="H263" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I263" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J263" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K263" t="s">
         <v>1565</v>
@@ -16621,7 +16621,7 @@
         <v>1566</v>
       </c>
       <c r="M263" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N263" t="s">
         <v>1568</v>
@@ -16638,13 +16638,13 @@
         <v>1053</v>
       </c>
       <c r="D264" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="E264" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F264" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G264" t="s">
         <v>1561</v>
@@ -16656,16 +16656,16 @@
         <v>1564</v>
       </c>
       <c r="J264" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K264" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L264" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M264" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N264" t="s">
         <v>1568</v>
@@ -16682,19 +16682,19 @@
         <v>1054</v>
       </c>
       <c r="D265" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="E265" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F265" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G265" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H265" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="I265" t="s">
         <v>1564</v>
@@ -16706,7 +16706,7 @@
         <v>1562</v>
       </c>
       <c r="L265" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M265" t="s">
         <v>1566</v>
@@ -16726,31 +16726,31 @@
         <v>1055</v>
       </c>
       <c r="D266" t="s">
-        <v>1333</v>
+        <v>1262</v>
       </c>
       <c r="E266" t="s">
-        <v>1521</v>
+        <v>1450</v>
       </c>
       <c r="F266" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G266" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H266" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I266" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J266" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K266" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L266" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M266" t="s">
         <v>1566</v>
@@ -16770,28 +16770,28 @@
         <v>1056</v>
       </c>
       <c r="D267" t="s">
-        <v>1262</v>
+        <v>1329</v>
       </c>
       <c r="E267" t="s">
-        <v>1450</v>
+        <v>1517</v>
       </c>
       <c r="F267" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G267" t="s">
         <v>1561</v>
       </c>
       <c r="H267" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I267" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J267" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K267" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L267" t="s">
         <v>1565</v>
@@ -16814,34 +16814,34 @@
         <v>1057</v>
       </c>
       <c r="D268" t="s">
-        <v>1329</v>
+        <v>1246</v>
       </c>
       <c r="E268" t="s">
-        <v>1517</v>
+        <v>1434</v>
       </c>
       <c r="F268" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G268" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H268" t="s">
         <v>1564</v>
       </c>
       <c r="I268" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J268" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K268" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L268" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M268" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N268" t="s">
         <v>1568</v>
@@ -16858,25 +16858,25 @@
         <v>1058</v>
       </c>
       <c r="D269" t="s">
-        <v>1246</v>
+        <v>1265</v>
       </c>
       <c r="E269" t="s">
-        <v>1434</v>
+        <v>1453</v>
       </c>
       <c r="F269" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G269" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H269" t="s">
         <v>1564</v>
       </c>
       <c r="I269" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J269" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K269" t="s">
         <v>1565</v>
@@ -16885,7 +16885,7 @@
         <v>1566</v>
       </c>
       <c r="M269" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N269" t="s">
         <v>1568</v>
@@ -16902,34 +16902,34 @@
         <v>1059</v>
       </c>
       <c r="D270" t="s">
-        <v>1265</v>
+        <v>1240</v>
       </c>
       <c r="E270" t="s">
-        <v>1453</v>
+        <v>1428</v>
       </c>
       <c r="F270" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G270" t="s">
         <v>1561</v>
       </c>
       <c r="H270" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I270" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J270" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K270" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L270" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M270" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N270" t="s">
         <v>1568</v>
@@ -16946,10 +16946,10 @@
         <v>1060</v>
       </c>
       <c r="D271" t="s">
-        <v>1240</v>
+        <v>1194</v>
       </c>
       <c r="E271" t="s">
-        <v>1428</v>
+        <v>1382</v>
       </c>
       <c r="F271" t="s">
         <v>1555</v>
@@ -16961,19 +16961,19 @@
         <v>1562</v>
       </c>
       <c r="I271" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J271" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K271" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L271" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M271" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N271" t="s">
         <v>1568</v>
@@ -16990,10 +16990,10 @@
         <v>1061</v>
       </c>
       <c r="D272" t="s">
-        <v>1194</v>
+        <v>1241</v>
       </c>
       <c r="E272" t="s">
-        <v>1382</v>
+        <v>1429</v>
       </c>
       <c r="F272" t="s">
         <v>1555</v>
@@ -17005,19 +17005,19 @@
         <v>1562</v>
       </c>
       <c r="I272" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J272" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K272" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L272" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M272" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N272" t="s">
         <v>1568</v>
@@ -17034,22 +17034,22 @@
         <v>1062</v>
       </c>
       <c r="D273" t="s">
-        <v>1241</v>
+        <v>1310</v>
       </c>
       <c r="E273" t="s">
-        <v>1429</v>
+        <v>1498</v>
       </c>
       <c r="F273" t="s">
         <v>1555</v>
       </c>
       <c r="G273" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H273" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I273" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J273" t="s">
         <v>1567</v>
@@ -17058,7 +17058,7 @@
         <v>1563</v>
       </c>
       <c r="L273" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M273" t="s">
         <v>1566</v>
@@ -17075,37 +17075,37 @@
         <v>674</v>
       </c>
       <c r="C274" t="s">
-        <v>1063</v>
+        <v>824</v>
       </c>
       <c r="D274" t="s">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="E274" t="s">
-        <v>1498</v>
+        <v>1522</v>
       </c>
       <c r="F274" t="s">
         <v>1555</v>
       </c>
       <c r="G274" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H274" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I274" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J274" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K274" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L274" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M274" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N274" t="s">
         <v>1568</v>
@@ -17119,13 +17119,13 @@
         <v>675</v>
       </c>
       <c r="C275" t="s">
-        <v>824</v>
+        <v>1063</v>
       </c>
       <c r="D275" t="s">
-        <v>1334</v>
+        <v>1300</v>
       </c>
       <c r="E275" t="s">
-        <v>1522</v>
+        <v>1488</v>
       </c>
       <c r="F275" t="s">
         <v>1555</v>
@@ -17134,22 +17134,22 @@
         <v>1561</v>
       </c>
       <c r="H275" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I275" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J275" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K275" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L275" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M275" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N275" t="s">
         <v>1568</v>
@@ -17166,34 +17166,34 @@
         <v>1064</v>
       </c>
       <c r="D276" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="E276" t="s">
-        <v>1488</v>
+        <v>1459</v>
       </c>
       <c r="F276" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G276" t="s">
         <v>1561</v>
       </c>
       <c r="H276" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I276" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J276" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K276" t="s">
         <v>1563</v>
       </c>
       <c r="L276" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M276" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N276" t="s">
         <v>1568</v>
@@ -17210,13 +17210,13 @@
         <v>1065</v>
       </c>
       <c r="D277" t="s">
-        <v>1271</v>
+        <v>1302</v>
       </c>
       <c r="E277" t="s">
-        <v>1459</v>
+        <v>1490</v>
       </c>
       <c r="F277" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G277" t="s">
         <v>1561</v>
@@ -17228,7 +17228,7 @@
         <v>1567</v>
       </c>
       <c r="J277" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K277" t="s">
         <v>1563</v>
@@ -17237,7 +17237,7 @@
         <v>1562</v>
       </c>
       <c r="M277" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N277" t="s">
         <v>1568</v>
@@ -17254,10 +17254,10 @@
         <v>1066</v>
       </c>
       <c r="D278" t="s">
-        <v>1302</v>
+        <v>1206</v>
       </c>
       <c r="E278" t="s">
-        <v>1490</v>
+        <v>1394</v>
       </c>
       <c r="F278" t="s">
         <v>1555</v>
@@ -17272,13 +17272,13 @@
         <v>1567</v>
       </c>
       <c r="J278" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K278" t="s">
         <v>1563</v>
       </c>
       <c r="L278" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M278" t="s">
         <v>1566</v>
@@ -17298,10 +17298,10 @@
         <v>1067</v>
       </c>
       <c r="D279" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="E279" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="F279" t="s">
         <v>1555</v>
@@ -17316,16 +17316,16 @@
         <v>1567</v>
       </c>
       <c r="J279" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K279" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L279" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M279" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N279" t="s">
         <v>1568</v>
@@ -17342,13 +17342,13 @@
         <v>1068</v>
       </c>
       <c r="D280" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E280" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="F280" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G280" t="s">
         <v>1561</v>
@@ -17357,19 +17357,19 @@
         <v>1564</v>
       </c>
       <c r="I280" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J280" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K280" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L280" t="s">
         <v>1562</v>
       </c>
       <c r="M280" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N280" t="s">
         <v>1568</v>
@@ -17386,10 +17386,10 @@
         <v>1069</v>
       </c>
       <c r="D281" t="s">
-        <v>1212</v>
+        <v>1191</v>
       </c>
       <c r="E281" t="s">
-        <v>1400</v>
+        <v>1379</v>
       </c>
       <c r="F281" t="s">
         <v>1556</v>
@@ -17398,22 +17398,22 @@
         <v>1561</v>
       </c>
       <c r="H281" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I281" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J281" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K281" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L281" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M281" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N281" t="s">
         <v>1568</v>
@@ -17430,25 +17430,25 @@
         <v>1070</v>
       </c>
       <c r="D282" t="s">
-        <v>1191</v>
+        <v>1335</v>
       </c>
       <c r="E282" t="s">
-        <v>1379</v>
+        <v>1523</v>
       </c>
       <c r="F282" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G282" t="s">
         <v>1561</v>
       </c>
       <c r="H282" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I282" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J282" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K282" t="s">
         <v>1562</v>
@@ -17457,7 +17457,7 @@
         <v>1566</v>
       </c>
       <c r="M282" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N282" t="s">
         <v>1568</v>
@@ -17474,34 +17474,34 @@
         <v>1071</v>
       </c>
       <c r="D283" t="s">
-        <v>1335</v>
+        <v>1179</v>
       </c>
       <c r="E283" t="s">
-        <v>1523</v>
+        <v>1367</v>
       </c>
       <c r="F283" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G283" t="s">
         <v>1561</v>
       </c>
       <c r="H283" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="I283" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J283" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="K283" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L283" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M283" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="N283" t="s">
         <v>1568</v>
@@ -17518,34 +17518,34 @@
         <v>1072</v>
       </c>
       <c r="D284" t="s">
-        <v>1179</v>
+        <v>1278</v>
       </c>
       <c r="E284" t="s">
-        <v>1367</v>
+        <v>1466</v>
       </c>
       <c r="F284" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G284" t="s">
         <v>1561</v>
       </c>
       <c r="H284" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I284" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J284" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K284" t="s">
         <v>1565</v>
       </c>
       <c r="L284" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M284" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N284" t="s">
         <v>1568</v>
@@ -17562,22 +17562,22 @@
         <v>1073</v>
       </c>
       <c r="D285" t="s">
-        <v>1278</v>
+        <v>1256</v>
       </c>
       <c r="E285" t="s">
-        <v>1466</v>
+        <v>1444</v>
       </c>
       <c r="F285" t="s">
         <v>1555</v>
       </c>
       <c r="G285" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="H285" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I285" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J285" t="s">
         <v>1564</v>
@@ -17586,10 +17586,10 @@
         <v>1565</v>
       </c>
       <c r="L285" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="M285" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N285" t="s">
         <v>1568</v>
@@ -17606,34 +17606,34 @@
         <v>1074</v>
       </c>
       <c r="D286" t="s">
-        <v>1256</v>
+        <v>1228</v>
       </c>
       <c r="E286" t="s">
-        <v>1444</v>
+        <v>1416</v>
       </c>
       <c r="F286" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G286" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="H286" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I286" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J286" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K286" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L286" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M286" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N286" t="s">
         <v>1568</v>
@@ -17650,13 +17650,13 @@
         <v>1075</v>
       </c>
       <c r="D287" t="s">
-        <v>1228</v>
+        <v>1185</v>
       </c>
       <c r="E287" t="s">
-        <v>1416</v>
+        <v>1373</v>
       </c>
       <c r="F287" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G287" t="s">
         <v>1561</v>
@@ -17665,19 +17665,19 @@
         <v>1567</v>
       </c>
       <c r="I287" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J287" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K287" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L287" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M287" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N287" t="s">
         <v>1568</v>
@@ -17694,34 +17694,34 @@
         <v>1076</v>
       </c>
       <c r="D288" t="s">
-        <v>1185</v>
+        <v>1336</v>
       </c>
       <c r="E288" t="s">
-        <v>1373</v>
+        <v>1524</v>
       </c>
       <c r="F288" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G288" t="s">
         <v>1561</v>
       </c>
       <c r="H288" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I288" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J288" t="s">
         <v>1562</v>
       </c>
       <c r="K288" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L288" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M288" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N288" t="s">
         <v>1568</v>
@@ -17738,22 +17738,22 @@
         <v>1077</v>
       </c>
       <c r="D289" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="E289" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="F289" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G289" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H289" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I289" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J289" t="s">
         <v>1562</v>
@@ -17762,10 +17762,10 @@
         <v>1565</v>
       </c>
       <c r="L289" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M289" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N289" t="s">
         <v>1568</v>
@@ -17782,28 +17782,28 @@
         <v>1078</v>
       </c>
       <c r="D290" t="s">
-        <v>1337</v>
+        <v>1256</v>
       </c>
       <c r="E290" t="s">
-        <v>1525</v>
+        <v>1444</v>
       </c>
       <c r="F290" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G290" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H290" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I290" t="s">
         <v>1567</v>
       </c>
       <c r="J290" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K290" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L290" t="s">
         <v>1566</v>
@@ -17826,13 +17826,13 @@
         <v>1079</v>
       </c>
       <c r="D291" t="s">
-        <v>1256</v>
+        <v>1329</v>
       </c>
       <c r="E291" t="s">
-        <v>1444</v>
+        <v>1517</v>
       </c>
       <c r="F291" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G291" t="s">
         <v>1561</v>
@@ -17847,13 +17847,13 @@
         <v>1565</v>
       </c>
       <c r="K291" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L291" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M291" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N291" t="s">
         <v>1568</v>
@@ -17870,10 +17870,10 @@
         <v>1080</v>
       </c>
       <c r="D292" t="s">
-        <v>1329</v>
+        <v>1274</v>
       </c>
       <c r="E292" t="s">
-        <v>1517</v>
+        <v>1462</v>
       </c>
       <c r="F292" t="s">
         <v>1556</v>
@@ -17882,22 +17882,22 @@
         <v>1561</v>
       </c>
       <c r="H292" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I292" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J292" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K292" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L292" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M292" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N292" t="s">
         <v>1568</v>
@@ -17914,10 +17914,10 @@
         <v>1081</v>
       </c>
       <c r="D293" t="s">
-        <v>1274</v>
+        <v>1338</v>
       </c>
       <c r="E293" t="s">
-        <v>1462</v>
+        <v>1526</v>
       </c>
       <c r="F293" t="s">
         <v>1556</v>
@@ -17926,22 +17926,22 @@
         <v>1561</v>
       </c>
       <c r="H293" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="I293" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J293" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K293" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L293" t="s">
         <v>1565</v>
       </c>
       <c r="M293" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N293" t="s">
         <v>1568</v>
@@ -17958,25 +17958,25 @@
         <v>1082</v>
       </c>
       <c r="D294" t="s">
-        <v>1338</v>
+        <v>1211</v>
       </c>
       <c r="E294" t="s">
-        <v>1526</v>
+        <v>1399</v>
       </c>
       <c r="F294" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G294" t="s">
         <v>1561</v>
       </c>
       <c r="H294" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I294" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J294" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K294" t="s">
         <v>1566</v>
@@ -17985,7 +17985,7 @@
         <v>1565</v>
       </c>
       <c r="M294" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N294" t="s">
         <v>1568</v>
@@ -18002,13 +18002,13 @@
         <v>1083</v>
       </c>
       <c r="D295" t="s">
-        <v>1211</v>
+        <v>1284</v>
       </c>
       <c r="E295" t="s">
-        <v>1399</v>
+        <v>1472</v>
       </c>
       <c r="F295" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G295" t="s">
         <v>1561</v>
@@ -18046,19 +18046,19 @@
         <v>1084</v>
       </c>
       <c r="D296" t="s">
-        <v>1284</v>
+        <v>1179</v>
       </c>
       <c r="E296" t="s">
-        <v>1472</v>
+        <v>1367</v>
       </c>
       <c r="F296" t="s">
         <v>1555</v>
       </c>
       <c r="G296" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H296" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I296" t="s">
         <v>1567</v>
@@ -18067,13 +18067,13 @@
         <v>1562</v>
       </c>
       <c r="K296" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L296" t="s">
         <v>1565</v>
       </c>
       <c r="M296" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N296" t="s">
         <v>1568</v>
@@ -18090,34 +18090,34 @@
         <v>1085</v>
       </c>
       <c r="D297" t="s">
-        <v>1179</v>
+        <v>1194</v>
       </c>
       <c r="E297" t="s">
-        <v>1367</v>
+        <v>1382</v>
       </c>
       <c r="F297" t="s">
         <v>1555</v>
       </c>
       <c r="G297" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H297" t="s">
         <v>1561</v>
       </c>
       <c r="I297" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J297" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K297" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L297" t="s">
         <v>1565</v>
       </c>
       <c r="M297" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N297" t="s">
         <v>1568</v>
@@ -18134,34 +18134,34 @@
         <v>1086</v>
       </c>
       <c r="D298" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="E298" t="s">
-        <v>1382</v>
+        <v>1401</v>
       </c>
       <c r="F298" t="s">
         <v>1555</v>
       </c>
       <c r="G298" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H298" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I298" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J298" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K298" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L298" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M298" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N298" t="s">
         <v>1568</v>
@@ -18178,34 +18178,34 @@
         <v>1087</v>
       </c>
       <c r="D299" t="s">
-        <v>1213</v>
+        <v>1339</v>
       </c>
       <c r="E299" t="s">
-        <v>1401</v>
+        <v>1527</v>
       </c>
       <c r="F299" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G299" t="s">
         <v>1561</v>
       </c>
       <c r="H299" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I299" t="s">
         <v>1564</v>
       </c>
       <c r="J299" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K299" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L299" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M299" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N299" t="s">
         <v>1568</v>
@@ -18222,31 +18222,31 @@
         <v>1088</v>
       </c>
       <c r="D300" t="s">
-        <v>1339</v>
+        <v>1227</v>
       </c>
       <c r="E300" t="s">
-        <v>1527</v>
+        <v>1415</v>
       </c>
       <c r="F300" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G300" t="s">
         <v>1561</v>
       </c>
       <c r="H300" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I300" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J300" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K300" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L300" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M300" t="s">
         <v>1563</v>
@@ -18266,34 +18266,34 @@
         <v>1089</v>
       </c>
       <c r="D301" t="s">
-        <v>1227</v>
+        <v>1256</v>
       </c>
       <c r="E301" t="s">
-        <v>1415</v>
+        <v>1444</v>
       </c>
       <c r="F301" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G301" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="H301" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I301" t="s">
         <v>1566</v>
       </c>
       <c r="J301" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="K301" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L301" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M301" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N301" t="s">
         <v>1568</v>
@@ -18310,34 +18310,34 @@
         <v>1090</v>
       </c>
       <c r="D302" t="s">
-        <v>1256</v>
+        <v>1191</v>
       </c>
       <c r="E302" t="s">
-        <v>1444</v>
+        <v>1379</v>
       </c>
       <c r="F302" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G302" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H302" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I302" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J302" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K302" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L302" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M302" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N302" t="s">
         <v>1568</v>
@@ -18354,10 +18354,10 @@
         <v>1091</v>
       </c>
       <c r="D303" t="s">
-        <v>1191</v>
+        <v>1297</v>
       </c>
       <c r="E303" t="s">
-        <v>1379</v>
+        <v>1485</v>
       </c>
       <c r="F303" t="s">
         <v>1555</v>
@@ -18375,13 +18375,13 @@
         <v>1562</v>
       </c>
       <c r="K303" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L303" t="s">
         <v>1565</v>
       </c>
       <c r="M303" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N303" t="s">
         <v>1568</v>
@@ -18398,10 +18398,10 @@
         <v>1092</v>
       </c>
       <c r="D304" t="s">
-        <v>1297</v>
+        <v>1340</v>
       </c>
       <c r="E304" t="s">
-        <v>1485</v>
+        <v>1528</v>
       </c>
       <c r="F304" t="s">
         <v>1555</v>
@@ -18410,19 +18410,19 @@
         <v>1561</v>
       </c>
       <c r="H304" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I304" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J304" t="s">
         <v>1562</v>
       </c>
       <c r="K304" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L304" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M304" t="s">
         <v>1563</v>
@@ -18442,13 +18442,13 @@
         <v>1093</v>
       </c>
       <c r="D305" t="s">
-        <v>1340</v>
+        <v>1196</v>
       </c>
       <c r="E305" t="s">
-        <v>1528</v>
+        <v>1384</v>
       </c>
       <c r="F305" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G305" t="s">
         <v>1561</v>
@@ -18460,16 +18460,16 @@
         <v>1567</v>
       </c>
       <c r="J305" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K305" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L305" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M305" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N305" t="s">
         <v>1568</v>
@@ -18486,13 +18486,13 @@
         <v>1094</v>
       </c>
       <c r="D306" t="s">
-        <v>1196</v>
+        <v>1332</v>
       </c>
       <c r="E306" t="s">
-        <v>1384</v>
+        <v>1520</v>
       </c>
       <c r="F306" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G306" t="s">
         <v>1561</v>
@@ -18501,16 +18501,16 @@
         <v>1564</v>
       </c>
       <c r="I306" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J306" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K306" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L306" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M306" t="s">
         <v>1566</v>
@@ -18530,13 +18530,13 @@
         <v>1095</v>
       </c>
       <c r="D307" t="s">
-        <v>1332</v>
+        <v>1202</v>
       </c>
       <c r="E307" t="s">
-        <v>1520</v>
+        <v>1390</v>
       </c>
       <c r="F307" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G307" t="s">
         <v>1561</v>
@@ -18545,19 +18545,19 @@
         <v>1564</v>
       </c>
       <c r="I307" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J307" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K307" t="s">
         <v>1565</v>
       </c>
       <c r="L307" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M307" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N307" t="s">
         <v>1568</v>
@@ -18574,34 +18574,34 @@
         <v>1096</v>
       </c>
       <c r="D308" t="s">
-        <v>1202</v>
+        <v>1291</v>
       </c>
       <c r="E308" t="s">
-        <v>1390</v>
+        <v>1479</v>
       </c>
       <c r="F308" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G308" t="s">
         <v>1561</v>
       </c>
       <c r="H308" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I308" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J308" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K308" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L308" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M308" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N308" t="s">
         <v>1568</v>
@@ -18618,10 +18618,10 @@
         <v>1097</v>
       </c>
       <c r="D309" t="s">
-        <v>1291</v>
+        <v>1321</v>
       </c>
       <c r="E309" t="s">
-        <v>1479</v>
+        <v>1509</v>
       </c>
       <c r="F309" t="s">
         <v>1556</v>
@@ -18630,7 +18630,7 @@
         <v>1561</v>
       </c>
       <c r="H309" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I309" t="s">
         <v>1563</v>
@@ -18639,7 +18639,7 @@
         <v>1567</v>
       </c>
       <c r="K309" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L309" t="s">
         <v>1566</v>
@@ -18662,13 +18662,13 @@
         <v>1098</v>
       </c>
       <c r="D310" t="s">
-        <v>1321</v>
+        <v>1337</v>
       </c>
       <c r="E310" t="s">
-        <v>1509</v>
+        <v>1525</v>
       </c>
       <c r="F310" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G310" t="s">
         <v>1561</v>
@@ -18706,34 +18706,34 @@
         <v>1099</v>
       </c>
       <c r="D311" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="E311" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="F311" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G311" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H311" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I311" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J311" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="K311" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L311" t="s">
         <v>1566</v>
       </c>
       <c r="M311" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N311" t="s">
         <v>1568</v>
@@ -18750,34 +18750,34 @@
         <v>1100</v>
       </c>
       <c r="D312" t="s">
-        <v>1341</v>
+        <v>1211</v>
       </c>
       <c r="E312" t="s">
-        <v>1529</v>
+        <v>1399</v>
       </c>
       <c r="F312" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G312" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H312" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I312" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J312" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K312" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L312" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M312" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N312" t="s">
         <v>1568</v>
@@ -18794,31 +18794,31 @@
         <v>1101</v>
       </c>
       <c r="D313" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="E313" t="s">
-        <v>1399</v>
+        <v>1454</v>
       </c>
       <c r="F313" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G313" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H313" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I313" t="s">
         <v>1567</v>
       </c>
       <c r="J313" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K313" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="L313" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M313" t="s">
         <v>1563</v>
@@ -18838,28 +18838,28 @@
         <v>1102</v>
       </c>
       <c r="D314" t="s">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="E314" t="s">
-        <v>1454</v>
+        <v>1473</v>
       </c>
       <c r="F314" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G314" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H314" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I314" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J314" t="s">
         <v>1565</v>
       </c>
       <c r="K314" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L314" t="s">
         <v>1566</v>
@@ -18882,34 +18882,34 @@
         <v>1103</v>
       </c>
       <c r="D315" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="E315" t="s">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="F315" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G315" t="s">
         <v>1561</v>
       </c>
       <c r="H315" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I315" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J315" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K315" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L315" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M315" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N315" t="s">
         <v>1568</v>
@@ -18926,13 +18926,13 @@
         <v>1104</v>
       </c>
       <c r="D316" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="E316" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="F316" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G316" t="s">
         <v>1561</v>
@@ -18941,19 +18941,19 @@
         <v>1567</v>
       </c>
       <c r="I316" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J316" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K316" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L316" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M316" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N316" t="s">
         <v>1568</v>
@@ -18970,10 +18970,10 @@
         <v>1105</v>
       </c>
       <c r="D317" t="s">
-        <v>1318</v>
+        <v>1229</v>
       </c>
       <c r="E317" t="s">
-        <v>1506</v>
+        <v>1417</v>
       </c>
       <c r="F317" t="s">
         <v>1556</v>
@@ -18985,19 +18985,19 @@
         <v>1567</v>
       </c>
       <c r="I317" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J317" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K317" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L317" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M317" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N317" t="s">
         <v>1568</v>
@@ -19014,13 +19014,13 @@
         <v>1106</v>
       </c>
       <c r="D318" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="E318" t="s">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="F318" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G318" t="s">
         <v>1561</v>
@@ -19029,10 +19029,10 @@
         <v>1567</v>
       </c>
       <c r="I318" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J318" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K318" t="s">
         <v>1566</v>
@@ -19058,10 +19058,10 @@
         <v>1107</v>
       </c>
       <c r="D319" t="s">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="E319" t="s">
-        <v>1433</v>
+        <v>1530</v>
       </c>
       <c r="F319" t="s">
         <v>1555</v>
@@ -19070,22 +19070,22 @@
         <v>1561</v>
       </c>
       <c r="H319" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I319" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J319" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K319" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L319" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M319" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N319" t="s">
         <v>1568</v>
@@ -19102,34 +19102,34 @@
         <v>1108</v>
       </c>
       <c r="D320" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E320" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F320" t="s">
         <v>1555</v>
       </c>
       <c r="G320" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H320" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I320" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J320" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K320" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L320" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M320" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N320" t="s">
         <v>1568</v>
@@ -19146,10 +19146,10 @@
         <v>1109</v>
       </c>
       <c r="D321" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E321" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F321" t="s">
         <v>1555</v>
@@ -19190,34 +19190,34 @@
         <v>1110</v>
       </c>
       <c r="D322" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E322" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F322" t="s">
         <v>1555</v>
       </c>
       <c r="G322" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H322" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I322" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J322" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K322" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L322" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M322" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="N322" t="s">
         <v>1568</v>
@@ -19234,34 +19234,34 @@
         <v>1111</v>
       </c>
       <c r="D323" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E323" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F323" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G323" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H323" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I323" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J323" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K323" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L323" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M323" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N323" t="s">
         <v>1568</v>
@@ -19278,34 +19278,34 @@
         <v>1112</v>
       </c>
       <c r="D324" t="s">
-        <v>1346</v>
+        <v>1315</v>
       </c>
       <c r="E324" t="s">
-        <v>1534</v>
+        <v>1503</v>
       </c>
       <c r="F324" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G324" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H324" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I324" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J324" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K324" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L324" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M324" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N324" t="s">
         <v>1568</v>
@@ -19322,13 +19322,13 @@
         <v>1113</v>
       </c>
       <c r="D325" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="E325" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="F325" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G325" t="s">
         <v>1561</v>
@@ -19343,13 +19343,13 @@
         <v>1563</v>
       </c>
       <c r="K325" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L325" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M325" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N325" t="s">
         <v>1568</v>
@@ -19366,10 +19366,10 @@
         <v>1114</v>
       </c>
       <c r="D326" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
       <c r="E326" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F326" t="s">
         <v>1555</v>
@@ -19384,16 +19384,16 @@
         <v>1567</v>
       </c>
       <c r="J326" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K326" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L326" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M326" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N326" t="s">
         <v>1568</v>
@@ -19410,31 +19410,31 @@
         <v>1115</v>
       </c>
       <c r="D327" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E327" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F327" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G327" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H327" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I327" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J327" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K327" t="s">
         <v>1565</v>
       </c>
       <c r="L327" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M327" t="s">
         <v>1563</v>
@@ -19454,34 +19454,34 @@
         <v>1116</v>
       </c>
       <c r="D328" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="E328" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="F328" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G328" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H328" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I328" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J328" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K328" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L328" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M328" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N328" t="s">
         <v>1568</v>
@@ -19498,34 +19498,34 @@
         <v>1117</v>
       </c>
       <c r="D329" t="s">
-        <v>1314</v>
+        <v>1224</v>
       </c>
       <c r="E329" t="s">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="F329" t="s">
         <v>1556</v>
       </c>
       <c r="G329" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H329" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I329" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="J329" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K329" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L329" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M329" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="N329" t="s">
         <v>1568</v>
@@ -19542,34 +19542,34 @@
         <v>1118</v>
       </c>
       <c r="D330" t="s">
-        <v>1224</v>
+        <v>1262</v>
       </c>
       <c r="E330" t="s">
-        <v>1412</v>
+        <v>1450</v>
       </c>
       <c r="F330" t="s">
         <v>1556</v>
       </c>
       <c r="G330" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H330" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I330" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J330" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K330" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L330" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M330" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N330" t="s">
         <v>1568</v>
@@ -19586,34 +19586,34 @@
         <v>1119</v>
       </c>
       <c r="D331" t="s">
-        <v>1262</v>
+        <v>1291</v>
       </c>
       <c r="E331" t="s">
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="F331" t="s">
         <v>1556</v>
       </c>
       <c r="G331" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H331" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I331" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J331" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K331" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L331" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M331" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N331" t="s">
         <v>1568</v>
@@ -19630,34 +19630,34 @@
         <v>1120</v>
       </c>
       <c r="D332" t="s">
-        <v>1291</v>
+        <v>1262</v>
       </c>
       <c r="E332" t="s">
-        <v>1479</v>
+        <v>1450</v>
       </c>
       <c r="F332" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G332" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="H332" t="s">
         <v>1561</v>
       </c>
       <c r="I332" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J332" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K332" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L332" t="s">
         <v>1566</v>
       </c>
       <c r="M332" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N332" t="s">
         <v>1568</v>
@@ -19674,31 +19674,31 @@
         <v>1121</v>
       </c>
       <c r="D333" t="s">
-        <v>1262</v>
+        <v>1349</v>
       </c>
       <c r="E333" t="s">
-        <v>1450</v>
+        <v>1537</v>
       </c>
       <c r="F333" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G333" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H333" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I333" t="s">
         <v>1567</v>
       </c>
       <c r="J333" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K333" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L333" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M333" t="s">
         <v>1562</v>
@@ -19718,10 +19718,10 @@
         <v>1122</v>
       </c>
       <c r="D334" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E334" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F334" t="s">
         <v>1559</v>
@@ -19736,16 +19736,16 @@
         <v>1567</v>
       </c>
       <c r="J334" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K334" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L334" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M334" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N334" t="s">
         <v>1568</v>
@@ -19762,13 +19762,13 @@
         <v>1123</v>
       </c>
       <c r="D335" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E335" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F335" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G335" t="s">
         <v>1561</v>
@@ -19780,13 +19780,13 @@
         <v>1567</v>
       </c>
       <c r="J335" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K335" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L335" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M335" t="s">
         <v>1563</v>
@@ -19806,34 +19806,34 @@
         <v>1124</v>
       </c>
       <c r="D336" t="s">
-        <v>1351</v>
+        <v>1331</v>
       </c>
       <c r="E336" t="s">
-        <v>1539</v>
+        <v>1519</v>
       </c>
       <c r="F336" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G336" t="s">
         <v>1561</v>
       </c>
       <c r="H336" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I336" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J336" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K336" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L336" t="s">
         <v>1562</v>
       </c>
       <c r="M336" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N336" t="s">
         <v>1568</v>
@@ -19850,25 +19850,25 @@
         <v>1125</v>
       </c>
       <c r="D337" t="s">
-        <v>1331</v>
+        <v>1201</v>
       </c>
       <c r="E337" t="s">
-        <v>1519</v>
+        <v>1389</v>
       </c>
       <c r="F337" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G337" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H337" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I337" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J337" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K337" t="s">
         <v>1565</v>
@@ -19894,31 +19894,31 @@
         <v>1126</v>
       </c>
       <c r="D338" t="s">
-        <v>1201</v>
+        <v>1271</v>
       </c>
       <c r="E338" t="s">
-        <v>1389</v>
+        <v>1459</v>
       </c>
       <c r="F338" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G338" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H338" t="s">
         <v>1564</v>
       </c>
       <c r="I338" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J338" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K338" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L338" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M338" t="s">
         <v>1566</v>
@@ -19938,34 +19938,34 @@
         <v>1127</v>
       </c>
       <c r="D339" t="s">
-        <v>1271</v>
+        <v>1352</v>
       </c>
       <c r="E339" t="s">
-        <v>1459</v>
+        <v>1540</v>
       </c>
       <c r="F339" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G339" t="s">
         <v>1561</v>
       </c>
       <c r="H339" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I339" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J339" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K339" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L339" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M339" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N339" t="s">
         <v>1568</v>
@@ -19982,34 +19982,34 @@
         <v>1128</v>
       </c>
       <c r="D340" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E340" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F340" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G340" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H340" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I340" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J340" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K340" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L340" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M340" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N340" t="s">
         <v>1568</v>
@@ -20026,34 +20026,34 @@
         <v>1129</v>
       </c>
       <c r="D341" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E341" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F341" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G341" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H341" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I341" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J341" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K341" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L341" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M341" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N341" t="s">
         <v>1568</v>
@@ -20070,34 +20070,34 @@
         <v>1130</v>
       </c>
       <c r="D342" t="s">
-        <v>1354</v>
+        <v>1230</v>
       </c>
       <c r="E342" t="s">
-        <v>1542</v>
+        <v>1418</v>
       </c>
       <c r="F342" t="s">
         <v>1557</v>
       </c>
       <c r="G342" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="H342" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I342" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J342" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K342" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L342" t="s">
         <v>1566</v>
       </c>
       <c r="M342" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N342" t="s">
         <v>1568</v>
@@ -20114,10 +20114,10 @@
         <v>1131</v>
       </c>
       <c r="D343" t="s">
-        <v>1230</v>
+        <v>1355</v>
       </c>
       <c r="E343" t="s">
-        <v>1418</v>
+        <v>1543</v>
       </c>
       <c r="F343" t="s">
         <v>1557</v>
@@ -20126,13 +20126,13 @@
         <v>1562</v>
       </c>
       <c r="H343" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I343" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J343" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K343" t="s">
         <v>1567</v>
@@ -20141,7 +20141,7 @@
         <v>1566</v>
       </c>
       <c r="M343" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N343" t="s">
         <v>1568</v>
@@ -20158,34 +20158,34 @@
         <v>1132</v>
       </c>
       <c r="D344" t="s">
-        <v>1355</v>
+        <v>1196</v>
       </c>
       <c r="E344" t="s">
-        <v>1543</v>
+        <v>1384</v>
       </c>
       <c r="F344" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G344" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H344" t="s">
         <v>1561</v>
       </c>
       <c r="I344" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J344" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K344" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L344" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M344" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N344" t="s">
         <v>1568</v>
@@ -20202,34 +20202,34 @@
         <v>1133</v>
       </c>
       <c r="D345" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E345" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F345" t="s">
         <v>1555</v>
       </c>
       <c r="G345" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H345" t="s">
         <v>1561</v>
       </c>
       <c r="I345" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J345" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K345" t="s">
         <v>1565</v>
       </c>
       <c r="L345" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M345" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N345" t="s">
         <v>1568</v>
@@ -20246,34 +20246,34 @@
         <v>1134</v>
       </c>
       <c r="D346" t="s">
-        <v>1194</v>
+        <v>1329</v>
       </c>
       <c r="E346" t="s">
-        <v>1382</v>
+        <v>1517</v>
       </c>
       <c r="F346" t="s">
         <v>1555</v>
       </c>
       <c r="G346" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H346" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I346" t="s">
         <v>1564</v>
       </c>
       <c r="J346" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K346" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L346" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M346" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N346" t="s">
         <v>1568</v>
@@ -20290,34 +20290,34 @@
         <v>1135</v>
       </c>
       <c r="D347" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
       <c r="E347" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F347" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G347" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H347" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I347" t="s">
         <v>1564</v>
       </c>
       <c r="J347" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K347" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L347" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M347" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N347" t="s">
         <v>1568</v>
@@ -20334,34 +20334,34 @@
         <v>1136</v>
       </c>
       <c r="D348" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E348" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F348" t="s">
         <v>1556</v>
       </c>
       <c r="G348" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="H348" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="I348" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J348" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="K348" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L348" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M348" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N348" t="s">
         <v>1568</v>
@@ -20378,34 +20378,34 @@
         <v>1137</v>
       </c>
       <c r="D349" t="s">
-        <v>1357</v>
+        <v>1262</v>
       </c>
       <c r="E349" t="s">
-        <v>1545</v>
+        <v>1450</v>
       </c>
       <c r="F349" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G349" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H349" t="s">
         <v>1561</v>
       </c>
       <c r="I349" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="J349" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K349" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L349" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M349" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N349" t="s">
         <v>1568</v>
@@ -20422,28 +20422,28 @@
         <v>1138</v>
       </c>
       <c r="D350" t="s">
-        <v>1262</v>
+        <v>1227</v>
       </c>
       <c r="E350" t="s">
-        <v>1450</v>
+        <v>1415</v>
       </c>
       <c r="F350" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G350" t="s">
         <v>1565</v>
       </c>
       <c r="H350" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I350" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J350" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K350" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L350" t="s">
         <v>1562</v>
@@ -20466,31 +20466,31 @@
         <v>1139</v>
       </c>
       <c r="D351" t="s">
-        <v>1227</v>
+        <v>1303</v>
       </c>
       <c r="E351" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
       <c r="F351" t="s">
         <v>1556</v>
       </c>
       <c r="G351" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H351" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I351" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J351" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K351" t="s">
         <v>1563</v>
       </c>
       <c r="L351" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M351" t="s">
         <v>1566</v>
@@ -20510,31 +20510,31 @@
         <v>1140</v>
       </c>
       <c r="D352" t="s">
-        <v>1303</v>
+        <v>1358</v>
       </c>
       <c r="E352" t="s">
-        <v>1491</v>
+        <v>1546</v>
       </c>
       <c r="F352" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G352" t="s">
         <v>1561</v>
       </c>
       <c r="H352" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I352" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J352" t="s">
         <v>1562</v>
       </c>
       <c r="K352" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L352" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M352" t="s">
         <v>1566</v>
@@ -20554,13 +20554,13 @@
         <v>1141</v>
       </c>
       <c r="D353" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E353" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F353" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G353" t="s">
         <v>1561</v>
@@ -20572,16 +20572,16 @@
         <v>1567</v>
       </c>
       <c r="J353" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K353" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L353" t="s">
         <v>1563</v>
       </c>
       <c r="M353" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N353" t="s">
         <v>1568</v>
@@ -20598,13 +20598,13 @@
         <v>1142</v>
       </c>
       <c r="D354" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E354" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F354" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G354" t="s">
         <v>1561</v>
@@ -20616,16 +20616,16 @@
         <v>1567</v>
       </c>
       <c r="J354" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K354" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L354" t="s">
         <v>1563</v>
       </c>
       <c r="M354" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N354" t="s">
         <v>1568</v>
@@ -20642,31 +20642,31 @@
         <v>1143</v>
       </c>
       <c r="D355" t="s">
-        <v>1360</v>
+        <v>1225</v>
       </c>
       <c r="E355" t="s">
-        <v>1548</v>
+        <v>1413</v>
       </c>
       <c r="F355" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G355" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H355" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I355" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J355" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K355" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L355" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M355" t="s">
         <v>1566</v>
@@ -20686,34 +20686,34 @@
         <v>1144</v>
       </c>
       <c r="D356" t="s">
-        <v>1225</v>
+        <v>1361</v>
       </c>
       <c r="E356" t="s">
-        <v>1413</v>
+        <v>1549</v>
       </c>
       <c r="F356" t="s">
         <v>1556</v>
       </c>
       <c r="G356" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H356" t="s">
         <v>1562</v>
       </c>
       <c r="I356" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J356" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K356" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L356" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M356" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N356" t="s">
         <v>1568</v>
@@ -20730,13 +20730,13 @@
         <v>1145</v>
       </c>
       <c r="D357" t="s">
-        <v>1361</v>
+        <v>1203</v>
       </c>
       <c r="E357" t="s">
-        <v>1549</v>
+        <v>1391</v>
       </c>
       <c r="F357" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G357" t="s">
         <v>1561</v>
@@ -20745,16 +20745,16 @@
         <v>1562</v>
       </c>
       <c r="I357" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J357" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K357" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="L357" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M357" t="s">
         <v>1565</v>
@@ -20774,10 +20774,10 @@
         <v>1146</v>
       </c>
       <c r="D358" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E358" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F358" t="s">
         <v>1555</v>
@@ -20818,10 +20818,10 @@
         <v>1147</v>
       </c>
       <c r="D359" t="s">
-        <v>1205</v>
+        <v>1353</v>
       </c>
       <c r="E359" t="s">
-        <v>1393</v>
+        <v>1541</v>
       </c>
       <c r="F359" t="s">
         <v>1555</v>
@@ -20830,22 +20830,22 @@
         <v>1561</v>
       </c>
       <c r="H359" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="I359" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J359" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K359" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L359" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M359" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N359" t="s">
         <v>1568</v>
@@ -20862,34 +20862,34 @@
         <v>1148</v>
       </c>
       <c r="D360" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E360" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F360" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G360" t="s">
         <v>1561</v>
       </c>
       <c r="H360" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="I360" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J360" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K360" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L360" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M360" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N360" t="s">
         <v>1568</v>
@@ -20906,13 +20906,13 @@
         <v>1149</v>
       </c>
       <c r="D361" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="E361" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="F361" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G361" t="s">
         <v>1561</v>
@@ -20921,19 +20921,19 @@
         <v>1562</v>
       </c>
       <c r="I361" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J361" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K361" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L361" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M361" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N361" t="s">
         <v>1568</v>
@@ -20950,10 +20950,10 @@
         <v>1150</v>
       </c>
       <c r="D362" t="s">
-        <v>1362</v>
+        <v>1316</v>
       </c>
       <c r="E362" t="s">
-        <v>1550</v>
+        <v>1504</v>
       </c>
       <c r="F362" t="s">
         <v>1557</v>
@@ -20962,22 +20962,22 @@
         <v>1561</v>
       </c>
       <c r="H362" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I362" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J362" t="s">
         <v>1563</v>
       </c>
       <c r="K362" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L362" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M362" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N362" t="s">
         <v>1568</v>
@@ -20994,13 +20994,13 @@
         <v>1151</v>
       </c>
       <c r="D363" t="s">
-        <v>1316</v>
+        <v>1277</v>
       </c>
       <c r="E363" t="s">
-        <v>1504</v>
+        <v>1465</v>
       </c>
       <c r="F363" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G363" t="s">
         <v>1561</v>
@@ -21009,19 +21009,19 @@
         <v>1564</v>
       </c>
       <c r="I363" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J363" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K363" t="s">
         <v>1562</v>
       </c>
       <c r="L363" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M363" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N363" t="s">
         <v>1568</v>
@@ -21038,34 +21038,34 @@
         <v>1152</v>
       </c>
       <c r="D364" t="s">
-        <v>1277</v>
+        <v>1256</v>
       </c>
       <c r="E364" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="F364" t="s">
         <v>1556</v>
       </c>
       <c r="G364" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H364" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I364" t="s">
         <v>1565</v>
       </c>
       <c r="J364" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K364" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L364" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M364" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N364" t="s">
         <v>1568</v>
@@ -21082,34 +21082,34 @@
         <v>1153</v>
       </c>
       <c r="D365" t="s">
-        <v>1256</v>
+        <v>1216</v>
       </c>
       <c r="E365" t="s">
-        <v>1444</v>
+        <v>1404</v>
       </c>
       <c r="F365" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G365" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H365" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="I365" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J365" t="s">
         <v>1562</v>
       </c>
       <c r="K365" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L365" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M365" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="N365" t="s">
         <v>1568</v>
@@ -21126,34 +21126,34 @@
         <v>1154</v>
       </c>
       <c r="D366" t="s">
-        <v>1216</v>
+        <v>1334</v>
       </c>
       <c r="E366" t="s">
-        <v>1404</v>
+        <v>1522</v>
       </c>
       <c r="F366" t="s">
         <v>1555</v>
       </c>
       <c r="G366" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H366" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="I366" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J366" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K366" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L366" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M366" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="N366" t="s">
         <v>1568</v>
@@ -21170,10 +21170,10 @@
         <v>1155</v>
       </c>
       <c r="D367" t="s">
-        <v>1334</v>
+        <v>1280</v>
       </c>
       <c r="E367" t="s">
-        <v>1522</v>
+        <v>1468</v>
       </c>
       <c r="F367" t="s">
         <v>1555</v>
@@ -21185,16 +21185,16 @@
         <v>1564</v>
       </c>
       <c r="I367" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="J367" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K367" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L367" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M367" t="s">
         <v>1562</v>
@@ -21214,34 +21214,34 @@
         <v>1156</v>
       </c>
       <c r="D368" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="E368" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="F368" t="s">
         <v>1555</v>
       </c>
       <c r="G368" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H368" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I368" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J368" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K368" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L368" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M368" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N368" t="s">
         <v>1568</v>
@@ -21258,34 +21258,34 @@
         <v>1157</v>
       </c>
       <c r="D369" t="s">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="E369" t="s">
-        <v>1498</v>
+        <v>1453</v>
       </c>
       <c r="F369" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G369" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H369" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I369" t="s">
         <v>1561</v>
       </c>
       <c r="J369" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K369" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L369" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M369" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N369" t="s">
         <v>1568</v>
@@ -21302,34 +21302,34 @@
         <v>1158</v>
       </c>
       <c r="D370" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="E370" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="F370" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G370" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H370" t="s">
         <v>1564</v>
       </c>
       <c r="I370" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J370" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K370" t="s">
         <v>1565</v>
       </c>
       <c r="L370" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M370" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N370" t="s">
         <v>1568</v>
@@ -21346,34 +21346,34 @@
         <v>1159</v>
       </c>
       <c r="D371" t="s">
-        <v>1255</v>
+        <v>1203</v>
       </c>
       <c r="E371" t="s">
-        <v>1443</v>
+        <v>1391</v>
       </c>
       <c r="F371" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G371" t="s">
         <v>1561</v>
       </c>
       <c r="H371" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I371" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J371" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K371" t="s">
         <v>1565</v>
       </c>
       <c r="L371" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M371" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N371" t="s">
         <v>1568</v>
@@ -21390,34 +21390,34 @@
         <v>1160</v>
       </c>
       <c r="D372" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="E372" t="s">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="F372" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G372" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H372" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I372" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J372" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K372" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L372" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M372" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N372" t="s">
         <v>1568</v>
@@ -21434,34 +21434,34 @@
         <v>1161</v>
       </c>
       <c r="D373" t="s">
-        <v>1219</v>
+        <v>1267</v>
       </c>
       <c r="E373" t="s">
-        <v>1407</v>
+        <v>1455</v>
       </c>
       <c r="F373" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G373" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="H373" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I373" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J373" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K373" t="s">
         <v>1563</v>
       </c>
       <c r="L373" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M373" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N373" t="s">
         <v>1568</v>
@@ -21478,19 +21478,19 @@
         <v>1162</v>
       </c>
       <c r="D374" t="s">
-        <v>1267</v>
+        <v>1286</v>
       </c>
       <c r="E374" t="s">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F374" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G374" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H374" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I374" t="s">
         <v>1564</v>
@@ -21499,10 +21499,10 @@
         <v>1567</v>
       </c>
       <c r="K374" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L374" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M374" t="s">
         <v>1566</v>
@@ -21522,34 +21522,34 @@
         <v>1163</v>
       </c>
       <c r="D375" t="s">
-        <v>1286</v>
+        <v>1200</v>
       </c>
       <c r="E375" t="s">
-        <v>1474</v>
+        <v>1388</v>
       </c>
       <c r="F375" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G375" t="s">
         <v>1562</v>
       </c>
       <c r="H375" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I375" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J375" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K375" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L375" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M375" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N375" t="s">
         <v>1568</v>
@@ -21566,34 +21566,34 @@
         <v>1164</v>
       </c>
       <c r="D376" t="s">
-        <v>1200</v>
+        <v>1361</v>
       </c>
       <c r="E376" t="s">
-        <v>1388</v>
+        <v>1549</v>
       </c>
       <c r="F376" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G376" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H376" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I376" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J376" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K376" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="L376" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M376" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N376" t="s">
         <v>1568</v>
@@ -21610,34 +21610,34 @@
         <v>1165</v>
       </c>
       <c r="D377" t="s">
-        <v>1361</v>
+        <v>1246</v>
       </c>
       <c r="E377" t="s">
-        <v>1549</v>
+        <v>1434</v>
       </c>
       <c r="F377" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G377" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H377" t="s">
         <v>1564</v>
       </c>
       <c r="I377" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J377" t="s">
         <v>1563</v>
       </c>
       <c r="K377" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="L377" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M377" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N377" t="s">
         <v>1568</v>
@@ -21654,34 +21654,34 @@
         <v>1166</v>
       </c>
       <c r="D378" t="s">
-        <v>1246</v>
+        <v>1255</v>
       </c>
       <c r="E378" t="s">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="F378" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G378" t="s">
         <v>1561</v>
       </c>
       <c r="H378" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I378" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J378" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K378" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L378" t="s">
         <v>1565</v>
       </c>
       <c r="M378" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N378" t="s">
         <v>1568</v>
@@ -21698,34 +21698,34 @@
         <v>1167</v>
       </c>
       <c r="D379" t="s">
-        <v>1255</v>
+        <v>1215</v>
       </c>
       <c r="E379" t="s">
-        <v>1443</v>
+        <v>1403</v>
       </c>
       <c r="F379" t="s">
         <v>1556</v>
       </c>
       <c r="G379" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H379" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I379" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J379" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K379" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L379" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M379" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N379" t="s">
         <v>1568</v>
@@ -21742,31 +21742,31 @@
         <v>1168</v>
       </c>
       <c r="D380" t="s">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="E380" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="F380" t="s">
         <v>1556</v>
       </c>
       <c r="G380" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H380" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I380" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J380" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K380" t="s">
         <v>1565</v>
       </c>
       <c r="L380" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="M380" t="s">
         <v>1566</v>
@@ -21786,31 +21786,31 @@
         <v>1169</v>
       </c>
       <c r="D381" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="E381" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="F381" t="s">
         <v>1556</v>
       </c>
       <c r="G381" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H381" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I381" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J381" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K381" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L381" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M381" t="s">
         <v>1566</v>
@@ -21830,34 +21830,34 @@
         <v>1170</v>
       </c>
       <c r="D382" t="s">
-        <v>1226</v>
+        <v>1312</v>
       </c>
       <c r="E382" t="s">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="F382" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G382" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H382" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I382" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="J382" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K382" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L382" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M382" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="N382" t="s">
         <v>1568</v>
@@ -21874,10 +21874,10 @@
         <v>1171</v>
       </c>
       <c r="D383" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E383" t="s">
-        <v>1500</v>
+        <v>1551</v>
       </c>
       <c r="F383" t="s">
         <v>1555</v>
@@ -21918,34 +21918,34 @@
         <v>1172</v>
       </c>
       <c r="D384" t="s">
-        <v>1363</v>
+        <v>1199</v>
       </c>
       <c r="E384" t="s">
-        <v>1551</v>
+        <v>1387</v>
       </c>
       <c r="F384" t="s">
         <v>1555</v>
       </c>
       <c r="G384" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H384" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I384" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J384" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K384" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L384" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M384" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="N384" t="s">
         <v>1568</v>
@@ -21962,31 +21962,31 @@
         <v>1173</v>
       </c>
       <c r="D385" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="E385" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F385" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G385" t="s">
         <v>1561</v>
       </c>
       <c r="H385" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I385" t="s">
         <v>1567</v>
       </c>
       <c r="J385" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K385" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L385" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M385" t="s">
         <v>1566</v>
@@ -22006,34 +22006,34 @@
         <v>1174</v>
       </c>
       <c r="D386" t="s">
-        <v>1211</v>
+        <v>1364</v>
       </c>
       <c r="E386" t="s">
-        <v>1399</v>
+        <v>1552</v>
       </c>
       <c r="F386" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G386" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H386" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I386" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J386" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K386" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L386" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M386" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N386" t="s">
         <v>1568</v>
@@ -22050,34 +22050,34 @@
         <v>1175</v>
       </c>
       <c r="D387" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E387" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F387" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G387" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H387" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I387" t="s">
         <v>1563</v>
       </c>
       <c r="J387" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K387" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L387" t="s">
         <v>1565</v>
       </c>
       <c r="M387" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N387" t="s">
         <v>1568</v>
@@ -22094,34 +22094,34 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E388" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F388" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G388" t="s">
         <v>1561</v>
       </c>
       <c r="H388" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I388" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J388" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K388" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L388" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M388" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N388" t="s">
         <v>1568</v>
@@ -22138,13 +22138,13 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1366</v>
+        <v>1209</v>
       </c>
       <c r="E389" t="s">
-        <v>1554</v>
+        <v>1397</v>
       </c>
       <c r="F389" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G389" t="s">
         <v>1561</v>
@@ -22159,13 +22159,13 @@
         <v>1562</v>
       </c>
       <c r="K389" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L389" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M389" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N389" t="s">
         <v>1568</v>
@@ -22182,13 +22182,13 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1448</v>
+        <v>1360</v>
       </c>
       <c r="E390">
-        <v>72.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="F390" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G390" t="s">
         <v>1561</v>
@@ -22200,16 +22200,16 @@
         <v>1567</v>
       </c>
       <c r="J390" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K390" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L390" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M390" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N390" t="s">
         <v>1568</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1186,45 +1186,45 @@
     <t>سارة رضا عبد المنعم محمد</t>
   </si>
   <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
     <t>المختار مجدى مختار احمد</t>
   </si>
   <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2350,45 +2350,45 @@
     <t>30509102401829</t>
   </si>
   <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
     <t>30407012403477</t>
   </si>
   <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3514,43 +3514,43 @@
     <t>01067724736</t>
   </si>
   <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
     <t>01012291526</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
   </si>
   <si>
     <t>1353</t>
@@ -21654,34 +21654,34 @@
         <v>1166</v>
       </c>
       <c r="D378" t="s">
-        <v>1255</v>
+        <v>1215</v>
       </c>
       <c r="E378" t="s">
-        <v>1443</v>
+        <v>1403</v>
       </c>
       <c r="F378" t="s">
         <v>1556</v>
       </c>
       <c r="G378" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H378" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I378" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J378" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K378" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L378" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M378" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N378" t="s">
         <v>1568</v>
@@ -21698,31 +21698,31 @@
         <v>1167</v>
       </c>
       <c r="D379" t="s">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="E379" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="F379" t="s">
         <v>1556</v>
       </c>
       <c r="G379" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H379" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I379" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J379" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K379" t="s">
         <v>1565</v>
       </c>
       <c r="L379" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="M379" t="s">
         <v>1566</v>
@@ -21742,31 +21742,31 @@
         <v>1168</v>
       </c>
       <c r="D380" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="E380" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="F380" t="s">
         <v>1556</v>
       </c>
       <c r="G380" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H380" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I380" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J380" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K380" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L380" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M380" t="s">
         <v>1566</v>
@@ -21786,34 +21786,34 @@
         <v>1169</v>
       </c>
       <c r="D381" t="s">
-        <v>1226</v>
+        <v>1312</v>
       </c>
       <c r="E381" t="s">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="F381" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G381" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H381" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I381" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="J381" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K381" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L381" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M381" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="N381" t="s">
         <v>1568</v>
@@ -21830,10 +21830,10 @@
         <v>1170</v>
       </c>
       <c r="D382" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E382" t="s">
-        <v>1500</v>
+        <v>1551</v>
       </c>
       <c r="F382" t="s">
         <v>1555</v>
@@ -21874,34 +21874,34 @@
         <v>1171</v>
       </c>
       <c r="D383" t="s">
-        <v>1363</v>
+        <v>1199</v>
       </c>
       <c r="E383" t="s">
-        <v>1551</v>
+        <v>1387</v>
       </c>
       <c r="F383" t="s">
         <v>1555</v>
       </c>
       <c r="G383" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H383" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I383" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J383" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K383" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L383" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M383" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="N383" t="s">
         <v>1568</v>
@@ -21918,31 +21918,31 @@
         <v>1172</v>
       </c>
       <c r="D384" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="E384" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F384" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G384" t="s">
         <v>1561</v>
       </c>
       <c r="H384" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I384" t="s">
         <v>1567</v>
       </c>
       <c r="J384" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K384" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L384" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M384" t="s">
         <v>1566</v>
@@ -21962,34 +21962,34 @@
         <v>1173</v>
       </c>
       <c r="D385" t="s">
-        <v>1211</v>
+        <v>1364</v>
       </c>
       <c r="E385" t="s">
-        <v>1399</v>
+        <v>1552</v>
       </c>
       <c r="F385" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G385" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H385" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I385" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J385" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K385" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L385" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M385" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N385" t="s">
         <v>1568</v>
@@ -22006,34 +22006,34 @@
         <v>1174</v>
       </c>
       <c r="D386" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E386" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F386" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G386" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H386" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I386" t="s">
         <v>1563</v>
       </c>
       <c r="J386" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K386" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L386" t="s">
         <v>1565</v>
       </c>
       <c r="M386" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N386" t="s">
         <v>1568</v>
@@ -22050,34 +22050,34 @@
         <v>1175</v>
       </c>
       <c r="D387" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E387" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F387" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G387" t="s">
         <v>1561</v>
       </c>
       <c r="H387" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I387" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J387" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K387" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L387" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M387" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N387" t="s">
         <v>1568</v>
@@ -22094,13 +22094,13 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1366</v>
+        <v>1209</v>
       </c>
       <c r="E388" t="s">
-        <v>1554</v>
+        <v>1397</v>
       </c>
       <c r="F388" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G388" t="s">
         <v>1561</v>
@@ -22115,13 +22115,13 @@
         <v>1562</v>
       </c>
       <c r="K388" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L388" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M388" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N388" t="s">
         <v>1568</v>
@@ -22138,13 +22138,13 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="E389" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="F389" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G389" t="s">
         <v>1561</v>
@@ -22156,16 +22156,16 @@
         <v>1567</v>
       </c>
       <c r="J389" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K389" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L389" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M389" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N389" t="s">
         <v>1568</v>
@@ -22182,34 +22182,34 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1360</v>
+        <v>1351</v>
       </c>
       <c r="E390">
-        <v>68</v>
+        <v>67.55</v>
       </c>
       <c r="F390" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G390" t="s">
         <v>1561</v>
       </c>
       <c r="H390" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I390" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J390" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K390" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L390" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M390" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N390" t="s">
         <v>1568</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1219,12 +1219,12 @@
     <t>محمد ناصف عبدالعظيم محمد</t>
   </si>
   <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
     <t>المختار مجدى مختار احمد</t>
   </si>
   <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>30504152400759</t>
   </si>
   <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
     <t>30407012403477</t>
   </si>
   <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3547,10 +3547,10 @@
     <t>01129974304</t>
   </si>
   <si>
+    <t>01113132202</t>
+  </si>
+  <si>
     <t>01012291526</t>
-  </si>
-  <si>
-    <t>01113132202</t>
   </si>
   <si>
     <t>1353</t>
@@ -22138,34 +22138,34 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="E389" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="F389" t="s">
         <v>1556</v>
       </c>
       <c r="G389" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H389" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="I389" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J389" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K389" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L389" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="M389" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N389" t="s">
         <v>1568</v>
@@ -22182,31 +22182,31 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="E390">
-        <v>67.25</v>
+        <v>67.55</v>
       </c>
       <c r="F390" t="s">
         <v>1556</v>
       </c>
       <c r="G390" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H390" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="I390" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J390" t="s">
         <v>1563</v>
       </c>
       <c r="K390" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L390" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M390" t="s">
         <v>1567</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -733,498 +733,498 @@
     <t>احمد وائل عبدالغنى عبدالمقصود</t>
   </si>
   <si>
+    <t>آلاء تجانى حسين على</t>
+  </si>
+  <si>
+    <t>رقيه محمد احمد عرابي</t>
+  </si>
+  <si>
+    <t>جاسر جدامى محمد محمد</t>
+  </si>
+  <si>
+    <t>اياد خيرى لطفى عبد الجيد</t>
+  </si>
+  <si>
+    <t>محمود عيد عبدالله عبدالله</t>
+  </si>
+  <si>
+    <t>آيه اسامه محمد السعيد أمين</t>
+  </si>
+  <si>
+    <t>احمد عبد الرؤوف احمد فضل</t>
+  </si>
+  <si>
+    <t>يوسف علاء الدين محمد محمد</t>
+  </si>
+  <si>
+    <t>فاطمه ضاحى محمد محمود</t>
+  </si>
+  <si>
+    <t>مارفينا مجدى خميس رشدى</t>
+  </si>
+  <si>
+    <t>ليديا عصام مكرم نجيب</t>
+  </si>
+  <si>
+    <t>شادي احمد علي مهني</t>
+  </si>
+  <si>
+    <t>شهاب محمد مخلوف محمد</t>
+  </si>
+  <si>
+    <t>نورهان محمود محمد احمد</t>
+  </si>
+  <si>
+    <t>عمرو محمد أحمد دردير</t>
+  </si>
+  <si>
+    <t>محمد احمد حسن محمد</t>
+  </si>
+  <si>
+    <t>اسلام عبد العال عبد السلام عبد الحميد</t>
+  </si>
+  <si>
+    <t>حسام احمد عبد المطلب احمد</t>
+  </si>
+  <si>
+    <t>حازم ياسر عبد النبى عبد الوهاب</t>
+  </si>
+  <si>
+    <t>أحمد عاطف حسين محمد</t>
+  </si>
+  <si>
+    <t>فاتن حماد عبد الحليم على</t>
+  </si>
+  <si>
+    <t>كريم جمال سعيد على</t>
+  </si>
+  <si>
+    <t>يحيى صفوت يحيى رمضان</t>
+  </si>
+  <si>
+    <t>احمد محمود عبدالمنعم احمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد محمود أحمد</t>
+  </si>
+  <si>
+    <t>زياد محمد رجائى محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن اشرف موسى هاشم</t>
+  </si>
+  <si>
+    <t>دميانه أشرف ماهر اسحق</t>
+  </si>
+  <si>
+    <t>زياد أشرف محمد محمود</t>
+  </si>
+  <si>
+    <t>ابراهيم محمد محمد ذكى</t>
+  </si>
+  <si>
+    <t>اميره حمدى مصطفى محمد</t>
+  </si>
+  <si>
+    <t>يوسف مصطفي سيد يوسف</t>
+  </si>
+  <si>
+    <t>رانيا سيد صلاح الدين على</t>
+  </si>
+  <si>
+    <t>حازم عباس خليفة عباس</t>
+  </si>
+  <si>
+    <t>رقيه على محمد خلف</t>
+  </si>
+  <si>
+    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
+  </si>
+  <si>
+    <t>ابراهيم محمود محمد عبدالنعيم</t>
+  </si>
+  <si>
+    <t>بهاء الدين محمد ابراهيم على</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>يوسف احمد سمير محمد</t>
+  </si>
+  <si>
+    <t>محمد رجب لطفى كامل</t>
+  </si>
+  <si>
+    <t>احمد طارق محمد محمود</t>
+  </si>
+  <si>
+    <t>عبدالله محمد سيد صادق</t>
+  </si>
+  <si>
+    <t>سهيله عبد القادر احمد عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد توفيق محمد محمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>مريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>شهد حسين محمود صابر</t>
+  </si>
+  <si>
+    <t>محمد سرحان محمد زكى</t>
+  </si>
+  <si>
+    <t>لمياء عبد القادر محمد فتحى</t>
+  </si>
+  <si>
+    <t>أميمة رأفت محمود احمد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>احمد رمضان محمد عبد الحميد</t>
+  </si>
+  <si>
+    <t>كريم محمد عبد الوهاب عيد</t>
+  </si>
+  <si>
+    <t>عمر رضا تونى طلبه</t>
+  </si>
+  <si>
+    <t>عبدالله ناصر أنور عبد المجيد</t>
+  </si>
+  <si>
+    <t>اندرو محروس مختار مهنى</t>
+  </si>
+  <si>
+    <t>فاطمه ناجى عبد السلام حسن</t>
+  </si>
+  <si>
+    <t>ماركو مجدى مكرم فريد</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
     <t>عمر احمد عبد الرحيم محمد</t>
   </si>
   <si>
-    <t>آلاء تجانى حسين على</t>
-  </si>
-  <si>
-    <t>رقيه محمد احمد عرابي</t>
-  </si>
-  <si>
-    <t>جاسر جدامى محمد محمد</t>
-  </si>
-  <si>
-    <t>اياد خيرى لطفى عبد الجيد</t>
-  </si>
-  <si>
-    <t>محمود عيد عبدالله عبدالله</t>
-  </si>
-  <si>
-    <t>آيه اسامه محمد السعيد أمين</t>
-  </si>
-  <si>
-    <t>احمد عبد الرؤوف احمد فضل</t>
-  </si>
-  <si>
-    <t>يوسف علاء الدين محمد محمد</t>
-  </si>
-  <si>
-    <t>فاطمه ضاحى محمد محمود</t>
-  </si>
-  <si>
-    <t>مارفينا مجدى خميس رشدى</t>
-  </si>
-  <si>
-    <t>ليديا عصام مكرم نجيب</t>
-  </si>
-  <si>
-    <t>شادي احمد علي مهني</t>
-  </si>
-  <si>
-    <t>شهاب محمد مخلوف محمد</t>
-  </si>
-  <si>
-    <t>نورهان محمود محمد احمد</t>
-  </si>
-  <si>
-    <t>عمرو محمد أحمد دردير</t>
-  </si>
-  <si>
-    <t>محمد احمد حسن محمد</t>
-  </si>
-  <si>
-    <t>اسلام عبد العال عبد السلام عبد الحميد</t>
-  </si>
-  <si>
-    <t>حسام احمد عبد المطلب احمد</t>
-  </si>
-  <si>
-    <t>حازم ياسر عبد النبى عبد الوهاب</t>
-  </si>
-  <si>
-    <t>أحمد عاطف حسين محمد</t>
-  </si>
-  <si>
-    <t>فاتن حماد عبد الحليم على</t>
-  </si>
-  <si>
-    <t>كريم جمال سعيد على</t>
-  </si>
-  <si>
-    <t>يحيى صفوت يحيى رمضان</t>
-  </si>
-  <si>
-    <t>احمد محمود عبدالمنعم احمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد محمود أحمد</t>
-  </si>
-  <si>
-    <t>زياد محمد رجائى محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن اشرف موسى هاشم</t>
-  </si>
-  <si>
-    <t>دميانه أشرف ماهر اسحق</t>
-  </si>
-  <si>
-    <t>زياد أشرف محمد محمود</t>
-  </si>
-  <si>
-    <t>ابراهيم محمد محمد ذكى</t>
-  </si>
-  <si>
-    <t>اميره حمدى مصطفى محمد</t>
-  </si>
-  <si>
-    <t>يوسف مصطفي سيد يوسف</t>
-  </si>
-  <si>
-    <t>رانيا سيد صلاح الدين على</t>
-  </si>
-  <si>
-    <t>حازم عباس خليفة عباس</t>
-  </si>
-  <si>
-    <t>رقيه على محمد خلف</t>
-  </si>
-  <si>
-    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
-  </si>
-  <si>
-    <t>ابراهيم محمود محمد عبدالنعيم</t>
-  </si>
-  <si>
-    <t>بهاء الدين محمد ابراهيم على</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>يوسف احمد سمير محمد</t>
-  </si>
-  <si>
-    <t>محمد رجب لطفى كامل</t>
-  </si>
-  <si>
-    <t>احمد طارق محمد محمود</t>
-  </si>
-  <si>
-    <t>عبدالله محمد سيد صادق</t>
-  </si>
-  <si>
-    <t>سهيله عبد القادر احمد عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد توفيق محمد محمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>مريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>شهد حسين محمود صابر</t>
-  </si>
-  <si>
-    <t>محمد سرحان محمد زكى</t>
-  </si>
-  <si>
-    <t>لمياء عبد القادر محمد فتحى</t>
-  </si>
-  <si>
-    <t>أميمة رأفت محمود احمد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>احمد رمضان محمد عبد الحميد</t>
-  </si>
-  <si>
-    <t>كريم محمد عبد الوهاب عيد</t>
-  </si>
-  <si>
-    <t>عمر رضا تونى طلبه</t>
-  </si>
-  <si>
-    <t>عبدالله ناصر أنور عبد المجيد</t>
-  </si>
-  <si>
-    <t>اندرو محروس مختار مهنى</t>
-  </si>
-  <si>
-    <t>فاطمه ناجى عبد السلام حسن</t>
-  </si>
-  <si>
-    <t>ماركو مجدى مكرم فريد</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -1900,495 +1900,495 @@
     <t>30408052402216</t>
   </si>
   <si>
+    <t>30504272400043</t>
+  </si>
+  <si>
+    <t>30503012408168</t>
+  </si>
+  <si>
+    <t>30404012401718</t>
+  </si>
+  <si>
+    <t>30505062400713</t>
+  </si>
+  <si>
+    <t>30504072401878</t>
+  </si>
+  <si>
+    <t>30402152404161</t>
+  </si>
+  <si>
+    <t>30406152402776</t>
+  </si>
+  <si>
+    <t>30510012425255</t>
+  </si>
+  <si>
+    <t>30411212400089</t>
+  </si>
+  <si>
+    <t>30509112401606</t>
+  </si>
+  <si>
+    <t>30310262401948</t>
+  </si>
+  <si>
+    <t>30508312401078</t>
+  </si>
+  <si>
+    <t>30408102403154</t>
+  </si>
+  <si>
+    <t>30303262400287</t>
+  </si>
+  <si>
+    <t>30507152404052</t>
+  </si>
+  <si>
+    <t>30205122402776</t>
+  </si>
+  <si>
+    <t>30511242401912</t>
+  </si>
+  <si>
+    <t>30512202400154</t>
+  </si>
+  <si>
+    <t>30411012411337</t>
+  </si>
+  <si>
+    <t>٣٠٣٠٤١٣٢٤٠٠٦٠٥</t>
+  </si>
+  <si>
+    <t>30507232402859</t>
+  </si>
+  <si>
+    <t>30305232401877</t>
+  </si>
+  <si>
+    <t>30102042403077</t>
+  </si>
+  <si>
+    <t>30411062404552</t>
+  </si>
+  <si>
+    <t>30408062402354</t>
+  </si>
+  <si>
+    <t>30307102401398</t>
+  </si>
+  <si>
+    <t>30507032403826</t>
+  </si>
+  <si>
+    <t>30504282401757</t>
+  </si>
+  <si>
+    <t>30504142403393</t>
+  </si>
+  <si>
+    <t>30407122401208</t>
+  </si>
+  <si>
+    <t>30506282400915</t>
+  </si>
+  <si>
+    <t>30409222403367</t>
+  </si>
+  <si>
+    <t>30507012411733</t>
+  </si>
+  <si>
+    <t>30411102404968</t>
+  </si>
+  <si>
+    <t>30310012403406</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
+  </si>
+  <si>
+    <t>30506082400619</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30503242401413</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
+  </si>
+  <si>
+    <t>30507262401954</t>
+  </si>
+  <si>
+    <t>30405262402457</t>
+  </si>
+  <si>
+    <t>30410312400403</t>
+  </si>
+  <si>
+    <t>30506152402932</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30509052401709</t>
+  </si>
+  <si>
+    <t>30408182401521</t>
+  </si>
+  <si>
+    <t>30410232401859</t>
+  </si>
+  <si>
+    <t>30409222402263</t>
+  </si>
+  <si>
+    <t>30308062400144</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30302142401658</t>
+  </si>
+  <si>
+    <t>30506272400259</t>
+  </si>
+  <si>
+    <t>30409012413599</t>
+  </si>
+  <si>
+    <t>30601162402453</t>
+  </si>
+  <si>
+    <t>30310012402973</t>
+  </si>
+  <si>
+    <t>30506170300209</t>
+  </si>
+  <si>
+    <t>30409172401791</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
     <t>30508192400552</t>
   </si>
   <si>
-    <t>30504272400043</t>
-  </si>
-  <si>
-    <t>30503012408168</t>
-  </si>
-  <si>
-    <t>30404012401718</t>
-  </si>
-  <si>
-    <t>30505062400713</t>
-  </si>
-  <si>
-    <t>30504072401878</t>
-  </si>
-  <si>
-    <t>30402152404161</t>
-  </si>
-  <si>
-    <t>30406152402776</t>
-  </si>
-  <si>
-    <t>30510012425255</t>
-  </si>
-  <si>
-    <t>30411212400089</t>
-  </si>
-  <si>
-    <t>30509112401606</t>
-  </si>
-  <si>
-    <t>30310262401948</t>
-  </si>
-  <si>
-    <t>30508312401078</t>
-  </si>
-  <si>
-    <t>30408102403154</t>
-  </si>
-  <si>
-    <t>30303262400287</t>
-  </si>
-  <si>
-    <t>30507152404052</t>
-  </si>
-  <si>
-    <t>30205122402776</t>
-  </si>
-  <si>
-    <t>30511242401912</t>
-  </si>
-  <si>
-    <t>30512202400154</t>
-  </si>
-  <si>
-    <t>30411012411337</t>
-  </si>
-  <si>
-    <t>٣٠٣٠٤١٣٢٤٠٠٦٠٥</t>
-  </si>
-  <si>
-    <t>30507232402859</t>
-  </si>
-  <si>
-    <t>30305232401877</t>
-  </si>
-  <si>
-    <t>30102042403077</t>
-  </si>
-  <si>
-    <t>30411062404552</t>
-  </si>
-  <si>
-    <t>30408062402354</t>
-  </si>
-  <si>
-    <t>30307102401398</t>
-  </si>
-  <si>
-    <t>30507032403826</t>
-  </si>
-  <si>
-    <t>30504282401757</t>
-  </si>
-  <si>
-    <t>30504142403393</t>
-  </si>
-  <si>
-    <t>30407122401208</t>
-  </si>
-  <si>
-    <t>30506282400915</t>
-  </si>
-  <si>
-    <t>30409222403367</t>
-  </si>
-  <si>
-    <t>30507012411733</t>
-  </si>
-  <si>
-    <t>30411102404968</t>
-  </si>
-  <si>
-    <t>30310012403406</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
-  </si>
-  <si>
-    <t>30506082400619</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30503242401413</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
-  </si>
-  <si>
-    <t>30507262401954</t>
-  </si>
-  <si>
-    <t>30405262402457</t>
-  </si>
-  <si>
-    <t>30410312400403</t>
-  </si>
-  <si>
-    <t>30506152402932</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30509052401709</t>
-  </si>
-  <si>
-    <t>30408182401521</t>
-  </si>
-  <si>
-    <t>30410232401859</t>
-  </si>
-  <si>
-    <t>30409222402263</t>
-  </si>
-  <si>
-    <t>30308062400144</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30302142401658</t>
-  </si>
-  <si>
-    <t>30506272400259</t>
-  </si>
-  <si>
-    <t>30409012413599</t>
-  </si>
-  <si>
-    <t>30601162402453</t>
-  </si>
-  <si>
-    <t>30310012402973</t>
-  </si>
-  <si>
-    <t>30506170300209</t>
-  </si>
-  <si>
-    <t>30409172401791</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3064,493 +3064,493 @@
     <t>01124580279</t>
   </si>
   <si>
+    <t>01120793251</t>
+  </si>
+  <si>
+    <t>01558381570</t>
+  </si>
+  <si>
+    <t>01026897744</t>
+  </si>
+  <si>
+    <t>01155709241</t>
+  </si>
+  <si>
+    <t>01029832053</t>
+  </si>
+  <si>
+    <t>1111461693</t>
+  </si>
+  <si>
+    <t>01015307003</t>
+  </si>
+  <si>
+    <t>01030604456</t>
+  </si>
+  <si>
+    <t>01113502763</t>
+  </si>
+  <si>
+    <t>1225691232</t>
+  </si>
+  <si>
+    <t>٠١٢٨٤٧٧٦٢٠٠</t>
+  </si>
+  <si>
+    <t>01555790021</t>
+  </si>
+  <si>
+    <t>01146575843</t>
+  </si>
+  <si>
+    <t>01558260721</t>
+  </si>
+  <si>
+    <t>01097343197</t>
+  </si>
+  <si>
+    <t>01154234758</t>
+  </si>
+  <si>
+    <t>01144281472</t>
+  </si>
+  <si>
+    <t>01066421775</t>
+  </si>
+  <si>
+    <t>01080154633</t>
+  </si>
+  <si>
+    <t>01005889381</t>
+  </si>
+  <si>
+    <t>٠١٢٠٧١٢٨١٠٠</t>
+  </si>
+  <si>
+    <t>01027583374</t>
+  </si>
+  <si>
+    <t>01032751655</t>
+  </si>
+  <si>
+    <t>01026737117</t>
+  </si>
+  <si>
+    <t>01068564500</t>
+  </si>
+  <si>
+    <t>01007841835</t>
+  </si>
+  <si>
+    <t>01093117713</t>
+  </si>
+  <si>
+    <t>01211926379</t>
+  </si>
+  <si>
+    <t>01142528896</t>
+  </si>
+  <si>
+    <t>01027158830</t>
+  </si>
+  <si>
+    <t>01036343803</t>
+  </si>
+  <si>
+    <t>01156509914</t>
+  </si>
+  <si>
+    <t>01016327718</t>
+  </si>
+  <si>
+    <t>01094773238</t>
+  </si>
+  <si>
+    <t>01127048374</t>
+  </si>
+  <si>
+    <t>01006270603</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0114356079</t>
+  </si>
+  <si>
+    <t>01012467272</t>
+  </si>
+  <si>
+    <t>1010934419</t>
+  </si>
+  <si>
+    <t>01005363873</t>
+  </si>
+  <si>
+    <t>01146971936</t>
+  </si>
+  <si>
+    <t>01143749439</t>
+  </si>
+  <si>
+    <t>01099101872</t>
+  </si>
+  <si>
+    <t>01060726096</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01101609533</t>
+  </si>
+  <si>
+    <t>0111590035</t>
+  </si>
+  <si>
+    <t>01148375746</t>
+  </si>
+  <si>
+    <t>01115291432</t>
+  </si>
+  <si>
+    <t>01121482192</t>
+  </si>
+  <si>
+    <t>1060458756</t>
+  </si>
+  <si>
+    <t>01021408975</t>
+  </si>
+  <si>
+    <t>01068360992</t>
+  </si>
+  <si>
+    <t>01061982978</t>
+  </si>
+  <si>
+    <t>01092079993</t>
+  </si>
+  <si>
+    <t>01288364393</t>
+  </si>
+  <si>
+    <t>01157384981</t>
+  </si>
+  <si>
+    <t>01283970879</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01099393313</t>
+  </si>
+  <si>
+    <t>01093075647</t>
+  </si>
+  <si>
+    <t>01037186555</t>
+  </si>
+  <si>
+    <t>01129169104</t>
+  </si>
+  <si>
+    <t>01001362969</t>
+  </si>
+  <si>
+    <t>01151741232</t>
+  </si>
+  <si>
+    <t>01013305686</t>
+  </si>
+  <si>
+    <t>01150936407</t>
+  </si>
+  <si>
+    <t>01002331784</t>
+  </si>
+  <si>
+    <t>01150905692</t>
+  </si>
+  <si>
+    <t>01028993616</t>
+  </si>
+  <si>
+    <t>01119364560</t>
+  </si>
+  <si>
+    <t>01114623756</t>
+  </si>
+  <si>
+    <t>01110180758</t>
+  </si>
+  <si>
+    <t>01098408936</t>
+  </si>
+  <si>
+    <t>01026439570</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
     <t>01067089320</t>
-  </si>
-  <si>
-    <t>01120793251</t>
-  </si>
-  <si>
-    <t>01558381570</t>
-  </si>
-  <si>
-    <t>01026897744</t>
-  </si>
-  <si>
-    <t>01155709241</t>
-  </si>
-  <si>
-    <t>01029832053</t>
-  </si>
-  <si>
-    <t>1111461693</t>
-  </si>
-  <si>
-    <t>01015307003</t>
-  </si>
-  <si>
-    <t>01030604456</t>
-  </si>
-  <si>
-    <t>01113502763</t>
-  </si>
-  <si>
-    <t>1225691232</t>
-  </si>
-  <si>
-    <t>٠١٢٨٤٧٧٦٢٠٠</t>
-  </si>
-  <si>
-    <t>01555790021</t>
-  </si>
-  <si>
-    <t>01146575843</t>
-  </si>
-  <si>
-    <t>01558260721</t>
-  </si>
-  <si>
-    <t>01097343197</t>
-  </si>
-  <si>
-    <t>01154234758</t>
-  </si>
-  <si>
-    <t>01144281472</t>
-  </si>
-  <si>
-    <t>01066421775</t>
-  </si>
-  <si>
-    <t>01080154633</t>
-  </si>
-  <si>
-    <t>01005889381</t>
-  </si>
-  <si>
-    <t>٠١٢٠٧١٢٨١٠٠</t>
-  </si>
-  <si>
-    <t>01027583374</t>
-  </si>
-  <si>
-    <t>01032751655</t>
-  </si>
-  <si>
-    <t>01026737117</t>
-  </si>
-  <si>
-    <t>01068564500</t>
-  </si>
-  <si>
-    <t>01007841835</t>
-  </si>
-  <si>
-    <t>01093117713</t>
-  </si>
-  <si>
-    <t>01211926379</t>
-  </si>
-  <si>
-    <t>01142528896</t>
-  </si>
-  <si>
-    <t>01027158830</t>
-  </si>
-  <si>
-    <t>01036343803</t>
-  </si>
-  <si>
-    <t>01156509914</t>
-  </si>
-  <si>
-    <t>01016327718</t>
-  </si>
-  <si>
-    <t>01094773238</t>
-  </si>
-  <si>
-    <t>01127048374</t>
-  </si>
-  <si>
-    <t>01006270603</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0114356079</t>
-  </si>
-  <si>
-    <t>01012467272</t>
-  </si>
-  <si>
-    <t>1010934419</t>
-  </si>
-  <si>
-    <t>01005363873</t>
-  </si>
-  <si>
-    <t>01146971936</t>
-  </si>
-  <si>
-    <t>01143749439</t>
-  </si>
-  <si>
-    <t>01099101872</t>
-  </si>
-  <si>
-    <t>01060726096</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01101609533</t>
-  </si>
-  <si>
-    <t>0111590035</t>
-  </si>
-  <si>
-    <t>01148375746</t>
-  </si>
-  <si>
-    <t>01115291432</t>
-  </si>
-  <si>
-    <t>01121482192</t>
-  </si>
-  <si>
-    <t>1060458756</t>
-  </si>
-  <si>
-    <t>01021408975</t>
-  </si>
-  <si>
-    <t>01068360992</t>
-  </si>
-  <si>
-    <t>01061982978</t>
-  </si>
-  <si>
-    <t>01092079993</t>
-  </si>
-  <si>
-    <t>01288364393</t>
-  </si>
-  <si>
-    <t>01157384981</t>
-  </si>
-  <si>
-    <t>01283970879</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01099393313</t>
-  </si>
-  <si>
-    <t>01093075647</t>
-  </si>
-  <si>
-    <t>01037186555</t>
-  </si>
-  <si>
-    <t>01129169104</t>
-  </si>
-  <si>
-    <t>01001362969</t>
-  </si>
-  <si>
-    <t>01151741232</t>
-  </si>
-  <si>
-    <t>01013305686</t>
-  </si>
-  <si>
-    <t>01150936407</t>
-  </si>
-  <si>
-    <t>01002331784</t>
-  </si>
-  <si>
-    <t>01150905692</t>
-  </si>
-  <si>
-    <t>01028993616</t>
-  </si>
-  <si>
-    <t>01119364560</t>
-  </si>
-  <si>
-    <t>01114623756</t>
-  </si>
-  <si>
-    <t>01110180758</t>
-  </si>
-  <si>
-    <t>01098408936</t>
-  </si>
-  <si>
-    <t>01026439570</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
   </si>
   <si>
     <t>1353</t>
@@ -15010,22 +15010,22 @@
         <v>1016</v>
       </c>
       <c r="D227" t="s">
-        <v>1217</v>
+        <v>1314</v>
       </c>
       <c r="E227" t="s">
-        <v>1405</v>
+        <v>1502</v>
       </c>
       <c r="F227" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G227" t="s">
         <v>1561</v>
       </c>
       <c r="H227" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I227" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J227" t="s">
         <v>1562</v>
@@ -15054,34 +15054,34 @@
         <v>1017</v>
       </c>
       <c r="D228" t="s">
-        <v>1314</v>
+        <v>1206</v>
       </c>
       <c r="E228" t="s">
-        <v>1502</v>
+        <v>1394</v>
       </c>
       <c r="F228" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G228" t="s">
         <v>1561</v>
       </c>
       <c r="H228" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I228" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J228" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K228" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L228" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M228" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N228" t="s">
         <v>1568</v>
@@ -15098,10 +15098,10 @@
         <v>1018</v>
       </c>
       <c r="D229" t="s">
-        <v>1206</v>
+        <v>1315</v>
       </c>
       <c r="E229" t="s">
-        <v>1394</v>
+        <v>1503</v>
       </c>
       <c r="F229" t="s">
         <v>1555</v>
@@ -15110,22 +15110,22 @@
         <v>1561</v>
       </c>
       <c r="H229" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I229" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J229" t="s">
         <v>1567</v>
       </c>
       <c r="K229" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L229" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M229" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N229" t="s">
         <v>1568</v>
@@ -15142,13 +15142,13 @@
         <v>1019</v>
       </c>
       <c r="D230" t="s">
-        <v>1315</v>
+        <v>1184</v>
       </c>
       <c r="E230" t="s">
-        <v>1503</v>
+        <v>1372</v>
       </c>
       <c r="F230" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G230" t="s">
         <v>1561</v>
@@ -15186,34 +15186,34 @@
         <v>1020</v>
       </c>
       <c r="D231" t="s">
-        <v>1184</v>
+        <v>1316</v>
       </c>
       <c r="E231" t="s">
-        <v>1372</v>
+        <v>1504</v>
       </c>
       <c r="F231" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G231" t="s">
         <v>1561</v>
       </c>
       <c r="H231" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I231" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J231" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K231" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L231" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M231" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N231" t="s">
         <v>1568</v>
@@ -15230,34 +15230,34 @@
         <v>1021</v>
       </c>
       <c r="D232" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="E232" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="F232" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G232" t="s">
         <v>1561</v>
       </c>
       <c r="H232" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I232" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J232" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K232" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L232" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M232" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="N232" t="s">
         <v>1568</v>
@@ -15274,34 +15274,34 @@
         <v>1022</v>
       </c>
       <c r="D233" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E233" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="F233" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G233" t="s">
         <v>1561</v>
       </c>
       <c r="H233" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I233" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J233" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K233" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L233" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M233" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N233" t="s">
         <v>1568</v>
@@ -15318,13 +15318,13 @@
         <v>1023</v>
       </c>
       <c r="D234" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E234" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="F234" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G234" t="s">
         <v>1561</v>
@@ -15333,19 +15333,19 @@
         <v>1564</v>
       </c>
       <c r="I234" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J234" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K234" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L234" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M234" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N234" t="s">
         <v>1568</v>
@@ -15362,13 +15362,13 @@
         <v>1024</v>
       </c>
       <c r="D235" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E235" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="F235" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G235" t="s">
         <v>1561</v>
@@ -15377,19 +15377,19 @@
         <v>1564</v>
       </c>
       <c r="I235" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="J235" t="s">
         <v>1567</v>
       </c>
       <c r="K235" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L235" t="s">
         <v>1565</v>
       </c>
       <c r="M235" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N235" t="s">
         <v>1568</v>
@@ -15406,34 +15406,34 @@
         <v>1025</v>
       </c>
       <c r="D236" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E236" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="F236" t="s">
         <v>1556</v>
       </c>
       <c r="G236" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H236" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I236" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="J236" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K236" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L236" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M236" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N236" t="s">
         <v>1568</v>
@@ -15450,13 +15450,13 @@
         <v>1026</v>
       </c>
       <c r="D237" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E237" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F237" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G237" t="s">
         <v>1564</v>
@@ -15494,34 +15494,34 @@
         <v>1027</v>
       </c>
       <c r="D238" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="E238" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="F238" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G238" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H238" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="I238" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="J238" t="s">
         <v>1565</v>
       </c>
       <c r="K238" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L238" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="M238" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N238" t="s">
         <v>1568</v>
@@ -15538,34 +15538,34 @@
         <v>1028</v>
       </c>
       <c r="D239" t="s">
-        <v>1323</v>
+        <v>1225</v>
       </c>
       <c r="E239" t="s">
-        <v>1511</v>
+        <v>1413</v>
       </c>
       <c r="F239" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G239" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H239" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I239" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J239" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K239" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L239" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M239" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N239" t="s">
         <v>1568</v>
@@ -15582,10 +15582,10 @@
         <v>1029</v>
       </c>
       <c r="D240" t="s">
-        <v>1225</v>
+        <v>1194</v>
       </c>
       <c r="E240" t="s">
-        <v>1413</v>
+        <v>1382</v>
       </c>
       <c r="F240" t="s">
         <v>1556</v>
@@ -15600,16 +15600,16 @@
         <v>1567</v>
       </c>
       <c r="J240" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K240" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L240" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M240" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="N240" t="s">
         <v>1568</v>
@@ -15626,34 +15626,34 @@
         <v>1030</v>
       </c>
       <c r="D241" t="s">
-        <v>1194</v>
+        <v>1322</v>
       </c>
       <c r="E241" t="s">
-        <v>1382</v>
+        <v>1510</v>
       </c>
       <c r="F241" t="s">
         <v>1556</v>
       </c>
       <c r="G241" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H241" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I241" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J241" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K241" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L241" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M241" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N241" t="s">
         <v>1568</v>
@@ -15670,34 +15670,34 @@
         <v>1031</v>
       </c>
       <c r="D242" t="s">
-        <v>1322</v>
+        <v>1262</v>
       </c>
       <c r="E242" t="s">
-        <v>1510</v>
+        <v>1450</v>
       </c>
       <c r="F242" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G242" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H242" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I242" t="s">
         <v>1564</v>
       </c>
       <c r="J242" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K242" t="s">
         <v>1565</v>
       </c>
       <c r="L242" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M242" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N242" t="s">
         <v>1568</v>
@@ -15708,16 +15708,16 @@
         <v>255</v>
       </c>
       <c r="B243" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C243" t="s">
         <v>1032</v>
       </c>
       <c r="D243" t="s">
-        <v>1262</v>
+        <v>1315</v>
       </c>
       <c r="E243" t="s">
-        <v>1450</v>
+        <v>1503</v>
       </c>
       <c r="F243" t="s">
         <v>1555</v>
@@ -15726,22 +15726,22 @@
         <v>1561</v>
       </c>
       <c r="H243" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I243" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J243" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K243" t="s">
         <v>1565</v>
       </c>
       <c r="L243" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M243" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N243" t="s">
         <v>1568</v>
@@ -15758,34 +15758,34 @@
         <v>1033</v>
       </c>
       <c r="D244" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
       <c r="E244" t="s">
-        <v>1503</v>
+        <v>1512</v>
       </c>
       <c r="F244" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G244" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H244" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I244" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J244" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K244" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L244" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="M244" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N244" t="s">
         <v>1568</v>
@@ -15802,13 +15802,13 @@
         <v>1034</v>
       </c>
       <c r="D245" t="s">
-        <v>1324</v>
+        <v>1219</v>
       </c>
       <c r="E245" t="s">
-        <v>1512</v>
+        <v>1407</v>
       </c>
       <c r="F245" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G245" t="s">
         <v>1563</v>
@@ -15846,34 +15846,34 @@
         <v>1035</v>
       </c>
       <c r="D246" t="s">
-        <v>1219</v>
+        <v>1325</v>
       </c>
       <c r="E246" t="s">
-        <v>1407</v>
+        <v>1513</v>
       </c>
       <c r="F246" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G246" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H246" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I246" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J246" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K246" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L246" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M246" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N246" t="s">
         <v>1568</v>
@@ -15890,13 +15890,13 @@
         <v>1036</v>
       </c>
       <c r="D247" t="s">
-        <v>1325</v>
+        <v>1216</v>
       </c>
       <c r="E247" t="s">
-        <v>1513</v>
+        <v>1404</v>
       </c>
       <c r="F247" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G247" t="s">
         <v>1561</v>
@@ -15905,16 +15905,16 @@
         <v>1564</v>
       </c>
       <c r="I247" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J247" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K247" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L247" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M247" t="s">
         <v>1566</v>
@@ -15934,13 +15934,13 @@
         <v>1037</v>
       </c>
       <c r="D248" t="s">
-        <v>1216</v>
+        <v>1326</v>
       </c>
       <c r="E248" t="s">
-        <v>1404</v>
+        <v>1514</v>
       </c>
       <c r="F248" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G248" t="s">
         <v>1561</v>
@@ -15952,16 +15952,16 @@
         <v>1562</v>
       </c>
       <c r="J248" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K248" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L248" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M248" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N248" t="s">
         <v>1568</v>
@@ -15978,13 +15978,13 @@
         <v>1038</v>
       </c>
       <c r="D249" t="s">
-        <v>1326</v>
+        <v>1224</v>
       </c>
       <c r="E249" t="s">
-        <v>1514</v>
+        <v>1412</v>
       </c>
       <c r="F249" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G249" t="s">
         <v>1561</v>
@@ -15993,13 +15993,13 @@
         <v>1564</v>
       </c>
       <c r="I249" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J249" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K249" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L249" t="s">
         <v>1565</v>
@@ -16022,13 +16022,13 @@
         <v>1039</v>
       </c>
       <c r="D250" t="s">
-        <v>1224</v>
+        <v>1327</v>
       </c>
       <c r="E250" t="s">
-        <v>1412</v>
+        <v>1515</v>
       </c>
       <c r="F250" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="G250" t="s">
         <v>1561</v>
@@ -16037,19 +16037,19 @@
         <v>1564</v>
       </c>
       <c r="I250" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J250" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K250" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L250" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M250" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N250" t="s">
         <v>1568</v>
@@ -16066,34 +16066,34 @@
         <v>1040</v>
       </c>
       <c r="D251" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E251" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="F251" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G251" t="s">
         <v>1561</v>
       </c>
       <c r="H251" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="I251" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J251" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K251" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L251" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M251" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N251" t="s">
         <v>1568</v>
@@ -16110,10 +16110,10 @@
         <v>1041</v>
       </c>
       <c r="D252" t="s">
-        <v>1328</v>
+        <v>1214</v>
       </c>
       <c r="E252" t="s">
-        <v>1516</v>
+        <v>1402</v>
       </c>
       <c r="F252" t="s">
         <v>1556</v>
@@ -16122,22 +16122,22 @@
         <v>1561</v>
       </c>
       <c r="H252" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="I252" t="s">
         <v>1567</v>
       </c>
       <c r="J252" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K252" t="s">
         <v>1562</v>
       </c>
       <c r="L252" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M252" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N252" t="s">
         <v>1568</v>
@@ -16154,10 +16154,10 @@
         <v>1042</v>
       </c>
       <c r="D253" t="s">
-        <v>1214</v>
+        <v>1269</v>
       </c>
       <c r="E253" t="s">
-        <v>1402</v>
+        <v>1457</v>
       </c>
       <c r="F253" t="s">
         <v>1556</v>
@@ -16169,10 +16169,10 @@
         <v>1564</v>
       </c>
       <c r="I253" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J253" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K253" t="s">
         <v>1562</v>
@@ -16181,7 +16181,7 @@
         <v>1566</v>
       </c>
       <c r="M253" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N253" t="s">
         <v>1568</v>
@@ -16198,10 +16198,10 @@
         <v>1043</v>
       </c>
       <c r="D254" t="s">
-        <v>1269</v>
+        <v>1329</v>
       </c>
       <c r="E254" t="s">
-        <v>1457</v>
+        <v>1517</v>
       </c>
       <c r="F254" t="s">
         <v>1556</v>
@@ -16210,22 +16210,22 @@
         <v>1561</v>
       </c>
       <c r="H254" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I254" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J254" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K254" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L254" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M254" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N254" t="s">
         <v>1568</v>
@@ -16242,34 +16242,34 @@
         <v>1044</v>
       </c>
       <c r="D255" t="s">
-        <v>1329</v>
+        <v>1225</v>
       </c>
       <c r="E255" t="s">
-        <v>1517</v>
+        <v>1413</v>
       </c>
       <c r="F255" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G255" t="s">
         <v>1561</v>
       </c>
       <c r="H255" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I255" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J255" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="K255" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L255" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M255" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N255" t="s">
         <v>1568</v>
@@ -16286,10 +16286,10 @@
         <v>1045</v>
       </c>
       <c r="D256" t="s">
-        <v>1225</v>
+        <v>1245</v>
       </c>
       <c r="E256" t="s">
-        <v>1413</v>
+        <v>1433</v>
       </c>
       <c r="F256" t="s">
         <v>1555</v>
@@ -16310,10 +16310,10 @@
         <v>1562</v>
       </c>
       <c r="L256" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M256" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N256" t="s">
         <v>1568</v>
@@ -16330,34 +16330,34 @@
         <v>1046</v>
       </c>
       <c r="D257" t="s">
-        <v>1245</v>
+        <v>1300</v>
       </c>
       <c r="E257" t="s">
-        <v>1433</v>
+        <v>1488</v>
       </c>
       <c r="F257" t="s">
         <v>1555</v>
       </c>
       <c r="G257" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H257" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I257" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J257" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K257" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L257" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M257" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N257" t="s">
         <v>1568</v>
@@ -16374,34 +16374,34 @@
         <v>1047</v>
       </c>
       <c r="D258" t="s">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="E258" t="s">
-        <v>1488</v>
+        <v>1518</v>
       </c>
       <c r="F258" t="s">
         <v>1555</v>
       </c>
       <c r="G258" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H258" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I258" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J258" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K258" t="s">
         <v>1566</v>
       </c>
       <c r="L258" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M258" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N258" t="s">
         <v>1568</v>
@@ -16418,10 +16418,10 @@
         <v>1048</v>
       </c>
       <c r="D259" t="s">
-        <v>1330</v>
+        <v>1278</v>
       </c>
       <c r="E259" t="s">
-        <v>1518</v>
+        <v>1466</v>
       </c>
       <c r="F259" t="s">
         <v>1555</v>
@@ -16433,19 +16433,19 @@
         <v>1564</v>
       </c>
       <c r="I259" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J259" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K259" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L259" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M259" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N259" t="s">
         <v>1568</v>
@@ -16462,10 +16462,10 @@
         <v>1049</v>
       </c>
       <c r="D260" t="s">
-        <v>1278</v>
+        <v>1331</v>
       </c>
       <c r="E260" t="s">
-        <v>1466</v>
+        <v>1519</v>
       </c>
       <c r="F260" t="s">
         <v>1555</v>
@@ -16474,13 +16474,13 @@
         <v>1561</v>
       </c>
       <c r="H260" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I260" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J260" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K260" t="s">
         <v>1565</v>
@@ -16489,7 +16489,7 @@
         <v>1566</v>
       </c>
       <c r="M260" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N260" t="s">
         <v>1568</v>
@@ -16506,13 +16506,13 @@
         <v>1050</v>
       </c>
       <c r="D261" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="E261" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="F261" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G261" t="s">
         <v>1561</v>
@@ -16524,16 +16524,16 @@
         <v>1564</v>
       </c>
       <c r="J261" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K261" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L261" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M261" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N261" t="s">
         <v>1568</v>
@@ -16550,19 +16550,19 @@
         <v>1051</v>
       </c>
       <c r="D262" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="E262" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="F262" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G262" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H262" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="I262" t="s">
         <v>1564</v>
@@ -16574,7 +16574,7 @@
         <v>1562</v>
       </c>
       <c r="L262" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M262" t="s">
         <v>1566</v>
@@ -16594,31 +16594,31 @@
         <v>1052</v>
       </c>
       <c r="D263" t="s">
-        <v>1333</v>
+        <v>1262</v>
       </c>
       <c r="E263" t="s">
-        <v>1521</v>
+        <v>1450</v>
       </c>
       <c r="F263" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G263" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H263" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I263" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J263" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K263" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L263" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M263" t="s">
         <v>1566</v>
@@ -16638,28 +16638,28 @@
         <v>1053</v>
       </c>
       <c r="D264" t="s">
-        <v>1262</v>
+        <v>1329</v>
       </c>
       <c r="E264" t="s">
-        <v>1450</v>
+        <v>1517</v>
       </c>
       <c r="F264" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G264" t="s">
         <v>1561</v>
       </c>
       <c r="H264" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I264" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J264" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K264" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L264" t="s">
         <v>1565</v>
@@ -16682,34 +16682,34 @@
         <v>1054</v>
       </c>
       <c r="D265" t="s">
-        <v>1329</v>
+        <v>1246</v>
       </c>
       <c r="E265" t="s">
-        <v>1517</v>
+        <v>1434</v>
       </c>
       <c r="F265" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G265" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H265" t="s">
         <v>1564</v>
       </c>
       <c r="I265" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J265" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K265" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L265" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M265" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N265" t="s">
         <v>1568</v>
@@ -16726,25 +16726,25 @@
         <v>1055</v>
       </c>
       <c r="D266" t="s">
-        <v>1246</v>
+        <v>1265</v>
       </c>
       <c r="E266" t="s">
-        <v>1434</v>
+        <v>1453</v>
       </c>
       <c r="F266" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G266" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H266" t="s">
         <v>1564</v>
       </c>
       <c r="I266" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J266" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K266" t="s">
         <v>1565</v>
@@ -16753,7 +16753,7 @@
         <v>1566</v>
       </c>
       <c r="M266" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N266" t="s">
         <v>1568</v>
@@ -16770,34 +16770,34 @@
         <v>1056</v>
       </c>
       <c r="D267" t="s">
-        <v>1265</v>
+        <v>1240</v>
       </c>
       <c r="E267" t="s">
-        <v>1453</v>
+        <v>1428</v>
       </c>
       <c r="F267" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G267" t="s">
         <v>1561</v>
       </c>
       <c r="H267" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I267" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J267" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K267" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L267" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M267" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N267" t="s">
         <v>1568</v>
@@ -16814,10 +16814,10 @@
         <v>1057</v>
       </c>
       <c r="D268" t="s">
-        <v>1240</v>
+        <v>1194</v>
       </c>
       <c r="E268" t="s">
-        <v>1428</v>
+        <v>1382</v>
       </c>
       <c r="F268" t="s">
         <v>1555</v>
@@ -16829,19 +16829,19 @@
         <v>1562</v>
       </c>
       <c r="I268" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J268" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K268" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L268" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M268" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N268" t="s">
         <v>1568</v>
@@ -16858,10 +16858,10 @@
         <v>1058</v>
       </c>
       <c r="D269" t="s">
-        <v>1194</v>
+        <v>1241</v>
       </c>
       <c r="E269" t="s">
-        <v>1382</v>
+        <v>1429</v>
       </c>
       <c r="F269" t="s">
         <v>1555</v>
@@ -16873,19 +16873,19 @@
         <v>1562</v>
       </c>
       <c r="I269" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J269" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K269" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L269" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M269" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N269" t="s">
         <v>1568</v>
@@ -16902,22 +16902,22 @@
         <v>1059</v>
       </c>
       <c r="D270" t="s">
-        <v>1241</v>
+        <v>1310</v>
       </c>
       <c r="E270" t="s">
-        <v>1429</v>
+        <v>1498</v>
       </c>
       <c r="F270" t="s">
         <v>1555</v>
       </c>
       <c r="G270" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H270" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I270" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J270" t="s">
         <v>1567</v>
@@ -16926,7 +16926,7 @@
         <v>1563</v>
       </c>
       <c r="L270" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M270" t="s">
         <v>1566</v>
@@ -16943,37 +16943,37 @@
         <v>671</v>
       </c>
       <c r="C271" t="s">
-        <v>1060</v>
+        <v>824</v>
       </c>
       <c r="D271" t="s">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="E271" t="s">
-        <v>1498</v>
+        <v>1522</v>
       </c>
       <c r="F271" t="s">
         <v>1555</v>
       </c>
       <c r="G271" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H271" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I271" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J271" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K271" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L271" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M271" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N271" t="s">
         <v>1568</v>
@@ -16987,13 +16987,13 @@
         <v>672</v>
       </c>
       <c r="C272" t="s">
-        <v>824</v>
+        <v>1060</v>
       </c>
       <c r="D272" t="s">
-        <v>1334</v>
+        <v>1300</v>
       </c>
       <c r="E272" t="s">
-        <v>1522</v>
+        <v>1488</v>
       </c>
       <c r="F272" t="s">
         <v>1555</v>
@@ -17002,22 +17002,22 @@
         <v>1561</v>
       </c>
       <c r="H272" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I272" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J272" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K272" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L272" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M272" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N272" t="s">
         <v>1568</v>
@@ -17034,34 +17034,34 @@
         <v>1061</v>
       </c>
       <c r="D273" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="E273" t="s">
-        <v>1488</v>
+        <v>1459</v>
       </c>
       <c r="F273" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G273" t="s">
         <v>1561</v>
       </c>
       <c r="H273" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I273" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J273" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K273" t="s">
         <v>1563</v>
       </c>
       <c r="L273" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M273" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N273" t="s">
         <v>1568</v>
@@ -17078,13 +17078,13 @@
         <v>1062</v>
       </c>
       <c r="D274" t="s">
-        <v>1271</v>
+        <v>1302</v>
       </c>
       <c r="E274" t="s">
-        <v>1459</v>
+        <v>1490</v>
       </c>
       <c r="F274" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G274" t="s">
         <v>1561</v>
@@ -17096,7 +17096,7 @@
         <v>1567</v>
       </c>
       <c r="J274" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K274" t="s">
         <v>1563</v>
@@ -17105,7 +17105,7 @@
         <v>1562</v>
       </c>
       <c r="M274" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N274" t="s">
         <v>1568</v>
@@ -17122,10 +17122,10 @@
         <v>1063</v>
       </c>
       <c r="D275" t="s">
-        <v>1302</v>
+        <v>1206</v>
       </c>
       <c r="E275" t="s">
-        <v>1490</v>
+        <v>1394</v>
       </c>
       <c r="F275" t="s">
         <v>1555</v>
@@ -17140,13 +17140,13 @@
         <v>1567</v>
       </c>
       <c r="J275" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K275" t="s">
         <v>1563</v>
       </c>
       <c r="L275" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M275" t="s">
         <v>1566</v>
@@ -17166,10 +17166,10 @@
         <v>1064</v>
       </c>
       <c r="D276" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="E276" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="F276" t="s">
         <v>1555</v>
@@ -17184,16 +17184,16 @@
         <v>1567</v>
       </c>
       <c r="J276" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K276" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L276" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M276" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N276" t="s">
         <v>1568</v>
@@ -17210,13 +17210,13 @@
         <v>1065</v>
       </c>
       <c r="D277" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E277" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="F277" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G277" t="s">
         <v>1561</v>
@@ -17225,19 +17225,19 @@
         <v>1564</v>
       </c>
       <c r="I277" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J277" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K277" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L277" t="s">
         <v>1562</v>
       </c>
       <c r="M277" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N277" t="s">
         <v>1568</v>
@@ -17254,10 +17254,10 @@
         <v>1066</v>
       </c>
       <c r="D278" t="s">
-        <v>1212</v>
+        <v>1191</v>
       </c>
       <c r="E278" t="s">
-        <v>1400</v>
+        <v>1379</v>
       </c>
       <c r="F278" t="s">
         <v>1556</v>
@@ -17266,22 +17266,22 @@
         <v>1561</v>
       </c>
       <c r="H278" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I278" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J278" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K278" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L278" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M278" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N278" t="s">
         <v>1568</v>
@@ -17298,25 +17298,25 @@
         <v>1067</v>
       </c>
       <c r="D279" t="s">
-        <v>1191</v>
+        <v>1335</v>
       </c>
       <c r="E279" t="s">
-        <v>1379</v>
+        <v>1523</v>
       </c>
       <c r="F279" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G279" t="s">
         <v>1561</v>
       </c>
       <c r="H279" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I279" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J279" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K279" t="s">
         <v>1562</v>
@@ -17325,7 +17325,7 @@
         <v>1566</v>
       </c>
       <c r="M279" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N279" t="s">
         <v>1568</v>
@@ -17342,34 +17342,34 @@
         <v>1068</v>
       </c>
       <c r="D280" t="s">
-        <v>1335</v>
+        <v>1179</v>
       </c>
       <c r="E280" t="s">
-        <v>1523</v>
+        <v>1367</v>
       </c>
       <c r="F280" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G280" t="s">
         <v>1561</v>
       </c>
       <c r="H280" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="I280" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J280" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="K280" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L280" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M280" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="N280" t="s">
         <v>1568</v>
@@ -17386,34 +17386,34 @@
         <v>1069</v>
       </c>
       <c r="D281" t="s">
-        <v>1179</v>
+        <v>1278</v>
       </c>
       <c r="E281" t="s">
-        <v>1367</v>
+        <v>1466</v>
       </c>
       <c r="F281" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G281" t="s">
         <v>1561</v>
       </c>
       <c r="H281" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I281" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J281" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K281" t="s">
         <v>1565</v>
       </c>
       <c r="L281" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M281" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N281" t="s">
         <v>1568</v>
@@ -17430,22 +17430,22 @@
         <v>1070</v>
       </c>
       <c r="D282" t="s">
-        <v>1278</v>
+        <v>1256</v>
       </c>
       <c r="E282" t="s">
-        <v>1466</v>
+        <v>1444</v>
       </c>
       <c r="F282" t="s">
         <v>1555</v>
       </c>
       <c r="G282" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="H282" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I282" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J282" t="s">
         <v>1564</v>
@@ -17454,10 +17454,10 @@
         <v>1565</v>
       </c>
       <c r="L282" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="M282" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N282" t="s">
         <v>1568</v>
@@ -17474,34 +17474,34 @@
         <v>1071</v>
       </c>
       <c r="D283" t="s">
-        <v>1256</v>
+        <v>1228</v>
       </c>
       <c r="E283" t="s">
-        <v>1444</v>
+        <v>1416</v>
       </c>
       <c r="F283" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G283" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="H283" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I283" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J283" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K283" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L283" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M283" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N283" t="s">
         <v>1568</v>
@@ -17518,13 +17518,13 @@
         <v>1072</v>
       </c>
       <c r="D284" t="s">
-        <v>1228</v>
+        <v>1185</v>
       </c>
       <c r="E284" t="s">
-        <v>1416</v>
+        <v>1373</v>
       </c>
       <c r="F284" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G284" t="s">
         <v>1561</v>
@@ -17533,19 +17533,19 @@
         <v>1567</v>
       </c>
       <c r="I284" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J284" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K284" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L284" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M284" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N284" t="s">
         <v>1568</v>
@@ -17562,34 +17562,34 @@
         <v>1073</v>
       </c>
       <c r="D285" t="s">
-        <v>1185</v>
+        <v>1336</v>
       </c>
       <c r="E285" t="s">
-        <v>1373</v>
+        <v>1524</v>
       </c>
       <c r="F285" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G285" t="s">
         <v>1561</v>
       </c>
       <c r="H285" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I285" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J285" t="s">
         <v>1562</v>
       </c>
       <c r="K285" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L285" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M285" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N285" t="s">
         <v>1568</v>
@@ -17606,22 +17606,22 @@
         <v>1074</v>
       </c>
       <c r="D286" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="E286" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="F286" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G286" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H286" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I286" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J286" t="s">
         <v>1562</v>
@@ -17630,10 +17630,10 @@
         <v>1565</v>
       </c>
       <c r="L286" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M286" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N286" t="s">
         <v>1568</v>
@@ -17650,28 +17650,28 @@
         <v>1075</v>
       </c>
       <c r="D287" t="s">
-        <v>1337</v>
+        <v>1256</v>
       </c>
       <c r="E287" t="s">
-        <v>1525</v>
+        <v>1444</v>
       </c>
       <c r="F287" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G287" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H287" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I287" t="s">
         <v>1567</v>
       </c>
       <c r="J287" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K287" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L287" t="s">
         <v>1566</v>
@@ -17694,13 +17694,13 @@
         <v>1076</v>
       </c>
       <c r="D288" t="s">
-        <v>1256</v>
+        <v>1329</v>
       </c>
       <c r="E288" t="s">
-        <v>1444</v>
+        <v>1517</v>
       </c>
       <c r="F288" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G288" t="s">
         <v>1561</v>
@@ -17715,13 +17715,13 @@
         <v>1565</v>
       </c>
       <c r="K288" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L288" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M288" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N288" t="s">
         <v>1568</v>
@@ -17738,10 +17738,10 @@
         <v>1077</v>
       </c>
       <c r="D289" t="s">
-        <v>1329</v>
+        <v>1274</v>
       </c>
       <c r="E289" t="s">
-        <v>1517</v>
+        <v>1462</v>
       </c>
       <c r="F289" t="s">
         <v>1556</v>
@@ -17750,22 +17750,22 @@
         <v>1561</v>
       </c>
       <c r="H289" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I289" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J289" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K289" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L289" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M289" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N289" t="s">
         <v>1568</v>
@@ -17782,10 +17782,10 @@
         <v>1078</v>
       </c>
       <c r="D290" t="s">
-        <v>1274</v>
+        <v>1338</v>
       </c>
       <c r="E290" t="s">
-        <v>1462</v>
+        <v>1526</v>
       </c>
       <c r="F290" t="s">
         <v>1556</v>
@@ -17794,22 +17794,22 @@
         <v>1561</v>
       </c>
       <c r="H290" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="I290" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J290" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K290" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L290" t="s">
         <v>1565</v>
       </c>
       <c r="M290" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N290" t="s">
         <v>1568</v>
@@ -17826,25 +17826,25 @@
         <v>1079</v>
       </c>
       <c r="D291" t="s">
-        <v>1338</v>
+        <v>1211</v>
       </c>
       <c r="E291" t="s">
-        <v>1526</v>
+        <v>1399</v>
       </c>
       <c r="F291" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G291" t="s">
         <v>1561</v>
       </c>
       <c r="H291" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I291" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J291" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K291" t="s">
         <v>1566</v>
@@ -17853,7 +17853,7 @@
         <v>1565</v>
       </c>
       <c r="M291" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N291" t="s">
         <v>1568</v>
@@ -17870,13 +17870,13 @@
         <v>1080</v>
       </c>
       <c r="D292" t="s">
-        <v>1211</v>
+        <v>1284</v>
       </c>
       <c r="E292" t="s">
-        <v>1399</v>
+        <v>1472</v>
       </c>
       <c r="F292" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G292" t="s">
         <v>1561</v>
@@ -17914,19 +17914,19 @@
         <v>1081</v>
       </c>
       <c r="D293" t="s">
-        <v>1284</v>
+        <v>1179</v>
       </c>
       <c r="E293" t="s">
-        <v>1472</v>
+        <v>1367</v>
       </c>
       <c r="F293" t="s">
         <v>1555</v>
       </c>
       <c r="G293" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H293" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I293" t="s">
         <v>1567</v>
@@ -17935,13 +17935,13 @@
         <v>1562</v>
       </c>
       <c r="K293" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L293" t="s">
         <v>1565</v>
       </c>
       <c r="M293" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N293" t="s">
         <v>1568</v>
@@ -17958,34 +17958,34 @@
         <v>1082</v>
       </c>
       <c r="D294" t="s">
-        <v>1179</v>
+        <v>1194</v>
       </c>
       <c r="E294" t="s">
-        <v>1367</v>
+        <v>1382</v>
       </c>
       <c r="F294" t="s">
         <v>1555</v>
       </c>
       <c r="G294" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H294" t="s">
         <v>1561</v>
       </c>
       <c r="I294" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J294" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K294" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L294" t="s">
         <v>1565</v>
       </c>
       <c r="M294" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N294" t="s">
         <v>1568</v>
@@ -18002,34 +18002,34 @@
         <v>1083</v>
       </c>
       <c r="D295" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="E295" t="s">
-        <v>1382</v>
+        <v>1401</v>
       </c>
       <c r="F295" t="s">
         <v>1555</v>
       </c>
       <c r="G295" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H295" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I295" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J295" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K295" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L295" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M295" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N295" t="s">
         <v>1568</v>
@@ -18046,34 +18046,34 @@
         <v>1084</v>
       </c>
       <c r="D296" t="s">
-        <v>1213</v>
+        <v>1339</v>
       </c>
       <c r="E296" t="s">
-        <v>1401</v>
+        <v>1527</v>
       </c>
       <c r="F296" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G296" t="s">
         <v>1561</v>
       </c>
       <c r="H296" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I296" t="s">
         <v>1564</v>
       </c>
       <c r="J296" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K296" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L296" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M296" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N296" t="s">
         <v>1568</v>
@@ -18090,31 +18090,31 @@
         <v>1085</v>
       </c>
       <c r="D297" t="s">
-        <v>1339</v>
+        <v>1227</v>
       </c>
       <c r="E297" t="s">
-        <v>1527</v>
+        <v>1415</v>
       </c>
       <c r="F297" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G297" t="s">
         <v>1561</v>
       </c>
       <c r="H297" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I297" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J297" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K297" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L297" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M297" t="s">
         <v>1563</v>
@@ -18134,34 +18134,34 @@
         <v>1086</v>
       </c>
       <c r="D298" t="s">
-        <v>1227</v>
+        <v>1256</v>
       </c>
       <c r="E298" t="s">
-        <v>1415</v>
+        <v>1444</v>
       </c>
       <c r="F298" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G298" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="H298" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I298" t="s">
         <v>1566</v>
       </c>
       <c r="J298" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="K298" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L298" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M298" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N298" t="s">
         <v>1568</v>
@@ -18178,34 +18178,34 @@
         <v>1087</v>
       </c>
       <c r="D299" t="s">
-        <v>1256</v>
+        <v>1191</v>
       </c>
       <c r="E299" t="s">
-        <v>1444</v>
+        <v>1379</v>
       </c>
       <c r="F299" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G299" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H299" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I299" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J299" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K299" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L299" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M299" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N299" t="s">
         <v>1568</v>
@@ -18222,10 +18222,10 @@
         <v>1088</v>
       </c>
       <c r="D300" t="s">
-        <v>1191</v>
+        <v>1297</v>
       </c>
       <c r="E300" t="s">
-        <v>1379</v>
+        <v>1485</v>
       </c>
       <c r="F300" t="s">
         <v>1555</v>
@@ -18243,13 +18243,13 @@
         <v>1562</v>
       </c>
       <c r="K300" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L300" t="s">
         <v>1565</v>
       </c>
       <c r="M300" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N300" t="s">
         <v>1568</v>
@@ -18266,10 +18266,10 @@
         <v>1089</v>
       </c>
       <c r="D301" t="s">
-        <v>1297</v>
+        <v>1340</v>
       </c>
       <c r="E301" t="s">
-        <v>1485</v>
+        <v>1528</v>
       </c>
       <c r="F301" t="s">
         <v>1555</v>
@@ -18278,19 +18278,19 @@
         <v>1561</v>
       </c>
       <c r="H301" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I301" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J301" t="s">
         <v>1562</v>
       </c>
       <c r="K301" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L301" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M301" t="s">
         <v>1563</v>
@@ -18310,13 +18310,13 @@
         <v>1090</v>
       </c>
       <c r="D302" t="s">
-        <v>1340</v>
+        <v>1196</v>
       </c>
       <c r="E302" t="s">
-        <v>1528</v>
+        <v>1384</v>
       </c>
       <c r="F302" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G302" t="s">
         <v>1561</v>
@@ -18328,16 +18328,16 @@
         <v>1567</v>
       </c>
       <c r="J302" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K302" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L302" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M302" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N302" t="s">
         <v>1568</v>
@@ -18354,13 +18354,13 @@
         <v>1091</v>
       </c>
       <c r="D303" t="s">
-        <v>1196</v>
+        <v>1332</v>
       </c>
       <c r="E303" t="s">
-        <v>1384</v>
+        <v>1520</v>
       </c>
       <c r="F303" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G303" t="s">
         <v>1561</v>
@@ -18369,16 +18369,16 @@
         <v>1564</v>
       </c>
       <c r="I303" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J303" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K303" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L303" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M303" t="s">
         <v>1566</v>
@@ -18398,13 +18398,13 @@
         <v>1092</v>
       </c>
       <c r="D304" t="s">
-        <v>1332</v>
+        <v>1202</v>
       </c>
       <c r="E304" t="s">
-        <v>1520</v>
+        <v>1390</v>
       </c>
       <c r="F304" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G304" t="s">
         <v>1561</v>
@@ -18413,19 +18413,19 @@
         <v>1564</v>
       </c>
       <c r="I304" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J304" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K304" t="s">
         <v>1565</v>
       </c>
       <c r="L304" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M304" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N304" t="s">
         <v>1568</v>
@@ -18442,34 +18442,34 @@
         <v>1093</v>
       </c>
       <c r="D305" t="s">
-        <v>1202</v>
+        <v>1291</v>
       </c>
       <c r="E305" t="s">
-        <v>1390</v>
+        <v>1479</v>
       </c>
       <c r="F305" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G305" t="s">
         <v>1561</v>
       </c>
       <c r="H305" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I305" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J305" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K305" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L305" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M305" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N305" t="s">
         <v>1568</v>
@@ -18486,10 +18486,10 @@
         <v>1094</v>
       </c>
       <c r="D306" t="s">
-        <v>1291</v>
+        <v>1321</v>
       </c>
       <c r="E306" t="s">
-        <v>1479</v>
+        <v>1509</v>
       </c>
       <c r="F306" t="s">
         <v>1556</v>
@@ -18498,7 +18498,7 @@
         <v>1561</v>
       </c>
       <c r="H306" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I306" t="s">
         <v>1563</v>
@@ -18507,7 +18507,7 @@
         <v>1567</v>
       </c>
       <c r="K306" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L306" t="s">
         <v>1566</v>
@@ -18530,13 +18530,13 @@
         <v>1095</v>
       </c>
       <c r="D307" t="s">
-        <v>1321</v>
+        <v>1337</v>
       </c>
       <c r="E307" t="s">
-        <v>1509</v>
+        <v>1525</v>
       </c>
       <c r="F307" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G307" t="s">
         <v>1561</v>
@@ -18574,34 +18574,34 @@
         <v>1096</v>
       </c>
       <c r="D308" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="E308" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="F308" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G308" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H308" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I308" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J308" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="K308" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L308" t="s">
         <v>1566</v>
       </c>
       <c r="M308" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N308" t="s">
         <v>1568</v>
@@ -18618,34 +18618,34 @@
         <v>1097</v>
       </c>
       <c r="D309" t="s">
-        <v>1341</v>
+        <v>1211</v>
       </c>
       <c r="E309" t="s">
-        <v>1529</v>
+        <v>1399</v>
       </c>
       <c r="F309" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G309" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H309" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I309" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J309" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K309" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L309" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M309" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N309" t="s">
         <v>1568</v>
@@ -18662,31 +18662,31 @@
         <v>1098</v>
       </c>
       <c r="D310" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="E310" t="s">
-        <v>1399</v>
+        <v>1454</v>
       </c>
       <c r="F310" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G310" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H310" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I310" t="s">
         <v>1567</v>
       </c>
       <c r="J310" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K310" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="L310" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M310" t="s">
         <v>1563</v>
@@ -18706,28 +18706,28 @@
         <v>1099</v>
       </c>
       <c r="D311" t="s">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="E311" t="s">
-        <v>1454</v>
+        <v>1473</v>
       </c>
       <c r="F311" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G311" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H311" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I311" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J311" t="s">
         <v>1565</v>
       </c>
       <c r="K311" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L311" t="s">
         <v>1566</v>
@@ -18750,34 +18750,34 @@
         <v>1100</v>
       </c>
       <c r="D312" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="E312" t="s">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="F312" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G312" t="s">
         <v>1561</v>
       </c>
       <c r="H312" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I312" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J312" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K312" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L312" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M312" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N312" t="s">
         <v>1568</v>
@@ -18794,13 +18794,13 @@
         <v>1101</v>
       </c>
       <c r="D313" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="E313" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="F313" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G313" t="s">
         <v>1561</v>
@@ -18809,19 +18809,19 @@
         <v>1567</v>
       </c>
       <c r="I313" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J313" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K313" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L313" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M313" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N313" t="s">
         <v>1568</v>
@@ -18838,10 +18838,10 @@
         <v>1102</v>
       </c>
       <c r="D314" t="s">
-        <v>1318</v>
+        <v>1229</v>
       </c>
       <c r="E314" t="s">
-        <v>1506</v>
+        <v>1417</v>
       </c>
       <c r="F314" t="s">
         <v>1556</v>
@@ -18853,19 +18853,19 @@
         <v>1567</v>
       </c>
       <c r="I314" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J314" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K314" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L314" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M314" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N314" t="s">
         <v>1568</v>
@@ -18882,13 +18882,13 @@
         <v>1103</v>
       </c>
       <c r="D315" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="E315" t="s">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="F315" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G315" t="s">
         <v>1561</v>
@@ -18897,10 +18897,10 @@
         <v>1567</v>
       </c>
       <c r="I315" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J315" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K315" t="s">
         <v>1566</v>
@@ -18926,10 +18926,10 @@
         <v>1104</v>
       </c>
       <c r="D316" t="s">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="E316" t="s">
-        <v>1433</v>
+        <v>1530</v>
       </c>
       <c r="F316" t="s">
         <v>1555</v>
@@ -18938,22 +18938,22 @@
         <v>1561</v>
       </c>
       <c r="H316" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I316" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J316" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K316" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L316" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M316" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N316" t="s">
         <v>1568</v>
@@ -18970,34 +18970,34 @@
         <v>1105</v>
       </c>
       <c r="D317" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E317" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F317" t="s">
         <v>1555</v>
       </c>
       <c r="G317" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H317" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I317" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J317" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K317" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L317" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M317" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N317" t="s">
         <v>1568</v>
@@ -19014,10 +19014,10 @@
         <v>1106</v>
       </c>
       <c r="D318" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E318" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F318" t="s">
         <v>1555</v>
@@ -19058,34 +19058,34 @@
         <v>1107</v>
       </c>
       <c r="D319" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E319" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F319" t="s">
         <v>1555</v>
       </c>
       <c r="G319" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H319" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I319" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J319" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K319" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L319" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M319" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="N319" t="s">
         <v>1568</v>
@@ -19102,34 +19102,34 @@
         <v>1108</v>
       </c>
       <c r="D320" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E320" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F320" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G320" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H320" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I320" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J320" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K320" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L320" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M320" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N320" t="s">
         <v>1568</v>
@@ -19146,34 +19146,34 @@
         <v>1109</v>
       </c>
       <c r="D321" t="s">
-        <v>1346</v>
+        <v>1315</v>
       </c>
       <c r="E321" t="s">
-        <v>1534</v>
+        <v>1503</v>
       </c>
       <c r="F321" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G321" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H321" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I321" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J321" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K321" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L321" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M321" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N321" t="s">
         <v>1568</v>
@@ -19190,13 +19190,13 @@
         <v>1110</v>
       </c>
       <c r="D322" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="E322" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="F322" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G322" t="s">
         <v>1561</v>
@@ -19211,13 +19211,13 @@
         <v>1563</v>
       </c>
       <c r="K322" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L322" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M322" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N322" t="s">
         <v>1568</v>
@@ -19234,10 +19234,10 @@
         <v>1111</v>
       </c>
       <c r="D323" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
       <c r="E323" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F323" t="s">
         <v>1555</v>
@@ -19252,16 +19252,16 @@
         <v>1567</v>
       </c>
       <c r="J323" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K323" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L323" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M323" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N323" t="s">
         <v>1568</v>
@@ -19278,31 +19278,31 @@
         <v>1112</v>
       </c>
       <c r="D324" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E324" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F324" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G324" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H324" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I324" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J324" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K324" t="s">
         <v>1565</v>
       </c>
       <c r="L324" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M324" t="s">
         <v>1563</v>
@@ -19322,34 +19322,34 @@
         <v>1113</v>
       </c>
       <c r="D325" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="E325" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="F325" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G325" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H325" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I325" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J325" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K325" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L325" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M325" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N325" t="s">
         <v>1568</v>
@@ -19366,34 +19366,34 @@
         <v>1114</v>
       </c>
       <c r="D326" t="s">
-        <v>1314</v>
+        <v>1224</v>
       </c>
       <c r="E326" t="s">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="F326" t="s">
         <v>1556</v>
       </c>
       <c r="G326" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H326" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I326" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="J326" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K326" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L326" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M326" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="N326" t="s">
         <v>1568</v>
@@ -19410,34 +19410,34 @@
         <v>1115</v>
       </c>
       <c r="D327" t="s">
-        <v>1224</v>
+        <v>1262</v>
       </c>
       <c r="E327" t="s">
-        <v>1412</v>
+        <v>1450</v>
       </c>
       <c r="F327" t="s">
         <v>1556</v>
       </c>
       <c r="G327" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H327" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I327" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J327" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K327" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L327" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M327" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N327" t="s">
         <v>1568</v>
@@ -19454,34 +19454,34 @@
         <v>1116</v>
       </c>
       <c r="D328" t="s">
-        <v>1262</v>
+        <v>1291</v>
       </c>
       <c r="E328" t="s">
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="F328" t="s">
         <v>1556</v>
       </c>
       <c r="G328" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H328" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I328" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J328" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K328" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L328" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M328" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N328" t="s">
         <v>1568</v>
@@ -19498,34 +19498,34 @@
         <v>1117</v>
       </c>
       <c r="D329" t="s">
-        <v>1291</v>
+        <v>1262</v>
       </c>
       <c r="E329" t="s">
-        <v>1479</v>
+        <v>1450</v>
       </c>
       <c r="F329" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G329" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="H329" t="s">
         <v>1561</v>
       </c>
       <c r="I329" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J329" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K329" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L329" t="s">
         <v>1566</v>
       </c>
       <c r="M329" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N329" t="s">
         <v>1568</v>
@@ -19542,31 +19542,31 @@
         <v>1118</v>
       </c>
       <c r="D330" t="s">
-        <v>1262</v>
+        <v>1349</v>
       </c>
       <c r="E330" t="s">
-        <v>1450</v>
+        <v>1537</v>
       </c>
       <c r="F330" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G330" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H330" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I330" t="s">
         <v>1567</v>
       </c>
       <c r="J330" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K330" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L330" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M330" t="s">
         <v>1562</v>
@@ -19586,10 +19586,10 @@
         <v>1119</v>
       </c>
       <c r="D331" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E331" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F331" t="s">
         <v>1559</v>
@@ -19604,16 +19604,16 @@
         <v>1567</v>
       </c>
       <c r="J331" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K331" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L331" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M331" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N331" t="s">
         <v>1568</v>
@@ -19630,13 +19630,13 @@
         <v>1120</v>
       </c>
       <c r="D332" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E332" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F332" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G332" t="s">
         <v>1561</v>
@@ -19648,13 +19648,13 @@
         <v>1567</v>
       </c>
       <c r="J332" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K332" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L332" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M332" t="s">
         <v>1563</v>
@@ -19674,34 +19674,34 @@
         <v>1121</v>
       </c>
       <c r="D333" t="s">
-        <v>1351</v>
+        <v>1331</v>
       </c>
       <c r="E333" t="s">
-        <v>1539</v>
+        <v>1519</v>
       </c>
       <c r="F333" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G333" t="s">
         <v>1561</v>
       </c>
       <c r="H333" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I333" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J333" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K333" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L333" t="s">
         <v>1562</v>
       </c>
       <c r="M333" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N333" t="s">
         <v>1568</v>
@@ -19718,25 +19718,25 @@
         <v>1122</v>
       </c>
       <c r="D334" t="s">
-        <v>1331</v>
+        <v>1201</v>
       </c>
       <c r="E334" t="s">
-        <v>1519</v>
+        <v>1389</v>
       </c>
       <c r="F334" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G334" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H334" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I334" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J334" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K334" t="s">
         <v>1565</v>
@@ -19762,31 +19762,31 @@
         <v>1123</v>
       </c>
       <c r="D335" t="s">
-        <v>1201</v>
+        <v>1271</v>
       </c>
       <c r="E335" t="s">
-        <v>1389</v>
+        <v>1459</v>
       </c>
       <c r="F335" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G335" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H335" t="s">
         <v>1564</v>
       </c>
       <c r="I335" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J335" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K335" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L335" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M335" t="s">
         <v>1566</v>
@@ -19806,34 +19806,34 @@
         <v>1124</v>
       </c>
       <c r="D336" t="s">
-        <v>1271</v>
+        <v>1352</v>
       </c>
       <c r="E336" t="s">
-        <v>1459</v>
+        <v>1540</v>
       </c>
       <c r="F336" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G336" t="s">
         <v>1561</v>
       </c>
       <c r="H336" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I336" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J336" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K336" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L336" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M336" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N336" t="s">
         <v>1568</v>
@@ -19850,34 +19850,34 @@
         <v>1125</v>
       </c>
       <c r="D337" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E337" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F337" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G337" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H337" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I337" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J337" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K337" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L337" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M337" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N337" t="s">
         <v>1568</v>
@@ -19894,34 +19894,34 @@
         <v>1126</v>
       </c>
       <c r="D338" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E338" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F338" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G338" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H338" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I338" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J338" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K338" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L338" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M338" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N338" t="s">
         <v>1568</v>
@@ -19938,34 +19938,34 @@
         <v>1127</v>
       </c>
       <c r="D339" t="s">
-        <v>1354</v>
+        <v>1230</v>
       </c>
       <c r="E339" t="s">
-        <v>1542</v>
+        <v>1418</v>
       </c>
       <c r="F339" t="s">
         <v>1557</v>
       </c>
       <c r="G339" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="H339" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I339" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J339" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K339" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L339" t="s">
         <v>1566</v>
       </c>
       <c r="M339" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N339" t="s">
         <v>1568</v>
@@ -19982,10 +19982,10 @@
         <v>1128</v>
       </c>
       <c r="D340" t="s">
-        <v>1230</v>
+        <v>1355</v>
       </c>
       <c r="E340" t="s">
-        <v>1418</v>
+        <v>1543</v>
       </c>
       <c r="F340" t="s">
         <v>1557</v>
@@ -19994,13 +19994,13 @@
         <v>1562</v>
       </c>
       <c r="H340" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I340" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J340" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K340" t="s">
         <v>1567</v>
@@ -20009,7 +20009,7 @@
         <v>1566</v>
       </c>
       <c r="M340" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N340" t="s">
         <v>1568</v>
@@ -20026,34 +20026,34 @@
         <v>1129</v>
       </c>
       <c r="D341" t="s">
-        <v>1355</v>
+        <v>1196</v>
       </c>
       <c r="E341" t="s">
-        <v>1543</v>
+        <v>1384</v>
       </c>
       <c r="F341" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G341" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H341" t="s">
         <v>1561</v>
       </c>
       <c r="I341" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J341" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K341" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L341" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M341" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N341" t="s">
         <v>1568</v>
@@ -20070,34 +20070,34 @@
         <v>1130</v>
       </c>
       <c r="D342" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E342" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F342" t="s">
         <v>1555</v>
       </c>
       <c r="G342" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H342" t="s">
         <v>1561</v>
       </c>
       <c r="I342" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J342" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K342" t="s">
         <v>1565</v>
       </c>
       <c r="L342" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M342" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N342" t="s">
         <v>1568</v>
@@ -20114,34 +20114,34 @@
         <v>1131</v>
       </c>
       <c r="D343" t="s">
-        <v>1194</v>
+        <v>1329</v>
       </c>
       <c r="E343" t="s">
-        <v>1382</v>
+        <v>1517</v>
       </c>
       <c r="F343" t="s">
         <v>1555</v>
       </c>
       <c r="G343" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H343" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I343" t="s">
         <v>1564</v>
       </c>
       <c r="J343" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K343" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L343" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M343" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N343" t="s">
         <v>1568</v>
@@ -20158,34 +20158,34 @@
         <v>1132</v>
       </c>
       <c r="D344" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
       <c r="E344" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F344" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G344" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H344" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I344" t="s">
         <v>1564</v>
       </c>
       <c r="J344" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K344" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L344" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M344" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N344" t="s">
         <v>1568</v>
@@ -20202,34 +20202,34 @@
         <v>1133</v>
       </c>
       <c r="D345" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E345" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F345" t="s">
         <v>1556</v>
       </c>
       <c r="G345" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="H345" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="I345" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J345" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="K345" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L345" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M345" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N345" t="s">
         <v>1568</v>
@@ -20246,34 +20246,34 @@
         <v>1134</v>
       </c>
       <c r="D346" t="s">
-        <v>1357</v>
+        <v>1262</v>
       </c>
       <c r="E346" t="s">
-        <v>1545</v>
+        <v>1450</v>
       </c>
       <c r="F346" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G346" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H346" t="s">
         <v>1561</v>
       </c>
       <c r="I346" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="J346" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K346" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L346" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M346" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N346" t="s">
         <v>1568</v>
@@ -20290,28 +20290,28 @@
         <v>1135</v>
       </c>
       <c r="D347" t="s">
-        <v>1262</v>
+        <v>1227</v>
       </c>
       <c r="E347" t="s">
-        <v>1450</v>
+        <v>1415</v>
       </c>
       <c r="F347" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G347" t="s">
         <v>1565</v>
       </c>
       <c r="H347" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I347" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J347" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K347" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L347" t="s">
         <v>1562</v>
@@ -20334,31 +20334,31 @@
         <v>1136</v>
       </c>
       <c r="D348" t="s">
-        <v>1227</v>
+        <v>1303</v>
       </c>
       <c r="E348" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
       <c r="F348" t="s">
         <v>1556</v>
       </c>
       <c r="G348" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H348" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I348" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J348" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K348" t="s">
         <v>1563</v>
       </c>
       <c r="L348" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M348" t="s">
         <v>1566</v>
@@ -20378,31 +20378,31 @@
         <v>1137</v>
       </c>
       <c r="D349" t="s">
-        <v>1303</v>
+        <v>1358</v>
       </c>
       <c r="E349" t="s">
-        <v>1491</v>
+        <v>1546</v>
       </c>
       <c r="F349" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G349" t="s">
         <v>1561</v>
       </c>
       <c r="H349" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I349" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J349" t="s">
         <v>1562</v>
       </c>
       <c r="K349" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L349" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M349" t="s">
         <v>1566</v>
@@ -20422,13 +20422,13 @@
         <v>1138</v>
       </c>
       <c r="D350" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E350" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F350" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G350" t="s">
         <v>1561</v>
@@ -20440,16 +20440,16 @@
         <v>1567</v>
       </c>
       <c r="J350" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K350" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L350" t="s">
         <v>1563</v>
       </c>
       <c r="M350" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N350" t="s">
         <v>1568</v>
@@ -20466,13 +20466,13 @@
         <v>1139</v>
       </c>
       <c r="D351" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E351" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F351" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G351" t="s">
         <v>1561</v>
@@ -20484,16 +20484,16 @@
         <v>1567</v>
       </c>
       <c r="J351" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K351" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L351" t="s">
         <v>1563</v>
       </c>
       <c r="M351" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N351" t="s">
         <v>1568</v>
@@ -20510,31 +20510,31 @@
         <v>1140</v>
       </c>
       <c r="D352" t="s">
-        <v>1360</v>
+        <v>1225</v>
       </c>
       <c r="E352" t="s">
-        <v>1548</v>
+        <v>1413</v>
       </c>
       <c r="F352" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G352" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H352" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I352" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J352" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K352" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L352" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M352" t="s">
         <v>1566</v>
@@ -20554,34 +20554,34 @@
         <v>1141</v>
       </c>
       <c r="D353" t="s">
-        <v>1225</v>
+        <v>1361</v>
       </c>
       <c r="E353" t="s">
-        <v>1413</v>
+        <v>1549</v>
       </c>
       <c r="F353" t="s">
         <v>1556</v>
       </c>
       <c r="G353" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H353" t="s">
         <v>1562</v>
       </c>
       <c r="I353" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J353" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K353" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L353" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M353" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N353" t="s">
         <v>1568</v>
@@ -20598,13 +20598,13 @@
         <v>1142</v>
       </c>
       <c r="D354" t="s">
-        <v>1361</v>
+        <v>1203</v>
       </c>
       <c r="E354" t="s">
-        <v>1549</v>
+        <v>1391</v>
       </c>
       <c r="F354" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G354" t="s">
         <v>1561</v>
@@ -20613,16 +20613,16 @@
         <v>1562</v>
       </c>
       <c r="I354" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J354" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K354" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="L354" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M354" t="s">
         <v>1565</v>
@@ -20642,10 +20642,10 @@
         <v>1143</v>
       </c>
       <c r="D355" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E355" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F355" t="s">
         <v>1555</v>
@@ -20686,10 +20686,10 @@
         <v>1144</v>
       </c>
       <c r="D356" t="s">
-        <v>1205</v>
+        <v>1353</v>
       </c>
       <c r="E356" t="s">
-        <v>1393</v>
+        <v>1541</v>
       </c>
       <c r="F356" t="s">
         <v>1555</v>
@@ -20698,22 +20698,22 @@
         <v>1561</v>
       </c>
       <c r="H356" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="I356" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J356" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K356" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L356" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M356" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N356" t="s">
         <v>1568</v>
@@ -20730,34 +20730,34 @@
         <v>1145</v>
       </c>
       <c r="D357" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E357" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F357" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G357" t="s">
         <v>1561</v>
       </c>
       <c r="H357" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="I357" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J357" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K357" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L357" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M357" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N357" t="s">
         <v>1568</v>
@@ -20774,13 +20774,13 @@
         <v>1146</v>
       </c>
       <c r="D358" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="E358" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="F358" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G358" t="s">
         <v>1561</v>
@@ -20789,19 +20789,19 @@
         <v>1562</v>
       </c>
       <c r="I358" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J358" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K358" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L358" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M358" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N358" t="s">
         <v>1568</v>
@@ -20818,10 +20818,10 @@
         <v>1147</v>
       </c>
       <c r="D359" t="s">
-        <v>1362</v>
+        <v>1316</v>
       </c>
       <c r="E359" t="s">
-        <v>1550</v>
+        <v>1504</v>
       </c>
       <c r="F359" t="s">
         <v>1557</v>
@@ -20830,22 +20830,22 @@
         <v>1561</v>
       </c>
       <c r="H359" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I359" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J359" t="s">
         <v>1563</v>
       </c>
       <c r="K359" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L359" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M359" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N359" t="s">
         <v>1568</v>
@@ -20862,13 +20862,13 @@
         <v>1148</v>
       </c>
       <c r="D360" t="s">
-        <v>1316</v>
+        <v>1277</v>
       </c>
       <c r="E360" t="s">
-        <v>1504</v>
+        <v>1465</v>
       </c>
       <c r="F360" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G360" t="s">
         <v>1561</v>
@@ -20877,19 +20877,19 @@
         <v>1564</v>
       </c>
       <c r="I360" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J360" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K360" t="s">
         <v>1562</v>
       </c>
       <c r="L360" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M360" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N360" t="s">
         <v>1568</v>
@@ -20906,34 +20906,34 @@
         <v>1149</v>
       </c>
       <c r="D361" t="s">
-        <v>1277</v>
+        <v>1256</v>
       </c>
       <c r="E361" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="F361" t="s">
         <v>1556</v>
       </c>
       <c r="G361" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H361" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I361" t="s">
         <v>1565</v>
       </c>
       <c r="J361" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K361" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L361" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M361" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N361" t="s">
         <v>1568</v>
@@ -20950,34 +20950,34 @@
         <v>1150</v>
       </c>
       <c r="D362" t="s">
-        <v>1256</v>
+        <v>1216</v>
       </c>
       <c r="E362" t="s">
-        <v>1444</v>
+        <v>1404</v>
       </c>
       <c r="F362" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G362" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H362" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="I362" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J362" t="s">
         <v>1562</v>
       </c>
       <c r="K362" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L362" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M362" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="N362" t="s">
         <v>1568</v>
@@ -20994,34 +20994,34 @@
         <v>1151</v>
       </c>
       <c r="D363" t="s">
-        <v>1216</v>
+        <v>1334</v>
       </c>
       <c r="E363" t="s">
-        <v>1404</v>
+        <v>1522</v>
       </c>
       <c r="F363" t="s">
         <v>1555</v>
       </c>
       <c r="G363" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H363" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="I363" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J363" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K363" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L363" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M363" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="N363" t="s">
         <v>1568</v>
@@ -21038,10 +21038,10 @@
         <v>1152</v>
       </c>
       <c r="D364" t="s">
-        <v>1334</v>
+        <v>1280</v>
       </c>
       <c r="E364" t="s">
-        <v>1522</v>
+        <v>1468</v>
       </c>
       <c r="F364" t="s">
         <v>1555</v>
@@ -21053,16 +21053,16 @@
         <v>1564</v>
       </c>
       <c r="I364" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="J364" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K364" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L364" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M364" t="s">
         <v>1562</v>
@@ -21082,34 +21082,34 @@
         <v>1153</v>
       </c>
       <c r="D365" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="E365" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="F365" t="s">
         <v>1555</v>
       </c>
       <c r="G365" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H365" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I365" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J365" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K365" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L365" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M365" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N365" t="s">
         <v>1568</v>
@@ -21126,34 +21126,34 @@
         <v>1154</v>
       </c>
       <c r="D366" t="s">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="E366" t="s">
-        <v>1498</v>
+        <v>1453</v>
       </c>
       <c r="F366" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G366" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H366" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I366" t="s">
         <v>1561</v>
       </c>
       <c r="J366" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K366" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L366" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M366" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N366" t="s">
         <v>1568</v>
@@ -21170,34 +21170,34 @@
         <v>1155</v>
       </c>
       <c r="D367" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="E367" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="F367" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G367" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H367" t="s">
         <v>1564</v>
       </c>
       <c r="I367" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J367" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K367" t="s">
         <v>1565</v>
       </c>
       <c r="L367" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M367" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N367" t="s">
         <v>1568</v>
@@ -21214,34 +21214,34 @@
         <v>1156</v>
       </c>
       <c r="D368" t="s">
-        <v>1255</v>
+        <v>1203</v>
       </c>
       <c r="E368" t="s">
-        <v>1443</v>
+        <v>1391</v>
       </c>
       <c r="F368" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G368" t="s">
         <v>1561</v>
       </c>
       <c r="H368" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I368" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J368" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K368" t="s">
         <v>1565</v>
       </c>
       <c r="L368" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M368" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N368" t="s">
         <v>1568</v>
@@ -21258,34 +21258,34 @@
         <v>1157</v>
       </c>
       <c r="D369" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="E369" t="s">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="F369" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G369" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H369" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I369" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J369" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K369" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L369" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M369" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N369" t="s">
         <v>1568</v>
@@ -21302,34 +21302,34 @@
         <v>1158</v>
       </c>
       <c r="D370" t="s">
-        <v>1219</v>
+        <v>1267</v>
       </c>
       <c r="E370" t="s">
-        <v>1407</v>
+        <v>1455</v>
       </c>
       <c r="F370" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G370" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="H370" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I370" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J370" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K370" t="s">
         <v>1563</v>
       </c>
       <c r="L370" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M370" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N370" t="s">
         <v>1568</v>
@@ -21346,19 +21346,19 @@
         <v>1159</v>
       </c>
       <c r="D371" t="s">
-        <v>1267</v>
+        <v>1286</v>
       </c>
       <c r="E371" t="s">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F371" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G371" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H371" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I371" t="s">
         <v>1564</v>
@@ -21367,10 +21367,10 @@
         <v>1567</v>
       </c>
       <c r="K371" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L371" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M371" t="s">
         <v>1566</v>
@@ -21390,34 +21390,34 @@
         <v>1160</v>
       </c>
       <c r="D372" t="s">
-        <v>1286</v>
+        <v>1200</v>
       </c>
       <c r="E372" t="s">
-        <v>1474</v>
+        <v>1388</v>
       </c>
       <c r="F372" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G372" t="s">
         <v>1562</v>
       </c>
       <c r="H372" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I372" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J372" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K372" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L372" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M372" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N372" t="s">
         <v>1568</v>
@@ -21434,34 +21434,34 @@
         <v>1161</v>
       </c>
       <c r="D373" t="s">
-        <v>1200</v>
+        <v>1361</v>
       </c>
       <c r="E373" t="s">
-        <v>1388</v>
+        <v>1549</v>
       </c>
       <c r="F373" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G373" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H373" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I373" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J373" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K373" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="L373" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M373" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N373" t="s">
         <v>1568</v>
@@ -21478,34 +21478,34 @@
         <v>1162</v>
       </c>
       <c r="D374" t="s">
-        <v>1361</v>
+        <v>1246</v>
       </c>
       <c r="E374" t="s">
-        <v>1549</v>
+        <v>1434</v>
       </c>
       <c r="F374" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G374" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H374" t="s">
         <v>1564</v>
       </c>
       <c r="I374" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J374" t="s">
         <v>1563</v>
       </c>
       <c r="K374" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="L374" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M374" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N374" t="s">
         <v>1568</v>
@@ -21522,31 +21522,31 @@
         <v>1163</v>
       </c>
       <c r="D375" t="s">
-        <v>1246</v>
+        <v>1215</v>
       </c>
       <c r="E375" t="s">
-        <v>1434</v>
+        <v>1403</v>
       </c>
       <c r="F375" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G375" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H375" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I375" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J375" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K375" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L375" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M375" t="s">
         <v>1566</v>
@@ -21566,31 +21566,31 @@
         <v>1164</v>
       </c>
       <c r="D376" t="s">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="E376" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="F376" t="s">
         <v>1556</v>
       </c>
       <c r="G376" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H376" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I376" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J376" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K376" t="s">
         <v>1565</v>
       </c>
       <c r="L376" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="M376" t="s">
         <v>1566</v>
@@ -21610,31 +21610,31 @@
         <v>1165</v>
       </c>
       <c r="D377" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="E377" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="F377" t="s">
         <v>1556</v>
       </c>
       <c r="G377" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H377" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I377" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J377" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K377" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L377" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M377" t="s">
         <v>1566</v>
@@ -21654,34 +21654,34 @@
         <v>1166</v>
       </c>
       <c r="D378" t="s">
-        <v>1226</v>
+        <v>1312</v>
       </c>
       <c r="E378" t="s">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="F378" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G378" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H378" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I378" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="J378" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K378" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L378" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M378" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="N378" t="s">
         <v>1568</v>
@@ -21698,10 +21698,10 @@
         <v>1167</v>
       </c>
       <c r="D379" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E379" t="s">
-        <v>1500</v>
+        <v>1551</v>
       </c>
       <c r="F379" t="s">
         <v>1555</v>
@@ -21742,34 +21742,34 @@
         <v>1168</v>
       </c>
       <c r="D380" t="s">
-        <v>1363</v>
+        <v>1199</v>
       </c>
       <c r="E380" t="s">
-        <v>1551</v>
+        <v>1387</v>
       </c>
       <c r="F380" t="s">
         <v>1555</v>
       </c>
       <c r="G380" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H380" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I380" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J380" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K380" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L380" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M380" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="N380" t="s">
         <v>1568</v>
@@ -21786,31 +21786,31 @@
         <v>1169</v>
       </c>
       <c r="D381" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="E381" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F381" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G381" t="s">
         <v>1561</v>
       </c>
       <c r="H381" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I381" t="s">
         <v>1567</v>
       </c>
       <c r="J381" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K381" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L381" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M381" t="s">
         <v>1566</v>
@@ -21830,34 +21830,34 @@
         <v>1170</v>
       </c>
       <c r="D382" t="s">
-        <v>1211</v>
+        <v>1364</v>
       </c>
       <c r="E382" t="s">
-        <v>1399</v>
+        <v>1552</v>
       </c>
       <c r="F382" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G382" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H382" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I382" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J382" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K382" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L382" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M382" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N382" t="s">
         <v>1568</v>
@@ -21874,34 +21874,34 @@
         <v>1171</v>
       </c>
       <c r="D383" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E383" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F383" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G383" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H383" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I383" t="s">
         <v>1563</v>
       </c>
       <c r="J383" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K383" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L383" t="s">
         <v>1565</v>
       </c>
       <c r="M383" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N383" t="s">
         <v>1568</v>
@@ -21918,34 +21918,34 @@
         <v>1172</v>
       </c>
       <c r="D384" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E384" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F384" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G384" t="s">
         <v>1561</v>
       </c>
       <c r="H384" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I384" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J384" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K384" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L384" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M384" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N384" t="s">
         <v>1568</v>
@@ -21962,13 +21962,13 @@
         <v>1173</v>
       </c>
       <c r="D385" t="s">
-        <v>1366</v>
+        <v>1209</v>
       </c>
       <c r="E385" t="s">
-        <v>1554</v>
+        <v>1397</v>
       </c>
       <c r="F385" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G385" t="s">
         <v>1561</v>
@@ -21983,13 +21983,13 @@
         <v>1562</v>
       </c>
       <c r="K385" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L385" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M385" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N385" t="s">
         <v>1568</v>
@@ -22006,13 +22006,13 @@
         <v>1174</v>
       </c>
       <c r="D386" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="E386" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="F386" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G386" t="s">
         <v>1561</v>
@@ -22024,16 +22024,16 @@
         <v>1567</v>
       </c>
       <c r="J386" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K386" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L386" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M386" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N386" t="s">
         <v>1568</v>
@@ -22050,22 +22050,22 @@
         <v>1175</v>
       </c>
       <c r="D387" t="s">
-        <v>1191</v>
+        <v>1249</v>
       </c>
       <c r="E387" t="s">
-        <v>1379</v>
+        <v>1437</v>
       </c>
       <c r="F387" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G387" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H387" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="I387" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J387" t="s">
         <v>1563</v>
@@ -22074,10 +22074,10 @@
         <v>1565</v>
       </c>
       <c r="L387" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M387" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="N387" t="s">
         <v>1568</v>
@@ -22094,31 +22094,31 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="E388" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F388" t="s">
         <v>1556</v>
       </c>
       <c r="G388" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H388" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="I388" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J388" t="s">
         <v>1563</v>
       </c>
       <c r="K388" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L388" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M388" t="s">
         <v>1567</v>
@@ -22138,34 +22138,34 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1255</v>
+        <v>1195</v>
       </c>
       <c r="E389" t="s">
-        <v>1443</v>
+        <v>1383</v>
       </c>
       <c r="F389" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G389" t="s">
         <v>1561</v>
       </c>
       <c r="H389" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I389" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J389" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K389" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L389" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M389" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="N389" t="s">
         <v>1568</v>
@@ -22182,34 +22182,34 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1343</v>
+        <v>1328</v>
       </c>
       <c r="E390">
-        <v>67.15000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F390" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G390" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H390" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I390" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J390" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K390" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L390" t="s">
         <v>1566</v>
       </c>
       <c r="M390" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N390" t="s">
         <v>1568</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -910,321 +910,321 @@
     <t>ماركو مجدى مكرم فريد</t>
   </si>
   <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
     <t>شروق محمد هاشم احمد</t>
   </si>
   <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2074,321 +2074,321 @@
     <t>30409172401791</t>
   </si>
   <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
     <t>30510302401007</t>
   </si>
   <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3238,321 +3238,321 @@
     <t>01283970879</t>
   </si>
   <si>
+    <t>01099393313</t>
+  </si>
+  <si>
+    <t>01093075647</t>
+  </si>
+  <si>
+    <t>01037186555</t>
+  </si>
+  <si>
+    <t>01129169104</t>
+  </si>
+  <si>
+    <t>01001362969</t>
+  </si>
+  <si>
+    <t>01151741232</t>
+  </si>
+  <si>
+    <t>01013305686</t>
+  </si>
+  <si>
+    <t>01150936407</t>
+  </si>
+  <si>
+    <t>01002331784</t>
+  </si>
+  <si>
+    <t>01150905692</t>
+  </si>
+  <si>
+    <t>01028993616</t>
+  </si>
+  <si>
+    <t>01119364560</t>
+  </si>
+  <si>
+    <t>01114623756</t>
+  </si>
+  <si>
+    <t>01110180758</t>
+  </si>
+  <si>
+    <t>01098408936</t>
+  </si>
+  <si>
+    <t>01026439570</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
     <t>01152380733</t>
   </si>
   <si>
-    <t>01099393313</t>
-  </si>
-  <si>
-    <t>01093075647</t>
-  </si>
-  <si>
-    <t>01037186555</t>
-  </si>
-  <si>
-    <t>01129169104</t>
-  </si>
-  <si>
-    <t>01001362969</t>
-  </si>
-  <si>
-    <t>01151741232</t>
-  </si>
-  <si>
-    <t>01013305686</t>
-  </si>
-  <si>
-    <t>01150936407</t>
-  </si>
-  <si>
-    <t>01002331784</t>
-  </si>
-  <si>
-    <t>01150905692</t>
-  </si>
-  <si>
-    <t>01028993616</t>
-  </si>
-  <si>
-    <t>01119364560</t>
-  </si>
-  <si>
-    <t>01114623756</t>
-  </si>
-  <si>
-    <t>01110180758</t>
-  </si>
-  <si>
-    <t>01098408936</t>
-  </si>
-  <si>
-    <t>01026439570</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
     <t>1353</t>
   </si>
   <si>
@@ -4027,18 +4027,18 @@
     <t>1227</t>
   </si>
   <si>
+    <t>1419</t>
+  </si>
+  <si>
+    <t>1327</t>
+  </si>
+  <si>
+    <t>1451</t>
+  </si>
+  <si>
     <t>1270</t>
   </si>
   <si>
-    <t>1419</t>
-  </si>
-  <si>
-    <t>1327</t>
-  </si>
-  <si>
-    <t>1451</t>
-  </si>
-  <si>
     <t>1292</t>
   </si>
   <si>
@@ -4591,16 +4591,16 @@
     <t>61.35</t>
   </si>
   <si>
+    <t>70.95</t>
+  </si>
+  <si>
+    <t>66.35</t>
+  </si>
+  <si>
+    <t>72.55</t>
+  </si>
+  <si>
     <t>63.5</t>
-  </si>
-  <si>
-    <t>70.95</t>
-  </si>
-  <si>
-    <t>66.35</t>
-  </si>
-  <si>
-    <t>72.55</t>
   </si>
   <si>
     <t>64.6</t>
@@ -17606,28 +17606,28 @@
         <v>1074</v>
       </c>
       <c r="D286" t="s">
-        <v>1337</v>
+        <v>1256</v>
       </c>
       <c r="E286" t="s">
-        <v>1525</v>
+        <v>1444</v>
       </c>
       <c r="F286" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G286" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H286" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I286" t="s">
         <v>1567</v>
       </c>
       <c r="J286" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K286" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L286" t="s">
         <v>1566</v>
@@ -17650,13 +17650,13 @@
         <v>1075</v>
       </c>
       <c r="D287" t="s">
-        <v>1256</v>
+        <v>1329</v>
       </c>
       <c r="E287" t="s">
-        <v>1444</v>
+        <v>1517</v>
       </c>
       <c r="F287" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G287" t="s">
         <v>1561</v>
@@ -17671,13 +17671,13 @@
         <v>1565</v>
       </c>
       <c r="K287" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L287" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M287" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N287" t="s">
         <v>1568</v>
@@ -17694,10 +17694,10 @@
         <v>1076</v>
       </c>
       <c r="D288" t="s">
-        <v>1329</v>
+        <v>1274</v>
       </c>
       <c r="E288" t="s">
-        <v>1517</v>
+        <v>1462</v>
       </c>
       <c r="F288" t="s">
         <v>1556</v>
@@ -17706,22 +17706,22 @@
         <v>1561</v>
       </c>
       <c r="H288" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I288" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J288" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K288" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L288" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M288" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N288" t="s">
         <v>1568</v>
@@ -17738,10 +17738,10 @@
         <v>1077</v>
       </c>
       <c r="D289" t="s">
-        <v>1274</v>
+        <v>1337</v>
       </c>
       <c r="E289" t="s">
-        <v>1462</v>
+        <v>1525</v>
       </c>
       <c r="F289" t="s">
         <v>1556</v>
@@ -17750,22 +17750,22 @@
         <v>1561</v>
       </c>
       <c r="H289" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="I289" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J289" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K289" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L289" t="s">
         <v>1565</v>
       </c>
       <c r="M289" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N289" t="s">
         <v>1568</v>
@@ -17782,25 +17782,25 @@
         <v>1078</v>
       </c>
       <c r="D290" t="s">
-        <v>1338</v>
+        <v>1211</v>
       </c>
       <c r="E290" t="s">
-        <v>1526</v>
+        <v>1399</v>
       </c>
       <c r="F290" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G290" t="s">
         <v>1561</v>
       </c>
       <c r="H290" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I290" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J290" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K290" t="s">
         <v>1566</v>
@@ -17809,7 +17809,7 @@
         <v>1565</v>
       </c>
       <c r="M290" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N290" t="s">
         <v>1568</v>
@@ -17826,13 +17826,13 @@
         <v>1079</v>
       </c>
       <c r="D291" t="s">
-        <v>1211</v>
+        <v>1284</v>
       </c>
       <c r="E291" t="s">
-        <v>1399</v>
+        <v>1472</v>
       </c>
       <c r="F291" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G291" t="s">
         <v>1561</v>
@@ -17870,19 +17870,19 @@
         <v>1080</v>
       </c>
       <c r="D292" t="s">
-        <v>1284</v>
+        <v>1179</v>
       </c>
       <c r="E292" t="s">
-        <v>1472</v>
+        <v>1367</v>
       </c>
       <c r="F292" t="s">
         <v>1555</v>
       </c>
       <c r="G292" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H292" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I292" t="s">
         <v>1567</v>
@@ -17891,13 +17891,13 @@
         <v>1562</v>
       </c>
       <c r="K292" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L292" t="s">
         <v>1565</v>
       </c>
       <c r="M292" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N292" t="s">
         <v>1568</v>
@@ -17914,34 +17914,34 @@
         <v>1081</v>
       </c>
       <c r="D293" t="s">
-        <v>1179</v>
+        <v>1194</v>
       </c>
       <c r="E293" t="s">
-        <v>1367</v>
+        <v>1382</v>
       </c>
       <c r="F293" t="s">
         <v>1555</v>
       </c>
       <c r="G293" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H293" t="s">
         <v>1561</v>
       </c>
       <c r="I293" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J293" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K293" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L293" t="s">
         <v>1565</v>
       </c>
       <c r="M293" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N293" t="s">
         <v>1568</v>
@@ -17958,34 +17958,34 @@
         <v>1082</v>
       </c>
       <c r="D294" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="E294" t="s">
-        <v>1382</v>
+        <v>1401</v>
       </c>
       <c r="F294" t="s">
         <v>1555</v>
       </c>
       <c r="G294" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H294" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I294" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J294" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K294" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L294" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M294" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N294" t="s">
         <v>1568</v>
@@ -18002,34 +18002,34 @@
         <v>1083</v>
       </c>
       <c r="D295" t="s">
-        <v>1213</v>
+        <v>1338</v>
       </c>
       <c r="E295" t="s">
-        <v>1401</v>
+        <v>1526</v>
       </c>
       <c r="F295" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G295" t="s">
         <v>1561</v>
       </c>
       <c r="H295" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I295" t="s">
         <v>1564</v>
       </c>
       <c r="J295" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K295" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L295" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M295" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N295" t="s">
         <v>1568</v>
@@ -18046,31 +18046,31 @@
         <v>1084</v>
       </c>
       <c r="D296" t="s">
-        <v>1339</v>
+        <v>1227</v>
       </c>
       <c r="E296" t="s">
-        <v>1527</v>
+        <v>1415</v>
       </c>
       <c r="F296" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G296" t="s">
         <v>1561</v>
       </c>
       <c r="H296" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I296" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J296" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K296" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L296" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M296" t="s">
         <v>1563</v>
@@ -18090,34 +18090,34 @@
         <v>1085</v>
       </c>
       <c r="D297" t="s">
-        <v>1227</v>
+        <v>1256</v>
       </c>
       <c r="E297" t="s">
-        <v>1415</v>
+        <v>1444</v>
       </c>
       <c r="F297" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G297" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="H297" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I297" t="s">
         <v>1566</v>
       </c>
       <c r="J297" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="K297" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L297" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M297" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N297" t="s">
         <v>1568</v>
@@ -18134,34 +18134,34 @@
         <v>1086</v>
       </c>
       <c r="D298" t="s">
-        <v>1256</v>
+        <v>1191</v>
       </c>
       <c r="E298" t="s">
-        <v>1444</v>
+        <v>1379</v>
       </c>
       <c r="F298" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G298" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H298" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I298" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J298" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K298" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L298" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M298" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N298" t="s">
         <v>1568</v>
@@ -18178,10 +18178,10 @@
         <v>1087</v>
       </c>
       <c r="D299" t="s">
-        <v>1191</v>
+        <v>1297</v>
       </c>
       <c r="E299" t="s">
-        <v>1379</v>
+        <v>1485</v>
       </c>
       <c r="F299" t="s">
         <v>1555</v>
@@ -18199,13 +18199,13 @@
         <v>1562</v>
       </c>
       <c r="K299" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L299" t="s">
         <v>1565</v>
       </c>
       <c r="M299" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N299" t="s">
         <v>1568</v>
@@ -18222,10 +18222,10 @@
         <v>1088</v>
       </c>
       <c r="D300" t="s">
-        <v>1297</v>
+        <v>1339</v>
       </c>
       <c r="E300" t="s">
-        <v>1485</v>
+        <v>1527</v>
       </c>
       <c r="F300" t="s">
         <v>1555</v>
@@ -18234,19 +18234,19 @@
         <v>1561</v>
       </c>
       <c r="H300" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I300" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J300" t="s">
         <v>1562</v>
       </c>
       <c r="K300" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L300" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M300" t="s">
         <v>1563</v>
@@ -18266,13 +18266,13 @@
         <v>1089</v>
       </c>
       <c r="D301" t="s">
-        <v>1340</v>
+        <v>1196</v>
       </c>
       <c r="E301" t="s">
-        <v>1528</v>
+        <v>1384</v>
       </c>
       <c r="F301" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G301" t="s">
         <v>1561</v>
@@ -18284,16 +18284,16 @@
         <v>1567</v>
       </c>
       <c r="J301" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K301" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L301" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M301" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N301" t="s">
         <v>1568</v>
@@ -18310,13 +18310,13 @@
         <v>1090</v>
       </c>
       <c r="D302" t="s">
-        <v>1196</v>
+        <v>1332</v>
       </c>
       <c r="E302" t="s">
-        <v>1384</v>
+        <v>1520</v>
       </c>
       <c r="F302" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G302" t="s">
         <v>1561</v>
@@ -18325,16 +18325,16 @@
         <v>1564</v>
       </c>
       <c r="I302" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J302" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K302" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L302" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M302" t="s">
         <v>1566</v>
@@ -18354,13 +18354,13 @@
         <v>1091</v>
       </c>
       <c r="D303" t="s">
-        <v>1332</v>
+        <v>1202</v>
       </c>
       <c r="E303" t="s">
-        <v>1520</v>
+        <v>1390</v>
       </c>
       <c r="F303" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G303" t="s">
         <v>1561</v>
@@ -18369,19 +18369,19 @@
         <v>1564</v>
       </c>
       <c r="I303" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J303" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K303" t="s">
         <v>1565</v>
       </c>
       <c r="L303" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M303" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N303" t="s">
         <v>1568</v>
@@ -18398,34 +18398,34 @@
         <v>1092</v>
       </c>
       <c r="D304" t="s">
-        <v>1202</v>
+        <v>1291</v>
       </c>
       <c r="E304" t="s">
-        <v>1390</v>
+        <v>1479</v>
       </c>
       <c r="F304" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G304" t="s">
         <v>1561</v>
       </c>
       <c r="H304" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I304" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J304" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K304" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L304" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M304" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N304" t="s">
         <v>1568</v>
@@ -18442,10 +18442,10 @@
         <v>1093</v>
       </c>
       <c r="D305" t="s">
-        <v>1291</v>
+        <v>1321</v>
       </c>
       <c r="E305" t="s">
-        <v>1479</v>
+        <v>1509</v>
       </c>
       <c r="F305" t="s">
         <v>1556</v>
@@ -18454,7 +18454,7 @@
         <v>1561</v>
       </c>
       <c r="H305" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I305" t="s">
         <v>1563</v>
@@ -18463,7 +18463,7 @@
         <v>1567</v>
       </c>
       <c r="K305" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L305" t="s">
         <v>1566</v>
@@ -18486,13 +18486,13 @@
         <v>1094</v>
       </c>
       <c r="D306" t="s">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="E306" t="s">
-        <v>1509</v>
+        <v>1528</v>
       </c>
       <c r="F306" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G306" t="s">
         <v>1561</v>
@@ -18530,34 +18530,34 @@
         <v>1095</v>
       </c>
       <c r="D307" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="E307" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
       <c r="F307" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G307" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H307" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I307" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J307" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="K307" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L307" t="s">
         <v>1566</v>
       </c>
       <c r="M307" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N307" t="s">
         <v>1568</v>
@@ -18574,34 +18574,34 @@
         <v>1096</v>
       </c>
       <c r="D308" t="s">
-        <v>1341</v>
+        <v>1211</v>
       </c>
       <c r="E308" t="s">
-        <v>1529</v>
+        <v>1399</v>
       </c>
       <c r="F308" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G308" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H308" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I308" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J308" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K308" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L308" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M308" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N308" t="s">
         <v>1568</v>
@@ -18618,31 +18618,31 @@
         <v>1097</v>
       </c>
       <c r="D309" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="E309" t="s">
-        <v>1399</v>
+        <v>1454</v>
       </c>
       <c r="F309" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G309" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H309" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I309" t="s">
         <v>1567</v>
       </c>
       <c r="J309" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K309" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="L309" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M309" t="s">
         <v>1563</v>
@@ -18662,28 +18662,28 @@
         <v>1098</v>
       </c>
       <c r="D310" t="s">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="E310" t="s">
-        <v>1454</v>
+        <v>1473</v>
       </c>
       <c r="F310" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G310" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H310" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I310" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J310" t="s">
         <v>1565</v>
       </c>
       <c r="K310" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L310" t="s">
         <v>1566</v>
@@ -18706,34 +18706,34 @@
         <v>1099</v>
       </c>
       <c r="D311" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="E311" t="s">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="F311" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G311" t="s">
         <v>1561</v>
       </c>
       <c r="H311" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I311" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J311" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K311" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L311" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M311" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N311" t="s">
         <v>1568</v>
@@ -18750,13 +18750,13 @@
         <v>1100</v>
       </c>
       <c r="D312" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="E312" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="F312" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G312" t="s">
         <v>1561</v>
@@ -18765,19 +18765,19 @@
         <v>1567</v>
       </c>
       <c r="I312" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J312" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K312" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L312" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M312" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N312" t="s">
         <v>1568</v>
@@ -18794,10 +18794,10 @@
         <v>1101</v>
       </c>
       <c r="D313" t="s">
-        <v>1318</v>
+        <v>1229</v>
       </c>
       <c r="E313" t="s">
-        <v>1506</v>
+        <v>1417</v>
       </c>
       <c r="F313" t="s">
         <v>1556</v>
@@ -18809,19 +18809,19 @@
         <v>1567</v>
       </c>
       <c r="I313" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J313" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K313" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L313" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M313" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N313" t="s">
         <v>1568</v>
@@ -18838,13 +18838,13 @@
         <v>1102</v>
       </c>
       <c r="D314" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="E314" t="s">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="F314" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G314" t="s">
         <v>1561</v>
@@ -18853,10 +18853,10 @@
         <v>1567</v>
       </c>
       <c r="I314" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J314" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K314" t="s">
         <v>1566</v>
@@ -18882,10 +18882,10 @@
         <v>1103</v>
       </c>
       <c r="D315" t="s">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="E315" t="s">
-        <v>1433</v>
+        <v>1530</v>
       </c>
       <c r="F315" t="s">
         <v>1555</v>
@@ -18894,22 +18894,22 @@
         <v>1561</v>
       </c>
       <c r="H315" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I315" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J315" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K315" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L315" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M315" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N315" t="s">
         <v>1568</v>
@@ -18926,34 +18926,34 @@
         <v>1104</v>
       </c>
       <c r="D316" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E316" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F316" t="s">
         <v>1555</v>
       </c>
       <c r="G316" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H316" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I316" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J316" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K316" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L316" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M316" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N316" t="s">
         <v>1568</v>
@@ -18970,10 +18970,10 @@
         <v>1105</v>
       </c>
       <c r="D317" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E317" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F317" t="s">
         <v>1555</v>
@@ -19014,34 +19014,34 @@
         <v>1106</v>
       </c>
       <c r="D318" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E318" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F318" t="s">
         <v>1555</v>
       </c>
       <c r="G318" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H318" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I318" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J318" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K318" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L318" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M318" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="N318" t="s">
         <v>1568</v>
@@ -19058,34 +19058,34 @@
         <v>1107</v>
       </c>
       <c r="D319" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E319" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F319" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G319" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H319" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I319" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J319" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K319" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L319" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M319" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N319" t="s">
         <v>1568</v>
@@ -19102,34 +19102,34 @@
         <v>1108</v>
       </c>
       <c r="D320" t="s">
-        <v>1346</v>
+        <v>1315</v>
       </c>
       <c r="E320" t="s">
-        <v>1534</v>
+        <v>1503</v>
       </c>
       <c r="F320" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G320" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H320" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I320" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J320" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K320" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L320" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M320" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N320" t="s">
         <v>1568</v>
@@ -19146,13 +19146,13 @@
         <v>1109</v>
       </c>
       <c r="D321" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="E321" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="F321" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G321" t="s">
         <v>1561</v>
@@ -19167,13 +19167,13 @@
         <v>1563</v>
       </c>
       <c r="K321" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L321" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M321" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N321" t="s">
         <v>1568</v>
@@ -19190,10 +19190,10 @@
         <v>1110</v>
       </c>
       <c r="D322" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
       <c r="E322" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F322" t="s">
         <v>1555</v>
@@ -19208,16 +19208,16 @@
         <v>1567</v>
       </c>
       <c r="J322" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K322" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L322" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M322" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N322" t="s">
         <v>1568</v>
@@ -19234,31 +19234,31 @@
         <v>1111</v>
       </c>
       <c r="D323" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E323" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F323" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G323" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H323" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I323" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J323" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K323" t="s">
         <v>1565</v>
       </c>
       <c r="L323" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M323" t="s">
         <v>1563</v>
@@ -19278,34 +19278,34 @@
         <v>1112</v>
       </c>
       <c r="D324" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="E324" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="F324" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G324" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H324" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I324" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J324" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K324" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L324" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M324" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N324" t="s">
         <v>1568</v>
@@ -19322,34 +19322,34 @@
         <v>1113</v>
       </c>
       <c r="D325" t="s">
-        <v>1314</v>
+        <v>1224</v>
       </c>
       <c r="E325" t="s">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="F325" t="s">
         <v>1556</v>
       </c>
       <c r="G325" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H325" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I325" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="J325" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K325" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L325" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M325" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="N325" t="s">
         <v>1568</v>
@@ -19366,34 +19366,34 @@
         <v>1114</v>
       </c>
       <c r="D326" t="s">
-        <v>1224</v>
+        <v>1262</v>
       </c>
       <c r="E326" t="s">
-        <v>1412</v>
+        <v>1450</v>
       </c>
       <c r="F326" t="s">
         <v>1556</v>
       </c>
       <c r="G326" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H326" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I326" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J326" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K326" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L326" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M326" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N326" t="s">
         <v>1568</v>
@@ -19410,34 +19410,34 @@
         <v>1115</v>
       </c>
       <c r="D327" t="s">
-        <v>1262</v>
+        <v>1291</v>
       </c>
       <c r="E327" t="s">
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="F327" t="s">
         <v>1556</v>
       </c>
       <c r="G327" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H327" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I327" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J327" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K327" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L327" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M327" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N327" t="s">
         <v>1568</v>
@@ -19454,34 +19454,34 @@
         <v>1116</v>
       </c>
       <c r="D328" t="s">
-        <v>1291</v>
+        <v>1262</v>
       </c>
       <c r="E328" t="s">
-        <v>1479</v>
+        <v>1450</v>
       </c>
       <c r="F328" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G328" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="H328" t="s">
         <v>1561</v>
       </c>
       <c r="I328" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J328" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K328" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L328" t="s">
         <v>1566</v>
       </c>
       <c r="M328" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N328" t="s">
         <v>1568</v>
@@ -19498,31 +19498,31 @@
         <v>1117</v>
       </c>
       <c r="D329" t="s">
-        <v>1262</v>
+        <v>1349</v>
       </c>
       <c r="E329" t="s">
-        <v>1450</v>
+        <v>1537</v>
       </c>
       <c r="F329" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G329" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H329" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I329" t="s">
         <v>1567</v>
       </c>
       <c r="J329" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K329" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L329" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M329" t="s">
         <v>1562</v>
@@ -19542,10 +19542,10 @@
         <v>1118</v>
       </c>
       <c r="D330" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E330" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F330" t="s">
         <v>1559</v>
@@ -19560,16 +19560,16 @@
         <v>1567</v>
       </c>
       <c r="J330" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K330" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L330" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M330" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N330" t="s">
         <v>1568</v>
@@ -19586,13 +19586,13 @@
         <v>1119</v>
       </c>
       <c r="D331" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E331" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F331" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G331" t="s">
         <v>1561</v>
@@ -19604,13 +19604,13 @@
         <v>1567</v>
       </c>
       <c r="J331" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K331" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L331" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M331" t="s">
         <v>1563</v>
@@ -19630,34 +19630,34 @@
         <v>1120</v>
       </c>
       <c r="D332" t="s">
-        <v>1351</v>
+        <v>1331</v>
       </c>
       <c r="E332" t="s">
-        <v>1539</v>
+        <v>1519</v>
       </c>
       <c r="F332" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G332" t="s">
         <v>1561</v>
       </c>
       <c r="H332" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I332" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J332" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K332" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L332" t="s">
         <v>1562</v>
       </c>
       <c r="M332" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N332" t="s">
         <v>1568</v>
@@ -19674,25 +19674,25 @@
         <v>1121</v>
       </c>
       <c r="D333" t="s">
-        <v>1331</v>
+        <v>1201</v>
       </c>
       <c r="E333" t="s">
-        <v>1519</v>
+        <v>1389</v>
       </c>
       <c r="F333" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G333" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H333" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I333" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J333" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K333" t="s">
         <v>1565</v>
@@ -19718,31 +19718,31 @@
         <v>1122</v>
       </c>
       <c r="D334" t="s">
-        <v>1201</v>
+        <v>1271</v>
       </c>
       <c r="E334" t="s">
-        <v>1389</v>
+        <v>1459</v>
       </c>
       <c r="F334" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G334" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H334" t="s">
         <v>1564</v>
       </c>
       <c r="I334" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J334" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K334" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L334" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M334" t="s">
         <v>1566</v>
@@ -19762,34 +19762,34 @@
         <v>1123</v>
       </c>
       <c r="D335" t="s">
-        <v>1271</v>
+        <v>1352</v>
       </c>
       <c r="E335" t="s">
-        <v>1459</v>
+        <v>1540</v>
       </c>
       <c r="F335" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G335" t="s">
         <v>1561</v>
       </c>
       <c r="H335" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I335" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J335" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K335" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L335" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M335" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N335" t="s">
         <v>1568</v>
@@ -19806,34 +19806,34 @@
         <v>1124</v>
       </c>
       <c r="D336" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E336" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F336" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G336" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H336" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I336" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J336" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K336" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L336" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M336" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N336" t="s">
         <v>1568</v>
@@ -19850,34 +19850,34 @@
         <v>1125</v>
       </c>
       <c r="D337" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E337" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F337" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G337" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H337" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I337" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J337" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K337" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L337" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M337" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N337" t="s">
         <v>1568</v>
@@ -19894,34 +19894,34 @@
         <v>1126</v>
       </c>
       <c r="D338" t="s">
-        <v>1354</v>
+        <v>1230</v>
       </c>
       <c r="E338" t="s">
-        <v>1542</v>
+        <v>1418</v>
       </c>
       <c r="F338" t="s">
         <v>1557</v>
       </c>
       <c r="G338" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="H338" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I338" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J338" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K338" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L338" t="s">
         <v>1566</v>
       </c>
       <c r="M338" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N338" t="s">
         <v>1568</v>
@@ -19938,10 +19938,10 @@
         <v>1127</v>
       </c>
       <c r="D339" t="s">
-        <v>1230</v>
+        <v>1355</v>
       </c>
       <c r="E339" t="s">
-        <v>1418</v>
+        <v>1543</v>
       </c>
       <c r="F339" t="s">
         <v>1557</v>
@@ -19950,13 +19950,13 @@
         <v>1562</v>
       </c>
       <c r="H339" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I339" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J339" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K339" t="s">
         <v>1567</v>
@@ -19965,7 +19965,7 @@
         <v>1566</v>
       </c>
       <c r="M339" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N339" t="s">
         <v>1568</v>
@@ -19982,34 +19982,34 @@
         <v>1128</v>
       </c>
       <c r="D340" t="s">
-        <v>1355</v>
+        <v>1196</v>
       </c>
       <c r="E340" t="s">
-        <v>1543</v>
+        <v>1384</v>
       </c>
       <c r="F340" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G340" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H340" t="s">
         <v>1561</v>
       </c>
       <c r="I340" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J340" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K340" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L340" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M340" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N340" t="s">
         <v>1568</v>
@@ -20026,34 +20026,34 @@
         <v>1129</v>
       </c>
       <c r="D341" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E341" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F341" t="s">
         <v>1555</v>
       </c>
       <c r="G341" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H341" t="s">
         <v>1561</v>
       </c>
       <c r="I341" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J341" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K341" t="s">
         <v>1565</v>
       </c>
       <c r="L341" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M341" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N341" t="s">
         <v>1568</v>
@@ -20070,34 +20070,34 @@
         <v>1130</v>
       </c>
       <c r="D342" t="s">
-        <v>1194</v>
+        <v>1329</v>
       </c>
       <c r="E342" t="s">
-        <v>1382</v>
+        <v>1517</v>
       </c>
       <c r="F342" t="s">
         <v>1555</v>
       </c>
       <c r="G342" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H342" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I342" t="s">
         <v>1564</v>
       </c>
       <c r="J342" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K342" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L342" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M342" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N342" t="s">
         <v>1568</v>
@@ -20114,34 +20114,34 @@
         <v>1131</v>
       </c>
       <c r="D343" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
       <c r="E343" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F343" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G343" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H343" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I343" t="s">
         <v>1564</v>
       </c>
       <c r="J343" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K343" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L343" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M343" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N343" t="s">
         <v>1568</v>
@@ -20158,34 +20158,34 @@
         <v>1132</v>
       </c>
       <c r="D344" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E344" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F344" t="s">
         <v>1556</v>
       </c>
       <c r="G344" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="H344" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="I344" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J344" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="K344" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L344" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M344" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N344" t="s">
         <v>1568</v>
@@ -20202,34 +20202,34 @@
         <v>1133</v>
       </c>
       <c r="D345" t="s">
-        <v>1357</v>
+        <v>1262</v>
       </c>
       <c r="E345" t="s">
-        <v>1545</v>
+        <v>1450</v>
       </c>
       <c r="F345" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G345" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H345" t="s">
         <v>1561</v>
       </c>
       <c r="I345" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="J345" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K345" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L345" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M345" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N345" t="s">
         <v>1568</v>
@@ -20246,28 +20246,28 @@
         <v>1134</v>
       </c>
       <c r="D346" t="s">
-        <v>1262</v>
+        <v>1227</v>
       </c>
       <c r="E346" t="s">
-        <v>1450</v>
+        <v>1415</v>
       </c>
       <c r="F346" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G346" t="s">
         <v>1565</v>
       </c>
       <c r="H346" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I346" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J346" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K346" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L346" t="s">
         <v>1562</v>
@@ -20290,31 +20290,31 @@
         <v>1135</v>
       </c>
       <c r="D347" t="s">
-        <v>1227</v>
+        <v>1303</v>
       </c>
       <c r="E347" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
       <c r="F347" t="s">
         <v>1556</v>
       </c>
       <c r="G347" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H347" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I347" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J347" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K347" t="s">
         <v>1563</v>
       </c>
       <c r="L347" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M347" t="s">
         <v>1566</v>
@@ -20334,31 +20334,31 @@
         <v>1136</v>
       </c>
       <c r="D348" t="s">
-        <v>1303</v>
+        <v>1358</v>
       </c>
       <c r="E348" t="s">
-        <v>1491</v>
+        <v>1546</v>
       </c>
       <c r="F348" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G348" t="s">
         <v>1561</v>
       </c>
       <c r="H348" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I348" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J348" t="s">
         <v>1562</v>
       </c>
       <c r="K348" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L348" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M348" t="s">
         <v>1566</v>
@@ -20378,13 +20378,13 @@
         <v>1137</v>
       </c>
       <c r="D349" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E349" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F349" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G349" t="s">
         <v>1561</v>
@@ -20396,16 +20396,16 @@
         <v>1567</v>
       </c>
       <c r="J349" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K349" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L349" t="s">
         <v>1563</v>
       </c>
       <c r="M349" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N349" t="s">
         <v>1568</v>
@@ -20422,13 +20422,13 @@
         <v>1138</v>
       </c>
       <c r="D350" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E350" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F350" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G350" t="s">
         <v>1561</v>
@@ -20440,16 +20440,16 @@
         <v>1567</v>
       </c>
       <c r="J350" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K350" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L350" t="s">
         <v>1563</v>
       </c>
       <c r="M350" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N350" t="s">
         <v>1568</v>
@@ -20466,31 +20466,31 @@
         <v>1139</v>
       </c>
       <c r="D351" t="s">
-        <v>1360</v>
+        <v>1225</v>
       </c>
       <c r="E351" t="s">
-        <v>1548</v>
+        <v>1413</v>
       </c>
       <c r="F351" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G351" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H351" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I351" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J351" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K351" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L351" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M351" t="s">
         <v>1566</v>
@@ -20510,34 +20510,34 @@
         <v>1140</v>
       </c>
       <c r="D352" t="s">
-        <v>1225</v>
+        <v>1361</v>
       </c>
       <c r="E352" t="s">
-        <v>1413</v>
+        <v>1549</v>
       </c>
       <c r="F352" t="s">
         <v>1556</v>
       </c>
       <c r="G352" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H352" t="s">
         <v>1562</v>
       </c>
       <c r="I352" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J352" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K352" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L352" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M352" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N352" t="s">
         <v>1568</v>
@@ -20554,13 +20554,13 @@
         <v>1141</v>
       </c>
       <c r="D353" t="s">
-        <v>1361</v>
+        <v>1203</v>
       </c>
       <c r="E353" t="s">
-        <v>1549</v>
+        <v>1391</v>
       </c>
       <c r="F353" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G353" t="s">
         <v>1561</v>
@@ -20569,16 +20569,16 @@
         <v>1562</v>
       </c>
       <c r="I353" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J353" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K353" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="L353" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M353" t="s">
         <v>1565</v>
@@ -20598,10 +20598,10 @@
         <v>1142</v>
       </c>
       <c r="D354" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E354" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F354" t="s">
         <v>1555</v>
@@ -20642,10 +20642,10 @@
         <v>1143</v>
       </c>
       <c r="D355" t="s">
-        <v>1205</v>
+        <v>1353</v>
       </c>
       <c r="E355" t="s">
-        <v>1393</v>
+        <v>1541</v>
       </c>
       <c r="F355" t="s">
         <v>1555</v>
@@ -20654,22 +20654,22 @@
         <v>1561</v>
       </c>
       <c r="H355" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="I355" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J355" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K355" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L355" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M355" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N355" t="s">
         <v>1568</v>
@@ -20686,34 +20686,34 @@
         <v>1144</v>
       </c>
       <c r="D356" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E356" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F356" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G356" t="s">
         <v>1561</v>
       </c>
       <c r="H356" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="I356" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J356" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K356" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L356" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M356" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N356" t="s">
         <v>1568</v>
@@ -20730,13 +20730,13 @@
         <v>1145</v>
       </c>
       <c r="D357" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="E357" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="F357" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G357" t="s">
         <v>1561</v>
@@ -20745,19 +20745,19 @@
         <v>1562</v>
       </c>
       <c r="I357" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J357" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K357" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L357" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M357" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N357" t="s">
         <v>1568</v>
@@ -20774,10 +20774,10 @@
         <v>1146</v>
       </c>
       <c r="D358" t="s">
-        <v>1362</v>
+        <v>1316</v>
       </c>
       <c r="E358" t="s">
-        <v>1550</v>
+        <v>1504</v>
       </c>
       <c r="F358" t="s">
         <v>1557</v>
@@ -20786,22 +20786,22 @@
         <v>1561</v>
       </c>
       <c r="H358" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I358" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J358" t="s">
         <v>1563</v>
       </c>
       <c r="K358" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L358" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M358" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N358" t="s">
         <v>1568</v>
@@ -20818,13 +20818,13 @@
         <v>1147</v>
       </c>
       <c r="D359" t="s">
-        <v>1316</v>
+        <v>1277</v>
       </c>
       <c r="E359" t="s">
-        <v>1504</v>
+        <v>1465</v>
       </c>
       <c r="F359" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G359" t="s">
         <v>1561</v>
@@ -20833,19 +20833,19 @@
         <v>1564</v>
       </c>
       <c r="I359" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J359" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K359" t="s">
         <v>1562</v>
       </c>
       <c r="L359" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M359" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N359" t="s">
         <v>1568</v>
@@ -20862,34 +20862,34 @@
         <v>1148</v>
       </c>
       <c r="D360" t="s">
-        <v>1277</v>
+        <v>1256</v>
       </c>
       <c r="E360" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="F360" t="s">
         <v>1556</v>
       </c>
       <c r="G360" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H360" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I360" t="s">
         <v>1565</v>
       </c>
       <c r="J360" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K360" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L360" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M360" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N360" t="s">
         <v>1568</v>
@@ -20906,34 +20906,34 @@
         <v>1149</v>
       </c>
       <c r="D361" t="s">
-        <v>1256</v>
+        <v>1216</v>
       </c>
       <c r="E361" t="s">
-        <v>1444</v>
+        <v>1404</v>
       </c>
       <c r="F361" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G361" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H361" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="I361" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J361" t="s">
         <v>1562</v>
       </c>
       <c r="K361" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L361" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M361" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="N361" t="s">
         <v>1568</v>
@@ -20950,34 +20950,34 @@
         <v>1150</v>
       </c>
       <c r="D362" t="s">
-        <v>1216</v>
+        <v>1334</v>
       </c>
       <c r="E362" t="s">
-        <v>1404</v>
+        <v>1522</v>
       </c>
       <c r="F362" t="s">
         <v>1555</v>
       </c>
       <c r="G362" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H362" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="I362" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J362" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K362" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L362" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M362" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="N362" t="s">
         <v>1568</v>
@@ -20994,10 +20994,10 @@
         <v>1151</v>
       </c>
       <c r="D363" t="s">
-        <v>1334</v>
+        <v>1280</v>
       </c>
       <c r="E363" t="s">
-        <v>1522</v>
+        <v>1468</v>
       </c>
       <c r="F363" t="s">
         <v>1555</v>
@@ -21009,16 +21009,16 @@
         <v>1564</v>
       </c>
       <c r="I363" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="J363" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K363" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L363" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M363" t="s">
         <v>1562</v>
@@ -21038,34 +21038,34 @@
         <v>1152</v>
       </c>
       <c r="D364" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="E364" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="F364" t="s">
         <v>1555</v>
       </c>
       <c r="G364" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H364" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I364" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J364" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K364" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L364" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M364" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N364" t="s">
         <v>1568</v>
@@ -21082,34 +21082,34 @@
         <v>1153</v>
       </c>
       <c r="D365" t="s">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="E365" t="s">
-        <v>1498</v>
+        <v>1453</v>
       </c>
       <c r="F365" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G365" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H365" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I365" t="s">
         <v>1561</v>
       </c>
       <c r="J365" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K365" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L365" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M365" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N365" t="s">
         <v>1568</v>
@@ -21126,34 +21126,34 @@
         <v>1154</v>
       </c>
       <c r="D366" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="E366" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="F366" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G366" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H366" t="s">
         <v>1564</v>
       </c>
       <c r="I366" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J366" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K366" t="s">
         <v>1565</v>
       </c>
       <c r="L366" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M366" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N366" t="s">
         <v>1568</v>
@@ -21170,34 +21170,34 @@
         <v>1155</v>
       </c>
       <c r="D367" t="s">
-        <v>1255</v>
+        <v>1203</v>
       </c>
       <c r="E367" t="s">
-        <v>1443</v>
+        <v>1391</v>
       </c>
       <c r="F367" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G367" t="s">
         <v>1561</v>
       </c>
       <c r="H367" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I367" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J367" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K367" t="s">
         <v>1565</v>
       </c>
       <c r="L367" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M367" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N367" t="s">
         <v>1568</v>
@@ -21214,34 +21214,34 @@
         <v>1156</v>
       </c>
       <c r="D368" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="E368" t="s">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="F368" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G368" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H368" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I368" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J368" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K368" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L368" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M368" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N368" t="s">
         <v>1568</v>
@@ -21258,34 +21258,34 @@
         <v>1157</v>
       </c>
       <c r="D369" t="s">
-        <v>1219</v>
+        <v>1267</v>
       </c>
       <c r="E369" t="s">
-        <v>1407</v>
+        <v>1455</v>
       </c>
       <c r="F369" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G369" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="H369" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I369" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J369" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K369" t="s">
         <v>1563</v>
       </c>
       <c r="L369" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M369" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N369" t="s">
         <v>1568</v>
@@ -21302,19 +21302,19 @@
         <v>1158</v>
       </c>
       <c r="D370" t="s">
-        <v>1267</v>
+        <v>1286</v>
       </c>
       <c r="E370" t="s">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F370" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G370" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H370" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I370" t="s">
         <v>1564</v>
@@ -21323,10 +21323,10 @@
         <v>1567</v>
       </c>
       <c r="K370" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L370" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M370" t="s">
         <v>1566</v>
@@ -21346,34 +21346,34 @@
         <v>1159</v>
       </c>
       <c r="D371" t="s">
-        <v>1286</v>
+        <v>1200</v>
       </c>
       <c r="E371" t="s">
-        <v>1474</v>
+        <v>1388</v>
       </c>
       <c r="F371" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G371" t="s">
         <v>1562</v>
       </c>
       <c r="H371" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I371" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J371" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K371" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L371" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M371" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N371" t="s">
         <v>1568</v>
@@ -21390,34 +21390,34 @@
         <v>1160</v>
       </c>
       <c r="D372" t="s">
-        <v>1200</v>
+        <v>1361</v>
       </c>
       <c r="E372" t="s">
-        <v>1388</v>
+        <v>1549</v>
       </c>
       <c r="F372" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G372" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H372" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I372" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J372" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K372" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="L372" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M372" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N372" t="s">
         <v>1568</v>
@@ -21434,34 +21434,34 @@
         <v>1161</v>
       </c>
       <c r="D373" t="s">
-        <v>1361</v>
+        <v>1246</v>
       </c>
       <c r="E373" t="s">
-        <v>1549</v>
+        <v>1434</v>
       </c>
       <c r="F373" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G373" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H373" t="s">
         <v>1564</v>
       </c>
       <c r="I373" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J373" t="s">
         <v>1563</v>
       </c>
       <c r="K373" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="L373" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M373" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N373" t="s">
         <v>1568</v>
@@ -21478,31 +21478,31 @@
         <v>1162</v>
       </c>
       <c r="D374" t="s">
-        <v>1246</v>
+        <v>1215</v>
       </c>
       <c r="E374" t="s">
-        <v>1434</v>
+        <v>1403</v>
       </c>
       <c r="F374" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G374" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H374" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I374" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J374" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K374" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L374" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M374" t="s">
         <v>1566</v>
@@ -21522,31 +21522,31 @@
         <v>1163</v>
       </c>
       <c r="D375" t="s">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="E375" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="F375" t="s">
         <v>1556</v>
       </c>
       <c r="G375" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H375" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I375" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J375" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K375" t="s">
         <v>1565</v>
       </c>
       <c r="L375" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="M375" t="s">
         <v>1566</v>
@@ -21566,31 +21566,31 @@
         <v>1164</v>
       </c>
       <c r="D376" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="E376" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="F376" t="s">
         <v>1556</v>
       </c>
       <c r="G376" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H376" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I376" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J376" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K376" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L376" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M376" t="s">
         <v>1566</v>
@@ -21610,34 +21610,34 @@
         <v>1165</v>
       </c>
       <c r="D377" t="s">
-        <v>1226</v>
+        <v>1312</v>
       </c>
       <c r="E377" t="s">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="F377" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G377" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H377" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I377" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="J377" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K377" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L377" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M377" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="N377" t="s">
         <v>1568</v>
@@ -21654,10 +21654,10 @@
         <v>1166</v>
       </c>
       <c r="D378" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E378" t="s">
-        <v>1500</v>
+        <v>1551</v>
       </c>
       <c r="F378" t="s">
         <v>1555</v>
@@ -21698,34 +21698,34 @@
         <v>1167</v>
       </c>
       <c r="D379" t="s">
-        <v>1363</v>
+        <v>1199</v>
       </c>
       <c r="E379" t="s">
-        <v>1551</v>
+        <v>1387</v>
       </c>
       <c r="F379" t="s">
         <v>1555</v>
       </c>
       <c r="G379" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H379" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I379" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J379" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K379" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L379" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M379" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="N379" t="s">
         <v>1568</v>
@@ -21742,31 +21742,31 @@
         <v>1168</v>
       </c>
       <c r="D380" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="E380" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F380" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G380" t="s">
         <v>1561</v>
       </c>
       <c r="H380" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I380" t="s">
         <v>1567</v>
       </c>
       <c r="J380" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K380" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L380" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M380" t="s">
         <v>1566</v>
@@ -21786,34 +21786,34 @@
         <v>1169</v>
       </c>
       <c r="D381" t="s">
-        <v>1211</v>
+        <v>1364</v>
       </c>
       <c r="E381" t="s">
-        <v>1399</v>
+        <v>1552</v>
       </c>
       <c r="F381" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G381" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H381" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I381" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J381" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K381" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L381" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M381" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N381" t="s">
         <v>1568</v>
@@ -21830,34 +21830,34 @@
         <v>1170</v>
       </c>
       <c r="D382" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E382" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F382" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G382" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H382" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I382" t="s">
         <v>1563</v>
       </c>
       <c r="J382" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K382" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L382" t="s">
         <v>1565</v>
       </c>
       <c r="M382" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N382" t="s">
         <v>1568</v>
@@ -21874,34 +21874,34 @@
         <v>1171</v>
       </c>
       <c r="D383" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E383" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F383" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G383" t="s">
         <v>1561</v>
       </c>
       <c r="H383" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I383" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J383" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K383" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L383" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M383" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N383" t="s">
         <v>1568</v>
@@ -21918,13 +21918,13 @@
         <v>1172</v>
       </c>
       <c r="D384" t="s">
-        <v>1366</v>
+        <v>1209</v>
       </c>
       <c r="E384" t="s">
-        <v>1554</v>
+        <v>1397</v>
       </c>
       <c r="F384" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G384" t="s">
         <v>1561</v>
@@ -21939,13 +21939,13 @@
         <v>1562</v>
       </c>
       <c r="K384" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L384" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M384" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N384" t="s">
         <v>1568</v>
@@ -21962,13 +21962,13 @@
         <v>1173</v>
       </c>
       <c r="D385" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="E385" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="F385" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G385" t="s">
         <v>1561</v>
@@ -21980,16 +21980,16 @@
         <v>1567</v>
       </c>
       <c r="J385" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K385" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L385" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M385" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N385" t="s">
         <v>1568</v>
@@ -22006,22 +22006,22 @@
         <v>1174</v>
       </c>
       <c r="D386" t="s">
-        <v>1191</v>
+        <v>1249</v>
       </c>
       <c r="E386" t="s">
-        <v>1379</v>
+        <v>1437</v>
       </c>
       <c r="F386" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G386" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H386" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="I386" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J386" t="s">
         <v>1563</v>
@@ -22030,10 +22030,10 @@
         <v>1565</v>
       </c>
       <c r="L386" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M386" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="N386" t="s">
         <v>1568</v>
@@ -22050,31 +22050,31 @@
         <v>1175</v>
       </c>
       <c r="D387" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="E387" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F387" t="s">
         <v>1556</v>
       </c>
       <c r="G387" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H387" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="I387" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J387" t="s">
         <v>1563</v>
       </c>
       <c r="K387" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L387" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M387" t="s">
         <v>1567</v>
@@ -22094,34 +22094,34 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1255</v>
+        <v>1195</v>
       </c>
       <c r="E388" t="s">
-        <v>1443</v>
+        <v>1383</v>
       </c>
       <c r="F388" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G388" t="s">
         <v>1561</v>
       </c>
       <c r="H388" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I388" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J388" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K388" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L388" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M388" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="N388" t="s">
         <v>1568</v>
@@ -22138,34 +22138,34 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1195</v>
+        <v>1217</v>
       </c>
       <c r="E389" t="s">
-        <v>1383</v>
+        <v>1405</v>
       </c>
       <c r="F389" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G389" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H389" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I389" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J389" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K389" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L389" t="s">
         <v>1566</v>
       </c>
       <c r="M389" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N389" t="s">
         <v>1568</v>
@@ -22182,25 +22182,25 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1328</v>
+        <v>1270</v>
       </c>
       <c r="E390">
-        <v>66.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="F390" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G390" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="H390" t="s">
         <v>1561</v>
       </c>
       <c r="I390" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J390" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K390" t="s">
         <v>1565</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -967,264 +967,264 @@
     <t>الحسن محمود على نصار</t>
   </si>
   <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
     <t>صالح عزت صالح عبد السيد</t>
   </si>
   <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2131,264 +2131,264 @@
     <t>30507282402078</t>
   </si>
   <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
     <t>30209102406398</t>
   </si>
   <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3295,262 +3295,262 @@
     <t>01152609738</t>
   </si>
   <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
     <t>01553863411</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01152380733</t>
   </si>
   <si>
     <t>1353</t>
@@ -18442,13 +18442,13 @@
         <v>1093</v>
       </c>
       <c r="D305" t="s">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="E305" t="s">
-        <v>1509</v>
+        <v>1528</v>
       </c>
       <c r="F305" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G305" t="s">
         <v>1561</v>
@@ -18486,34 +18486,34 @@
         <v>1094</v>
       </c>
       <c r="D306" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E306" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F306" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G306" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H306" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I306" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J306" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="K306" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L306" t="s">
         <v>1566</v>
       </c>
       <c r="M306" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N306" t="s">
         <v>1568</v>
@@ -18530,34 +18530,34 @@
         <v>1095</v>
       </c>
       <c r="D307" t="s">
-        <v>1341</v>
+        <v>1211</v>
       </c>
       <c r="E307" t="s">
-        <v>1529</v>
+        <v>1399</v>
       </c>
       <c r="F307" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G307" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H307" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I307" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J307" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K307" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L307" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M307" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N307" t="s">
         <v>1568</v>
@@ -18574,31 +18574,31 @@
         <v>1096</v>
       </c>
       <c r="D308" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="E308" t="s">
-        <v>1399</v>
+        <v>1454</v>
       </c>
       <c r="F308" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G308" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H308" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I308" t="s">
         <v>1567</v>
       </c>
       <c r="J308" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K308" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="L308" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M308" t="s">
         <v>1563</v>
@@ -18618,28 +18618,28 @@
         <v>1097</v>
       </c>
       <c r="D309" t="s">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="E309" t="s">
-        <v>1454</v>
+        <v>1473</v>
       </c>
       <c r="F309" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G309" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H309" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I309" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J309" t="s">
         <v>1565</v>
       </c>
       <c r="K309" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L309" t="s">
         <v>1566</v>
@@ -18662,34 +18662,34 @@
         <v>1098</v>
       </c>
       <c r="D310" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="E310" t="s">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="F310" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G310" t="s">
         <v>1561</v>
       </c>
       <c r="H310" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I310" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J310" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K310" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L310" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M310" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N310" t="s">
         <v>1568</v>
@@ -18706,13 +18706,13 @@
         <v>1099</v>
       </c>
       <c r="D311" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="E311" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="F311" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G311" t="s">
         <v>1561</v>
@@ -18721,19 +18721,19 @@
         <v>1567</v>
       </c>
       <c r="I311" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J311" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K311" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L311" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M311" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N311" t="s">
         <v>1568</v>
@@ -18750,10 +18750,10 @@
         <v>1100</v>
       </c>
       <c r="D312" t="s">
-        <v>1318</v>
+        <v>1229</v>
       </c>
       <c r="E312" t="s">
-        <v>1506</v>
+        <v>1417</v>
       </c>
       <c r="F312" t="s">
         <v>1556</v>
@@ -18765,19 +18765,19 @@
         <v>1567</v>
       </c>
       <c r="I312" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J312" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K312" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L312" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M312" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N312" t="s">
         <v>1568</v>
@@ -18794,13 +18794,13 @@
         <v>1101</v>
       </c>
       <c r="D313" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="E313" t="s">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="F313" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G313" t="s">
         <v>1561</v>
@@ -18809,10 +18809,10 @@
         <v>1567</v>
       </c>
       <c r="I313" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J313" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K313" t="s">
         <v>1566</v>
@@ -18838,10 +18838,10 @@
         <v>1102</v>
       </c>
       <c r="D314" t="s">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="E314" t="s">
-        <v>1433</v>
+        <v>1530</v>
       </c>
       <c r="F314" t="s">
         <v>1555</v>
@@ -18850,22 +18850,22 @@
         <v>1561</v>
       </c>
       <c r="H314" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I314" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J314" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K314" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L314" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M314" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N314" t="s">
         <v>1568</v>
@@ -18882,34 +18882,34 @@
         <v>1103</v>
       </c>
       <c r="D315" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E315" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F315" t="s">
         <v>1555</v>
       </c>
       <c r="G315" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H315" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I315" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J315" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K315" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L315" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M315" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N315" t="s">
         <v>1568</v>
@@ -18926,10 +18926,10 @@
         <v>1104</v>
       </c>
       <c r="D316" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E316" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F316" t="s">
         <v>1555</v>
@@ -18970,34 +18970,34 @@
         <v>1105</v>
       </c>
       <c r="D317" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E317" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F317" t="s">
         <v>1555</v>
       </c>
       <c r="G317" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H317" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I317" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J317" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K317" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L317" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M317" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="N317" t="s">
         <v>1568</v>
@@ -19014,34 +19014,34 @@
         <v>1106</v>
       </c>
       <c r="D318" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E318" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F318" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G318" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H318" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I318" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J318" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K318" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L318" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M318" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N318" t="s">
         <v>1568</v>
@@ -19058,34 +19058,34 @@
         <v>1107</v>
       </c>
       <c r="D319" t="s">
-        <v>1346</v>
+        <v>1315</v>
       </c>
       <c r="E319" t="s">
-        <v>1534</v>
+        <v>1503</v>
       </c>
       <c r="F319" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G319" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H319" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I319" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J319" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K319" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L319" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M319" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N319" t="s">
         <v>1568</v>
@@ -19102,13 +19102,13 @@
         <v>1108</v>
       </c>
       <c r="D320" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="E320" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="F320" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G320" t="s">
         <v>1561</v>
@@ -19123,13 +19123,13 @@
         <v>1563</v>
       </c>
       <c r="K320" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L320" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M320" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N320" t="s">
         <v>1568</v>
@@ -19146,10 +19146,10 @@
         <v>1109</v>
       </c>
       <c r="D321" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
       <c r="E321" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F321" t="s">
         <v>1555</v>
@@ -19164,16 +19164,16 @@
         <v>1567</v>
       </c>
       <c r="J321" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K321" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L321" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M321" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N321" t="s">
         <v>1568</v>
@@ -19190,31 +19190,31 @@
         <v>1110</v>
       </c>
       <c r="D322" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E322" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F322" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G322" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H322" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I322" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J322" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K322" t="s">
         <v>1565</v>
       </c>
       <c r="L322" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M322" t="s">
         <v>1563</v>
@@ -19234,34 +19234,34 @@
         <v>1111</v>
       </c>
       <c r="D323" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="E323" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="F323" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G323" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H323" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I323" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J323" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K323" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L323" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M323" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N323" t="s">
         <v>1568</v>
@@ -19278,34 +19278,34 @@
         <v>1112</v>
       </c>
       <c r="D324" t="s">
-        <v>1314</v>
+        <v>1224</v>
       </c>
       <c r="E324" t="s">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="F324" t="s">
         <v>1556</v>
       </c>
       <c r="G324" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H324" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I324" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="J324" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K324" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L324" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M324" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="N324" t="s">
         <v>1568</v>
@@ -19322,34 +19322,34 @@
         <v>1113</v>
       </c>
       <c r="D325" t="s">
-        <v>1224</v>
+        <v>1262</v>
       </c>
       <c r="E325" t="s">
-        <v>1412</v>
+        <v>1450</v>
       </c>
       <c r="F325" t="s">
         <v>1556</v>
       </c>
       <c r="G325" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H325" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I325" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J325" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K325" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L325" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M325" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N325" t="s">
         <v>1568</v>
@@ -19366,34 +19366,34 @@
         <v>1114</v>
       </c>
       <c r="D326" t="s">
-        <v>1262</v>
+        <v>1291</v>
       </c>
       <c r="E326" t="s">
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="F326" t="s">
         <v>1556</v>
       </c>
       <c r="G326" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H326" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I326" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J326" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K326" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L326" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M326" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N326" t="s">
         <v>1568</v>
@@ -19410,34 +19410,34 @@
         <v>1115</v>
       </c>
       <c r="D327" t="s">
-        <v>1291</v>
+        <v>1262</v>
       </c>
       <c r="E327" t="s">
-        <v>1479</v>
+        <v>1450</v>
       </c>
       <c r="F327" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G327" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="H327" t="s">
         <v>1561</v>
       </c>
       <c r="I327" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J327" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K327" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L327" t="s">
         <v>1566</v>
       </c>
       <c r="M327" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N327" t="s">
         <v>1568</v>
@@ -19454,31 +19454,31 @@
         <v>1116</v>
       </c>
       <c r="D328" t="s">
-        <v>1262</v>
+        <v>1349</v>
       </c>
       <c r="E328" t="s">
-        <v>1450</v>
+        <v>1537</v>
       </c>
       <c r="F328" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G328" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H328" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I328" t="s">
         <v>1567</v>
       </c>
       <c r="J328" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K328" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L328" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M328" t="s">
         <v>1562</v>
@@ -19498,10 +19498,10 @@
         <v>1117</v>
       </c>
       <c r="D329" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E329" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F329" t="s">
         <v>1559</v>
@@ -19516,16 +19516,16 @@
         <v>1567</v>
       </c>
       <c r="J329" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K329" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L329" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M329" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N329" t="s">
         <v>1568</v>
@@ -19542,13 +19542,13 @@
         <v>1118</v>
       </c>
       <c r="D330" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E330" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F330" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G330" t="s">
         <v>1561</v>
@@ -19560,13 +19560,13 @@
         <v>1567</v>
       </c>
       <c r="J330" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K330" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L330" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M330" t="s">
         <v>1563</v>
@@ -19586,34 +19586,34 @@
         <v>1119</v>
       </c>
       <c r="D331" t="s">
-        <v>1351</v>
+        <v>1331</v>
       </c>
       <c r="E331" t="s">
-        <v>1539</v>
+        <v>1519</v>
       </c>
       <c r="F331" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G331" t="s">
         <v>1561</v>
       </c>
       <c r="H331" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I331" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J331" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K331" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L331" t="s">
         <v>1562</v>
       </c>
       <c r="M331" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N331" t="s">
         <v>1568</v>
@@ -19630,25 +19630,25 @@
         <v>1120</v>
       </c>
       <c r="D332" t="s">
-        <v>1331</v>
+        <v>1201</v>
       </c>
       <c r="E332" t="s">
-        <v>1519</v>
+        <v>1389</v>
       </c>
       <c r="F332" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G332" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H332" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I332" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J332" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K332" t="s">
         <v>1565</v>
@@ -19674,31 +19674,31 @@
         <v>1121</v>
       </c>
       <c r="D333" t="s">
-        <v>1201</v>
+        <v>1271</v>
       </c>
       <c r="E333" t="s">
-        <v>1389</v>
+        <v>1459</v>
       </c>
       <c r="F333" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G333" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H333" t="s">
         <v>1564</v>
       </c>
       <c r="I333" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J333" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K333" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L333" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M333" t="s">
         <v>1566</v>
@@ -19718,34 +19718,34 @@
         <v>1122</v>
       </c>
       <c r="D334" t="s">
-        <v>1271</v>
+        <v>1352</v>
       </c>
       <c r="E334" t="s">
-        <v>1459</v>
+        <v>1540</v>
       </c>
       <c r="F334" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G334" t="s">
         <v>1561</v>
       </c>
       <c r="H334" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I334" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J334" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K334" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L334" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M334" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N334" t="s">
         <v>1568</v>
@@ -19762,34 +19762,34 @@
         <v>1123</v>
       </c>
       <c r="D335" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E335" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F335" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G335" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H335" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I335" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J335" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K335" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L335" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M335" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N335" t="s">
         <v>1568</v>
@@ -19806,34 +19806,34 @@
         <v>1124</v>
       </c>
       <c r="D336" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E336" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F336" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G336" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H336" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I336" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J336" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K336" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L336" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M336" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N336" t="s">
         <v>1568</v>
@@ -19850,34 +19850,34 @@
         <v>1125</v>
       </c>
       <c r="D337" t="s">
-        <v>1354</v>
+        <v>1230</v>
       </c>
       <c r="E337" t="s">
-        <v>1542</v>
+        <v>1418</v>
       </c>
       <c r="F337" t="s">
         <v>1557</v>
       </c>
       <c r="G337" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="H337" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I337" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J337" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K337" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L337" t="s">
         <v>1566</v>
       </c>
       <c r="M337" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N337" t="s">
         <v>1568</v>
@@ -19894,10 +19894,10 @@
         <v>1126</v>
       </c>
       <c r="D338" t="s">
-        <v>1230</v>
+        <v>1355</v>
       </c>
       <c r="E338" t="s">
-        <v>1418</v>
+        <v>1543</v>
       </c>
       <c r="F338" t="s">
         <v>1557</v>
@@ -19906,13 +19906,13 @@
         <v>1562</v>
       </c>
       <c r="H338" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I338" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J338" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K338" t="s">
         <v>1567</v>
@@ -19921,7 +19921,7 @@
         <v>1566</v>
       </c>
       <c r="M338" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N338" t="s">
         <v>1568</v>
@@ -19938,34 +19938,34 @@
         <v>1127</v>
       </c>
       <c r="D339" t="s">
-        <v>1355</v>
+        <v>1196</v>
       </c>
       <c r="E339" t="s">
-        <v>1543</v>
+        <v>1384</v>
       </c>
       <c r="F339" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G339" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H339" t="s">
         <v>1561</v>
       </c>
       <c r="I339" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J339" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K339" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L339" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M339" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N339" t="s">
         <v>1568</v>
@@ -19982,34 +19982,34 @@
         <v>1128</v>
       </c>
       <c r="D340" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E340" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F340" t="s">
         <v>1555</v>
       </c>
       <c r="G340" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H340" t="s">
         <v>1561</v>
       </c>
       <c r="I340" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J340" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K340" t="s">
         <v>1565</v>
       </c>
       <c r="L340" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M340" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N340" t="s">
         <v>1568</v>
@@ -20026,34 +20026,34 @@
         <v>1129</v>
       </c>
       <c r="D341" t="s">
-        <v>1194</v>
+        <v>1329</v>
       </c>
       <c r="E341" t="s">
-        <v>1382</v>
+        <v>1517</v>
       </c>
       <c r="F341" t="s">
         <v>1555</v>
       </c>
       <c r="G341" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H341" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I341" t="s">
         <v>1564</v>
       </c>
       <c r="J341" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K341" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L341" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M341" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N341" t="s">
         <v>1568</v>
@@ -20070,34 +20070,34 @@
         <v>1130</v>
       </c>
       <c r="D342" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
       <c r="E342" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F342" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G342" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H342" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I342" t="s">
         <v>1564</v>
       </c>
       <c r="J342" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K342" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L342" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M342" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N342" t="s">
         <v>1568</v>
@@ -20114,34 +20114,34 @@
         <v>1131</v>
       </c>
       <c r="D343" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E343" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F343" t="s">
         <v>1556</v>
       </c>
       <c r="G343" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="H343" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="I343" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J343" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="K343" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L343" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M343" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N343" t="s">
         <v>1568</v>
@@ -20158,34 +20158,34 @@
         <v>1132</v>
       </c>
       <c r="D344" t="s">
-        <v>1357</v>
+        <v>1262</v>
       </c>
       <c r="E344" t="s">
-        <v>1545</v>
+        <v>1450</v>
       </c>
       <c r="F344" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G344" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H344" t="s">
         <v>1561</v>
       </c>
       <c r="I344" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="J344" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K344" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L344" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M344" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N344" t="s">
         <v>1568</v>
@@ -20202,28 +20202,28 @@
         <v>1133</v>
       </c>
       <c r="D345" t="s">
-        <v>1262</v>
+        <v>1227</v>
       </c>
       <c r="E345" t="s">
-        <v>1450</v>
+        <v>1415</v>
       </c>
       <c r="F345" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G345" t="s">
         <v>1565</v>
       </c>
       <c r="H345" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I345" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J345" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K345" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L345" t="s">
         <v>1562</v>
@@ -20246,31 +20246,31 @@
         <v>1134</v>
       </c>
       <c r="D346" t="s">
-        <v>1227</v>
+        <v>1303</v>
       </c>
       <c r="E346" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
       <c r="F346" t="s">
         <v>1556</v>
       </c>
       <c r="G346" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H346" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I346" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J346" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K346" t="s">
         <v>1563</v>
       </c>
       <c r="L346" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M346" t="s">
         <v>1566</v>
@@ -20290,31 +20290,31 @@
         <v>1135</v>
       </c>
       <c r="D347" t="s">
-        <v>1303</v>
+        <v>1358</v>
       </c>
       <c r="E347" t="s">
-        <v>1491</v>
+        <v>1546</v>
       </c>
       <c r="F347" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G347" t="s">
         <v>1561</v>
       </c>
       <c r="H347" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I347" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J347" t="s">
         <v>1562</v>
       </c>
       <c r="K347" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L347" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M347" t="s">
         <v>1566</v>
@@ -20334,13 +20334,13 @@
         <v>1136</v>
       </c>
       <c r="D348" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E348" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F348" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G348" t="s">
         <v>1561</v>
@@ -20352,16 +20352,16 @@
         <v>1567</v>
       </c>
       <c r="J348" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K348" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L348" t="s">
         <v>1563</v>
       </c>
       <c r="M348" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N348" t="s">
         <v>1568</v>
@@ -20378,13 +20378,13 @@
         <v>1137</v>
       </c>
       <c r="D349" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E349" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F349" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G349" t="s">
         <v>1561</v>
@@ -20396,16 +20396,16 @@
         <v>1567</v>
       </c>
       <c r="J349" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K349" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L349" t="s">
         <v>1563</v>
       </c>
       <c r="M349" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N349" t="s">
         <v>1568</v>
@@ -20422,31 +20422,31 @@
         <v>1138</v>
       </c>
       <c r="D350" t="s">
-        <v>1360</v>
+        <v>1225</v>
       </c>
       <c r="E350" t="s">
-        <v>1548</v>
+        <v>1413</v>
       </c>
       <c r="F350" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G350" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H350" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I350" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J350" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K350" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L350" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M350" t="s">
         <v>1566</v>
@@ -20466,34 +20466,34 @@
         <v>1139</v>
       </c>
       <c r="D351" t="s">
-        <v>1225</v>
+        <v>1361</v>
       </c>
       <c r="E351" t="s">
-        <v>1413</v>
+        <v>1549</v>
       </c>
       <c r="F351" t="s">
         <v>1556</v>
       </c>
       <c r="G351" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H351" t="s">
         <v>1562</v>
       </c>
       <c r="I351" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J351" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K351" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L351" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M351" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N351" t="s">
         <v>1568</v>
@@ -20510,13 +20510,13 @@
         <v>1140</v>
       </c>
       <c r="D352" t="s">
-        <v>1361</v>
+        <v>1203</v>
       </c>
       <c r="E352" t="s">
-        <v>1549</v>
+        <v>1391</v>
       </c>
       <c r="F352" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G352" t="s">
         <v>1561</v>
@@ -20525,16 +20525,16 @@
         <v>1562</v>
       </c>
       <c r="I352" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J352" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K352" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="L352" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M352" t="s">
         <v>1565</v>
@@ -20554,10 +20554,10 @@
         <v>1141</v>
       </c>
       <c r="D353" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E353" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F353" t="s">
         <v>1555</v>
@@ -20598,10 +20598,10 @@
         <v>1142</v>
       </c>
       <c r="D354" t="s">
-        <v>1205</v>
+        <v>1353</v>
       </c>
       <c r="E354" t="s">
-        <v>1393</v>
+        <v>1541</v>
       </c>
       <c r="F354" t="s">
         <v>1555</v>
@@ -20610,22 +20610,22 @@
         <v>1561</v>
       </c>
       <c r="H354" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="I354" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J354" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K354" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L354" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M354" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N354" t="s">
         <v>1568</v>
@@ -20642,34 +20642,34 @@
         <v>1143</v>
       </c>
       <c r="D355" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E355" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F355" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G355" t="s">
         <v>1561</v>
       </c>
       <c r="H355" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="I355" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J355" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K355" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L355" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M355" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N355" t="s">
         <v>1568</v>
@@ -20686,13 +20686,13 @@
         <v>1144</v>
       </c>
       <c r="D356" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="E356" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="F356" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G356" t="s">
         <v>1561</v>
@@ -20701,19 +20701,19 @@
         <v>1562</v>
       </c>
       <c r="I356" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J356" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K356" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L356" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M356" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N356" t="s">
         <v>1568</v>
@@ -20730,10 +20730,10 @@
         <v>1145</v>
       </c>
       <c r="D357" t="s">
-        <v>1362</v>
+        <v>1316</v>
       </c>
       <c r="E357" t="s">
-        <v>1550</v>
+        <v>1504</v>
       </c>
       <c r="F357" t="s">
         <v>1557</v>
@@ -20742,22 +20742,22 @@
         <v>1561</v>
       </c>
       <c r="H357" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I357" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J357" t="s">
         <v>1563</v>
       </c>
       <c r="K357" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L357" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M357" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N357" t="s">
         <v>1568</v>
@@ -20774,13 +20774,13 @@
         <v>1146</v>
       </c>
       <c r="D358" t="s">
-        <v>1316</v>
+        <v>1277</v>
       </c>
       <c r="E358" t="s">
-        <v>1504</v>
+        <v>1465</v>
       </c>
       <c r="F358" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G358" t="s">
         <v>1561</v>
@@ -20789,19 +20789,19 @@
         <v>1564</v>
       </c>
       <c r="I358" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J358" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K358" t="s">
         <v>1562</v>
       </c>
       <c r="L358" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M358" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N358" t="s">
         <v>1568</v>
@@ -20818,34 +20818,34 @@
         <v>1147</v>
       </c>
       <c r="D359" t="s">
-        <v>1277</v>
+        <v>1256</v>
       </c>
       <c r="E359" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="F359" t="s">
         <v>1556</v>
       </c>
       <c r="G359" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H359" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I359" t="s">
         <v>1565</v>
       </c>
       <c r="J359" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K359" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L359" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M359" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N359" t="s">
         <v>1568</v>
@@ -20862,34 +20862,34 @@
         <v>1148</v>
       </c>
       <c r="D360" t="s">
-        <v>1256</v>
+        <v>1216</v>
       </c>
       <c r="E360" t="s">
-        <v>1444</v>
+        <v>1404</v>
       </c>
       <c r="F360" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G360" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H360" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="I360" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J360" t="s">
         <v>1562</v>
       </c>
       <c r="K360" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L360" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M360" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="N360" t="s">
         <v>1568</v>
@@ -20906,34 +20906,34 @@
         <v>1149</v>
       </c>
       <c r="D361" t="s">
-        <v>1216</v>
+        <v>1334</v>
       </c>
       <c r="E361" t="s">
-        <v>1404</v>
+        <v>1522</v>
       </c>
       <c r="F361" t="s">
         <v>1555</v>
       </c>
       <c r="G361" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H361" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="I361" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J361" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K361" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L361" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M361" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="N361" t="s">
         <v>1568</v>
@@ -20950,10 +20950,10 @@
         <v>1150</v>
       </c>
       <c r="D362" t="s">
-        <v>1334</v>
+        <v>1280</v>
       </c>
       <c r="E362" t="s">
-        <v>1522</v>
+        <v>1468</v>
       </c>
       <c r="F362" t="s">
         <v>1555</v>
@@ -20965,16 +20965,16 @@
         <v>1564</v>
       </c>
       <c r="I362" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="J362" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K362" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L362" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M362" t="s">
         <v>1562</v>
@@ -20994,34 +20994,34 @@
         <v>1151</v>
       </c>
       <c r="D363" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="E363" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="F363" t="s">
         <v>1555</v>
       </c>
       <c r="G363" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H363" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I363" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J363" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K363" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L363" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M363" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N363" t="s">
         <v>1568</v>
@@ -21038,34 +21038,34 @@
         <v>1152</v>
       </c>
       <c r="D364" t="s">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="E364" t="s">
-        <v>1498</v>
+        <v>1453</v>
       </c>
       <c r="F364" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G364" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H364" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I364" t="s">
         <v>1561</v>
       </c>
       <c r="J364" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K364" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L364" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M364" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N364" t="s">
         <v>1568</v>
@@ -21082,34 +21082,34 @@
         <v>1153</v>
       </c>
       <c r="D365" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="E365" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="F365" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G365" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H365" t="s">
         <v>1564</v>
       </c>
       <c r="I365" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J365" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K365" t="s">
         <v>1565</v>
       </c>
       <c r="L365" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M365" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N365" t="s">
         <v>1568</v>
@@ -21126,34 +21126,34 @@
         <v>1154</v>
       </c>
       <c r="D366" t="s">
-        <v>1255</v>
+        <v>1203</v>
       </c>
       <c r="E366" t="s">
-        <v>1443</v>
+        <v>1391</v>
       </c>
       <c r="F366" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G366" t="s">
         <v>1561</v>
       </c>
       <c r="H366" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I366" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J366" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K366" t="s">
         <v>1565</v>
       </c>
       <c r="L366" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M366" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N366" t="s">
         <v>1568</v>
@@ -21170,34 +21170,34 @@
         <v>1155</v>
       </c>
       <c r="D367" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="E367" t="s">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="F367" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G367" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H367" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I367" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J367" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K367" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L367" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M367" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N367" t="s">
         <v>1568</v>
@@ -21214,34 +21214,34 @@
         <v>1156</v>
       </c>
       <c r="D368" t="s">
-        <v>1219</v>
+        <v>1267</v>
       </c>
       <c r="E368" t="s">
-        <v>1407</v>
+        <v>1455</v>
       </c>
       <c r="F368" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G368" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="H368" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I368" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J368" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K368" t="s">
         <v>1563</v>
       </c>
       <c r="L368" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M368" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N368" t="s">
         <v>1568</v>
@@ -21258,19 +21258,19 @@
         <v>1157</v>
       </c>
       <c r="D369" t="s">
-        <v>1267</v>
+        <v>1286</v>
       </c>
       <c r="E369" t="s">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F369" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G369" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H369" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I369" t="s">
         <v>1564</v>
@@ -21279,10 +21279,10 @@
         <v>1567</v>
       </c>
       <c r="K369" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L369" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M369" t="s">
         <v>1566</v>
@@ -21302,34 +21302,34 @@
         <v>1158</v>
       </c>
       <c r="D370" t="s">
-        <v>1286</v>
+        <v>1200</v>
       </c>
       <c r="E370" t="s">
-        <v>1474</v>
+        <v>1388</v>
       </c>
       <c r="F370" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G370" t="s">
         <v>1562</v>
       </c>
       <c r="H370" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I370" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J370" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K370" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L370" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M370" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N370" t="s">
         <v>1568</v>
@@ -21346,34 +21346,34 @@
         <v>1159</v>
       </c>
       <c r="D371" t="s">
-        <v>1200</v>
+        <v>1361</v>
       </c>
       <c r="E371" t="s">
-        <v>1388</v>
+        <v>1549</v>
       </c>
       <c r="F371" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G371" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H371" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I371" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J371" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K371" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="L371" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M371" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N371" t="s">
         <v>1568</v>
@@ -21390,34 +21390,34 @@
         <v>1160</v>
       </c>
       <c r="D372" t="s">
-        <v>1361</v>
+        <v>1246</v>
       </c>
       <c r="E372" t="s">
-        <v>1549</v>
+        <v>1434</v>
       </c>
       <c r="F372" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G372" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H372" t="s">
         <v>1564</v>
       </c>
       <c r="I372" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J372" t="s">
         <v>1563</v>
       </c>
       <c r="K372" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="L372" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M372" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N372" t="s">
         <v>1568</v>
@@ -21434,31 +21434,31 @@
         <v>1161</v>
       </c>
       <c r="D373" t="s">
-        <v>1246</v>
+        <v>1215</v>
       </c>
       <c r="E373" t="s">
-        <v>1434</v>
+        <v>1403</v>
       </c>
       <c r="F373" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G373" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H373" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I373" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J373" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K373" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L373" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M373" t="s">
         <v>1566</v>
@@ -21478,31 +21478,31 @@
         <v>1162</v>
       </c>
       <c r="D374" t="s">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="E374" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="F374" t="s">
         <v>1556</v>
       </c>
       <c r="G374" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H374" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I374" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J374" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K374" t="s">
         <v>1565</v>
       </c>
       <c r="L374" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="M374" t="s">
         <v>1566</v>
@@ -21522,31 +21522,31 @@
         <v>1163</v>
       </c>
       <c r="D375" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="E375" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="F375" t="s">
         <v>1556</v>
       </c>
       <c r="G375" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H375" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I375" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J375" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K375" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L375" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M375" t="s">
         <v>1566</v>
@@ -21566,34 +21566,34 @@
         <v>1164</v>
       </c>
       <c r="D376" t="s">
-        <v>1226</v>
+        <v>1312</v>
       </c>
       <c r="E376" t="s">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="F376" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G376" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H376" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I376" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="J376" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K376" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L376" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M376" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="N376" t="s">
         <v>1568</v>
@@ -21610,10 +21610,10 @@
         <v>1165</v>
       </c>
       <c r="D377" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E377" t="s">
-        <v>1500</v>
+        <v>1551</v>
       </c>
       <c r="F377" t="s">
         <v>1555</v>
@@ -21654,34 +21654,34 @@
         <v>1166</v>
       </c>
       <c r="D378" t="s">
-        <v>1363</v>
+        <v>1199</v>
       </c>
       <c r="E378" t="s">
-        <v>1551</v>
+        <v>1387</v>
       </c>
       <c r="F378" t="s">
         <v>1555</v>
       </c>
       <c r="G378" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H378" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I378" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J378" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K378" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L378" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M378" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="N378" t="s">
         <v>1568</v>
@@ -21698,31 +21698,31 @@
         <v>1167</v>
       </c>
       <c r="D379" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="E379" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F379" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G379" t="s">
         <v>1561</v>
       </c>
       <c r="H379" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I379" t="s">
         <v>1567</v>
       </c>
       <c r="J379" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K379" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L379" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M379" t="s">
         <v>1566</v>
@@ -21742,34 +21742,34 @@
         <v>1168</v>
       </c>
       <c r="D380" t="s">
-        <v>1211</v>
+        <v>1364</v>
       </c>
       <c r="E380" t="s">
-        <v>1399</v>
+        <v>1552</v>
       </c>
       <c r="F380" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G380" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H380" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I380" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J380" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K380" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L380" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M380" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N380" t="s">
         <v>1568</v>
@@ -21786,34 +21786,34 @@
         <v>1169</v>
       </c>
       <c r="D381" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E381" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F381" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G381" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H381" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I381" t="s">
         <v>1563</v>
       </c>
       <c r="J381" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K381" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L381" t="s">
         <v>1565</v>
       </c>
       <c r="M381" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N381" t="s">
         <v>1568</v>
@@ -21830,34 +21830,34 @@
         <v>1170</v>
       </c>
       <c r="D382" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E382" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F382" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G382" t="s">
         <v>1561</v>
       </c>
       <c r="H382" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I382" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J382" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K382" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L382" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M382" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N382" t="s">
         <v>1568</v>
@@ -21874,13 +21874,13 @@
         <v>1171</v>
       </c>
       <c r="D383" t="s">
-        <v>1366</v>
+        <v>1209</v>
       </c>
       <c r="E383" t="s">
-        <v>1554</v>
+        <v>1397</v>
       </c>
       <c r="F383" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G383" t="s">
         <v>1561</v>
@@ -21895,13 +21895,13 @@
         <v>1562</v>
       </c>
       <c r="K383" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L383" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M383" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N383" t="s">
         <v>1568</v>
@@ -21918,13 +21918,13 @@
         <v>1172</v>
       </c>
       <c r="D384" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="E384" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="F384" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G384" t="s">
         <v>1561</v>
@@ -21936,16 +21936,16 @@
         <v>1567</v>
       </c>
       <c r="J384" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K384" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L384" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M384" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N384" t="s">
         <v>1568</v>
@@ -21962,22 +21962,22 @@
         <v>1173</v>
       </c>
       <c r="D385" t="s">
-        <v>1191</v>
+        <v>1249</v>
       </c>
       <c r="E385" t="s">
-        <v>1379</v>
+        <v>1437</v>
       </c>
       <c r="F385" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G385" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H385" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="I385" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J385" t="s">
         <v>1563</v>
@@ -21986,10 +21986,10 @@
         <v>1565</v>
       </c>
       <c r="L385" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M385" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="N385" t="s">
         <v>1568</v>
@@ -22006,31 +22006,31 @@
         <v>1174</v>
       </c>
       <c r="D386" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="E386" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F386" t="s">
         <v>1556</v>
       </c>
       <c r="G386" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H386" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="I386" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J386" t="s">
         <v>1563</v>
       </c>
       <c r="K386" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L386" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M386" t="s">
         <v>1567</v>
@@ -22050,34 +22050,34 @@
         <v>1175</v>
       </c>
       <c r="D387" t="s">
-        <v>1255</v>
+        <v>1195</v>
       </c>
       <c r="E387" t="s">
-        <v>1443</v>
+        <v>1383</v>
       </c>
       <c r="F387" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G387" t="s">
         <v>1561</v>
       </c>
       <c r="H387" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I387" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J387" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K387" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L387" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M387" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="N387" t="s">
         <v>1568</v>
@@ -22094,34 +22094,34 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1195</v>
+        <v>1217</v>
       </c>
       <c r="E388" t="s">
-        <v>1383</v>
+        <v>1405</v>
       </c>
       <c r="F388" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G388" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H388" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I388" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J388" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K388" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L388" t="s">
         <v>1566</v>
       </c>
       <c r="M388" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N388" t="s">
         <v>1568</v>
@@ -22138,25 +22138,25 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1217</v>
+        <v>1340</v>
       </c>
       <c r="E389" t="s">
-        <v>1405</v>
+        <v>1528</v>
       </c>
       <c r="F389" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G389" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="H389" t="s">
         <v>1561</v>
       </c>
       <c r="I389" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J389" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K389" t="s">
         <v>1565</v>
@@ -22182,34 +22182,34 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1270</v>
+        <v>1303</v>
       </c>
       <c r="E390">
-        <v>63.5</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F390" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G390" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H390" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I390" t="s">
         <v>1567</v>
       </c>
       <c r="J390" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K390" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L390" t="s">
         <v>1566</v>
       </c>
       <c r="M390" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N390" t="s">
         <v>1568</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -886,345 +886,345 @@
     <t>أميمة رأفت محمود احمد</t>
   </si>
   <si>
+    <t>احمد رمضان محمد عبد الحميد</t>
+  </si>
+  <si>
+    <t>كريم محمد عبد الوهاب عيد</t>
+  </si>
+  <si>
+    <t>عمر رضا تونى طلبه</t>
+  </si>
+  <si>
+    <t>عبدالله ناصر أنور عبد المجيد</t>
+  </si>
+  <si>
+    <t>اندرو محروس مختار مهنى</t>
+  </si>
+  <si>
+    <t>فاطمه ناجى عبد السلام حسن</t>
+  </si>
+  <si>
+    <t>ماركو مجدى مكرم فريد</t>
+  </si>
+  <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
     <t>فاطمه طاهر عبد الحميد عبد العال</t>
   </si>
   <si>
-    <t>احمد رمضان محمد عبد الحميد</t>
-  </si>
-  <si>
-    <t>كريم محمد عبد الوهاب عيد</t>
-  </si>
-  <si>
-    <t>عمر رضا تونى طلبه</t>
-  </si>
-  <si>
-    <t>عبدالله ناصر أنور عبد المجيد</t>
-  </si>
-  <si>
-    <t>اندرو محروس مختار مهنى</t>
-  </si>
-  <si>
-    <t>فاطمه ناجى عبد السلام حسن</t>
-  </si>
-  <si>
-    <t>ماركو مجدى مكرم فريد</t>
-  </si>
-  <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2050,345 +2050,345 @@
     <t>30308062400144</t>
   </si>
   <si>
+    <t>30302142401658</t>
+  </si>
+  <si>
+    <t>30506272400259</t>
+  </si>
+  <si>
+    <t>30409012413599</t>
+  </si>
+  <si>
+    <t>30601162402453</t>
+  </si>
+  <si>
+    <t>30310012402973</t>
+  </si>
+  <si>
+    <t>30506170300209</t>
+  </si>
+  <si>
+    <t>30409172401791</t>
+  </si>
+  <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
     <t>30504252401205</t>
   </si>
   <si>
-    <t>30302142401658</t>
-  </si>
-  <si>
-    <t>30506272400259</t>
-  </si>
-  <si>
-    <t>30409012413599</t>
-  </si>
-  <si>
-    <t>30601162402453</t>
-  </si>
-  <si>
-    <t>30310012402973</t>
-  </si>
-  <si>
-    <t>30506170300209</t>
-  </si>
-  <si>
-    <t>30409172401791</t>
-  </si>
-  <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3214,9 +3214,6 @@
     <t>01121482192</t>
   </si>
   <si>
-    <t>1060458756</t>
-  </si>
-  <si>
     <t>01021408975</t>
   </si>
   <si>
@@ -3551,6 +3548,9 @@
   </si>
   <si>
     <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
   </si>
   <si>
     <t>1353</t>
@@ -17254,25 +17254,25 @@
         <v>1066</v>
       </c>
       <c r="D278" t="s">
-        <v>1191</v>
+        <v>1335</v>
       </c>
       <c r="E278" t="s">
-        <v>1379</v>
+        <v>1523</v>
       </c>
       <c r="F278" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G278" t="s">
         <v>1561</v>
       </c>
       <c r="H278" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I278" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J278" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K278" t="s">
         <v>1562</v>
@@ -17281,7 +17281,7 @@
         <v>1566</v>
       </c>
       <c r="M278" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N278" t="s">
         <v>1568</v>
@@ -17298,34 +17298,34 @@
         <v>1067</v>
       </c>
       <c r="D279" t="s">
-        <v>1335</v>
+        <v>1179</v>
       </c>
       <c r="E279" t="s">
-        <v>1523</v>
+        <v>1367</v>
       </c>
       <c r="F279" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G279" t="s">
         <v>1561</v>
       </c>
       <c r="H279" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="I279" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J279" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="K279" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L279" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M279" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="N279" t="s">
         <v>1568</v>
@@ -17342,34 +17342,34 @@
         <v>1068</v>
       </c>
       <c r="D280" t="s">
-        <v>1179</v>
+        <v>1278</v>
       </c>
       <c r="E280" t="s">
-        <v>1367</v>
+        <v>1466</v>
       </c>
       <c r="F280" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G280" t="s">
         <v>1561</v>
       </c>
       <c r="H280" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I280" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J280" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K280" t="s">
         <v>1565</v>
       </c>
       <c r="L280" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M280" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N280" t="s">
         <v>1568</v>
@@ -17386,22 +17386,22 @@
         <v>1069</v>
       </c>
       <c r="D281" t="s">
-        <v>1278</v>
+        <v>1256</v>
       </c>
       <c r="E281" t="s">
-        <v>1466</v>
+        <v>1444</v>
       </c>
       <c r="F281" t="s">
         <v>1555</v>
       </c>
       <c r="G281" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="H281" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I281" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J281" t="s">
         <v>1564</v>
@@ -17410,10 +17410,10 @@
         <v>1565</v>
       </c>
       <c r="L281" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="M281" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N281" t="s">
         <v>1568</v>
@@ -17430,34 +17430,34 @@
         <v>1070</v>
       </c>
       <c r="D282" t="s">
-        <v>1256</v>
+        <v>1228</v>
       </c>
       <c r="E282" t="s">
-        <v>1444</v>
+        <v>1416</v>
       </c>
       <c r="F282" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G282" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="H282" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I282" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J282" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K282" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L282" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M282" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N282" t="s">
         <v>1568</v>
@@ -17474,13 +17474,13 @@
         <v>1071</v>
       </c>
       <c r="D283" t="s">
-        <v>1228</v>
+        <v>1185</v>
       </c>
       <c r="E283" t="s">
-        <v>1416</v>
+        <v>1373</v>
       </c>
       <c r="F283" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G283" t="s">
         <v>1561</v>
@@ -17489,19 +17489,19 @@
         <v>1567</v>
       </c>
       <c r="I283" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J283" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K283" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L283" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M283" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N283" t="s">
         <v>1568</v>
@@ -17518,34 +17518,34 @@
         <v>1072</v>
       </c>
       <c r="D284" t="s">
-        <v>1185</v>
+        <v>1336</v>
       </c>
       <c r="E284" t="s">
-        <v>1373</v>
+        <v>1524</v>
       </c>
       <c r="F284" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G284" t="s">
         <v>1561</v>
       </c>
       <c r="H284" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I284" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J284" t="s">
         <v>1562</v>
       </c>
       <c r="K284" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L284" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M284" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N284" t="s">
         <v>1568</v>
@@ -17562,13 +17562,13 @@
         <v>1073</v>
       </c>
       <c r="D285" t="s">
-        <v>1336</v>
+        <v>1256</v>
       </c>
       <c r="E285" t="s">
-        <v>1524</v>
+        <v>1444</v>
       </c>
       <c r="F285" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G285" t="s">
         <v>1561</v>
@@ -17577,19 +17577,19 @@
         <v>1564</v>
       </c>
       <c r="I285" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J285" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K285" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L285" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M285" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N285" t="s">
         <v>1568</v>
@@ -17606,13 +17606,13 @@
         <v>1074</v>
       </c>
       <c r="D286" t="s">
-        <v>1256</v>
+        <v>1329</v>
       </c>
       <c r="E286" t="s">
-        <v>1444</v>
+        <v>1517</v>
       </c>
       <c r="F286" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G286" t="s">
         <v>1561</v>
@@ -17627,13 +17627,13 @@
         <v>1565</v>
       </c>
       <c r="K286" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L286" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M286" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N286" t="s">
         <v>1568</v>
@@ -17650,10 +17650,10 @@
         <v>1075</v>
       </c>
       <c r="D287" t="s">
-        <v>1329</v>
+        <v>1274</v>
       </c>
       <c r="E287" t="s">
-        <v>1517</v>
+        <v>1462</v>
       </c>
       <c r="F287" t="s">
         <v>1556</v>
@@ -17662,22 +17662,22 @@
         <v>1561</v>
       </c>
       <c r="H287" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I287" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J287" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K287" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L287" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M287" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N287" t="s">
         <v>1568</v>
@@ -17694,10 +17694,10 @@
         <v>1076</v>
       </c>
       <c r="D288" t="s">
-        <v>1274</v>
+        <v>1337</v>
       </c>
       <c r="E288" t="s">
-        <v>1462</v>
+        <v>1525</v>
       </c>
       <c r="F288" t="s">
         <v>1556</v>
@@ -17706,22 +17706,22 @@
         <v>1561</v>
       </c>
       <c r="H288" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="I288" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J288" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K288" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L288" t="s">
         <v>1565</v>
       </c>
       <c r="M288" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N288" t="s">
         <v>1568</v>
@@ -17738,25 +17738,25 @@
         <v>1077</v>
       </c>
       <c r="D289" t="s">
-        <v>1337</v>
+        <v>1211</v>
       </c>
       <c r="E289" t="s">
-        <v>1525</v>
+        <v>1399</v>
       </c>
       <c r="F289" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G289" t="s">
         <v>1561</v>
       </c>
       <c r="H289" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I289" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J289" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K289" t="s">
         <v>1566</v>
@@ -17765,7 +17765,7 @@
         <v>1565</v>
       </c>
       <c r="M289" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N289" t="s">
         <v>1568</v>
@@ -17782,13 +17782,13 @@
         <v>1078</v>
       </c>
       <c r="D290" t="s">
-        <v>1211</v>
+        <v>1284</v>
       </c>
       <c r="E290" t="s">
-        <v>1399</v>
+        <v>1472</v>
       </c>
       <c r="F290" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G290" t="s">
         <v>1561</v>
@@ -17826,19 +17826,19 @@
         <v>1079</v>
       </c>
       <c r="D291" t="s">
-        <v>1284</v>
+        <v>1179</v>
       </c>
       <c r="E291" t="s">
-        <v>1472</v>
+        <v>1367</v>
       </c>
       <c r="F291" t="s">
         <v>1555</v>
       </c>
       <c r="G291" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H291" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I291" t="s">
         <v>1567</v>
@@ -17847,13 +17847,13 @@
         <v>1562</v>
       </c>
       <c r="K291" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L291" t="s">
         <v>1565</v>
       </c>
       <c r="M291" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N291" t="s">
         <v>1568</v>
@@ -17870,34 +17870,34 @@
         <v>1080</v>
       </c>
       <c r="D292" t="s">
-        <v>1179</v>
+        <v>1194</v>
       </c>
       <c r="E292" t="s">
-        <v>1367</v>
+        <v>1382</v>
       </c>
       <c r="F292" t="s">
         <v>1555</v>
       </c>
       <c r="G292" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H292" t="s">
         <v>1561</v>
       </c>
       <c r="I292" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J292" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K292" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L292" t="s">
         <v>1565</v>
       </c>
       <c r="M292" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N292" t="s">
         <v>1568</v>
@@ -17914,34 +17914,34 @@
         <v>1081</v>
       </c>
       <c r="D293" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="E293" t="s">
-        <v>1382</v>
+        <v>1401</v>
       </c>
       <c r="F293" t="s">
         <v>1555</v>
       </c>
       <c r="G293" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H293" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I293" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J293" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K293" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L293" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M293" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N293" t="s">
         <v>1568</v>
@@ -17958,34 +17958,34 @@
         <v>1082</v>
       </c>
       <c r="D294" t="s">
-        <v>1213</v>
+        <v>1338</v>
       </c>
       <c r="E294" t="s">
-        <v>1401</v>
+        <v>1526</v>
       </c>
       <c r="F294" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G294" t="s">
         <v>1561</v>
       </c>
       <c r="H294" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I294" t="s">
         <v>1564</v>
       </c>
       <c r="J294" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K294" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L294" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M294" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N294" t="s">
         <v>1568</v>
@@ -18002,31 +18002,31 @@
         <v>1083</v>
       </c>
       <c r="D295" t="s">
-        <v>1338</v>
+        <v>1227</v>
       </c>
       <c r="E295" t="s">
-        <v>1526</v>
+        <v>1415</v>
       </c>
       <c r="F295" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G295" t="s">
         <v>1561</v>
       </c>
       <c r="H295" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I295" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J295" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K295" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L295" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M295" t="s">
         <v>1563</v>
@@ -18046,34 +18046,34 @@
         <v>1084</v>
       </c>
       <c r="D296" t="s">
-        <v>1227</v>
+        <v>1256</v>
       </c>
       <c r="E296" t="s">
-        <v>1415</v>
+        <v>1444</v>
       </c>
       <c r="F296" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G296" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="H296" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I296" t="s">
         <v>1566</v>
       </c>
       <c r="J296" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="K296" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L296" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M296" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N296" t="s">
         <v>1568</v>
@@ -18090,34 +18090,34 @@
         <v>1085</v>
       </c>
       <c r="D297" t="s">
-        <v>1256</v>
+        <v>1191</v>
       </c>
       <c r="E297" t="s">
-        <v>1444</v>
+        <v>1379</v>
       </c>
       <c r="F297" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G297" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H297" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I297" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J297" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K297" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L297" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M297" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N297" t="s">
         <v>1568</v>
@@ -18134,10 +18134,10 @@
         <v>1086</v>
       </c>
       <c r="D298" t="s">
-        <v>1191</v>
+        <v>1297</v>
       </c>
       <c r="E298" t="s">
-        <v>1379</v>
+        <v>1485</v>
       </c>
       <c r="F298" t="s">
         <v>1555</v>
@@ -18155,13 +18155,13 @@
         <v>1562</v>
       </c>
       <c r="K298" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L298" t="s">
         <v>1565</v>
       </c>
       <c r="M298" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N298" t="s">
         <v>1568</v>
@@ -18178,10 +18178,10 @@
         <v>1087</v>
       </c>
       <c r="D299" t="s">
-        <v>1297</v>
+        <v>1339</v>
       </c>
       <c r="E299" t="s">
-        <v>1485</v>
+        <v>1527</v>
       </c>
       <c r="F299" t="s">
         <v>1555</v>
@@ -18190,19 +18190,19 @@
         <v>1561</v>
       </c>
       <c r="H299" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I299" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J299" t="s">
         <v>1562</v>
       </c>
       <c r="K299" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L299" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M299" t="s">
         <v>1563</v>
@@ -18222,13 +18222,13 @@
         <v>1088</v>
       </c>
       <c r="D300" t="s">
-        <v>1339</v>
+        <v>1196</v>
       </c>
       <c r="E300" t="s">
-        <v>1527</v>
+        <v>1384</v>
       </c>
       <c r="F300" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G300" t="s">
         <v>1561</v>
@@ -18240,16 +18240,16 @@
         <v>1567</v>
       </c>
       <c r="J300" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K300" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L300" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M300" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N300" t="s">
         <v>1568</v>
@@ -18266,13 +18266,13 @@
         <v>1089</v>
       </c>
       <c r="D301" t="s">
-        <v>1196</v>
+        <v>1332</v>
       </c>
       <c r="E301" t="s">
-        <v>1384</v>
+        <v>1520</v>
       </c>
       <c r="F301" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G301" t="s">
         <v>1561</v>
@@ -18281,16 +18281,16 @@
         <v>1564</v>
       </c>
       <c r="I301" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J301" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K301" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L301" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M301" t="s">
         <v>1566</v>
@@ -18310,13 +18310,13 @@
         <v>1090</v>
       </c>
       <c r="D302" t="s">
-        <v>1332</v>
+        <v>1202</v>
       </c>
       <c r="E302" t="s">
-        <v>1520</v>
+        <v>1390</v>
       </c>
       <c r="F302" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G302" t="s">
         <v>1561</v>
@@ -18325,19 +18325,19 @@
         <v>1564</v>
       </c>
       <c r="I302" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J302" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K302" t="s">
         <v>1565</v>
       </c>
       <c r="L302" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M302" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N302" t="s">
         <v>1568</v>
@@ -18354,34 +18354,34 @@
         <v>1091</v>
       </c>
       <c r="D303" t="s">
-        <v>1202</v>
+        <v>1291</v>
       </c>
       <c r="E303" t="s">
-        <v>1390</v>
+        <v>1479</v>
       </c>
       <c r="F303" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G303" t="s">
         <v>1561</v>
       </c>
       <c r="H303" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I303" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J303" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K303" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L303" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M303" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N303" t="s">
         <v>1568</v>
@@ -18398,19 +18398,19 @@
         <v>1092</v>
       </c>
       <c r="D304" t="s">
-        <v>1291</v>
+        <v>1340</v>
       </c>
       <c r="E304" t="s">
-        <v>1479</v>
+        <v>1528</v>
       </c>
       <c r="F304" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G304" t="s">
         <v>1561</v>
       </c>
       <c r="H304" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I304" t="s">
         <v>1563</v>
@@ -18419,7 +18419,7 @@
         <v>1567</v>
       </c>
       <c r="K304" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L304" t="s">
         <v>1566</v>
@@ -18442,34 +18442,34 @@
         <v>1093</v>
       </c>
       <c r="D305" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E305" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F305" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G305" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H305" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I305" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J305" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="K305" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L305" t="s">
         <v>1566</v>
       </c>
       <c r="M305" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N305" t="s">
         <v>1568</v>
@@ -18486,34 +18486,34 @@
         <v>1094</v>
       </c>
       <c r="D306" t="s">
-        <v>1341</v>
+        <v>1211</v>
       </c>
       <c r="E306" t="s">
-        <v>1529</v>
+        <v>1399</v>
       </c>
       <c r="F306" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G306" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H306" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I306" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J306" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K306" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L306" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M306" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N306" t="s">
         <v>1568</v>
@@ -18530,31 +18530,31 @@
         <v>1095</v>
       </c>
       <c r="D307" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="E307" t="s">
-        <v>1399</v>
+        <v>1454</v>
       </c>
       <c r="F307" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G307" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H307" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I307" t="s">
         <v>1567</v>
       </c>
       <c r="J307" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K307" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="L307" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M307" t="s">
         <v>1563</v>
@@ -18574,28 +18574,28 @@
         <v>1096</v>
       </c>
       <c r="D308" t="s">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="E308" t="s">
-        <v>1454</v>
+        <v>1473</v>
       </c>
       <c r="F308" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G308" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H308" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I308" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J308" t="s">
         <v>1565</v>
       </c>
       <c r="K308" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L308" t="s">
         <v>1566</v>
@@ -18618,34 +18618,34 @@
         <v>1097</v>
       </c>
       <c r="D309" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="E309" t="s">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="F309" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G309" t="s">
         <v>1561</v>
       </c>
       <c r="H309" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I309" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J309" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K309" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L309" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M309" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N309" t="s">
         <v>1568</v>
@@ -18662,13 +18662,13 @@
         <v>1098</v>
       </c>
       <c r="D310" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="E310" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="F310" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G310" t="s">
         <v>1561</v>
@@ -18677,19 +18677,19 @@
         <v>1567</v>
       </c>
       <c r="I310" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J310" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K310" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L310" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M310" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N310" t="s">
         <v>1568</v>
@@ -18706,10 +18706,10 @@
         <v>1099</v>
       </c>
       <c r="D311" t="s">
-        <v>1318</v>
+        <v>1229</v>
       </c>
       <c r="E311" t="s">
-        <v>1506</v>
+        <v>1417</v>
       </c>
       <c r="F311" t="s">
         <v>1556</v>
@@ -18721,19 +18721,19 @@
         <v>1567</v>
       </c>
       <c r="I311" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J311" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K311" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L311" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M311" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N311" t="s">
         <v>1568</v>
@@ -18750,13 +18750,13 @@
         <v>1100</v>
       </c>
       <c r="D312" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="E312" t="s">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="F312" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G312" t="s">
         <v>1561</v>
@@ -18765,10 +18765,10 @@
         <v>1567</v>
       </c>
       <c r="I312" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J312" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K312" t="s">
         <v>1566</v>
@@ -18794,10 +18794,10 @@
         <v>1101</v>
       </c>
       <c r="D313" t="s">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="E313" t="s">
-        <v>1433</v>
+        <v>1530</v>
       </c>
       <c r="F313" t="s">
         <v>1555</v>
@@ -18806,22 +18806,22 @@
         <v>1561</v>
       </c>
       <c r="H313" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I313" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J313" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K313" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L313" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M313" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N313" t="s">
         <v>1568</v>
@@ -18838,34 +18838,34 @@
         <v>1102</v>
       </c>
       <c r="D314" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E314" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F314" t="s">
         <v>1555</v>
       </c>
       <c r="G314" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H314" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I314" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J314" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K314" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L314" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M314" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N314" t="s">
         <v>1568</v>
@@ -18882,10 +18882,10 @@
         <v>1103</v>
       </c>
       <c r="D315" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E315" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F315" t="s">
         <v>1555</v>
@@ -18926,34 +18926,34 @@
         <v>1104</v>
       </c>
       <c r="D316" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E316" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F316" t="s">
         <v>1555</v>
       </c>
       <c r="G316" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H316" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I316" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J316" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K316" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L316" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M316" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="N316" t="s">
         <v>1568</v>
@@ -18970,34 +18970,34 @@
         <v>1105</v>
       </c>
       <c r="D317" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E317" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F317" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G317" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H317" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I317" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J317" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K317" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L317" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M317" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N317" t="s">
         <v>1568</v>
@@ -19014,34 +19014,34 @@
         <v>1106</v>
       </c>
       <c r="D318" t="s">
-        <v>1346</v>
+        <v>1315</v>
       </c>
       <c r="E318" t="s">
-        <v>1534</v>
+        <v>1503</v>
       </c>
       <c r="F318" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G318" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H318" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I318" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J318" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K318" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L318" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M318" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N318" t="s">
         <v>1568</v>
@@ -19058,13 +19058,13 @@
         <v>1107</v>
       </c>
       <c r="D319" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="E319" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="F319" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G319" t="s">
         <v>1561</v>
@@ -19079,13 +19079,13 @@
         <v>1563</v>
       </c>
       <c r="K319" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L319" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M319" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N319" t="s">
         <v>1568</v>
@@ -19102,10 +19102,10 @@
         <v>1108</v>
       </c>
       <c r="D320" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
       <c r="E320" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F320" t="s">
         <v>1555</v>
@@ -19120,16 +19120,16 @@
         <v>1567</v>
       </c>
       <c r="J320" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K320" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L320" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M320" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N320" t="s">
         <v>1568</v>
@@ -19146,31 +19146,31 @@
         <v>1109</v>
       </c>
       <c r="D321" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E321" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F321" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G321" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H321" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I321" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J321" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K321" t="s">
         <v>1565</v>
       </c>
       <c r="L321" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M321" t="s">
         <v>1563</v>
@@ -19190,34 +19190,34 @@
         <v>1110</v>
       </c>
       <c r="D322" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="E322" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="F322" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G322" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H322" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I322" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J322" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K322" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L322" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M322" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N322" t="s">
         <v>1568</v>
@@ -19234,34 +19234,34 @@
         <v>1111</v>
       </c>
       <c r="D323" t="s">
-        <v>1314</v>
+        <v>1224</v>
       </c>
       <c r="E323" t="s">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="F323" t="s">
         <v>1556</v>
       </c>
       <c r="G323" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H323" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I323" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="J323" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K323" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L323" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M323" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="N323" t="s">
         <v>1568</v>
@@ -19278,34 +19278,34 @@
         <v>1112</v>
       </c>
       <c r="D324" t="s">
-        <v>1224</v>
+        <v>1262</v>
       </c>
       <c r="E324" t="s">
-        <v>1412</v>
+        <v>1450</v>
       </c>
       <c r="F324" t="s">
         <v>1556</v>
       </c>
       <c r="G324" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H324" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I324" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J324" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K324" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L324" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M324" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N324" t="s">
         <v>1568</v>
@@ -19322,34 +19322,34 @@
         <v>1113</v>
       </c>
       <c r="D325" t="s">
-        <v>1262</v>
+        <v>1291</v>
       </c>
       <c r="E325" t="s">
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="F325" t="s">
         <v>1556</v>
       </c>
       <c r="G325" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H325" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I325" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J325" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K325" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L325" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M325" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N325" t="s">
         <v>1568</v>
@@ -19366,34 +19366,34 @@
         <v>1114</v>
       </c>
       <c r="D326" t="s">
-        <v>1291</v>
+        <v>1262</v>
       </c>
       <c r="E326" t="s">
-        <v>1479</v>
+        <v>1450</v>
       </c>
       <c r="F326" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G326" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="H326" t="s">
         <v>1561</v>
       </c>
       <c r="I326" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J326" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K326" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L326" t="s">
         <v>1566</v>
       </c>
       <c r="M326" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N326" t="s">
         <v>1568</v>
@@ -19410,31 +19410,31 @@
         <v>1115</v>
       </c>
       <c r="D327" t="s">
-        <v>1262</v>
+        <v>1349</v>
       </c>
       <c r="E327" t="s">
-        <v>1450</v>
+        <v>1537</v>
       </c>
       <c r="F327" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G327" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H327" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I327" t="s">
         <v>1567</v>
       </c>
       <c r="J327" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K327" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L327" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M327" t="s">
         <v>1562</v>
@@ -19454,10 +19454,10 @@
         <v>1116</v>
       </c>
       <c r="D328" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E328" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F328" t="s">
         <v>1559</v>
@@ -19472,16 +19472,16 @@
         <v>1567</v>
       </c>
       <c r="J328" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K328" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L328" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M328" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N328" t="s">
         <v>1568</v>
@@ -19498,13 +19498,13 @@
         <v>1117</v>
       </c>
       <c r="D329" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E329" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F329" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G329" t="s">
         <v>1561</v>
@@ -19516,13 +19516,13 @@
         <v>1567</v>
       </c>
       <c r="J329" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K329" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L329" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M329" t="s">
         <v>1563</v>
@@ -19542,34 +19542,34 @@
         <v>1118</v>
       </c>
       <c r="D330" t="s">
-        <v>1351</v>
+        <v>1331</v>
       </c>
       <c r="E330" t="s">
-        <v>1539</v>
+        <v>1519</v>
       </c>
       <c r="F330" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G330" t="s">
         <v>1561</v>
       </c>
       <c r="H330" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I330" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J330" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K330" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L330" t="s">
         <v>1562</v>
       </c>
       <c r="M330" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N330" t="s">
         <v>1568</v>
@@ -19586,25 +19586,25 @@
         <v>1119</v>
       </c>
       <c r="D331" t="s">
-        <v>1331</v>
+        <v>1201</v>
       </c>
       <c r="E331" t="s">
-        <v>1519</v>
+        <v>1389</v>
       </c>
       <c r="F331" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G331" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H331" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I331" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J331" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K331" t="s">
         <v>1565</v>
@@ -19630,31 +19630,31 @@
         <v>1120</v>
       </c>
       <c r="D332" t="s">
-        <v>1201</v>
+        <v>1271</v>
       </c>
       <c r="E332" t="s">
-        <v>1389</v>
+        <v>1459</v>
       </c>
       <c r="F332" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G332" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H332" t="s">
         <v>1564</v>
       </c>
       <c r="I332" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J332" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K332" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L332" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M332" t="s">
         <v>1566</v>
@@ -19674,34 +19674,34 @@
         <v>1121</v>
       </c>
       <c r="D333" t="s">
-        <v>1271</v>
+        <v>1352</v>
       </c>
       <c r="E333" t="s">
-        <v>1459</v>
+        <v>1540</v>
       </c>
       <c r="F333" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G333" t="s">
         <v>1561</v>
       </c>
       <c r="H333" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I333" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J333" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K333" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L333" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M333" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N333" t="s">
         <v>1568</v>
@@ -19718,34 +19718,34 @@
         <v>1122</v>
       </c>
       <c r="D334" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E334" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F334" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G334" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H334" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I334" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J334" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K334" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L334" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M334" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N334" t="s">
         <v>1568</v>
@@ -19762,34 +19762,34 @@
         <v>1123</v>
       </c>
       <c r="D335" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E335" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F335" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G335" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H335" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I335" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J335" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K335" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L335" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M335" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N335" t="s">
         <v>1568</v>
@@ -19806,34 +19806,34 @@
         <v>1124</v>
       </c>
       <c r="D336" t="s">
-        <v>1354</v>
+        <v>1230</v>
       </c>
       <c r="E336" t="s">
-        <v>1542</v>
+        <v>1418</v>
       </c>
       <c r="F336" t="s">
         <v>1557</v>
       </c>
       <c r="G336" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="H336" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I336" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J336" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K336" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L336" t="s">
         <v>1566</v>
       </c>
       <c r="M336" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N336" t="s">
         <v>1568</v>
@@ -19850,10 +19850,10 @@
         <v>1125</v>
       </c>
       <c r="D337" t="s">
-        <v>1230</v>
+        <v>1355</v>
       </c>
       <c r="E337" t="s">
-        <v>1418</v>
+        <v>1543</v>
       </c>
       <c r="F337" t="s">
         <v>1557</v>
@@ -19862,13 +19862,13 @@
         <v>1562</v>
       </c>
       <c r="H337" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I337" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J337" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K337" t="s">
         <v>1567</v>
@@ -19877,7 +19877,7 @@
         <v>1566</v>
       </c>
       <c r="M337" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N337" t="s">
         <v>1568</v>
@@ -19894,34 +19894,34 @@
         <v>1126</v>
       </c>
       <c r="D338" t="s">
-        <v>1355</v>
+        <v>1196</v>
       </c>
       <c r="E338" t="s">
-        <v>1543</v>
+        <v>1384</v>
       </c>
       <c r="F338" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G338" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H338" t="s">
         <v>1561</v>
       </c>
       <c r="I338" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J338" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K338" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L338" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M338" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N338" t="s">
         <v>1568</v>
@@ -19938,34 +19938,34 @@
         <v>1127</v>
       </c>
       <c r="D339" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E339" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F339" t="s">
         <v>1555</v>
       </c>
       <c r="G339" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H339" t="s">
         <v>1561</v>
       </c>
       <c r="I339" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J339" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K339" t="s">
         <v>1565</v>
       </c>
       <c r="L339" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M339" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N339" t="s">
         <v>1568</v>
@@ -19982,34 +19982,34 @@
         <v>1128</v>
       </c>
       <c r="D340" t="s">
-        <v>1194</v>
+        <v>1329</v>
       </c>
       <c r="E340" t="s">
-        <v>1382</v>
+        <v>1517</v>
       </c>
       <c r="F340" t="s">
         <v>1555</v>
       </c>
       <c r="G340" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H340" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I340" t="s">
         <v>1564</v>
       </c>
       <c r="J340" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K340" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L340" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M340" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N340" t="s">
         <v>1568</v>
@@ -20026,34 +20026,34 @@
         <v>1129</v>
       </c>
       <c r="D341" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
       <c r="E341" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F341" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G341" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H341" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I341" t="s">
         <v>1564</v>
       </c>
       <c r="J341" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K341" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L341" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M341" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N341" t="s">
         <v>1568</v>
@@ -20070,34 +20070,34 @@
         <v>1130</v>
       </c>
       <c r="D342" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E342" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F342" t="s">
         <v>1556</v>
       </c>
       <c r="G342" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="H342" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="I342" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J342" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="K342" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L342" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M342" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N342" t="s">
         <v>1568</v>
@@ -20114,34 +20114,34 @@
         <v>1131</v>
       </c>
       <c r="D343" t="s">
-        <v>1357</v>
+        <v>1262</v>
       </c>
       <c r="E343" t="s">
-        <v>1545</v>
+        <v>1450</v>
       </c>
       <c r="F343" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G343" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H343" t="s">
         <v>1561</v>
       </c>
       <c r="I343" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="J343" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K343" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L343" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M343" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N343" t="s">
         <v>1568</v>
@@ -20158,28 +20158,28 @@
         <v>1132</v>
       </c>
       <c r="D344" t="s">
-        <v>1262</v>
+        <v>1227</v>
       </c>
       <c r="E344" t="s">
-        <v>1450</v>
+        <v>1415</v>
       </c>
       <c r="F344" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G344" t="s">
         <v>1565</v>
       </c>
       <c r="H344" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I344" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J344" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K344" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L344" t="s">
         <v>1562</v>
@@ -20202,31 +20202,31 @@
         <v>1133</v>
       </c>
       <c r="D345" t="s">
-        <v>1227</v>
+        <v>1303</v>
       </c>
       <c r="E345" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
       <c r="F345" t="s">
         <v>1556</v>
       </c>
       <c r="G345" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H345" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I345" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J345" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K345" t="s">
         <v>1563</v>
       </c>
       <c r="L345" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M345" t="s">
         <v>1566</v>
@@ -20246,31 +20246,31 @@
         <v>1134</v>
       </c>
       <c r="D346" t="s">
-        <v>1303</v>
+        <v>1358</v>
       </c>
       <c r="E346" t="s">
-        <v>1491</v>
+        <v>1546</v>
       </c>
       <c r="F346" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G346" t="s">
         <v>1561</v>
       </c>
       <c r="H346" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I346" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J346" t="s">
         <v>1562</v>
       </c>
       <c r="K346" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L346" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M346" t="s">
         <v>1566</v>
@@ -20290,13 +20290,13 @@
         <v>1135</v>
       </c>
       <c r="D347" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E347" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F347" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G347" t="s">
         <v>1561</v>
@@ -20308,16 +20308,16 @@
         <v>1567</v>
       </c>
       <c r="J347" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K347" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L347" t="s">
         <v>1563</v>
       </c>
       <c r="M347" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N347" t="s">
         <v>1568</v>
@@ -20334,13 +20334,13 @@
         <v>1136</v>
       </c>
       <c r="D348" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E348" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F348" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G348" t="s">
         <v>1561</v>
@@ -20352,16 +20352,16 @@
         <v>1567</v>
       </c>
       <c r="J348" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K348" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L348" t="s">
         <v>1563</v>
       </c>
       <c r="M348" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N348" t="s">
         <v>1568</v>
@@ -20378,31 +20378,31 @@
         <v>1137</v>
       </c>
       <c r="D349" t="s">
-        <v>1360</v>
+        <v>1225</v>
       </c>
       <c r="E349" t="s">
-        <v>1548</v>
+        <v>1413</v>
       </c>
       <c r="F349" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G349" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H349" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I349" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J349" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K349" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L349" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M349" t="s">
         <v>1566</v>
@@ -20422,34 +20422,34 @@
         <v>1138</v>
       </c>
       <c r="D350" t="s">
-        <v>1225</v>
+        <v>1361</v>
       </c>
       <c r="E350" t="s">
-        <v>1413</v>
+        <v>1549</v>
       </c>
       <c r="F350" t="s">
         <v>1556</v>
       </c>
       <c r="G350" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H350" t="s">
         <v>1562</v>
       </c>
       <c r="I350" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J350" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K350" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L350" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M350" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N350" t="s">
         <v>1568</v>
@@ -20466,13 +20466,13 @@
         <v>1139</v>
       </c>
       <c r="D351" t="s">
-        <v>1361</v>
+        <v>1203</v>
       </c>
       <c r="E351" t="s">
-        <v>1549</v>
+        <v>1391</v>
       </c>
       <c r="F351" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G351" t="s">
         <v>1561</v>
@@ -20481,16 +20481,16 @@
         <v>1562</v>
       </c>
       <c r="I351" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J351" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K351" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="L351" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M351" t="s">
         <v>1565</v>
@@ -20510,10 +20510,10 @@
         <v>1140</v>
       </c>
       <c r="D352" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E352" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F352" t="s">
         <v>1555</v>
@@ -20554,10 +20554,10 @@
         <v>1141</v>
       </c>
       <c r="D353" t="s">
-        <v>1205</v>
+        <v>1353</v>
       </c>
       <c r="E353" t="s">
-        <v>1393</v>
+        <v>1541</v>
       </c>
       <c r="F353" t="s">
         <v>1555</v>
@@ -20566,22 +20566,22 @@
         <v>1561</v>
       </c>
       <c r="H353" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="I353" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J353" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K353" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L353" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M353" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N353" t="s">
         <v>1568</v>
@@ -20598,34 +20598,34 @@
         <v>1142</v>
       </c>
       <c r="D354" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E354" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F354" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G354" t="s">
         <v>1561</v>
       </c>
       <c r="H354" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="I354" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J354" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K354" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L354" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M354" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N354" t="s">
         <v>1568</v>
@@ -20642,13 +20642,13 @@
         <v>1143</v>
       </c>
       <c r="D355" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="E355" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="F355" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G355" t="s">
         <v>1561</v>
@@ -20657,19 +20657,19 @@
         <v>1562</v>
       </c>
       <c r="I355" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J355" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K355" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L355" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M355" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N355" t="s">
         <v>1568</v>
@@ -20686,10 +20686,10 @@
         <v>1144</v>
       </c>
       <c r="D356" t="s">
-        <v>1362</v>
+        <v>1316</v>
       </c>
       <c r="E356" t="s">
-        <v>1550</v>
+        <v>1504</v>
       </c>
       <c r="F356" t="s">
         <v>1557</v>
@@ -20698,22 +20698,22 @@
         <v>1561</v>
       </c>
       <c r="H356" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I356" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J356" t="s">
         <v>1563</v>
       </c>
       <c r="K356" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L356" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M356" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N356" t="s">
         <v>1568</v>
@@ -20730,13 +20730,13 @@
         <v>1145</v>
       </c>
       <c r="D357" t="s">
-        <v>1316</v>
+        <v>1277</v>
       </c>
       <c r="E357" t="s">
-        <v>1504</v>
+        <v>1465</v>
       </c>
       <c r="F357" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G357" t="s">
         <v>1561</v>
@@ -20745,19 +20745,19 @@
         <v>1564</v>
       </c>
       <c r="I357" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J357" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K357" t="s">
         <v>1562</v>
       </c>
       <c r="L357" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M357" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N357" t="s">
         <v>1568</v>
@@ -20774,34 +20774,34 @@
         <v>1146</v>
       </c>
       <c r="D358" t="s">
-        <v>1277</v>
+        <v>1256</v>
       </c>
       <c r="E358" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="F358" t="s">
         <v>1556</v>
       </c>
       <c r="G358" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H358" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I358" t="s">
         <v>1565</v>
       </c>
       <c r="J358" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K358" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L358" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M358" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N358" t="s">
         <v>1568</v>
@@ -20818,34 +20818,34 @@
         <v>1147</v>
       </c>
       <c r="D359" t="s">
-        <v>1256</v>
+        <v>1216</v>
       </c>
       <c r="E359" t="s">
-        <v>1444</v>
+        <v>1404</v>
       </c>
       <c r="F359" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G359" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H359" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="I359" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J359" t="s">
         <v>1562</v>
       </c>
       <c r="K359" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L359" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M359" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="N359" t="s">
         <v>1568</v>
@@ -20862,34 +20862,34 @@
         <v>1148</v>
       </c>
       <c r="D360" t="s">
-        <v>1216</v>
+        <v>1334</v>
       </c>
       <c r="E360" t="s">
-        <v>1404</v>
+        <v>1522</v>
       </c>
       <c r="F360" t="s">
         <v>1555</v>
       </c>
       <c r="G360" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H360" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="I360" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J360" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K360" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L360" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M360" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="N360" t="s">
         <v>1568</v>
@@ -20906,10 +20906,10 @@
         <v>1149</v>
       </c>
       <c r="D361" t="s">
-        <v>1334</v>
+        <v>1280</v>
       </c>
       <c r="E361" t="s">
-        <v>1522</v>
+        <v>1468</v>
       </c>
       <c r="F361" t="s">
         <v>1555</v>
@@ -20921,16 +20921,16 @@
         <v>1564</v>
       </c>
       <c r="I361" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="J361" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K361" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L361" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M361" t="s">
         <v>1562</v>
@@ -20950,34 +20950,34 @@
         <v>1150</v>
       </c>
       <c r="D362" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="E362" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="F362" t="s">
         <v>1555</v>
       </c>
       <c r="G362" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H362" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I362" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J362" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K362" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L362" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M362" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N362" t="s">
         <v>1568</v>
@@ -20994,34 +20994,34 @@
         <v>1151</v>
       </c>
       <c r="D363" t="s">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="E363" t="s">
-        <v>1498</v>
+        <v>1453</v>
       </c>
       <c r="F363" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G363" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H363" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I363" t="s">
         <v>1561</v>
       </c>
       <c r="J363" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K363" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L363" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M363" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N363" t="s">
         <v>1568</v>
@@ -21038,34 +21038,34 @@
         <v>1152</v>
       </c>
       <c r="D364" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="E364" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="F364" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G364" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H364" t="s">
         <v>1564</v>
       </c>
       <c r="I364" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J364" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K364" t="s">
         <v>1565</v>
       </c>
       <c r="L364" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M364" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N364" t="s">
         <v>1568</v>
@@ -21082,34 +21082,34 @@
         <v>1153</v>
       </c>
       <c r="D365" t="s">
-        <v>1255</v>
+        <v>1203</v>
       </c>
       <c r="E365" t="s">
-        <v>1443</v>
+        <v>1391</v>
       </c>
       <c r="F365" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G365" t="s">
         <v>1561</v>
       </c>
       <c r="H365" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I365" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J365" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K365" t="s">
         <v>1565</v>
       </c>
       <c r="L365" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M365" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N365" t="s">
         <v>1568</v>
@@ -21126,34 +21126,34 @@
         <v>1154</v>
       </c>
       <c r="D366" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="E366" t="s">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="F366" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G366" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H366" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I366" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J366" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K366" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L366" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M366" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N366" t="s">
         <v>1568</v>
@@ -21170,34 +21170,34 @@
         <v>1155</v>
       </c>
       <c r="D367" t="s">
-        <v>1219</v>
+        <v>1267</v>
       </c>
       <c r="E367" t="s">
-        <v>1407</v>
+        <v>1455</v>
       </c>
       <c r="F367" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G367" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="H367" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I367" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J367" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K367" t="s">
         <v>1563</v>
       </c>
       <c r="L367" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M367" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N367" t="s">
         <v>1568</v>
@@ -21214,19 +21214,19 @@
         <v>1156</v>
       </c>
       <c r="D368" t="s">
-        <v>1267</v>
+        <v>1286</v>
       </c>
       <c r="E368" t="s">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F368" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G368" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H368" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I368" t="s">
         <v>1564</v>
@@ -21235,10 +21235,10 @@
         <v>1567</v>
       </c>
       <c r="K368" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L368" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M368" t="s">
         <v>1566</v>
@@ -21258,34 +21258,34 @@
         <v>1157</v>
       </c>
       <c r="D369" t="s">
-        <v>1286</v>
+        <v>1200</v>
       </c>
       <c r="E369" t="s">
-        <v>1474</v>
+        <v>1388</v>
       </c>
       <c r="F369" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G369" t="s">
         <v>1562</v>
       </c>
       <c r="H369" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I369" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J369" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K369" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L369" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M369" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N369" t="s">
         <v>1568</v>
@@ -21302,34 +21302,34 @@
         <v>1158</v>
       </c>
       <c r="D370" t="s">
-        <v>1200</v>
+        <v>1361</v>
       </c>
       <c r="E370" t="s">
-        <v>1388</v>
+        <v>1549</v>
       </c>
       <c r="F370" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G370" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H370" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I370" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J370" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K370" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="L370" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M370" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N370" t="s">
         <v>1568</v>
@@ -21346,34 +21346,34 @@
         <v>1159</v>
       </c>
       <c r="D371" t="s">
-        <v>1361</v>
+        <v>1246</v>
       </c>
       <c r="E371" t="s">
-        <v>1549</v>
+        <v>1434</v>
       </c>
       <c r="F371" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G371" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H371" t="s">
         <v>1564</v>
       </c>
       <c r="I371" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J371" t="s">
         <v>1563</v>
       </c>
       <c r="K371" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="L371" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M371" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N371" t="s">
         <v>1568</v>
@@ -21390,31 +21390,31 @@
         <v>1160</v>
       </c>
       <c r="D372" t="s">
-        <v>1246</v>
+        <v>1215</v>
       </c>
       <c r="E372" t="s">
-        <v>1434</v>
+        <v>1403</v>
       </c>
       <c r="F372" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G372" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H372" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I372" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J372" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K372" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L372" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M372" t="s">
         <v>1566</v>
@@ -21434,31 +21434,31 @@
         <v>1161</v>
       </c>
       <c r="D373" t="s">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="E373" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="F373" t="s">
         <v>1556</v>
       </c>
       <c r="G373" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H373" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I373" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J373" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K373" t="s">
         <v>1565</v>
       </c>
       <c r="L373" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="M373" t="s">
         <v>1566</v>
@@ -21478,31 +21478,31 @@
         <v>1162</v>
       </c>
       <c r="D374" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="E374" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="F374" t="s">
         <v>1556</v>
       </c>
       <c r="G374" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H374" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I374" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J374" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K374" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L374" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M374" t="s">
         <v>1566</v>
@@ -21522,34 +21522,34 @@
         <v>1163</v>
       </c>
       <c r="D375" t="s">
-        <v>1226</v>
+        <v>1312</v>
       </c>
       <c r="E375" t="s">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="F375" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G375" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H375" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I375" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="J375" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K375" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L375" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M375" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="N375" t="s">
         <v>1568</v>
@@ -21566,10 +21566,10 @@
         <v>1164</v>
       </c>
       <c r="D376" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E376" t="s">
-        <v>1500</v>
+        <v>1551</v>
       </c>
       <c r="F376" t="s">
         <v>1555</v>
@@ -21610,34 +21610,34 @@
         <v>1165</v>
       </c>
       <c r="D377" t="s">
-        <v>1363</v>
+        <v>1199</v>
       </c>
       <c r="E377" t="s">
-        <v>1551</v>
+        <v>1387</v>
       </c>
       <c r="F377" t="s">
         <v>1555</v>
       </c>
       <c r="G377" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H377" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I377" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J377" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K377" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L377" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M377" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="N377" t="s">
         <v>1568</v>
@@ -21654,31 +21654,31 @@
         <v>1166</v>
       </c>
       <c r="D378" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="E378" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F378" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G378" t="s">
         <v>1561</v>
       </c>
       <c r="H378" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I378" t="s">
         <v>1567</v>
       </c>
       <c r="J378" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K378" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L378" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M378" t="s">
         <v>1566</v>
@@ -21698,34 +21698,34 @@
         <v>1167</v>
       </c>
       <c r="D379" t="s">
-        <v>1211</v>
+        <v>1364</v>
       </c>
       <c r="E379" t="s">
-        <v>1399</v>
+        <v>1552</v>
       </c>
       <c r="F379" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G379" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H379" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I379" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J379" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K379" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L379" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M379" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N379" t="s">
         <v>1568</v>
@@ -21742,34 +21742,34 @@
         <v>1168</v>
       </c>
       <c r="D380" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E380" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F380" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G380" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H380" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I380" t="s">
         <v>1563</v>
       </c>
       <c r="J380" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K380" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L380" t="s">
         <v>1565</v>
       </c>
       <c r="M380" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N380" t="s">
         <v>1568</v>
@@ -21786,34 +21786,34 @@
         <v>1169</v>
       </c>
       <c r="D381" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E381" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F381" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G381" t="s">
         <v>1561</v>
       </c>
       <c r="H381" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I381" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J381" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K381" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L381" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M381" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N381" t="s">
         <v>1568</v>
@@ -21830,13 +21830,13 @@
         <v>1170</v>
       </c>
       <c r="D382" t="s">
-        <v>1366</v>
+        <v>1209</v>
       </c>
       <c r="E382" t="s">
-        <v>1554</v>
+        <v>1397</v>
       </c>
       <c r="F382" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G382" t="s">
         <v>1561</v>
@@ -21851,13 +21851,13 @@
         <v>1562</v>
       </c>
       <c r="K382" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L382" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M382" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N382" t="s">
         <v>1568</v>
@@ -21874,13 +21874,13 @@
         <v>1171</v>
       </c>
       <c r="D383" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="E383" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="F383" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G383" t="s">
         <v>1561</v>
@@ -21892,16 +21892,16 @@
         <v>1567</v>
       </c>
       <c r="J383" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K383" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L383" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M383" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N383" t="s">
         <v>1568</v>
@@ -21918,22 +21918,22 @@
         <v>1172</v>
       </c>
       <c r="D384" t="s">
-        <v>1191</v>
+        <v>1249</v>
       </c>
       <c r="E384" t="s">
-        <v>1379</v>
+        <v>1437</v>
       </c>
       <c r="F384" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G384" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H384" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="I384" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J384" t="s">
         <v>1563</v>
@@ -21942,10 +21942,10 @@
         <v>1565</v>
       </c>
       <c r="L384" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M384" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="N384" t="s">
         <v>1568</v>
@@ -21962,31 +21962,31 @@
         <v>1173</v>
       </c>
       <c r="D385" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="E385" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F385" t="s">
         <v>1556</v>
       </c>
       <c r="G385" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H385" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="I385" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J385" t="s">
         <v>1563</v>
       </c>
       <c r="K385" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L385" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M385" t="s">
         <v>1567</v>
@@ -22006,34 +22006,34 @@
         <v>1174</v>
       </c>
       <c r="D386" t="s">
-        <v>1255</v>
+        <v>1195</v>
       </c>
       <c r="E386" t="s">
-        <v>1443</v>
+        <v>1383</v>
       </c>
       <c r="F386" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G386" t="s">
         <v>1561</v>
       </c>
       <c r="H386" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I386" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J386" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K386" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L386" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M386" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="N386" t="s">
         <v>1568</v>
@@ -22050,34 +22050,34 @@
         <v>1175</v>
       </c>
       <c r="D387" t="s">
-        <v>1195</v>
+        <v>1217</v>
       </c>
       <c r="E387" t="s">
-        <v>1383</v>
+        <v>1405</v>
       </c>
       <c r="F387" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G387" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H387" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I387" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J387" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K387" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L387" t="s">
         <v>1566</v>
       </c>
       <c r="M387" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N387" t="s">
         <v>1568</v>
@@ -22094,25 +22094,25 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1217</v>
+        <v>1340</v>
       </c>
       <c r="E388" t="s">
-        <v>1405</v>
+        <v>1528</v>
       </c>
       <c r="F388" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G388" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="H388" t="s">
         <v>1561</v>
       </c>
       <c r="I388" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J388" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K388" t="s">
         <v>1565</v>
@@ -22138,34 +22138,34 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1340</v>
+        <v>1321</v>
       </c>
       <c r="E389" t="s">
-        <v>1528</v>
+        <v>1509</v>
       </c>
       <c r="F389" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G389" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H389" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I389" t="s">
         <v>1567</v>
       </c>
       <c r="J389" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K389" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L389" t="s">
         <v>1566</v>
       </c>
       <c r="M389" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N389" t="s">
         <v>1568</v>
@@ -22182,10 +22182,10 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1303</v>
+        <v>1360</v>
       </c>
       <c r="E390">
-        <v>65.15000000000001</v>
+        <v>68</v>
       </c>
       <c r="F390" t="s">
         <v>1556</v>
@@ -22194,13 +22194,13 @@
         <v>1561</v>
       </c>
       <c r="H390" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I390" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J390" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K390" t="s">
         <v>1562</v>
@@ -22209,7 +22209,7 @@
         <v>1566</v>
       </c>
       <c r="M390" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N390" t="s">
         <v>1568</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1216,15 +1216,15 @@
     <t>عمر احمد عبد الرحيم محمد</t>
   </si>
   <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
     <t>شروق محمد هاشم احمد</t>
   </si>
   <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2380,15 +2380,15 @@
     <t>30508192400552</t>
   </si>
   <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
     <t>30510302401007</t>
   </si>
   <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3544,13 +3544,13 @@
     <t>01067089320</t>
   </si>
   <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
     <t>01152380733</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
   </si>
   <si>
     <t>1353</t>
@@ -22094,34 +22094,34 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1340</v>
+        <v>1321</v>
       </c>
       <c r="E388" t="s">
-        <v>1528</v>
+        <v>1509</v>
       </c>
       <c r="F388" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G388" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H388" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I388" t="s">
         <v>1567</v>
       </c>
       <c r="J388" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K388" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L388" t="s">
         <v>1566</v>
       </c>
       <c r="M388" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N388" t="s">
         <v>1568</v>
@@ -22138,10 +22138,10 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1321</v>
+        <v>1191</v>
       </c>
       <c r="E389" t="s">
-        <v>1509</v>
+        <v>1379</v>
       </c>
       <c r="F389" t="s">
         <v>1556</v>
@@ -22150,13 +22150,13 @@
         <v>1561</v>
       </c>
       <c r="H389" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I389" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J389" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K389" t="s">
         <v>1562</v>
@@ -22165,7 +22165,7 @@
         <v>1566</v>
       </c>
       <c r="M389" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N389" t="s">
         <v>1568</v>
@@ -22182,28 +22182,28 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1360</v>
+        <v>1270</v>
       </c>
       <c r="E390">
-        <v>68</v>
+        <v>63.5</v>
       </c>
       <c r="F390" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G390" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H390" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="I390" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J390" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K390" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L390" t="s">
         <v>1566</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1219,12 +1219,12 @@
     <t>صالح عزت صالح عبد السيد</t>
   </si>
   <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
     <t>فاطمه طاهر عبد الحميد عبد العال</t>
   </si>
   <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>30209102406398</t>
   </si>
   <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
     <t>30504252401205</t>
   </si>
   <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3547,10 +3547,10 @@
     <t>01553863411</t>
   </si>
   <si>
+    <t>01152380733</t>
+  </si>
+  <si>
     <t>01060458756</t>
-  </si>
-  <si>
-    <t>01152380733</t>
   </si>
   <si>
     <t>1353</t>
@@ -22138,28 +22138,28 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1191</v>
+        <v>1340</v>
       </c>
       <c r="E389" t="s">
-        <v>1379</v>
+        <v>1528</v>
       </c>
       <c r="F389" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G389" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H389" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="I389" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J389" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K389" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L389" t="s">
         <v>1566</v>
@@ -22182,28 +22182,28 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1270</v>
+        <v>1360</v>
       </c>
       <c r="E390">
-        <v>63.5</v>
+        <v>68</v>
       </c>
       <c r="F390" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G390" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H390" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I390" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J390" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K390" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L390" t="s">
         <v>1566</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1219,12 +1219,12 @@
     <t>صالح عزت صالح عبد السيد</t>
   </si>
   <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
     <t>شروق محمد هاشم احمد</t>
   </si>
   <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2383,12 +2383,12 @@
     <t>30209102406398</t>
   </si>
   <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
     <t>30510302401007</t>
   </si>
   <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3547,10 +3547,10 @@
     <t>01553863411</t>
   </si>
   <si>
+    <t>01060458756</t>
+  </si>
+  <si>
     <t>01152380733</t>
-  </si>
-  <si>
-    <t>01060458756</t>
   </si>
   <si>
     <t>1353</t>
@@ -22138,28 +22138,28 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1340</v>
+        <v>1191</v>
       </c>
       <c r="E389" t="s">
-        <v>1528</v>
+        <v>1379</v>
       </c>
       <c r="F389" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G389" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H389" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I389" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J389" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K389" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L389" t="s">
         <v>1566</v>
@@ -22182,28 +22182,28 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1360</v>
+        <v>1270</v>
       </c>
       <c r="E390">
-        <v>68</v>
+        <v>63.5</v>
       </c>
       <c r="F390" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G390" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H390" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="I390" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J390" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K390" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L390" t="s">
         <v>1566</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -847,384 +847,384 @@
     <t>بهاء الدين محمد ابراهيم على</t>
   </si>
   <si>
+    <t>يوسف احمد سمير محمد</t>
+  </si>
+  <si>
+    <t>محمد رجب لطفى كامل</t>
+  </si>
+  <si>
+    <t>احمد طارق محمد محمود</t>
+  </si>
+  <si>
+    <t>عبدالله محمد سيد صادق</t>
+  </si>
+  <si>
+    <t>سهيله عبد القادر احمد عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد توفيق محمد محمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>مريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>شهد حسين محمود صابر</t>
+  </si>
+  <si>
+    <t>محمد سرحان محمد زكى</t>
+  </si>
+  <si>
+    <t>لمياء عبد القادر محمد فتحى</t>
+  </si>
+  <si>
+    <t>أميمة رأفت محمود احمد</t>
+  </si>
+  <si>
+    <t>احمد رمضان محمد عبد الحميد</t>
+  </si>
+  <si>
+    <t>كريم محمد عبد الوهاب عيد</t>
+  </si>
+  <si>
+    <t>عمر رضا تونى طلبه</t>
+  </si>
+  <si>
+    <t>عبدالله ناصر أنور عبد المجيد</t>
+  </si>
+  <si>
+    <t>اندرو محروس مختار مهنى</t>
+  </si>
+  <si>
+    <t>فاطمه ناجى عبد السلام حسن</t>
+  </si>
+  <si>
+    <t>ماركو مجدى مكرم فريد</t>
+  </si>
+  <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
     <t>اميره علاء جمال عبد الرازق</t>
   </si>
   <si>
-    <t>يوسف احمد سمير محمد</t>
-  </si>
-  <si>
-    <t>محمد رجب لطفى كامل</t>
-  </si>
-  <si>
-    <t>احمد طارق محمد محمود</t>
-  </si>
-  <si>
-    <t>عبدالله محمد سيد صادق</t>
-  </si>
-  <si>
-    <t>سهيله عبد القادر احمد عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد توفيق محمد محمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>مريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>شهد حسين محمود صابر</t>
-  </si>
-  <si>
-    <t>محمد سرحان محمد زكى</t>
-  </si>
-  <si>
-    <t>لمياء عبد القادر محمد فتحى</t>
-  </si>
-  <si>
-    <t>أميمة رأفت محمود احمد</t>
-  </si>
-  <si>
-    <t>احمد رمضان محمد عبد الحميد</t>
-  </si>
-  <si>
-    <t>كريم محمد عبد الوهاب عيد</t>
-  </si>
-  <si>
-    <t>عمر رضا تونى طلبه</t>
-  </si>
-  <si>
-    <t>عبدالله ناصر أنور عبد المجيد</t>
-  </si>
-  <si>
-    <t>اندرو محروس مختار مهنى</t>
-  </si>
-  <si>
-    <t>فاطمه ناجى عبد السلام حسن</t>
-  </si>
-  <si>
-    <t>ماركو مجدى مكرم فريد</t>
-  </si>
-  <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2011,384 +2011,384 @@
     <t>30506082400619</t>
   </si>
   <si>
+    <t>30503242401413</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
+  </si>
+  <si>
+    <t>30507262401954</t>
+  </si>
+  <si>
+    <t>30405262402457</t>
+  </si>
+  <si>
+    <t>30410312400403</t>
+  </si>
+  <si>
+    <t>30506152402932</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30509052401709</t>
+  </si>
+  <si>
+    <t>30408182401521</t>
+  </si>
+  <si>
+    <t>30410232401859</t>
+  </si>
+  <si>
+    <t>30409222402263</t>
+  </si>
+  <si>
+    <t>30308062400144</t>
+  </si>
+  <si>
+    <t>30302142401658</t>
+  </si>
+  <si>
+    <t>30506272400259</t>
+  </si>
+  <si>
+    <t>30409012413599</t>
+  </si>
+  <si>
+    <t>30601162402453</t>
+  </si>
+  <si>
+    <t>30310012402973</t>
+  </si>
+  <si>
+    <t>30506170300209</t>
+  </si>
+  <si>
+    <t>30409172401791</t>
+  </si>
+  <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
     <t>30512102404225</t>
   </si>
   <si>
-    <t>30503242401413</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
-  </si>
-  <si>
-    <t>30507262401954</t>
-  </si>
-  <si>
-    <t>30405262402457</t>
-  </si>
-  <si>
-    <t>30410312400403</t>
-  </si>
-  <si>
-    <t>30506152402932</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30509052401709</t>
-  </si>
-  <si>
-    <t>30408182401521</t>
-  </si>
-  <si>
-    <t>30410232401859</t>
-  </si>
-  <si>
-    <t>30409222402263</t>
-  </si>
-  <si>
-    <t>30308062400144</t>
-  </si>
-  <si>
-    <t>30302142401658</t>
-  </si>
-  <si>
-    <t>30506272400259</t>
-  </si>
-  <si>
-    <t>30409012413599</t>
-  </si>
-  <si>
-    <t>30601162402453</t>
-  </si>
-  <si>
-    <t>30310012402973</t>
-  </si>
-  <si>
-    <t>30506170300209</t>
-  </si>
-  <si>
-    <t>30409172401791</t>
-  </si>
-  <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3178,9 +3178,6 @@
     <t>01012467272</t>
   </si>
   <si>
-    <t>1010934419</t>
-  </si>
-  <si>
     <t>01005363873</t>
   </si>
   <si>
@@ -3551,6 +3548,9 @@
   </si>
   <si>
     <t>01152380733</t>
+  </si>
+  <si>
+    <t>01010934419</t>
   </si>
   <si>
     <t>1353</t>
@@ -16682,25 +16682,25 @@
         <v>1054</v>
       </c>
       <c r="D265" t="s">
-        <v>1246</v>
+        <v>1265</v>
       </c>
       <c r="E265" t="s">
-        <v>1434</v>
+        <v>1453</v>
       </c>
       <c r="F265" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G265" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H265" t="s">
         <v>1564</v>
       </c>
       <c r="I265" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J265" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K265" t="s">
         <v>1565</v>
@@ -16709,7 +16709,7 @@
         <v>1566</v>
       </c>
       <c r="M265" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N265" t="s">
         <v>1568</v>
@@ -16726,34 +16726,34 @@
         <v>1055</v>
       </c>
       <c r="D266" t="s">
-        <v>1265</v>
+        <v>1240</v>
       </c>
       <c r="E266" t="s">
-        <v>1453</v>
+        <v>1428</v>
       </c>
       <c r="F266" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G266" t="s">
         <v>1561</v>
       </c>
       <c r="H266" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I266" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J266" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K266" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L266" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M266" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N266" t="s">
         <v>1568</v>
@@ -16770,10 +16770,10 @@
         <v>1056</v>
       </c>
       <c r="D267" t="s">
-        <v>1240</v>
+        <v>1194</v>
       </c>
       <c r="E267" t="s">
-        <v>1428</v>
+        <v>1382</v>
       </c>
       <c r="F267" t="s">
         <v>1555</v>
@@ -16785,19 +16785,19 @@
         <v>1562</v>
       </c>
       <c r="I267" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J267" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K267" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L267" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M267" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N267" t="s">
         <v>1568</v>
@@ -16814,10 +16814,10 @@
         <v>1057</v>
       </c>
       <c r="D268" t="s">
-        <v>1194</v>
+        <v>1241</v>
       </c>
       <c r="E268" t="s">
-        <v>1382</v>
+        <v>1429</v>
       </c>
       <c r="F268" t="s">
         <v>1555</v>
@@ -16829,19 +16829,19 @@
         <v>1562</v>
       </c>
       <c r="I268" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J268" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K268" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L268" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M268" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N268" t="s">
         <v>1568</v>
@@ -16858,22 +16858,22 @@
         <v>1058</v>
       </c>
       <c r="D269" t="s">
-        <v>1241</v>
+        <v>1310</v>
       </c>
       <c r="E269" t="s">
-        <v>1429</v>
+        <v>1498</v>
       </c>
       <c r="F269" t="s">
         <v>1555</v>
       </c>
       <c r="G269" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H269" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I269" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J269" t="s">
         <v>1567</v>
@@ -16882,7 +16882,7 @@
         <v>1563</v>
       </c>
       <c r="L269" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M269" t="s">
         <v>1566</v>
@@ -16899,37 +16899,37 @@
         <v>670</v>
       </c>
       <c r="C270" t="s">
-        <v>1059</v>
+        <v>824</v>
       </c>
       <c r="D270" t="s">
-        <v>1310</v>
+        <v>1334</v>
       </c>
       <c r="E270" t="s">
-        <v>1498</v>
+        <v>1522</v>
       </c>
       <c r="F270" t="s">
         <v>1555</v>
       </c>
       <c r="G270" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H270" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I270" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J270" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K270" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L270" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M270" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N270" t="s">
         <v>1568</v>
@@ -16943,13 +16943,13 @@
         <v>671</v>
       </c>
       <c r="C271" t="s">
-        <v>824</v>
+        <v>1059</v>
       </c>
       <c r="D271" t="s">
-        <v>1334</v>
+        <v>1300</v>
       </c>
       <c r="E271" t="s">
-        <v>1522</v>
+        <v>1488</v>
       </c>
       <c r="F271" t="s">
         <v>1555</v>
@@ -16958,22 +16958,22 @@
         <v>1561</v>
       </c>
       <c r="H271" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I271" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J271" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K271" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L271" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M271" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N271" t="s">
         <v>1568</v>
@@ -16990,34 +16990,34 @@
         <v>1060</v>
       </c>
       <c r="D272" t="s">
-        <v>1300</v>
+        <v>1271</v>
       </c>
       <c r="E272" t="s">
-        <v>1488</v>
+        <v>1459</v>
       </c>
       <c r="F272" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G272" t="s">
         <v>1561</v>
       </c>
       <c r="H272" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I272" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J272" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K272" t="s">
         <v>1563</v>
       </c>
       <c r="L272" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M272" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N272" t="s">
         <v>1568</v>
@@ -17034,13 +17034,13 @@
         <v>1061</v>
       </c>
       <c r="D273" t="s">
-        <v>1271</v>
+        <v>1302</v>
       </c>
       <c r="E273" t="s">
-        <v>1459</v>
+        <v>1490</v>
       </c>
       <c r="F273" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G273" t="s">
         <v>1561</v>
@@ -17052,7 +17052,7 @@
         <v>1567</v>
       </c>
       <c r="J273" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="K273" t="s">
         <v>1563</v>
@@ -17061,7 +17061,7 @@
         <v>1562</v>
       </c>
       <c r="M273" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N273" t="s">
         <v>1568</v>
@@ -17078,10 +17078,10 @@
         <v>1062</v>
       </c>
       <c r="D274" t="s">
-        <v>1302</v>
+        <v>1206</v>
       </c>
       <c r="E274" t="s">
-        <v>1490</v>
+        <v>1394</v>
       </c>
       <c r="F274" t="s">
         <v>1555</v>
@@ -17096,13 +17096,13 @@
         <v>1567</v>
       </c>
       <c r="J274" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K274" t="s">
         <v>1563</v>
       </c>
       <c r="L274" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M274" t="s">
         <v>1566</v>
@@ -17122,10 +17122,10 @@
         <v>1063</v>
       </c>
       <c r="D275" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="E275" t="s">
-        <v>1394</v>
+        <v>1401</v>
       </c>
       <c r="F275" t="s">
         <v>1555</v>
@@ -17140,16 +17140,16 @@
         <v>1567</v>
       </c>
       <c r="J275" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K275" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L275" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M275" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N275" t="s">
         <v>1568</v>
@@ -17166,13 +17166,13 @@
         <v>1064</v>
       </c>
       <c r="D276" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E276" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="F276" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G276" t="s">
         <v>1561</v>
@@ -17181,19 +17181,19 @@
         <v>1564</v>
       </c>
       <c r="I276" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J276" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K276" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L276" t="s">
         <v>1562</v>
       </c>
       <c r="M276" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N276" t="s">
         <v>1568</v>
@@ -17210,34 +17210,34 @@
         <v>1065</v>
       </c>
       <c r="D277" t="s">
-        <v>1212</v>
+        <v>1335</v>
       </c>
       <c r="E277" t="s">
-        <v>1400</v>
+        <v>1523</v>
       </c>
       <c r="F277" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G277" t="s">
         <v>1561</v>
       </c>
       <c r="H277" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I277" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J277" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K277" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="L277" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M277" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N277" t="s">
         <v>1568</v>
@@ -17254,34 +17254,34 @@
         <v>1066</v>
       </c>
       <c r="D278" t="s">
-        <v>1335</v>
+        <v>1179</v>
       </c>
       <c r="E278" t="s">
-        <v>1523</v>
+        <v>1367</v>
       </c>
       <c r="F278" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G278" t="s">
         <v>1561</v>
       </c>
       <c r="H278" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="I278" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J278" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="K278" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L278" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M278" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="N278" t="s">
         <v>1568</v>
@@ -17298,34 +17298,34 @@
         <v>1067</v>
       </c>
       <c r="D279" t="s">
-        <v>1179</v>
+        <v>1278</v>
       </c>
       <c r="E279" t="s">
-        <v>1367</v>
+        <v>1466</v>
       </c>
       <c r="F279" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G279" t="s">
         <v>1561</v>
       </c>
       <c r="H279" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I279" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J279" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K279" t="s">
         <v>1565</v>
       </c>
       <c r="L279" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M279" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N279" t="s">
         <v>1568</v>
@@ -17342,22 +17342,22 @@
         <v>1068</v>
       </c>
       <c r="D280" t="s">
-        <v>1278</v>
+        <v>1256</v>
       </c>
       <c r="E280" t="s">
-        <v>1466</v>
+        <v>1444</v>
       </c>
       <c r="F280" t="s">
         <v>1555</v>
       </c>
       <c r="G280" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="H280" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I280" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J280" t="s">
         <v>1564</v>
@@ -17366,10 +17366,10 @@
         <v>1565</v>
       </c>
       <c r="L280" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="M280" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N280" t="s">
         <v>1568</v>
@@ -17386,34 +17386,34 @@
         <v>1069</v>
       </c>
       <c r="D281" t="s">
-        <v>1256</v>
+        <v>1228</v>
       </c>
       <c r="E281" t="s">
-        <v>1444</v>
+        <v>1416</v>
       </c>
       <c r="F281" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G281" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="H281" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I281" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J281" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K281" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L281" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M281" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N281" t="s">
         <v>1568</v>
@@ -17430,13 +17430,13 @@
         <v>1070</v>
       </c>
       <c r="D282" t="s">
-        <v>1228</v>
+        <v>1185</v>
       </c>
       <c r="E282" t="s">
-        <v>1416</v>
+        <v>1373</v>
       </c>
       <c r="F282" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G282" t="s">
         <v>1561</v>
@@ -17445,19 +17445,19 @@
         <v>1567</v>
       </c>
       <c r="I282" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J282" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K282" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L282" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M282" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N282" t="s">
         <v>1568</v>
@@ -17474,34 +17474,34 @@
         <v>1071</v>
       </c>
       <c r="D283" t="s">
-        <v>1185</v>
+        <v>1336</v>
       </c>
       <c r="E283" t="s">
-        <v>1373</v>
+        <v>1524</v>
       </c>
       <c r="F283" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G283" t="s">
         <v>1561</v>
       </c>
       <c r="H283" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I283" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J283" t="s">
         <v>1562</v>
       </c>
       <c r="K283" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L283" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M283" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N283" t="s">
         <v>1568</v>
@@ -17518,13 +17518,13 @@
         <v>1072</v>
       </c>
       <c r="D284" t="s">
-        <v>1336</v>
+        <v>1256</v>
       </c>
       <c r="E284" t="s">
-        <v>1524</v>
+        <v>1444</v>
       </c>
       <c r="F284" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G284" t="s">
         <v>1561</v>
@@ -17533,19 +17533,19 @@
         <v>1564</v>
       </c>
       <c r="I284" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J284" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K284" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L284" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M284" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N284" t="s">
         <v>1568</v>
@@ -17562,13 +17562,13 @@
         <v>1073</v>
       </c>
       <c r="D285" t="s">
-        <v>1256</v>
+        <v>1329</v>
       </c>
       <c r="E285" t="s">
-        <v>1444</v>
+        <v>1517</v>
       </c>
       <c r="F285" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G285" t="s">
         <v>1561</v>
@@ -17583,13 +17583,13 @@
         <v>1565</v>
       </c>
       <c r="K285" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L285" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M285" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N285" t="s">
         <v>1568</v>
@@ -17606,10 +17606,10 @@
         <v>1074</v>
       </c>
       <c r="D286" t="s">
-        <v>1329</v>
+        <v>1274</v>
       </c>
       <c r="E286" t="s">
-        <v>1517</v>
+        <v>1462</v>
       </c>
       <c r="F286" t="s">
         <v>1556</v>
@@ -17618,22 +17618,22 @@
         <v>1561</v>
       </c>
       <c r="H286" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I286" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J286" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K286" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L286" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M286" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N286" t="s">
         <v>1568</v>
@@ -17650,10 +17650,10 @@
         <v>1075</v>
       </c>
       <c r="D287" t="s">
-        <v>1274</v>
+        <v>1337</v>
       </c>
       <c r="E287" t="s">
-        <v>1462</v>
+        <v>1525</v>
       </c>
       <c r="F287" t="s">
         <v>1556</v>
@@ -17662,22 +17662,22 @@
         <v>1561</v>
       </c>
       <c r="H287" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="I287" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J287" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K287" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L287" t="s">
         <v>1565</v>
       </c>
       <c r="M287" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N287" t="s">
         <v>1568</v>
@@ -17694,25 +17694,25 @@
         <v>1076</v>
       </c>
       <c r="D288" t="s">
-        <v>1337</v>
+        <v>1211</v>
       </c>
       <c r="E288" t="s">
-        <v>1525</v>
+        <v>1399</v>
       </c>
       <c r="F288" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G288" t="s">
         <v>1561</v>
       </c>
       <c r="H288" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I288" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J288" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K288" t="s">
         <v>1566</v>
@@ -17721,7 +17721,7 @@
         <v>1565</v>
       </c>
       <c r="M288" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N288" t="s">
         <v>1568</v>
@@ -17738,13 +17738,13 @@
         <v>1077</v>
       </c>
       <c r="D289" t="s">
-        <v>1211</v>
+        <v>1284</v>
       </c>
       <c r="E289" t="s">
-        <v>1399</v>
+        <v>1472</v>
       </c>
       <c r="F289" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G289" t="s">
         <v>1561</v>
@@ -17782,19 +17782,19 @@
         <v>1078</v>
       </c>
       <c r="D290" t="s">
-        <v>1284</v>
+        <v>1179</v>
       </c>
       <c r="E290" t="s">
-        <v>1472</v>
+        <v>1367</v>
       </c>
       <c r="F290" t="s">
         <v>1555</v>
       </c>
       <c r="G290" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H290" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I290" t="s">
         <v>1567</v>
@@ -17803,13 +17803,13 @@
         <v>1562</v>
       </c>
       <c r="K290" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L290" t="s">
         <v>1565</v>
       </c>
       <c r="M290" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N290" t="s">
         <v>1568</v>
@@ -17826,34 +17826,34 @@
         <v>1079</v>
       </c>
       <c r="D291" t="s">
-        <v>1179</v>
+        <v>1194</v>
       </c>
       <c r="E291" t="s">
-        <v>1367</v>
+        <v>1382</v>
       </c>
       <c r="F291" t="s">
         <v>1555</v>
       </c>
       <c r="G291" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H291" t="s">
         <v>1561</v>
       </c>
       <c r="I291" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J291" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K291" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="L291" t="s">
         <v>1565</v>
       </c>
       <c r="M291" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N291" t="s">
         <v>1568</v>
@@ -17870,34 +17870,34 @@
         <v>1080</v>
       </c>
       <c r="D292" t="s">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="E292" t="s">
-        <v>1382</v>
+        <v>1401</v>
       </c>
       <c r="F292" t="s">
         <v>1555</v>
       </c>
       <c r="G292" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H292" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I292" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J292" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K292" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L292" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M292" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N292" t="s">
         <v>1568</v>
@@ -17914,34 +17914,34 @@
         <v>1081</v>
       </c>
       <c r="D293" t="s">
-        <v>1213</v>
+        <v>1338</v>
       </c>
       <c r="E293" t="s">
-        <v>1401</v>
+        <v>1526</v>
       </c>
       <c r="F293" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G293" t="s">
         <v>1561</v>
       </c>
       <c r="H293" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I293" t="s">
         <v>1564</v>
       </c>
       <c r="J293" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K293" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L293" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M293" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N293" t="s">
         <v>1568</v>
@@ -17958,31 +17958,31 @@
         <v>1082</v>
       </c>
       <c r="D294" t="s">
-        <v>1338</v>
+        <v>1227</v>
       </c>
       <c r="E294" t="s">
-        <v>1526</v>
+        <v>1415</v>
       </c>
       <c r="F294" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G294" t="s">
         <v>1561</v>
       </c>
       <c r="H294" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I294" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J294" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K294" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L294" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M294" t="s">
         <v>1563</v>
@@ -18002,34 +18002,34 @@
         <v>1083</v>
       </c>
       <c r="D295" t="s">
-        <v>1227</v>
+        <v>1256</v>
       </c>
       <c r="E295" t="s">
-        <v>1415</v>
+        <v>1444</v>
       </c>
       <c r="F295" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G295" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="H295" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I295" t="s">
         <v>1566</v>
       </c>
       <c r="J295" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="K295" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L295" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M295" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N295" t="s">
         <v>1568</v>
@@ -18046,34 +18046,34 @@
         <v>1084</v>
       </c>
       <c r="D296" t="s">
-        <v>1256</v>
+        <v>1191</v>
       </c>
       <c r="E296" t="s">
-        <v>1444</v>
+        <v>1379</v>
       </c>
       <c r="F296" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G296" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H296" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I296" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J296" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K296" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L296" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M296" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N296" t="s">
         <v>1568</v>
@@ -18090,10 +18090,10 @@
         <v>1085</v>
       </c>
       <c r="D297" t="s">
-        <v>1191</v>
+        <v>1297</v>
       </c>
       <c r="E297" t="s">
-        <v>1379</v>
+        <v>1485</v>
       </c>
       <c r="F297" t="s">
         <v>1555</v>
@@ -18111,13 +18111,13 @@
         <v>1562</v>
       </c>
       <c r="K297" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L297" t="s">
         <v>1565</v>
       </c>
       <c r="M297" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N297" t="s">
         <v>1568</v>
@@ -18134,10 +18134,10 @@
         <v>1086</v>
       </c>
       <c r="D298" t="s">
-        <v>1297</v>
+        <v>1339</v>
       </c>
       <c r="E298" t="s">
-        <v>1485</v>
+        <v>1527</v>
       </c>
       <c r="F298" t="s">
         <v>1555</v>
@@ -18146,19 +18146,19 @@
         <v>1561</v>
       </c>
       <c r="H298" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I298" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J298" t="s">
         <v>1562</v>
       </c>
       <c r="K298" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L298" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M298" t="s">
         <v>1563</v>
@@ -18178,13 +18178,13 @@
         <v>1087</v>
       </c>
       <c r="D299" t="s">
-        <v>1339</v>
+        <v>1196</v>
       </c>
       <c r="E299" t="s">
-        <v>1527</v>
+        <v>1384</v>
       </c>
       <c r="F299" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G299" t="s">
         <v>1561</v>
@@ -18196,16 +18196,16 @@
         <v>1567</v>
       </c>
       <c r="J299" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K299" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L299" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M299" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N299" t="s">
         <v>1568</v>
@@ -18222,13 +18222,13 @@
         <v>1088</v>
       </c>
       <c r="D300" t="s">
-        <v>1196</v>
+        <v>1332</v>
       </c>
       <c r="E300" t="s">
-        <v>1384</v>
+        <v>1520</v>
       </c>
       <c r="F300" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G300" t="s">
         <v>1561</v>
@@ -18237,16 +18237,16 @@
         <v>1564</v>
       </c>
       <c r="I300" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J300" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K300" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L300" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M300" t="s">
         <v>1566</v>
@@ -18266,13 +18266,13 @@
         <v>1089</v>
       </c>
       <c r="D301" t="s">
-        <v>1332</v>
+        <v>1202</v>
       </c>
       <c r="E301" t="s">
-        <v>1520</v>
+        <v>1390</v>
       </c>
       <c r="F301" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G301" t="s">
         <v>1561</v>
@@ -18281,19 +18281,19 @@
         <v>1564</v>
       </c>
       <c r="I301" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J301" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K301" t="s">
         <v>1565</v>
       </c>
       <c r="L301" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M301" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N301" t="s">
         <v>1568</v>
@@ -18310,34 +18310,34 @@
         <v>1090</v>
       </c>
       <c r="D302" t="s">
-        <v>1202</v>
+        <v>1291</v>
       </c>
       <c r="E302" t="s">
-        <v>1390</v>
+        <v>1479</v>
       </c>
       <c r="F302" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G302" t="s">
         <v>1561</v>
       </c>
       <c r="H302" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I302" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J302" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="K302" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L302" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M302" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N302" t="s">
         <v>1568</v>
@@ -18354,19 +18354,19 @@
         <v>1091</v>
       </c>
       <c r="D303" t="s">
-        <v>1291</v>
+        <v>1340</v>
       </c>
       <c r="E303" t="s">
-        <v>1479</v>
+        <v>1528</v>
       </c>
       <c r="F303" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G303" t="s">
         <v>1561</v>
       </c>
       <c r="H303" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I303" t="s">
         <v>1563</v>
@@ -18375,7 +18375,7 @@
         <v>1567</v>
       </c>
       <c r="K303" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L303" t="s">
         <v>1566</v>
@@ -18398,34 +18398,34 @@
         <v>1092</v>
       </c>
       <c r="D304" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E304" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="F304" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G304" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H304" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I304" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="J304" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="K304" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L304" t="s">
         <v>1566</v>
       </c>
       <c r="M304" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="N304" t="s">
         <v>1568</v>
@@ -18442,34 +18442,34 @@
         <v>1093</v>
       </c>
       <c r="D305" t="s">
-        <v>1341</v>
+        <v>1211</v>
       </c>
       <c r="E305" t="s">
-        <v>1529</v>
+        <v>1399</v>
       </c>
       <c r="F305" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G305" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H305" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I305" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J305" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K305" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L305" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M305" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="N305" t="s">
         <v>1568</v>
@@ -18486,31 +18486,31 @@
         <v>1094</v>
       </c>
       <c r="D306" t="s">
-        <v>1211</v>
+        <v>1266</v>
       </c>
       <c r="E306" t="s">
-        <v>1399</v>
+        <v>1454</v>
       </c>
       <c r="F306" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G306" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H306" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I306" t="s">
         <v>1567</v>
       </c>
       <c r="J306" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K306" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="L306" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M306" t="s">
         <v>1563</v>
@@ -18530,28 +18530,28 @@
         <v>1095</v>
       </c>
       <c r="D307" t="s">
-        <v>1266</v>
+        <v>1285</v>
       </c>
       <c r="E307" t="s">
-        <v>1454</v>
+        <v>1473</v>
       </c>
       <c r="F307" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G307" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H307" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="I307" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J307" t="s">
         <v>1565</v>
       </c>
       <c r="K307" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L307" t="s">
         <v>1566</v>
@@ -18574,34 +18574,34 @@
         <v>1096</v>
       </c>
       <c r="D308" t="s">
-        <v>1285</v>
+        <v>1297</v>
       </c>
       <c r="E308" t="s">
-        <v>1473</v>
+        <v>1485</v>
       </c>
       <c r="F308" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G308" t="s">
         <v>1561</v>
       </c>
       <c r="H308" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="I308" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J308" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K308" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L308" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M308" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N308" t="s">
         <v>1568</v>
@@ -18618,13 +18618,13 @@
         <v>1097</v>
       </c>
       <c r="D309" t="s">
-        <v>1297</v>
+        <v>1318</v>
       </c>
       <c r="E309" t="s">
-        <v>1485</v>
+        <v>1506</v>
       </c>
       <c r="F309" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G309" t="s">
         <v>1561</v>
@@ -18633,19 +18633,19 @@
         <v>1567</v>
       </c>
       <c r="I309" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J309" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K309" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L309" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M309" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N309" t="s">
         <v>1568</v>
@@ -18662,10 +18662,10 @@
         <v>1098</v>
       </c>
       <c r="D310" t="s">
-        <v>1318</v>
+        <v>1229</v>
       </c>
       <c r="E310" t="s">
-        <v>1506</v>
+        <v>1417</v>
       </c>
       <c r="F310" t="s">
         <v>1556</v>
@@ -18677,19 +18677,19 @@
         <v>1567</v>
       </c>
       <c r="I310" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J310" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K310" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L310" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M310" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N310" t="s">
         <v>1568</v>
@@ -18706,13 +18706,13 @@
         <v>1099</v>
       </c>
       <c r="D311" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="E311" t="s">
-        <v>1417</v>
+        <v>1433</v>
       </c>
       <c r="F311" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G311" t="s">
         <v>1561</v>
@@ -18721,10 +18721,10 @@
         <v>1567</v>
       </c>
       <c r="I311" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="J311" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K311" t="s">
         <v>1566</v>
@@ -18750,10 +18750,10 @@
         <v>1100</v>
       </c>
       <c r="D312" t="s">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="E312" t="s">
-        <v>1433</v>
+        <v>1530</v>
       </c>
       <c r="F312" t="s">
         <v>1555</v>
@@ -18762,22 +18762,22 @@
         <v>1561</v>
       </c>
       <c r="H312" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I312" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J312" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K312" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L312" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M312" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N312" t="s">
         <v>1568</v>
@@ -18794,34 +18794,34 @@
         <v>1101</v>
       </c>
       <c r="D313" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E313" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="F313" t="s">
         <v>1555</v>
       </c>
       <c r="G313" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H313" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I313" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J313" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K313" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L313" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M313" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N313" t="s">
         <v>1568</v>
@@ -18838,10 +18838,10 @@
         <v>1102</v>
       </c>
       <c r="D314" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="E314" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="F314" t="s">
         <v>1555</v>
@@ -18882,34 +18882,34 @@
         <v>1103</v>
       </c>
       <c r="D315" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E315" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="F315" t="s">
         <v>1555</v>
       </c>
       <c r="G315" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H315" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I315" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J315" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K315" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L315" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M315" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="N315" t="s">
         <v>1568</v>
@@ -18926,34 +18926,34 @@
         <v>1104</v>
       </c>
       <c r="D316" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E316" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="F316" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G316" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H316" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I316" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J316" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K316" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L316" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M316" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N316" t="s">
         <v>1568</v>
@@ -18970,34 +18970,34 @@
         <v>1105</v>
       </c>
       <c r="D317" t="s">
-        <v>1346</v>
+        <v>1315</v>
       </c>
       <c r="E317" t="s">
-        <v>1534</v>
+        <v>1503</v>
       </c>
       <c r="F317" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G317" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H317" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I317" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J317" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K317" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L317" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M317" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N317" t="s">
         <v>1568</v>
@@ -19014,13 +19014,13 @@
         <v>1106</v>
       </c>
       <c r="D318" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="E318" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="F318" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G318" t="s">
         <v>1561</v>
@@ -19035,13 +19035,13 @@
         <v>1563</v>
       </c>
       <c r="K318" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L318" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M318" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N318" t="s">
         <v>1568</v>
@@ -19058,10 +19058,10 @@
         <v>1107</v>
       </c>
       <c r="D319" t="s">
-        <v>1321</v>
+        <v>1347</v>
       </c>
       <c r="E319" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F319" t="s">
         <v>1555</v>
@@ -19076,16 +19076,16 @@
         <v>1567</v>
       </c>
       <c r="J319" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K319" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L319" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M319" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N319" t="s">
         <v>1568</v>
@@ -19102,31 +19102,31 @@
         <v>1108</v>
       </c>
       <c r="D320" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E320" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="F320" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G320" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H320" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I320" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J320" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="K320" t="s">
         <v>1565</v>
       </c>
       <c r="L320" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M320" t="s">
         <v>1563</v>
@@ -19146,34 +19146,34 @@
         <v>1109</v>
       </c>
       <c r="D321" t="s">
-        <v>1348</v>
+        <v>1314</v>
       </c>
       <c r="E321" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="F321" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G321" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="H321" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I321" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J321" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K321" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L321" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M321" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N321" t="s">
         <v>1568</v>
@@ -19190,34 +19190,34 @@
         <v>1110</v>
       </c>
       <c r="D322" t="s">
-        <v>1314</v>
+        <v>1224</v>
       </c>
       <c r="E322" t="s">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="F322" t="s">
         <v>1556</v>
       </c>
       <c r="G322" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H322" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I322" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="J322" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K322" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L322" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M322" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="N322" t="s">
         <v>1568</v>
@@ -19234,34 +19234,34 @@
         <v>1111</v>
       </c>
       <c r="D323" t="s">
-        <v>1224</v>
+        <v>1262</v>
       </c>
       <c r="E323" t="s">
-        <v>1412</v>
+        <v>1450</v>
       </c>
       <c r="F323" t="s">
         <v>1556</v>
       </c>
       <c r="G323" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H323" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I323" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J323" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K323" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L323" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="M323" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N323" t="s">
         <v>1568</v>
@@ -19278,34 +19278,34 @@
         <v>1112</v>
       </c>
       <c r="D324" t="s">
-        <v>1262</v>
+        <v>1291</v>
       </c>
       <c r="E324" t="s">
-        <v>1450</v>
+        <v>1479</v>
       </c>
       <c r="F324" t="s">
         <v>1556</v>
       </c>
       <c r="G324" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H324" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I324" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J324" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K324" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L324" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M324" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N324" t="s">
         <v>1568</v>
@@ -19322,34 +19322,34 @@
         <v>1113</v>
       </c>
       <c r="D325" t="s">
-        <v>1291</v>
+        <v>1262</v>
       </c>
       <c r="E325" t="s">
-        <v>1479</v>
+        <v>1450</v>
       </c>
       <c r="F325" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G325" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="H325" t="s">
         <v>1561</v>
       </c>
       <c r="I325" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J325" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K325" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L325" t="s">
         <v>1566</v>
       </c>
       <c r="M325" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="N325" t="s">
         <v>1568</v>
@@ -19366,31 +19366,31 @@
         <v>1114</v>
       </c>
       <c r="D326" t="s">
-        <v>1262</v>
+        <v>1349</v>
       </c>
       <c r="E326" t="s">
-        <v>1450</v>
+        <v>1537</v>
       </c>
       <c r="F326" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G326" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H326" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I326" t="s">
         <v>1567</v>
       </c>
       <c r="J326" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K326" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L326" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M326" t="s">
         <v>1562</v>
@@ -19410,10 +19410,10 @@
         <v>1115</v>
       </c>
       <c r="D327" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E327" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F327" t="s">
         <v>1559</v>
@@ -19428,16 +19428,16 @@
         <v>1567</v>
       </c>
       <c r="J327" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K327" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L327" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M327" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N327" t="s">
         <v>1568</v>
@@ -19454,13 +19454,13 @@
         <v>1116</v>
       </c>
       <c r="D328" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E328" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F328" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G328" t="s">
         <v>1561</v>
@@ -19472,13 +19472,13 @@
         <v>1567</v>
       </c>
       <c r="J328" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K328" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L328" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M328" t="s">
         <v>1563</v>
@@ -19498,34 +19498,34 @@
         <v>1117</v>
       </c>
       <c r="D329" t="s">
-        <v>1351</v>
+        <v>1331</v>
       </c>
       <c r="E329" t="s">
-        <v>1539</v>
+        <v>1519</v>
       </c>
       <c r="F329" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G329" t="s">
         <v>1561</v>
       </c>
       <c r="H329" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I329" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J329" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="K329" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L329" t="s">
         <v>1562</v>
       </c>
       <c r="M329" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N329" t="s">
         <v>1568</v>
@@ -19542,25 +19542,25 @@
         <v>1118</v>
       </c>
       <c r="D330" t="s">
-        <v>1331</v>
+        <v>1201</v>
       </c>
       <c r="E330" t="s">
-        <v>1519</v>
+        <v>1389</v>
       </c>
       <c r="F330" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G330" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H330" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I330" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J330" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K330" t="s">
         <v>1565</v>
@@ -19586,31 +19586,31 @@
         <v>1119</v>
       </c>
       <c r="D331" t="s">
-        <v>1201</v>
+        <v>1271</v>
       </c>
       <c r="E331" t="s">
-        <v>1389</v>
+        <v>1459</v>
       </c>
       <c r="F331" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G331" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H331" t="s">
         <v>1564</v>
       </c>
       <c r="I331" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J331" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K331" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L331" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M331" t="s">
         <v>1566</v>
@@ -19630,34 +19630,34 @@
         <v>1120</v>
       </c>
       <c r="D332" t="s">
-        <v>1271</v>
+        <v>1352</v>
       </c>
       <c r="E332" t="s">
-        <v>1459</v>
+        <v>1540</v>
       </c>
       <c r="F332" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G332" t="s">
         <v>1561</v>
       </c>
       <c r="H332" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I332" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J332" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K332" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L332" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M332" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N332" t="s">
         <v>1568</v>
@@ -19674,34 +19674,34 @@
         <v>1121</v>
       </c>
       <c r="D333" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E333" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="F333" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G333" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H333" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I333" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J333" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K333" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L333" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M333" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N333" t="s">
         <v>1568</v>
@@ -19718,34 +19718,34 @@
         <v>1122</v>
       </c>
       <c r="D334" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E334" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="F334" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G334" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H334" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I334" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J334" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K334" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L334" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="M334" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N334" t="s">
         <v>1568</v>
@@ -19762,34 +19762,34 @@
         <v>1123</v>
       </c>
       <c r="D335" t="s">
-        <v>1354</v>
+        <v>1230</v>
       </c>
       <c r="E335" t="s">
-        <v>1542</v>
+        <v>1418</v>
       </c>
       <c r="F335" t="s">
         <v>1557</v>
       </c>
       <c r="G335" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="H335" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="I335" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="J335" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K335" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L335" t="s">
         <v>1566</v>
       </c>
       <c r="M335" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N335" t="s">
         <v>1568</v>
@@ -19806,10 +19806,10 @@
         <v>1124</v>
       </c>
       <c r="D336" t="s">
-        <v>1230</v>
+        <v>1355</v>
       </c>
       <c r="E336" t="s">
-        <v>1418</v>
+        <v>1543</v>
       </c>
       <c r="F336" t="s">
         <v>1557</v>
@@ -19818,13 +19818,13 @@
         <v>1562</v>
       </c>
       <c r="H336" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I336" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J336" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K336" t="s">
         <v>1567</v>
@@ -19833,7 +19833,7 @@
         <v>1566</v>
       </c>
       <c r="M336" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N336" t="s">
         <v>1568</v>
@@ -19850,34 +19850,34 @@
         <v>1125</v>
       </c>
       <c r="D337" t="s">
-        <v>1355</v>
+        <v>1196</v>
       </c>
       <c r="E337" t="s">
-        <v>1543</v>
+        <v>1384</v>
       </c>
       <c r="F337" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G337" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H337" t="s">
         <v>1561</v>
       </c>
       <c r="I337" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J337" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="K337" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L337" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M337" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N337" t="s">
         <v>1568</v>
@@ -19894,34 +19894,34 @@
         <v>1126</v>
       </c>
       <c r="D338" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E338" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F338" t="s">
         <v>1555</v>
       </c>
       <c r="G338" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H338" t="s">
         <v>1561</v>
       </c>
       <c r="I338" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J338" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K338" t="s">
         <v>1565</v>
       </c>
       <c r="L338" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M338" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N338" t="s">
         <v>1568</v>
@@ -19938,34 +19938,34 @@
         <v>1127</v>
       </c>
       <c r="D339" t="s">
-        <v>1194</v>
+        <v>1329</v>
       </c>
       <c r="E339" t="s">
-        <v>1382</v>
+        <v>1517</v>
       </c>
       <c r="F339" t="s">
         <v>1555</v>
       </c>
       <c r="G339" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H339" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I339" t="s">
         <v>1564</v>
       </c>
       <c r="J339" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K339" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L339" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M339" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N339" t="s">
         <v>1568</v>
@@ -19982,34 +19982,34 @@
         <v>1128</v>
       </c>
       <c r="D340" t="s">
-        <v>1329</v>
+        <v>1356</v>
       </c>
       <c r="E340" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="F340" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G340" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H340" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I340" t="s">
         <v>1564</v>
       </c>
       <c r="J340" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K340" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L340" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="M340" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N340" t="s">
         <v>1568</v>
@@ -20026,34 +20026,34 @@
         <v>1129</v>
       </c>
       <c r="D341" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E341" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F341" t="s">
         <v>1556</v>
       </c>
       <c r="G341" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="H341" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="I341" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J341" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="K341" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L341" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="M341" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N341" t="s">
         <v>1568</v>
@@ -20070,34 +20070,34 @@
         <v>1130</v>
       </c>
       <c r="D342" t="s">
-        <v>1357</v>
+        <v>1262</v>
       </c>
       <c r="E342" t="s">
-        <v>1545</v>
+        <v>1450</v>
       </c>
       <c r="F342" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G342" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="H342" t="s">
         <v>1561</v>
       </c>
       <c r="I342" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="J342" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K342" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L342" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="M342" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N342" t="s">
         <v>1568</v>
@@ -20114,28 +20114,28 @@
         <v>1131</v>
       </c>
       <c r="D343" t="s">
-        <v>1262</v>
+        <v>1227</v>
       </c>
       <c r="E343" t="s">
-        <v>1450</v>
+        <v>1415</v>
       </c>
       <c r="F343" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G343" t="s">
         <v>1565</v>
       </c>
       <c r="H343" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I343" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J343" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="K343" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="L343" t="s">
         <v>1562</v>
@@ -20158,31 +20158,31 @@
         <v>1132</v>
       </c>
       <c r="D344" t="s">
-        <v>1227</v>
+        <v>1303</v>
       </c>
       <c r="E344" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
       <c r="F344" t="s">
         <v>1556</v>
       </c>
       <c r="G344" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H344" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I344" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J344" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="K344" t="s">
         <v>1563</v>
       </c>
       <c r="L344" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M344" t="s">
         <v>1566</v>
@@ -20202,31 +20202,31 @@
         <v>1133</v>
       </c>
       <c r="D345" t="s">
-        <v>1303</v>
+        <v>1358</v>
       </c>
       <c r="E345" t="s">
-        <v>1491</v>
+        <v>1546</v>
       </c>
       <c r="F345" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="G345" t="s">
         <v>1561</v>
       </c>
       <c r="H345" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I345" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J345" t="s">
         <v>1562</v>
       </c>
       <c r="K345" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L345" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M345" t="s">
         <v>1566</v>
@@ -20246,13 +20246,13 @@
         <v>1134</v>
       </c>
       <c r="D346" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E346" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F346" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G346" t="s">
         <v>1561</v>
@@ -20264,16 +20264,16 @@
         <v>1567</v>
       </c>
       <c r="J346" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K346" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L346" t="s">
         <v>1563</v>
       </c>
       <c r="M346" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N346" t="s">
         <v>1568</v>
@@ -20290,13 +20290,13 @@
         <v>1135</v>
       </c>
       <c r="D347" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E347" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F347" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="G347" t="s">
         <v>1561</v>
@@ -20308,16 +20308,16 @@
         <v>1567</v>
       </c>
       <c r="J347" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K347" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="L347" t="s">
         <v>1563</v>
       </c>
       <c r="M347" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="N347" t="s">
         <v>1568</v>
@@ -20334,31 +20334,31 @@
         <v>1136</v>
       </c>
       <c r="D348" t="s">
-        <v>1360</v>
+        <v>1225</v>
       </c>
       <c r="E348" t="s">
-        <v>1548</v>
+        <v>1413</v>
       </c>
       <c r="F348" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="G348" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="H348" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I348" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J348" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="K348" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L348" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M348" t="s">
         <v>1566</v>
@@ -20378,34 +20378,34 @@
         <v>1137</v>
       </c>
       <c r="D349" t="s">
-        <v>1225</v>
+        <v>1361</v>
       </c>
       <c r="E349" t="s">
-        <v>1413</v>
+        <v>1549</v>
       </c>
       <c r="F349" t="s">
         <v>1556</v>
       </c>
       <c r="G349" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H349" t="s">
         <v>1562</v>
       </c>
       <c r="I349" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J349" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="K349" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="L349" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M349" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N349" t="s">
         <v>1568</v>
@@ -20422,13 +20422,13 @@
         <v>1138</v>
       </c>
       <c r="D350" t="s">
-        <v>1361</v>
+        <v>1203</v>
       </c>
       <c r="E350" t="s">
-        <v>1549</v>
+        <v>1391</v>
       </c>
       <c r="F350" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G350" t="s">
         <v>1561</v>
@@ -20437,16 +20437,16 @@
         <v>1562</v>
       </c>
       <c r="I350" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J350" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="K350" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="L350" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="M350" t="s">
         <v>1565</v>
@@ -20466,10 +20466,10 @@
         <v>1139</v>
       </c>
       <c r="D351" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E351" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F351" t="s">
         <v>1555</v>
@@ -20510,10 +20510,10 @@
         <v>1140</v>
       </c>
       <c r="D352" t="s">
-        <v>1205</v>
+        <v>1353</v>
       </c>
       <c r="E352" t="s">
-        <v>1393</v>
+        <v>1541</v>
       </c>
       <c r="F352" t="s">
         <v>1555</v>
@@ -20522,22 +20522,22 @@
         <v>1561</v>
       </c>
       <c r="H352" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="I352" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J352" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K352" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="L352" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M352" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N352" t="s">
         <v>1568</v>
@@ -20554,34 +20554,34 @@
         <v>1141</v>
       </c>
       <c r="D353" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="E353" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F353" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G353" t="s">
         <v>1561</v>
       </c>
       <c r="H353" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="I353" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J353" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="K353" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="L353" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M353" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N353" t="s">
         <v>1568</v>
@@ -20598,13 +20598,13 @@
         <v>1142</v>
       </c>
       <c r="D354" t="s">
-        <v>1355</v>
+        <v>1362</v>
       </c>
       <c r="E354" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="F354" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G354" t="s">
         <v>1561</v>
@@ -20613,19 +20613,19 @@
         <v>1562</v>
       </c>
       <c r="I354" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="J354" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K354" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="L354" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M354" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N354" t="s">
         <v>1568</v>
@@ -20642,10 +20642,10 @@
         <v>1143</v>
       </c>
       <c r="D355" t="s">
-        <v>1362</v>
+        <v>1316</v>
       </c>
       <c r="E355" t="s">
-        <v>1550</v>
+        <v>1504</v>
       </c>
       <c r="F355" t="s">
         <v>1557</v>
@@ -20654,22 +20654,22 @@
         <v>1561</v>
       </c>
       <c r="H355" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I355" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J355" t="s">
         <v>1563</v>
       </c>
       <c r="K355" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="L355" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="M355" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N355" t="s">
         <v>1568</v>
@@ -20686,13 +20686,13 @@
         <v>1144</v>
       </c>
       <c r="D356" t="s">
-        <v>1316</v>
+        <v>1277</v>
       </c>
       <c r="E356" t="s">
-        <v>1504</v>
+        <v>1465</v>
       </c>
       <c r="F356" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G356" t="s">
         <v>1561</v>
@@ -20701,19 +20701,19 @@
         <v>1564</v>
       </c>
       <c r="I356" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J356" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K356" t="s">
         <v>1562</v>
       </c>
       <c r="L356" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M356" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N356" t="s">
         <v>1568</v>
@@ -20730,34 +20730,34 @@
         <v>1145</v>
       </c>
       <c r="D357" t="s">
-        <v>1277</v>
+        <v>1256</v>
       </c>
       <c r="E357" t="s">
-        <v>1465</v>
+        <v>1444</v>
       </c>
       <c r="F357" t="s">
         <v>1556</v>
       </c>
       <c r="G357" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H357" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I357" t="s">
         <v>1565</v>
       </c>
       <c r="J357" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K357" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="L357" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M357" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N357" t="s">
         <v>1568</v>
@@ -20774,34 +20774,34 @@
         <v>1146</v>
       </c>
       <c r="D358" t="s">
-        <v>1256</v>
+        <v>1216</v>
       </c>
       <c r="E358" t="s">
-        <v>1444</v>
+        <v>1404</v>
       </c>
       <c r="F358" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G358" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H358" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="I358" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J358" t="s">
         <v>1562</v>
       </c>
       <c r="K358" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L358" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M358" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="N358" t="s">
         <v>1568</v>
@@ -20818,34 +20818,34 @@
         <v>1147</v>
       </c>
       <c r="D359" t="s">
-        <v>1216</v>
+        <v>1334</v>
       </c>
       <c r="E359" t="s">
-        <v>1404</v>
+        <v>1522</v>
       </c>
       <c r="F359" t="s">
         <v>1555</v>
       </c>
       <c r="G359" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H359" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="I359" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J359" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K359" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L359" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M359" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="N359" t="s">
         <v>1568</v>
@@ -20862,10 +20862,10 @@
         <v>1148</v>
       </c>
       <c r="D360" t="s">
-        <v>1334</v>
+        <v>1280</v>
       </c>
       <c r="E360" t="s">
-        <v>1522</v>
+        <v>1468</v>
       </c>
       <c r="F360" t="s">
         <v>1555</v>
@@ -20877,16 +20877,16 @@
         <v>1564</v>
       </c>
       <c r="I360" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="J360" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="K360" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L360" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M360" t="s">
         <v>1562</v>
@@ -20906,34 +20906,34 @@
         <v>1149</v>
       </c>
       <c r="D361" t="s">
-        <v>1280</v>
+        <v>1310</v>
       </c>
       <c r="E361" t="s">
-        <v>1468</v>
+        <v>1498</v>
       </c>
       <c r="F361" t="s">
         <v>1555</v>
       </c>
       <c r="G361" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H361" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I361" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="J361" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K361" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L361" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M361" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N361" t="s">
         <v>1568</v>
@@ -20950,34 +20950,34 @@
         <v>1150</v>
       </c>
       <c r="D362" t="s">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="E362" t="s">
-        <v>1498</v>
+        <v>1453</v>
       </c>
       <c r="F362" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G362" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H362" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I362" t="s">
         <v>1561</v>
       </c>
       <c r="J362" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K362" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="L362" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="M362" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N362" t="s">
         <v>1568</v>
@@ -20994,34 +20994,34 @@
         <v>1151</v>
       </c>
       <c r="D363" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="E363" t="s">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="F363" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G363" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H363" t="s">
         <v>1564</v>
       </c>
       <c r="I363" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="J363" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K363" t="s">
         <v>1565</v>
       </c>
       <c r="L363" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M363" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N363" t="s">
         <v>1568</v>
@@ -21038,34 +21038,34 @@
         <v>1152</v>
       </c>
       <c r="D364" t="s">
-        <v>1255</v>
+        <v>1203</v>
       </c>
       <c r="E364" t="s">
-        <v>1443</v>
+        <v>1391</v>
       </c>
       <c r="F364" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G364" t="s">
         <v>1561</v>
       </c>
       <c r="H364" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I364" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J364" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K364" t="s">
         <v>1565</v>
       </c>
       <c r="L364" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M364" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N364" t="s">
         <v>1568</v>
@@ -21082,34 +21082,34 @@
         <v>1153</v>
       </c>
       <c r="D365" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="E365" t="s">
-        <v>1391</v>
+        <v>1407</v>
       </c>
       <c r="F365" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G365" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="H365" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I365" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J365" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="K365" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L365" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="M365" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="N365" t="s">
         <v>1568</v>
@@ -21126,34 +21126,34 @@
         <v>1154</v>
       </c>
       <c r="D366" t="s">
-        <v>1219</v>
+        <v>1267</v>
       </c>
       <c r="E366" t="s">
-        <v>1407</v>
+        <v>1455</v>
       </c>
       <c r="F366" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G366" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="H366" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I366" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J366" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K366" t="s">
         <v>1563</v>
       </c>
       <c r="L366" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M366" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="N366" t="s">
         <v>1568</v>
@@ -21170,19 +21170,19 @@
         <v>1155</v>
       </c>
       <c r="D367" t="s">
-        <v>1267</v>
+        <v>1286</v>
       </c>
       <c r="E367" t="s">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F367" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G367" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H367" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I367" t="s">
         <v>1564</v>
@@ -21191,10 +21191,10 @@
         <v>1567</v>
       </c>
       <c r="K367" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L367" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M367" t="s">
         <v>1566</v>
@@ -21214,34 +21214,34 @@
         <v>1156</v>
       </c>
       <c r="D368" t="s">
-        <v>1286</v>
+        <v>1200</v>
       </c>
       <c r="E368" t="s">
-        <v>1474</v>
+        <v>1388</v>
       </c>
       <c r="F368" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G368" t="s">
         <v>1562</v>
       </c>
       <c r="H368" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I368" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="J368" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="K368" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L368" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="M368" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N368" t="s">
         <v>1568</v>
@@ -21258,34 +21258,34 @@
         <v>1157</v>
       </c>
       <c r="D369" t="s">
-        <v>1200</v>
+        <v>1361</v>
       </c>
       <c r="E369" t="s">
-        <v>1388</v>
+        <v>1549</v>
       </c>
       <c r="F369" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G369" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="H369" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I369" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="J369" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K369" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="L369" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M369" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="N369" t="s">
         <v>1568</v>
@@ -21302,34 +21302,34 @@
         <v>1158</v>
       </c>
       <c r="D370" t="s">
-        <v>1361</v>
+        <v>1246</v>
       </c>
       <c r="E370" t="s">
-        <v>1549</v>
+        <v>1434</v>
       </c>
       <c r="F370" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G370" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="H370" t="s">
         <v>1564</v>
       </c>
       <c r="I370" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="J370" t="s">
         <v>1563</v>
       </c>
       <c r="K370" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="L370" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M370" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="N370" t="s">
         <v>1568</v>
@@ -21346,31 +21346,31 @@
         <v>1159</v>
       </c>
       <c r="D371" t="s">
-        <v>1246</v>
+        <v>1215</v>
       </c>
       <c r="E371" t="s">
-        <v>1434</v>
+        <v>1403</v>
       </c>
       <c r="F371" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G371" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H371" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I371" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J371" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K371" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L371" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="M371" t="s">
         <v>1566</v>
@@ -21390,31 +21390,31 @@
         <v>1160</v>
       </c>
       <c r="D372" t="s">
-        <v>1215</v>
+        <v>1259</v>
       </c>
       <c r="E372" t="s">
-        <v>1403</v>
+        <v>1447</v>
       </c>
       <c r="F372" t="s">
         <v>1556</v>
       </c>
       <c r="G372" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H372" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="I372" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="J372" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="K372" t="s">
         <v>1565</v>
       </c>
       <c r="L372" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="M372" t="s">
         <v>1566</v>
@@ -21434,31 +21434,31 @@
         <v>1161</v>
       </c>
       <c r="D373" t="s">
-        <v>1259</v>
+        <v>1226</v>
       </c>
       <c r="E373" t="s">
-        <v>1447</v>
+        <v>1414</v>
       </c>
       <c r="F373" t="s">
         <v>1556</v>
       </c>
       <c r="G373" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H373" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I373" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="J373" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="K373" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="L373" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="M373" t="s">
         <v>1566</v>
@@ -21478,34 +21478,34 @@
         <v>1162</v>
       </c>
       <c r="D374" t="s">
-        <v>1226</v>
+        <v>1312</v>
       </c>
       <c r="E374" t="s">
-        <v>1414</v>
+        <v>1500</v>
       </c>
       <c r="F374" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G374" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H374" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I374" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="J374" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="K374" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="L374" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="M374" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="N374" t="s">
         <v>1568</v>
@@ -21522,10 +21522,10 @@
         <v>1163</v>
       </c>
       <c r="D375" t="s">
-        <v>1312</v>
+        <v>1363</v>
       </c>
       <c r="E375" t="s">
-        <v>1500</v>
+        <v>1551</v>
       </c>
       <c r="F375" t="s">
         <v>1555</v>
@@ -21566,34 +21566,34 @@
         <v>1164</v>
       </c>
       <c r="D376" t="s">
-        <v>1363</v>
+        <v>1199</v>
       </c>
       <c r="E376" t="s">
-        <v>1551</v>
+        <v>1387</v>
       </c>
       <c r="F376" t="s">
         <v>1555</v>
       </c>
       <c r="G376" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H376" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="I376" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="J376" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="K376" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="L376" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="M376" t="s">
-        <v>1561</v>
+        <v>1566</v>
       </c>
       <c r="N376" t="s">
         <v>1568</v>
@@ -21610,31 +21610,31 @@
         <v>1165</v>
       </c>
       <c r="D377" t="s">
-        <v>1199</v>
+        <v>1211</v>
       </c>
       <c r="E377" t="s">
-        <v>1387</v>
+        <v>1399</v>
       </c>
       <c r="F377" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="G377" t="s">
         <v>1561</v>
       </c>
       <c r="H377" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="I377" t="s">
         <v>1567</v>
       </c>
       <c r="J377" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="K377" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="L377" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="M377" t="s">
         <v>1566</v>
@@ -21654,34 +21654,34 @@
         <v>1166</v>
       </c>
       <c r="D378" t="s">
-        <v>1211</v>
+        <v>1364</v>
       </c>
       <c r="E378" t="s">
-        <v>1399</v>
+        <v>1552</v>
       </c>
       <c r="F378" t="s">
-        <v>1559</v>
+        <v>1555</v>
       </c>
       <c r="G378" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H378" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="I378" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="J378" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="K378" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="L378" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="M378" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="N378" t="s">
         <v>1568</v>
@@ -21698,34 +21698,34 @@
         <v>1167</v>
       </c>
       <c r="D379" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E379" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F379" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="G379" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H379" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="I379" t="s">
         <v>1563</v>
       </c>
       <c r="J379" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="K379" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="L379" t="s">
         <v>1565</v>
       </c>
       <c r="M379" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="N379" t="s">
         <v>1568</v>
@@ -21742,34 +21742,34 @@
         <v>1168</v>
       </c>
       <c r="D380" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E380" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F380" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="G380" t="s">
         <v>1561</v>
       </c>
       <c r="H380" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="I380" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="J380" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="K380" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L380" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M380" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="N380" t="s">
         <v>1568</v>
@@ -21786,13 +21786,13 @@
         <v>1169</v>
       </c>
       <c r="D381" t="s">
-        <v>1366</v>
+        <v>1209</v>
       </c>
       <c r="E381" t="s">
-        <v>1554</v>
+        <v>1397</v>
       </c>
       <c r="F381" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="G381" t="s">
         <v>1561</v>
@@ -21807,13 +21807,13 @@
         <v>1562</v>
       </c>
       <c r="K381" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="L381" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="M381" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="N381" t="s">
         <v>1568</v>
@@ -21830,13 +21830,13 @@
         <v>1170</v>
       </c>
       <c r="D382" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="E382" t="s">
-        <v>1397</v>
+        <v>1379</v>
       </c>
       <c r="F382" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G382" t="s">
         <v>1561</v>
@@ -21848,16 +21848,16 @@
         <v>1567</v>
       </c>
       <c r="J382" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="K382" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L382" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M382" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="N382" t="s">
         <v>1568</v>
@@ -21874,22 +21874,22 @@
         <v>1171</v>
       </c>
       <c r="D383" t="s">
-        <v>1191</v>
+        <v>1249</v>
       </c>
       <c r="E383" t="s">
-        <v>1379</v>
+        <v>1437</v>
       </c>
       <c r="F383" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G383" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H383" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="I383" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J383" t="s">
         <v>1563</v>
@@ -21898,10 +21898,10 @@
         <v>1565</v>
       </c>
       <c r="L383" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M383" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="N383" t="s">
         <v>1568</v>
@@ -21918,31 +21918,31 @@
         <v>1172</v>
       </c>
       <c r="D384" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="E384" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="F384" t="s">
         <v>1556</v>
       </c>
       <c r="G384" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H384" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
       <c r="I384" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="J384" t="s">
         <v>1563</v>
       </c>
       <c r="K384" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="L384" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="M384" t="s">
         <v>1567</v>
@@ -21962,34 +21962,34 @@
         <v>1173</v>
       </c>
       <c r="D385" t="s">
-        <v>1255</v>
+        <v>1195</v>
       </c>
       <c r="E385" t="s">
-        <v>1443</v>
+        <v>1383</v>
       </c>
       <c r="F385" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G385" t="s">
         <v>1561</v>
       </c>
       <c r="H385" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="I385" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J385" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="K385" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="L385" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="M385" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="N385" t="s">
         <v>1568</v>
@@ -22006,34 +22006,34 @@
         <v>1174</v>
       </c>
       <c r="D386" t="s">
-        <v>1195</v>
+        <v>1217</v>
       </c>
       <c r="E386" t="s">
-        <v>1383</v>
+        <v>1405</v>
       </c>
       <c r="F386" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G386" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H386" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="I386" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J386" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K386" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="L386" t="s">
         <v>1566</v>
       </c>
       <c r="M386" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N386" t="s">
         <v>1568</v>
@@ -22050,34 +22050,34 @@
         <v>1175</v>
       </c>
       <c r="D387" t="s">
-        <v>1217</v>
+        <v>1321</v>
       </c>
       <c r="E387" t="s">
-        <v>1405</v>
+        <v>1509</v>
       </c>
       <c r="F387" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G387" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H387" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I387" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J387" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="K387" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="L387" t="s">
         <v>1566</v>
       </c>
       <c r="M387" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N387" t="s">
         <v>1568</v>
@@ -22094,10 +22094,10 @@
         <v>1176</v>
       </c>
       <c r="D388" t="s">
-        <v>1321</v>
+        <v>1191</v>
       </c>
       <c r="E388" t="s">
-        <v>1509</v>
+        <v>1379</v>
       </c>
       <c r="F388" t="s">
         <v>1556</v>
@@ -22106,13 +22106,13 @@
         <v>1561</v>
       </c>
       <c r="H388" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="I388" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J388" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K388" t="s">
         <v>1562</v>
@@ -22121,7 +22121,7 @@
         <v>1566</v>
       </c>
       <c r="M388" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="N388" t="s">
         <v>1568</v>
@@ -22138,28 +22138,28 @@
         <v>1177</v>
       </c>
       <c r="D389" t="s">
-        <v>1191</v>
+        <v>1340</v>
       </c>
       <c r="E389" t="s">
-        <v>1379</v>
+        <v>1528</v>
       </c>
       <c r="F389" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G389" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="H389" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="I389" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="J389" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="K389" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="L389" t="s">
         <v>1566</v>
@@ -22182,25 +22182,25 @@
         <v>1178</v>
       </c>
       <c r="D390">
-        <v>1270</v>
+        <v>1418</v>
       </c>
       <c r="E390">
-        <v>63.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F390" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G390" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="H390" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="I390" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="J390" t="s">
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="K390" t="s">
         <v>1565</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1222,12 +1222,12 @@
     <t>شرين احمد ابو بكر خلف</t>
   </si>
   <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
     <t>احمد جمال عبد الرحمن علي</t>
   </si>
   <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2389,12 +2389,12 @@
     <t>30509142400469</t>
   </si>
   <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
     <t>30312032402115</t>
   </si>
   <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3556,10 +3556,10 @@
     <t>01117927379</t>
   </si>
   <si>
+    <t>01279747878</t>
+  </si>
+  <si>
     <t>01116308543</t>
-  </si>
-  <si>
-    <t>01279747878</t>
   </si>
   <si>
     <t>1353</t>
@@ -22191,34 +22191,34 @@
         <v>1180</v>
       </c>
       <c r="D390" t="s">
-        <v>1216</v>
+        <v>1369</v>
       </c>
       <c r="E390" t="s">
-        <v>1404</v>
+        <v>1557</v>
       </c>
       <c r="F390" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="G390" t="s">
         <v>1564</v>
       </c>
       <c r="H390" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="I390" t="s">
         <v>1570</v>
       </c>
       <c r="J390" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K390" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L390" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M390" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="N390" t="s">
         <v>1571</v>
@@ -22235,34 +22235,34 @@
         <v>1181</v>
       </c>
       <c r="D391">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="E391">
-        <v>65.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F391" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="G391" t="s">
         <v>1564</v>
       </c>
       <c r="H391" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="I391" t="s">
         <v>1570</v>
       </c>
       <c r="J391" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K391" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L391" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="M391" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N391" t="s">
         <v>1571</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1222,12 +1222,12 @@
     <t>شرين احمد ابو بكر خلف</t>
   </si>
   <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
     <t>محمد اشرف محمد مختار اسماعيل</t>
   </si>
   <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2389,12 +2389,12 @@
     <t>30509142400469</t>
   </si>
   <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
     <t>30102232400732</t>
   </si>
   <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3556,10 +3556,10 @@
     <t>01117927379</t>
   </si>
   <si>
+    <t>01116308543</t>
+  </si>
+  <si>
     <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
   </si>
   <si>
     <t>1353</t>
@@ -22191,34 +22191,34 @@
         <v>1180</v>
       </c>
       <c r="D390" t="s">
-        <v>1369</v>
+        <v>1216</v>
       </c>
       <c r="E390" t="s">
-        <v>1557</v>
+        <v>1404</v>
       </c>
       <c r="F390" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="G390" t="s">
         <v>1564</v>
       </c>
       <c r="H390" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="I390" t="s">
         <v>1570</v>
       </c>
       <c r="J390" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K390" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="L390" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="M390" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="N390" t="s">
         <v>1571</v>
@@ -22235,34 +22235,34 @@
         <v>1181</v>
       </c>
       <c r="D391">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="E391">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="F391" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="G391" t="s">
         <v>1564</v>
       </c>
       <c r="H391" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="I391" t="s">
         <v>1570</v>
       </c>
       <c r="J391" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="K391" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="L391" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="M391" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="N391" t="s">
         <v>1571</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1060,183 +1060,183 @@
     <t>كريم علاء امين محمد</t>
   </si>
   <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
     <t>حازم بدر خلف خليفة</t>
   </si>
   <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2236,183 +2236,183 @@
     <t>30510252403755</t>
   </si>
   <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
     <t>30303072402097</t>
   </si>
   <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3412,183 +3412,183 @@
     <t>01003284398</t>
   </si>
   <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
     <t>01114113833</t>
   </si>
   <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
     <t>1353</t>
   </si>
   <si>
@@ -4120,9 +4120,6 @@
     <t>1272</t>
   </si>
   <si>
-    <t>1208</t>
-  </si>
-  <si>
     <t>1280</t>
   </si>
   <si>
@@ -4156,6 +4153,9 @@
     <t>1511</t>
   </si>
   <si>
+    <t>1136</t>
+  </si>
+  <si>
     <t>67.65</t>
   </si>
   <si>
@@ -4687,9 +4687,6 @@
     <t>63.6</t>
   </si>
   <si>
-    <t>60.4</t>
-  </si>
-  <si>
     <t>64</t>
   </si>
   <si>
@@ -4721,6 +4718,9 @@
   </si>
   <si>
     <t>75.55</t>
+  </si>
+  <si>
+    <t>56.8</t>
   </si>
   <si>
     <t>جيد</t>
@@ -19857,25 +19857,25 @@
         <v>1570</v>
       </c>
       <c r="G336" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="H336" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="I336" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="J336" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="K336" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L336" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="M336" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="N336" t="s">
         <v>1582</v>
@@ -19892,34 +19892,34 @@
         <v>1133</v>
       </c>
       <c r="D337" t="s">
-        <v>1369</v>
+        <v>1273</v>
       </c>
       <c r="E337" t="s">
-        <v>1558</v>
+        <v>1462</v>
       </c>
       <c r="F337" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="G337" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="H337" t="s">
         <v>1575</v>
       </c>
       <c r="I337" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="J337" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K337" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L337" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="M337" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="N337" t="s">
         <v>1582</v>
@@ -19936,28 +19936,28 @@
         <v>1134</v>
       </c>
       <c r="D338" t="s">
-        <v>1273</v>
+        <v>1238</v>
       </c>
       <c r="E338" t="s">
-        <v>1462</v>
+        <v>1427</v>
       </c>
       <c r="F338" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="G338" t="s">
         <v>1579</v>
       </c>
       <c r="H338" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="I338" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J338" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="K338" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="L338" t="s">
         <v>1576</v>
@@ -19980,31 +19980,31 @@
         <v>1135</v>
       </c>
       <c r="D339" t="s">
-        <v>1238</v>
+        <v>1314</v>
       </c>
       <c r="E339" t="s">
-        <v>1427</v>
+        <v>1503</v>
       </c>
       <c r="F339" t="s">
         <v>1570</v>
       </c>
       <c r="G339" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="H339" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="I339" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="J339" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="K339" t="s">
         <v>1577</v>
       </c>
       <c r="L339" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="M339" t="s">
         <v>1580</v>
@@ -20024,31 +20024,31 @@
         <v>1136</v>
       </c>
       <c r="D340" t="s">
-        <v>1314</v>
+        <v>1369</v>
       </c>
       <c r="E340" t="s">
-        <v>1503</v>
+        <v>1558</v>
       </c>
       <c r="F340" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="G340" t="s">
         <v>1575</v>
       </c>
       <c r="H340" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="I340" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J340" t="s">
         <v>1576</v>
       </c>
       <c r="K340" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L340" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="M340" t="s">
         <v>1580</v>
@@ -20074,7 +20074,7 @@
         <v>1559</v>
       </c>
       <c r="F341" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G341" t="s">
         <v>1575</v>
@@ -20086,16 +20086,16 @@
         <v>1581</v>
       </c>
       <c r="J341" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="K341" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="L341" t="s">
         <v>1577</v>
       </c>
       <c r="M341" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="N341" t="s">
         <v>1582</v>
@@ -20118,7 +20118,7 @@
         <v>1560</v>
       </c>
       <c r="F342" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G342" t="s">
         <v>1575</v>
@@ -20130,16 +20130,16 @@
         <v>1581</v>
       </c>
       <c r="J342" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="K342" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L342" t="s">
         <v>1577</v>
       </c>
       <c r="M342" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="N342" t="s">
         <v>1582</v>
@@ -20156,31 +20156,31 @@
         <v>1139</v>
       </c>
       <c r="D343" t="s">
-        <v>1372</v>
+        <v>1236</v>
       </c>
       <c r="E343" t="s">
-        <v>1561</v>
+        <v>1425</v>
       </c>
       <c r="F343" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="G343" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="H343" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="I343" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="J343" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="K343" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="L343" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="M343" t="s">
         <v>1580</v>
@@ -20200,34 +20200,34 @@
         <v>1140</v>
       </c>
       <c r="D344" t="s">
-        <v>1236</v>
+        <v>1372</v>
       </c>
       <c r="E344" t="s">
-        <v>1425</v>
+        <v>1561</v>
       </c>
       <c r="F344" t="s">
         <v>1570</v>
       </c>
       <c r="G344" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="H344" t="s">
         <v>1576</v>
       </c>
       <c r="I344" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="J344" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="K344" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="L344" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="M344" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="N344" t="s">
         <v>1582</v>
@@ -20244,13 +20244,13 @@
         <v>1141</v>
       </c>
       <c r="D345" t="s">
-        <v>1373</v>
+        <v>1214</v>
       </c>
       <c r="E345" t="s">
-        <v>1562</v>
+        <v>1403</v>
       </c>
       <c r="F345" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G345" t="s">
         <v>1575</v>
@@ -20259,16 +20259,16 @@
         <v>1576</v>
       </c>
       <c r="I345" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="J345" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K345" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="L345" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="M345" t="s">
         <v>1579</v>
@@ -20288,10 +20288,10 @@
         <v>1142</v>
       </c>
       <c r="D346" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E346" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="F346" t="s">
         <v>1569</v>
@@ -20332,10 +20332,10 @@
         <v>1143</v>
       </c>
       <c r="D347" t="s">
-        <v>1216</v>
+        <v>1365</v>
       </c>
       <c r="E347" t="s">
-        <v>1405</v>
+        <v>1554</v>
       </c>
       <c r="F347" t="s">
         <v>1569</v>
@@ -20344,22 +20344,22 @@
         <v>1575</v>
       </c>
       <c r="H347" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="I347" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="J347" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="K347" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="L347" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="M347" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="N347" t="s">
         <v>1582</v>
@@ -20376,34 +20376,34 @@
         <v>1144</v>
       </c>
       <c r="D348" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E348" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="F348" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="G348" t="s">
         <v>1575</v>
       </c>
       <c r="H348" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="I348" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="J348" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K348" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="L348" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="M348" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="N348" t="s">
         <v>1582</v>
@@ -20420,13 +20420,13 @@
         <v>1145</v>
       </c>
       <c r="D349" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="E349" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="F349" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G349" t="s">
         <v>1575</v>
@@ -20435,19 +20435,19 @@
         <v>1576</v>
       </c>
       <c r="I349" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="J349" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="K349" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="L349" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M349" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="N349" t="s">
         <v>1582</v>
@@ -20464,10 +20464,10 @@
         <v>1146</v>
       </c>
       <c r="D350" t="s">
-        <v>1374</v>
+        <v>1327</v>
       </c>
       <c r="E350" t="s">
-        <v>1563</v>
+        <v>1516</v>
       </c>
       <c r="F350" t="s">
         <v>1571</v>
@@ -20476,22 +20476,22 @@
         <v>1575</v>
       </c>
       <c r="H350" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="I350" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="J350" t="s">
         <v>1577</v>
       </c>
       <c r="K350" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="L350" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="M350" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="N350" t="s">
         <v>1582</v>
@@ -20508,13 +20508,13 @@
         <v>1147</v>
       </c>
       <c r="D351" t="s">
-        <v>1327</v>
+        <v>1288</v>
       </c>
       <c r="E351" t="s">
-        <v>1516</v>
+        <v>1477</v>
       </c>
       <c r="F351" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="G351" t="s">
         <v>1575</v>
@@ -20523,19 +20523,19 @@
         <v>1578</v>
       </c>
       <c r="I351" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="J351" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="K351" t="s">
         <v>1576</v>
       </c>
       <c r="L351" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="M351" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="N351" t="s">
         <v>1582</v>
@@ -20552,34 +20552,34 @@
         <v>1148</v>
       </c>
       <c r="D352" t="s">
-        <v>1288</v>
+        <v>1267</v>
       </c>
       <c r="E352" t="s">
-        <v>1477</v>
+        <v>1456</v>
       </c>
       <c r="F352" t="s">
         <v>1570</v>
       </c>
       <c r="G352" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="H352" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="I352" t="s">
         <v>1579</v>
       </c>
       <c r="J352" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="K352" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="L352" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="M352" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="N352" t="s">
         <v>1582</v>
@@ -20596,34 +20596,34 @@
         <v>1149</v>
       </c>
       <c r="D353" t="s">
-        <v>1267</v>
+        <v>1227</v>
       </c>
       <c r="E353" t="s">
-        <v>1456</v>
+        <v>1416</v>
       </c>
       <c r="F353" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G353" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H353" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="I353" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="J353" t="s">
         <v>1576</v>
       </c>
       <c r="K353" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L353" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="M353" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="N353" t="s">
         <v>1582</v>
@@ -20640,34 +20640,34 @@
         <v>1150</v>
       </c>
       <c r="D354" t="s">
-        <v>1227</v>
+        <v>1345</v>
       </c>
       <c r="E354" t="s">
-        <v>1416</v>
+        <v>1534</v>
       </c>
       <c r="F354" t="s">
         <v>1569</v>
       </c>
       <c r="G354" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="H354" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I354" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="J354" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K354" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="L354" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M354" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="N354" t="s">
         <v>1582</v>
@@ -20684,10 +20684,10 @@
         <v>1151</v>
       </c>
       <c r="D355" t="s">
-        <v>1345</v>
+        <v>1291</v>
       </c>
       <c r="E355" t="s">
-        <v>1534</v>
+        <v>1480</v>
       </c>
       <c r="F355" t="s">
         <v>1569</v>
@@ -20699,16 +20699,16 @@
         <v>1578</v>
       </c>
       <c r="I355" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J355" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="K355" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="L355" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="M355" t="s">
         <v>1576</v>
@@ -20728,34 +20728,34 @@
         <v>1152</v>
       </c>
       <c r="D356" t="s">
-        <v>1291</v>
+        <v>1276</v>
       </c>
       <c r="E356" t="s">
-        <v>1480</v>
+        <v>1465</v>
       </c>
       <c r="F356" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="G356" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H356" t="s">
         <v>1578</v>
       </c>
       <c r="I356" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="J356" t="s">
         <v>1581</v>
       </c>
       <c r="K356" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L356" t="s">
         <v>1577</v>
       </c>
       <c r="M356" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="N356" t="s">
         <v>1582</v>
@@ -20772,34 +20772,34 @@
         <v>1153</v>
       </c>
       <c r="D357" t="s">
-        <v>1276</v>
+        <v>1266</v>
       </c>
       <c r="E357" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="F357" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G357" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H357" t="s">
         <v>1578</v>
       </c>
       <c r="I357" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="J357" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="K357" t="s">
         <v>1579</v>
       </c>
       <c r="L357" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="M357" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="N357" t="s">
         <v>1582</v>
@@ -20816,34 +20816,34 @@
         <v>1154</v>
       </c>
       <c r="D358" t="s">
-        <v>1266</v>
+        <v>1214</v>
       </c>
       <c r="E358" t="s">
-        <v>1455</v>
+        <v>1403</v>
       </c>
       <c r="F358" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="G358" t="s">
         <v>1575</v>
       </c>
       <c r="H358" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="I358" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="J358" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="K358" t="s">
         <v>1579</v>
       </c>
       <c r="L358" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="M358" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="N358" t="s">
         <v>1582</v>
@@ -20860,34 +20860,34 @@
         <v>1155</v>
       </c>
       <c r="D359" t="s">
-        <v>1214</v>
+        <v>1230</v>
       </c>
       <c r="E359" t="s">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="F359" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="G359" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="H359" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="I359" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="J359" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="K359" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="L359" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="M359" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="N359" t="s">
         <v>1582</v>
@@ -20904,34 +20904,34 @@
         <v>1156</v>
       </c>
       <c r="D360" t="s">
-        <v>1230</v>
+        <v>1278</v>
       </c>
       <c r="E360" t="s">
-        <v>1419</v>
+        <v>1467</v>
       </c>
       <c r="F360" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="G360" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="H360" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="I360" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="J360" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="K360" t="s">
         <v>1577</v>
       </c>
       <c r="L360" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="M360" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="N360" t="s">
         <v>1582</v>
@@ -20948,19 +20948,19 @@
         <v>1157</v>
       </c>
       <c r="D361" t="s">
-        <v>1278</v>
+        <v>1297</v>
       </c>
       <c r="E361" t="s">
-        <v>1467</v>
+        <v>1486</v>
       </c>
       <c r="F361" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="G361" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H361" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="I361" t="s">
         <v>1578</v>
@@ -20969,10 +20969,10 @@
         <v>1581</v>
       </c>
       <c r="K361" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L361" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="M361" t="s">
         <v>1580</v>
@@ -20992,34 +20992,34 @@
         <v>1158</v>
       </c>
       <c r="D362" t="s">
-        <v>1297</v>
+        <v>1211</v>
       </c>
       <c r="E362" t="s">
-        <v>1486</v>
+        <v>1400</v>
       </c>
       <c r="F362" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="G362" t="s">
         <v>1576</v>
       </c>
       <c r="H362" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="I362" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="J362" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K362" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="L362" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="M362" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="N362" t="s">
         <v>1582</v>
@@ -21036,34 +21036,34 @@
         <v>1159</v>
       </c>
       <c r="D363" t="s">
-        <v>1211</v>
+        <v>1372</v>
       </c>
       <c r="E363" t="s">
-        <v>1400</v>
+        <v>1561</v>
       </c>
       <c r="F363" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="G363" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="H363" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="I363" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="J363" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K363" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="L363" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="M363" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="N363" t="s">
         <v>1582</v>
@@ -21080,34 +21080,34 @@
         <v>1160</v>
       </c>
       <c r="D364" t="s">
-        <v>1373</v>
+        <v>1257</v>
       </c>
       <c r="E364" t="s">
-        <v>1562</v>
+        <v>1446</v>
       </c>
       <c r="F364" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G364" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="H364" t="s">
         <v>1578</v>
       </c>
       <c r="I364" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="J364" t="s">
         <v>1577</v>
       </c>
       <c r="K364" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="L364" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="M364" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="N364" t="s">
         <v>1582</v>
@@ -21124,31 +21124,31 @@
         <v>1161</v>
       </c>
       <c r="D365" t="s">
-        <v>1257</v>
+        <v>1226</v>
       </c>
       <c r="E365" t="s">
-        <v>1446</v>
+        <v>1415</v>
       </c>
       <c r="F365" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="G365" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="H365" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="I365" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="J365" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="K365" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="L365" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="M365" t="s">
         <v>1580</v>
@@ -21168,31 +21168,31 @@
         <v>1162</v>
       </c>
       <c r="D366" t="s">
-        <v>1226</v>
+        <v>1270</v>
       </c>
       <c r="E366" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="F366" t="s">
         <v>1570</v>
       </c>
       <c r="G366" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="H366" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="I366" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="J366" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="K366" t="s">
         <v>1579</v>
       </c>
       <c r="L366" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="M366" t="s">
         <v>1580</v>
@@ -21212,31 +21212,31 @@
         <v>1163</v>
       </c>
       <c r="D367" t="s">
-        <v>1270</v>
+        <v>1237</v>
       </c>
       <c r="E367" t="s">
-        <v>1459</v>
+        <v>1426</v>
       </c>
       <c r="F367" t="s">
         <v>1570</v>
       </c>
       <c r="G367" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H367" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="I367" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="J367" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K367" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L367" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="M367" t="s">
         <v>1580</v>
@@ -21256,34 +21256,34 @@
         <v>1164</v>
       </c>
       <c r="D368" t="s">
-        <v>1237</v>
+        <v>1323</v>
       </c>
       <c r="E368" t="s">
-        <v>1426</v>
+        <v>1512</v>
       </c>
       <c r="F368" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G368" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H368" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="I368" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="J368" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="K368" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L368" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M368" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="N368" t="s">
         <v>1582</v>
@@ -21300,10 +21300,10 @@
         <v>1165</v>
       </c>
       <c r="D369" t="s">
-        <v>1323</v>
+        <v>1374</v>
       </c>
       <c r="E369" t="s">
-        <v>1512</v>
+        <v>1563</v>
       </c>
       <c r="F369" t="s">
         <v>1569</v>
@@ -21344,34 +21344,34 @@
         <v>1166</v>
       </c>
       <c r="D370" t="s">
-        <v>1375</v>
+        <v>1210</v>
       </c>
       <c r="E370" t="s">
-        <v>1564</v>
+        <v>1399</v>
       </c>
       <c r="F370" t="s">
         <v>1569</v>
       </c>
       <c r="G370" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H370" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="I370" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="J370" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="K370" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="L370" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="M370" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="N370" t="s">
         <v>1582</v>
@@ -21388,31 +21388,31 @@
         <v>1167</v>
       </c>
       <c r="D371" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="E371" t="s">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="F371" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="G371" t="s">
         <v>1575</v>
       </c>
       <c r="H371" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="I371" t="s">
         <v>1581</v>
       </c>
       <c r="J371" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="K371" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="L371" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="M371" t="s">
         <v>1580</v>
@@ -21432,34 +21432,34 @@
         <v>1168</v>
       </c>
       <c r="D372" t="s">
-        <v>1222</v>
+        <v>1375</v>
       </c>
       <c r="E372" t="s">
-        <v>1411</v>
+        <v>1564</v>
       </c>
       <c r="F372" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="G372" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H372" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="I372" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="J372" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="K372" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L372" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="M372" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="N372" t="s">
         <v>1582</v>
@@ -21482,28 +21482,28 @@
         <v>1565</v>
       </c>
       <c r="F373" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="G373" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H373" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="I373" t="s">
         <v>1577</v>
       </c>
       <c r="J373" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="K373" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="L373" t="s">
         <v>1579</v>
       </c>
       <c r="M373" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="N373" t="s">
         <v>1582</v>
@@ -21526,28 +21526,28 @@
         <v>1566</v>
       </c>
       <c r="F374" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="G374" t="s">
         <v>1575</v>
       </c>
       <c r="H374" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="I374" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="J374" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="K374" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="L374" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="M374" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="N374" t="s">
         <v>1582</v>
@@ -21564,13 +21564,13 @@
         <v>1171</v>
       </c>
       <c r="D375" t="s">
-        <v>1378</v>
+        <v>1220</v>
       </c>
       <c r="E375" t="s">
-        <v>1567</v>
+        <v>1409</v>
       </c>
       <c r="F375" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G375" t="s">
         <v>1575</v>
@@ -21585,13 +21585,13 @@
         <v>1576</v>
       </c>
       <c r="K375" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="L375" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="M375" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="N375" t="s">
         <v>1582</v>
@@ -21608,13 +21608,13 @@
         <v>1172</v>
       </c>
       <c r="D376" t="s">
-        <v>1220</v>
+        <v>1202</v>
       </c>
       <c r="E376" t="s">
-        <v>1409</v>
+        <v>1391</v>
       </c>
       <c r="F376" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="G376" t="s">
         <v>1575</v>
@@ -21626,16 +21626,16 @@
         <v>1581</v>
       </c>
       <c r="J376" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="K376" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L376" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="M376" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="N376" t="s">
         <v>1582</v>
@@ -21652,22 +21652,22 @@
         <v>1173</v>
       </c>
       <c r="D377" t="s">
-        <v>1202</v>
+        <v>1260</v>
       </c>
       <c r="E377" t="s">
-        <v>1391</v>
+        <v>1449</v>
       </c>
       <c r="F377" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="G377" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H377" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="I377" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="J377" t="s">
         <v>1577</v>
@@ -21676,10 +21676,10 @@
         <v>1579</v>
       </c>
       <c r="L377" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="M377" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="N377" t="s">
         <v>1582</v>
@@ -21696,31 +21696,31 @@
         <v>1174</v>
       </c>
       <c r="D378" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="E378" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="F378" t="s">
         <v>1570</v>
       </c>
       <c r="G378" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H378" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="I378" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="J378" t="s">
         <v>1577</v>
       </c>
       <c r="K378" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="L378" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="M378" t="s">
         <v>1581</v>
@@ -21740,34 +21740,34 @@
         <v>1175</v>
       </c>
       <c r="D379" t="s">
-        <v>1266</v>
+        <v>1206</v>
       </c>
       <c r="E379" t="s">
-        <v>1455</v>
+        <v>1395</v>
       </c>
       <c r="F379" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="G379" t="s">
         <v>1575</v>
       </c>
       <c r="H379" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="I379" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J379" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="K379" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="L379" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="M379" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N379" t="s">
         <v>1582</v>
@@ -21784,34 +21784,34 @@
         <v>1176</v>
       </c>
       <c r="D380" t="s">
-        <v>1206</v>
+        <v>1228</v>
       </c>
       <c r="E380" t="s">
-        <v>1395</v>
+        <v>1417</v>
       </c>
       <c r="F380" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="G380" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H380" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="I380" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="J380" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="K380" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L380" t="s">
         <v>1580</v>
       </c>
       <c r="M380" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="N380" t="s">
         <v>1582</v>
@@ -21828,34 +21828,34 @@
         <v>1177</v>
       </c>
       <c r="D381" t="s">
-        <v>1228</v>
+        <v>1332</v>
       </c>
       <c r="E381" t="s">
-        <v>1417</v>
+        <v>1521</v>
       </c>
       <c r="F381" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="G381" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H381" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="I381" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J381" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="K381" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="L381" t="s">
         <v>1580</v>
       </c>
       <c r="M381" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="N381" t="s">
         <v>1582</v>
@@ -21872,10 +21872,10 @@
         <v>1178</v>
       </c>
       <c r="D382" t="s">
-        <v>1332</v>
+        <v>1202</v>
       </c>
       <c r="E382" t="s">
-        <v>1521</v>
+        <v>1391</v>
       </c>
       <c r="F382" t="s">
         <v>1570</v>
@@ -21884,13 +21884,13 @@
         <v>1575</v>
       </c>
       <c r="H382" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="I382" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="J382" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="K382" t="s">
         <v>1576</v>
@@ -21899,7 +21899,7 @@
         <v>1580</v>
       </c>
       <c r="M382" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="N382" t="s">
         <v>1582</v>
@@ -21916,28 +21916,28 @@
         <v>1179</v>
       </c>
       <c r="D383" t="s">
-        <v>1202</v>
+        <v>1352</v>
       </c>
       <c r="E383" t="s">
-        <v>1391</v>
+        <v>1541</v>
       </c>
       <c r="F383" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="G383" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="H383" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="I383" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J383" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="K383" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="L383" t="s">
         <v>1580</v>
@@ -21960,25 +21960,25 @@
         <v>1180</v>
       </c>
       <c r="D384" t="s">
-        <v>1352</v>
+        <v>1257</v>
       </c>
       <c r="E384" t="s">
-        <v>1541</v>
+        <v>1446</v>
       </c>
       <c r="F384" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="G384" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="H384" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="I384" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="J384" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="K384" t="s">
         <v>1579</v>
@@ -22004,31 +22004,31 @@
         <v>1181</v>
       </c>
       <c r="D385" t="s">
-        <v>1257</v>
+        <v>1239</v>
       </c>
       <c r="E385" t="s">
-        <v>1446</v>
+        <v>1428</v>
       </c>
       <c r="F385" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="G385" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H385" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="I385" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="J385" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K385" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="L385" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="M385" t="s">
         <v>1577</v>
@@ -22048,25 +22048,25 @@
         <v>1182</v>
       </c>
       <c r="D386" t="s">
-        <v>1239</v>
+        <v>1347</v>
       </c>
       <c r="E386" t="s">
-        <v>1428</v>
+        <v>1536</v>
       </c>
       <c r="F386" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="G386" t="s">
         <v>1575</v>
       </c>
       <c r="H386" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="I386" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J386" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="K386" t="s">
         <v>1576</v>
@@ -22075,7 +22075,7 @@
         <v>1579</v>
       </c>
       <c r="M386" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="N386" t="s">
         <v>1582</v>
@@ -22092,34 +22092,34 @@
         <v>1183</v>
       </c>
       <c r="D387" t="s">
-        <v>1347</v>
+        <v>1321</v>
       </c>
       <c r="E387" t="s">
-        <v>1536</v>
+        <v>1510</v>
       </c>
       <c r="F387" t="s">
         <v>1569</v>
       </c>
       <c r="G387" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="H387" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="I387" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="J387" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="K387" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="L387" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="M387" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="N387" t="s">
         <v>1582</v>
@@ -22136,34 +22136,34 @@
         <v>1184</v>
       </c>
       <c r="D388" t="s">
-        <v>1321</v>
+        <v>1377</v>
       </c>
       <c r="E388" t="s">
-        <v>1510</v>
+        <v>1566</v>
       </c>
       <c r="F388" t="s">
         <v>1569</v>
       </c>
       <c r="G388" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="H388" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="I388" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="J388" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="K388" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L388" t="s">
         <v>1580</v>
       </c>
       <c r="M388" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="N388" t="s">
         <v>1582</v>
@@ -22180,34 +22180,34 @@
         <v>1185</v>
       </c>
       <c r="D389" t="s">
-        <v>1378</v>
+        <v>1225</v>
       </c>
       <c r="E389" t="s">
-        <v>1567</v>
+        <v>1414</v>
       </c>
       <c r="F389" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="G389" t="s">
         <v>1575</v>
       </c>
       <c r="H389" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="I389" t="s">
         <v>1581</v>
       </c>
       <c r="J389" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="K389" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="L389" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="M389" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="N389" t="s">
         <v>1582</v>
@@ -22224,34 +22224,34 @@
         <v>1186</v>
       </c>
       <c r="D390" t="s">
-        <v>1225</v>
+        <v>1239</v>
       </c>
       <c r="E390" t="s">
-        <v>1414</v>
+        <v>1428</v>
       </c>
       <c r="F390" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G390" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H390" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="I390" t="s">
         <v>1581</v>
       </c>
       <c r="J390" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="K390" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="L390" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="M390" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="N390" t="s">
         <v>1582</v>
@@ -22268,34 +22268,34 @@
         <v>1187</v>
       </c>
       <c r="D391" t="s">
-        <v>1239</v>
+        <v>1378</v>
       </c>
       <c r="E391" t="s">
-        <v>1428</v>
+        <v>1567</v>
       </c>
       <c r="F391" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G391" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H391" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="I391" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="J391" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="K391" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="L391" t="s">
         <v>1580</v>
       </c>
       <c r="M391" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="N391" t="s">
         <v>1582</v>
@@ -22312,34 +22312,34 @@
         <v>1188</v>
       </c>
       <c r="D392" t="s">
-        <v>1379</v>
+        <v>1357</v>
       </c>
       <c r="E392" t="s">
-        <v>1568</v>
+        <v>1546</v>
       </c>
       <c r="F392" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="G392" t="s">
         <v>1575</v>
       </c>
       <c r="H392" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="I392" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J392" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="K392" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L392" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="M392" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="N392" t="s">
         <v>1582</v>
@@ -22356,13 +22356,13 @@
         <v>1189</v>
       </c>
       <c r="D393" t="s">
-        <v>1357</v>
+        <v>1379</v>
       </c>
       <c r="E393" t="s">
-        <v>1546</v>
+        <v>1568</v>
       </c>
       <c r="F393" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="G393" t="s">
         <v>1575</v>
@@ -22374,13 +22374,13 @@
         <v>1581</v>
       </c>
       <c r="J393" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K393" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="L393" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="M393" t="s">
         <v>1577</v>
@@ -22400,34 +22400,34 @@
         <v>1190</v>
       </c>
       <c r="D394">
-        <v>1136</v>
+        <v>1208</v>
       </c>
       <c r="E394">
-        <v>56.8</v>
+        <v>60.4</v>
       </c>
       <c r="F394" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="G394" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="H394" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="I394" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="J394" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="K394" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="L394" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="M394" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="N394" t="s">
         <v>1582</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -850,393 +850,393 @@
     <t>زياد توفيق محمد محمد</t>
   </si>
   <si>
+    <t>مريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>شهد حسين محمود صابر</t>
+  </si>
+  <si>
+    <t>محمد سرحان محمد زكى</t>
+  </si>
+  <si>
+    <t>لمياء عبد القادر محمد فتحى</t>
+  </si>
+  <si>
+    <t>أميمة رأفت محمود احمد</t>
+  </si>
+  <si>
+    <t>احمد رمضان محمد عبد الحميد</t>
+  </si>
+  <si>
+    <t>كريم محمد عبد الوهاب عيد</t>
+  </si>
+  <si>
+    <t>عمر رضا تونى طلبه</t>
+  </si>
+  <si>
+    <t>عبدالله ناصر أنور عبد المجيد</t>
+  </si>
+  <si>
+    <t>اندرو محروس مختار مهنى</t>
+  </si>
+  <si>
+    <t>فاطمه ناجى عبد السلام حسن</t>
+  </si>
+  <si>
+    <t>ماركو مجدى مكرم فريد</t>
+  </si>
+  <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
     <t>عبدالله محمد محمد احمد</t>
   </si>
   <si>
-    <t>مريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>شهد حسين محمود صابر</t>
-  </si>
-  <si>
-    <t>محمد سرحان محمد زكى</t>
-  </si>
-  <si>
-    <t>لمياء عبد القادر محمد فتحى</t>
-  </si>
-  <si>
-    <t>أميمة رأفت محمود احمد</t>
-  </si>
-  <si>
-    <t>احمد رمضان محمد عبد الحميد</t>
-  </si>
-  <si>
-    <t>كريم محمد عبد الوهاب عيد</t>
-  </si>
-  <si>
-    <t>عمر رضا تونى طلبه</t>
-  </si>
-  <si>
-    <t>عبدالله ناصر أنور عبد المجيد</t>
-  </si>
-  <si>
-    <t>اندرو محروس مختار مهنى</t>
-  </si>
-  <si>
-    <t>فاطمه ناجى عبد السلام حسن</t>
-  </si>
-  <si>
-    <t>ماركو مجدى مكرم فريد</t>
-  </si>
-  <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2026,393 +2026,393 @@
     <t>30506152402932</t>
   </si>
   <si>
+    <t>30509052401709</t>
+  </si>
+  <si>
+    <t>30408182401521</t>
+  </si>
+  <si>
+    <t>30410232401859</t>
+  </si>
+  <si>
+    <t>30409222402263</t>
+  </si>
+  <si>
+    <t>30308062400144</t>
+  </si>
+  <si>
+    <t>30302142401658</t>
+  </si>
+  <si>
+    <t>30506272400259</t>
+  </si>
+  <si>
+    <t>30409012413599</t>
+  </si>
+  <si>
+    <t>30601162402453</t>
+  </si>
+  <si>
+    <t>30310012402973</t>
+  </si>
+  <si>
+    <t>30506170300209</t>
+  </si>
+  <si>
+    <t>30409172401791</t>
+  </si>
+  <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
     <t>30412262402097</t>
   </si>
   <si>
-    <t>30509052401709</t>
-  </si>
-  <si>
-    <t>30408182401521</t>
-  </si>
-  <si>
-    <t>30410232401859</t>
-  </si>
-  <si>
-    <t>30409222402263</t>
-  </si>
-  <si>
-    <t>30308062400144</t>
-  </si>
-  <si>
-    <t>30302142401658</t>
-  </si>
-  <si>
-    <t>30506272400259</t>
-  </si>
-  <si>
-    <t>30409012413599</t>
-  </si>
-  <si>
-    <t>30601162402453</t>
-  </si>
-  <si>
-    <t>30310012402973</t>
-  </si>
-  <si>
-    <t>30506170300209</t>
-  </si>
-  <si>
-    <t>30409172401791</t>
-  </si>
-  <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3202,391 +3202,391 @@
     <t>01060726096</t>
   </si>
   <si>
+    <t>01101609533</t>
+  </si>
+  <si>
+    <t>0111590035</t>
+  </si>
+  <si>
+    <t>01148375746</t>
+  </si>
+  <si>
+    <t>01115291432</t>
+  </si>
+  <si>
+    <t>01121482192</t>
+  </si>
+  <si>
+    <t>01021408975</t>
+  </si>
+  <si>
+    <t>01068360992</t>
+  </si>
+  <si>
+    <t>01061982978</t>
+  </si>
+  <si>
+    <t>01092079993</t>
+  </si>
+  <si>
+    <t>01288364393</t>
+  </si>
+  <si>
+    <t>01157384981</t>
+  </si>
+  <si>
+    <t>01283970879</t>
+  </si>
+  <si>
+    <t>01099393313</t>
+  </si>
+  <si>
+    <t>01093075647</t>
+  </si>
+  <si>
+    <t>01037186555</t>
+  </si>
+  <si>
+    <t>01129169104</t>
+  </si>
+  <si>
+    <t>01001362969</t>
+  </si>
+  <si>
+    <t>01151741232</t>
+  </si>
+  <si>
+    <t>01013305686</t>
+  </si>
+  <si>
+    <t>01150936407</t>
+  </si>
+  <si>
+    <t>01002331784</t>
+  </si>
+  <si>
+    <t>01150905692</t>
+  </si>
+  <si>
+    <t>01028993616</t>
+  </si>
+  <si>
+    <t>01119364560</t>
+  </si>
+  <si>
+    <t>01114623756</t>
+  </si>
+  <si>
+    <t>01110180758</t>
+  </si>
+  <si>
+    <t>01098408936</t>
+  </si>
+  <si>
+    <t>01026439570</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
     <t>01121846011</t>
-  </si>
-  <si>
-    <t>01101609533</t>
-  </si>
-  <si>
-    <t>0111590035</t>
-  </si>
-  <si>
-    <t>01148375746</t>
-  </si>
-  <si>
-    <t>01115291432</t>
-  </si>
-  <si>
-    <t>01121482192</t>
-  </si>
-  <si>
-    <t>01021408975</t>
-  </si>
-  <si>
-    <t>01068360992</t>
-  </si>
-  <si>
-    <t>01061982978</t>
-  </si>
-  <si>
-    <t>01092079993</t>
-  </si>
-  <si>
-    <t>01288364393</t>
-  </si>
-  <si>
-    <t>01157384981</t>
-  </si>
-  <si>
-    <t>01283970879</t>
-  </si>
-  <si>
-    <t>01099393313</t>
-  </si>
-  <si>
-    <t>01093075647</t>
-  </si>
-  <si>
-    <t>01037186555</t>
-  </si>
-  <si>
-    <t>01129169104</t>
-  </si>
-  <si>
-    <t>01001362969</t>
-  </si>
-  <si>
-    <t>01151741232</t>
-  </si>
-  <si>
-    <t>01013305686</t>
-  </si>
-  <si>
-    <t>01150936407</t>
-  </si>
-  <si>
-    <t>01002331784</t>
-  </si>
-  <si>
-    <t>01150905692</t>
-  </si>
-  <si>
-    <t>01028993616</t>
-  </si>
-  <si>
-    <t>01119364560</t>
-  </si>
-  <si>
-    <t>01114623756</t>
-  </si>
-  <si>
-    <t>01110180758</t>
-  </si>
-  <si>
-    <t>01098408936</t>
-  </si>
-  <si>
-    <t>01026439570</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
   </si>
   <si>
     <t>1353</t>
@@ -16774,34 +16774,34 @@
         <v>1062</v>
       </c>
       <c r="D266" t="s">
-        <v>1311</v>
+        <v>1282</v>
       </c>
       <c r="E266" t="s">
-        <v>1501</v>
+        <v>1472</v>
       </c>
       <c r="F266" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G266" t="s">
         <v>1577</v>
       </c>
       <c r="H266" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I266" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J266" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="K266" t="s">
         <v>1579</v>
       </c>
       <c r="L266" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="M266" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="N266" t="s">
         <v>1584</v>
@@ -16818,13 +16818,13 @@
         <v>1063</v>
       </c>
       <c r="D267" t="s">
-        <v>1282</v>
+        <v>1313</v>
       </c>
       <c r="E267" t="s">
-        <v>1472</v>
+        <v>1503</v>
       </c>
       <c r="F267" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G267" t="s">
         <v>1577</v>
@@ -16836,7 +16836,7 @@
         <v>1583</v>
       </c>
       <c r="J267" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="K267" t="s">
         <v>1579</v>
@@ -16845,7 +16845,7 @@
         <v>1578</v>
       </c>
       <c r="M267" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="N267" t="s">
         <v>1584</v>
@@ -16862,10 +16862,10 @@
         <v>1064</v>
       </c>
       <c r="D268" t="s">
-        <v>1313</v>
+        <v>1217</v>
       </c>
       <c r="E268" t="s">
-        <v>1503</v>
+        <v>1407</v>
       </c>
       <c r="F268" t="s">
         <v>1571</v>
@@ -16880,13 +16880,13 @@
         <v>1583</v>
       </c>
       <c r="J268" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K268" t="s">
         <v>1579</v>
       </c>
       <c r="L268" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="M268" t="s">
         <v>1582</v>
@@ -16906,10 +16906,10 @@
         <v>1065</v>
       </c>
       <c r="D269" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="E269" t="s">
-        <v>1407</v>
+        <v>1414</v>
       </c>
       <c r="F269" t="s">
         <v>1571</v>
@@ -16924,16 +16924,16 @@
         <v>1583</v>
       </c>
       <c r="J269" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K269" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="L269" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="M269" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N269" t="s">
         <v>1584</v>
@@ -16950,13 +16950,13 @@
         <v>1066</v>
       </c>
       <c r="D270" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E270" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F270" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G270" t="s">
         <v>1577</v>
@@ -16965,19 +16965,19 @@
         <v>1580</v>
       </c>
       <c r="I270" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="J270" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="K270" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="L270" t="s">
         <v>1578</v>
       </c>
       <c r="M270" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N270" t="s">
         <v>1584</v>
@@ -16994,34 +16994,34 @@
         <v>1067</v>
       </c>
       <c r="D271" t="s">
-        <v>1223</v>
+        <v>1346</v>
       </c>
       <c r="E271" t="s">
-        <v>1413</v>
+        <v>1536</v>
       </c>
       <c r="F271" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G271" t="s">
         <v>1577</v>
       </c>
       <c r="H271" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="I271" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="J271" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="K271" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="L271" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M271" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="N271" t="s">
         <v>1584</v>
@@ -17038,34 +17038,34 @@
         <v>1068</v>
       </c>
       <c r="D272" t="s">
-        <v>1346</v>
+        <v>1191</v>
       </c>
       <c r="E272" t="s">
-        <v>1536</v>
+        <v>1381</v>
       </c>
       <c r="F272" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G272" t="s">
         <v>1577</v>
       </c>
       <c r="H272" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="I272" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J272" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="K272" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L272" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="M272" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="N272" t="s">
         <v>1584</v>
@@ -17082,34 +17082,34 @@
         <v>1069</v>
       </c>
       <c r="D273" t="s">
-        <v>1191</v>
+        <v>1289</v>
       </c>
       <c r="E273" t="s">
-        <v>1381</v>
+        <v>1479</v>
       </c>
       <c r="F273" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G273" t="s">
         <v>1577</v>
       </c>
       <c r="H273" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="I273" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J273" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="K273" t="s">
         <v>1581</v>
       </c>
       <c r="L273" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="M273" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="N273" t="s">
         <v>1584</v>
@@ -17126,22 +17126,22 @@
         <v>1070</v>
       </c>
       <c r="D274" t="s">
-        <v>1289</v>
+        <v>1267</v>
       </c>
       <c r="E274" t="s">
-        <v>1479</v>
+        <v>1457</v>
       </c>
       <c r="F274" t="s">
         <v>1571</v>
       </c>
       <c r="G274" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="H274" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="I274" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="J274" t="s">
         <v>1580</v>
@@ -17150,10 +17150,10 @@
         <v>1581</v>
       </c>
       <c r="L274" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="M274" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="N274" t="s">
         <v>1584</v>
@@ -17170,34 +17170,34 @@
         <v>1071</v>
       </c>
       <c r="D275" t="s">
-        <v>1267</v>
+        <v>1239</v>
       </c>
       <c r="E275" t="s">
-        <v>1457</v>
+        <v>1429</v>
       </c>
       <c r="F275" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G275" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="H275" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="I275" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="J275" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K275" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="L275" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="M275" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="N275" t="s">
         <v>1584</v>
@@ -17214,13 +17214,13 @@
         <v>1072</v>
       </c>
       <c r="D276" t="s">
-        <v>1239</v>
+        <v>1347</v>
       </c>
       <c r="E276" t="s">
-        <v>1429</v>
+        <v>1537</v>
       </c>
       <c r="F276" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G276" t="s">
         <v>1577</v>
@@ -17229,19 +17229,19 @@
         <v>1583</v>
       </c>
       <c r="I276" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="J276" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K276" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="L276" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="M276" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N276" t="s">
         <v>1584</v>
@@ -17258,34 +17258,34 @@
         <v>1073</v>
       </c>
       <c r="D277" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E277" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="F277" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G277" t="s">
         <v>1577</v>
       </c>
       <c r="H277" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I277" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J277" t="s">
         <v>1578</v>
       </c>
       <c r="K277" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L277" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="M277" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N277" t="s">
         <v>1584</v>
@@ -17302,13 +17302,13 @@
         <v>1074</v>
       </c>
       <c r="D278" t="s">
-        <v>1348</v>
+        <v>1267</v>
       </c>
       <c r="E278" t="s">
-        <v>1538</v>
+        <v>1457</v>
       </c>
       <c r="F278" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G278" t="s">
         <v>1577</v>
@@ -17317,19 +17317,19 @@
         <v>1580</v>
       </c>
       <c r="I278" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="J278" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K278" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L278" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="M278" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N278" t="s">
         <v>1584</v>
@@ -17346,13 +17346,13 @@
         <v>1075</v>
       </c>
       <c r="D279" t="s">
-        <v>1267</v>
+        <v>1340</v>
       </c>
       <c r="E279" t="s">
-        <v>1457</v>
+        <v>1530</v>
       </c>
       <c r="F279" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G279" t="s">
         <v>1577</v>
@@ -17367,13 +17367,13 @@
         <v>1581</v>
       </c>
       <c r="K279" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="L279" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="M279" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="N279" t="s">
         <v>1584</v>
@@ -17390,10 +17390,10 @@
         <v>1076</v>
       </c>
       <c r="D280" t="s">
-        <v>1340</v>
+        <v>1285</v>
       </c>
       <c r="E280" t="s">
-        <v>1530</v>
+        <v>1475</v>
       </c>
       <c r="F280" t="s">
         <v>1572</v>
@@ -17402,22 +17402,22 @@
         <v>1577</v>
       </c>
       <c r="H280" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I280" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J280" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="K280" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="L280" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M280" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="N280" t="s">
         <v>1584</v>
@@ -17434,10 +17434,10 @@
         <v>1077</v>
       </c>
       <c r="D281" t="s">
-        <v>1285</v>
+        <v>1349</v>
       </c>
       <c r="E281" t="s">
-        <v>1475</v>
+        <v>1539</v>
       </c>
       <c r="F281" t="s">
         <v>1572</v>
@@ -17446,22 +17446,22 @@
         <v>1577</v>
       </c>
       <c r="H281" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="I281" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J281" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="K281" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="L281" t="s">
         <v>1581</v>
       </c>
       <c r="M281" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="N281" t="s">
         <v>1584</v>
@@ -17478,25 +17478,25 @@
         <v>1078</v>
       </c>
       <c r="D282" t="s">
-        <v>1349</v>
+        <v>1222</v>
       </c>
       <c r="E282" t="s">
-        <v>1539</v>
+        <v>1412</v>
       </c>
       <c r="F282" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="G282" t="s">
         <v>1577</v>
       </c>
       <c r="H282" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="I282" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="J282" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="K282" t="s">
         <v>1582</v>
@@ -17505,7 +17505,7 @@
         <v>1581</v>
       </c>
       <c r="M282" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="N282" t="s">
         <v>1584</v>
@@ -17522,13 +17522,13 @@
         <v>1079</v>
       </c>
       <c r="D283" t="s">
-        <v>1222</v>
+        <v>1295</v>
       </c>
       <c r="E283" t="s">
-        <v>1412</v>
+        <v>1485</v>
       </c>
       <c r="F283" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="G283" t="s">
         <v>1577</v>
@@ -17566,19 +17566,19 @@
         <v>1080</v>
       </c>
       <c r="D284" t="s">
-        <v>1295</v>
+        <v>1191</v>
       </c>
       <c r="E284" t="s">
-        <v>1485</v>
+        <v>1381</v>
       </c>
       <c r="F284" t="s">
         <v>1571</v>
       </c>
       <c r="G284" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="H284" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I284" t="s">
         <v>1583</v>
@@ -17587,13 +17587,13 @@
         <v>1578</v>
       </c>
       <c r="K284" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="L284" t="s">
         <v>1581</v>
       </c>
       <c r="M284" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N284" t="s">
         <v>1584</v>
@@ -17610,34 +17610,34 @@
         <v>1081</v>
       </c>
       <c r="D285" t="s">
-        <v>1191</v>
+        <v>1205</v>
       </c>
       <c r="E285" t="s">
-        <v>1381</v>
+        <v>1395</v>
       </c>
       <c r="F285" t="s">
         <v>1571</v>
       </c>
       <c r="G285" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="H285" t="s">
         <v>1577</v>
       </c>
       <c r="I285" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="J285" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K285" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="L285" t="s">
         <v>1581</v>
       </c>
       <c r="M285" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N285" t="s">
         <v>1584</v>
@@ -17654,34 +17654,34 @@
         <v>1082</v>
       </c>
       <c r="D286" t="s">
-        <v>1205</v>
+        <v>1224</v>
       </c>
       <c r="E286" t="s">
-        <v>1395</v>
+        <v>1414</v>
       </c>
       <c r="F286" t="s">
         <v>1571</v>
       </c>
       <c r="G286" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H286" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="I286" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="J286" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K286" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="L286" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="M286" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N286" t="s">
         <v>1584</v>
@@ -17698,34 +17698,34 @@
         <v>1083</v>
       </c>
       <c r="D287" t="s">
-        <v>1224</v>
+        <v>1350</v>
       </c>
       <c r="E287" t="s">
-        <v>1414</v>
+        <v>1540</v>
       </c>
       <c r="F287" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G287" t="s">
         <v>1577</v>
       </c>
       <c r="H287" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="I287" t="s">
         <v>1580</v>
       </c>
       <c r="J287" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K287" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L287" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="M287" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N287" t="s">
         <v>1584</v>
@@ -17742,31 +17742,31 @@
         <v>1084</v>
       </c>
       <c r="D288" t="s">
-        <v>1350</v>
+        <v>1238</v>
       </c>
       <c r="E288" t="s">
-        <v>1540</v>
+        <v>1428</v>
       </c>
       <c r="F288" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G288" t="s">
         <v>1577</v>
       </c>
       <c r="H288" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I288" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="J288" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K288" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L288" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="M288" t="s">
         <v>1579</v>
@@ -17786,34 +17786,34 @@
         <v>1085</v>
       </c>
       <c r="D289" t="s">
-        <v>1238</v>
+        <v>1267</v>
       </c>
       <c r="E289" t="s">
-        <v>1428</v>
+        <v>1457</v>
       </c>
       <c r="F289" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G289" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="H289" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I289" t="s">
         <v>1582</v>
       </c>
       <c r="J289" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="K289" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="L289" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="M289" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="N289" t="s">
         <v>1584</v>
@@ -17830,34 +17830,34 @@
         <v>1086</v>
       </c>
       <c r="D290" t="s">
-        <v>1267</v>
+        <v>1202</v>
       </c>
       <c r="E290" t="s">
-        <v>1457</v>
+        <v>1392</v>
       </c>
       <c r="F290" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G290" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="H290" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="I290" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="J290" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K290" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L290" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M290" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="N290" t="s">
         <v>1584</v>
@@ -17874,10 +17874,10 @@
         <v>1087</v>
       </c>
       <c r="D291" t="s">
-        <v>1202</v>
+        <v>1308</v>
       </c>
       <c r="E291" t="s">
-        <v>1392</v>
+        <v>1498</v>
       </c>
       <c r="F291" t="s">
         <v>1571</v>
@@ -17895,13 +17895,13 @@
         <v>1578</v>
       </c>
       <c r="K291" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="L291" t="s">
         <v>1581</v>
       </c>
       <c r="M291" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N291" t="s">
         <v>1584</v>
@@ -17918,10 +17918,10 @@
         <v>1088</v>
       </c>
       <c r="D292" t="s">
-        <v>1308</v>
+        <v>1351</v>
       </c>
       <c r="E292" t="s">
-        <v>1498</v>
+        <v>1541</v>
       </c>
       <c r="F292" t="s">
         <v>1571</v>
@@ -17930,19 +17930,19 @@
         <v>1577</v>
       </c>
       <c r="H292" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I292" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J292" t="s">
         <v>1578</v>
       </c>
       <c r="K292" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L292" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M292" t="s">
         <v>1579</v>
@@ -17962,13 +17962,13 @@
         <v>1089</v>
       </c>
       <c r="D293" t="s">
-        <v>1351</v>
+        <v>1207</v>
       </c>
       <c r="E293" t="s">
-        <v>1541</v>
+        <v>1397</v>
       </c>
       <c r="F293" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G293" t="s">
         <v>1577</v>
@@ -17980,16 +17980,16 @@
         <v>1583</v>
       </c>
       <c r="J293" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K293" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L293" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="M293" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N293" t="s">
         <v>1584</v>
@@ -18006,13 +18006,13 @@
         <v>1090</v>
       </c>
       <c r="D294" t="s">
-        <v>1207</v>
+        <v>1343</v>
       </c>
       <c r="E294" t="s">
-        <v>1397</v>
+        <v>1533</v>
       </c>
       <c r="F294" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G294" t="s">
         <v>1577</v>
@@ -18021,16 +18021,16 @@
         <v>1580</v>
       </c>
       <c r="I294" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="J294" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="K294" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L294" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="M294" t="s">
         <v>1582</v>
@@ -18050,13 +18050,13 @@
         <v>1091</v>
       </c>
       <c r="D295" t="s">
-        <v>1343</v>
+        <v>1213</v>
       </c>
       <c r="E295" t="s">
-        <v>1533</v>
+        <v>1403</v>
       </c>
       <c r="F295" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G295" t="s">
         <v>1577</v>
@@ -18065,19 +18065,19 @@
         <v>1580</v>
       </c>
       <c r="I295" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="J295" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="K295" t="s">
         <v>1581</v>
       </c>
       <c r="L295" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="M295" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N295" t="s">
         <v>1584</v>
@@ -18094,34 +18094,34 @@
         <v>1092</v>
       </c>
       <c r="D296" t="s">
-        <v>1213</v>
+        <v>1302</v>
       </c>
       <c r="E296" t="s">
-        <v>1403</v>
+        <v>1492</v>
       </c>
       <c r="F296" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G296" t="s">
         <v>1577</v>
       </c>
       <c r="H296" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I296" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="J296" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="K296" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="L296" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M296" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N296" t="s">
         <v>1584</v>
@@ -18138,19 +18138,19 @@
         <v>1093</v>
       </c>
       <c r="D297" t="s">
-        <v>1302</v>
+        <v>1352</v>
       </c>
       <c r="E297" t="s">
-        <v>1492</v>
+        <v>1542</v>
       </c>
       <c r="F297" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G297" t="s">
         <v>1577</v>
       </c>
       <c r="H297" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="I297" t="s">
         <v>1579</v>
@@ -18159,7 +18159,7 @@
         <v>1583</v>
       </c>
       <c r="K297" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="L297" t="s">
         <v>1582</v>
@@ -18182,34 +18182,34 @@
         <v>1094</v>
       </c>
       <c r="D298" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E298" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="F298" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G298" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H298" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="I298" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="J298" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="K298" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="L298" t="s">
         <v>1582</v>
       </c>
       <c r="M298" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="N298" t="s">
         <v>1584</v>
@@ -18226,34 +18226,34 @@
         <v>1095</v>
       </c>
       <c r="D299" t="s">
-        <v>1353</v>
+        <v>1222</v>
       </c>
       <c r="E299" t="s">
-        <v>1543</v>
+        <v>1412</v>
       </c>
       <c r="F299" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="G299" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H299" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="I299" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="J299" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K299" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="L299" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M299" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="N299" t="s">
         <v>1584</v>
@@ -18270,31 +18270,31 @@
         <v>1096</v>
       </c>
       <c r="D300" t="s">
-        <v>1222</v>
+        <v>1277</v>
       </c>
       <c r="E300" t="s">
-        <v>1412</v>
+        <v>1467</v>
       </c>
       <c r="F300" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="G300" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H300" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I300" t="s">
         <v>1583</v>
       </c>
       <c r="J300" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K300" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="L300" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M300" t="s">
         <v>1579</v>
@@ -18314,28 +18314,28 @@
         <v>1097</v>
       </c>
       <c r="D301" t="s">
-        <v>1277</v>
+        <v>1296</v>
       </c>
       <c r="E301" t="s">
-        <v>1467</v>
+        <v>1486</v>
       </c>
       <c r="F301" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G301" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H301" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="I301" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J301" t="s">
         <v>1581</v>
       </c>
       <c r="K301" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="L301" t="s">
         <v>1582</v>
@@ -18358,34 +18358,34 @@
         <v>1098</v>
       </c>
       <c r="D302" t="s">
-        <v>1296</v>
+        <v>1308</v>
       </c>
       <c r="E302" t="s">
-        <v>1486</v>
+        <v>1498</v>
       </c>
       <c r="F302" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G302" t="s">
         <v>1577</v>
       </c>
       <c r="H302" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="I302" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J302" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K302" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="L302" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M302" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="N302" t="s">
         <v>1584</v>
@@ -18402,13 +18402,13 @@
         <v>1099</v>
       </c>
       <c r="D303" t="s">
-        <v>1308</v>
+        <v>1329</v>
       </c>
       <c r="E303" t="s">
-        <v>1498</v>
+        <v>1519</v>
       </c>
       <c r="F303" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G303" t="s">
         <v>1577</v>
@@ -18417,19 +18417,19 @@
         <v>1583</v>
       </c>
       <c r="I303" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="J303" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="K303" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L303" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="M303" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="N303" t="s">
         <v>1584</v>
@@ -18446,10 +18446,10 @@
         <v>1100</v>
       </c>
       <c r="D304" t="s">
-        <v>1329</v>
+        <v>1240</v>
       </c>
       <c r="E304" t="s">
-        <v>1519</v>
+        <v>1430</v>
       </c>
       <c r="F304" t="s">
         <v>1572</v>
@@ -18461,19 +18461,19 @@
         <v>1583</v>
       </c>
       <c r="I304" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J304" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K304" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L304" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M304" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="N304" t="s">
         <v>1584</v>
@@ -18490,13 +18490,13 @@
         <v>1101</v>
       </c>
       <c r="D305" t="s">
-        <v>1240</v>
+        <v>1256</v>
       </c>
       <c r="E305" t="s">
-        <v>1430</v>
+        <v>1446</v>
       </c>
       <c r="F305" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G305" t="s">
         <v>1577</v>
@@ -18505,10 +18505,10 @@
         <v>1583</v>
       </c>
       <c r="I305" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="J305" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K305" t="s">
         <v>1582</v>
@@ -18534,10 +18534,10 @@
         <v>1102</v>
       </c>
       <c r="D306" t="s">
-        <v>1256</v>
+        <v>1354</v>
       </c>
       <c r="E306" t="s">
-        <v>1446</v>
+        <v>1544</v>
       </c>
       <c r="F306" t="s">
         <v>1571</v>
@@ -18546,22 +18546,22 @@
         <v>1577</v>
       </c>
       <c r="H306" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I306" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J306" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K306" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L306" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M306" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="N306" t="s">
         <v>1584</v>
@@ -18578,34 +18578,34 @@
         <v>1103</v>
       </c>
       <c r="D307" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="E307" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="F307" t="s">
         <v>1571</v>
       </c>
       <c r="G307" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H307" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I307" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="J307" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K307" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L307" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="M307" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="N307" t="s">
         <v>1584</v>
@@ -18622,10 +18622,10 @@
         <v>1104</v>
       </c>
       <c r="D308" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="E308" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="F308" t="s">
         <v>1571</v>
@@ -18666,34 +18666,34 @@
         <v>1105</v>
       </c>
       <c r="D309" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E309" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="F309" t="s">
         <v>1571</v>
       </c>
       <c r="G309" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H309" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I309" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="J309" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K309" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L309" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="M309" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="N309" t="s">
         <v>1584</v>
@@ -18710,34 +18710,34 @@
         <v>1106</v>
       </c>
       <c r="D310" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E310" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="F310" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="G310" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H310" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I310" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J310" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K310" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L310" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="M310" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N310" t="s">
         <v>1584</v>
@@ -18754,34 +18754,34 @@
         <v>1107</v>
       </c>
       <c r="D311" t="s">
-        <v>1358</v>
+        <v>1326</v>
       </c>
       <c r="E311" t="s">
-        <v>1548</v>
+        <v>1516</v>
       </c>
       <c r="F311" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="G311" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H311" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I311" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J311" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="K311" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L311" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="M311" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="N311" t="s">
         <v>1584</v>
@@ -18798,13 +18798,13 @@
         <v>1108</v>
       </c>
       <c r="D312" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="E312" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="F312" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G312" t="s">
         <v>1577</v>
@@ -18819,13 +18819,13 @@
         <v>1579</v>
       </c>
       <c r="K312" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L312" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M312" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="N312" t="s">
         <v>1584</v>
@@ -18842,10 +18842,10 @@
         <v>1109</v>
       </c>
       <c r="D313" t="s">
-        <v>1332</v>
+        <v>1359</v>
       </c>
       <c r="E313" t="s">
-        <v>1522</v>
+        <v>1549</v>
       </c>
       <c r="F313" t="s">
         <v>1571</v>
@@ -18860,16 +18860,16 @@
         <v>1583</v>
       </c>
       <c r="J313" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K313" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L313" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M313" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N313" t="s">
         <v>1584</v>
@@ -18886,31 +18886,31 @@
         <v>1110</v>
       </c>
       <c r="D314" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E314" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F314" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G314" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="H314" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I314" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="J314" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="K314" t="s">
         <v>1581</v>
       </c>
       <c r="L314" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M314" t="s">
         <v>1579</v>
@@ -18930,34 +18930,34 @@
         <v>1111</v>
       </c>
       <c r="D315" t="s">
-        <v>1360</v>
+        <v>1325</v>
       </c>
       <c r="E315" t="s">
-        <v>1550</v>
+        <v>1515</v>
       </c>
       <c r="F315" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G315" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="H315" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="I315" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="J315" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="K315" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L315" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M315" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N315" t="s">
         <v>1584</v>
@@ -18974,34 +18974,34 @@
         <v>1112</v>
       </c>
       <c r="D316" t="s">
-        <v>1325</v>
+        <v>1235</v>
       </c>
       <c r="E316" t="s">
-        <v>1515</v>
+        <v>1425</v>
       </c>
       <c r="F316" t="s">
         <v>1572</v>
       </c>
       <c r="G316" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H316" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="I316" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="J316" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="K316" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="L316" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="M316" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="N316" t="s">
         <v>1584</v>
@@ -19018,34 +19018,34 @@
         <v>1113</v>
       </c>
       <c r="D317" t="s">
-        <v>1235</v>
+        <v>1273</v>
       </c>
       <c r="E317" t="s">
-        <v>1425</v>
+        <v>1463</v>
       </c>
       <c r="F317" t="s">
         <v>1572</v>
       </c>
       <c r="G317" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H317" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I317" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="J317" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="K317" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L317" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="M317" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="N317" t="s">
         <v>1584</v>
@@ -19062,34 +19062,34 @@
         <v>1114</v>
       </c>
       <c r="D318" t="s">
-        <v>1273</v>
+        <v>1302</v>
       </c>
       <c r="E318" t="s">
-        <v>1463</v>
+        <v>1492</v>
       </c>
       <c r="F318" t="s">
         <v>1572</v>
       </c>
       <c r="G318" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="H318" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I318" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J318" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="K318" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L318" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M318" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N318" t="s">
         <v>1584</v>
@@ -19106,34 +19106,34 @@
         <v>1115</v>
       </c>
       <c r="D319" t="s">
-        <v>1302</v>
+        <v>1273</v>
       </c>
       <c r="E319" t="s">
-        <v>1492</v>
+        <v>1463</v>
       </c>
       <c r="F319" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G319" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="H319" t="s">
         <v>1577</v>
       </c>
       <c r="I319" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J319" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K319" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L319" t="s">
         <v>1582</v>
       </c>
       <c r="M319" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="N319" t="s">
         <v>1584</v>
@@ -19150,31 +19150,31 @@
         <v>1116</v>
       </c>
       <c r="D320" t="s">
-        <v>1273</v>
+        <v>1361</v>
       </c>
       <c r="E320" t="s">
-        <v>1463</v>
+        <v>1551</v>
       </c>
       <c r="F320" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="G320" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H320" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I320" t="s">
         <v>1583</v>
       </c>
       <c r="J320" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K320" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L320" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M320" t="s">
         <v>1578</v>
@@ -19194,10 +19194,10 @@
         <v>1117</v>
       </c>
       <c r="D321" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E321" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="F321" t="s">
         <v>1575</v>
@@ -19212,16 +19212,16 @@
         <v>1583</v>
       </c>
       <c r="J321" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K321" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L321" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M321" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="N321" t="s">
         <v>1584</v>
@@ -19238,13 +19238,13 @@
         <v>1118</v>
       </c>
       <c r="D322" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="E322" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="F322" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="G322" t="s">
         <v>1577</v>
@@ -19256,13 +19256,13 @@
         <v>1583</v>
       </c>
       <c r="J322" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K322" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L322" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M322" t="s">
         <v>1579</v>
@@ -19282,34 +19282,34 @@
         <v>1119</v>
       </c>
       <c r="D323" t="s">
-        <v>1363</v>
+        <v>1342</v>
       </c>
       <c r="E323" t="s">
-        <v>1553</v>
+        <v>1532</v>
       </c>
       <c r="F323" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G323" t="s">
         <v>1577</v>
       </c>
       <c r="H323" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I323" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J323" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="K323" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L323" t="s">
         <v>1578</v>
       </c>
       <c r="M323" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N323" t="s">
         <v>1584</v>
@@ -19326,25 +19326,25 @@
         <v>1120</v>
       </c>
       <c r="D324" t="s">
-        <v>1342</v>
+        <v>1212</v>
       </c>
       <c r="E324" t="s">
-        <v>1532</v>
+        <v>1402</v>
       </c>
       <c r="F324" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="G324" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H324" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I324" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J324" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="K324" t="s">
         <v>1581</v>
@@ -19370,31 +19370,31 @@
         <v>1121</v>
       </c>
       <c r="D325" t="s">
-        <v>1212</v>
+        <v>1282</v>
       </c>
       <c r="E325" t="s">
-        <v>1402</v>
+        <v>1472</v>
       </c>
       <c r="F325" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="G325" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H325" t="s">
         <v>1580</v>
       </c>
       <c r="I325" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="J325" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="K325" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L325" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="M325" t="s">
         <v>1582</v>
@@ -19414,34 +19414,34 @@
         <v>1122</v>
       </c>
       <c r="D326" t="s">
-        <v>1282</v>
+        <v>1364</v>
       </c>
       <c r="E326" t="s">
-        <v>1472</v>
+        <v>1554</v>
       </c>
       <c r="F326" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G326" t="s">
         <v>1577</v>
       </c>
       <c r="H326" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I326" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="J326" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="K326" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L326" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="M326" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N326" t="s">
         <v>1584</v>
@@ -19458,34 +19458,34 @@
         <v>1123</v>
       </c>
       <c r="D327" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="E327" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="F327" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G327" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H327" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="I327" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="J327" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K327" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L327" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="M327" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N327" t="s">
         <v>1584</v>
@@ -19502,34 +19502,34 @@
         <v>1124</v>
       </c>
       <c r="D328" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E328" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="F328" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G328" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="H328" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="I328" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="J328" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="K328" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="L328" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="M328" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N328" t="s">
         <v>1584</v>
@@ -19546,34 +19546,34 @@
         <v>1125</v>
       </c>
       <c r="D329" t="s">
-        <v>1366</v>
+        <v>1241</v>
       </c>
       <c r="E329" t="s">
-        <v>1556</v>
+        <v>1431</v>
       </c>
       <c r="F329" t="s">
         <v>1573</v>
       </c>
       <c r="G329" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="H329" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="I329" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="J329" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="K329" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="L329" t="s">
         <v>1582</v>
       </c>
       <c r="M329" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N329" t="s">
         <v>1584</v>
@@ -19590,10 +19590,10 @@
         <v>1126</v>
       </c>
       <c r="D330" t="s">
-        <v>1241</v>
+        <v>1367</v>
       </c>
       <c r="E330" t="s">
-        <v>1431</v>
+        <v>1557</v>
       </c>
       <c r="F330" t="s">
         <v>1573</v>
@@ -19602,13 +19602,13 @@
         <v>1578</v>
       </c>
       <c r="H330" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="I330" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="J330" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="K330" t="s">
         <v>1583</v>
@@ -19617,7 +19617,7 @@
         <v>1582</v>
       </c>
       <c r="M330" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N330" t="s">
         <v>1584</v>
@@ -19634,34 +19634,34 @@
         <v>1127</v>
       </c>
       <c r="D331" t="s">
-        <v>1367</v>
+        <v>1207</v>
       </c>
       <c r="E331" t="s">
-        <v>1557</v>
+        <v>1397</v>
       </c>
       <c r="F331" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G331" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H331" t="s">
         <v>1577</v>
       </c>
       <c r="I331" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="J331" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K331" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="L331" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M331" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="N331" t="s">
         <v>1584</v>
@@ -19678,34 +19678,34 @@
         <v>1128</v>
       </c>
       <c r="D332" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="E332" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F332" t="s">
         <v>1571</v>
       </c>
       <c r="G332" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H332" t="s">
         <v>1577</v>
       </c>
       <c r="I332" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="J332" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="K332" t="s">
         <v>1581</v>
       </c>
       <c r="L332" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="M332" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="N332" t="s">
         <v>1584</v>
@@ -19722,34 +19722,34 @@
         <v>1129</v>
       </c>
       <c r="D333" t="s">
-        <v>1205</v>
+        <v>1340</v>
       </c>
       <c r="E333" t="s">
-        <v>1395</v>
+        <v>1530</v>
       </c>
       <c r="F333" t="s">
         <v>1571</v>
       </c>
       <c r="G333" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H333" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="I333" t="s">
         <v>1580</v>
       </c>
       <c r="J333" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="K333" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L333" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M333" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="N333" t="s">
         <v>1584</v>
@@ -19766,34 +19766,34 @@
         <v>1130</v>
       </c>
       <c r="D334" t="s">
-        <v>1340</v>
+        <v>1368</v>
       </c>
       <c r="E334" t="s">
-        <v>1530</v>
+        <v>1558</v>
       </c>
       <c r="F334" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G334" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="H334" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="I334" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="J334" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="K334" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L334" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M334" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="N334" t="s">
         <v>1584</v>
@@ -19810,34 +19810,34 @@
         <v>1131</v>
       </c>
       <c r="D335" t="s">
-        <v>1368</v>
+        <v>1273</v>
       </c>
       <c r="E335" t="s">
-        <v>1558</v>
+        <v>1463</v>
       </c>
       <c r="F335" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G335" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="H335" t="s">
         <v>1577</v>
       </c>
       <c r="I335" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="J335" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K335" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L335" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M335" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N335" t="s">
         <v>1584</v>
@@ -19854,28 +19854,28 @@
         <v>1132</v>
       </c>
       <c r="D336" t="s">
-        <v>1273</v>
+        <v>1238</v>
       </c>
       <c r="E336" t="s">
-        <v>1463</v>
+        <v>1428</v>
       </c>
       <c r="F336" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G336" t="s">
         <v>1581</v>
       </c>
       <c r="H336" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I336" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J336" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="K336" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="L336" t="s">
         <v>1578</v>
@@ -19898,31 +19898,31 @@
         <v>1133</v>
       </c>
       <c r="D337" t="s">
-        <v>1238</v>
+        <v>1314</v>
       </c>
       <c r="E337" t="s">
-        <v>1428</v>
+        <v>1504</v>
       </c>
       <c r="F337" t="s">
         <v>1572</v>
       </c>
       <c r="G337" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="H337" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I337" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J337" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K337" t="s">
         <v>1579</v>
       </c>
       <c r="L337" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="M337" t="s">
         <v>1582</v>
@@ -19942,31 +19942,31 @@
         <v>1134</v>
       </c>
       <c r="D338" t="s">
-        <v>1314</v>
+        <v>1369</v>
       </c>
       <c r="E338" t="s">
-        <v>1504</v>
+        <v>1559</v>
       </c>
       <c r="F338" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="G338" t="s">
         <v>1577</v>
       </c>
       <c r="H338" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I338" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J338" t="s">
         <v>1578</v>
       </c>
       <c r="K338" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L338" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="M338" t="s">
         <v>1582</v>
@@ -19986,13 +19986,13 @@
         <v>1135</v>
       </c>
       <c r="D339" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E339" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="F339" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="G339" t="s">
         <v>1577</v>
@@ -20004,16 +20004,16 @@
         <v>1583</v>
       </c>
       <c r="J339" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K339" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L339" t="s">
         <v>1579</v>
       </c>
       <c r="M339" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="N339" t="s">
         <v>1584</v>
@@ -20030,13 +20030,13 @@
         <v>1136</v>
       </c>
       <c r="D340" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="E340" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="F340" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="G340" t="s">
         <v>1577</v>
@@ -20048,16 +20048,16 @@
         <v>1583</v>
       </c>
       <c r="J340" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K340" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L340" t="s">
         <v>1579</v>
       </c>
       <c r="M340" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="N340" t="s">
         <v>1584</v>
@@ -20074,31 +20074,31 @@
         <v>1137</v>
       </c>
       <c r="D341" t="s">
-        <v>1371</v>
+        <v>1236</v>
       </c>
       <c r="E341" t="s">
-        <v>1561</v>
+        <v>1426</v>
       </c>
       <c r="F341" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="G341" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H341" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I341" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="J341" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K341" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="L341" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="M341" t="s">
         <v>1582</v>
@@ -20118,34 +20118,34 @@
         <v>1138</v>
       </c>
       <c r="D342" t="s">
-        <v>1236</v>
+        <v>1372</v>
       </c>
       <c r="E342" t="s">
-        <v>1426</v>
+        <v>1562</v>
       </c>
       <c r="F342" t="s">
         <v>1572</v>
       </c>
       <c r="G342" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H342" t="s">
         <v>1578</v>
       </c>
       <c r="I342" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="J342" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="K342" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L342" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="M342" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="N342" t="s">
         <v>1584</v>
@@ -20162,13 +20162,13 @@
         <v>1139</v>
       </c>
       <c r="D343" t="s">
-        <v>1372</v>
+        <v>1214</v>
       </c>
       <c r="E343" t="s">
-        <v>1562</v>
+        <v>1404</v>
       </c>
       <c r="F343" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G343" t="s">
         <v>1577</v>
@@ -20177,16 +20177,16 @@
         <v>1578</v>
       </c>
       <c r="I343" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J343" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="K343" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="L343" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="M343" t="s">
         <v>1581</v>
@@ -20206,10 +20206,10 @@
         <v>1140</v>
       </c>
       <c r="D344" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E344" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="F344" t="s">
         <v>1571</v>
@@ -20250,10 +20250,10 @@
         <v>1141</v>
       </c>
       <c r="D345" t="s">
-        <v>1216</v>
+        <v>1365</v>
       </c>
       <c r="E345" t="s">
-        <v>1406</v>
+        <v>1555</v>
       </c>
       <c r="F345" t="s">
         <v>1571</v>
@@ -20262,22 +20262,22 @@
         <v>1577</v>
       </c>
       <c r="H345" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="I345" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="J345" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="K345" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="L345" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="M345" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N345" t="s">
         <v>1584</v>
@@ -20294,34 +20294,34 @@
         <v>1142</v>
       </c>
       <c r="D346" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E346" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="F346" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="G346" t="s">
         <v>1577</v>
       </c>
       <c r="H346" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="I346" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J346" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="K346" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="L346" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M346" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N346" t="s">
         <v>1584</v>
@@ -20338,13 +20338,13 @@
         <v>1143</v>
       </c>
       <c r="D347" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="E347" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="F347" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="G347" t="s">
         <v>1577</v>
@@ -20353,19 +20353,19 @@
         <v>1578</v>
       </c>
       <c r="I347" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="J347" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="K347" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="L347" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="M347" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="N347" t="s">
         <v>1584</v>
@@ -20382,10 +20382,10 @@
         <v>1144</v>
       </c>
       <c r="D348" t="s">
-        <v>1373</v>
+        <v>1327</v>
       </c>
       <c r="E348" t="s">
-        <v>1563</v>
+        <v>1517</v>
       </c>
       <c r="F348" t="s">
         <v>1573</v>
@@ -20394,22 +20394,22 @@
         <v>1577</v>
       </c>
       <c r="H348" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="I348" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="J348" t="s">
         <v>1579</v>
       </c>
       <c r="K348" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="L348" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="M348" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="N348" t="s">
         <v>1584</v>
@@ -20426,13 +20426,13 @@
         <v>1145</v>
       </c>
       <c r="D349" t="s">
-        <v>1327</v>
+        <v>1288</v>
       </c>
       <c r="E349" t="s">
-        <v>1517</v>
+        <v>1478</v>
       </c>
       <c r="F349" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G349" t="s">
         <v>1577</v>
@@ -20441,19 +20441,19 @@
         <v>1580</v>
       </c>
       <c r="I349" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="J349" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="K349" t="s">
         <v>1578</v>
       </c>
       <c r="L349" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M349" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N349" t="s">
         <v>1584</v>
@@ -20470,34 +20470,34 @@
         <v>1146</v>
       </c>
       <c r="D350" t="s">
-        <v>1288</v>
+        <v>1267</v>
       </c>
       <c r="E350" t="s">
-        <v>1478</v>
+        <v>1457</v>
       </c>
       <c r="F350" t="s">
         <v>1572</v>
       </c>
       <c r="G350" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="H350" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I350" t="s">
         <v>1581</v>
       </c>
       <c r="J350" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="K350" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="L350" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="M350" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N350" t="s">
         <v>1584</v>
@@ -20514,34 +20514,34 @@
         <v>1147</v>
       </c>
       <c r="D351" t="s">
-        <v>1267</v>
+        <v>1227</v>
       </c>
       <c r="E351" t="s">
-        <v>1457</v>
+        <v>1417</v>
       </c>
       <c r="F351" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G351" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H351" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="I351" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="J351" t="s">
         <v>1578</v>
       </c>
       <c r="K351" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="L351" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M351" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="N351" t="s">
         <v>1584</v>
@@ -20558,34 +20558,34 @@
         <v>1148</v>
       </c>
       <c r="D352" t="s">
-        <v>1227</v>
+        <v>1345</v>
       </c>
       <c r="E352" t="s">
-        <v>1417</v>
+        <v>1535</v>
       </c>
       <c r="F352" t="s">
         <v>1571</v>
       </c>
       <c r="G352" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H352" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="I352" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="J352" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="K352" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="L352" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="M352" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="N352" t="s">
         <v>1584</v>
@@ -20602,10 +20602,10 @@
         <v>1149</v>
       </c>
       <c r="D353" t="s">
-        <v>1345</v>
+        <v>1291</v>
       </c>
       <c r="E353" t="s">
-        <v>1535</v>
+        <v>1481</v>
       </c>
       <c r="F353" t="s">
         <v>1571</v>
@@ -20617,16 +20617,16 @@
         <v>1580</v>
       </c>
       <c r="I353" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="J353" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="K353" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L353" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="M353" t="s">
         <v>1578</v>
@@ -20646,34 +20646,34 @@
         <v>1150</v>
       </c>
       <c r="D354" t="s">
-        <v>1291</v>
+        <v>1276</v>
       </c>
       <c r="E354" t="s">
-        <v>1481</v>
+        <v>1466</v>
       </c>
       <c r="F354" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G354" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H354" t="s">
         <v>1580</v>
       </c>
       <c r="I354" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="J354" t="s">
         <v>1583</v>
       </c>
       <c r="K354" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="L354" t="s">
         <v>1579</v>
       </c>
       <c r="M354" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="N354" t="s">
         <v>1584</v>
@@ -20690,34 +20690,34 @@
         <v>1151</v>
       </c>
       <c r="D355" t="s">
-        <v>1276</v>
+        <v>1266</v>
       </c>
       <c r="E355" t="s">
-        <v>1466</v>
+        <v>1456</v>
       </c>
       <c r="F355" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G355" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H355" t="s">
         <v>1580</v>
       </c>
       <c r="I355" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="J355" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="K355" t="s">
         <v>1581</v>
       </c>
       <c r="L355" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="M355" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N355" t="s">
         <v>1584</v>
@@ -20734,34 +20734,34 @@
         <v>1152</v>
       </c>
       <c r="D356" t="s">
-        <v>1266</v>
+        <v>1214</v>
       </c>
       <c r="E356" t="s">
-        <v>1456</v>
+        <v>1404</v>
       </c>
       <c r="F356" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G356" t="s">
         <v>1577</v>
       </c>
       <c r="H356" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I356" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="J356" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="K356" t="s">
         <v>1581</v>
       </c>
       <c r="L356" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="M356" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N356" t="s">
         <v>1584</v>
@@ -20778,34 +20778,34 @@
         <v>1153</v>
       </c>
       <c r="D357" t="s">
-        <v>1214</v>
+        <v>1230</v>
       </c>
       <c r="E357" t="s">
-        <v>1404</v>
+        <v>1420</v>
       </c>
       <c r="F357" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G357" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="H357" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="I357" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="J357" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="K357" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L357" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="M357" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="N357" t="s">
         <v>1584</v>
@@ -20822,34 +20822,34 @@
         <v>1154</v>
       </c>
       <c r="D358" t="s">
-        <v>1230</v>
+        <v>1278</v>
       </c>
       <c r="E358" t="s">
-        <v>1420</v>
+        <v>1468</v>
       </c>
       <c r="F358" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G358" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="H358" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I358" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="J358" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="K358" t="s">
         <v>1579</v>
       </c>
       <c r="L358" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M358" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="N358" t="s">
         <v>1584</v>
@@ -20866,19 +20866,19 @@
         <v>1155</v>
       </c>
       <c r="D359" t="s">
-        <v>1278</v>
+        <v>1297</v>
       </c>
       <c r="E359" t="s">
-        <v>1468</v>
+        <v>1487</v>
       </c>
       <c r="F359" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G359" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H359" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="I359" t="s">
         <v>1580</v>
@@ -20887,10 +20887,10 @@
         <v>1583</v>
       </c>
       <c r="K359" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L359" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="M359" t="s">
         <v>1582</v>
@@ -20910,34 +20910,34 @@
         <v>1156</v>
       </c>
       <c r="D360" t="s">
-        <v>1297</v>
+        <v>1211</v>
       </c>
       <c r="E360" t="s">
-        <v>1487</v>
+        <v>1401</v>
       </c>
       <c r="F360" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G360" t="s">
         <v>1578</v>
       </c>
       <c r="H360" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="I360" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="J360" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="K360" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L360" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="M360" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N360" t="s">
         <v>1584</v>
@@ -20954,34 +20954,34 @@
         <v>1157</v>
       </c>
       <c r="D361" t="s">
-        <v>1211</v>
+        <v>1372</v>
       </c>
       <c r="E361" t="s">
-        <v>1401</v>
+        <v>1562</v>
       </c>
       <c r="F361" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G361" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="H361" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I361" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="J361" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K361" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="L361" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M361" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="N361" t="s">
         <v>1584</v>
@@ -20998,34 +20998,34 @@
         <v>1158</v>
       </c>
       <c r="D362" t="s">
-        <v>1372</v>
+        <v>1257</v>
       </c>
       <c r="E362" t="s">
-        <v>1562</v>
+        <v>1447</v>
       </c>
       <c r="F362" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G362" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="H362" t="s">
         <v>1580</v>
       </c>
       <c r="I362" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="J362" t="s">
         <v>1579</v>
       </c>
       <c r="K362" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="L362" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M362" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="N362" t="s">
         <v>1584</v>
@@ -21042,31 +21042,31 @@
         <v>1159</v>
       </c>
       <c r="D363" t="s">
-        <v>1257</v>
+        <v>1226</v>
       </c>
       <c r="E363" t="s">
-        <v>1447</v>
+        <v>1416</v>
       </c>
       <c r="F363" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G363" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="H363" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I363" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="J363" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K363" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L363" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="M363" t="s">
         <v>1582</v>
@@ -21086,31 +21086,31 @@
         <v>1160</v>
       </c>
       <c r="D364" t="s">
-        <v>1226</v>
+        <v>1270</v>
       </c>
       <c r="E364" t="s">
-        <v>1416</v>
+        <v>1460</v>
       </c>
       <c r="F364" t="s">
         <v>1572</v>
       </c>
       <c r="G364" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="H364" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="I364" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="J364" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K364" t="s">
         <v>1581</v>
       </c>
       <c r="L364" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="M364" t="s">
         <v>1582</v>
@@ -21130,31 +21130,31 @@
         <v>1161</v>
       </c>
       <c r="D365" t="s">
-        <v>1270</v>
+        <v>1237</v>
       </c>
       <c r="E365" t="s">
-        <v>1460</v>
+        <v>1427</v>
       </c>
       <c r="F365" t="s">
         <v>1572</v>
       </c>
       <c r="G365" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H365" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="I365" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="J365" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="K365" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L365" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="M365" t="s">
         <v>1582</v>
@@ -21174,34 +21174,34 @@
         <v>1162</v>
       </c>
       <c r="D366" t="s">
-        <v>1237</v>
+        <v>1323</v>
       </c>
       <c r="E366" t="s">
-        <v>1427</v>
+        <v>1513</v>
       </c>
       <c r="F366" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G366" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H366" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="I366" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="J366" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="K366" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="L366" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="M366" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="N366" t="s">
         <v>1584</v>
@@ -21218,10 +21218,10 @@
         <v>1163</v>
       </c>
       <c r="D367" t="s">
-        <v>1323</v>
+        <v>1374</v>
       </c>
       <c r="E367" t="s">
-        <v>1513</v>
+        <v>1564</v>
       </c>
       <c r="F367" t="s">
         <v>1571</v>
@@ -21262,34 +21262,34 @@
         <v>1164</v>
       </c>
       <c r="D368" t="s">
-        <v>1374</v>
+        <v>1210</v>
       </c>
       <c r="E368" t="s">
-        <v>1564</v>
+        <v>1400</v>
       </c>
       <c r="F368" t="s">
         <v>1571</v>
       </c>
       <c r="G368" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H368" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="I368" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="J368" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="K368" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="L368" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="M368" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="N368" t="s">
         <v>1584</v>
@@ -21306,31 +21306,31 @@
         <v>1165</v>
       </c>
       <c r="D369" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="E369" t="s">
-        <v>1400</v>
+        <v>1412</v>
       </c>
       <c r="F369" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="G369" t="s">
         <v>1577</v>
       </c>
       <c r="H369" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="I369" t="s">
         <v>1583</v>
       </c>
       <c r="J369" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K369" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="L369" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="M369" t="s">
         <v>1582</v>
@@ -21350,34 +21350,34 @@
         <v>1166</v>
       </c>
       <c r="D370" t="s">
-        <v>1222</v>
+        <v>1375</v>
       </c>
       <c r="E370" t="s">
-        <v>1412</v>
+        <v>1565</v>
       </c>
       <c r="F370" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="G370" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H370" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="I370" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="J370" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="K370" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="L370" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="M370" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="N370" t="s">
         <v>1584</v>
@@ -21394,34 +21394,34 @@
         <v>1167</v>
       </c>
       <c r="D371" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E371" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F371" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="G371" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H371" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="I371" t="s">
         <v>1579</v>
       </c>
       <c r="J371" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="K371" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="L371" t="s">
         <v>1581</v>
       </c>
       <c r="M371" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="N371" t="s">
         <v>1584</v>
@@ -21438,34 +21438,34 @@
         <v>1168</v>
       </c>
       <c r="D372" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="E372" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="F372" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="G372" t="s">
         <v>1577</v>
       </c>
       <c r="H372" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I372" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="J372" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="K372" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L372" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M372" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N372" t="s">
         <v>1584</v>
@@ -21482,13 +21482,13 @@
         <v>1169</v>
       </c>
       <c r="D373" t="s">
-        <v>1377</v>
+        <v>1220</v>
       </c>
       <c r="E373" t="s">
-        <v>1567</v>
+        <v>1410</v>
       </c>
       <c r="F373" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G373" t="s">
         <v>1577</v>
@@ -21503,13 +21503,13 @@
         <v>1578</v>
       </c>
       <c r="K373" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L373" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M373" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N373" t="s">
         <v>1584</v>
@@ -21526,13 +21526,13 @@
         <v>1170</v>
       </c>
       <c r="D374" t="s">
-        <v>1220</v>
+        <v>1202</v>
       </c>
       <c r="E374" t="s">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F374" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G374" t="s">
         <v>1577</v>
@@ -21544,16 +21544,16 @@
         <v>1583</v>
       </c>
       <c r="J374" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="K374" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L374" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M374" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="N374" t="s">
         <v>1584</v>
@@ -21570,22 +21570,22 @@
         <v>1171</v>
       </c>
       <c r="D375" t="s">
-        <v>1202</v>
+        <v>1260</v>
       </c>
       <c r="E375" t="s">
-        <v>1392</v>
+        <v>1450</v>
       </c>
       <c r="F375" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G375" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H375" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="I375" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="J375" t="s">
         <v>1579</v>
@@ -21594,10 +21594,10 @@
         <v>1581</v>
       </c>
       <c r="L375" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="M375" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="N375" t="s">
         <v>1584</v>
@@ -21614,31 +21614,31 @@
         <v>1172</v>
       </c>
       <c r="D376" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="E376" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="F376" t="s">
         <v>1572</v>
       </c>
       <c r="G376" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H376" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="I376" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="J376" t="s">
         <v>1579</v>
       </c>
       <c r="K376" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="L376" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="M376" t="s">
         <v>1583</v>
@@ -21658,34 +21658,34 @@
         <v>1173</v>
       </c>
       <c r="D377" t="s">
-        <v>1266</v>
+        <v>1206</v>
       </c>
       <c r="E377" t="s">
-        <v>1456</v>
+        <v>1396</v>
       </c>
       <c r="F377" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G377" t="s">
         <v>1577</v>
       </c>
       <c r="H377" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="I377" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J377" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K377" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="L377" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M377" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="N377" t="s">
         <v>1584</v>
@@ -21702,34 +21702,34 @@
         <v>1174</v>
       </c>
       <c r="D378" t="s">
-        <v>1206</v>
+        <v>1228</v>
       </c>
       <c r="E378" t="s">
-        <v>1396</v>
+        <v>1418</v>
       </c>
       <c r="F378" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G378" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H378" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="I378" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J378" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="K378" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L378" t="s">
         <v>1582</v>
       </c>
       <c r="M378" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N378" t="s">
         <v>1584</v>
@@ -21746,34 +21746,34 @@
         <v>1175</v>
       </c>
       <c r="D379" t="s">
-        <v>1228</v>
+        <v>1332</v>
       </c>
       <c r="E379" t="s">
-        <v>1418</v>
+        <v>1522</v>
       </c>
       <c r="F379" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="G379" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H379" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I379" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J379" t="s">
-        <v>1583</v>
+        <v>1579</v>
       </c>
       <c r="K379" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L379" t="s">
         <v>1582</v>
       </c>
       <c r="M379" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N379" t="s">
         <v>1584</v>
@@ -21790,10 +21790,10 @@
         <v>1176</v>
       </c>
       <c r="D380" t="s">
-        <v>1332</v>
+        <v>1202</v>
       </c>
       <c r="E380" t="s">
-        <v>1522</v>
+        <v>1392</v>
       </c>
       <c r="F380" t="s">
         <v>1572</v>
@@ -21802,13 +21802,13 @@
         <v>1577</v>
       </c>
       <c r="H380" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I380" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J380" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="K380" t="s">
         <v>1578</v>
@@ -21817,7 +21817,7 @@
         <v>1582</v>
       </c>
       <c r="M380" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N380" t="s">
         <v>1584</v>
@@ -21834,28 +21834,28 @@
         <v>1177</v>
       </c>
       <c r="D381" t="s">
-        <v>1202</v>
+        <v>1352</v>
       </c>
       <c r="E381" t="s">
-        <v>1392</v>
+        <v>1542</v>
       </c>
       <c r="F381" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="G381" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="H381" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="I381" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J381" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K381" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="L381" t="s">
         <v>1582</v>
@@ -21878,25 +21878,25 @@
         <v>1178</v>
       </c>
       <c r="D382" t="s">
-        <v>1352</v>
+        <v>1257</v>
       </c>
       <c r="E382" t="s">
-        <v>1542</v>
+        <v>1447</v>
       </c>
       <c r="F382" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G382" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="H382" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I382" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="J382" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="K382" t="s">
         <v>1581</v>
@@ -21922,31 +21922,31 @@
         <v>1179</v>
       </c>
       <c r="D383" t="s">
-        <v>1257</v>
+        <v>1239</v>
       </c>
       <c r="E383" t="s">
-        <v>1447</v>
+        <v>1429</v>
       </c>
       <c r="F383" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G383" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H383" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I383" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="J383" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="K383" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L383" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M383" t="s">
         <v>1579</v>
@@ -21966,25 +21966,25 @@
         <v>1180</v>
       </c>
       <c r="D384" t="s">
-        <v>1239</v>
+        <v>1347</v>
       </c>
       <c r="E384" t="s">
-        <v>1429</v>
+        <v>1537</v>
       </c>
       <c r="F384" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G384" t="s">
         <v>1577</v>
       </c>
       <c r="H384" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I384" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J384" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="K384" t="s">
         <v>1578</v>
@@ -21993,7 +21993,7 @@
         <v>1581</v>
       </c>
       <c r="M384" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N384" t="s">
         <v>1584</v>
@@ -22010,34 +22010,34 @@
         <v>1181</v>
       </c>
       <c r="D385" t="s">
-        <v>1347</v>
+        <v>1321</v>
       </c>
       <c r="E385" t="s">
-        <v>1537</v>
+        <v>1511</v>
       </c>
       <c r="F385" t="s">
         <v>1571</v>
       </c>
       <c r="G385" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="H385" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I385" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="J385" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="K385" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="L385" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M385" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N385" t="s">
         <v>1584</v>
@@ -22054,34 +22054,34 @@
         <v>1182</v>
       </c>
       <c r="D386" t="s">
-        <v>1321</v>
+        <v>1377</v>
       </c>
       <c r="E386" t="s">
-        <v>1511</v>
+        <v>1567</v>
       </c>
       <c r="F386" t="s">
         <v>1571</v>
       </c>
       <c r="G386" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="H386" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="I386" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="J386" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K386" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="L386" t="s">
         <v>1582</v>
       </c>
       <c r="M386" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N386" t="s">
         <v>1584</v>
@@ -22098,34 +22098,34 @@
         <v>1183</v>
       </c>
       <c r="D387" t="s">
-        <v>1377</v>
+        <v>1225</v>
       </c>
       <c r="E387" t="s">
-        <v>1567</v>
+        <v>1415</v>
       </c>
       <c r="F387" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G387" t="s">
         <v>1577</v>
       </c>
       <c r="H387" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="I387" t="s">
         <v>1583</v>
       </c>
       <c r="J387" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K387" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L387" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M387" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="N387" t="s">
         <v>1584</v>
@@ -22142,34 +22142,34 @@
         <v>1184</v>
       </c>
       <c r="D388" t="s">
-        <v>1225</v>
+        <v>1239</v>
       </c>
       <c r="E388" t="s">
-        <v>1415</v>
+        <v>1429</v>
       </c>
       <c r="F388" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="G388" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H388" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="I388" t="s">
         <v>1583</v>
       </c>
       <c r="J388" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="K388" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="L388" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M388" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N388" t="s">
         <v>1584</v>
@@ -22186,34 +22186,34 @@
         <v>1185</v>
       </c>
       <c r="D389" t="s">
-        <v>1239</v>
+        <v>1378</v>
       </c>
       <c r="E389" t="s">
-        <v>1429</v>
+        <v>1568</v>
       </c>
       <c r="F389" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="G389" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H389" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="I389" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J389" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K389" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L389" t="s">
         <v>1582</v>
       </c>
       <c r="M389" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N389" t="s">
         <v>1584</v>
@@ -22230,34 +22230,34 @@
         <v>1186</v>
       </c>
       <c r="D390" t="s">
-        <v>1378</v>
+        <v>1357</v>
       </c>
       <c r="E390" t="s">
-        <v>1568</v>
+        <v>1547</v>
       </c>
       <c r="F390" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="G390" t="s">
         <v>1577</v>
       </c>
       <c r="H390" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I390" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J390" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="K390" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L390" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M390" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N390" t="s">
         <v>1584</v>
@@ -22274,13 +22274,13 @@
         <v>1187</v>
       </c>
       <c r="D391" t="s">
-        <v>1357</v>
+        <v>1379</v>
       </c>
       <c r="E391" t="s">
-        <v>1547</v>
+        <v>1569</v>
       </c>
       <c r="F391" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G391" t="s">
         <v>1577</v>
@@ -22292,13 +22292,13 @@
         <v>1583</v>
       </c>
       <c r="J391" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="K391" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L391" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M391" t="s">
         <v>1579</v>
@@ -22318,34 +22318,34 @@
         <v>1188</v>
       </c>
       <c r="D392" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E392" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F392" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G392" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H392" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="I392" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J392" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="K392" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="L392" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M392" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N392" t="s">
         <v>1584</v>
@@ -22362,34 +22362,34 @@
         <v>1189</v>
       </c>
       <c r="D393" t="s">
-        <v>1380</v>
+        <v>1266</v>
       </c>
       <c r="E393" t="s">
-        <v>1570</v>
+        <v>1456</v>
       </c>
       <c r="F393" t="s">
         <v>1572</v>
       </c>
       <c r="G393" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H393" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="I393" t="s">
         <v>1580</v>
       </c>
       <c r="J393" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K393" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="L393" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M393" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N393" t="s">
         <v>1584</v>
@@ -22406,16 +22406,16 @@
         <v>1190</v>
       </c>
       <c r="D394">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="E394">
-        <v>67.55</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F394" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G394" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H394" t="s">
         <v>1583</v>
@@ -22424,16 +22424,16 @@
         <v>1580</v>
       </c>
       <c r="J394" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K394" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L394" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M394" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N394" t="s">
         <v>1584</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1222,21 +1222,21 @@
     <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
   </si>
   <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
     <t>حسام اسامه سعد حسين</t>
   </si>
   <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2398,21 +2398,21 @@
     <t>30509112403153</t>
   </si>
   <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
     <t>30511082403239</t>
   </si>
   <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3574,19 +3574,19 @@
     <t>01006926646</t>
   </si>
   <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
     <t>01007937368</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01121846011</t>
   </si>
   <si>
     <t>1353</t>
@@ -22230,13 +22230,13 @@
         <v>1186</v>
       </c>
       <c r="D390" t="s">
-        <v>1357</v>
+        <v>1379</v>
       </c>
       <c r="E390" t="s">
-        <v>1547</v>
+        <v>1569</v>
       </c>
       <c r="F390" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G390" t="s">
         <v>1577</v>
@@ -22248,13 +22248,13 @@
         <v>1583</v>
       </c>
       <c r="J390" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="K390" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L390" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M390" t="s">
         <v>1579</v>
@@ -22274,34 +22274,34 @@
         <v>1187</v>
       </c>
       <c r="D391" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E391" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F391" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G391" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H391" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="I391" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J391" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="K391" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="L391" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M391" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N391" t="s">
         <v>1584</v>
@@ -22318,34 +22318,34 @@
         <v>1188</v>
       </c>
       <c r="D392" t="s">
-        <v>1380</v>
+        <v>1266</v>
       </c>
       <c r="E392" t="s">
-        <v>1570</v>
+        <v>1456</v>
       </c>
       <c r="F392" t="s">
         <v>1572</v>
       </c>
       <c r="G392" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H392" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="I392" t="s">
         <v>1580</v>
       </c>
       <c r="J392" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K392" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="L392" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M392" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N392" t="s">
         <v>1584</v>
@@ -22362,16 +22362,16 @@
         <v>1189</v>
       </c>
       <c r="D393" t="s">
-        <v>1266</v>
+        <v>1311</v>
       </c>
       <c r="E393" t="s">
-        <v>1456</v>
+        <v>1501</v>
       </c>
       <c r="F393" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G393" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H393" t="s">
         <v>1583</v>
@@ -22380,16 +22380,16 @@
         <v>1580</v>
       </c>
       <c r="J393" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K393" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L393" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M393" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N393" t="s">
         <v>1584</v>
@@ -22406,34 +22406,34 @@
         <v>1190</v>
       </c>
       <c r="D394">
-        <v>1347</v>
+        <v>1384</v>
       </c>
       <c r="E394">
-        <v>67.34999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="F394" t="s">
         <v>1571</v>
       </c>
       <c r="G394" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H394" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I394" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J394" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="K394" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L394" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="M394" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N394" t="s">
         <v>1584</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1231,12 +1231,12 @@
     <t>مصطفى صافى توفيق صالح</t>
   </si>
   <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
     <t>عبدالله محمد محمد احمد</t>
   </si>
   <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2407,12 +2407,12 @@
     <t>30405042403592</t>
   </si>
   <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
     <t>30412262402097</t>
   </si>
   <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3583,10 +3583,10 @@
     <t>01208634063</t>
   </si>
   <si>
+    <t>01007937368</t>
+  </si>
+  <si>
     <t>01121846011</t>
-  </si>
-  <si>
-    <t>01007937368</t>
   </si>
   <si>
     <t>1353</t>
@@ -22362,34 +22362,34 @@
         <v>1189</v>
       </c>
       <c r="D393" t="s">
-        <v>1311</v>
+        <v>1357</v>
       </c>
       <c r="E393" t="s">
-        <v>1501</v>
+        <v>1547</v>
       </c>
       <c r="F393" t="s">
         <v>1571</v>
       </c>
       <c r="G393" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H393" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I393" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J393" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="K393" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L393" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="M393" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N393" t="s">
         <v>1584</v>
@@ -22406,34 +22406,34 @@
         <v>1190</v>
       </c>
       <c r="D394">
-        <v>1384</v>
+        <v>1347</v>
       </c>
       <c r="E394">
-        <v>69.2</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F394" t="s">
         <v>1571</v>
       </c>
       <c r="G394" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H394" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I394" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J394" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="K394" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L394" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="M394" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N394" t="s">
         <v>1584</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1195,48 +1195,48 @@
     <t>فاطمه طاهر عبد الحميد عبد العال</t>
   </si>
   <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
     <t>شروق محمد هاشم احمد</t>
   </si>
   <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2371,48 +2371,48 @@
     <t>30504252401205</t>
   </si>
   <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
     <t>30510302401007</t>
   </si>
   <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3547,46 +3547,46 @@
     <t>01060458756</t>
   </si>
   <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
     <t>01152380733</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01121846011</t>
   </si>
   <si>
     <t>1353</t>
@@ -21834,25 +21834,25 @@
         <v>1177</v>
       </c>
       <c r="D381" t="s">
-        <v>1352</v>
+        <v>1257</v>
       </c>
       <c r="E381" t="s">
-        <v>1542</v>
+        <v>1447</v>
       </c>
       <c r="F381" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G381" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="H381" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="I381" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="J381" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="K381" t="s">
         <v>1581</v>
@@ -21878,31 +21878,31 @@
         <v>1178</v>
       </c>
       <c r="D382" t="s">
-        <v>1257</v>
+        <v>1239</v>
       </c>
       <c r="E382" t="s">
-        <v>1447</v>
+        <v>1429</v>
       </c>
       <c r="F382" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G382" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H382" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I382" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="J382" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="K382" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="L382" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M382" t="s">
         <v>1579</v>
@@ -21922,25 +21922,25 @@
         <v>1179</v>
       </c>
       <c r="D383" t="s">
-        <v>1239</v>
+        <v>1347</v>
       </c>
       <c r="E383" t="s">
-        <v>1429</v>
+        <v>1537</v>
       </c>
       <c r="F383" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G383" t="s">
         <v>1577</v>
       </c>
       <c r="H383" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I383" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J383" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="K383" t="s">
         <v>1578</v>
@@ -21949,7 +21949,7 @@
         <v>1581</v>
       </c>
       <c r="M383" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N383" t="s">
         <v>1584</v>
@@ -21966,34 +21966,34 @@
         <v>1180</v>
       </c>
       <c r="D384" t="s">
-        <v>1347</v>
+        <v>1321</v>
       </c>
       <c r="E384" t="s">
-        <v>1537</v>
+        <v>1511</v>
       </c>
       <c r="F384" t="s">
         <v>1571</v>
       </c>
       <c r="G384" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="H384" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I384" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="J384" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="K384" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="L384" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M384" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N384" t="s">
         <v>1584</v>
@@ -22010,34 +22010,34 @@
         <v>1181</v>
       </c>
       <c r="D385" t="s">
-        <v>1321</v>
+        <v>1377</v>
       </c>
       <c r="E385" t="s">
-        <v>1511</v>
+        <v>1567</v>
       </c>
       <c r="F385" t="s">
         <v>1571</v>
       </c>
       <c r="G385" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="H385" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="I385" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="J385" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K385" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="L385" t="s">
         <v>1582</v>
       </c>
       <c r="M385" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N385" t="s">
         <v>1584</v>
@@ -22054,34 +22054,34 @@
         <v>1182</v>
       </c>
       <c r="D386" t="s">
-        <v>1377</v>
+        <v>1225</v>
       </c>
       <c r="E386" t="s">
-        <v>1567</v>
+        <v>1415</v>
       </c>
       <c r="F386" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G386" t="s">
         <v>1577</v>
       </c>
       <c r="H386" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="I386" t="s">
         <v>1583</v>
       </c>
       <c r="J386" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K386" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L386" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M386" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="N386" t="s">
         <v>1584</v>
@@ -22098,34 +22098,34 @@
         <v>1183</v>
       </c>
       <c r="D387" t="s">
-        <v>1225</v>
+        <v>1239</v>
       </c>
       <c r="E387" t="s">
-        <v>1415</v>
+        <v>1429</v>
       </c>
       <c r="F387" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="G387" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H387" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="I387" t="s">
         <v>1583</v>
       </c>
       <c r="J387" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="K387" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="L387" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M387" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N387" t="s">
         <v>1584</v>
@@ -22142,34 +22142,34 @@
         <v>1184</v>
       </c>
       <c r="D388" t="s">
-        <v>1239</v>
+        <v>1378</v>
       </c>
       <c r="E388" t="s">
-        <v>1429</v>
+        <v>1568</v>
       </c>
       <c r="F388" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="G388" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H388" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="I388" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J388" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="K388" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="L388" t="s">
         <v>1582</v>
       </c>
       <c r="M388" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="N388" t="s">
         <v>1584</v>
@@ -22186,34 +22186,34 @@
         <v>1185</v>
       </c>
       <c r="D389" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="E389" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F389" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="G389" t="s">
         <v>1577</v>
       </c>
       <c r="H389" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I389" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J389" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="K389" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="L389" t="s">
         <v>1582</v>
       </c>
       <c r="M389" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="N389" t="s">
         <v>1584</v>
@@ -22230,34 +22230,34 @@
         <v>1186</v>
       </c>
       <c r="D390" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E390" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="F390" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G390" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="H390" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="I390" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J390" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="K390" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="L390" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M390" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N390" t="s">
         <v>1584</v>
@@ -22274,34 +22274,34 @@
         <v>1187</v>
       </c>
       <c r="D391" t="s">
-        <v>1380</v>
+        <v>1266</v>
       </c>
       <c r="E391" t="s">
-        <v>1570</v>
+        <v>1456</v>
       </c>
       <c r="F391" t="s">
         <v>1572</v>
       </c>
       <c r="G391" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H391" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="I391" t="s">
         <v>1580</v>
       </c>
       <c r="J391" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K391" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="L391" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="M391" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N391" t="s">
         <v>1584</v>
@@ -22318,31 +22318,31 @@
         <v>1188</v>
       </c>
       <c r="D392" t="s">
-        <v>1266</v>
+        <v>1357</v>
       </c>
       <c r="E392" t="s">
-        <v>1456</v>
+        <v>1547</v>
       </c>
       <c r="F392" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="G392" t="s">
         <v>1577</v>
       </c>
       <c r="H392" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="I392" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J392" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="K392" t="s">
         <v>1581</v>
       </c>
       <c r="L392" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="M392" t="s">
         <v>1579</v>
@@ -22362,34 +22362,34 @@
         <v>1189</v>
       </c>
       <c r="D393" t="s">
-        <v>1357</v>
+        <v>1311</v>
       </c>
       <c r="E393" t="s">
-        <v>1547</v>
+        <v>1501</v>
       </c>
       <c r="F393" t="s">
         <v>1571</v>
       </c>
       <c r="G393" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H393" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="I393" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J393" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="K393" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L393" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="M393" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N393" t="s">
         <v>1584</v>
@@ -22406,34 +22406,34 @@
         <v>1190</v>
       </c>
       <c r="D394">
-        <v>1347</v>
+        <v>1270</v>
       </c>
       <c r="E394">
-        <v>67.34999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="F394" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G394" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="H394" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="I394" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J394" t="s">
         <v>1577</v>
       </c>
       <c r="K394" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L394" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M394" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N394" t="s">
         <v>1584</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1231,12 +1231,12 @@
     <t>حسام اسامه سعد حسين</t>
   </si>
   <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
     <t>عبدالله محمد محمد احمد</t>
   </si>
   <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2407,12 +2407,12 @@
     <t>30511082403239</t>
   </si>
   <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
     <t>30412262402097</t>
   </si>
   <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3583,10 +3583,10 @@
     <t>01007937368</t>
   </si>
   <si>
+    <t>01152380733</t>
+  </si>
+  <si>
     <t>01121846011</t>
-  </si>
-  <si>
-    <t>01152380733</t>
   </si>
   <si>
     <t>1353</t>
@@ -22362,34 +22362,34 @@
         <v>1189</v>
       </c>
       <c r="D393" t="s">
-        <v>1311</v>
+        <v>1352</v>
       </c>
       <c r="E393" t="s">
-        <v>1501</v>
+        <v>1542</v>
       </c>
       <c r="F393" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="G393" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="H393" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="I393" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="J393" t="s">
         <v>1577</v>
       </c>
       <c r="K393" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L393" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="M393" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="N393" t="s">
         <v>1584</v>
@@ -22406,34 +22406,34 @@
         <v>1190</v>
       </c>
       <c r="D394">
-        <v>1270</v>
+        <v>1347</v>
       </c>
       <c r="E394">
-        <v>63.5</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F394" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="G394" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="H394" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="I394" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="J394" t="s">
         <v>1577</v>
       </c>
       <c r="K394" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="L394" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="M394" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="N394" t="s">
         <v>1584</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1252,15 +1252,15 @@
     <t>خالد محمود ابوالعلا حمدان</t>
   </si>
   <si>
+    <t>محمود عبد العال احمد حماده</t>
+  </si>
+  <si>
+    <t>كريم عبد الصالحين دخيل ابوسمره</t>
+  </si>
+  <si>
     <t>احمد محمد رجب عبد الحكيم</t>
   </si>
   <si>
-    <t>محمود عبد العال احمد حماده</t>
-  </si>
-  <si>
-    <t>كريم عبد الصالحين دخيل ابوسمره</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2452,15 +2452,15 @@
     <t>30512272400097</t>
   </si>
   <si>
+    <t>30504182400893</t>
+  </si>
+  <si>
+    <t>30311152404492</t>
+  </si>
+  <si>
     <t>30510012412811</t>
   </si>
   <si>
-    <t>30504182400893</t>
-  </si>
-  <si>
-    <t>30311152404492</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3652,13 +3652,13 @@
     <t>01157718533</t>
   </si>
   <si>
+    <t>01055420368</t>
+  </si>
+  <si>
+    <t>01068463842</t>
+  </si>
+  <si>
     <t>01142212131</t>
-  </si>
-  <si>
-    <t>01055420368</t>
-  </si>
-  <si>
-    <t>01068463842</t>
   </si>
   <si>
     <t>1353</t>
@@ -22760,34 +22760,34 @@
         <v>1212</v>
       </c>
       <c r="D400" t="s">
-        <v>1225</v>
+        <v>1407</v>
       </c>
       <c r="E400" t="s">
-        <v>1418</v>
+        <v>1600</v>
       </c>
       <c r="F400" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="G400" t="s">
         <v>1607</v>
       </c>
       <c r="H400" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="I400" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="J400" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="K400" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L400" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="M400" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N400" t="s">
         <v>1614</v>
@@ -22804,34 +22804,34 @@
         <v>1213</v>
       </c>
       <c r="D401" t="s">
-        <v>1407</v>
+        <v>1232</v>
       </c>
       <c r="E401" t="s">
-        <v>1600</v>
+        <v>1425</v>
       </c>
       <c r="F401" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="G401" t="s">
         <v>1607</v>
       </c>
       <c r="H401" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="I401" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J401" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="K401" t="s">
         <v>1613</v>
       </c>
       <c r="L401" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M401" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N401" t="s">
         <v>1614</v>
@@ -22848,34 +22848,34 @@
         <v>1214</v>
       </c>
       <c r="D402">
-        <v>1317</v>
+        <v>1354</v>
       </c>
       <c r="E402">
-        <v>65.84999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="F402" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G402" t="s">
         <v>1607</v>
       </c>
       <c r="H402" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="I402" t="s">
         <v>1610</v>
       </c>
       <c r="J402" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="K402" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="L402" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="M402" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="N402" t="s">
         <v>1614</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -931,336 +931,336 @@
     <t>منار فتحى عبد الجليل محمد</t>
   </si>
   <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>كريم عبد الصالحين دخيل ابوسمره</t>
+  </si>
+  <si>
+    <t>محمود عبد العال احمد حماده</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
     <t>منه اسماعيل ابراهيم شحاته</t>
   </si>
   <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>كريم عبد الصالحين دخيل ابوسمره</t>
-  </si>
-  <si>
-    <t>محمود عبد العال احمد حماده</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2131,336 +2131,336 @@
     <t>30601092401047</t>
   </si>
   <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30311152404492</t>
+  </si>
+  <si>
+    <t>30504182400893</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
     <t>30405282400485</t>
   </si>
   <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30311152404492</t>
-  </si>
-  <si>
-    <t>30504182400893</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3331,334 +3331,334 @@
     <t>01026439570</t>
   </si>
   <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01068463842</t>
+  </si>
+  <si>
+    <t>01055420368</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
     <t>01037905359</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01068463842</t>
-  </si>
-  <si>
-    <t>01055420368</t>
-  </si>
-  <si>
-    <t>01142212131</t>
   </si>
   <si>
     <t>1353</t>
@@ -18052,34 +18052,34 @@
         <v>1105</v>
       </c>
       <c r="D293" t="s">
-        <v>1237</v>
+        <v>1325</v>
       </c>
       <c r="E293" t="s">
-        <v>1430</v>
+        <v>1518</v>
       </c>
       <c r="F293" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G293" t="s">
         <v>1607</v>
       </c>
       <c r="H293" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I293" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="J293" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="K293" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="L293" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="M293" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N293" t="s">
         <v>1614</v>
@@ -18096,19 +18096,19 @@
         <v>1106</v>
       </c>
       <c r="D294" t="s">
-        <v>1325</v>
+        <v>1375</v>
       </c>
       <c r="E294" t="s">
-        <v>1518</v>
+        <v>1568</v>
       </c>
       <c r="F294" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="G294" t="s">
         <v>1607</v>
       </c>
       <c r="H294" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="I294" t="s">
         <v>1609</v>
@@ -18117,7 +18117,7 @@
         <v>1613</v>
       </c>
       <c r="K294" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="L294" t="s">
         <v>1612</v>
@@ -18140,34 +18140,34 @@
         <v>1107</v>
       </c>
       <c r="D295" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E295" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="F295" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G295" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H295" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="I295" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="J295" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="K295" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="L295" t="s">
         <v>1612</v>
       </c>
       <c r="M295" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="N295" t="s">
         <v>1614</v>
@@ -18184,34 +18184,34 @@
         <v>1108</v>
       </c>
       <c r="D296" t="s">
-        <v>1376</v>
+        <v>1246</v>
       </c>
       <c r="E296" t="s">
-        <v>1569</v>
+        <v>1439</v>
       </c>
       <c r="F296" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="G296" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H296" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="I296" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="J296" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="K296" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="L296" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M296" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="N296" t="s">
         <v>1614</v>
@@ -18228,31 +18228,31 @@
         <v>1109</v>
       </c>
       <c r="D297" t="s">
-        <v>1246</v>
+        <v>1300</v>
       </c>
       <c r="E297" t="s">
-        <v>1439</v>
+        <v>1493</v>
       </c>
       <c r="F297" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="G297" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H297" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="I297" t="s">
         <v>1613</v>
       </c>
       <c r="J297" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K297" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="L297" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M297" t="s">
         <v>1609</v>
@@ -18272,28 +18272,28 @@
         <v>1110</v>
       </c>
       <c r="D298" t="s">
-        <v>1300</v>
+        <v>1319</v>
       </c>
       <c r="E298" t="s">
-        <v>1493</v>
+        <v>1512</v>
       </c>
       <c r="F298" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G298" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H298" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="I298" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J298" t="s">
         <v>1611</v>
       </c>
       <c r="K298" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="L298" t="s">
         <v>1612</v>
@@ -18316,34 +18316,34 @@
         <v>1111</v>
       </c>
       <c r="D299" t="s">
-        <v>1319</v>
+        <v>1331</v>
       </c>
       <c r="E299" t="s">
-        <v>1512</v>
+        <v>1524</v>
       </c>
       <c r="F299" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G299" t="s">
         <v>1607</v>
       </c>
       <c r="H299" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="I299" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="J299" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="K299" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="L299" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M299" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="N299" t="s">
         <v>1614</v>
@@ -18360,13 +18360,13 @@
         <v>1112</v>
       </c>
       <c r="D300" t="s">
-        <v>1331</v>
+        <v>1352</v>
       </c>
       <c r="E300" t="s">
-        <v>1524</v>
+        <v>1545</v>
       </c>
       <c r="F300" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G300" t="s">
         <v>1607</v>
@@ -18375,19 +18375,19 @@
         <v>1613</v>
       </c>
       <c r="I300" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="J300" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="K300" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L300" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M300" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="N300" t="s">
         <v>1614</v>
@@ -18404,10 +18404,10 @@
         <v>1113</v>
       </c>
       <c r="D301" t="s">
-        <v>1352</v>
+        <v>1264</v>
       </c>
       <c r="E301" t="s">
-        <v>1545</v>
+        <v>1457</v>
       </c>
       <c r="F301" t="s">
         <v>1602</v>
@@ -18419,19 +18419,19 @@
         <v>1613</v>
       </c>
       <c r="I301" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="J301" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="K301" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L301" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="M301" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="N301" t="s">
         <v>1614</v>
@@ -18448,13 +18448,13 @@
         <v>1114</v>
       </c>
       <c r="D302" t="s">
-        <v>1264</v>
+        <v>1280</v>
       </c>
       <c r="E302" t="s">
-        <v>1457</v>
+        <v>1473</v>
       </c>
       <c r="F302" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G302" t="s">
         <v>1607</v>
@@ -18463,10 +18463,10 @@
         <v>1613</v>
       </c>
       <c r="I302" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="J302" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K302" t="s">
         <v>1612</v>
@@ -18492,10 +18492,10 @@
         <v>1115</v>
       </c>
       <c r="D303" t="s">
-        <v>1280</v>
+        <v>1377</v>
       </c>
       <c r="E303" t="s">
-        <v>1473</v>
+        <v>1570</v>
       </c>
       <c r="F303" t="s">
         <v>1601</v>
@@ -18504,22 +18504,22 @@
         <v>1607</v>
       </c>
       <c r="H303" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I303" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J303" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="K303" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L303" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M303" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="N303" t="s">
         <v>1614</v>
@@ -18536,34 +18536,34 @@
         <v>1116</v>
       </c>
       <c r="D304" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="E304" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="F304" t="s">
         <v>1601</v>
       </c>
       <c r="G304" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="H304" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="I304" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="J304" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K304" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L304" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="M304" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="N304" t="s">
         <v>1614</v>
@@ -18580,10 +18580,10 @@
         <v>1117</v>
       </c>
       <c r="D305" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="E305" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F305" t="s">
         <v>1601</v>
@@ -18624,34 +18624,34 @@
         <v>1118</v>
       </c>
       <c r="D306" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E306" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="F306" t="s">
         <v>1601</v>
       </c>
       <c r="G306" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H306" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I306" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="J306" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="K306" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L306" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="M306" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="N306" t="s">
         <v>1614</v>
@@ -18668,34 +18668,34 @@
         <v>1119</v>
       </c>
       <c r="D307" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E307" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="F307" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="G307" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="H307" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="I307" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J307" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K307" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L307" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="M307" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N307" t="s">
         <v>1614</v>
@@ -18712,34 +18712,34 @@
         <v>1120</v>
       </c>
       <c r="D308" t="s">
-        <v>1381</v>
+        <v>1349</v>
       </c>
       <c r="E308" t="s">
-        <v>1574</v>
+        <v>1542</v>
       </c>
       <c r="F308" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="G308" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H308" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I308" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J308" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="K308" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L308" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="M308" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="N308" t="s">
         <v>1614</v>
@@ -18756,13 +18756,13 @@
         <v>1121</v>
       </c>
       <c r="D309" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="E309" t="s">
-        <v>1542</v>
+        <v>1548</v>
       </c>
       <c r="F309" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G309" t="s">
         <v>1607</v>
@@ -18777,13 +18777,13 @@
         <v>1609</v>
       </c>
       <c r="K309" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L309" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M309" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="N309" t="s">
         <v>1614</v>
@@ -18800,10 +18800,10 @@
         <v>1122</v>
       </c>
       <c r="D310" t="s">
-        <v>1355</v>
+        <v>1382</v>
       </c>
       <c r="E310" t="s">
-        <v>1548</v>
+        <v>1575</v>
       </c>
       <c r="F310" t="s">
         <v>1601</v>
@@ -18818,16 +18818,16 @@
         <v>1613</v>
       </c>
       <c r="J310" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="K310" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L310" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M310" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N310" t="s">
         <v>1614</v>
@@ -18844,31 +18844,31 @@
         <v>1123</v>
       </c>
       <c r="D311" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="E311" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="F311" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G311" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="H311" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I311" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="J311" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="K311" t="s">
         <v>1611</v>
       </c>
       <c r="L311" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="M311" t="s">
         <v>1609</v>
@@ -18888,34 +18888,34 @@
         <v>1124</v>
       </c>
       <c r="D312" t="s">
-        <v>1383</v>
+        <v>1348</v>
       </c>
       <c r="E312" t="s">
-        <v>1576</v>
+        <v>1541</v>
       </c>
       <c r="F312" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G312" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="H312" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="I312" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="J312" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="K312" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L312" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="M312" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N312" t="s">
         <v>1614</v>
@@ -18932,34 +18932,34 @@
         <v>1125</v>
       </c>
       <c r="D313" t="s">
-        <v>1348</v>
+        <v>1259</v>
       </c>
       <c r="E313" t="s">
-        <v>1541</v>
+        <v>1452</v>
       </c>
       <c r="F313" t="s">
         <v>1602</v>
       </c>
       <c r="G313" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="H313" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="I313" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="J313" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="K313" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="L313" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="M313" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="N313" t="s">
         <v>1614</v>
@@ -18976,34 +18976,34 @@
         <v>1126</v>
       </c>
       <c r="D314" t="s">
-        <v>1259</v>
+        <v>1296</v>
       </c>
       <c r="E314" t="s">
-        <v>1452</v>
+        <v>1489</v>
       </c>
       <c r="F314" t="s">
         <v>1602</v>
       </c>
       <c r="G314" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H314" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I314" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="J314" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="K314" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L314" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="M314" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="N314" t="s">
         <v>1614</v>
@@ -19020,34 +19020,34 @@
         <v>1127</v>
       </c>
       <c r="D315" t="s">
-        <v>1296</v>
+        <v>1325</v>
       </c>
       <c r="E315" t="s">
-        <v>1489</v>
+        <v>1518</v>
       </c>
       <c r="F315" t="s">
         <v>1602</v>
       </c>
       <c r="G315" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="H315" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="I315" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J315" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="K315" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L315" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="M315" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N315" t="s">
         <v>1614</v>
@@ -19064,34 +19064,34 @@
         <v>1128</v>
       </c>
       <c r="D316" t="s">
-        <v>1325</v>
+        <v>1296</v>
       </c>
       <c r="E316" t="s">
-        <v>1518</v>
+        <v>1489</v>
       </c>
       <c r="F316" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G316" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="H316" t="s">
         <v>1607</v>
       </c>
       <c r="I316" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J316" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="K316" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L316" t="s">
         <v>1612</v>
       </c>
       <c r="M316" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="N316" t="s">
         <v>1614</v>
@@ -19108,31 +19108,31 @@
         <v>1129</v>
       </c>
       <c r="D317" t="s">
-        <v>1296</v>
+        <v>1384</v>
       </c>
       <c r="E317" t="s">
-        <v>1489</v>
+        <v>1577</v>
       </c>
       <c r="F317" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="G317" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H317" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I317" t="s">
         <v>1613</v>
       </c>
       <c r="J317" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K317" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L317" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M317" t="s">
         <v>1608</v>
@@ -19152,10 +19152,10 @@
         <v>1130</v>
       </c>
       <c r="D318" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="E318" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="F318" t="s">
         <v>1605</v>
@@ -19170,16 +19170,16 @@
         <v>1613</v>
       </c>
       <c r="J318" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="K318" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L318" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M318" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="N318" t="s">
         <v>1614</v>
@@ -19196,13 +19196,13 @@
         <v>1131</v>
       </c>
       <c r="D319" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="E319" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="F319" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="G319" t="s">
         <v>1607</v>
@@ -19214,13 +19214,13 @@
         <v>1613</v>
       </c>
       <c r="J319" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K319" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L319" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="M319" t="s">
         <v>1609</v>
@@ -19240,34 +19240,34 @@
         <v>1132</v>
       </c>
       <c r="D320" t="s">
-        <v>1386</v>
+        <v>1365</v>
       </c>
       <c r="E320" t="s">
-        <v>1579</v>
+        <v>1558</v>
       </c>
       <c r="F320" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G320" t="s">
         <v>1607</v>
       </c>
       <c r="H320" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I320" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J320" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="K320" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L320" t="s">
         <v>1608</v>
       </c>
       <c r="M320" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N320" t="s">
         <v>1614</v>
@@ -19284,25 +19284,25 @@
         <v>1133</v>
       </c>
       <c r="D321" t="s">
-        <v>1365</v>
+        <v>1236</v>
       </c>
       <c r="E321" t="s">
-        <v>1558</v>
+        <v>1429</v>
       </c>
       <c r="F321" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="G321" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="H321" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I321" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J321" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="K321" t="s">
         <v>1611</v>
@@ -19328,31 +19328,31 @@
         <v>1134</v>
       </c>
       <c r="D322" t="s">
-        <v>1236</v>
+        <v>1305</v>
       </c>
       <c r="E322" t="s">
-        <v>1429</v>
+        <v>1498</v>
       </c>
       <c r="F322" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="G322" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H322" t="s">
         <v>1610</v>
       </c>
       <c r="I322" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="J322" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="K322" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L322" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="M322" t="s">
         <v>1612</v>
@@ -19372,34 +19372,34 @@
         <v>1135</v>
       </c>
       <c r="D323" t="s">
-        <v>1305</v>
+        <v>1387</v>
       </c>
       <c r="E323" t="s">
-        <v>1498</v>
+        <v>1580</v>
       </c>
       <c r="F323" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G323" t="s">
         <v>1607</v>
       </c>
       <c r="H323" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I323" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="J323" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="K323" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L323" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="M323" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N323" t="s">
         <v>1614</v>
@@ -19416,34 +19416,34 @@
         <v>1136</v>
       </c>
       <c r="D324" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="E324" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F324" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G324" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H324" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="I324" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="J324" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K324" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L324" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="M324" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N324" t="s">
         <v>1614</v>
@@ -19460,34 +19460,34 @@
         <v>1137</v>
       </c>
       <c r="D325" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E325" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="F325" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="G325" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="H325" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="I325" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="J325" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="K325" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="L325" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="M325" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N325" t="s">
         <v>1614</v>
@@ -19504,34 +19504,34 @@
         <v>1138</v>
       </c>
       <c r="D326" t="s">
-        <v>1389</v>
+        <v>1265</v>
       </c>
       <c r="E326" t="s">
-        <v>1582</v>
+        <v>1458</v>
       </c>
       <c r="F326" t="s">
         <v>1603</v>
       </c>
       <c r="G326" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="H326" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="I326" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J326" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="K326" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="L326" t="s">
         <v>1612</v>
       </c>
       <c r="M326" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N326" t="s">
         <v>1614</v>
@@ -19548,10 +19548,10 @@
         <v>1139</v>
       </c>
       <c r="D327" t="s">
-        <v>1265</v>
+        <v>1390</v>
       </c>
       <c r="E327" t="s">
-        <v>1458</v>
+        <v>1583</v>
       </c>
       <c r="F327" t="s">
         <v>1603</v>
@@ -19560,13 +19560,13 @@
         <v>1608</v>
       </c>
       <c r="H327" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="I327" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="J327" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="K327" t="s">
         <v>1613</v>
@@ -19575,7 +19575,7 @@
         <v>1612</v>
       </c>
       <c r="M327" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="N327" t="s">
         <v>1614</v>
@@ -19592,34 +19592,34 @@
         <v>1140</v>
       </c>
       <c r="D328" t="s">
-        <v>1390</v>
+        <v>1231</v>
       </c>
       <c r="E328" t="s">
-        <v>1583</v>
+        <v>1424</v>
       </c>
       <c r="F328" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G328" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H328" t="s">
         <v>1607</v>
       </c>
       <c r="I328" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="J328" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="K328" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="L328" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="M328" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="N328" t="s">
         <v>1614</v>
@@ -19636,34 +19636,34 @@
         <v>1141</v>
       </c>
       <c r="D329" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="E329" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="F329" t="s">
         <v>1601</v>
       </c>
       <c r="G329" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H329" t="s">
         <v>1607</v>
       </c>
       <c r="I329" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J329" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="K329" t="s">
         <v>1611</v>
       </c>
       <c r="L329" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="M329" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="N329" t="s">
         <v>1614</v>
@@ -19680,34 +19680,34 @@
         <v>1142</v>
       </c>
       <c r="D330" t="s">
-        <v>1229</v>
+        <v>1363</v>
       </c>
       <c r="E330" t="s">
-        <v>1422</v>
+        <v>1556</v>
       </c>
       <c r="F330" t="s">
         <v>1601</v>
       </c>
       <c r="G330" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H330" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="I330" t="s">
         <v>1610</v>
       </c>
       <c r="J330" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="K330" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L330" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="M330" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="N330" t="s">
         <v>1614</v>
@@ -19724,34 +19724,34 @@
         <v>1143</v>
       </c>
       <c r="D331" t="s">
-        <v>1363</v>
+        <v>1391</v>
       </c>
       <c r="E331" t="s">
-        <v>1556</v>
+        <v>1584</v>
       </c>
       <c r="F331" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G331" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="H331" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="I331" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="J331" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="K331" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L331" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M331" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="N331" t="s">
         <v>1614</v>
@@ -19768,34 +19768,34 @@
         <v>1144</v>
       </c>
       <c r="D332" t="s">
-        <v>1391</v>
+        <v>1296</v>
       </c>
       <c r="E332" t="s">
-        <v>1584</v>
+        <v>1489</v>
       </c>
       <c r="F332" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="G332" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="H332" t="s">
         <v>1607</v>
       </c>
       <c r="I332" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="J332" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K332" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L332" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="M332" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N332" t="s">
         <v>1614</v>
@@ -19812,28 +19812,28 @@
         <v>1145</v>
       </c>
       <c r="D333" t="s">
-        <v>1296</v>
+        <v>1262</v>
       </c>
       <c r="E333" t="s">
-        <v>1489</v>
+        <v>1455</v>
       </c>
       <c r="F333" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G333" t="s">
         <v>1611</v>
       </c>
       <c r="H333" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I333" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J333" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="K333" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="L333" t="s">
         <v>1608</v>
@@ -19856,31 +19856,31 @@
         <v>1146</v>
       </c>
       <c r="D334" t="s">
-        <v>1262</v>
+        <v>1337</v>
       </c>
       <c r="E334" t="s">
-        <v>1455</v>
+        <v>1530</v>
       </c>
       <c r="F334" t="s">
         <v>1602</v>
       </c>
       <c r="G334" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="H334" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I334" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J334" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="K334" t="s">
         <v>1609</v>
       </c>
       <c r="L334" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="M334" t="s">
         <v>1612</v>
@@ -19900,31 +19900,31 @@
         <v>1147</v>
       </c>
       <c r="D335" t="s">
-        <v>1337</v>
+        <v>1392</v>
       </c>
       <c r="E335" t="s">
-        <v>1530</v>
+        <v>1585</v>
       </c>
       <c r="F335" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="G335" t="s">
         <v>1607</v>
       </c>
       <c r="H335" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I335" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J335" t="s">
         <v>1608</v>
       </c>
       <c r="K335" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="L335" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M335" t="s">
         <v>1612</v>
@@ -19944,13 +19944,13 @@
         <v>1148</v>
       </c>
       <c r="D336" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E336" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="F336" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="G336" t="s">
         <v>1607</v>
@@ -19962,16 +19962,16 @@
         <v>1613</v>
       </c>
       <c r="J336" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K336" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L336" t="s">
         <v>1609</v>
       </c>
       <c r="M336" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="N336" t="s">
         <v>1614</v>
@@ -19988,13 +19988,13 @@
         <v>1149</v>
       </c>
       <c r="D337" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="E337" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F337" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="G337" t="s">
         <v>1607</v>
@@ -20006,16 +20006,16 @@
         <v>1613</v>
       </c>
       <c r="J337" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="K337" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L337" t="s">
         <v>1609</v>
       </c>
       <c r="M337" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="N337" t="s">
         <v>1614</v>
@@ -20032,31 +20032,31 @@
         <v>1150</v>
       </c>
       <c r="D338" t="s">
-        <v>1394</v>
+        <v>1260</v>
       </c>
       <c r="E338" t="s">
-        <v>1587</v>
+        <v>1453</v>
       </c>
       <c r="F338" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="G338" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="H338" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I338" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="J338" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="K338" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="L338" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="M338" t="s">
         <v>1612</v>
@@ -20076,34 +20076,34 @@
         <v>1151</v>
       </c>
       <c r="D339" t="s">
-        <v>1260</v>
+        <v>1395</v>
       </c>
       <c r="E339" t="s">
-        <v>1453</v>
+        <v>1588</v>
       </c>
       <c r="F339" t="s">
         <v>1602</v>
       </c>
       <c r="G339" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H339" t="s">
         <v>1608</v>
       </c>
       <c r="I339" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="J339" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="K339" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="L339" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="M339" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="N339" t="s">
         <v>1614</v>
@@ -20120,13 +20120,13 @@
         <v>1152</v>
       </c>
       <c r="D340" t="s">
-        <v>1395</v>
+        <v>1238</v>
       </c>
       <c r="E340" t="s">
-        <v>1588</v>
+        <v>1431</v>
       </c>
       <c r="F340" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G340" t="s">
         <v>1607</v>
@@ -20135,16 +20135,16 @@
         <v>1608</v>
       </c>
       <c r="I340" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="J340" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="K340" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="L340" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="M340" t="s">
         <v>1611</v>
@@ -20164,10 +20164,10 @@
         <v>1153</v>
       </c>
       <c r="D341" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E341" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="F341" t="s">
         <v>1601</v>
@@ -20208,10 +20208,10 @@
         <v>1154</v>
       </c>
       <c r="D342" t="s">
-        <v>1240</v>
+        <v>1388</v>
       </c>
       <c r="E342" t="s">
-        <v>1433</v>
+        <v>1581</v>
       </c>
       <c r="F342" t="s">
         <v>1601</v>
@@ -20220,22 +20220,22 @@
         <v>1607</v>
       </c>
       <c r="H342" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="I342" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="J342" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="K342" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="L342" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="M342" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="N342" t="s">
         <v>1614</v>
@@ -20252,34 +20252,34 @@
         <v>1155</v>
       </c>
       <c r="D343" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="E343" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="F343" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="G343" t="s">
         <v>1607</v>
       </c>
       <c r="H343" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="I343" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J343" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="K343" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="L343" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M343" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N343" t="s">
         <v>1614</v>
@@ -20296,13 +20296,13 @@
         <v>1156</v>
       </c>
       <c r="D344" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="E344" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="F344" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="G344" t="s">
         <v>1607</v>
@@ -20311,19 +20311,19 @@
         <v>1608</v>
       </c>
       <c r="I344" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="J344" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="K344" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="L344" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="M344" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="N344" t="s">
         <v>1614</v>
@@ -20340,10 +20340,10 @@
         <v>1157</v>
       </c>
       <c r="D345" t="s">
-        <v>1396</v>
+        <v>1350</v>
       </c>
       <c r="E345" t="s">
-        <v>1589</v>
+        <v>1543</v>
       </c>
       <c r="F345" t="s">
         <v>1603</v>
@@ -20352,22 +20352,22 @@
         <v>1607</v>
       </c>
       <c r="H345" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="I345" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="J345" t="s">
         <v>1609</v>
       </c>
       <c r="K345" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="L345" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="M345" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="N345" t="s">
         <v>1614</v>
@@ -20384,13 +20384,13 @@
         <v>1158</v>
       </c>
       <c r="D346" t="s">
-        <v>1350</v>
+        <v>1311</v>
       </c>
       <c r="E346" t="s">
-        <v>1543</v>
+        <v>1504</v>
       </c>
       <c r="F346" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G346" t="s">
         <v>1607</v>
@@ -20399,19 +20399,19 @@
         <v>1610</v>
       </c>
       <c r="I346" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="J346" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="K346" t="s">
         <v>1608</v>
       </c>
       <c r="L346" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M346" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N346" t="s">
         <v>1614</v>
@@ -20428,34 +20428,34 @@
         <v>1159</v>
       </c>
       <c r="D347" t="s">
-        <v>1311</v>
+        <v>1291</v>
       </c>
       <c r="E347" t="s">
-        <v>1504</v>
+        <v>1484</v>
       </c>
       <c r="F347" t="s">
         <v>1602</v>
       </c>
       <c r="G347" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="H347" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="I347" t="s">
         <v>1611</v>
       </c>
       <c r="J347" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="K347" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="L347" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="M347" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N347" t="s">
         <v>1614</v>
@@ -20472,34 +20472,34 @@
         <v>1160</v>
       </c>
       <c r="D348" t="s">
-        <v>1291</v>
+        <v>1251</v>
       </c>
       <c r="E348" t="s">
-        <v>1484</v>
+        <v>1444</v>
       </c>
       <c r="F348" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G348" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H348" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="I348" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="J348" t="s">
         <v>1608</v>
       </c>
       <c r="K348" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="L348" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="M348" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="N348" t="s">
         <v>1614</v>
@@ -20516,34 +20516,34 @@
         <v>1161</v>
       </c>
       <c r="D349" t="s">
-        <v>1251</v>
+        <v>1368</v>
       </c>
       <c r="E349" t="s">
-        <v>1444</v>
+        <v>1561</v>
       </c>
       <c r="F349" t="s">
         <v>1601</v>
       </c>
       <c r="G349" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H349" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="I349" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="J349" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="K349" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="L349" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="M349" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="N349" t="s">
         <v>1614</v>
@@ -20560,10 +20560,10 @@
         <v>1162</v>
       </c>
       <c r="D350" t="s">
-        <v>1368</v>
+        <v>1314</v>
       </c>
       <c r="E350" t="s">
-        <v>1561</v>
+        <v>1507</v>
       </c>
       <c r="F350" t="s">
         <v>1601</v>
@@ -20575,16 +20575,16 @@
         <v>1610</v>
       </c>
       <c r="I350" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="J350" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="K350" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L350" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="M350" t="s">
         <v>1608</v>
@@ -20604,34 +20604,34 @@
         <v>1163</v>
       </c>
       <c r="D351" t="s">
-        <v>1314</v>
+        <v>1299</v>
       </c>
       <c r="E351" t="s">
-        <v>1507</v>
+        <v>1492</v>
       </c>
       <c r="F351" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G351" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H351" t="s">
         <v>1610</v>
       </c>
       <c r="I351" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="J351" t="s">
         <v>1613</v>
       </c>
       <c r="K351" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L351" t="s">
         <v>1609</v>
       </c>
       <c r="M351" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="N351" t="s">
         <v>1614</v>
@@ -20648,34 +20648,34 @@
         <v>1164</v>
       </c>
       <c r="D352" t="s">
-        <v>1299</v>
+        <v>1290</v>
       </c>
       <c r="E352" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
       <c r="F352" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G352" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H352" t="s">
         <v>1610</v>
       </c>
       <c r="I352" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="J352" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="K352" t="s">
         <v>1611</v>
       </c>
       <c r="L352" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="M352" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N352" t="s">
         <v>1614</v>
@@ -20692,34 +20692,34 @@
         <v>1165</v>
       </c>
       <c r="D353" t="s">
-        <v>1290</v>
+        <v>1238</v>
       </c>
       <c r="E353" t="s">
-        <v>1483</v>
+        <v>1431</v>
       </c>
       <c r="F353" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G353" t="s">
         <v>1607</v>
       </c>
       <c r="H353" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I353" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J353" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="K353" t="s">
         <v>1611</v>
       </c>
       <c r="L353" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="M353" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N353" t="s">
         <v>1614</v>
@@ -20736,34 +20736,34 @@
         <v>1166</v>
       </c>
       <c r="D354" t="s">
-        <v>1238</v>
+        <v>1254</v>
       </c>
       <c r="E354" t="s">
-        <v>1431</v>
+        <v>1447</v>
       </c>
       <c r="F354" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="G354" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="H354" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="I354" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="J354" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="K354" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="L354" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="M354" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="N354" t="s">
         <v>1614</v>
@@ -20780,34 +20780,34 @@
         <v>1167</v>
       </c>
       <c r="D355" t="s">
-        <v>1254</v>
+        <v>1301</v>
       </c>
       <c r="E355" t="s">
-        <v>1447</v>
+        <v>1494</v>
       </c>
       <c r="F355" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G355" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="H355" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I355" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="J355" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="K355" t="s">
         <v>1609</v>
       </c>
       <c r="L355" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M355" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="N355" t="s">
         <v>1614</v>
@@ -20824,19 +20824,19 @@
         <v>1168</v>
       </c>
       <c r="D356" t="s">
-        <v>1301</v>
+        <v>1320</v>
       </c>
       <c r="E356" t="s">
-        <v>1494</v>
+        <v>1513</v>
       </c>
       <c r="F356" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G356" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H356" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="I356" t="s">
         <v>1610</v>
@@ -20845,10 +20845,10 @@
         <v>1613</v>
       </c>
       <c r="K356" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="L356" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M356" t="s">
         <v>1612</v>
@@ -20868,34 +20868,34 @@
         <v>1169</v>
       </c>
       <c r="D357" t="s">
-        <v>1320</v>
+        <v>1235</v>
       </c>
       <c r="E357" t="s">
-        <v>1513</v>
+        <v>1428</v>
       </c>
       <c r="F357" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G357" t="s">
         <v>1608</v>
       </c>
       <c r="H357" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="I357" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="J357" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="K357" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L357" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="M357" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N357" t="s">
         <v>1614</v>
@@ -20912,34 +20912,34 @@
         <v>1170</v>
       </c>
       <c r="D358" t="s">
-        <v>1235</v>
+        <v>1395</v>
       </c>
       <c r="E358" t="s">
-        <v>1428</v>
+        <v>1588</v>
       </c>
       <c r="F358" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G358" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="H358" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I358" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="J358" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K358" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="L358" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M358" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="N358" t="s">
         <v>1614</v>
@@ -20956,34 +20956,34 @@
         <v>1171</v>
       </c>
       <c r="D359" t="s">
-        <v>1395</v>
+        <v>1281</v>
       </c>
       <c r="E359" t="s">
-        <v>1588</v>
+        <v>1474</v>
       </c>
       <c r="F359" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G359" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="H359" t="s">
         <v>1610</v>
       </c>
       <c r="I359" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="J359" t="s">
         <v>1609</v>
       </c>
       <c r="K359" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="L359" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M359" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="N359" t="s">
         <v>1614</v>
@@ -21000,31 +21000,31 @@
         <v>1172</v>
       </c>
       <c r="D360" t="s">
-        <v>1281</v>
+        <v>1250</v>
       </c>
       <c r="E360" t="s">
-        <v>1474</v>
+        <v>1443</v>
       </c>
       <c r="F360" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G360" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="H360" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I360" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="J360" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="K360" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L360" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M360" t="s">
         <v>1612</v>
@@ -21044,31 +21044,31 @@
         <v>1173</v>
       </c>
       <c r="D361" t="s">
-        <v>1250</v>
+        <v>1293</v>
       </c>
       <c r="E361" t="s">
-        <v>1443</v>
+        <v>1486</v>
       </c>
       <c r="F361" t="s">
         <v>1602</v>
       </c>
       <c r="G361" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="H361" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="I361" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="J361" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="K361" t="s">
         <v>1611</v>
       </c>
       <c r="L361" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="M361" t="s">
         <v>1612</v>
@@ -21088,31 +21088,31 @@
         <v>1174</v>
       </c>
       <c r="D362" t="s">
-        <v>1293</v>
+        <v>1261</v>
       </c>
       <c r="E362" t="s">
-        <v>1486</v>
+        <v>1454</v>
       </c>
       <c r="F362" t="s">
         <v>1602</v>
       </c>
       <c r="G362" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H362" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="I362" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="J362" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K362" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L362" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="M362" t="s">
         <v>1612</v>
@@ -21132,34 +21132,34 @@
         <v>1175</v>
       </c>
       <c r="D363" t="s">
-        <v>1261</v>
+        <v>1346</v>
       </c>
       <c r="E363" t="s">
-        <v>1454</v>
+        <v>1539</v>
       </c>
       <c r="F363" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G363" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H363" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="I363" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="J363" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="K363" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="L363" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="M363" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="N363" t="s">
         <v>1614</v>
@@ -21176,10 +21176,10 @@
         <v>1176</v>
       </c>
       <c r="D364" t="s">
-        <v>1346</v>
+        <v>1397</v>
       </c>
       <c r="E364" t="s">
-        <v>1539</v>
+        <v>1590</v>
       </c>
       <c r="F364" t="s">
         <v>1601</v>
@@ -21220,34 +21220,34 @@
         <v>1177</v>
       </c>
       <c r="D365" t="s">
-        <v>1397</v>
+        <v>1234</v>
       </c>
       <c r="E365" t="s">
-        <v>1590</v>
+        <v>1427</v>
       </c>
       <c r="F365" t="s">
         <v>1601</v>
       </c>
       <c r="G365" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H365" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="I365" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="J365" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="K365" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="L365" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="M365" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="N365" t="s">
         <v>1614</v>
@@ -21264,31 +21264,31 @@
         <v>1178</v>
       </c>
       <c r="D366" t="s">
-        <v>1234</v>
+        <v>1246</v>
       </c>
       <c r="E366" t="s">
-        <v>1427</v>
+        <v>1439</v>
       </c>
       <c r="F366" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="G366" t="s">
         <v>1607</v>
       </c>
       <c r="H366" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="I366" t="s">
         <v>1613</v>
       </c>
       <c r="J366" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K366" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="L366" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="M366" t="s">
         <v>1612</v>
@@ -21308,34 +21308,34 @@
         <v>1179</v>
       </c>
       <c r="D367" t="s">
-        <v>1246</v>
+        <v>1398</v>
       </c>
       <c r="E367" t="s">
-        <v>1439</v>
+        <v>1591</v>
       </c>
       <c r="F367" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="G367" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H367" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="I367" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="J367" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="K367" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="L367" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="M367" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="N367" t="s">
         <v>1614</v>
@@ -21352,34 +21352,34 @@
         <v>1180</v>
       </c>
       <c r="D368" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="E368" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="F368" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="G368" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H368" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="I368" t="s">
         <v>1609</v>
       </c>
       <c r="J368" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="K368" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="L368" t="s">
         <v>1611</v>
       </c>
       <c r="M368" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="N368" t="s">
         <v>1614</v>
@@ -21396,34 +21396,34 @@
         <v>1181</v>
       </c>
       <c r="D369" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="E369" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="F369" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="G369" t="s">
         <v>1607</v>
       </c>
       <c r="H369" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I369" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="J369" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="K369" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L369" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M369" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N369" t="s">
         <v>1614</v>
@@ -21440,13 +21440,13 @@
         <v>1182</v>
       </c>
       <c r="D370" t="s">
-        <v>1400</v>
+        <v>1244</v>
       </c>
       <c r="E370" t="s">
-        <v>1593</v>
+        <v>1437</v>
       </c>
       <c r="F370" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G370" t="s">
         <v>1607</v>
@@ -21461,13 +21461,13 @@
         <v>1608</v>
       </c>
       <c r="K370" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="L370" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M370" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N370" t="s">
         <v>1614</v>
@@ -21484,13 +21484,13 @@
         <v>1183</v>
       </c>
       <c r="D371" t="s">
-        <v>1244</v>
+        <v>1226</v>
       </c>
       <c r="E371" t="s">
-        <v>1437</v>
+        <v>1419</v>
       </c>
       <c r="F371" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G371" t="s">
         <v>1607</v>
@@ -21502,16 +21502,16 @@
         <v>1613</v>
       </c>
       <c r="J371" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="K371" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="L371" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M371" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="N371" t="s">
         <v>1614</v>
@@ -21528,22 +21528,22 @@
         <v>1184</v>
       </c>
       <c r="D372" t="s">
-        <v>1226</v>
+        <v>1284</v>
       </c>
       <c r="E372" t="s">
-        <v>1419</v>
+        <v>1477</v>
       </c>
       <c r="F372" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G372" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H372" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="I372" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="J372" t="s">
         <v>1609</v>
@@ -21552,10 +21552,10 @@
         <v>1611</v>
       </c>
       <c r="L372" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="M372" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="N372" t="s">
         <v>1614</v>
@@ -21572,31 +21572,31 @@
         <v>1185</v>
       </c>
       <c r="D373" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="E373" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="F373" t="s">
         <v>1602</v>
       </c>
       <c r="G373" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H373" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="I373" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="J373" t="s">
         <v>1609</v>
       </c>
       <c r="K373" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L373" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="M373" t="s">
         <v>1613</v>
@@ -21616,34 +21616,34 @@
         <v>1186</v>
       </c>
       <c r="D374" t="s">
-        <v>1290</v>
+        <v>1230</v>
       </c>
       <c r="E374" t="s">
-        <v>1483</v>
+        <v>1423</v>
       </c>
       <c r="F374" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="G374" t="s">
         <v>1607</v>
       </c>
       <c r="H374" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="I374" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J374" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="K374" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="L374" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M374" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="N374" t="s">
         <v>1614</v>
@@ -21660,34 +21660,34 @@
         <v>1187</v>
       </c>
       <c r="D375" t="s">
-        <v>1230</v>
+        <v>1252</v>
       </c>
       <c r="E375" t="s">
-        <v>1423</v>
+        <v>1445</v>
       </c>
       <c r="F375" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G375" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H375" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="I375" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J375" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="K375" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="L375" t="s">
         <v>1612</v>
       </c>
       <c r="M375" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="N375" t="s">
         <v>1614</v>
@@ -21704,34 +21704,34 @@
         <v>1188</v>
       </c>
       <c r="D376" t="s">
-        <v>1252</v>
+        <v>1355</v>
       </c>
       <c r="E376" t="s">
-        <v>1445</v>
+        <v>1548</v>
       </c>
       <c r="F376" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G376" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H376" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I376" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J376" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="K376" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L376" t="s">
         <v>1612</v>
       </c>
       <c r="M376" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N376" t="s">
         <v>1614</v>
@@ -21748,10 +21748,10 @@
         <v>1189</v>
       </c>
       <c r="D377" t="s">
-        <v>1355</v>
+        <v>1226</v>
       </c>
       <c r="E377" t="s">
-        <v>1548</v>
+        <v>1419</v>
       </c>
       <c r="F377" t="s">
         <v>1602</v>
@@ -21760,13 +21760,13 @@
         <v>1607</v>
       </c>
       <c r="H377" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I377" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J377" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="K377" t="s">
         <v>1608</v>
@@ -21775,7 +21775,7 @@
         <v>1612</v>
       </c>
       <c r="M377" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="N377" t="s">
         <v>1614</v>
@@ -21792,28 +21792,28 @@
         <v>1190</v>
       </c>
       <c r="D378" t="s">
-        <v>1226</v>
+        <v>1281</v>
       </c>
       <c r="E378" t="s">
-        <v>1419</v>
+        <v>1474</v>
       </c>
       <c r="F378" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G378" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H378" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I378" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="J378" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="K378" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="L378" t="s">
         <v>1612</v>
@@ -21836,31 +21836,31 @@
         <v>1191</v>
       </c>
       <c r="D379" t="s">
-        <v>1281</v>
+        <v>1263</v>
       </c>
       <c r="E379" t="s">
-        <v>1474</v>
+        <v>1456</v>
       </c>
       <c r="F379" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G379" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H379" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I379" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="J379" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="K379" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L379" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M379" t="s">
         <v>1609</v>
@@ -21880,25 +21880,25 @@
         <v>1192</v>
       </c>
       <c r="D380" t="s">
-        <v>1263</v>
+        <v>1370</v>
       </c>
       <c r="E380" t="s">
-        <v>1456</v>
+        <v>1563</v>
       </c>
       <c r="F380" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G380" t="s">
         <v>1607</v>
       </c>
       <c r="H380" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I380" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J380" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="K380" t="s">
         <v>1608</v>
@@ -21907,7 +21907,7 @@
         <v>1611</v>
       </c>
       <c r="M380" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N380" t="s">
         <v>1614</v>
@@ -21924,34 +21924,34 @@
         <v>1193</v>
       </c>
       <c r="D381" t="s">
-        <v>1370</v>
+        <v>1344</v>
       </c>
       <c r="E381" t="s">
-        <v>1563</v>
+        <v>1537</v>
       </c>
       <c r="F381" t="s">
         <v>1601</v>
       </c>
       <c r="G381" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="H381" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I381" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="J381" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="K381" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="L381" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M381" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N381" t="s">
         <v>1614</v>
@@ -21968,34 +21968,34 @@
         <v>1194</v>
       </c>
       <c r="D382" t="s">
-        <v>1344</v>
+        <v>1400</v>
       </c>
       <c r="E382" t="s">
-        <v>1537</v>
+        <v>1593</v>
       </c>
       <c r="F382" t="s">
         <v>1601</v>
       </c>
       <c r="G382" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="H382" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="I382" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="J382" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="K382" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="L382" t="s">
         <v>1612</v>
       </c>
       <c r="M382" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N382" t="s">
         <v>1614</v>
@@ -22012,34 +22012,34 @@
         <v>1195</v>
       </c>
       <c r="D383" t="s">
-        <v>1400</v>
+        <v>1249</v>
       </c>
       <c r="E383" t="s">
-        <v>1593</v>
+        <v>1442</v>
       </c>
       <c r="F383" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G383" t="s">
         <v>1607</v>
       </c>
       <c r="H383" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="I383" t="s">
         <v>1613</v>
       </c>
       <c r="J383" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="K383" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="L383" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M383" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="N383" t="s">
         <v>1614</v>
@@ -22056,34 +22056,34 @@
         <v>1196</v>
       </c>
       <c r="D384" t="s">
-        <v>1249</v>
+        <v>1263</v>
       </c>
       <c r="E384" t="s">
-        <v>1442</v>
+        <v>1456</v>
       </c>
       <c r="F384" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="G384" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H384" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="I384" t="s">
         <v>1613</v>
       </c>
       <c r="J384" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="K384" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="L384" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M384" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N384" t="s">
         <v>1614</v>
@@ -22100,34 +22100,34 @@
         <v>1197</v>
       </c>
       <c r="D385" t="s">
-        <v>1263</v>
+        <v>1401</v>
       </c>
       <c r="E385" t="s">
-        <v>1456</v>
+        <v>1594</v>
       </c>
       <c r="F385" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="G385" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H385" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="I385" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J385" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="K385" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="L385" t="s">
         <v>1612</v>
       </c>
       <c r="M385" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N385" t="s">
         <v>1614</v>
@@ -22144,34 +22144,34 @@
         <v>1198</v>
       </c>
       <c r="D386" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="E386" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="F386" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="G386" t="s">
         <v>1607</v>
       </c>
       <c r="H386" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I386" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J386" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K386" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="L386" t="s">
         <v>1612</v>
       </c>
       <c r="M386" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="N386" t="s">
         <v>1614</v>
@@ -22188,34 +22188,34 @@
         <v>1199</v>
       </c>
       <c r="D387" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="E387" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="F387" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G387" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="H387" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="I387" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J387" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="K387" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="L387" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="M387" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N387" t="s">
         <v>1614</v>
@@ -22232,34 +22232,34 @@
         <v>1200</v>
       </c>
       <c r="D388" t="s">
-        <v>1403</v>
+        <v>1290</v>
       </c>
       <c r="E388" t="s">
-        <v>1596</v>
+        <v>1483</v>
       </c>
       <c r="F388" t="s">
         <v>1602</v>
       </c>
       <c r="G388" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H388" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="I388" t="s">
         <v>1610</v>
       </c>
       <c r="J388" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="K388" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="L388" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="M388" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N388" t="s">
         <v>1614</v>
@@ -22276,31 +22276,31 @@
         <v>1201</v>
       </c>
       <c r="D389" t="s">
-        <v>1290</v>
+        <v>1380</v>
       </c>
       <c r="E389" t="s">
-        <v>1483</v>
+        <v>1573</v>
       </c>
       <c r="F389" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G389" t="s">
         <v>1607</v>
       </c>
       <c r="H389" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I389" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J389" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="K389" t="s">
         <v>1611</v>
       </c>
       <c r="L389" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="M389" t="s">
         <v>1609</v>
@@ -22320,31 +22320,31 @@
         <v>1202</v>
       </c>
       <c r="D390" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="E390" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="F390" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G390" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="H390" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I390" t="s">
         <v>1613</v>
       </c>
       <c r="J390" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="K390" t="s">
         <v>1611</v>
       </c>
       <c r="L390" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="M390" t="s">
         <v>1609</v>
@@ -22364,34 +22364,34 @@
         <v>1203</v>
       </c>
       <c r="D391" t="s">
-        <v>1375</v>
+        <v>1334</v>
       </c>
       <c r="E391" t="s">
-        <v>1568</v>
+        <v>1527</v>
       </c>
       <c r="F391" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G391" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="H391" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="I391" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J391" t="s">
         <v>1607</v>
       </c>
       <c r="K391" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="L391" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M391" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N391" t="s">
         <v>1614</v>
@@ -22408,16 +22408,16 @@
         <v>1204</v>
       </c>
       <c r="D392" t="s">
-        <v>1334</v>
+        <v>1404</v>
       </c>
       <c r="E392" t="s">
-        <v>1527</v>
+        <v>1597</v>
       </c>
       <c r="F392" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G392" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H392" t="s">
         <v>1613</v>
@@ -22426,13 +22426,13 @@
         <v>1610</v>
       </c>
       <c r="J392" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="K392" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="L392" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="M392" t="s">
         <v>1612</v>
@@ -22452,34 +22452,34 @@
         <v>1205</v>
       </c>
       <c r="D393" t="s">
-        <v>1404</v>
+        <v>1311</v>
       </c>
       <c r="E393" t="s">
-        <v>1597</v>
+        <v>1504</v>
       </c>
       <c r="F393" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G393" t="s">
         <v>1607</v>
       </c>
       <c r="H393" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I393" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J393" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="K393" t="s">
         <v>1608</v>
       </c>
       <c r="L393" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="M393" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N393" t="s">
         <v>1614</v>
@@ -22496,34 +22496,34 @@
         <v>1206</v>
       </c>
       <c r="D394" t="s">
-        <v>1311</v>
+        <v>1223</v>
       </c>
       <c r="E394" t="s">
-        <v>1504</v>
+        <v>1416</v>
       </c>
       <c r="F394" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G394" t="s">
         <v>1607</v>
       </c>
       <c r="H394" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="I394" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="J394" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="K394" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="L394" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="M394" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="N394" t="s">
         <v>1614</v>
@@ -22540,34 +22540,34 @@
         <v>1207</v>
       </c>
       <c r="D395" t="s">
-        <v>1223</v>
+        <v>1405</v>
       </c>
       <c r="E395" t="s">
-        <v>1416</v>
+        <v>1598</v>
       </c>
       <c r="F395" t="s">
         <v>1602</v>
       </c>
       <c r="G395" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H395" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="I395" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="J395" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="K395" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="L395" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="M395" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="N395" t="s">
         <v>1614</v>
@@ -22584,31 +22584,31 @@
         <v>1208</v>
       </c>
       <c r="D396" t="s">
-        <v>1405</v>
+        <v>1366</v>
       </c>
       <c r="E396" t="s">
-        <v>1598</v>
+        <v>1559</v>
       </c>
       <c r="F396" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G396" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H396" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I396" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="J396" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K396" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="L396" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="M396" t="s">
         <v>1612</v>
@@ -22628,34 +22628,34 @@
         <v>1209</v>
       </c>
       <c r="D397" t="s">
-        <v>1366</v>
+        <v>1231</v>
       </c>
       <c r="E397" t="s">
-        <v>1559</v>
+        <v>1424</v>
       </c>
       <c r="F397" t="s">
         <v>1601</v>
       </c>
       <c r="G397" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="H397" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I397" t="s">
         <v>1608</v>
       </c>
       <c r="J397" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="K397" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="L397" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="M397" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N397" t="s">
         <v>1614</v>
@@ -22672,34 +22672,34 @@
         <v>1210</v>
       </c>
       <c r="D398" t="s">
-        <v>1231</v>
+        <v>1406</v>
       </c>
       <c r="E398" t="s">
-        <v>1424</v>
+        <v>1599</v>
       </c>
       <c r="F398" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="G398" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="H398" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I398" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="J398" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="K398" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="L398" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="M398" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N398" t="s">
         <v>1614</v>
@@ -22716,10 +22716,10 @@
         <v>1211</v>
       </c>
       <c r="D399" t="s">
-        <v>1406</v>
+        <v>1232</v>
       </c>
       <c r="E399" t="s">
-        <v>1599</v>
+        <v>1425</v>
       </c>
       <c r="F399" t="s">
         <v>1602</v>
@@ -22728,22 +22728,22 @@
         <v>1607</v>
       </c>
       <c r="H399" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="I399" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="J399" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
       <c r="K399" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="L399" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M399" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="N399" t="s">
         <v>1614</v>
@@ -22760,34 +22760,34 @@
         <v>1212</v>
       </c>
       <c r="D400" t="s">
-        <v>1232</v>
+        <v>1407</v>
       </c>
       <c r="E400" t="s">
-        <v>1425</v>
+        <v>1600</v>
       </c>
       <c r="F400" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="G400" t="s">
         <v>1607</v>
       </c>
       <c r="H400" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="I400" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="J400" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="K400" t="s">
         <v>1613</v>
       </c>
       <c r="L400" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M400" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="N400" t="s">
         <v>1614</v>
@@ -22804,34 +22804,34 @@
         <v>1213</v>
       </c>
       <c r="D401" t="s">
-        <v>1407</v>
+        <v>1225</v>
       </c>
       <c r="E401" t="s">
-        <v>1600</v>
+        <v>1418</v>
       </c>
       <c r="F401" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="G401" t="s">
         <v>1607</v>
       </c>
       <c r="H401" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="I401" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J401" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="K401" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="L401" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="M401" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N401" t="s">
         <v>1614</v>
@@ -22848,25 +22848,25 @@
         <v>1214</v>
       </c>
       <c r="D402">
-        <v>1354</v>
+        <v>1301</v>
       </c>
       <c r="E402">
-        <v>67.7</v>
+        <v>65.05</v>
       </c>
       <c r="F402" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G402" t="s">
         <v>1607</v>
       </c>
       <c r="H402" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I402" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J402" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="K402" t="s">
         <v>1611</v>
@@ -22875,7 +22875,7 @@
         <v>1608</v>
       </c>
       <c r="M402" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N402" t="s">
         <v>1614</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1255,12 +1255,12 @@
     <t>محمود عبد العال احمد حماده</t>
   </si>
   <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
     <t>احمد محمد رجب عبد الحكيم</t>
   </si>
   <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2455,12 +2455,12 @@
     <t>30504182400893</t>
   </si>
   <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
     <t>30510012412811</t>
   </si>
   <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3655,10 +3655,10 @@
     <t>01055420368</t>
   </si>
   <si>
+    <t>01037905359</t>
+  </si>
+  <si>
     <t>01142212131</t>
-  </si>
-  <si>
-    <t>01037905359</t>
   </si>
   <si>
     <t>1353</t>
@@ -22804,25 +22804,25 @@
         <v>1213</v>
       </c>
       <c r="D401" t="s">
-        <v>1225</v>
+        <v>1237</v>
       </c>
       <c r="E401" t="s">
-        <v>1418</v>
+        <v>1430</v>
       </c>
       <c r="F401" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="G401" t="s">
         <v>1607</v>
       </c>
       <c r="H401" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="I401" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="J401" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="K401" t="s">
         <v>1611</v>
@@ -22831,7 +22831,7 @@
         <v>1608</v>
       </c>
       <c r="M401" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="N401" t="s">
         <v>1614</v>
@@ -22848,25 +22848,25 @@
         <v>1214</v>
       </c>
       <c r="D402">
-        <v>1301</v>
+        <v>1354</v>
       </c>
       <c r="E402">
-        <v>65.05</v>
+        <v>67.7</v>
       </c>
       <c r="F402" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="G402" t="s">
         <v>1607</v>
       </c>
       <c r="H402" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="I402" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J402" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="K402" t="s">
         <v>1611</v>
@@ -22875,7 +22875,7 @@
         <v>1608</v>
       </c>
       <c r="M402" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="N402" t="s">
         <v>1614</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1081,192 +1081,192 @@
     <t>فادى نصر موسى محمود</t>
   </si>
   <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>كريم عبد الصالحين دخيل ابوسمره</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمود عبد العال احمد حماده</t>
+  </si>
+  <si>
+    <t>كريم حسن فاروق مليجى</t>
+  </si>
+  <si>
+    <t>عبدالعظيم عصام مجدى جمعه</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
     <t>عمرو هشام جمال رياض</t>
   </si>
   <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>كريم عبد الصالحين دخيل ابوسمره</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمود عبد العال احمد حماده</t>
-  </si>
-  <si>
-    <t>كريم حسن فاروق مليجى</t>
-  </si>
-  <si>
-    <t>عبدالعظيم عصام مجدى جمعه</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2287,192 +2287,192 @@
     <t>30211012412911</t>
   </si>
   <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30311152404492</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30504182400893</t>
+  </si>
+  <si>
+    <t>30304010400698</t>
+  </si>
+  <si>
+    <t>30501252404612</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
     <t>30510172402537</t>
   </si>
   <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30311152404492</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30504182400893</t>
-  </si>
-  <si>
-    <t>30304010400698</t>
-  </si>
-  <si>
-    <t>30501252404612</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3493,192 +3493,192 @@
     <t>01099427041</t>
   </si>
   <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01068463842</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01055420368</t>
+  </si>
+  <si>
+    <t>01095305700</t>
+  </si>
+  <si>
+    <t>01032909577</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
     <t>01101887554</t>
   </si>
   <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01068463842</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01055420368</t>
-  </si>
-  <si>
-    <t>01095305700</t>
-  </si>
-  <si>
-    <t>01032909577</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
     <t>1353</t>
   </si>
   <si>
@@ -4219,9 +4219,6 @@
     <t>1323</t>
   </si>
   <si>
-    <t>1223</t>
-  </si>
-  <si>
     <t>1428</t>
   </si>
   <si>
@@ -4258,6 +4255,9 @@
     <t>1336</t>
   </si>
   <si>
+    <t>1292</t>
+  </si>
+  <si>
     <t>67.65</t>
   </si>
   <si>
@@ -4798,9 +4798,6 @@
     <t>66.15</t>
   </si>
   <si>
-    <t>61.15</t>
-  </si>
-  <si>
     <t>71.4</t>
   </si>
   <si>
@@ -4835,6 +4832,9 @@
   </si>
   <si>
     <t>66.8</t>
+  </si>
+  <si>
+    <t>64.6</t>
   </si>
   <si>
     <t>جيد</t>
@@ -20270,10 +20270,10 @@
         <v>1159</v>
       </c>
       <c r="D343" t="s">
-        <v>1401</v>
+        <v>1356</v>
       </c>
       <c r="E343" t="s">
-        <v>1594</v>
+        <v>1549</v>
       </c>
       <c r="F343" t="s">
         <v>1609</v>
@@ -20282,22 +20282,22 @@
         <v>1613</v>
       </c>
       <c r="H343" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="I343" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="J343" t="s">
         <v>1615</v>
       </c>
       <c r="K343" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="L343" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="M343" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="N343" t="s">
         <v>1620</v>
@@ -20314,13 +20314,13 @@
         <v>1160</v>
       </c>
       <c r="D344" t="s">
-        <v>1356</v>
+        <v>1317</v>
       </c>
       <c r="E344" t="s">
-        <v>1549</v>
+        <v>1510</v>
       </c>
       <c r="F344" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G344" t="s">
         <v>1613</v>
@@ -20329,19 +20329,19 @@
         <v>1616</v>
       </c>
       <c r="I344" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="J344" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="K344" t="s">
         <v>1614</v>
       </c>
       <c r="L344" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M344" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N344" t="s">
         <v>1620</v>
@@ -20358,34 +20358,34 @@
         <v>1161</v>
       </c>
       <c r="D345" t="s">
-        <v>1317</v>
+        <v>1297</v>
       </c>
       <c r="E345" t="s">
-        <v>1510</v>
+        <v>1490</v>
       </c>
       <c r="F345" t="s">
         <v>1608</v>
       </c>
       <c r="G345" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="H345" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="I345" t="s">
         <v>1617</v>
       </c>
       <c r="J345" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="K345" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="L345" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="M345" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N345" t="s">
         <v>1620</v>
@@ -20402,34 +20402,34 @@
         <v>1162</v>
       </c>
       <c r="D346" t="s">
-        <v>1297</v>
+        <v>1257</v>
       </c>
       <c r="E346" t="s">
-        <v>1490</v>
+        <v>1450</v>
       </c>
       <c r="F346" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G346" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H346" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="I346" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="J346" t="s">
         <v>1614</v>
       </c>
       <c r="K346" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="L346" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="M346" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="N346" t="s">
         <v>1620</v>
@@ -20446,34 +20446,34 @@
         <v>1163</v>
       </c>
       <c r="D347" t="s">
-        <v>1257</v>
+        <v>1374</v>
       </c>
       <c r="E347" t="s">
-        <v>1450</v>
+        <v>1567</v>
       </c>
       <c r="F347" t="s">
         <v>1607</v>
       </c>
       <c r="G347" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="H347" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="I347" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="J347" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="K347" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="L347" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="M347" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="N347" t="s">
         <v>1620</v>
@@ -20490,10 +20490,10 @@
         <v>1164</v>
       </c>
       <c r="D348" t="s">
-        <v>1374</v>
+        <v>1320</v>
       </c>
       <c r="E348" t="s">
-        <v>1567</v>
+        <v>1513</v>
       </c>
       <c r="F348" t="s">
         <v>1607</v>
@@ -20505,16 +20505,16 @@
         <v>1616</v>
       </c>
       <c r="I348" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="J348" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="K348" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="L348" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="M348" t="s">
         <v>1614</v>
@@ -20534,34 +20534,34 @@
         <v>1165</v>
       </c>
       <c r="D349" t="s">
-        <v>1320</v>
+        <v>1305</v>
       </c>
       <c r="E349" t="s">
-        <v>1513</v>
+        <v>1498</v>
       </c>
       <c r="F349" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="G349" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H349" t="s">
         <v>1616</v>
       </c>
       <c r="I349" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="J349" t="s">
         <v>1619</v>
       </c>
       <c r="K349" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="L349" t="s">
         <v>1615</v>
       </c>
       <c r="M349" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="N349" t="s">
         <v>1620</v>
@@ -20578,34 +20578,34 @@
         <v>1166</v>
       </c>
       <c r="D350" t="s">
-        <v>1305</v>
+        <v>1296</v>
       </c>
       <c r="E350" t="s">
-        <v>1498</v>
+        <v>1489</v>
       </c>
       <c r="F350" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G350" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H350" t="s">
         <v>1616</v>
       </c>
       <c r="I350" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="J350" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="K350" t="s">
         <v>1617</v>
       </c>
       <c r="L350" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="M350" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N350" t="s">
         <v>1620</v>
@@ -20622,34 +20622,34 @@
         <v>1167</v>
       </c>
       <c r="D351" t="s">
-        <v>1296</v>
+        <v>1244</v>
       </c>
       <c r="E351" t="s">
-        <v>1489</v>
+        <v>1437</v>
       </c>
       <c r="F351" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="G351" t="s">
         <v>1613</v>
       </c>
       <c r="H351" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I351" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="J351" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="K351" t="s">
         <v>1617</v>
       </c>
       <c r="L351" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="M351" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N351" t="s">
         <v>1620</v>
@@ -20666,34 +20666,34 @@
         <v>1168</v>
       </c>
       <c r="D352" t="s">
-        <v>1244</v>
+        <v>1260</v>
       </c>
       <c r="E352" t="s">
-        <v>1437</v>
+        <v>1453</v>
       </c>
       <c r="F352" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G352" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="H352" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="I352" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="J352" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="K352" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="L352" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="M352" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="N352" t="s">
         <v>1620</v>
@@ -20710,34 +20710,34 @@
         <v>1169</v>
       </c>
       <c r="D353" t="s">
-        <v>1260</v>
+        <v>1307</v>
       </c>
       <c r="E353" t="s">
-        <v>1453</v>
+        <v>1500</v>
       </c>
       <c r="F353" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="G353" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="H353" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I353" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="J353" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="K353" t="s">
         <v>1615</v>
       </c>
       <c r="L353" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M353" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="N353" t="s">
         <v>1620</v>
@@ -20754,19 +20754,19 @@
         <v>1170</v>
       </c>
       <c r="D354" t="s">
-        <v>1307</v>
+        <v>1326</v>
       </c>
       <c r="E354" t="s">
-        <v>1500</v>
+        <v>1519</v>
       </c>
       <c r="F354" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="G354" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H354" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="I354" t="s">
         <v>1616</v>
@@ -20775,10 +20775,10 @@
         <v>1619</v>
       </c>
       <c r="K354" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="L354" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M354" t="s">
         <v>1618</v>
@@ -20798,34 +20798,34 @@
         <v>1171</v>
       </c>
       <c r="D355" t="s">
-        <v>1326</v>
+        <v>1241</v>
       </c>
       <c r="E355" t="s">
-        <v>1519</v>
+        <v>1434</v>
       </c>
       <c r="F355" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="G355" t="s">
         <v>1614</v>
       </c>
       <c r="H355" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="I355" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="J355" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="K355" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="L355" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="M355" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N355" t="s">
         <v>1620</v>
@@ -20842,34 +20842,34 @@
         <v>1172</v>
       </c>
       <c r="D356" t="s">
-        <v>1241</v>
+        <v>1400</v>
       </c>
       <c r="E356" t="s">
-        <v>1434</v>
+        <v>1593</v>
       </c>
       <c r="F356" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="G356" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="H356" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I356" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="J356" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="K356" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="L356" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M356" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="N356" t="s">
         <v>1620</v>
@@ -20886,34 +20886,34 @@
         <v>1173</v>
       </c>
       <c r="D357" t="s">
-        <v>1400</v>
+        <v>1287</v>
       </c>
       <c r="E357" t="s">
-        <v>1593</v>
+        <v>1480</v>
       </c>
       <c r="F357" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G357" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="H357" t="s">
         <v>1616</v>
       </c>
       <c r="I357" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="J357" t="s">
         <v>1615</v>
       </c>
       <c r="K357" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="L357" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M357" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="N357" t="s">
         <v>1620</v>
@@ -20930,31 +20930,31 @@
         <v>1174</v>
       </c>
       <c r="D358" t="s">
-        <v>1287</v>
+        <v>1256</v>
       </c>
       <c r="E358" t="s">
-        <v>1480</v>
+        <v>1449</v>
       </c>
       <c r="F358" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="G358" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="H358" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="I358" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="J358" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="K358" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="L358" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M358" t="s">
         <v>1618</v>
@@ -20974,31 +20974,31 @@
         <v>1175</v>
       </c>
       <c r="D359" t="s">
-        <v>1256</v>
+        <v>1299</v>
       </c>
       <c r="E359" t="s">
-        <v>1449</v>
+        <v>1492</v>
       </c>
       <c r="F359" t="s">
         <v>1608</v>
       </c>
       <c r="G359" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="H359" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="I359" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="J359" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="K359" t="s">
         <v>1617</v>
       </c>
       <c r="L359" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="M359" t="s">
         <v>1618</v>
@@ -21018,31 +21018,31 @@
         <v>1176</v>
       </c>
       <c r="D360" t="s">
-        <v>1299</v>
+        <v>1267</v>
       </c>
       <c r="E360" t="s">
-        <v>1492</v>
+        <v>1460</v>
       </c>
       <c r="F360" t="s">
         <v>1608</v>
       </c>
       <c r="G360" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H360" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="I360" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="J360" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="K360" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="L360" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="M360" t="s">
         <v>1618</v>
@@ -21062,34 +21062,34 @@
         <v>1177</v>
       </c>
       <c r="D361" t="s">
-        <v>1267</v>
+        <v>1352</v>
       </c>
       <c r="E361" t="s">
-        <v>1460</v>
+        <v>1545</v>
       </c>
       <c r="F361" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G361" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H361" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="I361" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="J361" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="K361" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="L361" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="M361" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="N361" t="s">
         <v>1620</v>
@@ -21106,10 +21106,10 @@
         <v>1178</v>
       </c>
       <c r="D362" t="s">
-        <v>1352</v>
+        <v>1401</v>
       </c>
       <c r="E362" t="s">
-        <v>1545</v>
+        <v>1594</v>
       </c>
       <c r="F362" t="s">
         <v>1607</v>
@@ -21150,34 +21150,34 @@
         <v>1179</v>
       </c>
       <c r="D363" t="s">
-        <v>1402</v>
+        <v>1240</v>
       </c>
       <c r="E363" t="s">
-        <v>1595</v>
+        <v>1433</v>
       </c>
       <c r="F363" t="s">
         <v>1607</v>
       </c>
       <c r="G363" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H363" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="I363" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="J363" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="K363" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="L363" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="M363" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="N363" t="s">
         <v>1620</v>
@@ -21194,31 +21194,31 @@
         <v>1180</v>
       </c>
       <c r="D364" t="s">
-        <v>1240</v>
+        <v>1252</v>
       </c>
       <c r="E364" t="s">
-        <v>1433</v>
+        <v>1445</v>
       </c>
       <c r="F364" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="G364" t="s">
         <v>1613</v>
       </c>
       <c r="H364" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="I364" t="s">
         <v>1619</v>
       </c>
       <c r="J364" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="K364" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="L364" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="M364" t="s">
         <v>1618</v>
@@ -21238,34 +21238,34 @@
         <v>1181</v>
       </c>
       <c r="D365" t="s">
-        <v>1252</v>
+        <v>1402</v>
       </c>
       <c r="E365" t="s">
-        <v>1445</v>
+        <v>1595</v>
       </c>
       <c r="F365" t="s">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="G365" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H365" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="I365" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="J365" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="K365" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="L365" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="M365" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="N365" t="s">
         <v>1620</v>
@@ -21288,28 +21288,28 @@
         <v>1596</v>
       </c>
       <c r="F366" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="G366" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H366" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="I366" t="s">
         <v>1615</v>
       </c>
       <c r="J366" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="K366" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="L366" t="s">
         <v>1617</v>
       </c>
       <c r="M366" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="N366" t="s">
         <v>1620</v>
@@ -21332,28 +21332,28 @@
         <v>1597</v>
       </c>
       <c r="F367" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="G367" t="s">
         <v>1613</v>
       </c>
       <c r="H367" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I367" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="J367" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="K367" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="L367" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M367" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N367" t="s">
         <v>1620</v>
@@ -21370,13 +21370,13 @@
         <v>1184</v>
       </c>
       <c r="D368" t="s">
-        <v>1405</v>
+        <v>1250</v>
       </c>
       <c r="E368" t="s">
-        <v>1598</v>
+        <v>1443</v>
       </c>
       <c r="F368" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G368" t="s">
         <v>1613</v>
@@ -21391,13 +21391,13 @@
         <v>1614</v>
       </c>
       <c r="K368" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="L368" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M368" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N368" t="s">
         <v>1620</v>
@@ -21414,13 +21414,13 @@
         <v>1185</v>
       </c>
       <c r="D369" t="s">
-        <v>1250</v>
+        <v>1232</v>
       </c>
       <c r="E369" t="s">
-        <v>1443</v>
+        <v>1425</v>
       </c>
       <c r="F369" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="G369" t="s">
         <v>1613</v>
@@ -21432,16 +21432,16 @@
         <v>1619</v>
       </c>
       <c r="J369" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="K369" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="L369" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M369" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="N369" t="s">
         <v>1620</v>
@@ -21458,22 +21458,22 @@
         <v>1186</v>
       </c>
       <c r="D370" t="s">
-        <v>1232</v>
+        <v>1290</v>
       </c>
       <c r="E370" t="s">
-        <v>1425</v>
+        <v>1483</v>
       </c>
       <c r="F370" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G370" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H370" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="I370" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="J370" t="s">
         <v>1615</v>
@@ -21482,10 +21482,10 @@
         <v>1617</v>
       </c>
       <c r="L370" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M370" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="N370" t="s">
         <v>1620</v>
@@ -21502,31 +21502,31 @@
         <v>1187</v>
       </c>
       <c r="D371" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="E371" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="F371" t="s">
         <v>1608</v>
       </c>
       <c r="G371" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H371" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="I371" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="J371" t="s">
         <v>1615</v>
       </c>
       <c r="K371" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="L371" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="M371" t="s">
         <v>1619</v>
@@ -21546,34 +21546,34 @@
         <v>1188</v>
       </c>
       <c r="D372" t="s">
-        <v>1296</v>
+        <v>1236</v>
       </c>
       <c r="E372" t="s">
-        <v>1489</v>
+        <v>1429</v>
       </c>
       <c r="F372" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G372" t="s">
         <v>1613</v>
       </c>
       <c r="H372" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="I372" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="J372" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="K372" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="L372" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M372" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="N372" t="s">
         <v>1620</v>
@@ -21590,34 +21590,34 @@
         <v>1189</v>
       </c>
       <c r="D373" t="s">
-        <v>1236</v>
+        <v>1258</v>
       </c>
       <c r="E373" t="s">
-        <v>1429</v>
+        <v>1451</v>
       </c>
       <c r="F373" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="G373" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H373" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="I373" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="J373" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="K373" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="L373" t="s">
         <v>1618</v>
       </c>
       <c r="M373" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="N373" t="s">
         <v>1620</v>
@@ -21634,34 +21634,34 @@
         <v>1190</v>
       </c>
       <c r="D374" t="s">
-        <v>1258</v>
+        <v>1361</v>
       </c>
       <c r="E374" t="s">
-        <v>1451</v>
+        <v>1554</v>
       </c>
       <c r="F374" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="G374" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H374" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="I374" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="J374" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="K374" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="L374" t="s">
         <v>1618</v>
       </c>
       <c r="M374" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="N374" t="s">
         <v>1620</v>
@@ -21678,10 +21678,10 @@
         <v>1191</v>
       </c>
       <c r="D375" t="s">
-        <v>1361</v>
+        <v>1232</v>
       </c>
       <c r="E375" t="s">
-        <v>1554</v>
+        <v>1425</v>
       </c>
       <c r="F375" t="s">
         <v>1608</v>
@@ -21690,13 +21690,13 @@
         <v>1613</v>
       </c>
       <c r="H375" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="I375" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="J375" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="K375" t="s">
         <v>1614</v>
@@ -21705,7 +21705,7 @@
         <v>1618</v>
       </c>
       <c r="M375" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="N375" t="s">
         <v>1620</v>
@@ -21722,28 +21722,28 @@
         <v>1192</v>
       </c>
       <c r="D376" t="s">
-        <v>1232</v>
+        <v>1287</v>
       </c>
       <c r="E376" t="s">
-        <v>1425</v>
+        <v>1480</v>
       </c>
       <c r="F376" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G376" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H376" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I376" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="J376" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="K376" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="L376" t="s">
         <v>1618</v>
@@ -21766,31 +21766,31 @@
         <v>1193</v>
       </c>
       <c r="D377" t="s">
-        <v>1287</v>
+        <v>1269</v>
       </c>
       <c r="E377" t="s">
-        <v>1480</v>
+        <v>1462</v>
       </c>
       <c r="F377" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="G377" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H377" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="I377" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="J377" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="K377" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="L377" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M377" t="s">
         <v>1615</v>
@@ -21810,25 +21810,25 @@
         <v>1194</v>
       </c>
       <c r="D378" t="s">
-        <v>1269</v>
+        <v>1376</v>
       </c>
       <c r="E378" t="s">
-        <v>1462</v>
+        <v>1569</v>
       </c>
       <c r="F378" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="G378" t="s">
         <v>1613</v>
       </c>
       <c r="H378" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I378" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="J378" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="K378" t="s">
         <v>1614</v>
@@ -21837,7 +21837,7 @@
         <v>1617</v>
       </c>
       <c r="M378" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N378" t="s">
         <v>1620</v>
@@ -21854,34 +21854,34 @@
         <v>1195</v>
       </c>
       <c r="D379" t="s">
-        <v>1376</v>
+        <v>1350</v>
       </c>
       <c r="E379" t="s">
-        <v>1569</v>
+        <v>1543</v>
       </c>
       <c r="F379" t="s">
         <v>1607</v>
       </c>
       <c r="G379" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="H379" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I379" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="J379" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="K379" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="L379" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M379" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N379" t="s">
         <v>1620</v>
@@ -21898,34 +21898,34 @@
         <v>1196</v>
       </c>
       <c r="D380" t="s">
-        <v>1350</v>
+        <v>1404</v>
       </c>
       <c r="E380" t="s">
-        <v>1543</v>
+        <v>1597</v>
       </c>
       <c r="F380" t="s">
         <v>1607</v>
       </c>
       <c r="G380" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="H380" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="I380" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="J380" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="K380" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="L380" t="s">
         <v>1618</v>
       </c>
       <c r="M380" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="N380" t="s">
         <v>1620</v>
@@ -21942,34 +21942,34 @@
         <v>1197</v>
       </c>
       <c r="D381" t="s">
-        <v>1405</v>
+        <v>1255</v>
       </c>
       <c r="E381" t="s">
-        <v>1598</v>
+        <v>1448</v>
       </c>
       <c r="F381" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="G381" t="s">
         <v>1613</v>
       </c>
       <c r="H381" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="I381" t="s">
         <v>1619</v>
       </c>
       <c r="J381" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="K381" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="L381" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M381" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="N381" t="s">
         <v>1620</v>
@@ -21986,34 +21986,34 @@
         <v>1198</v>
       </c>
       <c r="D382" t="s">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="E382" t="s">
-        <v>1448</v>
+        <v>1462</v>
       </c>
       <c r="F382" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="G382" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H382" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="I382" t="s">
         <v>1619</v>
       </c>
       <c r="J382" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="K382" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="L382" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M382" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N382" t="s">
         <v>1620</v>
@@ -22030,34 +22030,34 @@
         <v>1199</v>
       </c>
       <c r="D383" t="s">
-        <v>1269</v>
+        <v>1405</v>
       </c>
       <c r="E383" t="s">
-        <v>1462</v>
+        <v>1598</v>
       </c>
       <c r="F383" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="G383" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H383" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="I383" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="J383" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="K383" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="L383" t="s">
         <v>1618</v>
       </c>
       <c r="M383" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="N383" t="s">
         <v>1620</v>
@@ -22080,28 +22080,28 @@
         <v>1599</v>
       </c>
       <c r="F384" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="G384" t="s">
         <v>1613</v>
       </c>
       <c r="H384" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I384" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="J384" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="K384" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="L384" t="s">
         <v>1618</v>
       </c>
       <c r="M384" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="N384" t="s">
         <v>1620</v>
@@ -22124,28 +22124,28 @@
         <v>1600</v>
       </c>
       <c r="F385" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G385" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="H385" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="I385" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="J385" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="K385" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="L385" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="M385" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N385" t="s">
         <v>1620</v>
@@ -22162,34 +22162,34 @@
         <v>1202</v>
       </c>
       <c r="D386" t="s">
-        <v>1408</v>
+        <v>1296</v>
       </c>
       <c r="E386" t="s">
-        <v>1601</v>
+        <v>1489</v>
       </c>
       <c r="F386" t="s">
         <v>1608</v>
       </c>
       <c r="G386" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="H386" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="I386" t="s">
         <v>1616</v>
       </c>
       <c r="J386" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="K386" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="L386" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="M386" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N386" t="s">
         <v>1620</v>
@@ -22206,31 +22206,31 @@
         <v>1203</v>
       </c>
       <c r="D387" t="s">
-        <v>1296</v>
+        <v>1385</v>
       </c>
       <c r="E387" t="s">
-        <v>1489</v>
+        <v>1578</v>
       </c>
       <c r="F387" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G387" t="s">
         <v>1613</v>
       </c>
       <c r="H387" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I387" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="J387" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="K387" t="s">
         <v>1617</v>
       </c>
       <c r="L387" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="M387" t="s">
         <v>1615</v>
@@ -22250,31 +22250,31 @@
         <v>1204</v>
       </c>
       <c r="D388" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="E388" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="F388" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="G388" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="H388" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I388" t="s">
         <v>1619</v>
       </c>
       <c r="J388" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="K388" t="s">
         <v>1617</v>
       </c>
       <c r="L388" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="M388" t="s">
         <v>1615</v>
@@ -22294,34 +22294,34 @@
         <v>1205</v>
       </c>
       <c r="D389" t="s">
-        <v>1381</v>
+        <v>1340</v>
       </c>
       <c r="E389" t="s">
-        <v>1574</v>
+        <v>1533</v>
       </c>
       <c r="F389" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="G389" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="H389" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="I389" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="J389" t="s">
         <v>1613</v>
       </c>
       <c r="K389" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="L389" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M389" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N389" t="s">
         <v>1620</v>
@@ -22338,16 +22338,16 @@
         <v>1206</v>
       </c>
       <c r="D390" t="s">
-        <v>1340</v>
+        <v>1408</v>
       </c>
       <c r="E390" t="s">
-        <v>1533</v>
+        <v>1601</v>
       </c>
       <c r="F390" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="G390" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H390" t="s">
         <v>1619</v>
@@ -22356,13 +22356,13 @@
         <v>1616</v>
       </c>
       <c r="J390" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="K390" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="L390" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="M390" t="s">
         <v>1618</v>
@@ -22382,34 +22382,34 @@
         <v>1207</v>
       </c>
       <c r="D391" t="s">
-        <v>1409</v>
+        <v>1317</v>
       </c>
       <c r="E391" t="s">
-        <v>1602</v>
+        <v>1510</v>
       </c>
       <c r="F391" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="G391" t="s">
         <v>1613</v>
       </c>
       <c r="H391" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I391" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="J391" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="K391" t="s">
         <v>1614</v>
       </c>
       <c r="L391" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="M391" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N391" t="s">
         <v>1620</v>
@@ -22426,34 +22426,34 @@
         <v>1208</v>
       </c>
       <c r="D392" t="s">
-        <v>1317</v>
+        <v>1229</v>
       </c>
       <c r="E392" t="s">
-        <v>1510</v>
+        <v>1422</v>
       </c>
       <c r="F392" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="G392" t="s">
         <v>1613</v>
       </c>
       <c r="H392" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="I392" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="J392" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="K392" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="L392" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="M392" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="N392" t="s">
         <v>1620</v>
@@ -22470,34 +22470,34 @@
         <v>1209</v>
       </c>
       <c r="D393" t="s">
-        <v>1229</v>
+        <v>1409</v>
       </c>
       <c r="E393" t="s">
-        <v>1422</v>
+        <v>1602</v>
       </c>
       <c r="F393" t="s">
         <v>1608</v>
       </c>
       <c r="G393" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H393" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="I393" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="J393" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="K393" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="L393" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="M393" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="N393" t="s">
         <v>1620</v>
@@ -22514,31 +22514,31 @@
         <v>1210</v>
       </c>
       <c r="D394" t="s">
-        <v>1410</v>
+        <v>1372</v>
       </c>
       <c r="E394" t="s">
-        <v>1603</v>
+        <v>1565</v>
       </c>
       <c r="F394" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G394" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H394" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="I394" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="J394" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="K394" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="L394" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="M394" t="s">
         <v>1618</v>
@@ -22558,34 +22558,34 @@
         <v>1211</v>
       </c>
       <c r="D395" t="s">
-        <v>1372</v>
+        <v>1237</v>
       </c>
       <c r="E395" t="s">
-        <v>1565</v>
+        <v>1430</v>
       </c>
       <c r="F395" t="s">
         <v>1607</v>
       </c>
       <c r="G395" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="H395" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="I395" t="s">
         <v>1614</v>
       </c>
       <c r="J395" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="K395" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="L395" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="M395" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N395" t="s">
         <v>1620</v>
@@ -22602,34 +22602,34 @@
         <v>1212</v>
       </c>
       <c r="D396" t="s">
-        <v>1237</v>
+        <v>1410</v>
       </c>
       <c r="E396" t="s">
-        <v>1430</v>
+        <v>1603</v>
       </c>
       <c r="F396" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="G396" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="H396" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="I396" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="J396" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="K396" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="L396" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="M396" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N396" t="s">
         <v>1620</v>
@@ -22646,10 +22646,10 @@
         <v>1213</v>
       </c>
       <c r="D397" t="s">
-        <v>1411</v>
+        <v>1238</v>
       </c>
       <c r="E397" t="s">
-        <v>1604</v>
+        <v>1431</v>
       </c>
       <c r="F397" t="s">
         <v>1608</v>
@@ -22658,22 +22658,22 @@
         <v>1613</v>
       </c>
       <c r="H397" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="I397" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="J397" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="K397" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="L397" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M397" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="N397" t="s">
         <v>1620</v>
@@ -22690,34 +22690,34 @@
         <v>1214</v>
       </c>
       <c r="D398" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
       <c r="E398" t="s">
-        <v>1431</v>
+        <v>1436</v>
       </c>
       <c r="F398" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G398" t="s">
         <v>1613</v>
       </c>
       <c r="H398" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="I398" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="J398" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="K398" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="L398" t="s">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="M398" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="N398" t="s">
         <v>1620</v>
@@ -22734,25 +22734,25 @@
         <v>1215</v>
       </c>
       <c r="D399" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="E399" t="s">
-        <v>1436</v>
+        <v>1424</v>
       </c>
       <c r="F399" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="G399" t="s">
         <v>1613</v>
       </c>
       <c r="H399" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="I399" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="J399" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="K399" t="s">
         <v>1617</v>
@@ -22761,7 +22761,7 @@
         <v>1614</v>
       </c>
       <c r="M399" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="N399" t="s">
         <v>1620</v>
@@ -22778,34 +22778,34 @@
         <v>1216</v>
       </c>
       <c r="D400" t="s">
-        <v>1231</v>
+        <v>1411</v>
       </c>
       <c r="E400" t="s">
-        <v>1424</v>
+        <v>1604</v>
       </c>
       <c r="F400" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="G400" t="s">
         <v>1613</v>
       </c>
       <c r="H400" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="I400" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="J400" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="K400" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="L400" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="M400" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="N400" t="s">
         <v>1620</v>
@@ -22828,28 +22828,28 @@
         <v>1605</v>
       </c>
       <c r="F401" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="G401" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="H401" t="s">
         <v>1614</v>
       </c>
       <c r="I401" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="J401" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="K401" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="L401" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M401" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="N401" t="s">
         <v>1620</v>
@@ -22866,34 +22866,34 @@
         <v>1218</v>
       </c>
       <c r="D402" t="s">
-        <v>1413</v>
+        <v>1350</v>
       </c>
       <c r="E402" t="s">
-        <v>1606</v>
+        <v>1543</v>
       </c>
       <c r="F402" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G402" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="H402" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="I402" t="s">
         <v>1616</v>
       </c>
       <c r="J402" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="K402" t="s">
         <v>1615</v>
       </c>
       <c r="L402" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M402" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="N402" t="s">
         <v>1620</v>
@@ -22910,34 +22910,34 @@
         <v>1219</v>
       </c>
       <c r="D403" t="s">
-        <v>1350</v>
+        <v>1413</v>
       </c>
       <c r="E403" t="s">
-        <v>1543</v>
+        <v>1606</v>
       </c>
       <c r="F403" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G403" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H403" t="s">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="I403" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="J403" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="K403" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="L403" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M403" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="N403" t="s">
         <v>1620</v>
@@ -22954,34 +22954,34 @@
         <v>1220</v>
       </c>
       <c r="D404">
-        <v>1292</v>
+        <v>1223</v>
       </c>
       <c r="E404">
-        <v>64.59999999999999</v>
+        <v>61.15</v>
       </c>
       <c r="F404" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G404" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H404" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="I404" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="J404" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="K404" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="L404" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="M404" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="N404" t="s">
         <v>1620</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1261,12 +1261,12 @@
     <t>عبدالعظيم عصام مجدى جمعه</t>
   </si>
   <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
     <t>الحسن صلاح عبد المعز متولى</t>
   </si>
   <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2467,12 +2467,12 @@
     <t>30501252404612</t>
   </si>
   <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
     <t>30410232403738</t>
   </si>
   <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3673,12 +3673,12 @@
     <t>01032909577</t>
   </si>
   <si>
+    <t>01101887554</t>
+  </si>
+  <si>
     <t>01015294024</t>
   </si>
   <si>
-    <t>01101887554</t>
-  </si>
-  <si>
     <t>1353</t>
   </si>
   <si>
@@ -4255,7 +4255,7 @@
     <t>1336</t>
   </si>
   <si>
-    <t>1292</t>
+    <t>1223</t>
   </si>
   <si>
     <t>67.65</t>
@@ -4834,7 +4834,7 @@
     <t>66.8</t>
   </si>
   <si>
-    <t>64.6</t>
+    <t>61.15</t>
   </si>
   <si>
     <t>جيد</t>
@@ -22916,28 +22916,28 @@
         <v>1606</v>
       </c>
       <c r="F403" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G403" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H403" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="I403" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="J403" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="K403" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="L403" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="M403" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="N403" t="s">
         <v>1620</v>
@@ -22954,34 +22954,34 @@
         <v>1220</v>
       </c>
       <c r="D404">
-        <v>1223</v>
+        <v>1292</v>
       </c>
       <c r="E404">
-        <v>61.15</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F404" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G404" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H404" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="I404" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="J404" t="s">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="K404" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="L404" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="M404" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="N404" t="s">
         <v>1620</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1102,174 +1102,174 @@
     <t>شروق محمود زين محمد</t>
   </si>
   <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>كريم عبد الصالحين دخيل ابوسمره</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمود عبد العال احمد حماده</t>
+  </si>
+  <si>
+    <t>كريم حسن فاروق مليجى</t>
+  </si>
+  <si>
+    <t>عبدالعظيم عصام مجدى جمعه</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>نجوه ابراهيم عبد المستجاب عبد الغني</t>
+  </si>
+  <si>
     <t>روان محمد عبد الله حسن</t>
   </si>
   <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>كريم عبد الصالحين دخيل ابوسمره</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمود عبد العال احمد حماده</t>
-  </si>
-  <si>
-    <t>كريم حسن فاروق مليجى</t>
-  </si>
-  <si>
-    <t>عبدالعظيم عصام مجدى جمعه</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>نجوه ابراهيم عبد المستجاب عبد الغني</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2311,174 +2311,174 @@
     <t>30511062403607</t>
   </si>
   <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30311152404492</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30504182400893</t>
+  </si>
+  <si>
+    <t>30304010400698</t>
+  </si>
+  <si>
+    <t>30501252404612</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>٣٠٣١٠١٥٢٤٠٣٣٢٥</t>
+  </si>
+  <si>
     <t>30511052402505</t>
   </si>
   <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30311152404492</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30504182400893</t>
-  </si>
-  <si>
-    <t>30304010400698</t>
-  </si>
-  <si>
-    <t>30501252404612</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>٣٠٣١٠١٥٢٤٠٣٣٢٥</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3520,172 +3520,172 @@
     <t>01039109316</t>
   </si>
   <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01068463842</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01055420368</t>
+  </si>
+  <si>
+    <t>01095305700</t>
+  </si>
+  <si>
+    <t>01032909577</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01122877252</t>
+  </si>
+  <si>
     <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01068463842</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01055420368</t>
-  </si>
-  <si>
-    <t>01095305700</t>
-  </si>
-  <si>
-    <t>01032909577</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01122877252</t>
   </si>
   <si>
     <t>1353</t>
@@ -20593,34 +20593,34 @@
         <v>1168</v>
       </c>
       <c r="D350" t="s">
-        <v>1299</v>
+        <v>1247</v>
       </c>
       <c r="E350" t="s">
-        <v>1493</v>
+        <v>1441</v>
       </c>
       <c r="F350" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G350" t="s">
         <v>1618</v>
       </c>
       <c r="H350" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="I350" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="J350" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="K350" t="s">
         <v>1622</v>
       </c>
       <c r="L350" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="M350" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="N350" t="s">
         <v>1625</v>
@@ -20637,34 +20637,34 @@
         <v>1169</v>
       </c>
       <c r="D351" t="s">
-        <v>1247</v>
+        <v>1263</v>
       </c>
       <c r="E351" t="s">
-        <v>1441</v>
+        <v>1457</v>
       </c>
       <c r="F351" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="G351" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="H351" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="I351" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="J351" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="K351" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="L351" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="M351" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="N351" t="s">
         <v>1625</v>
@@ -20681,34 +20681,34 @@
         <v>1170</v>
       </c>
       <c r="D352" t="s">
-        <v>1263</v>
+        <v>1310</v>
       </c>
       <c r="E352" t="s">
-        <v>1457</v>
+        <v>1504</v>
       </c>
       <c r="F352" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G352" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="H352" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="I352" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="J352" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="K352" t="s">
         <v>1620</v>
       </c>
       <c r="L352" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M352" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="N352" t="s">
         <v>1625</v>
@@ -20725,19 +20725,19 @@
         <v>1171</v>
       </c>
       <c r="D353" t="s">
-        <v>1310</v>
+        <v>1329</v>
       </c>
       <c r="E353" t="s">
-        <v>1504</v>
+        <v>1523</v>
       </c>
       <c r="F353" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="G353" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H353" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="I353" t="s">
         <v>1621</v>
@@ -20746,10 +20746,10 @@
         <v>1624</v>
       </c>
       <c r="K353" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="L353" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="M353" t="s">
         <v>1623</v>
@@ -20769,34 +20769,34 @@
         <v>1172</v>
       </c>
       <c r="D354" t="s">
-        <v>1329</v>
+        <v>1244</v>
       </c>
       <c r="E354" t="s">
-        <v>1523</v>
+        <v>1438</v>
       </c>
       <c r="F354" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G354" t="s">
         <v>1619</v>
       </c>
       <c r="H354" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="I354" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="J354" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="K354" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="L354" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="M354" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N354" t="s">
         <v>1625</v>
@@ -20813,34 +20813,34 @@
         <v>1173</v>
       </c>
       <c r="D355" t="s">
-        <v>1244</v>
+        <v>1403</v>
       </c>
       <c r="E355" t="s">
-        <v>1438</v>
+        <v>1597</v>
       </c>
       <c r="F355" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G355" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="H355" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I355" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="J355" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="K355" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="L355" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M355" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="N355" t="s">
         <v>1625</v>
@@ -20857,34 +20857,34 @@
         <v>1174</v>
       </c>
       <c r="D356" t="s">
-        <v>1403</v>
+        <v>1290</v>
       </c>
       <c r="E356" t="s">
-        <v>1597</v>
+        <v>1484</v>
       </c>
       <c r="F356" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G356" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="H356" t="s">
         <v>1621</v>
       </c>
       <c r="I356" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="J356" t="s">
         <v>1620</v>
       </c>
       <c r="K356" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="L356" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M356" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="N356" t="s">
         <v>1625</v>
@@ -20901,31 +20901,31 @@
         <v>1175</v>
       </c>
       <c r="D357" t="s">
-        <v>1290</v>
+        <v>1259</v>
       </c>
       <c r="E357" t="s">
-        <v>1484</v>
+        <v>1453</v>
       </c>
       <c r="F357" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G357" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="H357" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="I357" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="J357" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="K357" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="L357" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="M357" t="s">
         <v>1623</v>
@@ -20945,31 +20945,31 @@
         <v>1176</v>
       </c>
       <c r="D358" t="s">
-        <v>1259</v>
+        <v>1302</v>
       </c>
       <c r="E358" t="s">
-        <v>1453</v>
+        <v>1496</v>
       </c>
       <c r="F358" t="s">
         <v>1613</v>
       </c>
       <c r="G358" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="H358" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="I358" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="J358" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="K358" t="s">
         <v>1622</v>
       </c>
       <c r="L358" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="M358" t="s">
         <v>1623</v>
@@ -20989,31 +20989,31 @@
         <v>1177</v>
       </c>
       <c r="D359" t="s">
-        <v>1302</v>
+        <v>1270</v>
       </c>
       <c r="E359" t="s">
-        <v>1496</v>
+        <v>1464</v>
       </c>
       <c r="F359" t="s">
         <v>1613</v>
       </c>
       <c r="G359" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H359" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="I359" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="J359" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="K359" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="L359" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="M359" t="s">
         <v>1623</v>
@@ -21033,34 +21033,34 @@
         <v>1178</v>
       </c>
       <c r="D360" t="s">
-        <v>1270</v>
+        <v>1355</v>
       </c>
       <c r="E360" t="s">
-        <v>1464</v>
+        <v>1549</v>
       </c>
       <c r="F360" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G360" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H360" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="I360" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="J360" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="K360" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="L360" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="M360" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="N360" t="s">
         <v>1625</v>
@@ -21077,10 +21077,10 @@
         <v>1179</v>
       </c>
       <c r="D361" t="s">
-        <v>1355</v>
+        <v>1404</v>
       </c>
       <c r="E361" t="s">
-        <v>1549</v>
+        <v>1598</v>
       </c>
       <c r="F361" t="s">
         <v>1612</v>
@@ -21121,34 +21121,34 @@
         <v>1180</v>
       </c>
       <c r="D362" t="s">
-        <v>1404</v>
+        <v>1243</v>
       </c>
       <c r="E362" t="s">
-        <v>1598</v>
+        <v>1437</v>
       </c>
       <c r="F362" t="s">
         <v>1612</v>
       </c>
       <c r="G362" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H362" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="I362" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="J362" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="K362" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="L362" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="M362" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="N362" t="s">
         <v>1625</v>
@@ -21165,31 +21165,31 @@
         <v>1181</v>
       </c>
       <c r="D363" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
       <c r="E363" t="s">
-        <v>1437</v>
+        <v>1449</v>
       </c>
       <c r="F363" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="G363" t="s">
         <v>1618</v>
       </c>
       <c r="H363" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="I363" t="s">
         <v>1624</v>
       </c>
       <c r="J363" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="K363" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="L363" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="M363" t="s">
         <v>1623</v>
@@ -21209,34 +21209,34 @@
         <v>1182</v>
       </c>
       <c r="D364" t="s">
-        <v>1255</v>
+        <v>1405</v>
       </c>
       <c r="E364" t="s">
-        <v>1449</v>
+        <v>1599</v>
       </c>
       <c r="F364" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="G364" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H364" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="I364" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="J364" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="K364" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="L364" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="M364" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="N364" t="s">
         <v>1625</v>
@@ -21253,34 +21253,34 @@
         <v>1183</v>
       </c>
       <c r="D365" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E365" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="F365" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="G365" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H365" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="I365" t="s">
         <v>1620</v>
       </c>
       <c r="J365" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="K365" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="L365" t="s">
         <v>1622</v>
       </c>
       <c r="M365" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="N365" t="s">
         <v>1625</v>
@@ -21297,34 +21297,34 @@
         <v>1184</v>
       </c>
       <c r="D366" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="E366" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="F366" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="G366" t="s">
         <v>1618</v>
       </c>
       <c r="H366" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I366" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="J366" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="K366" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="L366" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M366" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N366" t="s">
         <v>1625</v>
@@ -21341,13 +21341,13 @@
         <v>1185</v>
       </c>
       <c r="D367" t="s">
-        <v>1407</v>
+        <v>1253</v>
       </c>
       <c r="E367" t="s">
-        <v>1601</v>
+        <v>1447</v>
       </c>
       <c r="F367" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G367" t="s">
         <v>1618</v>
@@ -21362,13 +21362,13 @@
         <v>1619</v>
       </c>
       <c r="K367" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="L367" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M367" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="N367" t="s">
         <v>1625</v>
@@ -21385,13 +21385,13 @@
         <v>1186</v>
       </c>
       <c r="D368" t="s">
-        <v>1253</v>
+        <v>1235</v>
       </c>
       <c r="E368" t="s">
-        <v>1447</v>
+        <v>1429</v>
       </c>
       <c r="F368" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="G368" t="s">
         <v>1618</v>
@@ -21403,16 +21403,16 @@
         <v>1624</v>
       </c>
       <c r="J368" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="K368" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="L368" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M368" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="N368" t="s">
         <v>1625</v>
@@ -21429,22 +21429,22 @@
         <v>1187</v>
       </c>
       <c r="D369" t="s">
-        <v>1235</v>
+        <v>1293</v>
       </c>
       <c r="E369" t="s">
-        <v>1429</v>
+        <v>1487</v>
       </c>
       <c r="F369" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="G369" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H369" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="I369" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="J369" t="s">
         <v>1620</v>
@@ -21453,10 +21453,10 @@
         <v>1622</v>
       </c>
       <c r="L369" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="M369" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="N369" t="s">
         <v>1625</v>
@@ -21473,31 +21473,31 @@
         <v>1188</v>
       </c>
       <c r="D370" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="E370" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="F370" t="s">
         <v>1613</v>
       </c>
       <c r="G370" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H370" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="I370" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="J370" t="s">
         <v>1620</v>
       </c>
       <c r="K370" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="L370" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="M370" t="s">
         <v>1624</v>
@@ -21517,34 +21517,34 @@
         <v>1189</v>
       </c>
       <c r="D371" t="s">
-        <v>1299</v>
+        <v>1239</v>
       </c>
       <c r="E371" t="s">
-        <v>1493</v>
+        <v>1433</v>
       </c>
       <c r="F371" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="G371" t="s">
         <v>1618</v>
       </c>
       <c r="H371" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="I371" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J371" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="K371" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="L371" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M371" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="N371" t="s">
         <v>1625</v>
@@ -21561,34 +21561,34 @@
         <v>1190</v>
       </c>
       <c r="D372" t="s">
-        <v>1239</v>
+        <v>1261</v>
       </c>
       <c r="E372" t="s">
-        <v>1433</v>
+        <v>1455</v>
       </c>
       <c r="F372" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G372" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H372" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="I372" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J372" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="K372" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="L372" t="s">
         <v>1623</v>
       </c>
       <c r="M372" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="N372" t="s">
         <v>1625</v>
@@ -21605,34 +21605,34 @@
         <v>1191</v>
       </c>
       <c r="D373" t="s">
-        <v>1261</v>
+        <v>1364</v>
       </c>
       <c r="E373" t="s">
-        <v>1455</v>
+        <v>1558</v>
       </c>
       <c r="F373" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G373" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H373" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="I373" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J373" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="K373" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="L373" t="s">
         <v>1623</v>
       </c>
       <c r="M373" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="N373" t="s">
         <v>1625</v>
@@ -21649,10 +21649,10 @@
         <v>1192</v>
       </c>
       <c r="D374" t="s">
-        <v>1364</v>
+        <v>1235</v>
       </c>
       <c r="E374" t="s">
-        <v>1558</v>
+        <v>1429</v>
       </c>
       <c r="F374" t="s">
         <v>1613</v>
@@ -21661,13 +21661,13 @@
         <v>1618</v>
       </c>
       <c r="H374" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="I374" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J374" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="K374" t="s">
         <v>1619</v>
@@ -21676,7 +21676,7 @@
         <v>1623</v>
       </c>
       <c r="M374" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="N374" t="s">
         <v>1625</v>
@@ -21693,28 +21693,28 @@
         <v>1193</v>
       </c>
       <c r="D375" t="s">
-        <v>1235</v>
+        <v>1290</v>
       </c>
       <c r="E375" t="s">
-        <v>1429</v>
+        <v>1484</v>
       </c>
       <c r="F375" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G375" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H375" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I375" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="J375" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="K375" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="L375" t="s">
         <v>1623</v>
@@ -21737,31 +21737,31 @@
         <v>1194</v>
       </c>
       <c r="D376" t="s">
-        <v>1290</v>
+        <v>1272</v>
       </c>
       <c r="E376" t="s">
-        <v>1484</v>
+        <v>1466</v>
       </c>
       <c r="F376" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="G376" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H376" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="I376" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="J376" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="K376" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="L376" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M376" t="s">
         <v>1620</v>
@@ -21781,25 +21781,25 @@
         <v>1195</v>
       </c>
       <c r="D377" t="s">
-        <v>1272</v>
+        <v>1379</v>
       </c>
       <c r="E377" t="s">
-        <v>1466</v>
+        <v>1573</v>
       </c>
       <c r="F377" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G377" t="s">
         <v>1618</v>
       </c>
       <c r="H377" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I377" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J377" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="K377" t="s">
         <v>1619</v>
@@ -21808,7 +21808,7 @@
         <v>1622</v>
       </c>
       <c r="M377" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="N377" t="s">
         <v>1625</v>
@@ -21825,34 +21825,34 @@
         <v>1196</v>
       </c>
       <c r="D378" t="s">
-        <v>1379</v>
+        <v>1353</v>
       </c>
       <c r="E378" t="s">
-        <v>1573</v>
+        <v>1547</v>
       </c>
       <c r="F378" t="s">
         <v>1612</v>
       </c>
       <c r="G378" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="H378" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="I378" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="J378" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="K378" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="L378" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M378" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N378" t="s">
         <v>1625</v>
@@ -21869,34 +21869,34 @@
         <v>1197</v>
       </c>
       <c r="D379" t="s">
-        <v>1353</v>
+        <v>1407</v>
       </c>
       <c r="E379" t="s">
-        <v>1547</v>
+        <v>1601</v>
       </c>
       <c r="F379" t="s">
         <v>1612</v>
       </c>
       <c r="G379" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="H379" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="I379" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="J379" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="K379" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="L379" t="s">
         <v>1623</v>
       </c>
       <c r="M379" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="N379" t="s">
         <v>1625</v>
@@ -21913,34 +21913,34 @@
         <v>1198</v>
       </c>
       <c r="D380" t="s">
-        <v>1407</v>
+        <v>1258</v>
       </c>
       <c r="E380" t="s">
-        <v>1601</v>
+        <v>1452</v>
       </c>
       <c r="F380" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="G380" t="s">
         <v>1618</v>
       </c>
       <c r="H380" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="I380" t="s">
         <v>1624</v>
       </c>
       <c r="J380" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="K380" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="L380" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M380" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="N380" t="s">
         <v>1625</v>
@@ -21957,34 +21957,34 @@
         <v>1199</v>
       </c>
       <c r="D381" t="s">
-        <v>1258</v>
+        <v>1272</v>
       </c>
       <c r="E381" t="s">
-        <v>1452</v>
+        <v>1466</v>
       </c>
       <c r="F381" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="G381" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H381" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="I381" t="s">
         <v>1624</v>
       </c>
       <c r="J381" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="K381" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="L381" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M381" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N381" t="s">
         <v>1625</v>
@@ -22001,34 +22001,34 @@
         <v>1200</v>
       </c>
       <c r="D382" t="s">
-        <v>1272</v>
+        <v>1408</v>
       </c>
       <c r="E382" t="s">
-        <v>1466</v>
+        <v>1602</v>
       </c>
       <c r="F382" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="G382" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H382" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="I382" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J382" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="K382" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="L382" t="s">
         <v>1623</v>
       </c>
       <c r="M382" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="N382" t="s">
         <v>1625</v>
@@ -22045,34 +22045,34 @@
         <v>1201</v>
       </c>
       <c r="D383" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="E383" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="F383" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="G383" t="s">
         <v>1618</v>
       </c>
       <c r="H383" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I383" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J383" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="K383" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="L383" t="s">
         <v>1623</v>
       </c>
       <c r="M383" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="N383" t="s">
         <v>1625</v>
@@ -22089,34 +22089,34 @@
         <v>1202</v>
       </c>
       <c r="D384" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E384" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="F384" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="G384" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="H384" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="I384" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J384" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="K384" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="L384" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="M384" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="N384" t="s">
         <v>1625</v>
@@ -22133,34 +22133,34 @@
         <v>1203</v>
       </c>
       <c r="D385" t="s">
-        <v>1410</v>
+        <v>1299</v>
       </c>
       <c r="E385" t="s">
-        <v>1604</v>
+        <v>1493</v>
       </c>
       <c r="F385" t="s">
         <v>1613</v>
       </c>
       <c r="G385" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="H385" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="I385" t="s">
         <v>1621</v>
       </c>
       <c r="J385" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="K385" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="L385" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="M385" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N385" t="s">
         <v>1625</v>
@@ -22177,31 +22177,31 @@
         <v>1204</v>
       </c>
       <c r="D386" t="s">
-        <v>1299</v>
+        <v>1388</v>
       </c>
       <c r="E386" t="s">
-        <v>1493</v>
+        <v>1582</v>
       </c>
       <c r="F386" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G386" t="s">
         <v>1618</v>
       </c>
       <c r="H386" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I386" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J386" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="K386" t="s">
         <v>1622</v>
       </c>
       <c r="L386" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="M386" t="s">
         <v>1620</v>
@@ -22221,31 +22221,31 @@
         <v>1205</v>
       </c>
       <c r="D387" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="E387" t="s">
-        <v>1582</v>
+        <v>1578</v>
       </c>
       <c r="F387" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="G387" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="H387" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="I387" t="s">
         <v>1624</v>
       </c>
       <c r="J387" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="K387" t="s">
         <v>1622</v>
       </c>
       <c r="L387" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="M387" t="s">
         <v>1620</v>
@@ -22265,34 +22265,34 @@
         <v>1206</v>
       </c>
       <c r="D388" t="s">
-        <v>1384</v>
+        <v>1343</v>
       </c>
       <c r="E388" t="s">
-        <v>1578</v>
+        <v>1537</v>
       </c>
       <c r="F388" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G388" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="H388" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="I388" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J388" t="s">
         <v>1618</v>
       </c>
       <c r="K388" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="L388" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M388" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="N388" t="s">
         <v>1625</v>
@@ -22309,16 +22309,16 @@
         <v>1207</v>
       </c>
       <c r="D389" t="s">
-        <v>1343</v>
+        <v>1411</v>
       </c>
       <c r="E389" t="s">
-        <v>1537</v>
+        <v>1605</v>
       </c>
       <c r="F389" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="G389" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H389" t="s">
         <v>1624</v>
@@ -22327,13 +22327,13 @@
         <v>1621</v>
       </c>
       <c r="J389" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="K389" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="L389" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="M389" t="s">
         <v>1623</v>
@@ -22353,34 +22353,34 @@
         <v>1208</v>
       </c>
       <c r="D390" t="s">
-        <v>1411</v>
+        <v>1320</v>
       </c>
       <c r="E390" t="s">
-        <v>1605</v>
+        <v>1514</v>
       </c>
       <c r="F390" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G390" t="s">
         <v>1618</v>
       </c>
       <c r="H390" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I390" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J390" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="K390" t="s">
         <v>1619</v>
       </c>
       <c r="L390" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="M390" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N390" t="s">
         <v>1625</v>
@@ -22397,34 +22397,34 @@
         <v>1209</v>
       </c>
       <c r="D391" t="s">
-        <v>1320</v>
+        <v>1232</v>
       </c>
       <c r="E391" t="s">
-        <v>1514</v>
+        <v>1426</v>
       </c>
       <c r="F391" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G391" t="s">
         <v>1618</v>
       </c>
       <c r="H391" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="I391" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="J391" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="K391" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="L391" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="M391" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="N391" t="s">
         <v>1625</v>
@@ -22441,34 +22441,34 @@
         <v>1210</v>
       </c>
       <c r="D392" t="s">
-        <v>1232</v>
+        <v>1412</v>
       </c>
       <c r="E392" t="s">
-        <v>1426</v>
+        <v>1606</v>
       </c>
       <c r="F392" t="s">
         <v>1613</v>
       </c>
       <c r="G392" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H392" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="I392" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="J392" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="K392" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="L392" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="M392" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="N392" t="s">
         <v>1625</v>
@@ -22485,31 +22485,31 @@
         <v>1211</v>
       </c>
       <c r="D393" t="s">
-        <v>1412</v>
+        <v>1375</v>
       </c>
       <c r="E393" t="s">
-        <v>1606</v>
+        <v>1569</v>
       </c>
       <c r="F393" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G393" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H393" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="I393" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="J393" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="K393" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="L393" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="M393" t="s">
         <v>1623</v>
@@ -22529,34 +22529,34 @@
         <v>1212</v>
       </c>
       <c r="D394" t="s">
-        <v>1375</v>
+        <v>1240</v>
       </c>
       <c r="E394" t="s">
-        <v>1569</v>
+        <v>1434</v>
       </c>
       <c r="F394" t="s">
         <v>1612</v>
       </c>
       <c r="G394" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="H394" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="I394" t="s">
         <v>1619</v>
       </c>
       <c r="J394" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="K394" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="L394" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="M394" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N394" t="s">
         <v>1625</v>
@@ -22573,34 +22573,34 @@
         <v>1213</v>
       </c>
       <c r="D395" t="s">
-        <v>1240</v>
+        <v>1413</v>
       </c>
       <c r="E395" t="s">
-        <v>1434</v>
+        <v>1607</v>
       </c>
       <c r="F395" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="G395" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="H395" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I395" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="J395" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="K395" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="L395" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="M395" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="N395" t="s">
         <v>1625</v>
@@ -22617,10 +22617,10 @@
         <v>1214</v>
       </c>
       <c r="D396" t="s">
-        <v>1413</v>
+        <v>1241</v>
       </c>
       <c r="E396" t="s">
-        <v>1607</v>
+        <v>1435</v>
       </c>
       <c r="F396" t="s">
         <v>1613</v>
@@ -22629,22 +22629,22 @@
         <v>1618</v>
       </c>
       <c r="H396" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="I396" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="J396" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="K396" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="L396" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M396" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="N396" t="s">
         <v>1625</v>
@@ -22661,34 +22661,34 @@
         <v>1215</v>
       </c>
       <c r="D397" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="E397" t="s">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="F397" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="G397" t="s">
         <v>1618</v>
       </c>
       <c r="H397" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="I397" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J397" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="K397" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="L397" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="M397" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="N397" t="s">
         <v>1625</v>
@@ -22705,25 +22705,25 @@
         <v>1216</v>
       </c>
       <c r="D398" t="s">
-        <v>1246</v>
+        <v>1234</v>
       </c>
       <c r="E398" t="s">
-        <v>1440</v>
+        <v>1428</v>
       </c>
       <c r="F398" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G398" t="s">
         <v>1618</v>
       </c>
       <c r="H398" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="I398" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J398" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="K398" t="s">
         <v>1622</v>
@@ -22732,7 +22732,7 @@
         <v>1619</v>
       </c>
       <c r="M398" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="N398" t="s">
         <v>1625</v>
@@ -22749,34 +22749,34 @@
         <v>1217</v>
       </c>
       <c r="D399" t="s">
-        <v>1234</v>
+        <v>1414</v>
       </c>
       <c r="E399" t="s">
-        <v>1428</v>
+        <v>1608</v>
       </c>
       <c r="F399" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="G399" t="s">
         <v>1618</v>
       </c>
       <c r="H399" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="I399" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="J399" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="K399" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="L399" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="M399" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="N399" t="s">
         <v>1625</v>
@@ -22793,34 +22793,34 @@
         <v>1218</v>
       </c>
       <c r="D400" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="E400" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="F400" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="G400" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="H400" t="s">
         <v>1619</v>
       </c>
       <c r="I400" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="J400" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="K400" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="L400" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="M400" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="N400" t="s">
         <v>1625</v>
@@ -22837,34 +22837,34 @@
         <v>1219</v>
       </c>
       <c r="D401" t="s">
-        <v>1415</v>
+        <v>1353</v>
       </c>
       <c r="E401" t="s">
-        <v>1609</v>
+        <v>1547</v>
       </c>
       <c r="F401" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="G401" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="H401" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="I401" t="s">
         <v>1621</v>
       </c>
       <c r="J401" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="K401" t="s">
         <v>1620</v>
       </c>
       <c r="L401" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="M401" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="N401" t="s">
         <v>1625</v>
@@ -22881,10 +22881,10 @@
         <v>1220</v>
       </c>
       <c r="D402" t="s">
-        <v>1353</v>
+        <v>1416</v>
       </c>
       <c r="E402" t="s">
-        <v>1547</v>
+        <v>1610</v>
       </c>
       <c r="F402" t="s">
         <v>1614</v>
@@ -22893,22 +22893,22 @@
         <v>1618</v>
       </c>
       <c r="H402" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
       <c r="I402" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="J402" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="K402" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="L402" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="M402" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="N402" t="s">
         <v>1625</v>
@@ -22925,34 +22925,34 @@
         <v>1221</v>
       </c>
       <c r="D403" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="E403" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="F403" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="G403" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H403" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="I403" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="J403" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="K403" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="L403" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="M403" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="N403" t="s">
         <v>1625</v>
@@ -22969,34 +22969,34 @@
         <v>1222</v>
       </c>
       <c r="D404" t="s">
-        <v>1417</v>
+        <v>1256</v>
       </c>
       <c r="E404" t="s">
-        <v>1611</v>
+        <v>1450</v>
       </c>
       <c r="F404" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="G404" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H404" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="I404" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="J404" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="K404" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="L404" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="M404" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="N404" t="s">
         <v>1625</v>
@@ -23013,10 +23013,10 @@
         <v>1223</v>
       </c>
       <c r="D405">
-        <v>1364</v>
+        <v>1351</v>
       </c>
       <c r="E405">
-        <v>68.2</v>
+        <v>67.55</v>
       </c>
       <c r="F405" t="s">
         <v>1612</v>
@@ -23025,19 +23025,19 @@
         <v>1618</v>
       </c>
       <c r="H405" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I405" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J405" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="K405" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="L405" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="M405" t="s">
         <v>1620</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1264,12 +1264,12 @@
     <t>الحسن صلاح عبد المعز متولى</t>
   </si>
   <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
     <t>نجوه ابراهيم عبد المستجاب عبد الغني</t>
   </si>
   <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2473,12 +2473,12 @@
     <t>30410232403738</t>
   </si>
   <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
     <t>٣٠٣١٠١٥٢٤٠٣٣٢٥</t>
   </si>
   <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3682,10 +3682,10 @@
     <t>01015294024</t>
   </si>
   <si>
+    <t>01148497118</t>
+  </si>
+  <si>
     <t>01122877252</t>
-  </si>
-  <si>
-    <t>01148497118</t>
   </si>
   <si>
     <t>1353</t>
@@ -22969,10 +22969,10 @@
         <v>1222</v>
       </c>
       <c r="D404" t="s">
-        <v>1256</v>
+        <v>1299</v>
       </c>
       <c r="E404" t="s">
-        <v>1450</v>
+        <v>1493</v>
       </c>
       <c r="F404" t="s">
         <v>1612</v>
@@ -22981,19 +22981,19 @@
         <v>1618</v>
       </c>
       <c r="H404" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="I404" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="J404" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="K404" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="L404" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="M404" t="s">
         <v>1620</v>
@@ -23013,10 +23013,10 @@
         <v>1223</v>
       </c>
       <c r="D405">
-        <v>1351</v>
+        <v>1364</v>
       </c>
       <c r="E405">
-        <v>67.55</v>
+        <v>68.2</v>
       </c>
       <c r="F405" t="s">
         <v>1612</v>
@@ -23025,19 +23025,19 @@
         <v>1618</v>
       </c>
       <c r="H405" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="I405" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J405" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="K405" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="L405" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="M405" t="s">
         <v>1620</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -808,480 +808,480 @@
     <t>رانيا سيد صلاح الدين على</t>
   </si>
   <si>
+    <t>رقيه على محمد خلف</t>
+  </si>
+  <si>
+    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
+  </si>
+  <si>
+    <t>ابراهيم محمود محمد عبدالنعيم</t>
+  </si>
+  <si>
+    <t>بهاء الدين محمد ابراهيم على</t>
+  </si>
+  <si>
+    <t>يوسف احمد سمير محمد</t>
+  </si>
+  <si>
+    <t>محمد رجب لطفى كامل</t>
+  </si>
+  <si>
+    <t>احمد طارق محمد محمود</t>
+  </si>
+  <si>
+    <t>عبدالله محمد سيد صادق</t>
+  </si>
+  <si>
+    <t>سهيله عبد القادر احمد عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد توفيق محمد محمد</t>
+  </si>
+  <si>
+    <t>مريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>شهد حسين محمود صابر</t>
+  </si>
+  <si>
+    <t>محمد سرحان محمد زكى</t>
+  </si>
+  <si>
+    <t>لمياء عبد القادر محمد فتحى</t>
+  </si>
+  <si>
+    <t>أميمة رأفت محمود احمد</t>
+  </si>
+  <si>
+    <t>احمد رمضان محمد عبد الحميد</t>
+  </si>
+  <si>
+    <t>كريم محمد عبد الوهاب عيد</t>
+  </si>
+  <si>
+    <t>عمر رضا تونى طلبه</t>
+  </si>
+  <si>
+    <t>عبدالله ناصر أنور عبد المجيد</t>
+  </si>
+  <si>
+    <t>اندرو محروس مختار مهنى</t>
+  </si>
+  <si>
+    <t>فاطمه ناجى عبد السلام حسن</t>
+  </si>
+  <si>
+    <t>ماركو مجدى مكرم فريد</t>
+  </si>
+  <si>
+    <t>رانيا نبيل احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
+  </si>
+  <si>
+    <t>كريمان فضل جابر محمد</t>
+  </si>
+  <si>
+    <t>احمد شحاته عطا أحمد</t>
+  </si>
+  <si>
+    <t>محمد عصام عبد العزيز دكرورى</t>
+  </si>
+  <si>
+    <t>يوسف محمد سعد اصمعى</t>
+  </si>
+  <si>
+    <t>حازم محمد احمد هارون</t>
+  </si>
+  <si>
+    <t>الاء سميح عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>احمد ربيع احمد خلف</t>
+  </si>
+  <si>
+    <t>هاجر حماد محمد حسن</t>
+  </si>
+  <si>
+    <t>حمزه محمد حمدى عرابى</t>
+  </si>
+  <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>كريم عبد الصالحين دخيل ابوسمره</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمود عبد العال احمد حماده</t>
+  </si>
+  <si>
+    <t>كريم حسن فاروق مليجى</t>
+  </si>
+  <si>
+    <t>عبدالعظيم عصام مجدى جمعه</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>نجوه ابراهيم عبد المستجاب عبد الغني</t>
+  </si>
+  <si>
+    <t>يوسف رمضان جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
+  </si>
+  <si>
+    <t>ابوزيد محمد ابوزيد عبدالرحيم</t>
+  </si>
+  <si>
+    <t>على فايز محمد سليمان</t>
+  </si>
+  <si>
+    <t>مصطفى محمود محمد حسان</t>
+  </si>
+  <si>
+    <t>نورهان يوسف عبدالرحيم يوسف</t>
+  </si>
+  <si>
     <t>حازم عباس خليفة عباس</t>
   </si>
   <si>
-    <t>رقيه على محمد خلف</t>
-  </si>
-  <si>
-    <t>زينب نشأت عبدالحميد محمود القشيرى</t>
-  </si>
-  <si>
-    <t>ابراهيم محمود محمد عبدالنعيم</t>
-  </si>
-  <si>
-    <t>بهاء الدين محمد ابراهيم على</t>
-  </si>
-  <si>
-    <t>يوسف احمد سمير محمد</t>
-  </si>
-  <si>
-    <t>محمد رجب لطفى كامل</t>
-  </si>
-  <si>
-    <t>احمد طارق محمد محمود</t>
-  </si>
-  <si>
-    <t>عبدالله محمد سيد صادق</t>
-  </si>
-  <si>
-    <t>سهيله عبد القادر احمد عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد توفيق محمد محمد</t>
-  </si>
-  <si>
-    <t>مريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>شهد حسين محمود صابر</t>
-  </si>
-  <si>
-    <t>محمد سرحان محمد زكى</t>
-  </si>
-  <si>
-    <t>لمياء عبد القادر محمد فتحى</t>
-  </si>
-  <si>
-    <t>أميمة رأفت محمود احمد</t>
-  </si>
-  <si>
-    <t>احمد رمضان محمد عبد الحميد</t>
-  </si>
-  <si>
-    <t>كريم محمد عبد الوهاب عيد</t>
-  </si>
-  <si>
-    <t>عمر رضا تونى طلبه</t>
-  </si>
-  <si>
-    <t>عبدالله ناصر أنور عبد المجيد</t>
-  </si>
-  <si>
-    <t>اندرو محروس مختار مهنى</t>
-  </si>
-  <si>
-    <t>فاطمه ناجى عبد السلام حسن</t>
-  </si>
-  <si>
-    <t>ماركو مجدى مكرم فريد</t>
-  </si>
-  <si>
-    <t>رانيا نبيل احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>منه الله اشرف عبدالعزيز توفيق عبدالنظير</t>
-  </si>
-  <si>
-    <t>كريمان فضل جابر محمد</t>
-  </si>
-  <si>
-    <t>احمد شحاته عطا أحمد</t>
-  </si>
-  <si>
-    <t>محمد عصام عبد العزيز دكرورى</t>
-  </si>
-  <si>
-    <t>يوسف محمد سعد اصمعى</t>
-  </si>
-  <si>
-    <t>حازم محمد احمد هارون</t>
-  </si>
-  <si>
-    <t>الاء سميح عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>احمد ربيع احمد خلف</t>
-  </si>
-  <si>
-    <t>هاجر حماد محمد حسن</t>
-  </si>
-  <si>
-    <t>حمزه محمد حمدى عرابى</t>
-  </si>
-  <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>كريم عبد الصالحين دخيل ابوسمره</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمود عبد العال احمد حماده</t>
-  </si>
-  <si>
-    <t>كريم حسن فاروق مليجى</t>
-  </si>
-  <si>
-    <t>عبدالعظيم عصام مجدى جمعه</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>نجوه ابراهيم عبد المستجاب عبد الغني</t>
-  </si>
-  <si>
-    <t>يوسف رمضان جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
-  </si>
-  <si>
-    <t>ابوزيد محمد ابوزيد عبدالرحيم</t>
-  </si>
-  <si>
-    <t>على فايز محمد سليمان</t>
-  </si>
-  <si>
-    <t>مصطفى محمود محمد حسان</t>
-  </si>
-  <si>
-    <t>نورهان يوسف عبدالرحيم يوسف</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2029,480 +2029,480 @@
     <t>30409222403367</t>
   </si>
   <si>
+    <t>30411102404968</t>
+  </si>
+  <si>
+    <t>30310012403406</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
+  </si>
+  <si>
+    <t>30506082400619</t>
+  </si>
+  <si>
+    <t>30503242401413</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
+  </si>
+  <si>
+    <t>30507262401954</t>
+  </si>
+  <si>
+    <t>30405262402457</t>
+  </si>
+  <si>
+    <t>30410312400403</t>
+  </si>
+  <si>
+    <t>30506152402932</t>
+  </si>
+  <si>
+    <t>30509052401709</t>
+  </si>
+  <si>
+    <t>30408182401521</t>
+  </si>
+  <si>
+    <t>30410232401859</t>
+  </si>
+  <si>
+    <t>30409222402263</t>
+  </si>
+  <si>
+    <t>30308062400144</t>
+  </si>
+  <si>
+    <t>30302142401658</t>
+  </si>
+  <si>
+    <t>30506272400259</t>
+  </si>
+  <si>
+    <t>30409012413599</t>
+  </si>
+  <si>
+    <t>30601162402453</t>
+  </si>
+  <si>
+    <t>30310012402973</t>
+  </si>
+  <si>
+    <t>30506170300209</t>
+  </si>
+  <si>
+    <t>30409172401791</t>
+  </si>
+  <si>
+    <t>30504252402961</t>
+  </si>
+  <si>
+    <t>30603112402846</t>
+  </si>
+  <si>
+    <t>30406012410949</t>
+  </si>
+  <si>
+    <t>30501092401999</t>
+  </si>
+  <si>
+    <t>30409012406231</t>
+  </si>
+  <si>
+    <t>30505012406451</t>
+  </si>
+  <si>
+    <t>30504302401554</t>
+  </si>
+  <si>
+    <t>30012012409985</t>
+  </si>
+  <si>
+    <t>30401022401237</t>
+  </si>
+  <si>
+    <t>30507152402505</t>
+  </si>
+  <si>
+    <t>30407012407316</t>
+  </si>
+  <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30311152404492</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30504182400893</t>
+  </si>
+  <si>
+    <t>30304010400698</t>
+  </si>
+  <si>
+    <t>30501252404612</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>٣٠٣١٠١٥٢٤٠٣٣٢٥</t>
+  </si>
+  <si>
+    <t>30510252406355</t>
+  </si>
+  <si>
+    <t>30411201403108</t>
+  </si>
+  <si>
+    <t>30311232401672</t>
+  </si>
+  <si>
+    <t>30506222400053</t>
+  </si>
+  <si>
+    <t>30506202400731</t>
+  </si>
+  <si>
+    <t>30310042401203</t>
+  </si>
+  <si>
     <t>30507012411733</t>
   </si>
   <si>
-    <t>30411102404968</t>
-  </si>
-  <si>
-    <t>30310012403406</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٩٢١٢٤٠٠٣١٣</t>
-  </si>
-  <si>
-    <t>30506082400619</t>
-  </si>
-  <si>
-    <t>30503242401413</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٤٠٤٢٤٠٢٩٩٣</t>
-  </si>
-  <si>
-    <t>30507262401954</t>
-  </si>
-  <si>
-    <t>30405262402457</t>
-  </si>
-  <si>
-    <t>30410312400403</t>
-  </si>
-  <si>
-    <t>30506152402932</t>
-  </si>
-  <si>
-    <t>30509052401709</t>
-  </si>
-  <si>
-    <t>30408182401521</t>
-  </si>
-  <si>
-    <t>30410232401859</t>
-  </si>
-  <si>
-    <t>30409222402263</t>
-  </si>
-  <si>
-    <t>30308062400144</t>
-  </si>
-  <si>
-    <t>30302142401658</t>
-  </si>
-  <si>
-    <t>30506272400259</t>
-  </si>
-  <si>
-    <t>30409012413599</t>
-  </si>
-  <si>
-    <t>30601162402453</t>
-  </si>
-  <si>
-    <t>30310012402973</t>
-  </si>
-  <si>
-    <t>30506170300209</t>
-  </si>
-  <si>
-    <t>30409172401791</t>
-  </si>
-  <si>
-    <t>30504252402961</t>
-  </si>
-  <si>
-    <t>30603112402846</t>
-  </si>
-  <si>
-    <t>30406012410949</t>
-  </si>
-  <si>
-    <t>30501092401999</t>
-  </si>
-  <si>
-    <t>30409012406231</t>
-  </si>
-  <si>
-    <t>30505012406451</t>
-  </si>
-  <si>
-    <t>30504302401554</t>
-  </si>
-  <si>
-    <t>30012012409985</t>
-  </si>
-  <si>
-    <t>30401022401237</t>
-  </si>
-  <si>
-    <t>30507152402505</t>
-  </si>
-  <si>
-    <t>30407012407316</t>
-  </si>
-  <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30311152404492</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30504182400893</t>
-  </si>
-  <si>
-    <t>30304010400698</t>
-  </si>
-  <si>
-    <t>30501252404612</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>٣٠٣١٠١٥٢٤٠٣٣٢٥</t>
-  </si>
-  <si>
-    <t>30510252406355</t>
-  </si>
-  <si>
-    <t>30411201403108</t>
-  </si>
-  <si>
-    <t>30311232401672</t>
-  </si>
-  <si>
-    <t>30506222400053</t>
-  </si>
-  <si>
-    <t>30506202400731</t>
-  </si>
-  <si>
-    <t>30310042401203</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3253,477 +3253,477 @@
     <t>01016327718</t>
   </si>
   <si>
+    <t>01127048374</t>
+  </si>
+  <si>
+    <t>01006270603</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0114356079</t>
+  </si>
+  <si>
+    <t>01012467272</t>
+  </si>
+  <si>
+    <t>01005363873</t>
+  </si>
+  <si>
+    <t>01146971936</t>
+  </si>
+  <si>
+    <t>01143749439</t>
+  </si>
+  <si>
+    <t>01099101872</t>
+  </si>
+  <si>
+    <t>01060726096</t>
+  </si>
+  <si>
+    <t>01101609533</t>
+  </si>
+  <si>
+    <t>0111590035</t>
+  </si>
+  <si>
+    <t>01148375746</t>
+  </si>
+  <si>
+    <t>01115291432</t>
+  </si>
+  <si>
+    <t>01121482192</t>
+  </si>
+  <si>
+    <t>01021408975</t>
+  </si>
+  <si>
+    <t>01068360992</t>
+  </si>
+  <si>
+    <t>01061982978</t>
+  </si>
+  <si>
+    <t>01092079993</t>
+  </si>
+  <si>
+    <t>01288364393</t>
+  </si>
+  <si>
+    <t>01157384981</t>
+  </si>
+  <si>
+    <t>01283970879</t>
+  </si>
+  <si>
+    <t>01099393313</t>
+  </si>
+  <si>
+    <t>01093075647</t>
+  </si>
+  <si>
+    <t>01037186555</t>
+  </si>
+  <si>
+    <t>01129169104</t>
+  </si>
+  <si>
+    <t>01001362969</t>
+  </si>
+  <si>
+    <t>01151741232</t>
+  </si>
+  <si>
+    <t>01013305686</t>
+  </si>
+  <si>
+    <t>01150936407</t>
+  </si>
+  <si>
+    <t>01002331784</t>
+  </si>
+  <si>
+    <t>01150905692</t>
+  </si>
+  <si>
+    <t>01028993616</t>
+  </si>
+  <si>
+    <t>01119364560</t>
+  </si>
+  <si>
+    <t>01114623756</t>
+  </si>
+  <si>
+    <t>01110180758</t>
+  </si>
+  <si>
+    <t>01098408936</t>
+  </si>
+  <si>
+    <t>01026439570</t>
+  </si>
+  <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01068463842</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01055420368</t>
+  </si>
+  <si>
+    <t>01095305700</t>
+  </si>
+  <si>
+    <t>01032909577</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01122877252</t>
+  </si>
+  <si>
+    <t>01008063893</t>
+  </si>
+  <si>
+    <t>01080345257</t>
+  </si>
+  <si>
+    <t>01090226593</t>
+  </si>
+  <si>
+    <t>01121207932</t>
+  </si>
+  <si>
+    <t>01153849518</t>
+  </si>
+  <si>
+    <t>01091493257</t>
+  </si>
+  <si>
     <t>01094773238</t>
   </si>
   <si>
-    <t>01127048374</t>
-  </si>
-  <si>
-    <t>01006270603</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0114356079</t>
-  </si>
-  <si>
-    <t>01012467272</t>
-  </si>
-  <si>
-    <t>01005363873</t>
-  </si>
-  <si>
-    <t>01146971936</t>
-  </si>
-  <si>
-    <t>01143749439</t>
-  </si>
-  <si>
-    <t>01099101872</t>
-  </si>
-  <si>
-    <t>01060726096</t>
-  </si>
-  <si>
-    <t>01101609533</t>
-  </si>
-  <si>
-    <t>0111590035</t>
-  </si>
-  <si>
-    <t>01148375746</t>
-  </si>
-  <si>
-    <t>01115291432</t>
-  </si>
-  <si>
-    <t>01121482192</t>
-  </si>
-  <si>
-    <t>01021408975</t>
-  </si>
-  <si>
-    <t>01068360992</t>
-  </si>
-  <si>
-    <t>01061982978</t>
-  </si>
-  <si>
-    <t>01092079993</t>
-  </si>
-  <si>
-    <t>01288364393</t>
-  </si>
-  <si>
-    <t>01157384981</t>
-  </si>
-  <si>
-    <t>01283970879</t>
-  </si>
-  <si>
-    <t>01099393313</t>
-  </si>
-  <si>
-    <t>01093075647</t>
-  </si>
-  <si>
-    <t>01037186555</t>
-  </si>
-  <si>
-    <t>01129169104</t>
-  </si>
-  <si>
-    <t>01001362969</t>
-  </si>
-  <si>
-    <t>01151741232</t>
-  </si>
-  <si>
-    <t>01013305686</t>
-  </si>
-  <si>
-    <t>01150936407</t>
-  </si>
-  <si>
-    <t>01002331784</t>
-  </si>
-  <si>
-    <t>01150905692</t>
-  </si>
-  <si>
-    <t>01028993616</t>
-  </si>
-  <si>
-    <t>01119364560</t>
-  </si>
-  <si>
-    <t>01114623756</t>
-  </si>
-  <si>
-    <t>01110180758</t>
-  </si>
-  <si>
-    <t>01098408936</t>
-  </si>
-  <si>
-    <t>01026439570</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01068463842</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01055420368</t>
-  </si>
-  <si>
-    <t>01095305700</t>
-  </si>
-  <si>
-    <t>01032909577</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01122877252</t>
-  </si>
-  <si>
-    <t>01008063893</t>
-  </si>
-  <si>
-    <t>01080345257</t>
-  </si>
-  <si>
-    <t>01090226593</t>
-  </si>
-  <si>
-    <t>01121207932</t>
-  </si>
-  <si>
-    <t>01153849518</t>
-  </si>
-  <si>
-    <t>01091493257</t>
-  </si>
-  <si>
     <t>1353</t>
   </si>
   <si>
@@ -4174,69 +4174,69 @@
     <t>1402</t>
   </si>
   <si>
+    <t>1356</t>
+  </si>
+  <si>
+    <t>1523</t>
+  </si>
+  <si>
+    <t>1435</t>
+  </si>
+  <si>
+    <t>1385</t>
+  </si>
+  <si>
+    <t>1396</t>
+  </si>
+  <si>
+    <t>1227</t>
+  </si>
+  <si>
+    <t>1419</t>
+  </si>
+  <si>
+    <t>1327</t>
+  </si>
+  <si>
+    <t>1451</t>
+  </si>
+  <si>
+    <t>1270</t>
+  </si>
+  <si>
+    <t>1404</t>
+  </si>
+  <si>
+    <t>1386</t>
+  </si>
+  <si>
+    <t>1373</t>
+  </si>
+  <si>
+    <t>1384</t>
+  </si>
+  <si>
+    <t>1521</t>
+  </si>
+  <si>
+    <t>1415</t>
+  </si>
+  <si>
+    <t>1232</t>
+  </si>
+  <si>
+    <t>1598</t>
+  </si>
+  <si>
+    <t>1588</t>
+  </si>
+  <si>
+    <t>1371</t>
+  </si>
+  <si>
     <t>1307</t>
   </si>
   <si>
-    <t>1356</t>
-  </si>
-  <si>
-    <t>1523</t>
-  </si>
-  <si>
-    <t>1435</t>
-  </si>
-  <si>
-    <t>1385</t>
-  </si>
-  <si>
-    <t>1396</t>
-  </si>
-  <si>
-    <t>1227</t>
-  </si>
-  <si>
-    <t>1419</t>
-  </si>
-  <si>
-    <t>1327</t>
-  </si>
-  <si>
-    <t>1451</t>
-  </si>
-  <si>
-    <t>1270</t>
-  </si>
-  <si>
-    <t>1404</t>
-  </si>
-  <si>
-    <t>1386</t>
-  </si>
-  <si>
-    <t>1373</t>
-  </si>
-  <si>
-    <t>1384</t>
-  </si>
-  <si>
-    <t>1521</t>
-  </si>
-  <si>
-    <t>1415</t>
-  </si>
-  <si>
-    <t>1232</t>
-  </si>
-  <si>
-    <t>1598</t>
-  </si>
-  <si>
-    <t>1588</t>
-  </si>
-  <si>
-    <t>1371</t>
-  </si>
-  <si>
     <t>1377</t>
   </si>
   <si>
@@ -4756,67 +4756,67 @@
     <t>70.1</t>
   </si>
   <si>
+    <t>67.8</t>
+  </si>
+  <si>
+    <t>76.15</t>
+  </si>
+  <si>
+    <t>71.75</t>
+  </si>
+  <si>
+    <t>69.25</t>
+  </si>
+  <si>
+    <t>69.8</t>
+  </si>
+  <si>
+    <t>61.35</t>
+  </si>
+  <si>
+    <t>70.95</t>
+  </si>
+  <si>
+    <t>66.35</t>
+  </si>
+  <si>
+    <t>72.55</t>
+  </si>
+  <si>
+    <t>63.5</t>
+  </si>
+  <si>
+    <t>70.2</t>
+  </si>
+  <si>
+    <t>69.3</t>
+  </si>
+  <si>
+    <t>68.65</t>
+  </si>
+  <si>
+    <t>69.2</t>
+  </si>
+  <si>
+    <t>76.05</t>
+  </si>
+  <si>
+    <t>70.75</t>
+  </si>
+  <si>
+    <t>61.6</t>
+  </si>
+  <si>
+    <t>79.9</t>
+  </si>
+  <si>
+    <t>79.4</t>
+  </si>
+  <si>
+    <t>68.55</t>
+  </si>
+  <si>
     <t>65.35</t>
-  </si>
-  <si>
-    <t>67.8</t>
-  </si>
-  <si>
-    <t>76.15</t>
-  </si>
-  <si>
-    <t>71.75</t>
-  </si>
-  <si>
-    <t>69.25</t>
-  </si>
-  <si>
-    <t>69.8</t>
-  </si>
-  <si>
-    <t>61.35</t>
-  </si>
-  <si>
-    <t>70.95</t>
-  </si>
-  <si>
-    <t>66.35</t>
-  </si>
-  <si>
-    <t>72.55</t>
-  </si>
-  <si>
-    <t>63.5</t>
-  </si>
-  <si>
-    <t>70.2</t>
-  </si>
-  <si>
-    <t>69.3</t>
-  </si>
-  <si>
-    <t>68.65</t>
-  </si>
-  <si>
-    <t>69.2</t>
-  </si>
-  <si>
-    <t>76.05</t>
-  </si>
-  <si>
-    <t>70.75</t>
-  </si>
-  <si>
-    <t>61.6</t>
-  </si>
-  <si>
-    <t>79.9</t>
-  </si>
-  <si>
-    <t>79.4</t>
-  </si>
-  <si>
-    <t>68.55</t>
   </si>
   <si>
     <t>68.85</t>
@@ -16323,7 +16323,7 @@
         <v>1580</v>
       </c>
       <c r="F252" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G252" t="s">
         <v>1630</v>
@@ -16335,16 +16335,16 @@
         <v>1633</v>
       </c>
       <c r="J252" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="K252" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L252" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="M252" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N252" t="s">
         <v>1637</v>
@@ -16367,13 +16367,13 @@
         <v>1581</v>
       </c>
       <c r="F253" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="G253" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H253" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="I253" t="s">
         <v>1633</v>
@@ -16385,7 +16385,7 @@
         <v>1631</v>
       </c>
       <c r="L253" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="M253" t="s">
         <v>1635</v>
@@ -16405,31 +16405,31 @@
         <v>1081</v>
       </c>
       <c r="D254" t="s">
-        <v>1388</v>
+        <v>1317</v>
       </c>
       <c r="E254" t="s">
-        <v>1582</v>
+        <v>1511</v>
       </c>
       <c r="F254" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="G254" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H254" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="I254" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="J254" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="K254" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="L254" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="M254" t="s">
         <v>1635</v>
@@ -16449,28 +16449,28 @@
         <v>1082</v>
       </c>
       <c r="D255" t="s">
-        <v>1317</v>
+        <v>1384</v>
       </c>
       <c r="E255" t="s">
-        <v>1511</v>
+        <v>1578</v>
       </c>
       <c r="F255" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G255" t="s">
         <v>1630</v>
       </c>
       <c r="H255" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I255" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="J255" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K255" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L255" t="s">
         <v>1634</v>
@@ -16493,13 +16493,13 @@
         <v>1083</v>
       </c>
       <c r="D256" t="s">
-        <v>1384</v>
+        <v>1320</v>
       </c>
       <c r="E256" t="s">
-        <v>1578</v>
+        <v>1514</v>
       </c>
       <c r="F256" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G256" t="s">
         <v>1630</v>
@@ -16514,13 +16514,13 @@
         <v>1632</v>
       </c>
       <c r="K256" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L256" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M256" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N256" t="s">
         <v>1637</v>
@@ -16537,34 +16537,34 @@
         <v>1084</v>
       </c>
       <c r="D257" t="s">
-        <v>1320</v>
+        <v>1296</v>
       </c>
       <c r="E257" t="s">
-        <v>1514</v>
+        <v>1490</v>
       </c>
       <c r="F257" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G257" t="s">
         <v>1630</v>
       </c>
       <c r="H257" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I257" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="J257" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="K257" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="L257" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="M257" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N257" t="s">
         <v>1637</v>
@@ -16581,10 +16581,10 @@
         <v>1085</v>
       </c>
       <c r="D258" t="s">
-        <v>1296</v>
+        <v>1250</v>
       </c>
       <c r="E258" t="s">
-        <v>1490</v>
+        <v>1444</v>
       </c>
       <c r="F258" t="s">
         <v>1624</v>
@@ -16596,19 +16596,19 @@
         <v>1631</v>
       </c>
       <c r="I258" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J258" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="K258" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="L258" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="M258" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N258" t="s">
         <v>1637</v>
@@ -16625,10 +16625,10 @@
         <v>1086</v>
       </c>
       <c r="D259" t="s">
-        <v>1250</v>
+        <v>1297</v>
       </c>
       <c r="E259" t="s">
-        <v>1444</v>
+        <v>1491</v>
       </c>
       <c r="F259" t="s">
         <v>1624</v>
@@ -16640,19 +16640,19 @@
         <v>1631</v>
       </c>
       <c r="I259" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="J259" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K259" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="L259" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="M259" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N259" t="s">
         <v>1637</v>
@@ -16669,22 +16669,22 @@
         <v>1087</v>
       </c>
       <c r="D260" t="s">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="E260" t="s">
-        <v>1491</v>
+        <v>1559</v>
       </c>
       <c r="F260" t="s">
         <v>1624</v>
       </c>
       <c r="G260" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H260" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="I260" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J260" t="s">
         <v>1636</v>
@@ -16693,7 +16693,7 @@
         <v>1632</v>
       </c>
       <c r="L260" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="M260" t="s">
         <v>1635</v>
@@ -16710,37 +16710,37 @@
         <v>680</v>
       </c>
       <c r="C261" t="s">
-        <v>1088</v>
+        <v>861</v>
       </c>
       <c r="D261" t="s">
-        <v>1365</v>
+        <v>1388</v>
       </c>
       <c r="E261" t="s">
-        <v>1559</v>
+        <v>1582</v>
       </c>
       <c r="F261" t="s">
         <v>1624</v>
       </c>
       <c r="G261" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H261" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I261" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J261" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="K261" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="L261" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="M261" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N261" t="s">
         <v>1637</v>
@@ -16754,16 +16754,16 @@
         <v>681</v>
       </c>
       <c r="C262" t="s">
-        <v>861</v>
+        <v>1088</v>
       </c>
       <c r="D262" t="s">
-        <v>1389</v>
+        <v>1326</v>
       </c>
       <c r="E262" t="s">
-        <v>1583</v>
+        <v>1520</v>
       </c>
       <c r="F262" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G262" t="s">
         <v>1630</v>
@@ -16778,13 +16778,13 @@
         <v>1635</v>
       </c>
       <c r="K262" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="L262" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="M262" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="N262" t="s">
         <v>1637</v>
@@ -16801,13 +16801,13 @@
         <v>1089</v>
       </c>
       <c r="D263" t="s">
-        <v>1326</v>
+        <v>1357</v>
       </c>
       <c r="E263" t="s">
-        <v>1520</v>
+        <v>1551</v>
       </c>
       <c r="F263" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G263" t="s">
         <v>1630</v>
@@ -16819,7 +16819,7 @@
         <v>1636</v>
       </c>
       <c r="J263" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="K263" t="s">
         <v>1632</v>
@@ -16828,7 +16828,7 @@
         <v>1631</v>
       </c>
       <c r="M263" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="N263" t="s">
         <v>1637</v>
@@ -16845,10 +16845,10 @@
         <v>1090</v>
       </c>
       <c r="D264" t="s">
-        <v>1357</v>
+        <v>1262</v>
       </c>
       <c r="E264" t="s">
-        <v>1551</v>
+        <v>1456</v>
       </c>
       <c r="F264" t="s">
         <v>1624</v>
@@ -16863,13 +16863,13 @@
         <v>1636</v>
       </c>
       <c r="J264" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="K264" t="s">
         <v>1632</v>
       </c>
       <c r="L264" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="M264" t="s">
         <v>1635</v>
@@ -16889,10 +16889,10 @@
         <v>1091</v>
       </c>
       <c r="D265" t="s">
-        <v>1262</v>
+        <v>1269</v>
       </c>
       <c r="E265" t="s">
-        <v>1456</v>
+        <v>1463</v>
       </c>
       <c r="F265" t="s">
         <v>1624</v>
@@ -16907,16 +16907,16 @@
         <v>1636</v>
       </c>
       <c r="J265" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K265" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="L265" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="M265" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N265" t="s">
         <v>1637</v>
@@ -16933,13 +16933,13 @@
         <v>1092</v>
       </c>
       <c r="D266" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E266" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F266" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G266" t="s">
         <v>1630</v>
@@ -16948,19 +16948,19 @@
         <v>1633</v>
       </c>
       <c r="I266" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="J266" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K266" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="L266" t="s">
         <v>1631</v>
       </c>
       <c r="M266" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N266" t="s">
         <v>1637</v>
@@ -16977,34 +16977,34 @@
         <v>1093</v>
       </c>
       <c r="D267" t="s">
-        <v>1268</v>
+        <v>1389</v>
       </c>
       <c r="E267" t="s">
-        <v>1462</v>
+        <v>1583</v>
       </c>
       <c r="F267" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G267" t="s">
         <v>1630</v>
       </c>
       <c r="H267" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="I267" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="J267" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="K267" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L267" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="M267" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="N267" t="s">
         <v>1637</v>
@@ -17021,34 +17021,34 @@
         <v>1094</v>
       </c>
       <c r="D268" t="s">
-        <v>1390</v>
+        <v>1236</v>
       </c>
       <c r="E268" t="s">
-        <v>1584</v>
+        <v>1430</v>
       </c>
       <c r="F268" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G268" t="s">
         <v>1630</v>
       </c>
       <c r="H268" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="I268" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J268" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="K268" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L268" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="M268" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="N268" t="s">
         <v>1637</v>
@@ -17065,34 +17065,34 @@
         <v>1095</v>
       </c>
       <c r="D269" t="s">
-        <v>1236</v>
+        <v>1333</v>
       </c>
       <c r="E269" t="s">
-        <v>1430</v>
+        <v>1527</v>
       </c>
       <c r="F269" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G269" t="s">
         <v>1630</v>
       </c>
       <c r="H269" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="I269" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J269" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="K269" t="s">
         <v>1634</v>
       </c>
       <c r="L269" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="M269" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N269" t="s">
         <v>1637</v>
@@ -17109,22 +17109,22 @@
         <v>1096</v>
       </c>
       <c r="D270" t="s">
-        <v>1333</v>
+        <v>1312</v>
       </c>
       <c r="E270" t="s">
-        <v>1527</v>
+        <v>1506</v>
       </c>
       <c r="F270" t="s">
         <v>1624</v>
       </c>
       <c r="G270" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="H270" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="I270" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="J270" t="s">
         <v>1633</v>
@@ -17133,10 +17133,10 @@
         <v>1634</v>
       </c>
       <c r="L270" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="M270" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N270" t="s">
         <v>1637</v>
@@ -17153,34 +17153,34 @@
         <v>1097</v>
       </c>
       <c r="D271" t="s">
-        <v>1312</v>
+        <v>1284</v>
       </c>
       <c r="E271" t="s">
-        <v>1506</v>
+        <v>1478</v>
       </c>
       <c r="F271" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G271" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="H271" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="I271" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="J271" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K271" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="L271" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="M271" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N271" t="s">
         <v>1637</v>
@@ -17197,13 +17197,13 @@
         <v>1098</v>
       </c>
       <c r="D272" t="s">
-        <v>1284</v>
+        <v>1390</v>
       </c>
       <c r="E272" t="s">
-        <v>1478</v>
+        <v>1584</v>
       </c>
       <c r="F272" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G272" t="s">
         <v>1630</v>
@@ -17212,19 +17212,19 @@
         <v>1636</v>
       </c>
       <c r="I272" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J272" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K272" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="L272" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="M272" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N272" t="s">
         <v>1637</v>
@@ -17247,28 +17247,28 @@
         <v>1585</v>
       </c>
       <c r="F273" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G273" t="s">
         <v>1630</v>
       </c>
       <c r="H273" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I273" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J273" t="s">
         <v>1631</v>
       </c>
       <c r="K273" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L273" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="M273" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N273" t="s">
         <v>1637</v>
@@ -17285,13 +17285,13 @@
         <v>1100</v>
       </c>
       <c r="D274" t="s">
-        <v>1392</v>
+        <v>1312</v>
       </c>
       <c r="E274" t="s">
-        <v>1586</v>
+        <v>1506</v>
       </c>
       <c r="F274" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G274" t="s">
         <v>1630</v>
@@ -17300,19 +17300,19 @@
         <v>1633</v>
       </c>
       <c r="I274" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="J274" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K274" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L274" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M274" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N274" t="s">
         <v>1637</v>
@@ -17329,13 +17329,13 @@
         <v>1101</v>
       </c>
       <c r="D275" t="s">
-        <v>1312</v>
+        <v>1384</v>
       </c>
       <c r="E275" t="s">
-        <v>1506</v>
+        <v>1578</v>
       </c>
       <c r="F275" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G275" t="s">
         <v>1630</v>
@@ -17350,13 +17350,13 @@
         <v>1634</v>
       </c>
       <c r="K275" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="L275" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="M275" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N275" t="s">
         <v>1637</v>
@@ -17373,10 +17373,10 @@
         <v>1102</v>
       </c>
       <c r="D276" t="s">
-        <v>1384</v>
+        <v>1329</v>
       </c>
       <c r="E276" t="s">
-        <v>1578</v>
+        <v>1523</v>
       </c>
       <c r="F276" t="s">
         <v>1625</v>
@@ -17385,22 +17385,22 @@
         <v>1630</v>
       </c>
       <c r="H276" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I276" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J276" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="K276" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="L276" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="M276" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N276" t="s">
         <v>1637</v>
@@ -17417,10 +17417,10 @@
         <v>1103</v>
       </c>
       <c r="D277" t="s">
-        <v>1329</v>
+        <v>1392</v>
       </c>
       <c r="E277" t="s">
-        <v>1523</v>
+        <v>1586</v>
       </c>
       <c r="F277" t="s">
         <v>1625</v>
@@ -17429,22 +17429,22 @@
         <v>1630</v>
       </c>
       <c r="H277" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="I277" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J277" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="K277" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="L277" t="s">
         <v>1634</v>
       </c>
       <c r="M277" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="N277" t="s">
         <v>1637</v>
@@ -17461,25 +17461,25 @@
         <v>1104</v>
       </c>
       <c r="D278" t="s">
-        <v>1393</v>
+        <v>1267</v>
       </c>
       <c r="E278" t="s">
-        <v>1587</v>
+        <v>1461</v>
       </c>
       <c r="F278" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="G278" t="s">
         <v>1630</v>
       </c>
       <c r="H278" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="I278" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="J278" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="K278" t="s">
         <v>1635</v>
@@ -17488,7 +17488,7 @@
         <v>1634</v>
       </c>
       <c r="M278" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="N278" t="s">
         <v>1637</v>
@@ -17505,13 +17505,13 @@
         <v>1105</v>
       </c>
       <c r="D279" t="s">
-        <v>1267</v>
+        <v>1339</v>
       </c>
       <c r="E279" t="s">
-        <v>1461</v>
+        <v>1533</v>
       </c>
       <c r="F279" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="G279" t="s">
         <v>1630</v>
@@ -17549,19 +17549,19 @@
         <v>1106</v>
       </c>
       <c r="D280" t="s">
-        <v>1339</v>
+        <v>1236</v>
       </c>
       <c r="E280" t="s">
-        <v>1533</v>
+        <v>1430</v>
       </c>
       <c r="F280" t="s">
         <v>1624</v>
       </c>
       <c r="G280" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H280" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I280" t="s">
         <v>1636</v>
@@ -17570,13 +17570,13 @@
         <v>1631</v>
       </c>
       <c r="K280" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="L280" t="s">
         <v>1634</v>
       </c>
       <c r="M280" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N280" t="s">
         <v>1637</v>
@@ -17593,34 +17593,34 @@
         <v>1107</v>
       </c>
       <c r="D281" t="s">
-        <v>1236</v>
+        <v>1250</v>
       </c>
       <c r="E281" t="s">
-        <v>1430</v>
+        <v>1444</v>
       </c>
       <c r="F281" t="s">
         <v>1624</v>
       </c>
       <c r="G281" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="H281" t="s">
         <v>1630</v>
       </c>
       <c r="I281" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="J281" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="K281" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="L281" t="s">
         <v>1634</v>
       </c>
       <c r="M281" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N281" t="s">
         <v>1637</v>
@@ -17637,34 +17637,34 @@
         <v>1108</v>
       </c>
       <c r="D282" t="s">
-        <v>1250</v>
+        <v>1269</v>
       </c>
       <c r="E282" t="s">
-        <v>1444</v>
+        <v>1463</v>
       </c>
       <c r="F282" t="s">
         <v>1624</v>
       </c>
       <c r="G282" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H282" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="I282" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="J282" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K282" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="L282" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="M282" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N282" t="s">
         <v>1637</v>
@@ -17681,34 +17681,34 @@
         <v>1109</v>
       </c>
       <c r="D283" t="s">
-        <v>1269</v>
+        <v>1393</v>
       </c>
       <c r="E283" t="s">
-        <v>1463</v>
+        <v>1587</v>
       </c>
       <c r="F283" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G283" t="s">
         <v>1630</v>
       </c>
       <c r="H283" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="I283" t="s">
         <v>1633</v>
       </c>
       <c r="J283" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K283" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L283" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M283" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N283" t="s">
         <v>1637</v>
@@ -17725,31 +17725,31 @@
         <v>1110</v>
       </c>
       <c r="D284" t="s">
-        <v>1394</v>
+        <v>1283</v>
       </c>
       <c r="E284" t="s">
-        <v>1588</v>
+        <v>1477</v>
       </c>
       <c r="F284" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G284" t="s">
         <v>1630</v>
       </c>
       <c r="H284" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I284" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="J284" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K284" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L284" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="M284" t="s">
         <v>1632</v>
@@ -17769,34 +17769,34 @@
         <v>1111</v>
       </c>
       <c r="D285" t="s">
-        <v>1283</v>
+        <v>1312</v>
       </c>
       <c r="E285" t="s">
-        <v>1477</v>
+        <v>1506</v>
       </c>
       <c r="F285" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G285" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="H285" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I285" t="s">
         <v>1635</v>
       </c>
       <c r="J285" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="K285" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="L285" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="M285" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="N285" t="s">
         <v>1637</v>
@@ -17813,34 +17813,34 @@
         <v>1112</v>
       </c>
       <c r="D286" t="s">
-        <v>1312</v>
+        <v>1247</v>
       </c>
       <c r="E286" t="s">
-        <v>1506</v>
+        <v>1441</v>
       </c>
       <c r="F286" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G286" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="H286" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="I286" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="J286" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K286" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="L286" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="M286" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="N286" t="s">
         <v>1637</v>
@@ -17857,10 +17857,10 @@
         <v>1113</v>
       </c>
       <c r="D287" t="s">
-        <v>1247</v>
+        <v>1352</v>
       </c>
       <c r="E287" t="s">
-        <v>1441</v>
+        <v>1546</v>
       </c>
       <c r="F287" t="s">
         <v>1624</v>
@@ -17878,13 +17878,13 @@
         <v>1631</v>
       </c>
       <c r="K287" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="L287" t="s">
         <v>1634</v>
       </c>
       <c r="M287" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N287" t="s">
         <v>1637</v>
@@ -17901,10 +17901,10 @@
         <v>1114</v>
       </c>
       <c r="D288" t="s">
-        <v>1352</v>
+        <v>1394</v>
       </c>
       <c r="E288" t="s">
-        <v>1546</v>
+        <v>1588</v>
       </c>
       <c r="F288" t="s">
         <v>1624</v>
@@ -17913,19 +17913,19 @@
         <v>1630</v>
       </c>
       <c r="H288" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I288" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J288" t="s">
         <v>1631</v>
       </c>
       <c r="K288" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L288" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M288" t="s">
         <v>1632</v>
@@ -17945,13 +17945,13 @@
         <v>1115</v>
       </c>
       <c r="D289" t="s">
-        <v>1395</v>
+        <v>1252</v>
       </c>
       <c r="E289" t="s">
-        <v>1589</v>
+        <v>1446</v>
       </c>
       <c r="F289" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G289" t="s">
         <v>1630</v>
@@ -17963,16 +17963,16 @@
         <v>1636</v>
       </c>
       <c r="J289" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K289" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L289" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="M289" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N289" t="s">
         <v>1637</v>
@@ -17989,10 +17989,10 @@
         <v>1116</v>
       </c>
       <c r="D290" t="s">
-        <v>1252</v>
+        <v>1346</v>
       </c>
       <c r="E290" t="s">
-        <v>1446</v>
+        <v>1540</v>
       </c>
       <c r="F290" t="s">
         <v>1625</v>
@@ -18001,22 +18001,22 @@
         <v>1630</v>
       </c>
       <c r="H290" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I290" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="J290" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K290" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="L290" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="M290" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="N290" t="s">
         <v>1637</v>
@@ -18033,19 +18033,19 @@
         <v>1117</v>
       </c>
       <c r="D291" t="s">
-        <v>1346</v>
+        <v>1395</v>
       </c>
       <c r="E291" t="s">
-        <v>1540</v>
+        <v>1589</v>
       </c>
       <c r="F291" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G291" t="s">
         <v>1630</v>
       </c>
       <c r="H291" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="I291" t="s">
         <v>1632</v>
@@ -18054,7 +18054,7 @@
         <v>1636</v>
       </c>
       <c r="K291" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="L291" t="s">
         <v>1635</v>
@@ -18077,13 +18077,13 @@
         <v>1118</v>
       </c>
       <c r="D292" t="s">
-        <v>1396</v>
+        <v>1267</v>
       </c>
       <c r="E292" t="s">
-        <v>1590</v>
+        <v>1461</v>
       </c>
       <c r="F292" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="G292" t="s">
         <v>1630</v>
@@ -18092,19 +18092,19 @@
         <v>1633</v>
       </c>
       <c r="I292" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="J292" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="K292" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="L292" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M292" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N292" t="s">
         <v>1637</v>
@@ -18121,31 +18121,31 @@
         <v>1119</v>
       </c>
       <c r="D293" t="s">
-        <v>1267</v>
+        <v>1321</v>
       </c>
       <c r="E293" t="s">
-        <v>1461</v>
+        <v>1515</v>
       </c>
       <c r="F293" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="G293" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H293" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I293" t="s">
         <v>1636</v>
       </c>
       <c r="J293" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K293" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="L293" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M293" t="s">
         <v>1632</v>
@@ -18165,28 +18165,28 @@
         <v>1120</v>
       </c>
       <c r="D294" t="s">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="E294" t="s">
-        <v>1515</v>
+        <v>1534</v>
       </c>
       <c r="F294" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G294" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H294" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="I294" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J294" t="s">
         <v>1634</v>
       </c>
       <c r="K294" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="L294" t="s">
         <v>1635</v>
@@ -18209,34 +18209,34 @@
         <v>1121</v>
       </c>
       <c r="D295" t="s">
-        <v>1340</v>
+        <v>1352</v>
       </c>
       <c r="E295" t="s">
-        <v>1534</v>
+        <v>1546</v>
       </c>
       <c r="F295" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G295" t="s">
         <v>1630</v>
       </c>
       <c r="H295" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="I295" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J295" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="K295" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="L295" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M295" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N295" t="s">
         <v>1637</v>
@@ -18253,13 +18253,13 @@
         <v>1122</v>
       </c>
       <c r="D296" t="s">
-        <v>1352</v>
+        <v>1373</v>
       </c>
       <c r="E296" t="s">
-        <v>1546</v>
+        <v>1567</v>
       </c>
       <c r="F296" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G296" t="s">
         <v>1630</v>
@@ -18268,19 +18268,19 @@
         <v>1636</v>
       </c>
       <c r="I296" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="J296" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="K296" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L296" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="M296" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N296" t="s">
         <v>1637</v>
@@ -18297,10 +18297,10 @@
         <v>1123</v>
       </c>
       <c r="D297" t="s">
-        <v>1373</v>
+        <v>1285</v>
       </c>
       <c r="E297" t="s">
-        <v>1567</v>
+        <v>1479</v>
       </c>
       <c r="F297" t="s">
         <v>1625</v>
@@ -18312,19 +18312,19 @@
         <v>1636</v>
       </c>
       <c r="I297" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J297" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="K297" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L297" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="M297" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N297" t="s">
         <v>1637</v>
@@ -18341,13 +18341,13 @@
         <v>1124</v>
       </c>
       <c r="D298" t="s">
-        <v>1285</v>
+        <v>1301</v>
       </c>
       <c r="E298" t="s">
-        <v>1479</v>
+        <v>1495</v>
       </c>
       <c r="F298" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G298" t="s">
         <v>1630</v>
@@ -18356,10 +18356,10 @@
         <v>1636</v>
       </c>
       <c r="I298" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="J298" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K298" t="s">
         <v>1635</v>
@@ -18385,10 +18385,10 @@
         <v>1125</v>
       </c>
       <c r="D299" t="s">
-        <v>1301</v>
+        <v>1396</v>
       </c>
       <c r="E299" t="s">
-        <v>1495</v>
+        <v>1590</v>
       </c>
       <c r="F299" t="s">
         <v>1624</v>
@@ -18397,22 +18397,22 @@
         <v>1630</v>
       </c>
       <c r="H299" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I299" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J299" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K299" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L299" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M299" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N299" t="s">
         <v>1637</v>
@@ -18438,25 +18438,25 @@
         <v>1624</v>
       </c>
       <c r="G300" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H300" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I300" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="J300" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K300" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L300" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="M300" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="N300" t="s">
         <v>1637</v>
@@ -18526,25 +18526,25 @@
         <v>1624</v>
       </c>
       <c r="G302" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H302" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I302" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="J302" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="K302" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L302" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M302" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="N302" t="s">
         <v>1637</v>
@@ -18567,28 +18567,28 @@
         <v>1594</v>
       </c>
       <c r="F303" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="G303" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H303" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I303" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J303" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K303" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L303" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="M303" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N303" t="s">
         <v>1637</v>
@@ -18605,34 +18605,34 @@
         <v>1130</v>
       </c>
       <c r="D304" t="s">
-        <v>1401</v>
+        <v>1370</v>
       </c>
       <c r="E304" t="s">
-        <v>1595</v>
+        <v>1564</v>
       </c>
       <c r="F304" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="G304" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H304" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I304" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J304" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="K304" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L304" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M304" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N304" t="s">
         <v>1637</v>
@@ -18649,13 +18649,13 @@
         <v>1131</v>
       </c>
       <c r="D305" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="E305" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="F305" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G305" t="s">
         <v>1630</v>
@@ -18670,13 +18670,13 @@
         <v>1632</v>
       </c>
       <c r="K305" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L305" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M305" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N305" t="s">
         <v>1637</v>
@@ -18693,10 +18693,10 @@
         <v>1132</v>
       </c>
       <c r="D306" t="s">
-        <v>1376</v>
+        <v>1401</v>
       </c>
       <c r="E306" t="s">
-        <v>1570</v>
+        <v>1595</v>
       </c>
       <c r="F306" t="s">
         <v>1624</v>
@@ -18711,16 +18711,16 @@
         <v>1636</v>
       </c>
       <c r="J306" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K306" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L306" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M306" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N306" t="s">
         <v>1637</v>
@@ -18743,25 +18743,25 @@
         <v>1596</v>
       </c>
       <c r="F307" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G307" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H307" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I307" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="J307" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="K307" t="s">
         <v>1634</v>
       </c>
       <c r="L307" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M307" t="s">
         <v>1632</v>
@@ -18781,34 +18781,34 @@
         <v>1134</v>
       </c>
       <c r="D308" t="s">
-        <v>1403</v>
+        <v>1369</v>
       </c>
       <c r="E308" t="s">
-        <v>1597</v>
+        <v>1563</v>
       </c>
       <c r="F308" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G308" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="H308" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="I308" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="J308" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="K308" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L308" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="M308" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N308" t="s">
         <v>1637</v>
@@ -18825,34 +18825,34 @@
         <v>1135</v>
       </c>
       <c r="D309" t="s">
-        <v>1369</v>
+        <v>1280</v>
       </c>
       <c r="E309" t="s">
-        <v>1563</v>
+        <v>1474</v>
       </c>
       <c r="F309" t="s">
         <v>1625</v>
       </c>
       <c r="G309" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H309" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="I309" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="J309" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="K309" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="L309" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="M309" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="N309" t="s">
         <v>1637</v>
@@ -18869,34 +18869,34 @@
         <v>1136</v>
       </c>
       <c r="D310" t="s">
-        <v>1280</v>
+        <v>1317</v>
       </c>
       <c r="E310" t="s">
-        <v>1474</v>
+        <v>1511</v>
       </c>
       <c r="F310" t="s">
         <v>1625</v>
       </c>
       <c r="G310" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H310" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I310" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="J310" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="K310" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L310" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="M310" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="N310" t="s">
         <v>1637</v>
@@ -18913,34 +18913,34 @@
         <v>1137</v>
       </c>
       <c r="D311" t="s">
-        <v>1317</v>
+        <v>1346</v>
       </c>
       <c r="E311" t="s">
-        <v>1511</v>
+        <v>1540</v>
       </c>
       <c r="F311" t="s">
         <v>1625</v>
       </c>
       <c r="G311" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="H311" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I311" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J311" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="K311" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L311" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="M311" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N311" t="s">
         <v>1637</v>
@@ -18957,34 +18957,34 @@
         <v>1138</v>
       </c>
       <c r="D312" t="s">
-        <v>1346</v>
+        <v>1317</v>
       </c>
       <c r="E312" t="s">
-        <v>1540</v>
+        <v>1511</v>
       </c>
       <c r="F312" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G312" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="H312" t="s">
         <v>1630</v>
       </c>
       <c r="I312" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J312" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="K312" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L312" t="s">
         <v>1635</v>
       </c>
       <c r="M312" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N312" t="s">
         <v>1637</v>
@@ -19001,31 +19001,31 @@
         <v>1139</v>
       </c>
       <c r="D313" t="s">
-        <v>1317</v>
+        <v>1403</v>
       </c>
       <c r="E313" t="s">
-        <v>1511</v>
+        <v>1597</v>
       </c>
       <c r="F313" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="G313" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H313" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I313" t="s">
         <v>1636</v>
       </c>
       <c r="J313" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K313" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L313" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M313" t="s">
         <v>1631</v>
@@ -19063,16 +19063,16 @@
         <v>1636</v>
       </c>
       <c r="J314" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K314" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L314" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M314" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N314" t="s">
         <v>1637</v>
@@ -19095,7 +19095,7 @@
         <v>1599</v>
       </c>
       <c r="F315" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="G315" t="s">
         <v>1630</v>
@@ -19107,13 +19107,13 @@
         <v>1636</v>
       </c>
       <c r="J315" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K315" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L315" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M315" t="s">
         <v>1632</v>
@@ -19139,28 +19139,28 @@
         <v>1600</v>
       </c>
       <c r="F316" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G316" t="s">
         <v>1630</v>
       </c>
       <c r="H316" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I316" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J316" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="K316" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L316" t="s">
         <v>1631</v>
       </c>
       <c r="M316" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N316" t="s">
         <v>1637</v>
@@ -19177,25 +19177,25 @@
         <v>1143</v>
       </c>
       <c r="D317" t="s">
-        <v>1386</v>
+        <v>1257</v>
       </c>
       <c r="E317" t="s">
-        <v>1580</v>
+        <v>1451</v>
       </c>
       <c r="F317" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="G317" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H317" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I317" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J317" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="K317" t="s">
         <v>1634</v>
@@ -19221,31 +19221,31 @@
         <v>1144</v>
       </c>
       <c r="D318" t="s">
-        <v>1257</v>
+        <v>1326</v>
       </c>
       <c r="E318" t="s">
-        <v>1451</v>
+        <v>1520</v>
       </c>
       <c r="F318" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="G318" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H318" t="s">
         <v>1633</v>
       </c>
       <c r="I318" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="J318" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="K318" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L318" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M318" t="s">
         <v>1635</v>
@@ -19265,34 +19265,34 @@
         <v>1145</v>
       </c>
       <c r="D319" t="s">
-        <v>1326</v>
+        <v>1407</v>
       </c>
       <c r="E319" t="s">
-        <v>1520</v>
+        <v>1601</v>
       </c>
       <c r="F319" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G319" t="s">
         <v>1630</v>
       </c>
       <c r="H319" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I319" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J319" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="K319" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L319" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="M319" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N319" t="s">
         <v>1637</v>
@@ -19309,34 +19309,34 @@
         <v>1146</v>
       </c>
       <c r="D320" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="E320" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="F320" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G320" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H320" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="I320" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="J320" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K320" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L320" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="M320" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N320" t="s">
         <v>1637</v>
@@ -19353,34 +19353,34 @@
         <v>1147</v>
       </c>
       <c r="D321" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="E321" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="F321" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G321" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="H321" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="I321" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="J321" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K321" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="L321" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="M321" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N321" t="s">
         <v>1637</v>
@@ -19397,34 +19397,34 @@
         <v>1148</v>
       </c>
       <c r="D322" t="s">
-        <v>1409</v>
+        <v>1286</v>
       </c>
       <c r="E322" t="s">
-        <v>1603</v>
+        <v>1480</v>
       </c>
       <c r="F322" t="s">
         <v>1626</v>
       </c>
       <c r="G322" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="H322" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="I322" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="J322" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="K322" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="L322" t="s">
         <v>1635</v>
       </c>
       <c r="M322" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N322" t="s">
         <v>1637</v>
@@ -19441,10 +19441,10 @@
         <v>1149</v>
       </c>
       <c r="D323" t="s">
-        <v>1286</v>
+        <v>1410</v>
       </c>
       <c r="E323" t="s">
-        <v>1480</v>
+        <v>1604</v>
       </c>
       <c r="F323" t="s">
         <v>1626</v>
@@ -19453,13 +19453,13 @@
         <v>1631</v>
       </c>
       <c r="H323" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="I323" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="J323" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="K323" t="s">
         <v>1636</v>
@@ -19468,7 +19468,7 @@
         <v>1635</v>
       </c>
       <c r="M323" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N323" t="s">
         <v>1637</v>
@@ -19485,34 +19485,34 @@
         <v>1150</v>
       </c>
       <c r="D324" t="s">
-        <v>1410</v>
+        <v>1252</v>
       </c>
       <c r="E324" t="s">
-        <v>1604</v>
+        <v>1446</v>
       </c>
       <c r="F324" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G324" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H324" t="s">
         <v>1630</v>
       </c>
       <c r="I324" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="J324" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="K324" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="L324" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M324" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="N324" t="s">
         <v>1637</v>
@@ -19529,34 +19529,34 @@
         <v>1151</v>
       </c>
       <c r="D325" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="E325" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="F325" t="s">
         <v>1624</v>
       </c>
       <c r="G325" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H325" t="s">
         <v>1630</v>
       </c>
       <c r="I325" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="J325" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="K325" t="s">
         <v>1634</v>
       </c>
       <c r="L325" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M325" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="N325" t="s">
         <v>1637</v>
@@ -19573,34 +19573,34 @@
         <v>1152</v>
       </c>
       <c r="D326" t="s">
-        <v>1250</v>
+        <v>1384</v>
       </c>
       <c r="E326" t="s">
-        <v>1444</v>
+        <v>1578</v>
       </c>
       <c r="F326" t="s">
         <v>1624</v>
       </c>
       <c r="G326" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H326" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="I326" t="s">
         <v>1633</v>
       </c>
       <c r="J326" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="K326" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L326" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="M326" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N326" t="s">
         <v>1637</v>
@@ -19617,34 +19617,34 @@
         <v>1153</v>
       </c>
       <c r="D327" t="s">
-        <v>1384</v>
+        <v>1411</v>
       </c>
       <c r="E327" t="s">
-        <v>1578</v>
+        <v>1605</v>
       </c>
       <c r="F327" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G327" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="H327" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="I327" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="J327" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="K327" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L327" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M327" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N327" t="s">
         <v>1637</v>
@@ -19661,34 +19661,34 @@
         <v>1154</v>
       </c>
       <c r="D328" t="s">
-        <v>1411</v>
+        <v>1317</v>
       </c>
       <c r="E328" t="s">
-        <v>1605</v>
+        <v>1511</v>
       </c>
       <c r="F328" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G328" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="H328" t="s">
         <v>1630</v>
       </c>
       <c r="I328" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="J328" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K328" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L328" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M328" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N328" t="s">
         <v>1637</v>
@@ -19705,28 +19705,28 @@
         <v>1155</v>
       </c>
       <c r="D329" t="s">
-        <v>1317</v>
+        <v>1283</v>
       </c>
       <c r="E329" t="s">
-        <v>1511</v>
+        <v>1477</v>
       </c>
       <c r="F329" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G329" t="s">
         <v>1634</v>
       </c>
       <c r="H329" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I329" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J329" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="K329" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="L329" t="s">
         <v>1631</v>
@@ -19749,31 +19749,31 @@
         <v>1156</v>
       </c>
       <c r="D330" t="s">
-        <v>1283</v>
+        <v>1358</v>
       </c>
       <c r="E330" t="s">
-        <v>1477</v>
+        <v>1552</v>
       </c>
       <c r="F330" t="s">
         <v>1625</v>
       </c>
       <c r="G330" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="H330" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I330" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J330" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K330" t="s">
         <v>1632</v>
       </c>
       <c r="L330" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="M330" t="s">
         <v>1635</v>
@@ -19793,31 +19793,31 @@
         <v>1157</v>
       </c>
       <c r="D331" t="s">
-        <v>1358</v>
+        <v>1412</v>
       </c>
       <c r="E331" t="s">
-        <v>1552</v>
+        <v>1606</v>
       </c>
       <c r="F331" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="G331" t="s">
         <v>1630</v>
       </c>
       <c r="H331" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I331" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J331" t="s">
         <v>1631</v>
       </c>
       <c r="K331" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="L331" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="M331" t="s">
         <v>1635</v>
@@ -19837,13 +19837,13 @@
         <v>1158</v>
       </c>
       <c r="D332" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E332" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="F332" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="G332" t="s">
         <v>1630</v>
@@ -19855,16 +19855,16 @@
         <v>1636</v>
       </c>
       <c r="J332" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K332" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L332" t="s">
         <v>1632</v>
       </c>
       <c r="M332" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N332" t="s">
         <v>1637</v>
@@ -19881,13 +19881,13 @@
         <v>1159</v>
       </c>
       <c r="D333" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="E333" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="F333" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="G333" t="s">
         <v>1630</v>
@@ -19899,16 +19899,16 @@
         <v>1636</v>
       </c>
       <c r="J333" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="K333" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L333" t="s">
         <v>1632</v>
       </c>
       <c r="M333" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N333" t="s">
         <v>1637</v>
@@ -19925,31 +19925,31 @@
         <v>1160</v>
       </c>
       <c r="D334" t="s">
-        <v>1414</v>
+        <v>1281</v>
       </c>
       <c r="E334" t="s">
-        <v>1608</v>
+        <v>1475</v>
       </c>
       <c r="F334" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="G334" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H334" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I334" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="J334" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="K334" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="L334" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="M334" t="s">
         <v>1635</v>
@@ -19969,34 +19969,34 @@
         <v>1161</v>
       </c>
       <c r="D335" t="s">
-        <v>1281</v>
+        <v>1415</v>
       </c>
       <c r="E335" t="s">
-        <v>1475</v>
+        <v>1609</v>
       </c>
       <c r="F335" t="s">
         <v>1625</v>
       </c>
       <c r="G335" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H335" t="s">
         <v>1631</v>
       </c>
       <c r="I335" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J335" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="K335" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="L335" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M335" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="N335" t="s">
         <v>1637</v>
@@ -20013,13 +20013,13 @@
         <v>1162</v>
       </c>
       <c r="D336" t="s">
-        <v>1415</v>
+        <v>1259</v>
       </c>
       <c r="E336" t="s">
-        <v>1609</v>
+        <v>1453</v>
       </c>
       <c r="F336" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G336" t="s">
         <v>1630</v>
@@ -20028,16 +20028,16 @@
         <v>1631</v>
       </c>
       <c r="I336" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J336" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="K336" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="L336" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="M336" t="s">
         <v>1634</v>
@@ -20057,10 +20057,10 @@
         <v>1163</v>
       </c>
       <c r="D337" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="E337" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="F337" t="s">
         <v>1624</v>
@@ -20101,10 +20101,10 @@
         <v>1164</v>
       </c>
       <c r="D338" t="s">
-        <v>1261</v>
+        <v>1408</v>
       </c>
       <c r="E338" t="s">
-        <v>1455</v>
+        <v>1602</v>
       </c>
       <c r="F338" t="s">
         <v>1624</v>
@@ -20113,22 +20113,22 @@
         <v>1630</v>
       </c>
       <c r="H338" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="I338" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="J338" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="K338" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="L338" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M338" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N338" t="s">
         <v>1637</v>
@@ -20145,34 +20145,34 @@
         <v>1165</v>
       </c>
       <c r="D339" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="E339" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="F339" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="G339" t="s">
         <v>1630</v>
       </c>
       <c r="H339" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="I339" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J339" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="K339" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="L339" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M339" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N339" t="s">
         <v>1637</v>
@@ -20189,28 +20189,28 @@
         <v>1166</v>
       </c>
       <c r="D340" t="s">
-        <v>1410</v>
+        <v>1371</v>
       </c>
       <c r="E340" t="s">
-        <v>1604</v>
+        <v>1565</v>
       </c>
       <c r="F340" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="G340" t="s">
         <v>1630</v>
       </c>
       <c r="H340" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="I340" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J340" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="K340" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L340" t="s">
         <v>1634</v>
@@ -20233,13 +20233,13 @@
         <v>1167</v>
       </c>
       <c r="D341" t="s">
-        <v>1371</v>
+        <v>1332</v>
       </c>
       <c r="E341" t="s">
-        <v>1565</v>
+        <v>1526</v>
       </c>
       <c r="F341" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G341" t="s">
         <v>1630</v>
@@ -20248,19 +20248,19 @@
         <v>1633</v>
       </c>
       <c r="I341" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="J341" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="K341" t="s">
         <v>1631</v>
       </c>
       <c r="L341" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M341" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N341" t="s">
         <v>1637</v>
@@ -20277,34 +20277,34 @@
         <v>1168</v>
       </c>
       <c r="D342" t="s">
-        <v>1332</v>
+        <v>1312</v>
       </c>
       <c r="E342" t="s">
-        <v>1526</v>
+        <v>1506</v>
       </c>
       <c r="F342" t="s">
         <v>1625</v>
       </c>
       <c r="G342" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H342" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I342" t="s">
         <v>1634</v>
       </c>
       <c r="J342" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="K342" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="L342" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="M342" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N342" t="s">
         <v>1637</v>
@@ -20321,34 +20321,34 @@
         <v>1169</v>
       </c>
       <c r="D343" t="s">
-        <v>1312</v>
+        <v>1272</v>
       </c>
       <c r="E343" t="s">
-        <v>1506</v>
+        <v>1466</v>
       </c>
       <c r="F343" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G343" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H343" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="I343" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="J343" t="s">
         <v>1631</v>
       </c>
       <c r="K343" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="L343" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="M343" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="N343" t="s">
         <v>1637</v>
@@ -20365,34 +20365,34 @@
         <v>1170</v>
       </c>
       <c r="D344" t="s">
-        <v>1272</v>
+        <v>1388</v>
       </c>
       <c r="E344" t="s">
-        <v>1466</v>
+        <v>1582</v>
       </c>
       <c r="F344" t="s">
         <v>1624</v>
       </c>
       <c r="G344" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H344" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="I344" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="J344" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="K344" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="L344" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="M344" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="N344" t="s">
         <v>1637</v>
@@ -20409,10 +20409,10 @@
         <v>1171</v>
       </c>
       <c r="D345" t="s">
-        <v>1389</v>
+        <v>1335</v>
       </c>
       <c r="E345" t="s">
-        <v>1583</v>
+        <v>1529</v>
       </c>
       <c r="F345" t="s">
         <v>1624</v>
@@ -20424,16 +20424,16 @@
         <v>1633</v>
       </c>
       <c r="I345" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="J345" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="K345" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L345" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="M345" t="s">
         <v>1631</v>
@@ -20453,34 +20453,34 @@
         <v>1172</v>
       </c>
       <c r="D346" t="s">
-        <v>1335</v>
+        <v>1320</v>
       </c>
       <c r="E346" t="s">
-        <v>1529</v>
+        <v>1514</v>
       </c>
       <c r="F346" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G346" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H346" t="s">
         <v>1633</v>
       </c>
       <c r="I346" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="J346" t="s">
         <v>1636</v>
       </c>
       <c r="K346" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L346" t="s">
         <v>1632</v>
       </c>
       <c r="M346" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="N346" t="s">
         <v>1637</v>
@@ -20497,22 +20497,22 @@
         <v>1173</v>
       </c>
       <c r="D347" t="s">
-        <v>1320</v>
+        <v>1259</v>
       </c>
       <c r="E347" t="s">
-        <v>1514</v>
+        <v>1453</v>
       </c>
       <c r="F347" t="s">
         <v>1625</v>
       </c>
       <c r="G347" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H347" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I347" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="J347" t="s">
         <v>1636</v>
@@ -20541,34 +20541,34 @@
         <v>1174</v>
       </c>
       <c r="D348" t="s">
-        <v>1259</v>
+        <v>1275</v>
       </c>
       <c r="E348" t="s">
-        <v>1453</v>
+        <v>1469</v>
       </c>
       <c r="F348" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G348" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="H348" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="I348" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="J348" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="K348" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="L348" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="M348" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="N348" t="s">
         <v>1637</v>
@@ -20585,34 +20585,34 @@
         <v>1175</v>
       </c>
       <c r="D349" t="s">
-        <v>1275</v>
+        <v>1322</v>
       </c>
       <c r="E349" t="s">
-        <v>1469</v>
+        <v>1516</v>
       </c>
       <c r="F349" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G349" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="H349" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I349" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="J349" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="K349" t="s">
         <v>1632</v>
       </c>
       <c r="L349" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M349" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="N349" t="s">
         <v>1637</v>
@@ -20629,19 +20629,19 @@
         <v>1176</v>
       </c>
       <c r="D350" t="s">
-        <v>1322</v>
+        <v>1341</v>
       </c>
       <c r="E350" t="s">
-        <v>1516</v>
+        <v>1535</v>
       </c>
       <c r="F350" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G350" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H350" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="I350" t="s">
         <v>1633</v>
@@ -20650,10 +20650,10 @@
         <v>1636</v>
       </c>
       <c r="K350" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="L350" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="M350" t="s">
         <v>1635</v>
@@ -20673,34 +20673,34 @@
         <v>1177</v>
       </c>
       <c r="D351" t="s">
-        <v>1341</v>
+        <v>1256</v>
       </c>
       <c r="E351" t="s">
-        <v>1535</v>
+        <v>1450</v>
       </c>
       <c r="F351" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G351" t="s">
         <v>1631</v>
       </c>
       <c r="H351" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="I351" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="J351" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="K351" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L351" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="M351" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N351" t="s">
         <v>1637</v>
@@ -20717,34 +20717,34 @@
         <v>1178</v>
       </c>
       <c r="D352" t="s">
-        <v>1256</v>
+        <v>1415</v>
       </c>
       <c r="E352" t="s">
-        <v>1450</v>
+        <v>1609</v>
       </c>
       <c r="F352" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G352" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="H352" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I352" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="J352" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K352" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="L352" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M352" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="N352" t="s">
         <v>1637</v>
@@ -20761,34 +20761,34 @@
         <v>1179</v>
       </c>
       <c r="D353" t="s">
-        <v>1415</v>
+        <v>1302</v>
       </c>
       <c r="E353" t="s">
-        <v>1609</v>
+        <v>1496</v>
       </c>
       <c r="F353" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G353" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="H353" t="s">
         <v>1633</v>
       </c>
       <c r="I353" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="J353" t="s">
         <v>1632</v>
       </c>
       <c r="K353" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L353" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M353" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="N353" t="s">
         <v>1637</v>
@@ -20805,31 +20805,31 @@
         <v>1180</v>
       </c>
       <c r="D354" t="s">
-        <v>1302</v>
+        <v>1271</v>
       </c>
       <c r="E354" t="s">
-        <v>1496</v>
+        <v>1465</v>
       </c>
       <c r="F354" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G354" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H354" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I354" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="J354" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K354" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L354" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="M354" t="s">
         <v>1635</v>
@@ -20849,31 +20849,31 @@
         <v>1181</v>
       </c>
       <c r="D355" t="s">
-        <v>1271</v>
+        <v>1314</v>
       </c>
       <c r="E355" t="s">
-        <v>1465</v>
+        <v>1508</v>
       </c>
       <c r="F355" t="s">
         <v>1625</v>
       </c>
       <c r="G355" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="H355" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="I355" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="J355" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="K355" t="s">
         <v>1634</v>
       </c>
       <c r="L355" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="M355" t="s">
         <v>1635</v>
@@ -20893,31 +20893,31 @@
         <v>1182</v>
       </c>
       <c r="D356" t="s">
-        <v>1314</v>
+        <v>1282</v>
       </c>
       <c r="E356" t="s">
-        <v>1508</v>
+        <v>1476</v>
       </c>
       <c r="F356" t="s">
         <v>1625</v>
       </c>
       <c r="G356" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H356" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="I356" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="J356" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K356" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L356" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="M356" t="s">
         <v>1635</v>
@@ -20937,34 +20937,34 @@
         <v>1183</v>
       </c>
       <c r="D357" t="s">
-        <v>1282</v>
+        <v>1367</v>
       </c>
       <c r="E357" t="s">
-        <v>1476</v>
+        <v>1561</v>
       </c>
       <c r="F357" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G357" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H357" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="I357" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="J357" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="K357" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="L357" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="M357" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="N357" t="s">
         <v>1637</v>
@@ -20981,10 +20981,10 @@
         <v>1184</v>
       </c>
       <c r="D358" t="s">
-        <v>1367</v>
+        <v>1416</v>
       </c>
       <c r="E358" t="s">
-        <v>1561</v>
+        <v>1610</v>
       </c>
       <c r="F358" t="s">
         <v>1624</v>
@@ -21025,34 +21025,34 @@
         <v>1185</v>
       </c>
       <c r="D359" t="s">
-        <v>1416</v>
+        <v>1255</v>
       </c>
       <c r="E359" t="s">
-        <v>1610</v>
+        <v>1449</v>
       </c>
       <c r="F359" t="s">
         <v>1624</v>
       </c>
       <c r="G359" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H359" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="I359" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="J359" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="K359" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="L359" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="M359" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="N359" t="s">
         <v>1637</v>
@@ -21069,31 +21069,31 @@
         <v>1186</v>
       </c>
       <c r="D360" t="s">
-        <v>1255</v>
+        <v>1267</v>
       </c>
       <c r="E360" t="s">
-        <v>1449</v>
+        <v>1461</v>
       </c>
       <c r="F360" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="G360" t="s">
         <v>1630</v>
       </c>
       <c r="H360" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="I360" t="s">
         <v>1636</v>
       </c>
       <c r="J360" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K360" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="L360" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="M360" t="s">
         <v>1635</v>
@@ -21113,34 +21113,34 @@
         <v>1187</v>
       </c>
       <c r="D361" t="s">
-        <v>1267</v>
+        <v>1417</v>
       </c>
       <c r="E361" t="s">
-        <v>1461</v>
+        <v>1611</v>
       </c>
       <c r="F361" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="G361" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H361" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="I361" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="J361" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="K361" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="L361" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="M361" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="N361" t="s">
         <v>1637</v>
@@ -21157,34 +21157,34 @@
         <v>1188</v>
       </c>
       <c r="D362" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="E362" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="F362" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="G362" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H362" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="I362" t="s">
         <v>1632</v>
       </c>
       <c r="J362" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="K362" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="L362" t="s">
         <v>1634</v>
       </c>
       <c r="M362" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="N362" t="s">
         <v>1637</v>
@@ -21201,34 +21201,34 @@
         <v>1189</v>
       </c>
       <c r="D363" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="E363" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F363" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="G363" t="s">
         <v>1630</v>
       </c>
       <c r="H363" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I363" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="J363" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="K363" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L363" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M363" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N363" t="s">
         <v>1637</v>
@@ -21245,13 +21245,13 @@
         <v>1190</v>
       </c>
       <c r="D364" t="s">
-        <v>1419</v>
+        <v>1265</v>
       </c>
       <c r="E364" t="s">
-        <v>1613</v>
+        <v>1459</v>
       </c>
       <c r="F364" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G364" t="s">
         <v>1630</v>
@@ -21266,13 +21266,13 @@
         <v>1631</v>
       </c>
       <c r="K364" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="L364" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M364" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N364" t="s">
         <v>1637</v>
@@ -21289,13 +21289,13 @@
         <v>1191</v>
       </c>
       <c r="D365" t="s">
-        <v>1265</v>
+        <v>1247</v>
       </c>
       <c r="E365" t="s">
-        <v>1459</v>
+        <v>1441</v>
       </c>
       <c r="F365" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G365" t="s">
         <v>1630</v>
@@ -21307,16 +21307,16 @@
         <v>1636</v>
       </c>
       <c r="J365" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="K365" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="L365" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M365" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="N365" t="s">
         <v>1637</v>
@@ -21333,22 +21333,22 @@
         <v>1192</v>
       </c>
       <c r="D366" t="s">
-        <v>1247</v>
+        <v>1305</v>
       </c>
       <c r="E366" t="s">
-        <v>1441</v>
+        <v>1499</v>
       </c>
       <c r="F366" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G366" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H366" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="I366" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="J366" t="s">
         <v>1632</v>
@@ -21357,10 +21357,10 @@
         <v>1634</v>
       </c>
       <c r="L366" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="M366" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="N366" t="s">
         <v>1637</v>
@@ -21377,31 +21377,31 @@
         <v>1193</v>
       </c>
       <c r="D367" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="E367" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="F367" t="s">
         <v>1625</v>
       </c>
       <c r="G367" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H367" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="I367" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="J367" t="s">
         <v>1632</v>
       </c>
       <c r="K367" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L367" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="M367" t="s">
         <v>1636</v>
@@ -21421,34 +21421,34 @@
         <v>1194</v>
       </c>
       <c r="D368" t="s">
-        <v>1311</v>
+        <v>1251</v>
       </c>
       <c r="E368" t="s">
-        <v>1505</v>
+        <v>1445</v>
       </c>
       <c r="F368" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G368" t="s">
         <v>1630</v>
       </c>
       <c r="H368" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="I368" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J368" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K368" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="L368" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M368" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="N368" t="s">
         <v>1637</v>
@@ -21465,34 +21465,34 @@
         <v>1195</v>
       </c>
       <c r="D369" t="s">
-        <v>1251</v>
+        <v>1273</v>
       </c>
       <c r="E369" t="s">
-        <v>1445</v>
+        <v>1467</v>
       </c>
       <c r="F369" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G369" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H369" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="I369" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J369" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="K369" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="L369" t="s">
         <v>1635</v>
       </c>
       <c r="M369" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N369" t="s">
         <v>1637</v>
@@ -21509,34 +21509,34 @@
         <v>1196</v>
       </c>
       <c r="D370" t="s">
-        <v>1273</v>
+        <v>1376</v>
       </c>
       <c r="E370" t="s">
-        <v>1467</v>
+        <v>1570</v>
       </c>
       <c r="F370" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G370" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H370" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I370" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J370" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="K370" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L370" t="s">
         <v>1635</v>
       </c>
       <c r="M370" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N370" t="s">
         <v>1637</v>
@@ -21553,10 +21553,10 @@
         <v>1197</v>
       </c>
       <c r="D371" t="s">
-        <v>1376</v>
+        <v>1247</v>
       </c>
       <c r="E371" t="s">
-        <v>1570</v>
+        <v>1441</v>
       </c>
       <c r="F371" t="s">
         <v>1625</v>
@@ -21565,13 +21565,13 @@
         <v>1630</v>
       </c>
       <c r="H371" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I371" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J371" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="K371" t="s">
         <v>1631</v>
@@ -21580,7 +21580,7 @@
         <v>1635</v>
       </c>
       <c r="M371" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N371" t="s">
         <v>1637</v>
@@ -21597,28 +21597,28 @@
         <v>1198</v>
       </c>
       <c r="D372" t="s">
-        <v>1247</v>
+        <v>1302</v>
       </c>
       <c r="E372" t="s">
-        <v>1441</v>
+        <v>1496</v>
       </c>
       <c r="F372" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G372" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H372" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I372" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="J372" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K372" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="L372" t="s">
         <v>1635</v>
@@ -21641,31 +21641,31 @@
         <v>1199</v>
       </c>
       <c r="D373" t="s">
-        <v>1302</v>
+        <v>1284</v>
       </c>
       <c r="E373" t="s">
-        <v>1496</v>
+        <v>1478</v>
       </c>
       <c r="F373" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G373" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H373" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I373" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="J373" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="K373" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L373" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M373" t="s">
         <v>1632</v>
@@ -21685,25 +21685,25 @@
         <v>1200</v>
       </c>
       <c r="D374" t="s">
-        <v>1284</v>
+        <v>1390</v>
       </c>
       <c r="E374" t="s">
-        <v>1478</v>
+        <v>1584</v>
       </c>
       <c r="F374" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G374" t="s">
         <v>1630</v>
       </c>
       <c r="H374" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I374" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J374" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="K374" t="s">
         <v>1631</v>
@@ -21712,7 +21712,7 @@
         <v>1634</v>
       </c>
       <c r="M374" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N374" t="s">
         <v>1637</v>
@@ -21729,34 +21729,34 @@
         <v>1201</v>
       </c>
       <c r="D375" t="s">
-        <v>1391</v>
+        <v>1365</v>
       </c>
       <c r="E375" t="s">
-        <v>1585</v>
+        <v>1559</v>
       </c>
       <c r="F375" t="s">
         <v>1624</v>
       </c>
       <c r="G375" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H375" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I375" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="J375" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="K375" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="L375" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M375" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N375" t="s">
         <v>1637</v>
@@ -21773,34 +21773,34 @@
         <v>1202</v>
       </c>
       <c r="D376" t="s">
-        <v>1365</v>
+        <v>1419</v>
       </c>
       <c r="E376" t="s">
-        <v>1559</v>
+        <v>1613</v>
       </c>
       <c r="F376" t="s">
         <v>1624</v>
       </c>
       <c r="G376" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="H376" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="I376" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="J376" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="K376" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="L376" t="s">
         <v>1635</v>
       </c>
       <c r="M376" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N376" t="s">
         <v>1637</v>
@@ -21817,34 +21817,34 @@
         <v>1203</v>
       </c>
       <c r="D377" t="s">
-        <v>1419</v>
+        <v>1270</v>
       </c>
       <c r="E377" t="s">
-        <v>1613</v>
+        <v>1464</v>
       </c>
       <c r="F377" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G377" t="s">
         <v>1630</v>
       </c>
       <c r="H377" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="I377" t="s">
         <v>1636</v>
       </c>
       <c r="J377" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="K377" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="L377" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M377" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="N377" t="s">
         <v>1637</v>
@@ -21861,34 +21861,34 @@
         <v>1204</v>
       </c>
       <c r="D378" t="s">
-        <v>1270</v>
+        <v>1284</v>
       </c>
       <c r="E378" t="s">
-        <v>1464</v>
+        <v>1478</v>
       </c>
       <c r="F378" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="G378" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H378" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="I378" t="s">
         <v>1636</v>
       </c>
       <c r="J378" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="K378" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="L378" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M378" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N378" t="s">
         <v>1637</v>
@@ -21905,34 +21905,34 @@
         <v>1205</v>
       </c>
       <c r="D379" t="s">
-        <v>1284</v>
+        <v>1420</v>
       </c>
       <c r="E379" t="s">
-        <v>1478</v>
+        <v>1614</v>
       </c>
       <c r="F379" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="G379" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H379" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="I379" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J379" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="K379" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="L379" t="s">
         <v>1635</v>
       </c>
       <c r="M379" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N379" t="s">
         <v>1637</v>
@@ -21949,34 +21949,34 @@
         <v>1206</v>
       </c>
       <c r="D380" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E380" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="F380" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="G380" t="s">
         <v>1630</v>
       </c>
       <c r="H380" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I380" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J380" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K380" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L380" t="s">
         <v>1635</v>
       </c>
       <c r="M380" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N380" t="s">
         <v>1637</v>
@@ -21993,34 +21993,34 @@
         <v>1207</v>
       </c>
       <c r="D381" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="E381" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="F381" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G381" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="H381" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="I381" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J381" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="K381" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="L381" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M381" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N381" t="s">
         <v>1637</v>
@@ -22037,34 +22037,34 @@
         <v>1208</v>
       </c>
       <c r="D382" t="s">
-        <v>1422</v>
+        <v>1311</v>
       </c>
       <c r="E382" t="s">
-        <v>1616</v>
+        <v>1505</v>
       </c>
       <c r="F382" t="s">
         <v>1625</v>
       </c>
       <c r="G382" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H382" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="I382" t="s">
         <v>1633</v>
       </c>
       <c r="J382" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K382" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="L382" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="M382" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N382" t="s">
         <v>1637</v>
@@ -22081,31 +22081,31 @@
         <v>1209</v>
       </c>
       <c r="D383" t="s">
-        <v>1311</v>
+        <v>1399</v>
       </c>
       <c r="E383" t="s">
-        <v>1505</v>
+        <v>1593</v>
       </c>
       <c r="F383" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G383" t="s">
         <v>1630</v>
       </c>
       <c r="H383" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I383" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J383" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="K383" t="s">
         <v>1634</v>
       </c>
       <c r="L383" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M383" t="s">
         <v>1632</v>
@@ -22125,31 +22125,31 @@
         <v>1210</v>
       </c>
       <c r="D384" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="E384" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="F384" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G384" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H384" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I384" t="s">
         <v>1636</v>
       </c>
       <c r="J384" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="K384" t="s">
         <v>1634</v>
       </c>
       <c r="L384" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="M384" t="s">
         <v>1632</v>
@@ -22169,34 +22169,34 @@
         <v>1211</v>
       </c>
       <c r="D385" t="s">
-        <v>1396</v>
+        <v>1355</v>
       </c>
       <c r="E385" t="s">
-        <v>1590</v>
+        <v>1549</v>
       </c>
       <c r="F385" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G385" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="H385" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="I385" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J385" t="s">
         <v>1630</v>
       </c>
       <c r="K385" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="L385" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M385" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N385" t="s">
         <v>1637</v>
@@ -22213,16 +22213,16 @@
         <v>1212</v>
       </c>
       <c r="D386" t="s">
-        <v>1355</v>
+        <v>1423</v>
       </c>
       <c r="E386" t="s">
-        <v>1549</v>
+        <v>1617</v>
       </c>
       <c r="F386" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="G386" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H386" t="s">
         <v>1636</v>
@@ -22231,13 +22231,13 @@
         <v>1633</v>
       </c>
       <c r="J386" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="K386" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L386" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="M386" t="s">
         <v>1635</v>
@@ -22257,34 +22257,34 @@
         <v>1213</v>
       </c>
       <c r="D387" t="s">
-        <v>1423</v>
+        <v>1332</v>
       </c>
       <c r="E387" t="s">
-        <v>1617</v>
+        <v>1526</v>
       </c>
       <c r="F387" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G387" t="s">
         <v>1630</v>
       </c>
       <c r="H387" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I387" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J387" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="K387" t="s">
         <v>1631</v>
       </c>
       <c r="L387" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="M387" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N387" t="s">
         <v>1637</v>
@@ -22301,34 +22301,34 @@
         <v>1214</v>
       </c>
       <c r="D388" t="s">
-        <v>1332</v>
+        <v>1244</v>
       </c>
       <c r="E388" t="s">
-        <v>1526</v>
+        <v>1438</v>
       </c>
       <c r="F388" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G388" t="s">
         <v>1630</v>
       </c>
       <c r="H388" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="I388" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="J388" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="K388" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="L388" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="M388" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N388" t="s">
         <v>1637</v>
@@ -22345,34 +22345,34 @@
         <v>1215</v>
       </c>
       <c r="D389" t="s">
-        <v>1244</v>
+        <v>1424</v>
       </c>
       <c r="E389" t="s">
-        <v>1438</v>
+        <v>1618</v>
       </c>
       <c r="F389" t="s">
         <v>1625</v>
       </c>
       <c r="G389" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H389" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="I389" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="J389" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="K389" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="L389" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="M389" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="N389" t="s">
         <v>1637</v>
@@ -22389,31 +22389,31 @@
         <v>1216</v>
       </c>
       <c r="D390" t="s">
-        <v>1424</v>
+        <v>1386</v>
       </c>
       <c r="E390" t="s">
-        <v>1618</v>
+        <v>1580</v>
       </c>
       <c r="F390" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G390" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H390" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I390" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="J390" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="K390" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="L390" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="M390" t="s">
         <v>1635</v>
@@ -22433,34 +22433,34 @@
         <v>1217</v>
       </c>
       <c r="D391" t="s">
-        <v>1387</v>
+        <v>1252</v>
       </c>
       <c r="E391" t="s">
-        <v>1581</v>
+        <v>1446</v>
       </c>
       <c r="F391" t="s">
         <v>1624</v>
       </c>
       <c r="G391" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H391" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I391" t="s">
         <v>1631</v>
       </c>
       <c r="J391" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="K391" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="L391" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="M391" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N391" t="s">
         <v>1637</v>
@@ -22477,34 +22477,34 @@
         <v>1218</v>
       </c>
       <c r="D392" t="s">
-        <v>1252</v>
+        <v>1425</v>
       </c>
       <c r="E392" t="s">
-        <v>1446</v>
+        <v>1619</v>
       </c>
       <c r="F392" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G392" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="H392" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I392" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="J392" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K392" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="L392" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="M392" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N392" t="s">
         <v>1637</v>
@@ -22521,10 +22521,10 @@
         <v>1219</v>
       </c>
       <c r="D393" t="s">
-        <v>1425</v>
+        <v>1253</v>
       </c>
       <c r="E393" t="s">
-        <v>1619</v>
+        <v>1447</v>
       </c>
       <c r="F393" t="s">
         <v>1625</v>
@@ -22533,22 +22533,22 @@
         <v>1630</v>
       </c>
       <c r="H393" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="I393" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="J393" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="K393" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="L393" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M393" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="N393" t="s">
         <v>1637</v>
@@ -22565,34 +22565,34 @@
         <v>1220</v>
       </c>
       <c r="D394" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="E394" t="s">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="F394" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G394" t="s">
         <v>1630</v>
       </c>
       <c r="H394" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="I394" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="J394" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="K394" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="L394" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M394" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N394" t="s">
         <v>1637</v>
@@ -22609,25 +22609,25 @@
         <v>1221</v>
       </c>
       <c r="D395" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
       <c r="E395" t="s">
-        <v>1452</v>
+        <v>1440</v>
       </c>
       <c r="F395" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G395" t="s">
         <v>1630</v>
       </c>
       <c r="H395" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I395" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J395" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="K395" t="s">
         <v>1634</v>
@@ -22636,7 +22636,7 @@
         <v>1631</v>
       </c>
       <c r="M395" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="N395" t="s">
         <v>1637</v>
@@ -22653,34 +22653,34 @@
         <v>1222</v>
       </c>
       <c r="D396" t="s">
-        <v>1246</v>
+        <v>1426</v>
       </c>
       <c r="E396" t="s">
-        <v>1440</v>
+        <v>1620</v>
       </c>
       <c r="F396" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="G396" t="s">
         <v>1630</v>
       </c>
       <c r="H396" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="I396" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="J396" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="K396" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L396" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="M396" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="N396" t="s">
         <v>1637</v>
@@ -22697,34 +22697,34 @@
         <v>1223</v>
       </c>
       <c r="D397" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E397" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="F397" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="G397" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="H397" t="s">
         <v>1631</v>
       </c>
       <c r="I397" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="J397" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="K397" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="L397" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="M397" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N397" t="s">
         <v>1637</v>
@@ -22741,34 +22741,34 @@
         <v>1224</v>
       </c>
       <c r="D398" t="s">
-        <v>1427</v>
+        <v>1365</v>
       </c>
       <c r="E398" t="s">
-        <v>1621</v>
+        <v>1559</v>
       </c>
       <c r="F398" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G398" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="H398" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="I398" t="s">
         <v>1633</v>
       </c>
       <c r="J398" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K398" t="s">
         <v>1632</v>
       </c>
       <c r="L398" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M398" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="N398" t="s">
         <v>1637</v>
@@ -22785,10 +22785,10 @@
         <v>1225</v>
       </c>
       <c r="D399" t="s">
-        <v>1365</v>
+        <v>1428</v>
       </c>
       <c r="E399" t="s">
-        <v>1559</v>
+        <v>1622</v>
       </c>
       <c r="F399" t="s">
         <v>1626</v>
@@ -22797,22 +22797,22 @@
         <v>1630</v>
       </c>
       <c r="H399" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="I399" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J399" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K399" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="L399" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="M399" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="N399" t="s">
         <v>1637</v>
@@ -22829,34 +22829,34 @@
         <v>1226</v>
       </c>
       <c r="D400" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E400" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="F400" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G400" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H400" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="I400" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="J400" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="K400" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="L400" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M400" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="N400" t="s">
         <v>1637</v>
@@ -22873,34 +22873,34 @@
         <v>1227</v>
       </c>
       <c r="D401" t="s">
-        <v>1429</v>
+        <v>1311</v>
       </c>
       <c r="E401" t="s">
-        <v>1623</v>
+        <v>1505</v>
       </c>
       <c r="F401" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="G401" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H401" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="I401" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="J401" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="K401" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="L401" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="M401" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="N401" t="s">
         <v>1637</v>
@@ -22917,10 +22917,10 @@
         <v>1228</v>
       </c>
       <c r="D402" t="s">
-        <v>1311</v>
+        <v>1268</v>
       </c>
       <c r="E402" t="s">
-        <v>1505</v>
+        <v>1462</v>
       </c>
       <c r="F402" t="s">
         <v>1624</v>
@@ -22929,19 +22929,19 @@
         <v>1630</v>
       </c>
       <c r="H402" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I402" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J402" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="K402" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="L402" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="M402" t="s">
         <v>1632</v>
@@ -22961,10 +22961,10 @@
         <v>1229</v>
       </c>
       <c r="D403" t="s">
-        <v>1268</v>
+        <v>1282</v>
       </c>
       <c r="E403" t="s">
-        <v>1462</v>
+        <v>1476</v>
       </c>
       <c r="F403" t="s">
         <v>1624</v>
@@ -22973,19 +22973,19 @@
         <v>1630</v>
       </c>
       <c r="H403" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="I403" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="J403" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K403" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L403" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="M403" t="s">
         <v>1632</v>
@@ -23005,13 +23005,13 @@
         <v>1230</v>
       </c>
       <c r="D404" t="s">
-        <v>1282</v>
+        <v>1258</v>
       </c>
       <c r="E404" t="s">
-        <v>1476</v>
+        <v>1452</v>
       </c>
       <c r="F404" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G404" t="s">
         <v>1630</v>
@@ -23020,19 +23020,19 @@
         <v>1633</v>
       </c>
       <c r="I404" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="J404" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="K404" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L404" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="M404" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N404" t="s">
         <v>1637</v>
@@ -23049,34 +23049,34 @@
         <v>1231</v>
       </c>
       <c r="D405" t="s">
-        <v>1258</v>
+        <v>1423</v>
       </c>
       <c r="E405" t="s">
-        <v>1452</v>
+        <v>1617</v>
       </c>
       <c r="F405" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G405" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="H405" t="s">
         <v>1633</v>
       </c>
       <c r="I405" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="J405" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="K405" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="L405" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M405" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N405" t="s">
         <v>1637</v>
@@ -23093,31 +23093,31 @@
         <v>1232</v>
       </c>
       <c r="D406" t="s">
-        <v>1423</v>
+        <v>1252</v>
       </c>
       <c r="E406" t="s">
-        <v>1617</v>
+        <v>1446</v>
       </c>
       <c r="F406" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G406" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="H406" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="I406" t="s">
         <v>1631</v>
       </c>
       <c r="J406" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="K406" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="L406" t="s">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="M406" t="s">
         <v>1632</v>
@@ -23137,34 +23137,34 @@
         <v>1233</v>
       </c>
       <c r="D407" t="s">
-        <v>1252</v>
+        <v>1262</v>
       </c>
       <c r="E407" t="s">
-        <v>1446</v>
+        <v>1456</v>
       </c>
       <c r="F407" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G407" t="s">
         <v>1630</v>
       </c>
       <c r="H407" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="I407" t="s">
-        <v>1631</v>
+        <v>1636</v>
       </c>
       <c r="J407" t="s">
         <v>1633</v>
       </c>
       <c r="K407" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="L407" t="s">
         <v>1635</v>
       </c>
       <c r="M407" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="N407" t="s">
         <v>1637</v>
@@ -23181,34 +23181,34 @@
         <v>1234</v>
       </c>
       <c r="D408" t="s">
-        <v>1262</v>
+        <v>1338</v>
       </c>
       <c r="E408" t="s">
-        <v>1456</v>
+        <v>1532</v>
       </c>
       <c r="F408" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="G408" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H408" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="I408" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="J408" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="K408" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="L408" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="M408" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="N408" t="s">
         <v>1637</v>
@@ -23225,34 +23225,34 @@
         <v>1235</v>
       </c>
       <c r="D409">
-        <v>1213</v>
+        <v>1307</v>
       </c>
       <c r="E409">
-        <v>60.65</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F409" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G409" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H409" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="I409" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="J409" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="K409" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="L409" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="M409" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N409" t="s">
         <v>1637</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1081,180 +1081,180 @@
     <t>يونس جمعه يونس على</t>
   </si>
   <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
     <t>محمد حسن محمد محمود</t>
   </si>
   <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2275,180 +2275,180 @@
     <t>30512012406318</t>
   </si>
   <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
     <t>30310312400832</t>
   </si>
   <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3469,178 +3469,178 @@
     <t>01148979466</t>
   </si>
   <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
     <t>01020592062</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01142212131</t>
   </si>
   <si>
     <t>1353</t>
@@ -20228,34 +20228,34 @@
         <v>1151</v>
       </c>
       <c r="D343" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="E343" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="F343" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="G343" t="s">
         <v>1599</v>
       </c>
       <c r="H343" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="I343" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="J343" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="K343" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="L343" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="M343" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N343" t="s">
         <v>1606</v>
@@ -20272,13 +20272,13 @@
         <v>1152</v>
       </c>
       <c r="D344" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="E344" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="F344" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="G344" t="s">
         <v>1599</v>
@@ -20287,19 +20287,19 @@
         <v>1600</v>
       </c>
       <c r="I344" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="J344" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="K344" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="L344" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="M344" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="N344" t="s">
         <v>1606</v>
@@ -20316,10 +20316,10 @@
         <v>1153</v>
       </c>
       <c r="D345" t="s">
-        <v>1390</v>
+        <v>1344</v>
       </c>
       <c r="E345" t="s">
-        <v>1582</v>
+        <v>1536</v>
       </c>
       <c r="F345" t="s">
         <v>1595</v>
@@ -20328,22 +20328,22 @@
         <v>1599</v>
       </c>
       <c r="H345" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="I345" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="J345" t="s">
         <v>1601</v>
       </c>
       <c r="K345" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="L345" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="M345" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="N345" t="s">
         <v>1606</v>
@@ -20360,13 +20360,13 @@
         <v>1154</v>
       </c>
       <c r="D346" t="s">
-        <v>1344</v>
+        <v>1305</v>
       </c>
       <c r="E346" t="s">
-        <v>1536</v>
+        <v>1497</v>
       </c>
       <c r="F346" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G346" t="s">
         <v>1599</v>
@@ -20375,19 +20375,19 @@
         <v>1602</v>
       </c>
       <c r="I346" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="J346" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="K346" t="s">
         <v>1600</v>
       </c>
       <c r="L346" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="M346" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N346" t="s">
         <v>1606</v>
@@ -20404,34 +20404,34 @@
         <v>1155</v>
       </c>
       <c r="D347" t="s">
-        <v>1305</v>
+        <v>1285</v>
       </c>
       <c r="E347" t="s">
-        <v>1497</v>
+        <v>1477</v>
       </c>
       <c r="F347" t="s">
         <v>1594</v>
       </c>
       <c r="G347" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="H347" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="I347" t="s">
         <v>1603</v>
       </c>
       <c r="J347" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="K347" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="L347" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="M347" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N347" t="s">
         <v>1606</v>
@@ -20448,34 +20448,34 @@
         <v>1156</v>
       </c>
       <c r="D348" t="s">
-        <v>1285</v>
+        <v>1245</v>
       </c>
       <c r="E348" t="s">
-        <v>1477</v>
+        <v>1437</v>
       </c>
       <c r="F348" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G348" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H348" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
       <c r="I348" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="J348" t="s">
         <v>1600</v>
       </c>
       <c r="K348" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="L348" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="M348" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="N348" t="s">
         <v>1606</v>
@@ -20492,34 +20492,34 @@
         <v>1157</v>
       </c>
       <c r="D349" t="s">
-        <v>1245</v>
+        <v>1362</v>
       </c>
       <c r="E349" t="s">
-        <v>1437</v>
+        <v>1554</v>
       </c>
       <c r="F349" t="s">
         <v>1593</v>
       </c>
       <c r="G349" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="H349" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="I349" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
       <c r="J349" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="K349" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="L349" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="M349" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="N349" t="s">
         <v>1606</v>
@@ -20536,10 +20536,10 @@
         <v>1158</v>
       </c>
       <c r="D350" t="s">
-        <v>1362</v>
+        <v>1308</v>
       </c>
       <c r="E350" t="s">
-        <v>1554</v>
+        <v>1500</v>
       </c>
       <c r="F350" t="s">
         <v>1593</v>
@@ -20551,16 +20551,16 @@
         <v>1602</v>
       </c>
       <c r="I350" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="J350" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="K350" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="L350" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="M350" t="s">
         <v>1600</v>
@@ -20580,34 +20580,34 @@
         <v>1159</v>
       </c>
       <c r="D351" t="s">
-        <v>1308</v>
+        <v>1293</v>
       </c>
       <c r="E351" t="s">
-        <v>1500</v>
+        <v>1485</v>
       </c>
       <c r="F351" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="G351" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H351" t="s">
         <v>1602</v>
       </c>
       <c r="I351" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="J351" t="s">
         <v>1605</v>
       </c>
       <c r="K351" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="L351" t="s">
         <v>1601</v>
       </c>
       <c r="M351" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="N351" t="s">
         <v>1606</v>
@@ -20624,34 +20624,34 @@
         <v>1160</v>
       </c>
       <c r="D352" t="s">
-        <v>1293</v>
+        <v>1284</v>
       </c>
       <c r="E352" t="s">
-        <v>1485</v>
+        <v>1476</v>
       </c>
       <c r="F352" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G352" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H352" t="s">
         <v>1602</v>
       </c>
       <c r="I352" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
       <c r="J352" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="K352" t="s">
         <v>1603</v>
       </c>
       <c r="L352" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="M352" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N352" t="s">
         <v>1606</v>
@@ -20668,34 +20668,34 @@
         <v>1161</v>
       </c>
       <c r="D353" t="s">
-        <v>1284</v>
+        <v>1232</v>
       </c>
       <c r="E353" t="s">
-        <v>1476</v>
+        <v>1424</v>
       </c>
       <c r="F353" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="G353" t="s">
         <v>1599</v>
       </c>
       <c r="H353" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="I353" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="J353" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="K353" t="s">
         <v>1603</v>
       </c>
       <c r="L353" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="M353" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N353" t="s">
         <v>1606</v>
@@ -20712,34 +20712,34 @@
         <v>1162</v>
       </c>
       <c r="D354" t="s">
-        <v>1232</v>
+        <v>1248</v>
       </c>
       <c r="E354" t="s">
-        <v>1424</v>
+        <v>1440</v>
       </c>
       <c r="F354" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G354" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="H354" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="I354" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="J354" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="K354" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="L354" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="M354" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="N354" t="s">
         <v>1606</v>
@@ -20756,34 +20756,34 @@
         <v>1163</v>
       </c>
       <c r="D355" t="s">
-        <v>1248</v>
+        <v>1295</v>
       </c>
       <c r="E355" t="s">
-        <v>1440</v>
+        <v>1487</v>
       </c>
       <c r="F355" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="G355" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="H355" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="I355" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="J355" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="K355" t="s">
         <v>1601</v>
       </c>
       <c r="L355" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="M355" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="N355" t="s">
         <v>1606</v>
@@ -20800,19 +20800,19 @@
         <v>1164</v>
       </c>
       <c r="D356" t="s">
-        <v>1295</v>
+        <v>1314</v>
       </c>
       <c r="E356" t="s">
-        <v>1487</v>
+        <v>1506</v>
       </c>
       <c r="F356" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="G356" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H356" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="I356" t="s">
         <v>1602</v>
@@ -20821,10 +20821,10 @@
         <v>1605</v>
       </c>
       <c r="K356" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="L356" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="M356" t="s">
         <v>1604</v>
@@ -20844,34 +20844,34 @@
         <v>1165</v>
       </c>
       <c r="D357" t="s">
-        <v>1314</v>
+        <v>1229</v>
       </c>
       <c r="E357" t="s">
-        <v>1506</v>
+        <v>1421</v>
       </c>
       <c r="F357" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="G357" t="s">
         <v>1600</v>
       </c>
       <c r="H357" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="I357" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="J357" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="K357" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="L357" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="M357" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N357" t="s">
         <v>1606</v>
@@ -20888,34 +20888,34 @@
         <v>1166</v>
       </c>
       <c r="D358" t="s">
-        <v>1229</v>
+        <v>1389</v>
       </c>
       <c r="E358" t="s">
-        <v>1421</v>
+        <v>1581</v>
       </c>
       <c r="F358" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="G358" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="H358" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I358" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="J358" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="K358" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="L358" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="M358" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="N358" t="s">
         <v>1606</v>
@@ -20932,34 +20932,34 @@
         <v>1167</v>
       </c>
       <c r="D359" t="s">
-        <v>1389</v>
+        <v>1275</v>
       </c>
       <c r="E359" t="s">
-        <v>1581</v>
+        <v>1467</v>
       </c>
       <c r="F359" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G359" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="H359" t="s">
         <v>1602</v>
       </c>
       <c r="I359" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="J359" t="s">
         <v>1601</v>
       </c>
       <c r="K359" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="L359" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="M359" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="N359" t="s">
         <v>1606</v>
@@ -20976,31 +20976,31 @@
         <v>1168</v>
       </c>
       <c r="D360" t="s">
-        <v>1275</v>
+        <v>1244</v>
       </c>
       <c r="E360" t="s">
-        <v>1467</v>
+        <v>1436</v>
       </c>
       <c r="F360" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="G360" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="H360" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="I360" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="J360" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="K360" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="L360" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="M360" t="s">
         <v>1604</v>
@@ -21020,31 +21020,31 @@
         <v>1169</v>
       </c>
       <c r="D361" t="s">
-        <v>1244</v>
+        <v>1287</v>
       </c>
       <c r="E361" t="s">
-        <v>1436</v>
+        <v>1479</v>
       </c>
       <c r="F361" t="s">
         <v>1594</v>
       </c>
       <c r="G361" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="H361" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="I361" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="J361" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="K361" t="s">
         <v>1603</v>
       </c>
       <c r="L361" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="M361" t="s">
         <v>1604</v>
@@ -21064,31 +21064,31 @@
         <v>1170</v>
       </c>
       <c r="D362" t="s">
-        <v>1287</v>
+        <v>1255</v>
       </c>
       <c r="E362" t="s">
-        <v>1479</v>
+        <v>1447</v>
       </c>
       <c r="F362" t="s">
         <v>1594</v>
       </c>
       <c r="G362" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H362" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="I362" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="J362" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="K362" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="L362" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="M362" t="s">
         <v>1604</v>
@@ -21108,34 +21108,34 @@
         <v>1171</v>
       </c>
       <c r="D363" t="s">
-        <v>1255</v>
+        <v>1340</v>
       </c>
       <c r="E363" t="s">
-        <v>1447</v>
+        <v>1532</v>
       </c>
       <c r="F363" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G363" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H363" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="I363" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="J363" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="K363" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="L363" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="M363" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="N363" t="s">
         <v>1606</v>
@@ -21152,10 +21152,10 @@
         <v>1172</v>
       </c>
       <c r="D364" t="s">
-        <v>1340</v>
+        <v>1391</v>
       </c>
       <c r="E364" t="s">
-        <v>1532</v>
+        <v>1583</v>
       </c>
       <c r="F364" t="s">
         <v>1593</v>
@@ -21196,34 +21196,34 @@
         <v>1173</v>
       </c>
       <c r="D365" t="s">
-        <v>1391</v>
+        <v>1228</v>
       </c>
       <c r="E365" t="s">
-        <v>1583</v>
+        <v>1420</v>
       </c>
       <c r="F365" t="s">
         <v>1593</v>
       </c>
       <c r="G365" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H365" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="I365" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="J365" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="K365" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="L365" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="M365" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
       <c r="N365" t="s">
         <v>1606</v>
@@ -21240,31 +21240,31 @@
         <v>1174</v>
       </c>
       <c r="D366" t="s">
-        <v>1228</v>
+        <v>1240</v>
       </c>
       <c r="E366" t="s">
-        <v>1420</v>
+        <v>1432</v>
       </c>
       <c r="F366" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="G366" t="s">
         <v>1599</v>
       </c>
       <c r="H366" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="I366" t="s">
         <v>1605</v>
       </c>
       <c r="J366" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="K366" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="L366" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="M366" t="s">
         <v>1604</v>
@@ -21284,34 +21284,34 @@
         <v>1175</v>
       </c>
       <c r="D367" t="s">
-        <v>1240</v>
+        <v>1392</v>
       </c>
       <c r="E367" t="s">
-        <v>1432</v>
+        <v>1584</v>
       </c>
       <c r="F367" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="G367" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H367" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="I367" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="J367" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K367" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="L367" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="M367" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="N367" t="s">
         <v>1606</v>
@@ -21328,34 +21328,34 @@
         <v>1176</v>
       </c>
       <c r="D368" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E368" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="F368" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="G368" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H368" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="I368" t="s">
         <v>1601</v>
       </c>
       <c r="J368" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="K368" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="L368" t="s">
         <v>1603</v>
       </c>
       <c r="M368" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="N368" t="s">
         <v>1606</v>
@@ -21372,34 +21372,34 @@
         <v>1177</v>
       </c>
       <c r="D369" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="E369" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="F369" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="G369" t="s">
         <v>1599</v>
       </c>
       <c r="H369" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I369" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="J369" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="K369" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="L369" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="M369" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N369" t="s">
         <v>1606</v>
@@ -21416,13 +21416,13 @@
         <v>1178</v>
       </c>
       <c r="D370" t="s">
-        <v>1394</v>
+        <v>1238</v>
       </c>
       <c r="E370" t="s">
-        <v>1586</v>
+        <v>1430</v>
       </c>
       <c r="F370" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G370" t="s">
         <v>1599</v>
@@ -21437,13 +21437,13 @@
         <v>1600</v>
       </c>
       <c r="K370" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="L370" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="M370" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N370" t="s">
         <v>1606</v>
@@ -21460,13 +21460,13 @@
         <v>1179</v>
       </c>
       <c r="D371" t="s">
-        <v>1238</v>
+        <v>1220</v>
       </c>
       <c r="E371" t="s">
-        <v>1430</v>
+        <v>1412</v>
       </c>
       <c r="F371" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="G371" t="s">
         <v>1599</v>
@@ -21478,16 +21478,16 @@
         <v>1605</v>
       </c>
       <c r="J371" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="K371" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="L371" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="M371" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="N371" t="s">
         <v>1606</v>
@@ -21504,22 +21504,22 @@
         <v>1180</v>
       </c>
       <c r="D372" t="s">
-        <v>1220</v>
+        <v>1278</v>
       </c>
       <c r="E372" t="s">
-        <v>1412</v>
+        <v>1470</v>
       </c>
       <c r="F372" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G372" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H372" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="I372" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="J372" t="s">
         <v>1601</v>
@@ -21528,10 +21528,10 @@
         <v>1603</v>
       </c>
       <c r="L372" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="M372" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="N372" t="s">
         <v>1606</v>
@@ -21548,31 +21548,31 @@
         <v>1181</v>
       </c>
       <c r="D373" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="E373" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="F373" t="s">
         <v>1594</v>
       </c>
       <c r="G373" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H373" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="I373" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="J373" t="s">
         <v>1601</v>
       </c>
       <c r="K373" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="L373" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="M373" t="s">
         <v>1605</v>
@@ -21592,34 +21592,34 @@
         <v>1182</v>
       </c>
       <c r="D374" t="s">
-        <v>1284</v>
+        <v>1224</v>
       </c>
       <c r="E374" t="s">
-        <v>1476</v>
+        <v>1416</v>
       </c>
       <c r="F374" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G374" t="s">
         <v>1599</v>
       </c>
       <c r="H374" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="I374" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="J374" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="K374" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="L374" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="M374" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="N374" t="s">
         <v>1606</v>
@@ -21636,34 +21636,34 @@
         <v>1183</v>
       </c>
       <c r="D375" t="s">
-        <v>1224</v>
+        <v>1246</v>
       </c>
       <c r="E375" t="s">
-        <v>1416</v>
+        <v>1438</v>
       </c>
       <c r="F375" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="G375" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H375" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="I375" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="J375" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="K375" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="L375" t="s">
         <v>1604</v>
       </c>
       <c r="M375" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="N375" t="s">
         <v>1606</v>
@@ -21680,34 +21680,34 @@
         <v>1184</v>
       </c>
       <c r="D376" t="s">
-        <v>1246</v>
+        <v>1349</v>
       </c>
       <c r="E376" t="s">
-        <v>1438</v>
+        <v>1541</v>
       </c>
       <c r="F376" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="G376" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H376" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="I376" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="J376" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="K376" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="L376" t="s">
         <v>1604</v>
       </c>
       <c r="M376" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="N376" t="s">
         <v>1606</v>
@@ -21724,10 +21724,10 @@
         <v>1185</v>
       </c>
       <c r="D377" t="s">
-        <v>1349</v>
+        <v>1220</v>
       </c>
       <c r="E377" t="s">
-        <v>1541</v>
+        <v>1412</v>
       </c>
       <c r="F377" t="s">
         <v>1594</v>
@@ -21736,13 +21736,13 @@
         <v>1599</v>
       </c>
       <c r="H377" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="I377" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="J377" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="K377" t="s">
         <v>1600</v>
@@ -21751,7 +21751,7 @@
         <v>1604</v>
       </c>
       <c r="M377" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="N377" t="s">
         <v>1606</v>
@@ -21768,28 +21768,28 @@
         <v>1186</v>
       </c>
       <c r="D378" t="s">
-        <v>1220</v>
+        <v>1275</v>
       </c>
       <c r="E378" t="s">
-        <v>1412</v>
+        <v>1467</v>
       </c>
       <c r="F378" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G378" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H378" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I378" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="J378" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="K378" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="L378" t="s">
         <v>1604</v>
@@ -21812,31 +21812,31 @@
         <v>1187</v>
       </c>
       <c r="D379" t="s">
-        <v>1275</v>
+        <v>1257</v>
       </c>
       <c r="E379" t="s">
-        <v>1467</v>
+        <v>1449</v>
       </c>
       <c r="F379" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="G379" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H379" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="I379" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="J379" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="K379" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="L379" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="M379" t="s">
         <v>1601</v>
@@ -21856,25 +21856,25 @@
         <v>1188</v>
       </c>
       <c r="D380" t="s">
-        <v>1257</v>
+        <v>1364</v>
       </c>
       <c r="E380" t="s">
-        <v>1449</v>
+        <v>1556</v>
       </c>
       <c r="F380" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="G380" t="s">
         <v>1599</v>
       </c>
       <c r="H380" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I380" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="J380" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="K380" t="s">
         <v>1600</v>
@@ -21883,7 +21883,7 @@
         <v>1603</v>
       </c>
       <c r="M380" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N380" t="s">
         <v>1606</v>
@@ -21900,34 +21900,34 @@
         <v>1189</v>
       </c>
       <c r="D381" t="s">
-        <v>1364</v>
+        <v>1338</v>
       </c>
       <c r="E381" t="s">
-        <v>1556</v>
+        <v>1530</v>
       </c>
       <c r="F381" t="s">
         <v>1593</v>
       </c>
       <c r="G381" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="H381" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="I381" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="J381" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="K381" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="L381" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="M381" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N381" t="s">
         <v>1606</v>
@@ -21944,34 +21944,34 @@
         <v>1190</v>
       </c>
       <c r="D382" t="s">
-        <v>1338</v>
+        <v>1394</v>
       </c>
       <c r="E382" t="s">
-        <v>1530</v>
+        <v>1586</v>
       </c>
       <c r="F382" t="s">
         <v>1593</v>
       </c>
       <c r="G382" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="H382" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="I382" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="J382" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="K382" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="L382" t="s">
         <v>1604</v>
       </c>
       <c r="M382" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="N382" t="s">
         <v>1606</v>
@@ -21988,34 +21988,34 @@
         <v>1191</v>
       </c>
       <c r="D383" t="s">
-        <v>1394</v>
+        <v>1243</v>
       </c>
       <c r="E383" t="s">
-        <v>1586</v>
+        <v>1435</v>
       </c>
       <c r="F383" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="G383" t="s">
         <v>1599</v>
       </c>
       <c r="H383" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="I383" t="s">
         <v>1605</v>
       </c>
       <c r="J383" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="K383" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="L383" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="M383" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="N383" t="s">
         <v>1606</v>
@@ -22032,34 +22032,34 @@
         <v>1192</v>
       </c>
       <c r="D384" t="s">
-        <v>1243</v>
+        <v>1257</v>
       </c>
       <c r="E384" t="s">
-        <v>1435</v>
+        <v>1449</v>
       </c>
       <c r="F384" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="G384" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H384" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="I384" t="s">
         <v>1605</v>
       </c>
       <c r="J384" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="K384" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="L384" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="M384" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N384" t="s">
         <v>1606</v>
@@ -22076,34 +22076,34 @@
         <v>1193</v>
       </c>
       <c r="D385" t="s">
-        <v>1257</v>
+        <v>1395</v>
       </c>
       <c r="E385" t="s">
-        <v>1449</v>
+        <v>1587</v>
       </c>
       <c r="F385" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="G385" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H385" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="I385" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="J385" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="K385" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="L385" t="s">
         <v>1604</v>
       </c>
       <c r="M385" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="N385" t="s">
         <v>1606</v>
@@ -22120,34 +22120,34 @@
         <v>1194</v>
       </c>
       <c r="D386" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="E386" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="F386" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="G386" t="s">
         <v>1599</v>
       </c>
       <c r="H386" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I386" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="J386" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="K386" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="L386" t="s">
         <v>1604</v>
       </c>
       <c r="M386" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="N386" t="s">
         <v>1606</v>
@@ -22164,34 +22164,34 @@
         <v>1195</v>
       </c>
       <c r="D387" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E387" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="F387" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G387" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="H387" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="I387" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="J387" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="K387" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="L387" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="M387" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N387" t="s">
         <v>1606</v>
@@ -22208,34 +22208,34 @@
         <v>1196</v>
       </c>
       <c r="D388" t="s">
-        <v>1397</v>
+        <v>1284</v>
       </c>
       <c r="E388" t="s">
-        <v>1589</v>
+        <v>1476</v>
       </c>
       <c r="F388" t="s">
         <v>1594</v>
       </c>
       <c r="G388" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="H388" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="I388" t="s">
         <v>1602</v>
       </c>
       <c r="J388" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="K388" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="L388" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="M388" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N388" t="s">
         <v>1606</v>
@@ -22252,31 +22252,31 @@
         <v>1197</v>
       </c>
       <c r="D389" t="s">
-        <v>1284</v>
+        <v>1374</v>
       </c>
       <c r="E389" t="s">
-        <v>1476</v>
+        <v>1566</v>
       </c>
       <c r="F389" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G389" t="s">
         <v>1599</v>
       </c>
       <c r="H389" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I389" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="J389" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="K389" t="s">
         <v>1603</v>
       </c>
       <c r="L389" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="M389" t="s">
         <v>1601</v>
@@ -22296,31 +22296,31 @@
         <v>1198</v>
       </c>
       <c r="D390" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="E390" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="F390" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="G390" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="H390" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="I390" t="s">
         <v>1605</v>
       </c>
       <c r="J390" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="K390" t="s">
         <v>1603</v>
       </c>
       <c r="L390" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="M390" t="s">
         <v>1601</v>
@@ -22340,34 +22340,34 @@
         <v>1199</v>
       </c>
       <c r="D391" t="s">
-        <v>1369</v>
+        <v>1328</v>
       </c>
       <c r="E391" t="s">
-        <v>1561</v>
+        <v>1520</v>
       </c>
       <c r="F391" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="G391" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="H391" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="I391" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="J391" t="s">
         <v>1599</v>
       </c>
       <c r="K391" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="L391" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="M391" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N391" t="s">
         <v>1606</v>
@@ -22384,16 +22384,16 @@
         <v>1200</v>
       </c>
       <c r="D392" t="s">
-        <v>1328</v>
+        <v>1398</v>
       </c>
       <c r="E392" t="s">
-        <v>1520</v>
+        <v>1590</v>
       </c>
       <c r="F392" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="G392" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H392" t="s">
         <v>1605</v>
@@ -22402,13 +22402,13 @@
         <v>1602</v>
       </c>
       <c r="J392" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="K392" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="L392" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="M392" t="s">
         <v>1604</v>
@@ -22428,34 +22428,34 @@
         <v>1201</v>
       </c>
       <c r="D393" t="s">
-        <v>1398</v>
+        <v>1305</v>
       </c>
       <c r="E393" t="s">
-        <v>1590</v>
+        <v>1497</v>
       </c>
       <c r="F393" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="G393" t="s">
         <v>1599</v>
       </c>
       <c r="H393" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I393" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="J393" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K393" t="s">
         <v>1600</v>
       </c>
       <c r="L393" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="M393" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N393" t="s">
         <v>1606</v>
@@ -22472,34 +22472,34 @@
         <v>1202</v>
       </c>
       <c r="D394" t="s">
-        <v>1305</v>
+        <v>1217</v>
       </c>
       <c r="E394" t="s">
-        <v>1497</v>
+        <v>1409</v>
       </c>
       <c r="F394" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="G394" t="s">
         <v>1599</v>
       </c>
       <c r="H394" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="I394" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="J394" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="K394" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="L394" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="M394" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="N394" t="s">
         <v>1606</v>
@@ -22516,34 +22516,34 @@
         <v>1203</v>
       </c>
       <c r="D395" t="s">
-        <v>1217</v>
+        <v>1399</v>
       </c>
       <c r="E395" t="s">
-        <v>1409</v>
+        <v>1591</v>
       </c>
       <c r="F395" t="s">
         <v>1594</v>
       </c>
       <c r="G395" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H395" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
       <c r="I395" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="J395" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="K395" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="L395" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="M395" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="N395" t="s">
         <v>1606</v>
@@ -22560,31 +22560,31 @@
         <v>1204</v>
       </c>
       <c r="D396" t="s">
-        <v>1399</v>
+        <v>1360</v>
       </c>
       <c r="E396" t="s">
-        <v>1591</v>
+        <v>1552</v>
       </c>
       <c r="F396" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G396" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H396" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="I396" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="J396" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="K396" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="L396" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="M396" t="s">
         <v>1604</v>
@@ -22604,34 +22604,34 @@
         <v>1205</v>
       </c>
       <c r="D397" t="s">
-        <v>1360</v>
+        <v>1225</v>
       </c>
       <c r="E397" t="s">
-        <v>1552</v>
+        <v>1417</v>
       </c>
       <c r="F397" t="s">
         <v>1593</v>
       </c>
       <c r="G397" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="H397" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="I397" t="s">
         <v>1600</v>
       </c>
       <c r="J397" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="K397" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="L397" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="M397" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N397" t="s">
         <v>1606</v>
@@ -22648,34 +22648,34 @@
         <v>1206</v>
       </c>
       <c r="D398" t="s">
-        <v>1225</v>
+        <v>1400</v>
       </c>
       <c r="E398" t="s">
-        <v>1417</v>
+        <v>1592</v>
       </c>
       <c r="F398" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="G398" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="H398" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="I398" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="J398" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="K398" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="L398" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="M398" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="N398" t="s">
         <v>1606</v>
@@ -22692,31 +22692,31 @@
         <v>1207</v>
       </c>
       <c r="D399" t="s">
-        <v>1400</v>
+        <v>1219</v>
       </c>
       <c r="E399" t="s">
-        <v>1592</v>
+        <v>1411</v>
       </c>
       <c r="F399" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="G399" t="s">
         <v>1599</v>
       </c>
       <c r="H399" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="I399" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="J399" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="K399" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="L399" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="M399" t="s">
         <v>1604</v>
@@ -22736,10 +22736,10 @@
         <v>1208</v>
       </c>
       <c r="D400">
-        <v>1354</v>
+        <v>1311</v>
       </c>
       <c r="E400">
-        <v>67.7</v>
+        <v>65.55</v>
       </c>
       <c r="F400" t="s">
         <v>1593</v>
@@ -22748,22 +22748,22 @@
         <v>1599</v>
       </c>
       <c r="H400" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="I400" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="J400" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="K400" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="L400" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="M400" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="N400" t="s">
         <v>1606</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1222,42 +1222,42 @@
     <t>شروق محمد هاشم احمد</t>
   </si>
   <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>يوسف سيف النصر سيد عبد العاطى</t>
+  </si>
+  <si>
+    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
+  </si>
+  <si>
     <t>عبدالله محمد محمد احمد</t>
   </si>
   <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>يوسف سيف النصر سيد عبد العاطى</t>
-  </si>
-  <si>
-    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2419,42 +2419,42 @@
     <t>30510302401007</t>
   </si>
   <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30404012410431</t>
+  </si>
+  <si>
+    <t>30411201403108</t>
+  </si>
+  <si>
     <t>30412262402097</t>
   </si>
   <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30404012410431</t>
-  </si>
-  <si>
-    <t>30411201403108</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3616,40 +3616,40 @@
     <t>01152380733</t>
   </si>
   <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01107909098</t>
+  </si>
+  <si>
+    <t>01080345257</t>
+  </si>
+  <si>
     <t>01121846011</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01107909098</t>
-  </si>
-  <si>
-    <t>01080345257</t>
   </si>
   <si>
     <t>1353</t>
@@ -22305,16 +22305,16 @@
         <v>1200</v>
       </c>
       <c r="D390" t="s">
-        <v>1330</v>
+        <v>1401</v>
       </c>
       <c r="E390" t="s">
-        <v>1522</v>
+        <v>1593</v>
       </c>
       <c r="F390" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="G390" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H390" t="s">
         <v>1608</v>
@@ -22323,13 +22323,13 @@
         <v>1605</v>
       </c>
       <c r="J390" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="K390" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="L390" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="M390" t="s">
         <v>1607</v>
@@ -22349,34 +22349,34 @@
         <v>1201</v>
       </c>
       <c r="D391" t="s">
-        <v>1401</v>
+        <v>1307</v>
       </c>
       <c r="E391" t="s">
-        <v>1593</v>
+        <v>1499</v>
       </c>
       <c r="F391" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G391" t="s">
         <v>1602</v>
       </c>
       <c r="H391" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="I391" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="J391" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="K391" t="s">
         <v>1603</v>
       </c>
       <c r="L391" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="M391" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="N391" t="s">
         <v>1609</v>
@@ -22393,34 +22393,34 @@
         <v>1202</v>
       </c>
       <c r="D392" t="s">
-        <v>1307</v>
+        <v>1220</v>
       </c>
       <c r="E392" t="s">
-        <v>1499</v>
+        <v>1412</v>
       </c>
       <c r="F392" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="G392" t="s">
         <v>1602</v>
       </c>
       <c r="H392" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="I392" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="J392" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="K392" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="L392" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="M392" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="N392" t="s">
         <v>1609</v>
@@ -22437,34 +22437,34 @@
         <v>1203</v>
       </c>
       <c r="D393" t="s">
-        <v>1220</v>
+        <v>1402</v>
       </c>
       <c r="E393" t="s">
-        <v>1412</v>
+        <v>1594</v>
       </c>
       <c r="F393" t="s">
         <v>1597</v>
       </c>
       <c r="G393" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H393" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="I393" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="J393" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="K393" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="L393" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="M393" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="N393" t="s">
         <v>1609</v>
@@ -22481,31 +22481,31 @@
         <v>1204</v>
       </c>
       <c r="D394" t="s">
-        <v>1402</v>
+        <v>1362</v>
       </c>
       <c r="E394" t="s">
-        <v>1594</v>
+        <v>1554</v>
       </c>
       <c r="F394" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="G394" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H394" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="I394" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J394" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="K394" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="L394" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="M394" t="s">
         <v>1607</v>
@@ -22525,34 +22525,34 @@
         <v>1205</v>
       </c>
       <c r="D395" t="s">
-        <v>1362</v>
+        <v>1228</v>
       </c>
       <c r="E395" t="s">
-        <v>1554</v>
+        <v>1420</v>
       </c>
       <c r="F395" t="s">
         <v>1596</v>
       </c>
       <c r="G395" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="H395" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="I395" t="s">
         <v>1603</v>
       </c>
       <c r="J395" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="K395" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="L395" t="s">
-        <v>1608</v>
+        <v>1602</v>
       </c>
       <c r="M395" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="N395" t="s">
         <v>1609</v>
@@ -22569,34 +22569,34 @@
         <v>1206</v>
       </c>
       <c r="D396" t="s">
-        <v>1228</v>
+        <v>1403</v>
       </c>
       <c r="E396" t="s">
-        <v>1420</v>
+        <v>1595</v>
       </c>
       <c r="F396" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="G396" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="H396" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="I396" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="J396" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="K396" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="L396" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="M396" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="N396" t="s">
         <v>1609</v>
@@ -22613,31 +22613,31 @@
         <v>1207</v>
       </c>
       <c r="D397" t="s">
-        <v>1403</v>
+        <v>1222</v>
       </c>
       <c r="E397" t="s">
-        <v>1595</v>
+        <v>1414</v>
       </c>
       <c r="F397" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="G397" t="s">
         <v>1602</v>
       </c>
       <c r="H397" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="I397" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="J397" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="K397" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="L397" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="M397" t="s">
         <v>1607</v>
@@ -22657,10 +22657,10 @@
         <v>1208</v>
       </c>
       <c r="D398" t="s">
-        <v>1222</v>
+        <v>1385</v>
       </c>
       <c r="E398" t="s">
-        <v>1414</v>
+        <v>1577</v>
       </c>
       <c r="F398" t="s">
         <v>1596</v>
@@ -22669,22 +22669,22 @@
         <v>1602</v>
       </c>
       <c r="H398" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="I398" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="J398" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="K398" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="L398" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="M398" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="N398" t="s">
         <v>1609</v>
@@ -22701,19 +22701,19 @@
         <v>1209</v>
       </c>
       <c r="D399" t="s">
-        <v>1385</v>
+        <v>1366</v>
       </c>
       <c r="E399" t="s">
-        <v>1577</v>
+        <v>1558</v>
       </c>
       <c r="F399" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="G399" t="s">
         <v>1602</v>
       </c>
       <c r="H399" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I399" t="s">
         <v>1608</v>
@@ -22722,7 +22722,7 @@
         <v>1605</v>
       </c>
       <c r="K399" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="L399" t="s">
         <v>1607</v>
@@ -22745,34 +22745,34 @@
         <v>1210</v>
       </c>
       <c r="D400" t="s">
-        <v>1366</v>
+        <v>1234</v>
       </c>
       <c r="E400" t="s">
-        <v>1558</v>
+        <v>1426</v>
       </c>
       <c r="F400" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="G400" t="s">
         <v>1602</v>
       </c>
       <c r="H400" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="I400" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="J400" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="K400" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="L400" t="s">
-        <v>1607</v>
+        <v>1603</v>
       </c>
       <c r="M400" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="N400" t="s">
         <v>1609</v>
@@ -22789,34 +22789,34 @@
         <v>1211</v>
       </c>
       <c r="D401">
-        <v>1301</v>
+        <v>1347</v>
       </c>
       <c r="E401">
-        <v>65.05</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F401" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="G401" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H401" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="I401" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="J401" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="K401" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="L401" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="M401" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="N401" t="s">
         <v>1609</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1252,12 +1252,12 @@
     <t>يوسف سيف النصر سيد عبد العاطى</t>
   </si>
   <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
     <t>نورهان عامر ابو الفتح عبد الوهاب</t>
   </si>
   <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2449,12 +2449,12 @@
     <t>30404012410431</t>
   </si>
   <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
     <t>30411201403108</t>
   </si>
   <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3646,10 +3646,10 @@
     <t>01107909098</t>
   </si>
   <si>
+    <t>01121846011</t>
+  </si>
+  <si>
     <t>01080345257</t>
-  </si>
-  <si>
-    <t>01121846011</t>
   </si>
   <si>
     <t>1353</t>
@@ -22745,34 +22745,34 @@
         <v>1210</v>
       </c>
       <c r="D400" t="s">
-        <v>1234</v>
+        <v>1330</v>
       </c>
       <c r="E400" t="s">
-        <v>1426</v>
+        <v>1522</v>
       </c>
       <c r="F400" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="G400" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H400" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="I400" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="J400" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
       <c r="K400" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="L400" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="M400" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="N400" t="s">
         <v>1609</v>
@@ -22789,34 +22789,34 @@
         <v>1211</v>
       </c>
       <c r="D401">
-        <v>1347</v>
+        <v>1301</v>
       </c>
       <c r="E401">
-        <v>67.34999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="F401" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="G401" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H401" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="I401" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="J401" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
       <c r="K401" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="L401" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="M401" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="N401" t="s">
         <v>1609</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1201,63 +1201,63 @@
     <t>هدير حماده حجازى فهمى</t>
   </si>
   <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>يوسف سيف النصر سيد عبد العاطى</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
+  </si>
+  <si>
+    <t>محمد خلف نبيشى محمد</t>
+  </si>
+  <si>
     <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
   </si>
   <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>يوسف سيف النصر سيد عبد العاطى</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
-  </si>
-  <si>
-    <t>محمد خلف نبيشى محمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2398,63 +2398,63 @@
     <t>30312132403143</t>
   </si>
   <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30404012410431</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30411201403108</t>
+  </si>
+  <si>
+    <t>30504212402195</t>
+  </si>
+  <si>
     <t>30509112403153</t>
   </si>
   <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30404012410431</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30411201403108</t>
-  </si>
-  <si>
-    <t>30504212402195</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3595,63 +3595,63 @@
     <t>01092965157</t>
   </si>
   <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01107909098</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01080345257</t>
+  </si>
+  <si>
+    <t>01140717605</t>
+  </si>
+  <si>
     <t>01006926646</t>
   </si>
   <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01107909098</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01080345257</t>
-  </si>
-  <si>
-    <t>01140717605</t>
-  </si>
-  <si>
     <t>1353</t>
   </si>
   <si>
@@ -4207,9 +4207,6 @@
     <t>1304</t>
   </si>
   <si>
-    <t>1511</t>
-  </si>
-  <si>
     <t>1136</t>
   </si>
   <si>
@@ -4225,6 +4222,9 @@
     <t>1235</t>
   </si>
   <si>
+    <t>1510</t>
+  </si>
+  <si>
     <t>67.65</t>
   </si>
   <si>
@@ -4780,9 +4780,6 @@
     <t>65.2</t>
   </si>
   <si>
-    <t>75.55</t>
-  </si>
-  <si>
     <t>56.8</t>
   </si>
   <si>
@@ -4796,6 +4793,9 @@
   </si>
   <si>
     <t>61.75</t>
+  </si>
+  <si>
+    <t>75.5</t>
   </si>
   <si>
     <t>جيد</t>
@@ -21997,28 +21997,28 @@
         <v>1588</v>
       </c>
       <c r="F383" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="G383" t="s">
         <v>1600</v>
       </c>
       <c r="H383" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I383" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="J383" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="K383" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="L383" t="s">
         <v>1605</v>
       </c>
       <c r="M383" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="N383" t="s">
         <v>1607</v>
@@ -22041,28 +22041,28 @@
         <v>1589</v>
       </c>
       <c r="F384" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="G384" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="H384" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="I384" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J384" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="K384" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="L384" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="M384" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="N384" t="s">
         <v>1607</v>
@@ -22079,34 +22079,34 @@
         <v>1195</v>
       </c>
       <c r="D385" t="s">
-        <v>1399</v>
+        <v>1285</v>
       </c>
       <c r="E385" t="s">
-        <v>1590</v>
+        <v>1476</v>
       </c>
       <c r="F385" t="s">
         <v>1595</v>
       </c>
       <c r="G385" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="H385" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="I385" t="s">
         <v>1603</v>
       </c>
       <c r="J385" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="K385" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="L385" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="M385" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="N385" t="s">
         <v>1607</v>
@@ -22123,31 +22123,31 @@
         <v>1196</v>
       </c>
       <c r="D386" t="s">
-        <v>1285</v>
+        <v>1376</v>
       </c>
       <c r="E386" t="s">
-        <v>1476</v>
+        <v>1567</v>
       </c>
       <c r="F386" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G386" t="s">
         <v>1600</v>
       </c>
       <c r="H386" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I386" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="J386" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="K386" t="s">
         <v>1604</v>
       </c>
       <c r="L386" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="M386" t="s">
         <v>1602</v>
@@ -22167,31 +22167,31 @@
         <v>1197</v>
       </c>
       <c r="D387" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="E387" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="F387" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="G387" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="H387" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="I387" t="s">
         <v>1606</v>
       </c>
       <c r="J387" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="K387" t="s">
         <v>1604</v>
       </c>
       <c r="L387" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="M387" t="s">
         <v>1602</v>
@@ -22211,34 +22211,34 @@
         <v>1198</v>
       </c>
       <c r="D388" t="s">
-        <v>1371</v>
+        <v>1399</v>
       </c>
       <c r="E388" t="s">
-        <v>1562</v>
+        <v>1590</v>
       </c>
       <c r="F388" t="s">
         <v>1596</v>
       </c>
       <c r="G388" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="H388" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="I388" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J388" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="K388" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="L388" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="M388" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="N388" t="s">
         <v>1607</v>
@@ -22255,34 +22255,34 @@
         <v>1199</v>
       </c>
       <c r="D389" t="s">
-        <v>1400</v>
+        <v>1306</v>
       </c>
       <c r="E389" t="s">
-        <v>1591</v>
+        <v>1497</v>
       </c>
       <c r="F389" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="G389" t="s">
         <v>1600</v>
       </c>
       <c r="H389" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I389" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="J389" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="K389" t="s">
         <v>1601</v>
       </c>
       <c r="L389" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="M389" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="N389" t="s">
         <v>1607</v>
@@ -22299,34 +22299,34 @@
         <v>1200</v>
       </c>
       <c r="D390" t="s">
-        <v>1306</v>
+        <v>1220</v>
       </c>
       <c r="E390" t="s">
-        <v>1497</v>
+        <v>1411</v>
       </c>
       <c r="F390" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G390" t="s">
         <v>1600</v>
       </c>
       <c r="H390" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="I390" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="J390" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="K390" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="L390" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="M390" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="N390" t="s">
         <v>1607</v>
@@ -22343,34 +22343,34 @@
         <v>1201</v>
       </c>
       <c r="D391" t="s">
-        <v>1220</v>
+        <v>1400</v>
       </c>
       <c r="E391" t="s">
-        <v>1411</v>
+        <v>1591</v>
       </c>
       <c r="F391" t="s">
         <v>1595</v>
       </c>
       <c r="G391" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H391" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="I391" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="J391" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="K391" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="L391" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="M391" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="N391" t="s">
         <v>1607</v>
@@ -22387,31 +22387,31 @@
         <v>1202</v>
       </c>
       <c r="D392" t="s">
-        <v>1401</v>
+        <v>1361</v>
       </c>
       <c r="E392" t="s">
-        <v>1592</v>
+        <v>1552</v>
       </c>
       <c r="F392" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G392" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H392" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="I392" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="J392" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="K392" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="L392" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="M392" t="s">
         <v>1605</v>
@@ -22431,34 +22431,34 @@
         <v>1203</v>
       </c>
       <c r="D393" t="s">
-        <v>1361</v>
+        <v>1228</v>
       </c>
       <c r="E393" t="s">
-        <v>1552</v>
+        <v>1419</v>
       </c>
       <c r="F393" t="s">
         <v>1594</v>
       </c>
       <c r="G393" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="H393" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="I393" t="s">
         <v>1601</v>
       </c>
       <c r="J393" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="K393" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="L393" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="M393" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="N393" t="s">
         <v>1607</v>
@@ -22475,34 +22475,34 @@
         <v>1204</v>
       </c>
       <c r="D394" t="s">
-        <v>1228</v>
+        <v>1401</v>
       </c>
       <c r="E394" t="s">
-        <v>1419</v>
+        <v>1592</v>
       </c>
       <c r="F394" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G394" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="H394" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I394" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="J394" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="K394" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="L394" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="M394" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="N394" t="s">
         <v>1607</v>
@@ -22519,31 +22519,31 @@
         <v>1205</v>
       </c>
       <c r="D395" t="s">
-        <v>1402</v>
+        <v>1222</v>
       </c>
       <c r="E395" t="s">
-        <v>1593</v>
+        <v>1413</v>
       </c>
       <c r="F395" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G395" t="s">
         <v>1600</v>
       </c>
       <c r="H395" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="I395" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="J395" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="K395" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="L395" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="M395" t="s">
         <v>1605</v>
@@ -22563,10 +22563,10 @@
         <v>1206</v>
       </c>
       <c r="D396" t="s">
-        <v>1222</v>
+        <v>1384</v>
       </c>
       <c r="E396" t="s">
-        <v>1413</v>
+        <v>1575</v>
       </c>
       <c r="F396" t="s">
         <v>1594</v>
@@ -22575,22 +22575,22 @@
         <v>1600</v>
       </c>
       <c r="H396" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I396" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="J396" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="K396" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="L396" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="M396" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="N396" t="s">
         <v>1607</v>
@@ -22607,19 +22607,19 @@
         <v>1207</v>
       </c>
       <c r="D397" t="s">
-        <v>1384</v>
+        <v>1365</v>
       </c>
       <c r="E397" t="s">
-        <v>1575</v>
+        <v>1556</v>
       </c>
       <c r="F397" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="G397" t="s">
         <v>1600</v>
       </c>
       <c r="H397" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="I397" t="s">
         <v>1606</v>
@@ -22628,7 +22628,7 @@
         <v>1603</v>
       </c>
       <c r="K397" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="L397" t="s">
         <v>1605</v>
@@ -22651,34 +22651,34 @@
         <v>1208</v>
       </c>
       <c r="D398" t="s">
-        <v>1365</v>
+        <v>1329</v>
       </c>
       <c r="E398" t="s">
-        <v>1556</v>
+        <v>1520</v>
       </c>
       <c r="F398" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="G398" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H398" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="I398" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J398" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="K398" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="L398" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="M398" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="N398" t="s">
         <v>1607</v>
@@ -22695,34 +22695,34 @@
         <v>1209</v>
       </c>
       <c r="D399" t="s">
-        <v>1329</v>
+        <v>1234</v>
       </c>
       <c r="E399" t="s">
-        <v>1520</v>
+        <v>1425</v>
       </c>
       <c r="F399" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G399" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H399" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I399" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="J399" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="K399" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="L399" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="M399" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="N399" t="s">
         <v>1607</v>
@@ -22739,13 +22739,13 @@
         <v>1210</v>
       </c>
       <c r="D400" t="s">
-        <v>1234</v>
+        <v>1402</v>
       </c>
       <c r="E400" t="s">
-        <v>1425</v>
+        <v>1593</v>
       </c>
       <c r="F400" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="G400" t="s">
         <v>1600</v>
@@ -22754,19 +22754,19 @@
         <v>1603</v>
       </c>
       <c r="I400" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="J400" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="K400" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="L400" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="M400" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="N400" t="s">
         <v>1607</v>
@@ -22783,10 +22783,10 @@
         <v>1211</v>
       </c>
       <c r="D401">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="E401">
-        <v>75.5</v>
+        <v>75.55</v>
       </c>
       <c r="F401" t="s">
         <v>1598</v>
@@ -22795,22 +22795,22 @@
         <v>1600</v>
       </c>
       <c r="H401" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="I401" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J401" t="s">
         <v>1601</v>
       </c>
       <c r="K401" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="L401" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="M401" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="N401" t="s">
         <v>1607</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1225,39 +1225,39 @@
     <t>محمد رجب عبدالله احمد</t>
   </si>
   <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>يوسف سيف النصر سيد عبد العاطى</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
+  </si>
+  <si>
+    <t>محمد خلف نبيشى محمد</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
     <t>عز الدين محمود شحاته سيد حنفى</t>
   </si>
   <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>يوسف سيف النصر سيد عبد العاطى</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
-  </si>
-  <si>
-    <t>محمد خلف نبيشى محمد</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2422,39 +2422,39 @@
     <t>30505262402419</t>
   </si>
   <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30404012410431</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30411201403108</t>
+  </si>
+  <si>
+    <t>30504212402195</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
     <t>30602172400056</t>
   </si>
   <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30404012410431</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30411201403108</t>
-  </si>
-  <si>
-    <t>30504212402195</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3619,39 +3619,39 @@
     <t>01097432947</t>
   </si>
   <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01107909098</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01080345257</t>
+  </si>
+  <si>
+    <t>01140717605</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
     <t>01551488731</t>
   </si>
   <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01107909098</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01080345257</t>
-  </si>
-  <si>
-    <t>01140717605</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
     <t>1353</t>
   </si>
   <si>
@@ -4216,15 +4216,15 @@
     <t>1242</t>
   </si>
   <si>
-    <t>1441</t>
-  </si>
-  <si>
     <t>1235</t>
   </si>
   <si>
     <t>1510</t>
   </si>
   <si>
+    <t>1511</t>
+  </si>
+  <si>
     <t>67.65</t>
   </si>
   <si>
@@ -4789,13 +4789,13 @@
     <t>62.1</t>
   </si>
   <si>
-    <t>72.05</t>
-  </si>
-  <si>
     <t>61.75</t>
   </si>
   <si>
     <t>75.5</t>
+  </si>
+  <si>
+    <t>75.55</t>
   </si>
   <si>
     <t>جيد</t>
@@ -22343,31 +22343,31 @@
         <v>1201</v>
       </c>
       <c r="D391" t="s">
-        <v>1400</v>
+        <v>1361</v>
       </c>
       <c r="E391" t="s">
-        <v>1591</v>
+        <v>1552</v>
       </c>
       <c r="F391" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G391" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H391" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="I391" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="J391" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="K391" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="L391" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="M391" t="s">
         <v>1605</v>
@@ -22387,34 +22387,34 @@
         <v>1202</v>
       </c>
       <c r="D392" t="s">
-        <v>1361</v>
+        <v>1228</v>
       </c>
       <c r="E392" t="s">
-        <v>1552</v>
+        <v>1419</v>
       </c>
       <c r="F392" t="s">
         <v>1594</v>
       </c>
       <c r="G392" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="H392" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="I392" t="s">
         <v>1601</v>
       </c>
       <c r="J392" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="K392" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="L392" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="M392" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="N392" t="s">
         <v>1607</v>
@@ -22431,34 +22431,34 @@
         <v>1203</v>
       </c>
       <c r="D393" t="s">
-        <v>1228</v>
+        <v>1400</v>
       </c>
       <c r="E393" t="s">
-        <v>1419</v>
+        <v>1591</v>
       </c>
       <c r="F393" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G393" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="H393" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I393" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="J393" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="K393" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="L393" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="M393" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="N393" t="s">
         <v>1607</v>
@@ -22475,31 +22475,31 @@
         <v>1204</v>
       </c>
       <c r="D394" t="s">
-        <v>1401</v>
+        <v>1222</v>
       </c>
       <c r="E394" t="s">
-        <v>1592</v>
+        <v>1413</v>
       </c>
       <c r="F394" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="G394" t="s">
         <v>1600</v>
       </c>
       <c r="H394" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="I394" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="J394" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="K394" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="L394" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="M394" t="s">
         <v>1605</v>
@@ -22519,10 +22519,10 @@
         <v>1205</v>
       </c>
       <c r="D395" t="s">
-        <v>1222</v>
+        <v>1384</v>
       </c>
       <c r="E395" t="s">
-        <v>1413</v>
+        <v>1575</v>
       </c>
       <c r="F395" t="s">
         <v>1594</v>
@@ -22531,22 +22531,22 @@
         <v>1600</v>
       </c>
       <c r="H395" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I395" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="J395" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="K395" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="L395" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="M395" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="N395" t="s">
         <v>1607</v>
@@ -22563,19 +22563,19 @@
         <v>1206</v>
       </c>
       <c r="D396" t="s">
-        <v>1384</v>
+        <v>1365</v>
       </c>
       <c r="E396" t="s">
-        <v>1575</v>
+        <v>1556</v>
       </c>
       <c r="F396" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="G396" t="s">
         <v>1600</v>
       </c>
       <c r="H396" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="I396" t="s">
         <v>1606</v>
@@ -22584,7 +22584,7 @@
         <v>1603</v>
       </c>
       <c r="K396" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="L396" t="s">
         <v>1605</v>
@@ -22607,34 +22607,34 @@
         <v>1207</v>
       </c>
       <c r="D397" t="s">
-        <v>1365</v>
+        <v>1329</v>
       </c>
       <c r="E397" t="s">
-        <v>1556</v>
+        <v>1520</v>
       </c>
       <c r="F397" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="G397" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H397" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="I397" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J397" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="K397" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="L397" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="M397" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="N397" t="s">
         <v>1607</v>
@@ -22651,34 +22651,34 @@
         <v>1208</v>
       </c>
       <c r="D398" t="s">
-        <v>1329</v>
+        <v>1234</v>
       </c>
       <c r="E398" t="s">
-        <v>1520</v>
+        <v>1425</v>
       </c>
       <c r="F398" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="G398" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H398" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="I398" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="J398" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="K398" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="L398" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="M398" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="N398" t="s">
         <v>1607</v>
@@ -22695,13 +22695,13 @@
         <v>1209</v>
       </c>
       <c r="D399" t="s">
-        <v>1234</v>
+        <v>1401</v>
       </c>
       <c r="E399" t="s">
-        <v>1425</v>
+        <v>1592</v>
       </c>
       <c r="F399" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="G399" t="s">
         <v>1600</v>
@@ -22710,19 +22710,19 @@
         <v>1603</v>
       </c>
       <c r="I399" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="J399" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="K399" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="L399" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="M399" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="N399" t="s">
         <v>1607</v>
@@ -22751,22 +22751,22 @@
         <v>1600</v>
       </c>
       <c r="H400" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="I400" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J400" t="s">
         <v>1601</v>
       </c>
       <c r="K400" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="L400" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="M400" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="N400" t="s">
         <v>1607</v>
@@ -22783,34 +22783,34 @@
         <v>1211</v>
       </c>
       <c r="D401">
-        <v>1511</v>
+        <v>1441</v>
       </c>
       <c r="E401">
-        <v>75.55</v>
+        <v>72.05</v>
       </c>
       <c r="F401" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="G401" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H401" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="I401" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="J401" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="K401" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="L401" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="M401" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="N401" t="s">
         <v>1607</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -3676,7 +3676,7 @@
     <t>01025520618</t>
   </si>
   <si>
-    <t xml:space="preserve">  010196677</t>
+    <t xml:space="preserve"> 0101966776</t>
   </si>
   <si>
     <t>1353</t>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -1102,180 +1102,180 @@
     <t>نور ناصر مسامح جاد</t>
   </si>
   <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>يوسف سيف النصر سيد عبد العاطى</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
+  </si>
+  <si>
+    <t>محمد خلف نبيشى محمد</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>بسمله أبوقرمان محمد عبد الغني</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>شروق احمد نصر الدين علي</t>
+  </si>
+  <si>
+    <t>محمد ياسر محمد فوزى محمد اللطيف</t>
+  </si>
+  <si>
+    <t>بلال محمد عيسى محمد على</t>
+  </si>
+  <si>
+    <t>محمود طلعت محمود سيد</t>
+  </si>
+  <si>
+    <t>روان رجب فتحى عبدالرحيم</t>
+  </si>
+  <si>
+    <t>كريم حسن فاروق مليجى</t>
+  </si>
+  <si>
+    <t>يوسف رمضان جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>يوسف مصطفي سيد يوسف</t>
+  </si>
+  <si>
+    <t>رغده مصطفى عبدالرازق عبدالفتاح</t>
+  </si>
+  <si>
+    <t>مصطفى محمود عبدالمنعم محمد محمد</t>
+  </si>
+  <si>
+    <t>محمد عطيه عبدالسلام عبدالعاطى</t>
+  </si>
+  <si>
+    <t>بهاء الدين محمد ابراهيم على</t>
+  </si>
+  <si>
     <t>عبدالرحيم سداد عبدالرحيم احمد</t>
   </si>
   <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>يوسف سيف النصر سيد عبد العاطى</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
-  </si>
-  <si>
-    <t>محمد خلف نبيشى محمد</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>بسمله أبوقرمان محمد عبد الغني</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>شروق احمد نصر الدين علي</t>
-  </si>
-  <si>
-    <t>محمد ياسر محمد فوزى محمد اللطيف</t>
-  </si>
-  <si>
-    <t>بلال محمد عيسى محمد على</t>
-  </si>
-  <si>
-    <t>محمود طلعت محمود سيد</t>
-  </si>
-  <si>
-    <t>روان رجب فتحى عبدالرحيم</t>
-  </si>
-  <si>
-    <t>كريم حسن فاروق مليجى</t>
-  </si>
-  <si>
-    <t>يوسف رمضان جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>يوسف مصطفي سيد يوسف</t>
-  </si>
-  <si>
-    <t>رغده مصطفى عبدالرازق عبدالفتاح</t>
-  </si>
-  <si>
-    <t>مصطفى محمود عبدالمنعم محمد محمد</t>
-  </si>
-  <si>
-    <t>محمد عطيه عبدالسلام عبدالعاطى</t>
-  </si>
-  <si>
-    <t>بهاء الدين محمد ابراهيم على</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2317,180 +2317,180 @@
     <t>30510012422787</t>
   </si>
   <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30404012410431</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30411201403108</t>
+  </si>
+  <si>
+    <t>30504212402195</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30401012422988</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30511272400503</t>
+  </si>
+  <si>
+    <t>30603052400636</t>
+  </si>
+  <si>
+    <t>30406222401055</t>
+  </si>
+  <si>
+    <t>30205152403718</t>
+  </si>
+  <si>
+    <t>30601172402745</t>
+  </si>
+  <si>
+    <t>30304010400698</t>
+  </si>
+  <si>
+    <t>30510252406355</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30506282400915</t>
+  </si>
+  <si>
+    <t>30506012405141</t>
+  </si>
+  <si>
+    <t>30512012410072</t>
+  </si>
+  <si>
+    <t>30411202405791</t>
+  </si>
+  <si>
+    <t>30506082400619</t>
+  </si>
+  <si>
     <t>30507252403118</t>
   </si>
   <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30404012410431</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30411201403108</t>
-  </si>
-  <si>
-    <t>30504212402195</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30401012422988</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30511272400503</t>
-  </si>
-  <si>
-    <t>30603052400636</t>
-  </si>
-  <si>
-    <t>30406222401055</t>
-  </si>
-  <si>
-    <t>30205152403718</t>
-  </si>
-  <si>
-    <t>30601172402745</t>
-  </si>
-  <si>
-    <t>30304010400698</t>
-  </si>
-  <si>
-    <t>30510252406355</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30506282400915</t>
-  </si>
-  <si>
-    <t>30506012405141</t>
-  </si>
-  <si>
-    <t>30512012410072</t>
-  </si>
-  <si>
-    <t>30411202405791</t>
-  </si>
-  <si>
-    <t>30506082400619</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3532,178 +3532,178 @@
     <t>01065745021</t>
   </si>
   <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01107909098</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01080345257</t>
+  </si>
+  <si>
+    <t>01140717605</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01126693628</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01063495341</t>
+  </si>
+  <si>
+    <t>01200941594</t>
+  </si>
+  <si>
+    <t>01100086115</t>
+  </si>
+  <si>
+    <t>01025520618</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0101966776</t>
+  </si>
+  <si>
+    <t>01095305700</t>
+  </si>
+  <si>
+    <t>01008063893</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01156509914</t>
+  </si>
+  <si>
+    <t>01120137745</t>
+  </si>
+  <si>
+    <t>01033989631</t>
+  </si>
+  <si>
+    <t>01156096723</t>
+  </si>
+  <si>
+    <t>01012467272</t>
+  </si>
+  <si>
     <t>01274116321</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01107909098</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01080345257</t>
-  </si>
-  <si>
-    <t>01140717605</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01126693628</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01063495341</t>
-  </si>
-  <si>
-    <t>01200941594</t>
-  </si>
-  <si>
-    <t>01100086115</t>
-  </si>
-  <si>
-    <t>01025520618</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0101966776</t>
-  </si>
-  <si>
-    <t>01095305700</t>
-  </si>
-  <si>
-    <t>01008063893</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01156509914</t>
-  </si>
-  <si>
-    <t>01120137745</t>
-  </si>
-  <si>
-    <t>01033989631</t>
-  </si>
-  <si>
-    <t>01156096723</t>
-  </si>
-  <si>
-    <t>01012467272</t>
   </si>
   <si>
     <t>1353</t>
@@ -20617,31 +20617,31 @@
         <v>1172</v>
       </c>
       <c r="D350" t="s">
-        <v>1305</v>
+        <v>1276</v>
       </c>
       <c r="E350" t="s">
-        <v>1500</v>
+        <v>1471</v>
       </c>
       <c r="F350" t="s">
         <v>1621</v>
       </c>
       <c r="G350" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H350" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="I350" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="J350" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="K350" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="L350" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="M350" t="s">
         <v>1631</v>
@@ -20661,34 +20661,34 @@
         <v>1173</v>
       </c>
       <c r="D351" t="s">
-        <v>1276</v>
+        <v>1357</v>
       </c>
       <c r="E351" t="s">
-        <v>1471</v>
+        <v>1552</v>
       </c>
       <c r="F351" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G351" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H351" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="I351" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="J351" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="K351" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="L351" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="M351" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="N351" t="s">
         <v>1633</v>
@@ -20705,10 +20705,10 @@
         <v>1174</v>
       </c>
       <c r="D352" t="s">
-        <v>1357</v>
+        <v>1408</v>
       </c>
       <c r="E352" t="s">
-        <v>1552</v>
+        <v>1603</v>
       </c>
       <c r="F352" t="s">
         <v>1620</v>
@@ -20749,34 +20749,34 @@
         <v>1175</v>
       </c>
       <c r="D353" t="s">
-        <v>1408</v>
+        <v>1249</v>
       </c>
       <c r="E353" t="s">
-        <v>1603</v>
+        <v>1444</v>
       </c>
       <c r="F353" t="s">
         <v>1620</v>
       </c>
       <c r="G353" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H353" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="I353" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="J353" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="K353" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="L353" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="M353" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="N353" t="s">
         <v>1633</v>
@@ -20793,31 +20793,31 @@
         <v>1176</v>
       </c>
       <c r="D354" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="E354" t="s">
-        <v>1444</v>
+        <v>1456</v>
       </c>
       <c r="F354" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G354" t="s">
         <v>1626</v>
       </c>
       <c r="H354" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="I354" t="s">
         <v>1632</v>
       </c>
       <c r="J354" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K354" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="L354" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="M354" t="s">
         <v>1631</v>
@@ -20837,34 +20837,34 @@
         <v>1177</v>
       </c>
       <c r="D355" t="s">
-        <v>1261</v>
+        <v>1409</v>
       </c>
       <c r="E355" t="s">
-        <v>1456</v>
+        <v>1604</v>
       </c>
       <c r="F355" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="G355" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H355" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="I355" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="J355" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K355" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="L355" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="M355" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="N355" t="s">
         <v>1633</v>
@@ -20881,34 +20881,34 @@
         <v>1178</v>
       </c>
       <c r="D356" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E356" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="F356" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="G356" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H356" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="I356" t="s">
         <v>1628</v>
       </c>
       <c r="J356" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="K356" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="L356" t="s">
         <v>1630</v>
       </c>
       <c r="M356" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="N356" t="s">
         <v>1633</v>
@@ -20925,34 +20925,34 @@
         <v>1179</v>
       </c>
       <c r="D357" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E357" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="F357" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="G357" t="s">
         <v>1626</v>
       </c>
       <c r="H357" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I357" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="J357" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="K357" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L357" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M357" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N357" t="s">
         <v>1633</v>
@@ -20969,13 +20969,13 @@
         <v>1180</v>
       </c>
       <c r="D358" t="s">
-        <v>1411</v>
+        <v>1259</v>
       </c>
       <c r="E358" t="s">
-        <v>1606</v>
+        <v>1454</v>
       </c>
       <c r="F358" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G358" t="s">
         <v>1626</v>
@@ -20990,13 +20990,13 @@
         <v>1627</v>
       </c>
       <c r="K358" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="L358" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M358" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N358" t="s">
         <v>1633</v>
@@ -21013,13 +21013,13 @@
         <v>1181</v>
       </c>
       <c r="D359" t="s">
-        <v>1259</v>
+        <v>1241</v>
       </c>
       <c r="E359" t="s">
-        <v>1454</v>
+        <v>1436</v>
       </c>
       <c r="F359" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G359" t="s">
         <v>1626</v>
@@ -21031,16 +21031,16 @@
         <v>1632</v>
       </c>
       <c r="J359" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K359" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L359" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M359" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="N359" t="s">
         <v>1633</v>
@@ -21057,22 +21057,22 @@
         <v>1182</v>
       </c>
       <c r="D360" t="s">
-        <v>1241</v>
+        <v>1296</v>
       </c>
       <c r="E360" t="s">
-        <v>1436</v>
+        <v>1491</v>
       </c>
       <c r="F360" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G360" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H360" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="I360" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="J360" t="s">
         <v>1628</v>
@@ -21081,10 +21081,10 @@
         <v>1630</v>
       </c>
       <c r="L360" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="M360" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="N360" t="s">
         <v>1633</v>
@@ -21101,31 +21101,31 @@
         <v>1183</v>
       </c>
       <c r="D361" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="E361" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="F361" t="s">
         <v>1621</v>
       </c>
       <c r="G361" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H361" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="I361" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="J361" t="s">
         <v>1628</v>
       </c>
       <c r="K361" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L361" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="M361" t="s">
         <v>1632</v>
@@ -21145,34 +21145,34 @@
         <v>1184</v>
       </c>
       <c r="D362" t="s">
-        <v>1302</v>
+        <v>1245</v>
       </c>
       <c r="E362" t="s">
-        <v>1497</v>
+        <v>1440</v>
       </c>
       <c r="F362" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G362" t="s">
         <v>1626</v>
       </c>
       <c r="H362" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="I362" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J362" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="K362" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="L362" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M362" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="N362" t="s">
         <v>1633</v>
@@ -21189,34 +21189,34 @@
         <v>1185</v>
       </c>
       <c r="D363" t="s">
-        <v>1245</v>
+        <v>1267</v>
       </c>
       <c r="E363" t="s">
-        <v>1440</v>
+        <v>1462</v>
       </c>
       <c r="F363" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G363" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H363" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I363" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J363" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="K363" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L363" t="s">
         <v>1631</v>
       </c>
       <c r="M363" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="N363" t="s">
         <v>1633</v>
@@ -21233,34 +21233,34 @@
         <v>1186</v>
       </c>
       <c r="D364" t="s">
-        <v>1267</v>
+        <v>1366</v>
       </c>
       <c r="E364" t="s">
-        <v>1462</v>
+        <v>1561</v>
       </c>
       <c r="F364" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G364" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H364" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I364" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J364" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="K364" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L364" t="s">
         <v>1631</v>
       </c>
       <c r="M364" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N364" t="s">
         <v>1633</v>
@@ -21277,10 +21277,10 @@
         <v>1187</v>
       </c>
       <c r="D365" t="s">
-        <v>1366</v>
+        <v>1241</v>
       </c>
       <c r="E365" t="s">
-        <v>1561</v>
+        <v>1436</v>
       </c>
       <c r="F365" t="s">
         <v>1621</v>
@@ -21289,13 +21289,13 @@
         <v>1626</v>
       </c>
       <c r="H365" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I365" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J365" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K365" t="s">
         <v>1627</v>
@@ -21304,7 +21304,7 @@
         <v>1631</v>
       </c>
       <c r="M365" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="N365" t="s">
         <v>1633</v>
@@ -21321,28 +21321,28 @@
         <v>1188</v>
       </c>
       <c r="D366" t="s">
-        <v>1241</v>
+        <v>1407</v>
       </c>
       <c r="E366" t="s">
-        <v>1436</v>
+        <v>1602</v>
       </c>
       <c r="F366" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G366" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H366" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I366" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="J366" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K366" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L366" t="s">
         <v>1631</v>
@@ -21365,31 +21365,31 @@
         <v>1189</v>
       </c>
       <c r="D367" t="s">
-        <v>1407</v>
+        <v>1380</v>
       </c>
       <c r="E367" t="s">
-        <v>1602</v>
+        <v>1575</v>
       </c>
       <c r="F367" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G367" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H367" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I367" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="J367" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K367" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L367" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M367" t="s">
         <v>1628</v>
@@ -21409,25 +21409,25 @@
         <v>1190</v>
       </c>
       <c r="D368" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E368" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="F368" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G368" t="s">
         <v>1626</v>
       </c>
       <c r="H368" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I368" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J368" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="K368" t="s">
         <v>1627</v>
@@ -21436,7 +21436,7 @@
         <v>1630</v>
       </c>
       <c r="M368" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N368" t="s">
         <v>1633</v>
@@ -21453,34 +21453,34 @@
         <v>1191</v>
       </c>
       <c r="D369" t="s">
-        <v>1381</v>
+        <v>1355</v>
       </c>
       <c r="E369" t="s">
-        <v>1576</v>
+        <v>1550</v>
       </c>
       <c r="F369" t="s">
         <v>1620</v>
       </c>
       <c r="G369" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H369" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I369" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="J369" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K369" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="L369" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M369" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N369" t="s">
         <v>1633</v>
@@ -21497,34 +21497,34 @@
         <v>1192</v>
       </c>
       <c r="D370" t="s">
-        <v>1355</v>
+        <v>1411</v>
       </c>
       <c r="E370" t="s">
-        <v>1550</v>
+        <v>1606</v>
       </c>
       <c r="F370" t="s">
         <v>1620</v>
       </c>
       <c r="G370" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H370" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="I370" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="J370" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="K370" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="L370" t="s">
         <v>1631</v>
       </c>
       <c r="M370" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N370" t="s">
         <v>1633</v>
@@ -21541,34 +21541,34 @@
         <v>1193</v>
       </c>
       <c r="D371" t="s">
-        <v>1411</v>
+        <v>1264</v>
       </c>
       <c r="E371" t="s">
-        <v>1606</v>
+        <v>1459</v>
       </c>
       <c r="F371" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G371" t="s">
         <v>1626</v>
       </c>
       <c r="H371" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I371" t="s">
         <v>1632</v>
       </c>
       <c r="J371" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="K371" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="L371" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M371" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="N371" t="s">
         <v>1633</v>
@@ -21585,34 +21585,34 @@
         <v>1194</v>
       </c>
       <c r="D372" t="s">
-        <v>1264</v>
+        <v>1380</v>
       </c>
       <c r="E372" t="s">
-        <v>1459</v>
+        <v>1575</v>
       </c>
       <c r="F372" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="G372" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H372" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="I372" t="s">
         <v>1632</v>
       </c>
       <c r="J372" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="K372" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="L372" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M372" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N372" t="s">
         <v>1633</v>
@@ -21629,19 +21629,19 @@
         <v>1195</v>
       </c>
       <c r="D373" t="s">
-        <v>1380</v>
+        <v>1412</v>
       </c>
       <c r="E373" t="s">
-        <v>1575</v>
+        <v>1607</v>
       </c>
       <c r="F373" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="G373" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H373" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I373" t="s">
         <v>1632</v>
@@ -21650,7 +21650,7 @@
         <v>1630</v>
       </c>
       <c r="K373" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="L373" t="s">
         <v>1631</v>
@@ -21673,34 +21673,34 @@
         <v>1196</v>
       </c>
       <c r="D374" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E374" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="F374" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G374" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H374" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="I374" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J374" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="K374" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="L374" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="M374" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N374" t="s">
         <v>1633</v>
@@ -21717,34 +21717,34 @@
         <v>1197</v>
       </c>
       <c r="D375" t="s">
-        <v>1413</v>
+        <v>1302</v>
       </c>
       <c r="E375" t="s">
-        <v>1608</v>
+        <v>1497</v>
       </c>
       <c r="F375" t="s">
         <v>1621</v>
       </c>
       <c r="G375" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H375" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="I375" t="s">
         <v>1629</v>
       </c>
       <c r="J375" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="K375" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="L375" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="M375" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N375" t="s">
         <v>1633</v>
@@ -21761,31 +21761,31 @@
         <v>1198</v>
       </c>
       <c r="D376" t="s">
-        <v>1302</v>
+        <v>1391</v>
       </c>
       <c r="E376" t="s">
-        <v>1497</v>
+        <v>1586</v>
       </c>
       <c r="F376" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G376" t="s">
         <v>1626</v>
       </c>
       <c r="H376" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I376" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J376" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="K376" t="s">
         <v>1630</v>
       </c>
       <c r="L376" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="M376" t="s">
         <v>1628</v>
@@ -21805,31 +21805,31 @@
         <v>1199</v>
       </c>
       <c r="D377" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="E377" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="F377" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G377" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H377" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I377" t="s">
         <v>1632</v>
       </c>
       <c r="J377" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="K377" t="s">
         <v>1630</v>
       </c>
       <c r="L377" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="M377" t="s">
         <v>1628</v>
@@ -21849,34 +21849,34 @@
         <v>1200</v>
       </c>
       <c r="D378" t="s">
-        <v>1386</v>
+        <v>1414</v>
       </c>
       <c r="E378" t="s">
-        <v>1581</v>
+        <v>1609</v>
       </c>
       <c r="F378" t="s">
         <v>1622</v>
       </c>
       <c r="G378" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H378" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="I378" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J378" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="K378" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L378" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="M378" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N378" t="s">
         <v>1633</v>
@@ -21893,34 +21893,34 @@
         <v>1201</v>
       </c>
       <c r="D379" t="s">
-        <v>1414</v>
+        <v>1322</v>
       </c>
       <c r="E379" t="s">
-        <v>1609</v>
+        <v>1517</v>
       </c>
       <c r="F379" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G379" t="s">
         <v>1626</v>
       </c>
       <c r="H379" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I379" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J379" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K379" t="s">
         <v>1627</v>
       </c>
       <c r="L379" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M379" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N379" t="s">
         <v>1633</v>
@@ -21937,34 +21937,34 @@
         <v>1202</v>
       </c>
       <c r="D380" t="s">
-        <v>1322</v>
+        <v>1238</v>
       </c>
       <c r="E380" t="s">
-        <v>1517</v>
+        <v>1433</v>
       </c>
       <c r="F380" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G380" t="s">
         <v>1626</v>
       </c>
       <c r="H380" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="I380" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="J380" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="K380" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="L380" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="M380" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N380" t="s">
         <v>1633</v>
@@ -21981,19 +21981,19 @@
         <v>1203</v>
       </c>
       <c r="D381" t="s">
-        <v>1238</v>
+        <v>1376</v>
       </c>
       <c r="E381" t="s">
-        <v>1433</v>
+        <v>1571</v>
       </c>
       <c r="F381" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G381" t="s">
         <v>1626</v>
       </c>
       <c r="H381" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="I381" t="s">
         <v>1627</v>
@@ -22002,13 +22002,13 @@
         <v>1628</v>
       </c>
       <c r="K381" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="L381" t="s">
         <v>1632</v>
       </c>
       <c r="M381" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="N381" t="s">
         <v>1633</v>
@@ -22025,34 +22025,34 @@
         <v>1204</v>
       </c>
       <c r="D382" t="s">
-        <v>1376</v>
+        <v>1246</v>
       </c>
       <c r="E382" t="s">
-        <v>1571</v>
+        <v>1441</v>
       </c>
       <c r="F382" t="s">
         <v>1620</v>
       </c>
       <c r="G382" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H382" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I382" t="s">
         <v>1627</v>
       </c>
       <c r="J382" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K382" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L382" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="M382" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N382" t="s">
         <v>1633</v>
@@ -22069,34 +22069,34 @@
         <v>1205</v>
       </c>
       <c r="D383" t="s">
-        <v>1246</v>
+        <v>1415</v>
       </c>
       <c r="E383" t="s">
-        <v>1441</v>
+        <v>1610</v>
       </c>
       <c r="F383" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G383" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H383" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I383" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="J383" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K383" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="L383" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="M383" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N383" t="s">
         <v>1633</v>
@@ -22113,31 +22113,31 @@
         <v>1206</v>
       </c>
       <c r="D384" t="s">
-        <v>1415</v>
+        <v>1240</v>
       </c>
       <c r="E384" t="s">
-        <v>1610</v>
+        <v>1435</v>
       </c>
       <c r="F384" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G384" t="s">
         <v>1626</v>
       </c>
       <c r="H384" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I384" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="J384" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="K384" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L384" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="M384" t="s">
         <v>1631</v>
@@ -22157,10 +22157,10 @@
         <v>1207</v>
       </c>
       <c r="D385" t="s">
-        <v>1240</v>
+        <v>1398</v>
       </c>
       <c r="E385" t="s">
-        <v>1435</v>
+        <v>1593</v>
       </c>
       <c r="F385" t="s">
         <v>1620</v>
@@ -22169,22 +22169,22 @@
         <v>1626</v>
       </c>
       <c r="H385" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="I385" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J385" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="K385" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L385" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="M385" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N385" t="s">
         <v>1633</v>
@@ -22201,19 +22201,19 @@
         <v>1208</v>
       </c>
       <c r="D386" t="s">
-        <v>1398</v>
+        <v>1380</v>
       </c>
       <c r="E386" t="s">
-        <v>1593</v>
+        <v>1575</v>
       </c>
       <c r="F386" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="G386" t="s">
         <v>1626</v>
       </c>
       <c r="H386" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="I386" t="s">
         <v>1632</v>
@@ -22222,7 +22222,7 @@
         <v>1629</v>
       </c>
       <c r="K386" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L386" t="s">
         <v>1631</v>
@@ -22245,34 +22245,34 @@
         <v>1209</v>
       </c>
       <c r="D387" t="s">
-        <v>1380</v>
+        <v>1345</v>
       </c>
       <c r="E387" t="s">
-        <v>1575</v>
+        <v>1540</v>
       </c>
       <c r="F387" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="G387" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H387" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="I387" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J387" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="K387" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="L387" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M387" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N387" t="s">
         <v>1633</v>
@@ -22289,34 +22289,34 @@
         <v>1210</v>
       </c>
       <c r="D388" t="s">
-        <v>1345</v>
+        <v>1252</v>
       </c>
       <c r="E388" t="s">
-        <v>1540</v>
+        <v>1447</v>
       </c>
       <c r="F388" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G388" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H388" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I388" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="J388" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="K388" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="L388" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="M388" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="N388" t="s">
         <v>1633</v>
@@ -22333,13 +22333,13 @@
         <v>1211</v>
       </c>
       <c r="D389" t="s">
-        <v>1252</v>
+        <v>1416</v>
       </c>
       <c r="E389" t="s">
-        <v>1447</v>
+        <v>1611</v>
       </c>
       <c r="F389" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="G389" t="s">
         <v>1626</v>
@@ -22348,19 +22348,19 @@
         <v>1629</v>
       </c>
       <c r="I389" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="J389" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="K389" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="L389" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="M389" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="N389" t="s">
         <v>1633</v>
@@ -22377,10 +22377,10 @@
         <v>1212</v>
       </c>
       <c r="D390" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="E390" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="F390" t="s">
         <v>1624</v>
@@ -22389,22 +22389,22 @@
         <v>1626</v>
       </c>
       <c r="H390" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I390" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J390" t="s">
         <v>1627</v>
       </c>
       <c r="K390" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="L390" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="M390" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="N390" t="s">
         <v>1633</v>
@@ -22421,34 +22421,34 @@
         <v>1213</v>
       </c>
       <c r="D391" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="E391" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F391" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="G391" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H391" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="I391" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="J391" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="K391" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="L391" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="M391" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="N391" t="s">
         <v>1633</v>
@@ -22465,10 +22465,10 @@
         <v>1214</v>
       </c>
       <c r="D392" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="E392" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="F392" t="s">
         <v>1621</v>
@@ -22477,16 +22477,16 @@
         <v>1627</v>
       </c>
       <c r="H392" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="I392" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J392" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="K392" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="L392" t="s">
         <v>1628</v>
@@ -22509,25 +22509,25 @@
         <v>1215</v>
       </c>
       <c r="D393" t="s">
-        <v>1419</v>
+        <v>1331</v>
       </c>
       <c r="E393" t="s">
-        <v>1614</v>
+        <v>1526</v>
       </c>
       <c r="F393" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G393" t="s">
         <v>1627</v>
       </c>
       <c r="H393" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="I393" t="s">
         <v>1629</v>
       </c>
       <c r="J393" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="K393" t="s">
         <v>1630</v>
@@ -22553,13 +22553,13 @@
         <v>1216</v>
       </c>
       <c r="D394" t="s">
-        <v>1331</v>
+        <v>1407</v>
       </c>
       <c r="E394" t="s">
-        <v>1526</v>
+        <v>1602</v>
       </c>
       <c r="F394" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G394" t="s">
         <v>1627</v>
@@ -22571,16 +22571,16 @@
         <v>1629</v>
       </c>
       <c r="J394" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="K394" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="L394" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="M394" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N394" t="s">
         <v>1633</v>
@@ -22597,34 +22597,34 @@
         <v>1217</v>
       </c>
       <c r="D395" t="s">
-        <v>1407</v>
+        <v>1261</v>
       </c>
       <c r="E395" t="s">
-        <v>1602</v>
+        <v>1456</v>
       </c>
       <c r="F395" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G395" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H395" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I395" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J395" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="K395" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="L395" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="M395" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N395" t="s">
         <v>1633</v>
@@ -22641,13 +22641,13 @@
         <v>1218</v>
       </c>
       <c r="D396" t="s">
-        <v>1261</v>
+        <v>1366</v>
       </c>
       <c r="E396" t="s">
-        <v>1456</v>
+        <v>1561</v>
       </c>
       <c r="F396" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="G396" t="s">
         <v>1626</v>
@@ -22662,13 +22662,13 @@
         <v>1627</v>
       </c>
       <c r="K396" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L396" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M396" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N396" t="s">
         <v>1633</v>
@@ -22685,34 +22685,34 @@
         <v>1219</v>
       </c>
       <c r="D397" t="s">
-        <v>1366</v>
+        <v>1420</v>
       </c>
       <c r="E397" t="s">
-        <v>1561</v>
+        <v>1615</v>
       </c>
       <c r="F397" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G397" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H397" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I397" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="J397" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K397" t="s">
         <v>1631</v>
       </c>
       <c r="L397" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="M397" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="N397" t="s">
         <v>1633</v>
@@ -22729,13 +22729,13 @@
         <v>1220</v>
       </c>
       <c r="D398" t="s">
-        <v>1420</v>
+        <v>1270</v>
       </c>
       <c r="E398" t="s">
-        <v>1615</v>
+        <v>1465</v>
       </c>
       <c r="F398" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="G398" t="s">
         <v>1627</v>
@@ -22744,19 +22744,19 @@
         <v>1626</v>
       </c>
       <c r="I398" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="J398" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K398" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L398" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="M398" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="N398" t="s">
         <v>1633</v>
@@ -22773,34 +22773,34 @@
         <v>1221</v>
       </c>
       <c r="D399" t="s">
-        <v>1270</v>
+        <v>1421</v>
       </c>
       <c r="E399" t="s">
-        <v>1465</v>
+        <v>1616</v>
       </c>
       <c r="F399" t="s">
         <v>1621</v>
       </c>
       <c r="G399" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="H399" t="s">
         <v>1626</v>
       </c>
       <c r="I399" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="J399" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="K399" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="L399" t="s">
         <v>1631</v>
       </c>
       <c r="M399" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N399" t="s">
         <v>1633</v>
@@ -22817,34 +22817,34 @@
         <v>1222</v>
       </c>
       <c r="D400" t="s">
-        <v>1421</v>
+        <v>1276</v>
       </c>
       <c r="E400" t="s">
-        <v>1616</v>
+        <v>1471</v>
       </c>
       <c r="F400" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G400" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="H400" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I400" t="s">
         <v>1627</v>
       </c>
       <c r="J400" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="K400" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="L400" t="s">
         <v>1631</v>
       </c>
       <c r="M400" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="N400" t="s">
         <v>1633</v>
@@ -22861,10 +22861,10 @@
         <v>1223</v>
       </c>
       <c r="D401" t="s">
-        <v>1276</v>
+        <v>1422</v>
       </c>
       <c r="E401" t="s">
-        <v>1471</v>
+        <v>1617</v>
       </c>
       <c r="F401" t="s">
         <v>1620</v>
@@ -22876,10 +22876,10 @@
         <v>1629</v>
       </c>
       <c r="I401" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="J401" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="K401" t="s">
         <v>1630</v>
@@ -22905,10 +22905,10 @@
         <v>1224</v>
       </c>
       <c r="D402" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="E402" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="F402" t="s">
         <v>1620</v>
@@ -22920,19 +22920,19 @@
         <v>1629</v>
       </c>
       <c r="I402" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="J402" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K402" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L402" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M402" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N402" t="s">
         <v>1633</v>
@@ -22949,13 +22949,13 @@
         <v>1225</v>
       </c>
       <c r="D403" t="s">
-        <v>1423</v>
+        <v>1255</v>
       </c>
       <c r="E403" t="s">
-        <v>1618</v>
+        <v>1450</v>
       </c>
       <c r="F403" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G403" t="s">
         <v>1626</v>
@@ -22964,19 +22964,19 @@
         <v>1629</v>
       </c>
       <c r="I403" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="J403" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K403" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="L403" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="M403" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="N403" t="s">
         <v>1633</v>
@@ -22993,13 +22993,13 @@
         <v>1226</v>
       </c>
       <c r="D404" t="s">
-        <v>1255</v>
+        <v>1381</v>
       </c>
       <c r="E404" t="s">
-        <v>1450</v>
+        <v>1576</v>
       </c>
       <c r="F404" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G404" t="s">
         <v>1626</v>
@@ -23011,13 +23011,13 @@
         <v>1632</v>
       </c>
       <c r="J404" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="K404" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L404" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="M404" t="s">
         <v>1631</v>
@@ -23037,13 +23037,13 @@
         <v>1227</v>
       </c>
       <c r="D405" t="s">
-        <v>1381</v>
+        <v>1424</v>
       </c>
       <c r="E405" t="s">
-        <v>1576</v>
+        <v>1619</v>
       </c>
       <c r="F405" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G405" t="s">
         <v>1626</v>
@@ -23052,19 +23052,19 @@
         <v>1629</v>
       </c>
       <c r="I405" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="J405" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K405" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L405" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M405" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N405" t="s">
         <v>1633</v>
@@ -23081,13 +23081,13 @@
         <v>1228</v>
       </c>
       <c r="D406" t="s">
-        <v>1424</v>
+        <v>1374</v>
       </c>
       <c r="E406" t="s">
-        <v>1619</v>
+        <v>1569</v>
       </c>
       <c r="F406" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G406" t="s">
         <v>1626</v>
@@ -23096,19 +23096,19 @@
         <v>1629</v>
       </c>
       <c r="I406" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="J406" t="s">
         <v>1628</v>
       </c>
       <c r="K406" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="L406" t="s">
         <v>1630</v>
       </c>
       <c r="M406" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N406" t="s">
         <v>1633</v>
@@ -23125,31 +23125,31 @@
         <v>1229</v>
       </c>
       <c r="D407">
-        <v>1365</v>
+        <v>1250</v>
       </c>
       <c r="E407">
-        <v>68.25</v>
+        <v>62.5</v>
       </c>
       <c r="F407" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G407" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H407" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="I407" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="J407" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="K407" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="L407" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="M407" t="s">
         <v>1631</v>

--- a/student_requests.xlsx
+++ b/student_requests.xlsx
@@ -886,396 +886,396 @@
     <t>هاجر حماد محمد حسن</t>
   </si>
   <si>
+    <t>ضحى حسن سيد عباس</t>
+  </si>
+  <si>
+    <t>حازم مصطفى عبد الله عبد القادر</t>
+  </si>
+  <si>
+    <t>زياد شعبان عبد الرشيد مرزوق</t>
+  </si>
+  <si>
+    <t>عثمان عادل عثمان حسن</t>
+  </si>
+  <si>
+    <t>منار فتحى عبد الجليل محمد</t>
+  </si>
+  <si>
+    <t>منه اسماعيل ابراهيم شحاته</t>
+  </si>
+  <si>
+    <t>الحسن محمود على نصار</t>
+  </si>
+  <si>
+    <t>وسام بدر عبد العظيم نصر</t>
+  </si>
+  <si>
+    <t>الحسن صلاح عبد المعز متولى</t>
+  </si>
+  <si>
+    <t>حسناء محمد حسب الله محمد</t>
+  </si>
+  <si>
+    <t>هدير عبد النعيم عبد الصالحين محمد</t>
+  </si>
+  <si>
+    <t>رنا رضا ممدوح محمد</t>
+  </si>
+  <si>
+    <t>خالد وليد حنفى محمود</t>
+  </si>
+  <si>
+    <t>شعبان محمود عبد السلام عثمان</t>
+  </si>
+  <si>
+    <t>أحمد محمد على محمد</t>
+  </si>
+  <si>
+    <t>يوسف عصام محمد تونى</t>
+  </si>
+  <si>
+    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
+  </si>
+  <si>
+    <t>محمد عماد حمدى عبد الفتاح</t>
+  </si>
+  <si>
+    <t>محمد على عبدالرحمن على</t>
+  </si>
+  <si>
+    <t>محمد خلف عبد المنعم سيد</t>
+  </si>
+  <si>
+    <t>بسمه طارق محمد حسن</t>
+  </si>
+  <si>
+    <t>محمود سعيد محمد دكرورى</t>
+  </si>
+  <si>
+    <t>محمود محمد محمود محمد</t>
+  </si>
+  <si>
+    <t>ايمن ابراهيم محمد على</t>
+  </si>
+  <si>
+    <t>احمد حسن جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد عمر محمود محمد</t>
+  </si>
+  <si>
+    <t>محسن ابراهيم مراد عبد الجواد</t>
+  </si>
+  <si>
+    <t>على عمر على محمد امين</t>
+  </si>
+  <si>
+    <t>صلاح محمد صلاح محمد</t>
+  </si>
+  <si>
+    <t>محمد معني فوزي شافعي</t>
+  </si>
+  <si>
+    <t>فاطمه محمود يونس عبدالغنى</t>
+  </si>
+  <si>
+    <t>منه الله حجازي فتحي عثمان</t>
+  </si>
+  <si>
+    <t>حمزه رضا احمد محمود</t>
+  </si>
+  <si>
+    <t>ياسمين على حامد على</t>
+  </si>
+  <si>
+    <t>ندا سيد قاعود محمود</t>
+  </si>
+  <si>
+    <t>محمد رضا بركات عبد الجابر</t>
+  </si>
+  <si>
+    <t>عمر صابر بيومى صابر</t>
+  </si>
+  <si>
+    <t>كريم احمد محمد محمود</t>
+  </si>
+  <si>
+    <t>احمد سعيد محمود عبدالعزيز</t>
+  </si>
+  <si>
+    <t>ضياء الدين محمد عنتر محمد</t>
+  </si>
+  <si>
+    <t>ساندى هانى فاروق ميخائيل</t>
+  </si>
+  <si>
+    <t>سهيله محمد محمد جمعه</t>
+  </si>
+  <si>
+    <t>كريم علاء امين محمد</t>
+  </si>
+  <si>
+    <t>ضياء محمد فاروق راشد</t>
+  </si>
+  <si>
+    <t>مريم ميخائيل مسعود قلته</t>
+  </si>
+  <si>
+    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
+  </si>
+  <si>
+    <t>عبدالرحمن علاء محمد احمد</t>
+  </si>
+  <si>
+    <t>بسمله حامد صلاح زكى</t>
+  </si>
+  <si>
+    <t>دياب اسامه دياب عبدالجابر</t>
+  </si>
+  <si>
+    <t>عيسى عبد القادر على سعد</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد اسماعيل</t>
+  </si>
+  <si>
+    <t>تيموثاوس داود محروس جرجس</t>
+  </si>
+  <si>
+    <t>يوسف شريف رضوان فزاع</t>
+  </si>
+  <si>
+    <t>يونس جمعه يونس على</t>
+  </si>
+  <si>
+    <t>فادى نصر موسى محمود</t>
+  </si>
+  <si>
+    <t>عمرو هشام جمال رياض</t>
+  </si>
+  <si>
+    <t>كرم عاطف عبد المنعم عبد السلام</t>
+  </si>
+  <si>
+    <t>ساره حاتم حسن عطيه</t>
+  </si>
+  <si>
+    <t>شهد احمد محمد حسين</t>
+  </si>
+  <si>
+    <t>عمرو خالد هديه عبدالموجود</t>
+  </si>
+  <si>
+    <t>مصطفى محمد فضل دردير</t>
+  </si>
+  <si>
+    <t>مهاب وائل عبد الهادى عبد الله</t>
+  </si>
+  <si>
+    <t>شروق محمود زين محمد</t>
+  </si>
+  <si>
+    <t>روان محمد عبد الله حسن</t>
+  </si>
+  <si>
+    <t>زينب محمود احمد محمود</t>
+  </si>
+  <si>
+    <t>بدر أحمد محمد كامل</t>
+  </si>
+  <si>
+    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمود كمال على</t>
+  </si>
+  <si>
+    <t>حبيبه عصام محمد حامد</t>
+  </si>
+  <si>
+    <t>سارة رضا عبد المنعم محمد</t>
+  </si>
+  <si>
+    <t>نور ناصر مسامح جاد</t>
+  </si>
+  <si>
+    <t>محمد رمضان محمد فرحان</t>
+  </si>
+  <si>
+    <t>ابراهيم عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>عمر عماد فرغلى على</t>
+  </si>
+  <si>
+    <t>محمود علاء سمير على</t>
+  </si>
+  <si>
+    <t>شهد صالح ضوى عبدالحميد</t>
+  </si>
+  <si>
+    <t>جمال مؤمن سيد احمد</t>
+  </si>
+  <si>
+    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
+  </si>
+  <si>
+    <t>اسراء محمد محمد على</t>
+  </si>
+  <si>
+    <t>نور شحاته نور الدين ابو الليل</t>
+  </si>
+  <si>
+    <t>محمد ناصف عبدالعظيم محمد</t>
+  </si>
+  <si>
+    <t>مصطفى احمد محمد احمد</t>
+  </si>
+  <si>
+    <t>المختار مجدى مختار احمد</t>
+  </si>
+  <si>
+    <t>خالد حماده خالد محمد</t>
+  </si>
+  <si>
+    <t>عمر احمد عبد الرحيم محمد</t>
+  </si>
+  <si>
+    <t>صالح عزت صالح عبد السيد</t>
+  </si>
+  <si>
+    <t>فاطمه طاهر عبد الحميد عبد العال</t>
+  </si>
+  <si>
+    <t>اميره علاء جمال عبد الرازق</t>
+  </si>
+  <si>
+    <t>مريم علاء انور محمد</t>
+  </si>
+  <si>
+    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
+  </si>
+  <si>
+    <t>شرين احمد ابو بكر خلف</t>
+  </si>
+  <si>
+    <t>محمد اشرف محمد مختار اسماعيل</t>
+  </si>
+  <si>
+    <t>احمد جمال عبد الرحمن علي</t>
+  </si>
+  <si>
+    <t>هدير حماده حجازى فهمى</t>
+  </si>
+  <si>
+    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
+  </si>
+  <si>
+    <t>حازم بدر خلف خليفة</t>
+  </si>
+  <si>
+    <t>مصطفى صافى توفيق صالح</t>
+  </si>
+  <si>
+    <t>حسام اسامه سعد حسين</t>
+  </si>
+  <si>
+    <t>شروق محمد هاشم احمد</t>
+  </si>
+  <si>
+    <t>كيرلس ناصر منير تكلا</t>
+  </si>
+  <si>
+    <t>ملك خالد محمد زهنى اسماعيل</t>
+  </si>
+  <si>
+    <t>محمد رجب عبدالله احمد</t>
+  </si>
+  <si>
+    <t>طاهر محمد عبدالقادر بركه الله</t>
+  </si>
+  <si>
+    <t>بسمله ممدوح عزت عبد النعيم</t>
+  </si>
+  <si>
+    <t>خالد محمود ابوالعلا حمدان</t>
+  </si>
+  <si>
+    <t>احمد محمد رجب عبد الحكيم</t>
+  </si>
+  <si>
+    <t>محمد حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>يوسف سيف النصر سيد عبد العاطى</t>
+  </si>
+  <si>
+    <t>عبدالله محمد محمد احمد</t>
+  </si>
+  <si>
+    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
+  </si>
+  <si>
+    <t>محمد خلف نبيشى محمد</t>
+  </si>
+  <si>
+    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
+  </si>
+  <si>
+    <t>عز الدين محمود شحاته سيد حنفى</t>
+  </si>
+  <si>
+    <t>بسمله أبوقرمان محمد عبد الغني</t>
+  </si>
+  <si>
+    <t>الاء جمال يوسف أحمد</t>
+  </si>
+  <si>
+    <t>شروق احمد نصر الدين علي</t>
+  </si>
+  <si>
+    <t>محمد ياسر محمد فوزى محمد اللطيف</t>
+  </si>
+  <si>
+    <t>بلال محمد عيسى محمد على</t>
+  </si>
+  <si>
+    <t>محمود طلعت محمود سيد</t>
+  </si>
+  <si>
+    <t>روان رجب فتحى عبدالرحيم</t>
+  </si>
+  <si>
+    <t>كريم حسن فاروق مليجى</t>
+  </si>
+  <si>
+    <t>يوسف رمضان جمعه ابراهيم</t>
+  </si>
+  <si>
+    <t>محمد رمضان متولى عبد الخالق</t>
+  </si>
+  <si>
+    <t>يوسف مصطفي سيد يوسف</t>
+  </si>
+  <si>
+    <t>رغده مصطفى عبدالرازق عبدالفتاح</t>
+  </si>
+  <si>
+    <t>مصطفى محمود عبدالمنعم محمد محمد</t>
+  </si>
+  <si>
+    <t>محمد عطيه عبدالسلام عبدالعاطى</t>
+  </si>
+  <si>
+    <t>بهاء الدين محمد ابراهيم على</t>
+  </si>
+  <si>
+    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
+  </si>
+  <si>
     <t>حمزه محمد حمدى عرابى</t>
   </si>
   <si>
-    <t>ضحى حسن سيد عباس</t>
-  </si>
-  <si>
-    <t>حازم مصطفى عبد الله عبد القادر</t>
-  </si>
-  <si>
-    <t>زياد شعبان عبد الرشيد مرزوق</t>
-  </si>
-  <si>
-    <t>عثمان عادل عثمان حسن</t>
-  </si>
-  <si>
-    <t>منار فتحى عبد الجليل محمد</t>
-  </si>
-  <si>
-    <t>منه اسماعيل ابراهيم شحاته</t>
-  </si>
-  <si>
-    <t>الحسن محمود على نصار</t>
-  </si>
-  <si>
-    <t>وسام بدر عبد العظيم نصر</t>
-  </si>
-  <si>
-    <t>الحسن صلاح عبد المعز متولى</t>
-  </si>
-  <si>
-    <t>حسناء محمد حسب الله محمد</t>
-  </si>
-  <si>
-    <t>هدير عبد النعيم عبد الصالحين محمد</t>
-  </si>
-  <si>
-    <t>رنا رضا ممدوح محمد</t>
-  </si>
-  <si>
-    <t>خالد وليد حنفى محمود</t>
-  </si>
-  <si>
-    <t>شعبان محمود عبد السلام عثمان</t>
-  </si>
-  <si>
-    <t>أحمد محمد على محمد</t>
-  </si>
-  <si>
-    <t>يوسف عصام محمد تونى</t>
-  </si>
-  <si>
-    <t>يوسف عبدالمنعم رياض عبدالمقصود</t>
-  </si>
-  <si>
-    <t>محمد عماد حمدى عبد الفتاح</t>
-  </si>
-  <si>
-    <t>محمد على عبدالرحمن على</t>
-  </si>
-  <si>
-    <t>محمد خلف عبد المنعم سيد</t>
-  </si>
-  <si>
-    <t>بسمه طارق محمد حسن</t>
-  </si>
-  <si>
-    <t>محمود سعيد محمد دكرورى</t>
-  </si>
-  <si>
-    <t>محمود محمد محمود محمد</t>
-  </si>
-  <si>
-    <t>ايمن ابراهيم محمد على</t>
-  </si>
-  <si>
-    <t>احمد حسن جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد عمر محمود محمد</t>
-  </si>
-  <si>
-    <t>محسن ابراهيم مراد عبد الجواد</t>
-  </si>
-  <si>
-    <t>على عمر على محمد امين</t>
-  </si>
-  <si>
-    <t>صلاح محمد صلاح محمد</t>
-  </si>
-  <si>
-    <t>محمد معني فوزي شافعي</t>
-  </si>
-  <si>
-    <t>فاطمه محمود يونس عبدالغنى</t>
-  </si>
-  <si>
-    <t>منه الله حجازي فتحي عثمان</t>
-  </si>
-  <si>
-    <t>حمزه رضا احمد محمود</t>
-  </si>
-  <si>
-    <t>ياسمين على حامد على</t>
-  </si>
-  <si>
-    <t>ندا سيد قاعود محمود</t>
-  </si>
-  <si>
-    <t>محمد رضا بركات عبد الجابر</t>
-  </si>
-  <si>
-    <t>عمر صابر بيومى صابر</t>
-  </si>
-  <si>
-    <t>كريم احمد محمد محمود</t>
-  </si>
-  <si>
-    <t>احمد سعيد محمود عبدالعزيز</t>
-  </si>
-  <si>
-    <t>ضياء الدين محمد عنتر محمد</t>
-  </si>
-  <si>
-    <t>ساندى هانى فاروق ميخائيل</t>
-  </si>
-  <si>
-    <t>سهيله محمد محمد جمعه</t>
-  </si>
-  <si>
-    <t>كريم علاء امين محمد</t>
-  </si>
-  <si>
-    <t>ضياء محمد فاروق راشد</t>
-  </si>
-  <si>
-    <t>مريم ميخائيل مسعود قلته</t>
-  </si>
-  <si>
-    <t>احمد زين العابدين احمد فؤاد عبد الحكيم</t>
-  </si>
-  <si>
-    <t>عبدالرحمن علاء محمد احمد</t>
-  </si>
-  <si>
-    <t>بسمله حامد صلاح زكى</t>
-  </si>
-  <si>
-    <t>دياب اسامه دياب عبدالجابر</t>
-  </si>
-  <si>
-    <t>عيسى عبد القادر على سعد</t>
-  </si>
-  <si>
-    <t>احمد محمد احمد اسماعيل</t>
-  </si>
-  <si>
-    <t>تيموثاوس داود محروس جرجس</t>
-  </si>
-  <si>
-    <t>يوسف شريف رضوان فزاع</t>
-  </si>
-  <si>
-    <t>يونس جمعه يونس على</t>
-  </si>
-  <si>
-    <t>فادى نصر موسى محمود</t>
-  </si>
-  <si>
-    <t>عمرو هشام جمال رياض</t>
-  </si>
-  <si>
-    <t>كرم عاطف عبد المنعم عبد السلام</t>
-  </si>
-  <si>
-    <t>ساره حاتم حسن عطيه</t>
-  </si>
-  <si>
-    <t>شهد احمد محمد حسين</t>
-  </si>
-  <si>
-    <t>عمرو خالد هديه عبدالموجود</t>
-  </si>
-  <si>
-    <t>مصطفى محمد فضل دردير</t>
-  </si>
-  <si>
-    <t>مهاب وائل عبد الهادى عبد الله</t>
-  </si>
-  <si>
-    <t>شروق محمود زين محمد</t>
-  </si>
-  <si>
-    <t>روان محمد عبد الله حسن</t>
-  </si>
-  <si>
-    <t>زينب محمود احمد محمود</t>
-  </si>
-  <si>
-    <t>بدر أحمد محمد كامل</t>
-  </si>
-  <si>
-    <t>المعتز بالله محمد محمد حمدى عبد العظيم احمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمود كمال على</t>
-  </si>
-  <si>
-    <t>حبيبه عصام محمد حامد</t>
-  </si>
-  <si>
-    <t>سارة رضا عبد المنعم محمد</t>
-  </si>
-  <si>
-    <t>نور ناصر مسامح جاد</t>
-  </si>
-  <si>
-    <t>محمد رمضان محمد فرحان</t>
-  </si>
-  <si>
-    <t>ابراهيم عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>عمر عماد فرغلى على</t>
-  </si>
-  <si>
-    <t>محمود علاء سمير على</t>
-  </si>
-  <si>
-    <t>شهد صالح ضوى عبدالحميد</t>
-  </si>
-  <si>
-    <t>جمال مؤمن سيد احمد</t>
-  </si>
-  <si>
-    <t>عبدالمالك صاوى عبدالمالك صاوى رضوان</t>
-  </si>
-  <si>
-    <t>اسراء محمد محمد على</t>
-  </si>
-  <si>
-    <t>نور شحاته نور الدين ابو الليل</t>
-  </si>
-  <si>
-    <t>محمد ناصف عبدالعظيم محمد</t>
-  </si>
-  <si>
-    <t>مصطفى احمد محمد احمد</t>
-  </si>
-  <si>
-    <t>المختار مجدى مختار احمد</t>
-  </si>
-  <si>
-    <t>خالد حماده خالد محمد</t>
-  </si>
-  <si>
-    <t>عمر احمد عبد الرحيم محمد</t>
-  </si>
-  <si>
-    <t>صالح عزت صالح عبد السيد</t>
-  </si>
-  <si>
-    <t>فاطمه طاهر عبد الحميد عبد العال</t>
-  </si>
-  <si>
-    <t>اميره علاء جمال عبد الرازق</t>
-  </si>
-  <si>
-    <t>مريم علاء انور محمد</t>
-  </si>
-  <si>
-    <t>عبدالرحمن محمد رفعت عبد الحكم</t>
-  </si>
-  <si>
-    <t>شرين احمد ابو بكر خلف</t>
-  </si>
-  <si>
-    <t>محمد اشرف محمد مختار اسماعيل</t>
-  </si>
-  <si>
-    <t>احمد جمال عبد الرحمن علي</t>
-  </si>
-  <si>
-    <t>هدير حماده حجازى فهمى</t>
-  </si>
-  <si>
-    <t>عبدالرحيم ابو بكر عبد الرحيم فرغلى</t>
-  </si>
-  <si>
-    <t>حازم بدر خلف خليفة</t>
-  </si>
-  <si>
-    <t>مصطفى صافى توفيق صالح</t>
-  </si>
-  <si>
-    <t>حسام اسامه سعد حسين</t>
-  </si>
-  <si>
-    <t>شروق محمد هاشم احمد</t>
-  </si>
-  <si>
-    <t>كيرلس ناصر منير تكلا</t>
-  </si>
-  <si>
-    <t>ملك خالد محمد زهنى اسماعيل</t>
-  </si>
-  <si>
-    <t>محمد رجب عبدالله احمد</t>
-  </si>
-  <si>
-    <t>طاهر محمد عبدالقادر بركه الله</t>
-  </si>
-  <si>
-    <t>بسمله ممدوح عزت عبد النعيم</t>
-  </si>
-  <si>
-    <t>خالد محمود ابوالعلا حمدان</t>
-  </si>
-  <si>
-    <t>احمد محمد رجب عبد الحكيم</t>
-  </si>
-  <si>
-    <t>محمد حسن محمد محمود</t>
-  </si>
-  <si>
-    <t>يوسف سيف النصر سيد عبد العاطى</t>
-  </si>
-  <si>
-    <t>عبدالله محمد محمد احمد</t>
-  </si>
-  <si>
-    <t>نورهان عامر ابو الفتح عبد الوهاب</t>
-  </si>
-  <si>
-    <t>محمد خلف نبيشى محمد</t>
-  </si>
-  <si>
-    <t>عبدالله عبدالمحسن محمد عبدالمحسن</t>
-  </si>
-  <si>
-    <t>عز الدين محمود شحاته سيد حنفى</t>
-  </si>
-  <si>
-    <t>بسمله أبوقرمان محمد عبد الغني</t>
-  </si>
-  <si>
-    <t>الاء جمال يوسف أحمد</t>
-  </si>
-  <si>
-    <t>شروق احمد نصر الدين علي</t>
-  </si>
-  <si>
-    <t>محمد ياسر محمد فوزى محمد اللطيف</t>
-  </si>
-  <si>
-    <t>بلال محمد عيسى محمد على</t>
-  </si>
-  <si>
-    <t>محمود طلعت محمود سيد</t>
-  </si>
-  <si>
-    <t>روان رجب فتحى عبدالرحيم</t>
-  </si>
-  <si>
-    <t>كريم حسن فاروق مليجى</t>
-  </si>
-  <si>
-    <t>يوسف رمضان جمعه ابراهيم</t>
-  </si>
-  <si>
-    <t>محمد رمضان متولى عبد الخالق</t>
-  </si>
-  <si>
-    <t>يوسف مصطفي سيد يوسف</t>
-  </si>
-  <si>
-    <t>رغده مصطفى عبدالرازق عبدالفتاح</t>
-  </si>
-  <si>
-    <t>مصطفى محمود عبدالمنعم محمد محمد</t>
-  </si>
-  <si>
-    <t>محمد عطيه عبدالسلام عبدالعاطى</t>
-  </si>
-  <si>
-    <t>بهاء الدين محمد ابراهيم على</t>
-  </si>
-  <si>
-    <t>عبدالرحيم سداد عبدالرحيم احمد</t>
-  </si>
-  <si>
     <t>30504262401831</t>
   </si>
   <si>
@@ -2101,396 +2101,396 @@
     <t>30507152402505</t>
   </si>
   <si>
+    <t>30511242400908</t>
+  </si>
+  <si>
+    <t>30406132403474</t>
+  </si>
+  <si>
+    <t>30306180240209</t>
+  </si>
+  <si>
+    <t>30409092401294</t>
+  </si>
+  <si>
+    <t>30601092401047</t>
+  </si>
+  <si>
+    <t>30405282400485</t>
+  </si>
+  <si>
+    <t>30507282402078</t>
+  </si>
+  <si>
+    <t>30502222402719</t>
+  </si>
+  <si>
+    <t>30410232403738</t>
+  </si>
+  <si>
+    <t>30506102403547</t>
+  </si>
+  <si>
+    <t>30508042403286</t>
+  </si>
+  <si>
+    <t>30508102403906</t>
+  </si>
+  <si>
+    <t>30501112401753</t>
+  </si>
+  <si>
+    <t>30401172404137</t>
+  </si>
+  <si>
+    <t>30510012414571</t>
+  </si>
+  <si>
+    <t>30511032402797</t>
+  </si>
+  <si>
+    <t>30509092402635</t>
+  </si>
+  <si>
+    <t>30509012413232</t>
+  </si>
+  <si>
+    <t>30302192400199</t>
+  </si>
+  <si>
+    <t>30601042400775</t>
+  </si>
+  <si>
+    <t>30601202402125</t>
+  </si>
+  <si>
+    <t>30502122403092</t>
+  </si>
+  <si>
+    <t>30406262403999</t>
+  </si>
+  <si>
+    <t>30411232402932</t>
+  </si>
+  <si>
+    <t>30501182401416</t>
+  </si>
+  <si>
+    <t>30411022403294</t>
+  </si>
+  <si>
+    <t>30404042404274</t>
+  </si>
+  <si>
+    <t>30510142402095</t>
+  </si>
+  <si>
+    <t>30511222403293</t>
+  </si>
+  <si>
+    <t>30505012408799</t>
+  </si>
+  <si>
+    <t>30504072402165</t>
+  </si>
+  <si>
+    <t>30512172400987</t>
+  </si>
+  <si>
+    <t>30409202401317</t>
+  </si>
+  <si>
+    <t>30508082400786</t>
+  </si>
+  <si>
+    <t>30409132402388</t>
+  </si>
+  <si>
+    <t>30506012404439</t>
+  </si>
+  <si>
+    <t>30409172401635</t>
+  </si>
+  <si>
+    <t>30207202403938</t>
+  </si>
+  <si>
+    <t>30408052403573</t>
+  </si>
+  <si>
+    <t>30511302400457</t>
+  </si>
+  <si>
+    <t>,3050830240200</t>
+  </si>
+  <si>
+    <t>30502132402329</t>
+  </si>
+  <si>
+    <t>30510252403755</t>
+  </si>
+  <si>
+    <t>30512222403273</t>
+  </si>
+  <si>
+    <t>30510192404366</t>
+  </si>
+  <si>
+    <t>30301112403595</t>
+  </si>
+  <si>
+    <t>30408142401219</t>
+  </si>
+  <si>
+    <t>30511202402088</t>
+  </si>
+  <si>
+    <t>30508102405194</t>
+  </si>
+  <si>
+    <t>30408242240229</t>
+  </si>
+  <si>
+    <t>30506302400232</t>
+  </si>
+  <si>
+    <t>30203292401399</t>
+  </si>
+  <si>
+    <t>30501012409115</t>
+  </si>
+  <si>
+    <t>30512012406318</t>
+  </si>
+  <si>
+    <t>30211012412911</t>
+  </si>
+  <si>
+    <t>30510172402537</t>
+  </si>
+  <si>
+    <t>30304022400375</t>
+  </si>
+  <si>
+    <t>30312152402488</t>
+  </si>
+  <si>
+    <t>30502032400965</t>
+  </si>
+  <si>
+    <t>30411272404253</t>
+  </si>
+  <si>
+    <t>30502262402118</t>
+  </si>
+  <si>
+    <t>30406272401471</t>
+  </si>
+  <si>
+    <t>30511062403607</t>
+  </si>
+  <si>
+    <t>30511052402505</t>
+  </si>
+  <si>
+    <t>30410282401507</t>
+  </si>
+  <si>
+    <t>30510122400932</t>
+  </si>
+  <si>
+    <t>30603232402254</t>
+  </si>
+  <si>
+    <t>30404152402099</t>
+  </si>
+  <si>
+    <t>30411202405961</t>
+  </si>
+  <si>
+    <t>30509102401829</t>
+  </si>
+  <si>
+    <t>30510012422787</t>
+  </si>
+  <si>
+    <t>30510022400692</t>
+  </si>
+  <si>
+    <t>30507022403496</t>
+  </si>
+  <si>
+    <t>30507022403518</t>
+  </si>
+  <si>
+    <t>30509252401231</t>
+  </si>
+  <si>
+    <t>33040529240150</t>
+  </si>
+  <si>
+    <t>30505132400031</t>
+  </si>
+  <si>
+    <t>30602172400536</t>
+  </si>
+  <si>
+    <t>30409262400727</t>
+  </si>
+  <si>
+    <t>30505142403454</t>
+  </si>
+  <si>
+    <t>30504152400759</t>
+  </si>
+  <si>
+    <t>30505152403797</t>
+  </si>
+  <si>
+    <t>30407012403477</t>
+  </si>
+  <si>
+    <t>30505052405598</t>
+  </si>
+  <si>
+    <t>30508192400552</t>
+  </si>
+  <si>
+    <t>30209102406398</t>
+  </si>
+  <si>
+    <t>30504252401205</t>
+  </si>
+  <si>
+    <t>30512102404225</t>
+  </si>
+  <si>
+    <t>30403112401565</t>
+  </si>
+  <si>
+    <t>30502152402376</t>
+  </si>
+  <si>
+    <t>30509142400469</t>
+  </si>
+  <si>
+    <t>30102232400732</t>
+  </si>
+  <si>
+    <t>30312032402115</t>
+  </si>
+  <si>
+    <t>30312132403143</t>
+  </si>
+  <si>
+    <t>30404124024011</t>
+  </si>
+  <si>
+    <t>30303072402097</t>
+  </si>
+  <si>
+    <t>30405042403592</t>
+  </si>
+  <si>
+    <t>30511082403239</t>
+  </si>
+  <si>
+    <t>30510302401007</t>
+  </si>
+  <si>
+    <t>30507112400038</t>
+  </si>
+  <si>
+    <t>30408262402383</t>
+  </si>
+  <si>
+    <t>30505262402419</t>
+  </si>
+  <si>
+    <t>30410172404179</t>
+  </si>
+  <si>
+    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
+  </si>
+  <si>
+    <t>30512272400097</t>
+  </si>
+  <si>
+    <t>30510012412811</t>
+  </si>
+  <si>
+    <t>30310312400832</t>
+  </si>
+  <si>
+    <t>30404012410431</t>
+  </si>
+  <si>
+    <t>30412262402097</t>
+  </si>
+  <si>
+    <t>30411201403108</t>
+  </si>
+  <si>
+    <t>30504212402195</t>
+  </si>
+  <si>
+    <t>30509112403153</t>
+  </si>
+  <si>
+    <t>30602172400056</t>
+  </si>
+  <si>
+    <t>30401012422988</t>
+  </si>
+  <si>
+    <t>30211122402121</t>
+  </si>
+  <si>
+    <t>30511272400503</t>
+  </si>
+  <si>
+    <t>30603052400636</t>
+  </si>
+  <si>
+    <t>30406222401055</t>
+  </si>
+  <si>
+    <t>30205152403718</t>
+  </si>
+  <si>
+    <t>30601172402745</t>
+  </si>
+  <si>
+    <t>30304010400698</t>
+  </si>
+  <si>
+    <t>30510252406355</t>
+  </si>
+  <si>
+    <t>30503012410936</t>
+  </si>
+  <si>
+    <t>30506282400915</t>
+  </si>
+  <si>
+    <t>30506012405141</t>
+  </si>
+  <si>
+    <t>30512012410072</t>
+  </si>
+  <si>
+    <t>30411202405791</t>
+  </si>
+  <si>
+    <t>30506082400619</t>
+  </si>
+  <si>
+    <t>30507252403118</t>
+  </si>
+  <si>
     <t>30407012407316</t>
   </si>
   <si>
-    <t>30511242400908</t>
-  </si>
-  <si>
-    <t>30406132403474</t>
-  </si>
-  <si>
-    <t>30306180240209</t>
-  </si>
-  <si>
-    <t>30409092401294</t>
-  </si>
-  <si>
-    <t>30601092401047</t>
-  </si>
-  <si>
-    <t>30405282400485</t>
-  </si>
-  <si>
-    <t>30507282402078</t>
-  </si>
-  <si>
-    <t>30502222402719</t>
-  </si>
-  <si>
-    <t>30410232403738</t>
-  </si>
-  <si>
-    <t>30506102403547</t>
-  </si>
-  <si>
-    <t>30508042403286</t>
-  </si>
-  <si>
-    <t>30508102403906</t>
-  </si>
-  <si>
-    <t>30501112401753</t>
-  </si>
-  <si>
-    <t>30401172404137</t>
-  </si>
-  <si>
-    <t>30510012414571</t>
-  </si>
-  <si>
-    <t>30511032402797</t>
-  </si>
-  <si>
-    <t>30509092402635</t>
-  </si>
-  <si>
-    <t>30509012413232</t>
-  </si>
-  <si>
-    <t>30302192400199</t>
-  </si>
-  <si>
-    <t>30601042400775</t>
-  </si>
-  <si>
-    <t>30601202402125</t>
-  </si>
-  <si>
-    <t>30502122403092</t>
-  </si>
-  <si>
-    <t>30406262403999</t>
-  </si>
-  <si>
-    <t>30411232402932</t>
-  </si>
-  <si>
-    <t>30501182401416</t>
-  </si>
-  <si>
-    <t>30411022403294</t>
-  </si>
-  <si>
-    <t>30404042404274</t>
-  </si>
-  <si>
-    <t>30510142402095</t>
-  </si>
-  <si>
-    <t>30511222403293</t>
-  </si>
-  <si>
-    <t>30505012408799</t>
-  </si>
-  <si>
-    <t>30504072402165</t>
-  </si>
-  <si>
-    <t>30512172400987</t>
-  </si>
-  <si>
-    <t>30409202401317</t>
-  </si>
-  <si>
-    <t>30508082400786</t>
-  </si>
-  <si>
-    <t>30409132402388</t>
-  </si>
-  <si>
-    <t>30506012404439</t>
-  </si>
-  <si>
-    <t>30409172401635</t>
-  </si>
-  <si>
-    <t>30207202403938</t>
-  </si>
-  <si>
-    <t>30408052403573</t>
-  </si>
-  <si>
-    <t>30511302400457</t>
-  </si>
-  <si>
-    <t>,3050830240200</t>
-  </si>
-  <si>
-    <t>30502132402329</t>
-  </si>
-  <si>
-    <t>30510252403755</t>
-  </si>
-  <si>
-    <t>30512222403273</t>
-  </si>
-  <si>
-    <t>30510192404366</t>
-  </si>
-  <si>
-    <t>30301112403595</t>
-  </si>
-  <si>
-    <t>30408142401219</t>
-  </si>
-  <si>
-    <t>30511202402088</t>
-  </si>
-  <si>
-    <t>30508102405194</t>
-  </si>
-  <si>
-    <t>30408242240229</t>
-  </si>
-  <si>
-    <t>30506302400232</t>
-  </si>
-  <si>
-    <t>30203292401399</t>
-  </si>
-  <si>
-    <t>30501012409115</t>
-  </si>
-  <si>
-    <t>30512012406318</t>
-  </si>
-  <si>
-    <t>30211012412911</t>
-  </si>
-  <si>
-    <t>30510172402537</t>
-  </si>
-  <si>
-    <t>30304022400375</t>
-  </si>
-  <si>
-    <t>30312152402488</t>
-  </si>
-  <si>
-    <t>30502032400965</t>
-  </si>
-  <si>
-    <t>30411272404253</t>
-  </si>
-  <si>
-    <t>30502262402118</t>
-  </si>
-  <si>
-    <t>30406272401471</t>
-  </si>
-  <si>
-    <t>30511062403607</t>
-  </si>
-  <si>
-    <t>30511052402505</t>
-  </si>
-  <si>
-    <t>30410282401507</t>
-  </si>
-  <si>
-    <t>30510122400932</t>
-  </si>
-  <si>
-    <t>30603232402254</t>
-  </si>
-  <si>
-    <t>30404152402099</t>
-  </si>
-  <si>
-    <t>30411202405961</t>
-  </si>
-  <si>
-    <t>30509102401829</t>
-  </si>
-  <si>
-    <t>30510012422787</t>
-  </si>
-  <si>
-    <t>30510022400692</t>
-  </si>
-  <si>
-    <t>30507022403496</t>
-  </si>
-  <si>
-    <t>30507022403518</t>
-  </si>
-  <si>
-    <t>30509252401231</t>
-  </si>
-  <si>
-    <t>33040529240150</t>
-  </si>
-  <si>
-    <t>30505132400031</t>
-  </si>
-  <si>
-    <t>30602172400536</t>
-  </si>
-  <si>
-    <t>30409262400727</t>
-  </si>
-  <si>
-    <t>30505142403454</t>
-  </si>
-  <si>
-    <t>30504152400759</t>
-  </si>
-  <si>
-    <t>30505152403797</t>
-  </si>
-  <si>
-    <t>30407012403477</t>
-  </si>
-  <si>
-    <t>30505052405598</t>
-  </si>
-  <si>
-    <t>30508192400552</t>
-  </si>
-  <si>
-    <t>30209102406398</t>
-  </si>
-  <si>
-    <t>30504252401205</t>
-  </si>
-  <si>
-    <t>30512102404225</t>
-  </si>
-  <si>
-    <t>30403112401565</t>
-  </si>
-  <si>
-    <t>30502152402376</t>
-  </si>
-  <si>
-    <t>30509142400469</t>
-  </si>
-  <si>
-    <t>30102232400732</t>
-  </si>
-  <si>
-    <t>30312032402115</t>
-  </si>
-  <si>
-    <t>30312132403143</t>
-  </si>
-  <si>
-    <t>30404124024011</t>
-  </si>
-  <si>
-    <t>30303072402097</t>
-  </si>
-  <si>
-    <t>30405042403592</t>
-  </si>
-  <si>
-    <t>30511082403239</t>
-  </si>
-  <si>
-    <t>30510302401007</t>
-  </si>
-  <si>
-    <t>30507112400038</t>
-  </si>
-  <si>
-    <t>30408262402383</t>
-  </si>
-  <si>
-    <t>30505262402419</t>
-  </si>
-  <si>
-    <t>30410172404179</t>
-  </si>
-  <si>
-    <t>٣٠٥٠٦١٧٢٤٠١٤٠١</t>
-  </si>
-  <si>
-    <t>30512272400097</t>
-  </si>
-  <si>
-    <t>30510012412811</t>
-  </si>
-  <si>
-    <t>30310312400832</t>
-  </si>
-  <si>
-    <t>30404012410431</t>
-  </si>
-  <si>
-    <t>30412262402097</t>
-  </si>
-  <si>
-    <t>30411201403108</t>
-  </si>
-  <si>
-    <t>30504212402195</t>
-  </si>
-  <si>
-    <t>30509112403153</t>
-  </si>
-  <si>
-    <t>30602172400056</t>
-  </si>
-  <si>
-    <t>30401012422988</t>
-  </si>
-  <si>
-    <t>30211122402121</t>
-  </si>
-  <si>
-    <t>30511272400503</t>
-  </si>
-  <si>
-    <t>30603052400636</t>
-  </si>
-  <si>
-    <t>30406222401055</t>
-  </si>
-  <si>
-    <t>30205152403718</t>
-  </si>
-  <si>
-    <t>30601172402745</t>
-  </si>
-  <si>
-    <t>30304010400698</t>
-  </si>
-  <si>
-    <t>30510252406355</t>
-  </si>
-  <si>
-    <t>30503012410936</t>
-  </si>
-  <si>
-    <t>30506282400915</t>
-  </si>
-  <si>
-    <t>30506012405141</t>
-  </si>
-  <si>
-    <t>30512012410072</t>
-  </si>
-  <si>
-    <t>30411202405791</t>
-  </si>
-  <si>
-    <t>30506082400619</t>
-  </si>
-  <si>
-    <t>30507252403118</t>
-  </si>
-  <si>
     <t>1127169056</t>
   </si>
   <si>
@@ -3316,394 +3316,394 @@
     <t>01150905692</t>
   </si>
   <si>
+    <t>01119364560</t>
+  </si>
+  <si>
+    <t>01114623756</t>
+  </si>
+  <si>
+    <t>01110180758</t>
+  </si>
+  <si>
+    <t>01098408936</t>
+  </si>
+  <si>
+    <t>01026439570</t>
+  </si>
+  <si>
+    <t>01037905359</t>
+  </si>
+  <si>
+    <t>01152609738</t>
+  </si>
+  <si>
+    <t>01012099267</t>
+  </si>
+  <si>
+    <t>01015294024</t>
+  </si>
+  <si>
+    <t>01272195817</t>
+  </si>
+  <si>
+    <t>01107541208</t>
+  </si>
+  <si>
+    <t>01027416150</t>
+  </si>
+  <si>
+    <t>01018746100</t>
+  </si>
+  <si>
+    <t>0109875241</t>
+  </si>
+  <si>
+    <t>1015062236</t>
+  </si>
+  <si>
+    <t>01029523988</t>
+  </si>
+  <si>
+    <t>01098585465</t>
+  </si>
+  <si>
+    <t>01095026407</t>
+  </si>
+  <si>
+    <t>01143412109</t>
+  </si>
+  <si>
+    <t>01157954761</t>
+  </si>
+  <si>
+    <t>01065277226</t>
+  </si>
+  <si>
+    <t>01080800884</t>
+  </si>
+  <si>
+    <t>01142897678</t>
+  </si>
+  <si>
+    <t>01153303914</t>
+  </si>
+  <si>
+    <t>01028612071</t>
+  </si>
+  <si>
+    <t>01101630321</t>
+  </si>
+  <si>
+    <t>02002075332</t>
+  </si>
+  <si>
+    <t>01100828140</t>
+  </si>
+  <si>
+    <t>01091924482</t>
+  </si>
+  <si>
+    <t>01110343713</t>
+  </si>
+  <si>
+    <t>01019603879</t>
+  </si>
+  <si>
+    <t>0111506743</t>
+  </si>
+  <si>
+    <t>01113779655</t>
+  </si>
+  <si>
+    <t>01063947688</t>
+  </si>
+  <si>
+    <t>01027089578</t>
+  </si>
+  <si>
+    <t>01149691630</t>
+  </si>
+  <si>
+    <t>01117606742</t>
+  </si>
+  <si>
+    <t>01114229055</t>
+  </si>
+  <si>
+    <t>01004964401</t>
+  </si>
+  <si>
+    <t>01050946387</t>
+  </si>
+  <si>
+    <t>01207696518</t>
+  </si>
+  <si>
+    <t>01062259734</t>
+  </si>
+  <si>
+    <t>01003284398</t>
+  </si>
+  <si>
+    <t>01008492654</t>
+  </si>
+  <si>
+    <t>01018849692</t>
+  </si>
+  <si>
+    <t>01028898127</t>
+  </si>
+  <si>
+    <t>01028909643</t>
+  </si>
+  <si>
+    <t>01029553675</t>
+  </si>
+  <si>
+    <t>01109064377</t>
+  </si>
+  <si>
+    <t>10115204570</t>
+  </si>
+  <si>
+    <t>01060965304</t>
+  </si>
+  <si>
+    <t>01289037098</t>
+  </si>
+  <si>
+    <t>01023254856</t>
+  </si>
+  <si>
+    <t>01148979466</t>
+  </si>
+  <si>
+    <t>01099427041</t>
+  </si>
+  <si>
+    <t>01101887554</t>
+  </si>
+  <si>
+    <t>01007083957</t>
+  </si>
+  <si>
+    <t>01113164297</t>
+  </si>
+  <si>
+    <t>01009364380</t>
+  </si>
+  <si>
+    <t>01281744500</t>
+  </si>
+  <si>
+    <t>01021898375</t>
+  </si>
+  <si>
+    <t>01008574990</t>
+  </si>
+  <si>
+    <t>01039109316</t>
+  </si>
+  <si>
+    <t>01148497118</t>
+  </si>
+  <si>
+    <t>01145232053</t>
+  </si>
+  <si>
+    <t>01143236848</t>
+  </si>
+  <si>
+    <t>01156603899</t>
+  </si>
+  <si>
+    <t>01129751356</t>
+  </si>
+  <si>
+    <t>01060389442</t>
+  </si>
+  <si>
+    <t>01067724736</t>
+  </si>
+  <si>
+    <t>01065745021</t>
+  </si>
+  <si>
+    <t>01060210319</t>
+  </si>
+  <si>
+    <t>01155904991</t>
+  </si>
+  <si>
+    <t>01155910557</t>
+  </si>
+  <si>
+    <t>01120018147</t>
+  </si>
+  <si>
+    <t>01080987405</t>
+  </si>
+  <si>
+    <t>01067941115</t>
+  </si>
+  <si>
+    <t>01027937552</t>
+  </si>
+  <si>
+    <t>01201603004</t>
+  </si>
+  <si>
+    <t>01159358898</t>
+  </si>
+  <si>
+    <t>01129974304</t>
+  </si>
+  <si>
+    <t>01113132202</t>
+  </si>
+  <si>
+    <t>01012291526</t>
+  </si>
+  <si>
+    <t>01062803660</t>
+  </si>
+  <si>
+    <t>01067089320</t>
+  </si>
+  <si>
+    <t>01553863411</t>
+  </si>
+  <si>
+    <t>01060458756</t>
+  </si>
+  <si>
+    <t>01010934419</t>
+  </si>
+  <si>
+    <t>01062817717</t>
+  </si>
+  <si>
+    <t>01012090499</t>
+  </si>
+  <si>
+    <t>01117927379</t>
+  </si>
+  <si>
+    <t>01279747878</t>
+  </si>
+  <si>
+    <t>01116308543</t>
+  </si>
+  <si>
+    <t>01092965157</t>
+  </si>
+  <si>
+    <t>01016307491</t>
+  </si>
+  <si>
+    <t>01114113833</t>
+  </si>
+  <si>
+    <t>01208634063</t>
+  </si>
+  <si>
+    <t>01007937368</t>
+  </si>
+  <si>
+    <t>01152380733</t>
+  </si>
+  <si>
+    <t>01210721472</t>
+  </si>
+  <si>
+    <t>01091007624</t>
+  </si>
+  <si>
+    <t>01097432947</t>
+  </si>
+  <si>
+    <t>01274410607</t>
+  </si>
+  <si>
+    <t>01025790469</t>
+  </si>
+  <si>
+    <t>01157718533</t>
+  </si>
+  <si>
+    <t>01142212131</t>
+  </si>
+  <si>
+    <t>01020592062</t>
+  </si>
+  <si>
+    <t>01107909098</t>
+  </si>
+  <si>
+    <t>01121846011</t>
+  </si>
+  <si>
+    <t>01080345257</t>
+  </si>
+  <si>
+    <t>01140717605</t>
+  </si>
+  <si>
+    <t>01006926646</t>
+  </si>
+  <si>
+    <t>01551488731</t>
+  </si>
+  <si>
+    <t>01126693628</t>
+  </si>
+  <si>
+    <t>01112511010</t>
+  </si>
+  <si>
+    <t>01063495341</t>
+  </si>
+  <si>
+    <t>01200941594</t>
+  </si>
+  <si>
+    <t>01100086115</t>
+  </si>
+  <si>
+    <t>01025520618</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0101966776</t>
+  </si>
+  <si>
+    <t>01095305700</t>
+  </si>
+  <si>
+    <t>01008063893</t>
+  </si>
+  <si>
+    <t>01154202604</t>
+  </si>
+  <si>
+    <t>01156509914</t>
+  </si>
+  <si>
+    <t>01120137745</t>
+  </si>
+  <si>
+    <t>01033989631</t>
+  </si>
+  <si>
+    <t>01156096723</t>
+  </si>
+  <si>
+    <t>01012467272</t>
+  </si>
+  <si>
+    <t>01274116321</t>
+  </si>
+  <si>
     <t>01028993616</t>
-  </si>
-  <si>
-    <t>01119364560</t>
-  </si>
-  <si>
-    <t>01114623756</t>
-  </si>
-  <si>
-    <t>01110180758</t>
-  </si>
-  <si>
-    <t>01098408936</t>
-  </si>
-  <si>
-    <t>01026439570</t>
-  </si>
-  <si>
-    <t>01037905359</t>
-  </si>
-  <si>
-    <t>01152609738</t>
-  </si>
-  <si>
-    <t>01012099267</t>
-  </si>
-  <si>
-    <t>01015294024</t>
-  </si>
-  <si>
-    <t>01272195817</t>
-  </si>
-  <si>
-    <t>01107541208</t>
-  </si>
-  <si>
-    <t>01027416150</t>
-  </si>
-  <si>
-    <t>01018746100</t>
-  </si>
-  <si>
-    <t>0109875241</t>
-  </si>
-  <si>
-    <t>1015062236</t>
-  </si>
-  <si>
-    <t>01029523988</t>
-  </si>
-  <si>
-    <t>01098585465</t>
-  </si>
-  <si>
-    <t>01095026407</t>
-  </si>
-  <si>
-    <t>01143412109</t>
-  </si>
-  <si>
-    <t>01157954761</t>
-  </si>
-  <si>
-    <t>01065277226</t>
-  </si>
-  <si>
-    <t>01080800884</t>
-  </si>
-  <si>
-    <t>01142897678</t>
-  </si>
-  <si>
-    <t>01153303914</t>
-  </si>
-  <si>
-    <t>01028612071</t>
-  </si>
-  <si>
-    <t>01101630321</t>
-  </si>
-  <si>
-    <t>02002075332</t>
-  </si>
-  <si>
-    <t>01100828140</t>
-  </si>
-  <si>
-    <t>01091924482</t>
-  </si>
-  <si>
-    <t>01110343713</t>
-  </si>
-  <si>
-    <t>01019603879</t>
-  </si>
-  <si>
-    <t>0111506743</t>
-  </si>
-  <si>
-    <t>01113779655</t>
-  </si>
-  <si>
-    <t>01063947688</t>
-  </si>
-  <si>
-    <t>01027089578</t>
-  </si>
-  <si>
-    <t>01149691630</t>
-  </si>
-  <si>
-    <t>01117606742</t>
-  </si>
-  <si>
-    <t>01114229055</t>
-  </si>
-  <si>
-    <t>01004964401</t>
-  </si>
-  <si>
-    <t>01050946387</t>
-  </si>
-  <si>
-    <t>01207696518</t>
-  </si>
-  <si>
-    <t>01062259734</t>
-  </si>
-  <si>
-    <t>01003284398</t>
-  </si>
-  <si>
-    <t>01008492654</t>
-  </si>
-  <si>
-    <t>01018849692</t>
-  </si>
-  <si>
-    <t>01028898127</t>
-  </si>
-  <si>
-    <t>01028909643</t>
-  </si>
-  <si>
-    <t>01029553675</t>
-  </si>
-  <si>
-    <t>01109064377</t>
-  </si>
-  <si>
-    <t>10115204570</t>
-  </si>
-  <si>
-    <t>01060965304</t>
-  </si>
-  <si>
-    <t>01289037098</t>
-  </si>
-  <si>
-    <t>01023254856</t>
-  </si>
-  <si>
-    <t>01148979466</t>
-  </si>
-  <si>
-    <t>01099427041</t>
-  </si>
-  <si>
-    <t>01101887554</t>
-  </si>
-  <si>
-    <t>01007083957</t>
-  </si>
-  <si>
-    <t>01113164297</t>
-  </si>
-  <si>
-    <t>01009364380</t>
-  </si>
-  <si>
-    <t>01281744500</t>
-  </si>
-  <si>
-    <t>01021898375</t>
-  </si>
-  <si>
-    <t>01008574990</t>
-  </si>
-  <si>
-    <t>01039109316</t>
-  </si>
-  <si>
-    <t>01148497118</t>
-  </si>
-  <si>
-    <t>01145232053</t>
-  </si>
-  <si>
-    <t>01143236848</t>
-  </si>
-  <si>
-    <t>01156603899</t>
-  </si>
-  <si>
-    <t>01129751356</t>
-  </si>
-  <si>
-    <t>01060389442</t>
-  </si>
-  <si>
-    <t>01067724736</t>
-  </si>
-  <si>
-    <t>01065745021</t>
-  </si>
-  <si>
-    <t>01060210319</t>
-  </si>
-  <si>
-    <t>01155904991</t>
-  </si>
-  <si>
-    <t>01155910557</t>
-  </si>
-  <si>
-    <t>01120018147</t>
-  </si>
-  <si>
-    <t>01080987405</t>
-  </si>
-  <si>
-    <t>01067941115</t>
-  </si>
-  <si>
-    <t>01027937552</t>
-  </si>
-  <si>
-    <t>01201603004</t>
-  </si>
-  <si>
-    <t>01159358898</t>
-  </si>
-  <si>
-    <t>01129974304</t>
-  </si>
-  <si>
-    <t>01113132202</t>
-  </si>
-  <si>
-    <t>01012291526</t>
-  </si>
-  <si>
-    <t>01062803660</t>
-  </si>
-  <si>
-    <t>01067089320</t>
-  </si>
-  <si>
-    <t>01553863411</t>
-  </si>
-  <si>
-    <t>01060458756</t>
-  </si>
-  <si>
-    <t>01010934419</t>
-  </si>
-  <si>
-    <t>01062817717</t>
-  </si>
-  <si>
-    <t>01012090499</t>
-  </si>
-  <si>
-    <t>01117927379</t>
-  </si>
-  <si>
-    <t>01279747878</t>
-  </si>
-  <si>
-    <t>01116308543</t>
-  </si>
-  <si>
-    <t>01092965157</t>
-  </si>
-  <si>
-    <t>01016307491</t>
-  </si>
-  <si>
-    <t>01114113833</t>
-  </si>
-  <si>
-    <t>01208634063</t>
-  </si>
-  <si>
-    <t>01007937368</t>
-  </si>
-  <si>
-    <t>01152380733</t>
-  </si>
-  <si>
-    <t>01210721472</t>
-  </si>
-  <si>
-    <t>01091007624</t>
-  </si>
-  <si>
-    <t>01097432947</t>
-  </si>
-  <si>
-    <t>01274410607</t>
-  </si>
-  <si>
-    <t>01025790469</t>
-  </si>
-  <si>
-    <t>01157718533</t>
-  </si>
-  <si>
-    <t>01142212131</t>
-  </si>
-  <si>
-    <t>01020592062</t>
-  </si>
-  <si>
-    <t>01107909098</t>
-  </si>
-  <si>
-    <t>01121846011</t>
-  </si>
-  <si>
-    <t>01080345257</t>
-  </si>
-  <si>
-    <t>01140717605</t>
-  </si>
-  <si>
-    <t>01006926646</t>
-  </si>
-  <si>
-    <t>01551488731</t>
-  </si>
-  <si>
-    <t>01126693628</t>
-  </si>
-  <si>
-    <t>01112511010</t>
-  </si>
-  <si>
-    <t>01063495341</t>
-  </si>
-  <si>
-    <t>01200941594</t>
-  </si>
-  <si>
-    <t>01100086115</t>
-  </si>
-  <si>
-    <t>01025520618</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0101966776</t>
-  </si>
-  <si>
-    <t>01095305700</t>
-  </si>
-  <si>
-    <t>01008063893</t>
-  </si>
-  <si>
-    <t>01154202604</t>
-  </si>
-  <si>
-    <t>01156509914</t>
-  </si>
-  <si>
-    <t>01120137745</t>
-  </si>
-  <si>
-    <t>01033989631</t>
-  </si>
-  <si>
-    <t>01156096723</t>
-  </si>
-  <si>
-    <t>01012467272</t>
-  </si>
-  <si>
-    <t>01274116321</t>
   </si>
   <si>
     <t>1353</t>
@@ -17449,34 +17449,34 @@
         <v>1100</v>
       </c>
       <c r="D278" t="s">
-        <v>1277</v>
+        <v>1303</v>
       </c>
       <c r="E278" t="s">
-        <v>1472</v>
+        <v>1498</v>
       </c>
       <c r="F278" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G278" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="H278" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I278" t="s">
         <v>1631</v>
       </c>
       <c r="J278" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="K278" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="L278" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="M278" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="N278" t="s">
         <v>1633</v>
@@ -17493,34 +17493,34 @@
         <v>1101</v>
       </c>
       <c r="D279" t="s">
-        <v>1303</v>
+        <v>1241</v>
       </c>
       <c r="E279" t="s">
-        <v>1498</v>
+        <v>1436</v>
       </c>
       <c r="F279" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G279" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="H279" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="I279" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="J279" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="K279" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="L279" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M279" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N279" t="s">
         <v>1633</v>
@@ -17537,10 +17537,10 @@
         <v>1102</v>
       </c>
       <c r="D280" t="s">
-        <v>1241</v>
+        <v>1342</v>
       </c>
       <c r="E280" t="s">
-        <v>1436</v>
+        <v>1537</v>
       </c>
       <c r="F280" t="s">
         <v>1620</v>
@@ -17558,13 +17558,13 @@
         <v>1627</v>
       </c>
       <c r="K280" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="L280" t="s">
         <v>1630</v>
       </c>
       <c r="M280" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N280" t="s">
         <v>1633</v>
@@ -17581,10 +17581,10 @@
         <v>1103</v>
       </c>
       <c r="D281" t="s">
-        <v>1342</v>
+        <v>1385</v>
       </c>
       <c r="E281" t="s">
-        <v>1537</v>
+        <v>1580</v>
       </c>
       <c r="F281" t="s">
         <v>1620</v>
@@ -17593,19 +17593,19 @@
         <v>1626</v>
       </c>
       <c r="H281" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I281" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J281" t="s">
         <v>1627</v>
       </c>
       <c r="K281" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L281" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M281" t="s">
         <v>1628</v>
@@ -17625,13 +17625,13 @@
         <v>1104</v>
       </c>
       <c r="D282" t="s">
-        <v>1385</v>
+        <v>1246</v>
       </c>
       <c r="E282" t="s">
-        <v>1580</v>
+        <v>1441</v>
       </c>
       <c r="F282" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G282" t="s">
         <v>1626</v>
@@ -17643,16 +17643,16 @@
         <v>1632</v>
       </c>
       <c r="J282" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K282" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L282" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="M282" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N282" t="s">
         <v>1633</v>
@@ -17669,13 +17669,13 @@
         <v>1105</v>
       </c>
       <c r="D283" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="E283" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="F283" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G283" t="s">
         <v>1626</v>
@@ -17687,16 +17687,16 @@
         <v>1632</v>
       </c>
       <c r="J283" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K283" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L283" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="M283" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N283" t="s">
         <v>1633</v>
@@ -17713,34 +17713,34 @@
         <v>1106</v>
       </c>
       <c r="D284" t="s">
-        <v>1252</v>
+        <v>1336</v>
       </c>
       <c r="E284" t="s">
-        <v>1447</v>
+        <v>1531</v>
       </c>
       <c r="F284" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G284" t="s">
         <v>1626</v>
       </c>
       <c r="H284" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I284" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="J284" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="K284" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="L284" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="M284" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N284" t="s">
         <v>1633</v>
@@ -17757,19 +17757,19 @@
         <v>1107</v>
       </c>
       <c r="D285" t="s">
-        <v>1336</v>
+        <v>1386</v>
       </c>
       <c r="E285" t="s">
-        <v>1531</v>
+        <v>1581</v>
       </c>
       <c r="F285" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G285" t="s">
         <v>1626</v>
       </c>
       <c r="H285" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="I285" t="s">
         <v>1628</v>
@@ -17778,7 +17778,7 @@
         <v>1632</v>
       </c>
       <c r="K285" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="L285" t="s">
         <v>1631</v>
@@ -17801,34 +17801,34 @@
         <v>1108</v>
       </c>
       <c r="D286" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="E286" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="F286" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G286" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H286" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="I286" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="J286" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="K286" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="L286" t="s">
         <v>1631</v>
       </c>
       <c r="M286" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="N286" t="s">
         <v>1633</v>
@@ -17845,34 +17845,34 @@
         <v>1109</v>
       </c>
       <c r="D287" t="s">
-        <v>1387</v>
+        <v>1261</v>
       </c>
       <c r="E287" t="s">
-        <v>1582</v>
+        <v>1456</v>
       </c>
       <c r="F287" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="G287" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H287" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="I287" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="J287" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="K287" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="L287" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M287" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="N287" t="s">
         <v>1633</v>
@@ -17889,31 +17889,31 @@
         <v>1110</v>
       </c>
       <c r="D288" t="s">
-        <v>1261</v>
+        <v>1311</v>
       </c>
       <c r="E288" t="s">
-        <v>1456</v>
+        <v>1506</v>
       </c>
       <c r="F288" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G288" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H288" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I288" t="s">
         <v>1632</v>
       </c>
       <c r="J288" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K288" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="L288" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M288" t="s">
         <v>1628</v>
@@ -17933,28 +17933,28 @@
         <v>1111</v>
       </c>
       <c r="D289" t="s">
-        <v>1311</v>
+        <v>1330</v>
       </c>
       <c r="E289" t="s">
-        <v>1506</v>
+        <v>1525</v>
       </c>
       <c r="F289" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G289" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H289" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="I289" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J289" t="s">
         <v>1630</v>
       </c>
       <c r="K289" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="L289" t="s">
         <v>1631</v>
@@ -17977,34 +17977,34 @@
         <v>1112</v>
       </c>
       <c r="D290" t="s">
-        <v>1330</v>
+        <v>1342</v>
       </c>
       <c r="E290" t="s">
-        <v>1525</v>
+        <v>1537</v>
       </c>
       <c r="F290" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G290" t="s">
         <v>1626</v>
       </c>
       <c r="H290" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="I290" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="J290" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="K290" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L290" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M290" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="N290" t="s">
         <v>1633</v>
@@ -18021,13 +18021,13 @@
         <v>1113</v>
       </c>
       <c r="D291" t="s">
-        <v>1342</v>
+        <v>1363</v>
       </c>
       <c r="E291" t="s">
-        <v>1537</v>
+        <v>1558</v>
       </c>
       <c r="F291" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G291" t="s">
         <v>1626</v>
@@ -18036,19 +18036,19 @@
         <v>1632</v>
       </c>
       <c r="I291" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="J291" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="K291" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L291" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="M291" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="N291" t="s">
         <v>1633</v>
@@ -18065,10 +18065,10 @@
         <v>1114</v>
       </c>
       <c r="D292" t="s">
-        <v>1363</v>
+        <v>1278</v>
       </c>
       <c r="E292" t="s">
-        <v>1558</v>
+        <v>1473</v>
       </c>
       <c r="F292" t="s">
         <v>1621</v>
@@ -18080,19 +18080,19 @@
         <v>1632</v>
       </c>
       <c r="I292" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="J292" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="K292" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L292" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M292" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="N292" t="s">
         <v>1633</v>
@@ -18109,13 +18109,13 @@
         <v>1115</v>
       </c>
       <c r="D293" t="s">
-        <v>1278</v>
+        <v>1293</v>
       </c>
       <c r="E293" t="s">
-        <v>1473</v>
+        <v>1488</v>
       </c>
       <c r="F293" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G293" t="s">
         <v>1626</v>
@@ -18124,10 +18124,10 @@
         <v>1632</v>
       </c>
       <c r="I293" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="J293" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="K293" t="s">
         <v>1631</v>
@@ -18153,10 +18153,10 @@
         <v>1116</v>
       </c>
       <c r="D294" t="s">
-        <v>1293</v>
+        <v>1388</v>
       </c>
       <c r="E294" t="s">
-        <v>1488</v>
+        <v>1583</v>
       </c>
       <c r="F294" t="s">
         <v>1620</v>
@@ -18165,22 +18165,22 @@
         <v>1626</v>
       </c>
       <c r="H294" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I294" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J294" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="K294" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L294" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M294" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="N294" t="s">
         <v>1633</v>
@@ -18197,34 +18197,34 @@
         <v>1117</v>
       </c>
       <c r="D295" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E295" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="F295" t="s">
         <v>1620</v>
       </c>
       <c r="G295" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H295" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I295" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="J295" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K295" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L295" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M295" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="N295" t="s">
         <v>1633</v>
@@ -18241,10 +18241,10 @@
         <v>1118</v>
       </c>
       <c r="D296" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="E296" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="F296" t="s">
         <v>1620</v>
@@ -18285,34 +18285,34 @@
         <v>1119</v>
       </c>
       <c r="D297" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="E297" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="F297" t="s">
         <v>1620</v>
       </c>
       <c r="G297" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H297" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I297" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="J297" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="K297" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L297" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="M297" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="N297" t="s">
         <v>1633</v>
@@ -18329,34 +18329,34 @@
         <v>1120</v>
       </c>
       <c r="D298" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="E298" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F298" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G298" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H298" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I298" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J298" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K298" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L298" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M298" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N298" t="s">
         <v>1633</v>
@@ -18373,34 +18373,34 @@
         <v>1121</v>
       </c>
       <c r="D299" t="s">
-        <v>1392</v>
+        <v>1360</v>
       </c>
       <c r="E299" t="s">
-        <v>1587</v>
+        <v>1555</v>
       </c>
       <c r="F299" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="G299" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H299" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I299" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J299" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="K299" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L299" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="M299" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="N299" t="s">
         <v>1633</v>
@@ -18417,13 +18417,13 @@
         <v>1122</v>
       </c>
       <c r="D300" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="E300" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
       <c r="F300" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G300" t="s">
         <v>1626</v>
@@ -18438,13 +18438,13 @@
         <v>1628</v>
       </c>
       <c r="K300" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L300" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M300" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="N300" t="s">
         <v>1633</v>
@@ -18461,34 +18461,34 @@
         <v>1123</v>
       </c>
       <c r="D301" t="s">
-        <v>1366</v>
+        <v>1393</v>
       </c>
       <c r="E301" t="s">
-        <v>1561</v>
+        <v>1588</v>
       </c>
       <c r="F301" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G301" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H301" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I301" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="J301" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="K301" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L301" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="M301" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N301" t="s">
         <v>1633</v>
@@ -18505,34 +18505,34 @@
         <v>1124</v>
       </c>
       <c r="D302" t="s">
-        <v>1393</v>
+        <v>1359</v>
       </c>
       <c r="E302" t="s">
-        <v>1588</v>
+        <v>1554</v>
       </c>
       <c r="F302" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G302" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H302" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="I302" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="J302" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="K302" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="L302" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="M302" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N302" t="s">
         <v>1633</v>
@@ -18549,34 +18549,34 @@
         <v>1125</v>
       </c>
       <c r="D303" t="s">
-        <v>1359</v>
+        <v>1274</v>
       </c>
       <c r="E303" t="s">
-        <v>1554</v>
+        <v>1469</v>
       </c>
       <c r="F303" t="s">
         <v>1621</v>
       </c>
       <c r="G303" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H303" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="I303" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="J303" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="K303" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="L303" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M303" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="N303" t="s">
         <v>1633</v>
@@ -18593,34 +18593,34 @@
         <v>1126</v>
       </c>
       <c r="D304" t="s">
-        <v>1274</v>
+        <v>1308</v>
       </c>
       <c r="E304" t="s">
-        <v>1469</v>
+        <v>1503</v>
       </c>
       <c r="F304" t="s">
         <v>1621</v>
       </c>
       <c r="G304" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H304" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I304" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="J304" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="K304" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L304" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="M304" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="N304" t="s">
         <v>1633</v>
@@ -18637,34 +18637,34 @@
         <v>1127</v>
       </c>
       <c r="D305" t="s">
-        <v>1308</v>
+        <v>1336</v>
       </c>
       <c r="E305" t="s">
-        <v>1503</v>
+        <v>1531</v>
       </c>
       <c r="F305" t="s">
         <v>1621</v>
       </c>
       <c r="G305" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="H305" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I305" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J305" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K305" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L305" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="M305" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N305" t="s">
         <v>1633</v>
@@ -18681,34 +18681,34 @@
         <v>1128</v>
       </c>
       <c r="D306" t="s">
-        <v>1336</v>
+        <v>1308</v>
       </c>
       <c r="E306" t="s">
-        <v>1531</v>
+        <v>1503</v>
       </c>
       <c r="F306" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G306" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="H306" t="s">
         <v>1626</v>
       </c>
       <c r="I306" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J306" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="K306" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L306" t="s">
         <v>1631</v>
       </c>
       <c r="M306" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="N306" t="s">
         <v>1633</v>
@@ -18725,31 +18725,31 @@
         <v>1129</v>
       </c>
       <c r="D307" t="s">
-        <v>1308</v>
+        <v>1394</v>
       </c>
       <c r="E307" t="s">
-        <v>1503</v>
+        <v>1589</v>
       </c>
       <c r="F307" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G307" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H307" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I307" t="s">
         <v>1632</v>
       </c>
       <c r="J307" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="K307" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L307" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M307" t="s">
         <v>1627</v>
@@ -18769,10 +18769,10 @@
         <v>1130</v>
       </c>
       <c r="D308" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="E308" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="F308" t="s">
         <v>1624</v>
@@ -18787,16 +18787,16 @@
         <v>1632</v>
       </c>
       <c r="J308" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="K308" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L308" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M308" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="N308" t="s">
         <v>1633</v>
@@ -18813,13 +18813,13 @@
         <v>1131</v>
       </c>
       <c r="D309" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="E309" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="F309" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="G309" t="s">
         <v>1626</v>
@@ -18831,13 +18831,13 @@
         <v>1632</v>
       </c>
       <c r="J309" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K309" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L309" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="M309" t="s">
         <v>1628</v>
@@ -18857,34 +18857,34 @@
         <v>1132</v>
       </c>
       <c r="D310" t="s">
-        <v>1396</v>
+        <v>1375</v>
       </c>
       <c r="E310" t="s">
-        <v>1591</v>
+        <v>1570</v>
       </c>
       <c r="F310" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G310" t="s">
         <v>1626</v>
       </c>
       <c r="H310" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I310" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J310" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="K310" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L310" t="s">
         <v>1627</v>
       </c>
       <c r="M310" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N310" t="s">
         <v>1633</v>
@@ -18901,25 +18901,25 @@
         <v>1133</v>
       </c>
       <c r="D311" t="s">
-        <v>1375</v>
+        <v>1251</v>
       </c>
       <c r="E311" t="s">
-        <v>1570</v>
+        <v>1446</v>
       </c>
       <c r="F311" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="G311" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H311" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I311" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J311" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="K311" t="s">
         <v>1630</v>
@@ -18945,31 +18945,31 @@
         <v>1134</v>
       </c>
       <c r="D312" t="s">
-        <v>1251</v>
+        <v>1316</v>
       </c>
       <c r="E312" t="s">
-        <v>1446</v>
+        <v>1511</v>
       </c>
       <c r="F312" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="G312" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H312" t="s">
         <v>1629</v>
       </c>
       <c r="I312" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="J312" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="K312" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L312" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="M312" t="s">
         <v>1631</v>
@@ -18989,34 +18989,34 @@
         <v>1135</v>
       </c>
       <c r="D313" t="s">
-        <v>1316</v>
+        <v>1397</v>
       </c>
       <c r="E313" t="s">
-        <v>1511</v>
+        <v>1592</v>
       </c>
       <c r="F313" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G313" t="s">
         <v>1626</v>
       </c>
       <c r="H313" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I313" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J313" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="K313" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L313" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="M313" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N313" t="s">
         <v>1633</v>
@@ -19033,34 +19033,34 @@
         <v>1136</v>
       </c>
       <c r="D314" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="E314" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="F314" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G314" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H314" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="I314" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="J314" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K314" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="L314" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="M314" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N314" t="s">
         <v>1633</v>
@@ -19077,34 +19077,34 @@
         <v>1137</v>
       </c>
       <c r="D315" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="E315" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="F315" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G315" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="H315" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="I315" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="J315" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K315" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="L315" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="M315" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N315" t="s">
         <v>1633</v>
@@ -19121,34 +19121,34 @@
         <v>1138</v>
       </c>
       <c r="D316" t="s">
-        <v>1399</v>
+        <v>1279</v>
       </c>
       <c r="E316" t="s">
-        <v>1594</v>
+        <v>1474</v>
       </c>
       <c r="F316" t="s">
         <v>1622</v>
       </c>
       <c r="G316" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="H316" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="I316" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="J316" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="K316" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="L316" t="s">
         <v>1631</v>
       </c>
       <c r="M316" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N316" t="s">
         <v>1633</v>
@@ -19165,10 +19165,10 @@
         <v>1139</v>
       </c>
       <c r="D317" t="s">
-        <v>1279</v>
+        <v>1400</v>
       </c>
       <c r="E317" t="s">
-        <v>1474</v>
+        <v>1595</v>
       </c>
       <c r="F317" t="s">
         <v>1622</v>
@@ -19177,13 +19177,13 @@
         <v>1627</v>
       </c>
       <c r="H317" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="I317" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="J317" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="K317" t="s">
         <v>1632</v>
@@ -19192,7 +19192,7 @@
         <v>1631</v>
       </c>
       <c r="M317" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="N317" t="s">
         <v>1633</v>
@@ -19209,34 +19209,34 @@
         <v>1140</v>
       </c>
       <c r="D318" t="s">
-        <v>1400</v>
+        <v>1246</v>
       </c>
       <c r="E318" t="s">
-        <v>1595</v>
+        <v>1441</v>
       </c>
       <c r="F318" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G318" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H318" t="s">
         <v>1626</v>
       </c>
       <c r="I318" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="J318" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="K318" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="L318" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="M318" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="N318" t="s">
         <v>1633</v>
@@ -19253,34 +19253,34 @@
         <v>1141</v>
       </c>
       <c r="D319" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="E319" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="F319" t="s">
         <v>1620</v>
       </c>
       <c r="G319" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H319" t="s">
         <v>1626</v>
       </c>
       <c r="I319" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="J319" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="K319" t="s">
         <v>1630</v>
       </c>
       <c r="L319" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="M319" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N319" t="s">
         <v>1633</v>
@@ -19297,34 +19297,34 @@
         <v>1142</v>
       </c>
       <c r="D320" t="s">
-        <v>1244</v>
+        <v>1374</v>
       </c>
       <c r="E320" t="s">
-        <v>1439</v>
+        <v>1569</v>
       </c>
       <c r="F320" t="s">
         <v>1620</v>
       </c>
       <c r="G320" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H320" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="I320" t="s">
         <v>1629</v>
       </c>
       <c r="J320" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="K320" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L320" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M320" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="N320" t="s">
         <v>1633</v>
@@ -19341,34 +19341,34 @@
         <v>1143</v>
       </c>
       <c r="D321" t="s">
-        <v>1374</v>
+        <v>1401</v>
       </c>
       <c r="E321" t="s">
-        <v>1569</v>
+        <v>1596</v>
       </c>
       <c r="F321" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G321" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="H321" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="I321" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="J321" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="K321" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L321" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M321" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="N321" t="s">
         <v>1633</v>
@@ -19385,34 +19385,34 @@
         <v>1144</v>
       </c>
       <c r="D322" t="s">
-        <v>1401</v>
+        <v>1308</v>
       </c>
       <c r="E322" t="s">
-        <v>1596</v>
+        <v>1503</v>
       </c>
       <c r="F322" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G322" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H322" t="s">
         <v>1626</v>
       </c>
       <c r="I322" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="J322" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="K322" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="L322" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="M322" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N322" t="s">
         <v>1633</v>
@@ -19429,28 +19429,28 @@
         <v>1145</v>
       </c>
       <c r="D323" t="s">
-        <v>1308</v>
+        <v>1277</v>
       </c>
       <c r="E323" t="s">
-        <v>1503</v>
+        <v>1472</v>
       </c>
       <c r="F323" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G323" t="s">
         <v>1630</v>
       </c>
       <c r="H323" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I323" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J323" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="K323" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="L323" t="s">
         <v>1627</v>
@@ -19473,31 +19473,31 @@
         <v>1146</v>
       </c>
       <c r="D324" t="s">
-        <v>1277</v>
+        <v>1348</v>
       </c>
       <c r="E324" t="s">
-        <v>1472</v>
+        <v>1543</v>
       </c>
       <c r="F324" t="s">
         <v>1621</v>
       </c>
       <c r="G324" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="H324" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I324" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J324" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="K324" t="s">
         <v>1628</v>
       </c>
       <c r="L324" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="M324" t="s">
         <v>1631</v>
@@ -19517,31 +19517,31 @@
         <v>1147</v>
       </c>
       <c r="D325" t="s">
-        <v>1348</v>
+        <v>1402</v>
       </c>
       <c r="E325" t="s">
-        <v>1543</v>
+        <v>1597</v>
       </c>
       <c r="F325" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="G325" t="s">
         <v>1626</v>
       </c>
       <c r="H325" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I325" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J325" t="s">
         <v>1627</v>
       </c>
       <c r="K325" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L325" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="M325" t="s">
         <v>1631</v>
@@ -19561,13 +19561,13 @@
         <v>1148</v>
       </c>
       <c r="D326" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="E326" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="F326" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="G326" t="s">
         <v>1626</v>
@@ -19579,16 +19579,16 @@
         <v>1632</v>
       </c>
       <c r="J326" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K326" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L326" t="s">
         <v>1628</v>
       </c>
       <c r="M326" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="N326" t="s">
         <v>1633</v>
@@ -19605,13 +19605,13 @@
         <v>1149</v>
       </c>
       <c r="D327" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="E327" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="F327" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="G327" t="s">
         <v>1626</v>
@@ -19623,16 +19623,16 @@
         <v>1632</v>
       </c>
       <c r="J327" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="K327" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L327" t="s">
         <v>1628</v>
       </c>
       <c r="M327" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="N327" t="s">
         <v>1633</v>
@@ -19649,31 +19649,31 @@
         <v>1150</v>
       </c>
       <c r="D328" t="s">
-        <v>1404</v>
+        <v>1275</v>
       </c>
       <c r="E328" t="s">
-        <v>1599</v>
+        <v>1470</v>
       </c>
       <c r="F328" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="G328" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="H328" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I328" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="J328" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="K328" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="L328" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="M328" t="s">
         <v>1631</v>
@@ -19693,34 +19693,34 @@
         <v>1151</v>
       </c>
       <c r="D329" t="s">
-        <v>1275</v>
+        <v>1405</v>
       </c>
       <c r="E329" t="s">
-        <v>1470</v>
+        <v>1600</v>
       </c>
       <c r="F329" t="s">
         <v>1621</v>
       </c>
       <c r="G329" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H329" t="s">
         <v>1627</v>
       </c>
       <c r="I329" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J329" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="K329" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="L329" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="M329" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="N329" t="s">
         <v>1633</v>
@@ -19737,13 +19737,13 @@
         <v>1152</v>
       </c>
       <c r="D330" t="s">
-        <v>1405</v>
+        <v>1253</v>
       </c>
       <c r="E330" t="s">
-        <v>1600</v>
+        <v>1448</v>
       </c>
       <c r="F330" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G330" t="s">
         <v>1626</v>
@@ -19752,16 +19752,16 @@
         <v>1627</v>
       </c>
       <c r="I330" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="J330" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K330" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="L330" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="M330" t="s">
         <v>1630</v>
@@ -19781,10 +19781,10 @@
         <v>1153</v>
       </c>
       <c r="D331" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E331" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F331" t="s">
         <v>1620</v>
@@ -19825,13 +19825,13 @@
         <v>1154</v>
       </c>
       <c r="D332" t="s">
-        <v>1255</v>
+        <v>1400</v>
       </c>
       <c r="E332" t="s">
-        <v>1450</v>
+        <v>1595</v>
       </c>
       <c r="F332" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="G332" t="s">
         <v>1626</v>
@@ -19840,19 +19840,19 @@
         <v>1627</v>
       </c>
       <c r="I332" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="J332" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="K332" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="L332" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="M332" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="N332" t="s">
         <v>1633</v>
@@ -19869,13 +19869,13 @@
         <v>1155</v>
       </c>
       <c r="D333" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="E333" t="s">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="F333" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="G333" t="s">
         <v>1626</v>
@@ -19884,19 +19884,19 @@
         <v>1627</v>
       </c>
       <c r="I333" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="J333" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="K333" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="L333" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="M333" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="N333" t="s">
         <v>1633</v>
@@ -19913,10 +19913,10 @@
         <v>1156</v>
       </c>
       <c r="D334" t="s">
-        <v>1406</v>
+        <v>1361</v>
       </c>
       <c r="E334" t="s">
-        <v>1601</v>
+        <v>1556</v>
       </c>
       <c r="F334" t="s">
         <v>1622</v>
@@ -19925,22 +19925,22 @@
         <v>1626</v>
       </c>
       <c r="H334" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="I334" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="J334" t="s">
         <v>1628</v>
       </c>
       <c r="K334" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="L334" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="M334" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="N334" t="s">
         <v>1633</v>
@@ -19957,13 +19957,13 @@
         <v>1157</v>
       </c>
       <c r="D335" t="s">
-        <v>1361</v>
+        <v>1322</v>
       </c>
       <c r="E335" t="s">
-        <v>1556</v>
+        <v>1517</v>
       </c>
       <c r="F335" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G335" t="s">
         <v>1626</v>
@@ -19972,19 +19972,19 @@
         <v>1629</v>
       </c>
       <c r="I335" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="J335" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="K335" t="s">
         <v>1627</v>
       </c>
       <c r="L335" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M335" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N335" t="s">
         <v>1633</v>
@@ -20001,34 +20001,34 @@
         <v>1158</v>
       </c>
       <c r="D336" t="s">
-        <v>1322</v>
+        <v>1303</v>
       </c>
       <c r="E336" t="s">
-        <v>1517</v>
+        <v>1498</v>
       </c>
       <c r="F336" t="s">
         <v>1621</v>
       </c>
       <c r="G336" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H336" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I336" t="s">
         <v>1630</v>
       </c>
       <c r="J336" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="K336" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="L336" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="M336" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N336" t="s">
         <v>1633</v>
@@ -20045,34 +20045,34 @@
         <v>1159</v>
       </c>
       <c r="D337" t="s">
-        <v>1303</v>
+        <v>1266</v>
       </c>
       <c r="E337" t="s">
-        <v>1498</v>
+        <v>1461</v>
       </c>
       <c r="F337" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G337" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H337" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="I337" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="J337" t="s">
         <v>1627</v>
       </c>
       <c r="K337" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="L337" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M337" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="N337" t="s">
         <v>1633</v>
@@ -20089,34 +20089,34 @@
         <v>1160</v>
       </c>
       <c r="D338" t="s">
-        <v>1266</v>
+        <v>1378</v>
       </c>
       <c r="E338" t="s">
-        <v>1461</v>
+        <v>1573</v>
       </c>
       <c r="F338" t="s">
         <v>1620</v>
       </c>
       <c r="G338" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H338" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="I338" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="J338" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K338" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="L338" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="M338" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="N338" t="s">
         <v>1633</v>
@@ -20133,10 +20133,10 @@
         <v>1161</v>
       </c>
       <c r="D339" t="s">
-        <v>1378</v>
+        <v>1325</v>
       </c>
       <c r="E339" t="s">
-        <v>1573</v>
+        <v>1520</v>
       </c>
       <c r="F339" t="s">
         <v>1620</v>
@@ -20148,16 +20148,16 @@
         <v>1629</v>
       </c>
       <c r="I339" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="J339" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="K339" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L339" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="M339" t="s">
         <v>1627</v>
@@ -20177,34 +20177,34 @@
         <v>1162</v>
       </c>
       <c r="D340" t="s">
-        <v>1325</v>
+        <v>1310</v>
       </c>
       <c r="E340" t="s">
-        <v>1520</v>
+        <v>1505</v>
       </c>
       <c r="F340" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G340" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H340" t="s">
         <v>1629</v>
       </c>
       <c r="I340" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="J340" t="s">
         <v>1632</v>
       </c>
       <c r="K340" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="L340" t="s">
         <v>1628</v>
       </c>
       <c r="M340" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="N340" t="s">
         <v>1633</v>
@@ -20221,34 +20221,34 @@
         <v>1163</v>
       </c>
       <c r="D341" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="E341" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
       <c r="F341" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G341" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H341" t="s">
         <v>1629</v>
       </c>
       <c r="I341" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="J341" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="K341" t="s">
         <v>1630</v>
       </c>
       <c r="L341" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="M341" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N341" t="s">
         <v>1633</v>
@@ -20265,34 +20265,34 @@
         <v>1164</v>
       </c>
       <c r="D342" t="s">
-        <v>1302</v>
+        <v>1253</v>
       </c>
       <c r="E342" t="s">
-        <v>1497</v>
+        <v>1448</v>
       </c>
       <c r="F342" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G342" t="s">
         <v>1626</v>
       </c>
       <c r="H342" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I342" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="J342" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="K342" t="s">
         <v>1630</v>
       </c>
       <c r="L342" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="M342" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N342" t="s">
         <v>1633</v>
@@ -20309,34 +20309,34 @@
         <v>1165</v>
       </c>
       <c r="D343" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="E343" t="s">
-        <v>1448</v>
+        <v>1464</v>
       </c>
       <c r="F343" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G343" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="H343" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="I343" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="J343" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="K343" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="L343" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="M343" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="N343" t="s">
         <v>1633</v>
@@ -20353,34 +20353,34 @@
         <v>1166</v>
       </c>
       <c r="D344" t="s">
-        <v>1269</v>
+        <v>1312</v>
       </c>
       <c r="E344" t="s">
-        <v>1464</v>
+        <v>1507</v>
       </c>
       <c r="F344" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G344" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="H344" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I344" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="J344" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="K344" t="s">
         <v>1628</v>
       </c>
       <c r="L344" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M344" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="N344" t="s">
         <v>1633</v>
@@ -20397,34 +20397,34 @@
         <v>1167</v>
       </c>
       <c r="D345" t="s">
-        <v>1312</v>
+        <v>1250</v>
       </c>
       <c r="E345" t="s">
-        <v>1507</v>
+        <v>1445</v>
       </c>
       <c r="F345" t="s">
         <v>1620</v>
       </c>
       <c r="G345" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H345" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="I345" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="J345" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="K345" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="L345" t="s">
         <v>1630</v>
       </c>
       <c r="M345" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N345" t="s">
         <v>1633</v>
@@ -20441,34 +20441,34 @@
         <v>1168</v>
       </c>
       <c r="D346" t="s">
-        <v>1250</v>
+        <v>1405</v>
       </c>
       <c r="E346" t="s">
-        <v>1445</v>
+        <v>1600</v>
       </c>
       <c r="F346" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G346" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="H346" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I346" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="J346" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="K346" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="L346" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M346" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="N346" t="s">
         <v>1633</v>
@@ -20485,34 +20485,34 @@
         <v>1169</v>
       </c>
       <c r="D347" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="E347" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="F347" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G347" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="H347" t="s">
         <v>1629</v>
       </c>
       <c r="I347" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="J347" t="s">
         <v>1628</v>
       </c>
       <c r="K347" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="L347" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M347" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="N347" t="s">
         <v>1633</v>
@@ -20529,31 +20529,31 @@
         <v>1170</v>
       </c>
       <c r="D348" t="s">
-        <v>1407</v>
+        <v>1265</v>
       </c>
       <c r="E348" t="s">
-        <v>1602</v>
+        <v>1460</v>
       </c>
       <c r="F348" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G348" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H348" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I348" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="J348" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="K348" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L348" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="M348" t="s">
         <v>1631</v>
@@ -20573,31 +20573,31 @@
         <v>1171</v>
       </c>
       <c r="D349" t="s">
-        <v>1265</v>
+        <v>1276</v>
       </c>
       <c r="E349" t="s">
-        <v>1460</v>
+        <v>1471</v>
       </c>
       <c r="F349" t="s">
         <v>1621</v>
       </c>
       <c r="G349" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H349" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I349" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="J349" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K349" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="L349" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="M349" t="s">
         <v>1631</v>
@@ -20617,34 +20617,34 @@
         <v>1172</v>
       </c>
       <c r="D350" t="s">
-        <v>1276</v>
+        <v>1357</v>
       </c>
       <c r="E350" t="s">
-        <v>1471</v>
+        <v>1552</v>
       </c>
       <c r="F350" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G350" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H350" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="I350" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="J350" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="K350" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="L350" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="M350" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="N350" t="s">
         <v>1633</v>
@@ -20661,10 +20661,10 @@
         <v>1173</v>
       </c>
       <c r="D351" t="s">
-        <v>1357</v>
+        <v>1408</v>
       </c>
       <c r="E351" t="s">
-        <v>1552</v>
+        <v>1603</v>
       </c>
       <c r="F351" t="s">
         <v>1620</v>
@@ -20705,34 +20705,34 @@
         <v>1174</v>
       </c>
       <c r="D352" t="s">
-        <v>1408</v>
+        <v>1249</v>
       </c>
       <c r="E352" t="s">
-        <v>1603</v>
+        <v>1444</v>
       </c>
       <c r="F352" t="s">
         <v>1620</v>
       </c>
       <c r="G352" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H352" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="I352" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="J352" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="K352" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="L352" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="M352" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="N352" t="s">
         <v>1633</v>
@@ -20749,31 +20749,31 @@
         <v>1175</v>
       </c>
       <c r="D353" t="s">
-        <v>1249</v>
+        <v>1261</v>
       </c>
       <c r="E353" t="s">
-        <v>1444</v>
+        <v>1456</v>
       </c>
       <c r="F353" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="G353" t="s">
         <v>1626</v>
       </c>
       <c r="H353" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="I353" t="s">
         <v>1632</v>
       </c>
       <c r="J353" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="K353" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="L353" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="M353" t="s">
         <v>1631</v>
@@ -20793,34 +20793,34 @@
         <v>1176</v>
       </c>
       <c r="D354" t="s">
-        <v>1261</v>
+        <v>1409</v>
       </c>
       <c r="E354" t="s">
-        <v>1456</v>
+        <v>1604</v>
       </c>
       <c r="F354" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="G354" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H354" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="I354" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="J354" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K354" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="L354" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="M354" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="N354" t="s">
         <v>1633</v>
@@ -20837,34 +20837,34 @@
         <v>1177</v>
       </c>
       <c r="D355" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E355" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="F355" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="G355" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H355" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="I355" t="s">
         <v>1628</v>
       </c>
       <c r="J355" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="K355" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="L355" t="s">
         <v>1630</v>
       </c>
       <c r="M355" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="N355" t="s">
         <v>1633</v>
@@ -20881,34 +20881,34 @@
         <v>1178</v>
       </c>
       <c r="D356" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E356" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="F356" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="G356" t="s">
         <v>1626</v>
       </c>
       <c r="H356" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I356" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="J356" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="K356" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L356" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M356" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N356" t="s">
         <v>1633</v>
@@ -20925,13 +20925,13 @@
         <v>1179</v>
       </c>
       <c r="D357" t="s">
-        <v>1411</v>
+        <v>1259</v>
       </c>
       <c r="E357" t="s">
-        <v>1606</v>
+        <v>1454</v>
       </c>
       <c r="F357" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G357" t="s">
         <v>1626</v>
@@ -20946,13 +20946,13 @@
         <v>1627</v>
       </c>
       <c r="K357" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="L357" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M357" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N357" t="s">
         <v>1633</v>
@@ -20969,13 +20969,13 @@
         <v>1180</v>
       </c>
       <c r="D358" t="s">
-        <v>1259</v>
+        <v>1241</v>
       </c>
       <c r="E358" t="s">
-        <v>1454</v>
+        <v>1436</v>
       </c>
       <c r="F358" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G358" t="s">
         <v>1626</v>
@@ -20987,16 +20987,16 @@
         <v>1632</v>
       </c>
       <c r="J358" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K358" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L358" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M358" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="N358" t="s">
         <v>1633</v>
@@ -21013,22 +21013,22 @@
         <v>1181</v>
       </c>
       <c r="D359" t="s">
-        <v>1241</v>
+        <v>1296</v>
       </c>
       <c r="E359" t="s">
-        <v>1436</v>
+        <v>1491</v>
       </c>
       <c r="F359" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="G359" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H359" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="I359" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="J359" t="s">
         <v>1628</v>
@@ -21037,10 +21037,10 @@
         <v>1630</v>
       </c>
       <c r="L359" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="M359" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="N359" t="s">
         <v>1633</v>
@@ -21057,31 +21057,31 @@
         <v>1182</v>
       </c>
       <c r="D360" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="E360" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="F360" t="s">
         <v>1621</v>
       </c>
       <c r="G360" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H360" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="I360" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="J360" t="s">
         <v>1628</v>
       </c>
       <c r="K360" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="L360" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="M360" t="s">
         <v>1632</v>
@@ -21101,34 +21101,34 @@
         <v>1183</v>
       </c>
       <c r="D361" t="s">
-        <v>1302</v>
+        <v>1245</v>
       </c>
       <c r="E361" t="s">
-        <v>1497</v>
+        <v>1440</v>
       </c>
       <c r="F361" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="G361" t="s">
         <v>1626</v>
       </c>
       <c r="H361" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="I361" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J361" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="K361" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="L361" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M361" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="N361" t="s">
         <v>1633</v>
@@ -21145,34 +21145,34 @@
         <v>1184</v>
       </c>
       <c r="D362" t="s">
-        <v>1245</v>
+        <v>1267</v>
       </c>
       <c r="E362" t="s">
-        <v>1440</v>
+        <v>1462</v>
       </c>
       <c r="F362" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G362" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H362" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="I362" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J362" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="K362" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L362" t="s">
         <v>1631</v>
       </c>
       <c r="M362" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="N362" t="s">
         <v>1633</v>
@@ -21189,34 +21189,34 @@
         <v>1185</v>
       </c>
       <c r="D363" t="s">
-        <v>1267</v>
+        <v>1366</v>
       </c>
       <c r="E363" t="s">
-        <v>1462</v>
+        <v>1561</v>
       </c>
       <c r="F363" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="G363" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H363" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="I363" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J363" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="K363" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L363" t="s">
         <v>1631</v>
       </c>
       <c r="M363" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N363" t="s">
         <v>1633</v>
@@ -21233,10 +21233,10 @@
         <v>1186</v>
       </c>
       <c r="D364" t="s">
-        <v>1366</v>
+        <v>1241</v>
       </c>
       <c r="E364" t="s">
-        <v>1561</v>
+        <v>1436</v>
       </c>
       <c r="F364" t="s">
         <v>1621</v>
@@ -21245,13 +21245,13 @@
         <v>1626</v>
       </c>
       <c r="H364" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I364" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J364" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K364" t="s">
         <v>1627</v>
@@ -21260,7 +21260,7 @@
         <v>1631</v>
       </c>
       <c r="M364" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="N364" t="s">
         <v>1633</v>
@@ -21277,28 +21277,28 @@
         <v>1187</v>
       </c>
       <c r="D365" t="s">
-        <v>1241</v>
+        <v>1407</v>
       </c>
       <c r="E365" t="s">
-        <v>1436</v>
+        <v>1602</v>
       </c>
       <c r="F365" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="G365" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H365" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I365" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="J365" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K365" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L365" t="s">
         <v>1631</v>
@@ -21321,31 +21321,31 @@
         <v>1188</v>
       </c>
       <c r="D366" t="s">
-        <v>1407</v>
+        <v>1380</v>
       </c>
       <c r="E366" t="s">
-        <v>1602</v>
+        <v>1575</v>
       </c>
       <c r="F366" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G366" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H366" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="I366" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="J366" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="K366" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="L366" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M366" t="s">
         <v>1628</v>
@@ -21365,25 +21365,25 @@
         <v>1189</v>
       </c>
       <c r="D367" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E367" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="F367" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="G367" t="s">
         <v>1626</v>
       </c>
       <c r="H367" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="I367" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="J367" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="K367" t="s">
         <v>1627</v>
@@ -21392,7 +21392,7 @@
         <v>1630</v>
       </c>
       <c r="M367" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="N367" t="s">
         <v>1633</v>
@@ -21409,34 +21409,34 @@
         <v>1190</v>
       </c>
       <c r="D368" t="s">
-        <v>1381</v>
+        <v>1355</v>
       </c>
       <c r="E368" t="s">
-        <v>1576</v>
+        <v>1550</v>
       </c>
       <c r="F368" t="s">
         <v>1620</v>
       </c>
       <c r="G368" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="H368" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I368" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="J368" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K368" t="s">
-        <v>1627</v>
+        <v>1632</v>
       </c>
       <c r="L368" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="M368" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="N368" t="s">
         <v>1633</v>
@@ -21453,34 +21453,34 @@
         <v>1191</v>
       </c>
       <c r="D369" t="s">
-        <v>1355</v>
+        <v>1411</v>
       </c>
       <c r="E369" t="s">
-        <v>1550</v>
+        <v>1606</v>
       </c>
       <c r="F369" t="s">
         <v>1620</v>
       </c>
       <c r="G369" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H369" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="I369" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="J369" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="K369" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="L369" t="s">
         <v>1631</v>
       </c>
       <c r="M369" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="N369" t="s">
         <v>1633</v>
@@ -21497,34 +21497,34 @@
         <v>1192</v>
       </c>
       <c r="D370" t="s">
-        <v>1411</v>
+        <v>1264</v>
       </c>
       <c r="E370" t="s">
-        <v>1606</v>
+        <v>1459</v>
       </c>
       <c r="F370" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="G370" t="s">
         <v>1626</v>
       </c>
       <c r="H370" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="I370" t="s">
         <v>1632</v>
       </c>
       <c r="J370" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="K370" t="s">
-        <v>1629</v>
+        <v>